--- a/api/2/clv2/xlsx/pt/HumanitarianPlan.xlsx
+++ b/api/2/clv2/xlsx/pt/HumanitarianPlan.xlsx
@@ -22,15 +22,15 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:plan-start-date</t>
+  </si>
+  <si>
+    <t>codeforiati:plan-end-date</t>
+  </si>
+  <si>
     <t>codeforiati:plan-year</t>
   </si>
   <si>
-    <t>codeforiati:plan-end-date</t>
-  </si>
-  <si>
-    <t>codeforiati:plan-start-date</t>
-  </si>
-  <si>
     <t>codeforiati:plan-type</t>
   </si>
   <si>
@@ -40,15 +40,15 @@
     <t>active</t>
   </si>
   <si>
+    <t>2025-01-01</t>
+  </si>
+  <si>
+    <t>2025-12-31</t>
+  </si>
+  <si>
     <t>2025</t>
   </si>
   <si>
-    <t>2025-12-31</t>
-  </si>
-  <si>
-    <t>2025-01-01</t>
-  </si>
-  <si>
     <t>Humanitarian needs and response plan</t>
   </si>
   <si>
@@ -217,15 +217,15 @@
     <t>HAFG24</t>
   </si>
   <si>
+    <t>2024-01-01</t>
+  </si>
+  <si>
+    <t>2024-12-31</t>
+  </si>
+  <si>
     <t>2024</t>
   </si>
   <si>
-    <t>2024-12-31</t>
-  </si>
-  <si>
-    <t>2024-01-01</t>
-  </si>
-  <si>
     <t>RAFG_RRP24</t>
   </si>
   <si>
@@ -421,15 +421,15 @@
     <t>HAFG23</t>
   </si>
   <si>
+    <t>2023-01-01</t>
+  </si>
+  <si>
+    <t>2023-12-31</t>
+  </si>
+  <si>
     <t>2023</t>
   </si>
   <si>
-    <t>2023-12-31</t>
-  </si>
-  <si>
-    <t>2023-01-01</t>
-  </si>
-  <si>
     <t>RAFG23</t>
   </si>
   <si>
@@ -493,21 +493,21 @@
     <t>OMNG2223</t>
   </si>
   <si>
+    <t>2022-12-01</t>
+  </si>
+  <si>
     <t>2023-05-31</t>
   </si>
   <si>
-    <t>2022-12-01</t>
-  </si>
-  <si>
     <t>OMOZ23</t>
   </si>
   <si>
+    <t>2023-03-01</t>
+  </si>
+  <si>
     <t>2023-09-30</t>
   </si>
   <si>
-    <t>2023-03-01</t>
-  </si>
-  <si>
     <t>HMOZ23</t>
   </si>
   <si>
@@ -553,12 +553,12 @@
     <t>RRSDN23</t>
   </si>
   <si>
+    <t>2023-05-01</t>
+  </si>
+  <si>
     <t>2023-10-31</t>
   </si>
   <si>
-    <t>2023-05-01</t>
-  </si>
-  <si>
     <t>HSDN23</t>
   </si>
   <si>
@@ -601,15 +601,15 @@
     <t>HAFG22</t>
   </si>
   <si>
+    <t>2022-01-01</t>
+  </si>
+  <si>
+    <t>2022-12-31</t>
+  </si>
+  <si>
     <t>2022</t>
   </si>
   <si>
-    <t>2022-12-31</t>
-  </si>
-  <si>
-    <t>2022-01-01</t>
-  </si>
-  <si>
     <t>RAFG22</t>
   </si>
   <si>
@@ -631,12 +631,12 @@
     <t>OCUB2223</t>
   </si>
   <si>
+    <t>2022-10-20</t>
+  </si>
+  <si>
     <t>2023-03-31</t>
   </si>
   <si>
-    <t>2022-10-20</t>
-  </si>
-  <si>
     <t>RDRCRRP22</t>
   </si>
   <si>
@@ -652,12 +652,12 @@
     <t>FHTI2223</t>
   </si>
   <si>
+    <t>2022-10-16</t>
+  </si>
+  <si>
     <t>2023-04-15</t>
   </si>
   <si>
-    <t>2022-10-16</t>
-  </si>
-  <si>
     <t>FHTI22</t>
   </si>
   <si>
@@ -688,24 +688,24 @@
     <t>FMWI22</t>
   </si>
   <si>
+    <t>2022-02-26</t>
+  </si>
+  <si>
     <t>2022-05-31</t>
   </si>
   <si>
-    <t>2022-02-26</t>
-  </si>
-  <si>
     <t>HMLI22</t>
   </si>
   <si>
     <t>FMOZ22</t>
   </si>
   <si>
+    <t>2022-04-01</t>
+  </si>
+  <si>
     <t>2022-09-30</t>
   </si>
   <si>
-    <t>2022-04-01</t>
-  </si>
-  <si>
     <t>HMOZ22</t>
   </si>
   <si>
@@ -736,12 +736,12 @@
     <t>OPHL2122</t>
   </si>
   <si>
+    <t>2021-12-24</t>
+  </si>
+  <si>
     <t>2022-06-30</t>
   </si>
   <si>
-    <t>2021-12-24</t>
-  </si>
-  <si>
     <t>RREG22</t>
   </si>
   <si>
@@ -805,15 +805,15 @@
     <t>FAFG21</t>
   </si>
   <si>
+    <t>2021-09-01</t>
+  </si>
+  <si>
+    <t>2021-12-31</t>
+  </si>
+  <si>
     <t>2021</t>
   </si>
   <si>
-    <t>2021-12-31</t>
-  </si>
-  <si>
-    <t>2021-09-01</t>
-  </si>
-  <si>
     <t>HAFG21</t>
   </si>
   <si>
@@ -862,12 +862,12 @@
     <t>FPSE21</t>
   </si>
   <si>
+    <t>2021-05-27</t>
+  </si>
+  <si>
     <t>2021-08-27</t>
   </si>
   <si>
-    <t>2021-05-27</t>
-  </si>
-  <si>
     <t>HETH21</t>
   </si>
   <si>
@@ -880,24 +880,24 @@
     <t>FHTI2122</t>
   </si>
   <si>
+    <t>2021-08-16</t>
+  </si>
+  <si>
     <t>2022-02-15</t>
   </si>
   <si>
-    <t>2021-08-16</t>
-  </si>
-  <si>
     <t>HHTI21</t>
   </si>
   <si>
     <t>FHND2021</t>
   </si>
   <si>
+    <t>2020-11-15</t>
+  </si>
+  <si>
     <t>2021-06-30</t>
   </si>
   <si>
-    <t>2020-11-15</t>
-  </si>
-  <si>
     <t>HHND21</t>
   </si>
   <si>
@@ -916,12 +916,12 @@
     <t>OLBN2122</t>
   </si>
   <si>
+    <t>2021-08-03</t>
+  </si>
+  <si>
     <t>2022-07-31</t>
   </si>
   <si>
-    <t>2021-08-03</t>
-  </si>
-  <si>
     <t>HLBY21</t>
   </si>
   <si>
@@ -1009,15 +1009,15 @@
     <t>HAFG20</t>
   </si>
   <si>
+    <t>2020-01-01</t>
+  </si>
+  <si>
+    <t>2020-12-31</t>
+  </si>
+  <si>
     <t>2020</t>
   </si>
   <si>
-    <t>2020-12-31</t>
-  </si>
-  <si>
-    <t>2020-01-01</t>
-  </si>
-  <si>
     <t>OBGD20</t>
   </si>
   <si>
@@ -1081,12 +1081,12 @@
     <t>FDJI1920</t>
   </si>
   <si>
+    <t>2019-12-17</t>
+  </si>
+  <si>
     <t>2020-03-31</t>
   </si>
   <si>
-    <t>2019-12-17</t>
-  </si>
-  <si>
     <t>ODJI20</t>
   </si>
   <si>
@@ -1135,24 +1135,24 @@
     <t>FLBN20</t>
   </si>
   <si>
+    <t>2020-08-05</t>
+  </si>
+  <si>
     <t>2020-11-13</t>
   </si>
   <si>
-    <t>2020-08-05</t>
-  </si>
-  <si>
     <t>OLBN20</t>
   </si>
   <si>
     <t>FLSO1920</t>
   </si>
   <si>
+    <t>2019-11-01</t>
+  </si>
+  <si>
     <t>2020-04-30</t>
   </si>
   <si>
-    <t>2019-11-01</t>
-  </si>
-  <si>
     <t>OLBR20</t>
   </si>
   <si>
@@ -1249,15 +1249,15 @@
     <t>HAFG19</t>
   </si>
   <si>
+    <t>2019-01-01</t>
+  </si>
+  <si>
+    <t>2019-12-31</t>
+  </si>
+  <si>
     <t>2019</t>
   </si>
   <si>
-    <t>2019-12-31</t>
-  </si>
-  <si>
-    <t>2019-01-01</t>
-  </si>
-  <si>
     <t>RBGD19</t>
   </si>
   <si>
@@ -1366,12 +1366,12 @@
     <t>FZWE1920</t>
   </si>
   <si>
+    <t>2019-02-01</t>
+  </si>
+  <si>
     <t>2020-04-29</t>
   </si>
   <si>
-    <t>2019-02-01</t>
-  </si>
-  <si>
     <t>FZWE1820</t>
   </si>
   <si>
@@ -1381,15 +1381,15 @@
     <t>HAFG18</t>
   </si>
   <si>
+    <t>2018-01-01</t>
+  </si>
+  <si>
+    <t>2018-12-31</t>
+  </si>
+  <si>
     <t>2018</t>
   </si>
   <si>
-    <t>2018-12-31</t>
-  </si>
-  <si>
-    <t>2018-01-01</t>
-  </si>
-  <si>
     <t>OBGD18</t>
   </si>
   <si>
@@ -1483,12 +1483,12 @@
     <t>HSYR18</t>
   </si>
   <si>
+    <t>2018-11-30</t>
+  </si>
+  <si>
     <t>2018-12-30</t>
   </si>
   <si>
-    <t>2018-11-30</t>
-  </si>
-  <si>
     <t>RSYR18</t>
   </si>
   <si>
@@ -1507,15 +1507,15 @@
     <t>OEUR17</t>
   </si>
   <si>
+    <t>2017-01-01</t>
+  </si>
+  <si>
+    <t>2017-12-31</t>
+  </si>
+  <si>
     <t>2017</t>
   </si>
   <si>
-    <t>2017-12-31</t>
-  </si>
-  <si>
-    <t>2017-01-01</t>
-  </si>
-  <si>
     <t>HAFG17</t>
   </si>
   <si>
@@ -1558,12 +1558,12 @@
     <t>FDMA17</t>
   </si>
   <si>
+    <t>2017-09-28</t>
+  </si>
+  <si>
     <t>2017-12-29</t>
   </si>
   <si>
-    <t>2017-09-28</t>
-  </si>
-  <si>
     <t>OPRK17</t>
   </si>
   <si>
@@ -1585,24 +1585,24 @@
     <t>FKEN17</t>
   </si>
   <si>
+    <t>2017-02-10</t>
+  </si>
+  <si>
     <t>2017-11-30</t>
   </si>
   <si>
-    <t>2017-02-10</t>
-  </si>
-  <si>
     <t>HLBY17</t>
   </si>
   <si>
     <t>FMDG17</t>
   </si>
   <si>
+    <t>2017-03-20</t>
+  </si>
+  <si>
     <t>2017-06-20</t>
   </si>
   <si>
-    <t>2017-03-20</t>
-  </si>
-  <si>
     <t>HMLI17</t>
   </si>
   <si>
@@ -1612,12 +1612,12 @@
     <t>FMOZ17</t>
   </si>
   <si>
+    <t>2017-02-28</t>
+  </si>
+  <si>
     <t>2017-05-31</t>
   </si>
   <si>
-    <t>2017-02-28</t>
-  </si>
-  <si>
     <t>HMMR17</t>
   </si>
   <si>
@@ -1636,12 +1636,12 @@
     <t>FPER17</t>
   </si>
   <si>
+    <t>2017-04-01</t>
+  </si>
+  <si>
     <t>2017-10-31</t>
   </si>
   <si>
-    <t>2017-04-01</t>
-  </si>
-  <si>
     <t>HCOG17</t>
   </si>
   <si>
@@ -1678,15 +1678,15 @@
     <t>OEUR16</t>
   </si>
   <si>
+    <t>2016-01-01</t>
+  </si>
+  <si>
+    <t>2016-12-31</t>
+  </si>
+  <si>
     <t>2016</t>
   </si>
   <si>
-    <t>2016-12-31</t>
-  </si>
-  <si>
-    <t>2016-01-01</t>
-  </si>
-  <si>
     <t>HAFG16</t>
   </si>
   <si>
@@ -1726,21 +1726,21 @@
     <t>FECU16</t>
   </si>
   <si>
+    <t>2016-04-16</t>
+  </si>
+  <si>
     <t>2016-10-31</t>
   </si>
   <si>
-    <t>2016-04-16</t>
-  </si>
-  <si>
     <t>FFJI16</t>
   </si>
   <si>
+    <t>2016-02-20</t>
+  </si>
+  <si>
     <t>2016-05-30</t>
   </si>
   <si>
-    <t>2016-02-20</t>
-  </si>
-  <si>
     <t>HGMB16</t>
   </si>
   <si>
@@ -1783,12 +1783,12 @@
     <t>FIRQ16</t>
   </si>
   <si>
+    <t>2016-07-20</t>
+  </si>
+  <si>
     <t>2016-10-01</t>
   </si>
   <si>
-    <t>2016-07-20</t>
-  </si>
-  <si>
     <t>HMMR16</t>
   </si>
   <si>
@@ -1831,24 +1831,24 @@
     <t>HZWE1617</t>
   </si>
   <si>
+    <t>2016-04-01</t>
+  </si>
+  <si>
     <t>2017-03-31</t>
   </si>
   <si>
-    <t>2016-04-01</t>
-  </si>
-  <si>
     <t>HAFG15</t>
   </si>
   <si>
+    <t>2015-01-01</t>
+  </si>
+  <si>
+    <t>2015-12-31</t>
+  </si>
+  <si>
     <t>2015</t>
   </si>
   <si>
-    <t>2015-12-31</t>
-  </si>
-  <si>
-    <t>2015-01-01</t>
-  </si>
-  <si>
     <t>Strategic response plan</t>
   </si>
   <si>
@@ -1879,12 +1879,12 @@
     <t>FGTM1415</t>
   </si>
   <si>
+    <t>2014-11-03</t>
+  </si>
+  <si>
     <t>2015-09-30</t>
   </si>
   <si>
-    <t>2014-11-03</t>
-  </si>
-  <si>
     <t>FHTI15</t>
   </si>
   <si>
@@ -1900,24 +1900,24 @@
     <t>FVUT15</t>
   </si>
   <si>
+    <t>2015-03-24</t>
+  </si>
+  <si>
     <t>2015-10-31</t>
   </si>
   <si>
-    <t>2015-03-24</t>
-  </si>
-  <si>
     <t>HIRQ15</t>
   </si>
   <si>
     <t>HLBY1415</t>
   </si>
   <si>
+    <t>2014-10-01</t>
+  </si>
+  <si>
     <t>2015-05-31</t>
   </si>
   <si>
-    <t>2014-10-01</t>
-  </si>
-  <si>
     <t>HMLI15</t>
   </si>
   <si>
@@ -1975,15 +1975,15 @@
     <t>HAFG14</t>
   </si>
   <si>
+    <t>2014-01-01</t>
+  </si>
+  <si>
+    <t>2014-12-31</t>
+  </si>
+  <si>
     <t>2014</t>
   </si>
   <si>
-    <t>2014-12-31</t>
-  </si>
-  <si>
-    <t>2014-01-01</t>
-  </si>
-  <si>
     <t>HBFA1314</t>
   </si>
   <si>
@@ -2059,21 +2059,21 @@
     <t>FPHL1314</t>
   </si>
   <si>
+    <t>2013-10-22</t>
+  </si>
+  <si>
     <t>2014-04-22</t>
   </si>
   <si>
-    <t>2013-10-22</t>
-  </si>
-  <si>
     <t>SPHL1314</t>
   </si>
   <si>
+    <t>2013-11-08</t>
+  </si>
+  <si>
     <t>2014-11-07</t>
   </si>
   <si>
-    <t>2013-11-08</t>
-  </si>
-  <si>
     <t>HPHL1314</t>
   </si>
   <si>
@@ -2083,12 +2083,12 @@
     <t>HPHL1314a</t>
   </si>
   <si>
+    <t>2013-10-01</t>
+  </si>
+  <si>
     <t>2014-08-31</t>
   </si>
   <si>
-    <t>2013-10-01</t>
-  </si>
-  <si>
     <t>SCOD14</t>
   </si>
   <si>
@@ -2149,12 +2149,12 @@
     <t>CAFG13</t>
   </si>
   <si>
+    <t>2013-12-31</t>
+  </si>
+  <si>
     <t>2013</t>
   </si>
   <si>
-    <t>2013-12-31</t>
-  </si>
-  <si>
     <t>Consolidated appeals process</t>
   </si>
   <si>
@@ -2242,15 +2242,15 @@
     <t>CKEN12</t>
   </si>
   <si>
+    <t>2012-01-01</t>
+  </si>
+  <si>
+    <t>2012-12-31</t>
+  </si>
+  <si>
     <t>2012</t>
   </si>
   <si>
-    <t>2012-12-31</t>
-  </si>
-  <si>
-    <t>2012-01-01</t>
-  </si>
-  <si>
     <t>CAFG1112</t>
   </si>
   <si>
@@ -2290,12 +2290,12 @@
     <t>FLSO1213</t>
   </si>
   <si>
+    <t>2012-09-18</t>
+  </si>
+  <si>
     <t>2013-03-25</t>
   </si>
   <si>
-    <t>2012-09-18</t>
-  </si>
-  <si>
     <t>CLBR12</t>
   </si>
   <si>
@@ -2335,12 +2335,12 @@
     <t>CSYR12</t>
   </si>
   <si>
+    <t>2012-06-05</t>
+  </si>
+  <si>
     <t>2012-12-05</t>
   </si>
   <si>
-    <t>2012-06-05</t>
-  </si>
-  <si>
     <t>CYEM12</t>
   </si>
   <si>
@@ -2353,12 +2353,12 @@
     <t>CKEN1113</t>
   </si>
   <si>
+    <t>2011-01-01</t>
+  </si>
+  <si>
     <t>2011</t>
   </si>
   <si>
-    <t>2011-01-01</t>
-  </si>
-  <si>
     <t>CAFG11</t>
   </si>
   <si>
@@ -2383,12 +2383,12 @@
     <t>FSLV1112</t>
   </si>
   <si>
+    <t>2011-10-25</t>
+  </si>
+  <si>
     <t>2012-04-25</t>
   </si>
   <si>
-    <t>2011-10-25</t>
-  </si>
-  <si>
     <t>CHTI1011</t>
   </si>
   <si>
@@ -2407,33 +2407,33 @@
     <t>FNAM11</t>
   </si>
   <si>
+    <t>2011-04-11</t>
+  </si>
+  <si>
     <t>2011-10-11</t>
   </si>
   <si>
-    <t>2011-04-11</t>
-  </si>
-  <si>
     <t>FNIC1112</t>
   </si>
   <si>
+    <t>2011-10-27</t>
+  </si>
+  <si>
     <t>2012-04-26</t>
   </si>
   <si>
-    <t>2011-10-27</t>
-  </si>
-  <si>
     <t>CNER11</t>
   </si>
   <si>
     <t>FPAK1112</t>
   </si>
   <si>
+    <t>2011-09-15</t>
+  </si>
+  <si>
     <t>2012-06-30</t>
   </si>
   <si>
-    <t>2011-09-15</t>
-  </si>
-  <si>
     <t>FXLBYREG11</t>
   </si>
   <si>
@@ -2476,24 +2476,24 @@
     <t>CAFG10</t>
   </si>
   <si>
+    <t>2010-01-01</t>
+  </si>
+  <si>
+    <t>2010-12-31</t>
+  </si>
+  <si>
     <t>2010</t>
   </si>
   <si>
-    <t>2010-12-31</t>
-  </si>
-  <si>
-    <t>2010-01-01</t>
-  </si>
-  <si>
     <t>OBFA1011</t>
   </si>
   <si>
+    <t>2010-08-01</t>
+  </si>
+  <si>
     <t>2011-01-31</t>
   </si>
   <si>
-    <t>2010-08-01</t>
-  </si>
-  <si>
     <t>CCAF10</t>
   </si>
   <si>
@@ -2506,30 +2506,30 @@
     <t>FSLV0910</t>
   </si>
   <si>
+    <t>2009-11-01</t>
+  </si>
+  <si>
     <t>2010-05-31</t>
   </si>
   <si>
-    <t>2009-11-01</t>
-  </si>
-  <si>
     <t>FGTM10</t>
   </si>
   <si>
+    <t>2010-06-10</t>
+  </si>
+  <si>
     <t>2010-12-09</t>
   </si>
   <si>
-    <t>2010-06-10</t>
-  </si>
-  <si>
     <t>CGTM10</t>
   </si>
   <si>
+    <t>2010-02-12</t>
+  </si>
+  <si>
     <t>2010-08-11</t>
   </si>
   <si>
-    <t>2010-02-12</t>
-  </si>
-  <si>
     <t>FHTI10</t>
   </si>
   <si>
@@ -2545,12 +2545,12 @@
     <t>FKGZ1011</t>
   </si>
   <si>
+    <t>2010-06-01</t>
+  </si>
+  <si>
     <t>2011-06-30</t>
   </si>
   <si>
-    <t>2010-06-01</t>
-  </si>
-  <si>
     <t>CMNG1011</t>
   </si>
   <si>
@@ -2608,24 +2608,24 @@
     <t>CAFG09</t>
   </si>
   <si>
+    <t>2009-01-01</t>
+  </si>
+  <si>
+    <t>2009-12-31</t>
+  </si>
+  <si>
     <t>2009</t>
   </si>
   <si>
-    <t>2009-12-31</t>
-  </si>
-  <si>
-    <t>2009-01-01</t>
-  </si>
-  <si>
     <t>FBFA0910</t>
   </si>
   <si>
+    <t>2009-09-10</t>
+  </si>
+  <si>
     <t>2010-03-09</t>
   </si>
   <si>
-    <t>2009-09-10</t>
-  </si>
-  <si>
     <t>CCAF09</t>
   </si>
   <si>
@@ -2662,21 +2662,21 @@
     <t>FMDG09</t>
   </si>
   <si>
+    <t>2009-04-01</t>
+  </si>
+  <si>
     <t>2009-10-31</t>
   </si>
   <si>
-    <t>2009-04-01</t>
-  </si>
-  <si>
     <t>FNAM09</t>
   </si>
   <si>
+    <t>2009-03-20</t>
+  </si>
+  <si>
     <t>2009-09-30</t>
   </si>
   <si>
-    <t>2009-03-20</t>
-  </si>
-  <si>
     <t>ONPL09</t>
   </si>
   <si>
@@ -2689,12 +2689,12 @@
     <t>FPHL0910</t>
   </si>
   <si>
+    <t>2009-10-03</t>
+  </si>
+  <si>
     <t>2010-03-31</t>
   </si>
   <si>
-    <t>2009-10-03</t>
-  </si>
-  <si>
     <t>CSOM09</t>
   </si>
   <si>
@@ -2707,12 +2707,12 @@
     <t>OSYR0910</t>
   </si>
   <si>
+    <t>2009-07-15</t>
+  </si>
+  <si>
     <t>2010-06-14</t>
   </si>
   <si>
-    <t>2009-07-15</t>
-  </si>
-  <si>
     <t>OTJK09</t>
   </si>
   <si>
@@ -2746,24 +2746,24 @@
     <t>OAFG08</t>
   </si>
   <si>
+    <t>2008-02-01</t>
+  </si>
+  <si>
+    <t>2008-06-30</t>
+  </si>
+  <si>
     <t>2008</t>
   </si>
   <si>
-    <t>2008-06-30</t>
-  </si>
-  <si>
-    <t>2008-02-01</t>
-  </si>
-  <si>
     <t>OAFG0809</t>
   </si>
   <si>
+    <t>2008-07-01</t>
+  </si>
+  <si>
     <t>2009-06-30</t>
   </si>
   <si>
-    <t>2008-07-01</t>
-  </si>
-  <si>
     <t>FBOL08</t>
   </si>
   <si>
@@ -2773,12 +2773,12 @@
     <t>CCAF08</t>
   </si>
   <si>
+    <t>2008-01-01</t>
+  </si>
+  <si>
     <t>2008-12-31</t>
   </si>
   <si>
-    <t>2008-01-01</t>
-  </si>
-  <si>
     <t>CTCD08</t>
   </si>
   <si>
@@ -2794,21 +2794,21 @@
     <t>ODJI0809</t>
   </si>
   <si>
+    <t>2008-08-01</t>
+  </si>
+  <si>
     <t>2009-02-28</t>
   </si>
   <si>
-    <t>2008-08-01</t>
-  </si>
-  <si>
     <t>FGEO0809</t>
   </si>
   <si>
+    <t>2008-08-09</t>
+  </si>
+  <si>
     <t>2009-02-09</t>
   </si>
   <si>
-    <t>2008-08-09</t>
-  </si>
-  <si>
     <t>FHTI0809</t>
   </si>
   <si>
@@ -2818,12 +2818,12 @@
     <t>FHND0809</t>
   </si>
   <si>
+    <t>2008-11-01</t>
+  </si>
+  <si>
     <t>2009-04-30</t>
   </si>
   <si>
-    <t>2008-11-01</t>
-  </si>
-  <si>
     <t>CIRQ08</t>
   </si>
   <si>
@@ -2833,12 +2833,12 @@
     <t>FKGZ0809</t>
   </si>
   <si>
+    <t>2008-12-01</t>
+  </si>
+  <si>
     <t>2009-05-31</t>
   </si>
   <si>
-    <t>2008-12-01</t>
-  </si>
-  <si>
     <t>OLAO0809</t>
   </si>
   <si>
@@ -2857,12 +2857,12 @@
     <t>FMMR08</t>
   </si>
   <si>
+    <t>2008-05-01</t>
+  </si>
+  <si>
     <t>2008-11-30</t>
   </si>
   <si>
-    <t>2008-05-01</t>
-  </si>
-  <si>
     <t>ONPL08</t>
   </si>
   <si>
@@ -2914,33 +2914,33 @@
     <t>FBOL07</t>
   </si>
   <si>
+    <t>2007-02-22</t>
+  </si>
+  <si>
+    <t>2007-08-21</t>
+  </si>
+  <si>
     <t>2007</t>
   </si>
   <si>
-    <t>2007-08-21</t>
-  </si>
-  <si>
-    <t>2007-02-22</t>
-  </si>
-  <si>
     <t>FBFA0708</t>
   </si>
   <si>
+    <t>2007-11-01</t>
+  </si>
+  <si>
     <t>2008-01-31</t>
   </si>
   <si>
-    <t>2007-11-01</t>
-  </si>
-  <si>
     <t>CBDI07</t>
   </si>
   <si>
+    <t>2007-01-01</t>
+  </si>
+  <si>
     <t>2007-12-31</t>
   </si>
   <si>
-    <t>2007-01-01</t>
-  </si>
-  <si>
     <t>CCAF07</t>
   </si>
   <si>
@@ -2962,12 +2962,12 @@
     <t>FGHA0708</t>
   </si>
   <si>
+    <t>2007-09-01</t>
+  </si>
+  <si>
     <t>2008-03-31</t>
   </si>
   <si>
-    <t>2007-09-01</t>
-  </si>
-  <si>
     <t>CXGLR07</t>
   </si>
   <si>
@@ -2980,75 +2980,75 @@
     <t>FPRK07</t>
   </si>
   <si>
+    <t>2007-08-28</t>
+  </si>
+  <si>
     <t>2007-11-30</t>
   </si>
   <si>
-    <t>2007-08-28</t>
-  </si>
-  <si>
     <t>OLBN07</t>
   </si>
   <si>
+    <t>2007-06-04</t>
+  </si>
+  <si>
     <t>2007-09-03</t>
   </si>
   <si>
-    <t>2007-06-04</t>
-  </si>
-  <si>
     <t>FLSO0708</t>
   </si>
   <si>
+    <t>2007-07-28</t>
+  </si>
+  <si>
     <t>2008-01-28</t>
   </si>
   <si>
-    <t>2007-07-28</t>
-  </si>
-  <si>
     <t>CLBR07</t>
   </si>
   <si>
     <t>FMDG07</t>
   </si>
   <si>
+    <t>2007-03-15</t>
+  </si>
+  <si>
     <t>2007-09-15</t>
   </si>
   <si>
-    <t>2007-03-15</t>
-  </si>
-  <si>
     <t>FMOZ07</t>
   </si>
   <si>
+    <t>2007-03-01</t>
+  </si>
+  <si>
     <t>2007-06-30</t>
   </si>
   <si>
-    <t>2007-03-01</t>
-  </si>
-  <si>
     <t>ONPL07</t>
   </si>
   <si>
     <t>FNIC0708</t>
   </si>
   <si>
+    <t>2007-09-07</t>
+  </si>
+  <si>
     <t>2008-02-28</t>
   </si>
   <si>
-    <t>2007-09-07</t>
-  </si>
-  <si>
     <t>ORUS07</t>
   </si>
   <si>
     <t>FPAK07</t>
   </si>
   <si>
+    <t>2007-07-15</t>
+  </si>
+  <si>
     <t>2007-10-31</t>
   </si>
   <si>
-    <t>2007-07-15</t>
-  </si>
-  <si>
     <t>FPER0708</t>
   </si>
   <si>
@@ -3082,12 +3082,12 @@
     <t>FSWZ0708</t>
   </si>
   <si>
+    <t>2007-07-20</t>
+  </si>
+  <si>
     <t>2008-01-20</t>
   </si>
   <si>
-    <t>2007-07-20</t>
-  </si>
-  <si>
     <t>CTLS07</t>
   </si>
   <si>
@@ -3112,15 +3112,15 @@
     <t>OAFG06</t>
   </si>
   <si>
+    <t>2006-07-01</t>
+  </si>
+  <si>
+    <t>2006-12-31</t>
+  </si>
+  <si>
     <t>2006</t>
   </si>
   <si>
-    <t>2006-12-31</t>
-  </si>
-  <si>
-    <t>2006-07-01</t>
-  </si>
-  <si>
     <t>CBDI06</t>
   </si>
   <si>
@@ -3145,21 +3145,21 @@
     <t>OETH06a</t>
   </si>
   <si>
+    <t>2006-08-25</t>
+  </si>
+  <si>
     <t>2006-11-25</t>
   </si>
   <si>
-    <t>2006-08-25</t>
-  </si>
-  <si>
     <t>OETH0607</t>
   </si>
   <si>
+    <t>2006-11-23</t>
+  </si>
+  <si>
     <t>2007-01-22</t>
   </si>
   <si>
-    <t>2006-11-23</t>
-  </si>
-  <si>
     <t>CXGLR06</t>
   </si>
   <si>
@@ -3169,12 +3169,12 @@
     <t>FGNB06</t>
   </si>
   <si>
+    <t>2006-05-01</t>
+  </si>
+  <si>
     <t>2006-11-30</t>
   </si>
   <si>
-    <t>2006-05-01</t>
-  </si>
-  <si>
     <t>CXHAF06</t>
   </si>
   <si>
@@ -3184,12 +3184,12 @@
     <t>FKEN0607</t>
   </si>
   <si>
+    <t>2006-10-16</t>
+  </si>
+  <si>
     <t>2007-04-15</t>
   </si>
   <si>
-    <t>2006-10-16</t>
-  </si>
-  <si>
     <t>FKEN06</t>
   </si>
   <si>
@@ -3199,12 +3199,12 @@
     <t>FLBN06</t>
   </si>
   <si>
+    <t>2006-07-24</t>
+  </si>
+  <si>
     <t>2006-10-23</t>
   </si>
   <si>
-    <t>2006-07-24</t>
-  </si>
-  <si>
     <t>CLBR06</t>
   </si>
   <si>
@@ -3232,12 +3232,12 @@
     <t>FSOM0607</t>
   </si>
   <si>
+    <t>2006-12-05</t>
+  </si>
+  <si>
     <t>2007-03-05</t>
   </si>
   <si>
-    <t>2006-12-05</t>
-  </si>
-  <si>
     <t>OLKA06</t>
   </si>
   <si>
@@ -3271,33 +3271,33 @@
     <t>FAGO05</t>
   </si>
   <si>
+    <t>2005-04-01</t>
+  </si>
+  <si>
+    <t>2005-06-30</t>
+  </si>
+  <si>
     <t>2005</t>
   </si>
   <si>
-    <t>2005-06-30</t>
-  </si>
-  <si>
-    <t>2005-04-01</t>
-  </si>
-  <si>
     <t>FBEN05</t>
   </si>
   <si>
+    <t>2005-05-01</t>
+  </si>
+  <si>
     <t>2005-10-31</t>
   </si>
   <si>
-    <t>2005-05-01</t>
-  </si>
-  <si>
     <t>CBDI05</t>
   </si>
   <si>
+    <t>2005-01-01</t>
+  </si>
+  <si>
     <t>2005-12-31</t>
   </si>
   <si>
-    <t>2005-01-01</t>
-  </si>
-  <si>
     <t>CCAF05</t>
   </si>
   <si>
@@ -3337,12 +3337,12 @@
     <t>FGUY05</t>
   </si>
   <si>
+    <t>2005-02-01</t>
+  </si>
+  <si>
     <t>2005-08-01</t>
   </si>
   <si>
-    <t>2005-02-01</t>
-  </si>
-  <si>
     <t>FXINDTSU05</t>
   </si>
   <si>
@@ -3355,12 +3355,12 @@
     <t>FNER05</t>
   </si>
   <si>
+    <t>2005-06-01</t>
+  </si>
+  <si>
     <t>2005-09-30</t>
   </si>
   <si>
-    <t>2005-06-01</t>
-  </si>
-  <si>
     <t>CCOG05</t>
   </si>
   <si>
@@ -3370,12 +3370,12 @@
     <t>FXSASIA0506</t>
   </si>
   <si>
+    <t>2005-10-11</t>
+  </si>
+  <si>
     <t>2006-04-10</t>
   </si>
   <si>
-    <t>2005-10-11</t>
-  </si>
-  <si>
     <t>CSDN05</t>
   </si>
   <si>
@@ -3388,27 +3388,27 @@
     <t>FXWAF0506</t>
   </si>
   <si>
+    <t>2005-11-01</t>
+  </si>
+  <si>
     <t>2006-05-31</t>
   </si>
   <si>
-    <t>2005-11-01</t>
-  </si>
-  <si>
     <t>CPSE05</t>
   </si>
   <si>
     <t>OAFG04</t>
   </si>
   <si>
+    <t>2004-09-01</t>
+  </si>
+  <si>
+    <t>2004-12-31</t>
+  </si>
+  <si>
     <t>2004</t>
   </si>
   <si>
-    <t>2004-12-31</t>
-  </si>
-  <si>
-    <t>2004-09-01</t>
-  </si>
-  <si>
     <t>CAGO04</t>
   </si>
   <si>
@@ -3418,21 +3418,21 @@
     <t>FBGD0405</t>
   </si>
   <si>
+    <t>2004-08-01</t>
+  </si>
+  <si>
     <t>2005-01-31</t>
   </si>
   <si>
-    <t>2004-08-01</t>
-  </si>
-  <si>
     <t>FBOL0405</t>
   </si>
   <si>
+    <t>2004-11-01</t>
+  </si>
+  <si>
     <t>2005-05-31</t>
   </si>
   <si>
-    <t>2004-11-01</t>
-  </si>
-  <si>
     <t>CBDI04</t>
   </si>
   <si>
@@ -3505,21 +3505,21 @@
     <t>FMDG04</t>
   </si>
   <si>
+    <t>2004-03-19</t>
+  </si>
+  <si>
     <t>2004-06-19</t>
   </si>
   <si>
-    <t>2004-03-19</t>
-  </si>
-  <si>
     <t>FPHL0405</t>
   </si>
   <si>
+    <t>2004-12-15</t>
+  </si>
+  <si>
     <t>2005-03-15</t>
   </si>
   <si>
-    <t>2004-12-15</t>
-  </si>
-  <si>
     <t>CSLE04</t>
   </si>
   <si>
@@ -3550,15 +3550,15 @@
     <t>OAFG03</t>
   </si>
   <si>
+    <t>2003-01-01</t>
+  </si>
+  <si>
+    <t>2003-12-31</t>
+  </si>
+  <si>
     <t>2003</t>
   </si>
   <si>
-    <t>2003-12-31</t>
-  </si>
-  <si>
-    <t>2003-01-01</t>
-  </si>
-  <si>
     <t>CAGO03</t>
   </si>
   <si>
@@ -3568,12 +3568,12 @@
     <t>FCAF03</t>
   </si>
   <si>
+    <t>2003-04-01</t>
+  </si>
+  <si>
     <t>2003-06-30</t>
   </si>
   <si>
-    <t>2003-04-01</t>
-  </si>
-  <si>
     <t>CRUS03</t>
   </si>
   <si>
@@ -3586,12 +3586,12 @@
     <t>FCIV0203</t>
   </si>
   <si>
+    <t>2002-11-01</t>
+  </si>
+  <si>
     <t>2003-01-31</t>
   </si>
   <si>
-    <t>2002-11-01</t>
-  </si>
-  <si>
     <t>CPRK03</t>
   </si>
   <si>
@@ -3610,21 +3610,21 @@
     <t>OHTI03</t>
   </si>
   <si>
+    <t>2003-03-01</t>
+  </si>
+  <si>
     <t>2003-08-31</t>
   </si>
   <si>
-    <t>2003-03-01</t>
-  </si>
-  <si>
     <t>CLSO0304</t>
   </si>
   <si>
+    <t>2003-07-01</t>
+  </si>
+  <si>
     <t>2004-06-30</t>
   </si>
   <si>
-    <t>2003-07-01</t>
-  </si>
-  <si>
     <t>CMWI03</t>
   </si>
   <si>
@@ -3676,15 +3676,15 @@
     <t>CAFG0102</t>
   </si>
   <si>
+    <t>2001-10-01</t>
+  </si>
+  <si>
+    <t>2002-12-31</t>
+  </si>
+  <si>
     <t>2002</t>
   </si>
   <si>
-    <t>2002-12-31</t>
-  </si>
-  <si>
-    <t>2001-10-01</t>
-  </si>
-  <si>
     <t>CAGO02</t>
   </si>
   <si>
@@ -3778,15 +3778,15 @@
     <t>CAFG01</t>
   </si>
   <si>
+    <t>2001-01-01</t>
+  </si>
+  <si>
+    <t>2001-09-30</t>
+  </si>
+  <si>
     <t>2001</t>
   </si>
   <si>
-    <t>2001-09-30</t>
-  </si>
-  <si>
-    <t>2001-01-01</t>
-  </si>
-  <si>
     <t>CAGO01</t>
   </si>
   <si>
@@ -3859,15 +3859,15 @@
     <t>CAGO00</t>
   </si>
   <si>
+    <t>2000-01-01</t>
+  </si>
+  <si>
+    <t>2000-12-31</t>
+  </si>
+  <si>
     <t>2000</t>
   </si>
   <si>
-    <t>2000-12-31</t>
-  </si>
-  <si>
-    <t>2000-01-01</t>
-  </si>
-  <si>
     <t>CBDI00</t>
   </si>
   <si>
@@ -3913,10 +3913,10 @@
     <t>CTLS9900</t>
   </si>
   <si>
+    <t>1999-10-01</t>
+  </si>
+  <si>
     <t>1999</t>
-  </si>
-  <si>
-    <t>1999-10-01</t>
   </si>
   <si>
     <t>CRUS9900</t>
@@ -4648,13 +4648,13 @@
         <v>7</v>
       </c>
       <c r="C20" t="s">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="D20" t="s">
         <v>9</v>
       </c>
       <c r="E20" t="s">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="F20" t="s">
         <v>11</v>
@@ -4928,13 +4928,13 @@
         <v>7</v>
       </c>
       <c r="C34" t="s">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="D34" t="s">
         <v>9</v>
       </c>
       <c r="E34" t="s">
-        <v>54</v>
+        <v>10</v>
       </c>
       <c r="F34" t="s">
         <v>24</v>
@@ -5208,13 +5208,13 @@
         <v>7</v>
       </c>
       <c r="C48" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="D48" t="s">
         <v>68</v>
       </c>
       <c r="E48" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F48" t="s">
         <v>16</v>
@@ -5248,13 +5248,13 @@
         <v>7</v>
       </c>
       <c r="C50" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="D50" t="s">
         <v>68</v>
       </c>
       <c r="E50" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="F50" t="s">
         <v>16</v>
@@ -5388,13 +5388,13 @@
         <v>7</v>
       </c>
       <c r="C57" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="D57" t="s">
         <v>68</v>
       </c>
       <c r="E57" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="F57" t="s">
         <v>24</v>
@@ -5468,13 +5468,13 @@
         <v>7</v>
       </c>
       <c r="C61" t="s">
-        <v>67</v>
+        <v>88</v>
       </c>
       <c r="D61" t="s">
         <v>68</v>
       </c>
       <c r="E61" t="s">
-        <v>88</v>
+        <v>69</v>
       </c>
       <c r="F61" t="s">
         <v>16</v>
@@ -5488,13 +5488,13 @@
         <v>7</v>
       </c>
       <c r="C62" t="s">
-        <v>67</v>
+        <v>88</v>
       </c>
       <c r="D62" t="s">
         <v>68</v>
       </c>
       <c r="E62" t="s">
-        <v>88</v>
+        <v>69</v>
       </c>
       <c r="F62" t="s">
         <v>24</v>
@@ -5548,13 +5548,13 @@
         <v>7</v>
       </c>
       <c r="C65" t="s">
-        <v>67</v>
+        <v>95</v>
       </c>
       <c r="D65" t="s">
         <v>68</v>
       </c>
       <c r="E65" t="s">
-        <v>95</v>
+        <v>69</v>
       </c>
       <c r="F65" t="s">
         <v>24</v>
@@ -5588,13 +5588,13 @@
         <v>7</v>
       </c>
       <c r="C67" t="s">
-        <v>67</v>
+        <v>98</v>
       </c>
       <c r="D67" t="s">
         <v>93</v>
       </c>
       <c r="E67" t="s">
-        <v>98</v>
+        <v>69</v>
       </c>
       <c r="F67" t="s">
         <v>16</v>
@@ -5608,13 +5608,13 @@
         <v>7</v>
       </c>
       <c r="C68" t="s">
-        <v>67</v>
+        <v>100</v>
       </c>
       <c r="D68" t="s">
         <v>68</v>
       </c>
       <c r="E68" t="s">
-        <v>100</v>
+        <v>69</v>
       </c>
       <c r="F68" t="s">
         <v>24</v>
@@ -5668,13 +5668,13 @@
         <v>7</v>
       </c>
       <c r="C71" t="s">
-        <v>67</v>
+        <v>104</v>
       </c>
       <c r="D71" t="s">
         <v>68</v>
       </c>
       <c r="E71" t="s">
-        <v>104</v>
+        <v>69</v>
       </c>
       <c r="F71" t="s">
         <v>16</v>
@@ -5728,13 +5728,13 @@
         <v>7</v>
       </c>
       <c r="C74" t="s">
-        <v>67</v>
+        <v>108</v>
       </c>
       <c r="D74" t="s">
         <v>68</v>
       </c>
       <c r="E74" t="s">
-        <v>108</v>
+        <v>69</v>
       </c>
       <c r="F74" t="s">
         <v>16</v>
@@ -5848,13 +5848,13 @@
         <v>7</v>
       </c>
       <c r="C80" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="D80" t="s">
         <v>68</v>
       </c>
       <c r="E80" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="F80" t="s">
         <v>24</v>
@@ -6108,13 +6108,13 @@
         <v>7</v>
       </c>
       <c r="C93" t="s">
-        <v>67</v>
+        <v>129</v>
       </c>
       <c r="D93" t="s">
         <v>68</v>
       </c>
       <c r="E93" t="s">
-        <v>129</v>
+        <v>69</v>
       </c>
       <c r="F93" t="s">
         <v>16</v>
@@ -6148,13 +6148,13 @@
         <v>7</v>
       </c>
       <c r="C95" t="s">
-        <v>67</v>
+        <v>132</v>
       </c>
       <c r="D95" t="s">
         <v>68</v>
       </c>
       <c r="E95" t="s">
-        <v>132</v>
+        <v>69</v>
       </c>
       <c r="F95" t="s">
         <v>24</v>
@@ -6168,13 +6168,13 @@
         <v>7</v>
       </c>
       <c r="C96" t="s">
-        <v>67</v>
+        <v>132</v>
       </c>
       <c r="D96" t="s">
         <v>68</v>
       </c>
       <c r="E96" t="s">
-        <v>132</v>
+        <v>69</v>
       </c>
       <c r="F96" t="s">
         <v>24</v>
@@ -6348,13 +6348,13 @@
         <v>7</v>
       </c>
       <c r="C105" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="D105" t="s">
         <v>136</v>
       </c>
       <c r="E105" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="F105" t="s">
         <v>24</v>
@@ -6508,13 +6508,13 @@
         <v>7</v>
       </c>
       <c r="C113" t="s">
-        <v>135</v>
+        <v>155</v>
       </c>
       <c r="D113" t="s">
         <v>136</v>
       </c>
       <c r="E113" t="s">
-        <v>155</v>
+        <v>137</v>
       </c>
       <c r="F113" t="s">
         <v>24</v>
@@ -6568,13 +6568,13 @@
         <v>7</v>
       </c>
       <c r="C116" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="D116" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E116" t="s">
-        <v>160</v>
+        <v>137</v>
       </c>
       <c r="F116" t="s">
         <v>16</v>
@@ -6588,13 +6588,13 @@
         <v>7</v>
       </c>
       <c r="C117" t="s">
-        <v>135</v>
+        <v>162</v>
       </c>
       <c r="D117" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E117" t="s">
-        <v>163</v>
+        <v>137</v>
       </c>
       <c r="F117" t="s">
         <v>16</v>
@@ -6691,7 +6691,7 @@
         <v>135</v>
       </c>
       <c r="D122" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E122" t="s">
         <v>137</v>
@@ -6711,7 +6711,7 @@
         <v>135</v>
       </c>
       <c r="D123" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E123" t="s">
         <v>137</v>
@@ -6888,13 +6888,13 @@
         <v>7</v>
       </c>
       <c r="C132" t="s">
-        <v>135</v>
+        <v>179</v>
       </c>
       <c r="D132" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E132" t="s">
-        <v>180</v>
+        <v>137</v>
       </c>
       <c r="F132" t="s">
         <v>13</v>
@@ -6928,13 +6928,13 @@
         <v>7</v>
       </c>
       <c r="C134" t="s">
-        <v>135</v>
+        <v>183</v>
       </c>
       <c r="D134" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E134" t="s">
-        <v>183</v>
+        <v>137</v>
       </c>
       <c r="F134" t="s">
         <v>24</v>
@@ -6968,13 +6968,13 @@
         <v>7</v>
       </c>
       <c r="C136" t="s">
-        <v>135</v>
+        <v>186</v>
       </c>
       <c r="D136" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E136" t="s">
-        <v>186</v>
+        <v>137</v>
       </c>
       <c r="F136" t="s">
         <v>24</v>
@@ -7268,13 +7268,13 @@
         <v>7</v>
       </c>
       <c r="C151" t="s">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="D151" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E151" t="s">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="F151" t="s">
         <v>16</v>
@@ -7368,13 +7368,13 @@
         <v>7</v>
       </c>
       <c r="C156" t="s">
-        <v>195</v>
+        <v>212</v>
       </c>
       <c r="D156" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E156" t="s">
-        <v>213</v>
+        <v>197</v>
       </c>
       <c r="F156" t="s">
         <v>24</v>
@@ -7388,13 +7388,13 @@
         <v>110</v>
       </c>
       <c r="C157" t="s">
-        <v>195</v>
+        <v>212</v>
       </c>
       <c r="D157" t="s">
         <v>196</v>
       </c>
       <c r="E157" t="s">
-        <v>213</v>
+        <v>197</v>
       </c>
       <c r="F157" t="s">
         <v>24</v>
@@ -7548,13 +7548,13 @@
         <v>7</v>
       </c>
       <c r="C165" t="s">
-        <v>195</v>
+        <v>224</v>
       </c>
       <c r="D165" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E165" t="s">
-        <v>225</v>
+        <v>197</v>
       </c>
       <c r="F165" t="s">
         <v>24</v>
@@ -7588,13 +7588,13 @@
         <v>7</v>
       </c>
       <c r="C167" t="s">
-        <v>195</v>
+        <v>228</v>
       </c>
       <c r="D167" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E167" t="s">
-        <v>229</v>
+        <v>197</v>
       </c>
       <c r="F167" t="s">
         <v>24</v>
@@ -7708,13 +7708,13 @@
         <v>7</v>
       </c>
       <c r="C173" t="s">
-        <v>195</v>
+        <v>236</v>
       </c>
       <c r="D173" t="s">
         <v>196</v>
       </c>
       <c r="E173" t="s">
-        <v>236</v>
+        <v>197</v>
       </c>
       <c r="F173" t="s">
         <v>16</v>
@@ -7728,13 +7728,13 @@
         <v>110</v>
       </c>
       <c r="C174" t="s">
-        <v>195</v>
+        <v>236</v>
       </c>
       <c r="D174" t="s">
         <v>238</v>
       </c>
       <c r="E174" t="s">
-        <v>236</v>
+        <v>197</v>
       </c>
       <c r="F174" t="s">
         <v>16</v>
@@ -7748,13 +7748,13 @@
         <v>7</v>
       </c>
       <c r="C175" t="s">
-        <v>195</v>
+        <v>240</v>
       </c>
       <c r="D175" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E175" t="s">
-        <v>241</v>
+        <v>197</v>
       </c>
       <c r="F175" t="s">
         <v>16</v>
@@ -7908,13 +7908,13 @@
         <v>7</v>
       </c>
       <c r="C183" t="s">
-        <v>195</v>
+        <v>250</v>
       </c>
       <c r="D183" t="s">
         <v>196</v>
       </c>
       <c r="E183" t="s">
-        <v>250</v>
+        <v>197</v>
       </c>
       <c r="F183" t="s">
         <v>16</v>
@@ -8008,13 +8008,13 @@
         <v>7</v>
       </c>
       <c r="C188" t="s">
-        <v>195</v>
+        <v>256</v>
       </c>
       <c r="D188" t="s">
         <v>196</v>
       </c>
       <c r="E188" t="s">
-        <v>256</v>
+        <v>197</v>
       </c>
       <c r="F188" t="s">
         <v>24</v>
@@ -8048,13 +8048,13 @@
         <v>7</v>
       </c>
       <c r="C190" t="s">
-        <v>195</v>
+        <v>256</v>
       </c>
       <c r="D190" t="s">
         <v>259</v>
       </c>
       <c r="E190" t="s">
-        <v>256</v>
+        <v>197</v>
       </c>
       <c r="F190" t="s">
         <v>13</v>
@@ -8128,13 +8128,13 @@
         <v>7</v>
       </c>
       <c r="C194" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="D194" t="s">
         <v>264</v>
       </c>
       <c r="E194" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F194" t="s">
         <v>19</v>
@@ -8148,13 +8148,13 @@
         <v>7</v>
       </c>
       <c r="C195" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="D195" t="s">
         <v>264</v>
       </c>
       <c r="E195" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F195" t="s">
         <v>13</v>
@@ -8168,13 +8168,13 @@
         <v>7</v>
       </c>
       <c r="C196" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="D196" t="s">
         <v>264</v>
       </c>
       <c r="E196" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F196" t="s">
         <v>19</v>
@@ -8188,13 +8188,13 @@
         <v>7</v>
       </c>
       <c r="C197" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="D197" t="s">
         <v>264</v>
       </c>
       <c r="E197" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F197" t="s">
         <v>19</v>
@@ -8208,13 +8208,13 @@
         <v>7</v>
       </c>
       <c r="C198" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="D198" t="s">
         <v>264</v>
       </c>
       <c r="E198" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F198" t="s">
         <v>13</v>
@@ -8228,13 +8228,13 @@
         <v>7</v>
       </c>
       <c r="C199" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="D199" t="s">
         <v>264</v>
       </c>
       <c r="E199" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F199" t="s">
         <v>19</v>
@@ -8248,13 +8248,13 @@
         <v>7</v>
       </c>
       <c r="C200" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="D200" t="s">
         <v>264</v>
       </c>
       <c r="E200" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F200" t="s">
         <v>19</v>
@@ -8268,13 +8268,13 @@
         <v>7</v>
       </c>
       <c r="C201" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="D201" t="s">
         <v>264</v>
       </c>
       <c r="E201" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F201" t="s">
         <v>19</v>
@@ -8288,13 +8288,13 @@
         <v>7</v>
       </c>
       <c r="C202" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="D202" t="s">
         <v>264</v>
       </c>
       <c r="E202" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F202" t="s">
         <v>19</v>
@@ -8308,13 +8308,13 @@
         <v>7</v>
       </c>
       <c r="C203" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="D203" t="s">
         <v>264</v>
       </c>
       <c r="E203" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F203" t="s">
         <v>19</v>
@@ -8328,13 +8328,13 @@
         <v>7</v>
       </c>
       <c r="C204" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="D204" t="s">
         <v>264</v>
       </c>
       <c r="E204" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F204" t="s">
         <v>13</v>
@@ -8348,13 +8348,13 @@
         <v>7</v>
       </c>
       <c r="C205" t="s">
-        <v>263</v>
+        <v>279</v>
       </c>
       <c r="D205" t="s">
         <v>264</v>
       </c>
       <c r="E205" t="s">
-        <v>279</v>
+        <v>265</v>
       </c>
       <c r="F205" t="s">
         <v>19</v>
@@ -8368,13 +8368,13 @@
         <v>110</v>
       </c>
       <c r="C206" t="s">
-        <v>263</v>
+        <v>279</v>
       </c>
       <c r="D206" t="s">
         <v>196</v>
       </c>
       <c r="E206" t="s">
-        <v>279</v>
+        <v>265</v>
       </c>
       <c r="F206" t="s">
         <v>19</v>
@@ -8388,13 +8388,13 @@
         <v>7</v>
       </c>
       <c r="C207" t="s">
-        <v>263</v>
+        <v>282</v>
       </c>
       <c r="D207" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E207" t="s">
-        <v>283</v>
+        <v>265</v>
       </c>
       <c r="F207" t="s">
         <v>24</v>
@@ -8408,13 +8408,13 @@
         <v>7</v>
       </c>
       <c r="C208" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="D208" t="s">
         <v>264</v>
       </c>
       <c r="E208" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F208" t="s">
         <v>19</v>
@@ -8428,13 +8428,13 @@
         <v>7</v>
       </c>
       <c r="C209" t="s">
-        <v>263</v>
+        <v>279</v>
       </c>
       <c r="D209" t="s">
         <v>264</v>
       </c>
       <c r="E209" t="s">
-        <v>279</v>
+        <v>265</v>
       </c>
       <c r="F209" t="s">
         <v>19</v>
@@ -8448,13 +8448,13 @@
         <v>110</v>
       </c>
       <c r="C210" t="s">
-        <v>263</v>
+        <v>279</v>
       </c>
       <c r="D210" t="s">
         <v>196</v>
       </c>
       <c r="E210" t="s">
-        <v>279</v>
+        <v>265</v>
       </c>
       <c r="F210" t="s">
         <v>19</v>
@@ -8468,13 +8468,13 @@
         <v>7</v>
       </c>
       <c r="C211" t="s">
-        <v>263</v>
+        <v>288</v>
       </c>
       <c r="D211" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E211" t="s">
-        <v>289</v>
+        <v>265</v>
       </c>
       <c r="F211" t="s">
         <v>24</v>
@@ -8488,13 +8488,13 @@
         <v>7</v>
       </c>
       <c r="C212" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="D212" t="s">
         <v>264</v>
       </c>
       <c r="E212" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F212" t="s">
         <v>19</v>
@@ -8508,13 +8508,13 @@
         <v>7</v>
       </c>
       <c r="C213" t="s">
-        <v>263</v>
+        <v>292</v>
       </c>
       <c r="D213" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E213" t="s">
-        <v>293</v>
+        <v>265</v>
       </c>
       <c r="F213" t="s">
         <v>24</v>
@@ -8528,13 +8528,13 @@
         <v>7</v>
       </c>
       <c r="C214" t="s">
-        <v>263</v>
+        <v>279</v>
       </c>
       <c r="D214" t="s">
         <v>264</v>
       </c>
       <c r="E214" t="s">
-        <v>279</v>
+        <v>265</v>
       </c>
       <c r="F214" t="s">
         <v>19</v>
@@ -8548,13 +8548,13 @@
         <v>110</v>
       </c>
       <c r="C215" t="s">
-        <v>263</v>
+        <v>279</v>
       </c>
       <c r="D215" t="s">
         <v>196</v>
       </c>
       <c r="E215" t="s">
-        <v>279</v>
+        <v>265</v>
       </c>
       <c r="F215" t="s">
         <v>19</v>
@@ -8568,13 +8568,13 @@
         <v>7</v>
       </c>
       <c r="C216" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="D216" t="s">
         <v>264</v>
       </c>
       <c r="E216" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F216" t="s">
         <v>19</v>
@@ -8588,13 +8588,13 @@
         <v>7</v>
       </c>
       <c r="C217" t="s">
-        <v>263</v>
+        <v>298</v>
       </c>
       <c r="D217" t="s">
         <v>264</v>
       </c>
       <c r="E217" t="s">
-        <v>298</v>
+        <v>265</v>
       </c>
       <c r="F217" t="s">
         <v>24</v>
@@ -8608,13 +8608,13 @@
         <v>7</v>
       </c>
       <c r="C218" t="s">
-        <v>263</v>
+        <v>300</v>
       </c>
       <c r="D218" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E218" t="s">
-        <v>301</v>
+        <v>265</v>
       </c>
       <c r="F218" t="s">
         <v>16</v>
@@ -8628,13 +8628,13 @@
         <v>7</v>
       </c>
       <c r="C219" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="D219" t="s">
         <v>264</v>
       </c>
       <c r="E219" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F219" t="s">
         <v>19</v>
@@ -8648,13 +8648,13 @@
         <v>110</v>
       </c>
       <c r="C220" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="D220" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E220" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F220" t="s">
         <v>24</v>
@@ -8668,13 +8668,13 @@
         <v>7</v>
       </c>
       <c r="C221" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="D221" t="s">
         <v>264</v>
       </c>
       <c r="E221" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F221" t="s">
         <v>24</v>
@@ -8688,13 +8688,13 @@
         <v>7</v>
       </c>
       <c r="C222" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="D222" t="s">
         <v>264</v>
       </c>
       <c r="E222" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F222" t="s">
         <v>19</v>
@@ -8708,13 +8708,13 @@
         <v>7</v>
       </c>
       <c r="C223" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="D223" t="s">
         <v>264</v>
       </c>
       <c r="E223" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F223" t="s">
         <v>19</v>
@@ -8728,13 +8728,13 @@
         <v>7</v>
       </c>
       <c r="C224" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="D224" t="s">
         <v>264</v>
       </c>
       <c r="E224" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F224" t="s">
         <v>19</v>
@@ -8748,13 +8748,13 @@
         <v>7</v>
       </c>
       <c r="C225" t="s">
-        <v>263</v>
+        <v>309</v>
       </c>
       <c r="D225" t="s">
         <v>264</v>
       </c>
       <c r="E225" t="s">
-        <v>309</v>
+        <v>265</v>
       </c>
       <c r="F225" t="s">
         <v>16</v>
@@ -8768,13 +8768,13 @@
         <v>7</v>
       </c>
       <c r="C226" t="s">
-        <v>263</v>
+        <v>311</v>
       </c>
       <c r="D226" t="s">
         <v>264</v>
       </c>
       <c r="E226" t="s">
-        <v>311</v>
+        <v>265</v>
       </c>
       <c r="F226" t="s">
         <v>16</v>
@@ -8788,13 +8788,13 @@
         <v>7</v>
       </c>
       <c r="C227" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="D227" t="s">
         <v>264</v>
       </c>
       <c r="E227" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F227" t="s">
         <v>19</v>
@@ -8808,13 +8808,13 @@
         <v>7</v>
       </c>
       <c r="C228" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="D228" t="s">
         <v>264</v>
       </c>
       <c r="E228" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F228" t="s">
         <v>19</v>
@@ -8828,13 +8828,13 @@
         <v>7</v>
       </c>
       <c r="C229" t="s">
-        <v>263</v>
+        <v>311</v>
       </c>
       <c r="D229" t="s">
         <v>264</v>
       </c>
       <c r="E229" t="s">
-        <v>311</v>
+        <v>265</v>
       </c>
       <c r="F229" t="s">
         <v>24</v>
@@ -8848,13 +8848,13 @@
         <v>110</v>
       </c>
       <c r="C230" t="s">
-        <v>263</v>
+        <v>311</v>
       </c>
       <c r="D230" t="s">
         <v>264</v>
       </c>
       <c r="E230" t="s">
-        <v>311</v>
+        <v>265</v>
       </c>
       <c r="F230" t="s">
         <v>16</v>
@@ -8868,13 +8868,13 @@
         <v>7</v>
       </c>
       <c r="C231" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="D231" t="s">
         <v>264</v>
       </c>
       <c r="E231" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F231" t="s">
         <v>19</v>
@@ -8888,13 +8888,13 @@
         <v>7</v>
       </c>
       <c r="C232" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="D232" t="s">
         <v>264</v>
       </c>
       <c r="E232" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F232" t="s">
         <v>19</v>
@@ -8908,13 +8908,13 @@
         <v>7</v>
       </c>
       <c r="C233" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="D233" t="s">
         <v>264</v>
       </c>
       <c r="E233" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F233" t="s">
         <v>13</v>
@@ -8928,13 +8928,13 @@
         <v>7</v>
       </c>
       <c r="C234" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="D234" t="s">
         <v>264</v>
       </c>
       <c r="E234" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F234" t="s">
         <v>13</v>
@@ -8948,13 +8948,13 @@
         <v>7</v>
       </c>
       <c r="C235" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="D235" t="s">
         <v>264</v>
       </c>
       <c r="E235" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F235" t="s">
         <v>19</v>
@@ -8968,13 +8968,13 @@
         <v>7</v>
       </c>
       <c r="C236" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="D236" t="s">
         <v>264</v>
       </c>
       <c r="E236" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F236" t="s">
         <v>19</v>
@@ -8988,13 +8988,13 @@
         <v>7</v>
       </c>
       <c r="C237" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="D237" t="s">
         <v>264</v>
       </c>
       <c r="E237" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F237" t="s">
         <v>13</v>
@@ -9008,13 +9008,13 @@
         <v>7</v>
       </c>
       <c r="C238" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="D238" t="s">
         <v>264</v>
       </c>
       <c r="E238" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F238" t="s">
         <v>19</v>
@@ -9028,13 +9028,13 @@
         <v>7</v>
       </c>
       <c r="C239" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="D239" t="s">
         <v>264</v>
       </c>
       <c r="E239" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F239" t="s">
         <v>19</v>
@@ -9048,13 +9048,13 @@
         <v>7</v>
       </c>
       <c r="C240" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="D240" t="s">
         <v>264</v>
       </c>
       <c r="E240" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F240" t="s">
         <v>13</v>
@@ -9068,13 +9068,13 @@
         <v>7</v>
       </c>
       <c r="C241" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="D241" t="s">
         <v>264</v>
       </c>
       <c r="E241" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F241" t="s">
         <v>19</v>
@@ -9088,13 +9088,13 @@
         <v>7</v>
       </c>
       <c r="C242" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="D242" t="s">
         <v>264</v>
       </c>
       <c r="E242" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F242" t="s">
         <v>19</v>
@@ -9108,13 +9108,13 @@
         <v>7</v>
       </c>
       <c r="C243" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="D243" t="s">
         <v>264</v>
       </c>
       <c r="E243" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F243" t="s">
         <v>19</v>
@@ -9128,13 +9128,13 @@
         <v>7</v>
       </c>
       <c r="C244" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="D244" t="s">
         <v>264</v>
       </c>
       <c r="E244" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F244" t="s">
         <v>19</v>
@@ -9168,13 +9168,13 @@
         <v>7</v>
       </c>
       <c r="C246" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="D246" t="s">
         <v>332</v>
       </c>
       <c r="E246" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="F246" t="s">
         <v>16</v>
@@ -9208,13 +9208,13 @@
         <v>7</v>
       </c>
       <c r="C248" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="D248" t="s">
         <v>332</v>
       </c>
       <c r="E248" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="F248" t="s">
         <v>16</v>
@@ -9288,13 +9288,13 @@
         <v>7</v>
       </c>
       <c r="C252" t="s">
-        <v>331</v>
+        <v>342</v>
       </c>
       <c r="D252" t="s">
         <v>332</v>
       </c>
       <c r="E252" t="s">
-        <v>342</v>
+        <v>333</v>
       </c>
       <c r="F252" t="s">
         <v>16</v>
@@ -9328,13 +9328,13 @@
         <v>7</v>
       </c>
       <c r="C254" t="s">
-        <v>331</v>
+        <v>345</v>
       </c>
       <c r="D254" t="s">
         <v>267</v>
       </c>
       <c r="E254" t="s">
-        <v>345</v>
+        <v>333</v>
       </c>
       <c r="F254" t="s">
         <v>19</v>
@@ -9388,13 +9388,13 @@
         <v>7</v>
       </c>
       <c r="C257" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="D257" t="s">
         <v>332</v>
       </c>
       <c r="E257" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="F257" t="s">
         <v>16</v>
@@ -9408,13 +9408,13 @@
         <v>7</v>
       </c>
       <c r="C258" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="D258" t="s">
         <v>332</v>
       </c>
       <c r="E258" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="F258" t="s">
         <v>16</v>
@@ -9428,13 +9428,13 @@
         <v>110</v>
       </c>
       <c r="C259" t="s">
-        <v>331</v>
+        <v>351</v>
       </c>
       <c r="D259" t="s">
         <v>332</v>
       </c>
       <c r="E259" t="s">
-        <v>351</v>
+        <v>333</v>
       </c>
       <c r="F259" t="s">
         <v>19</v>
@@ -9488,13 +9488,13 @@
         <v>7</v>
       </c>
       <c r="C262" t="s">
-        <v>331</v>
+        <v>355</v>
       </c>
       <c r="D262" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="E262" t="s">
-        <v>356</v>
+        <v>333</v>
       </c>
       <c r="F262" t="s">
         <v>24</v>
@@ -9508,13 +9508,13 @@
         <v>7</v>
       </c>
       <c r="C263" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="D263" t="s">
         <v>332</v>
       </c>
       <c r="E263" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="F263" t="s">
         <v>16</v>
@@ -9528,13 +9528,13 @@
         <v>110</v>
       </c>
       <c r="C264" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="D264" t="s">
         <v>332</v>
       </c>
       <c r="E264" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="F264" t="s">
         <v>16</v>
@@ -9568,13 +9568,13 @@
         <v>7</v>
       </c>
       <c r="C266" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="D266" t="s">
         <v>332</v>
       </c>
       <c r="E266" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="F266" t="s">
         <v>16</v>
@@ -9608,13 +9608,13 @@
         <v>7</v>
       </c>
       <c r="C268" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="D268" t="s">
         <v>332</v>
       </c>
       <c r="E268" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="F268" t="s">
         <v>16</v>
@@ -9628,13 +9628,13 @@
         <v>7</v>
       </c>
       <c r="C269" t="s">
-        <v>331</v>
+        <v>351</v>
       </c>
       <c r="D269" t="s">
         <v>332</v>
       </c>
       <c r="E269" t="s">
-        <v>351</v>
+        <v>333</v>
       </c>
       <c r="F269" t="s">
         <v>16</v>
@@ -9648,13 +9648,13 @@
         <v>110</v>
       </c>
       <c r="C270" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="D270" t="s">
         <v>332</v>
       </c>
       <c r="E270" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="F270" t="s">
         <v>16</v>
@@ -9668,13 +9668,13 @@
         <v>7</v>
       </c>
       <c r="C271" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="D271" t="s">
         <v>332</v>
       </c>
       <c r="E271" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="F271" t="s">
         <v>16</v>
@@ -9708,13 +9708,13 @@
         <v>7</v>
       </c>
       <c r="C273" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="D273" t="s">
         <v>332</v>
       </c>
       <c r="E273" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="F273" t="s">
         <v>16</v>
@@ -9748,13 +9748,13 @@
         <v>7</v>
       </c>
       <c r="C275" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="D275" t="s">
         <v>332</v>
       </c>
       <c r="E275" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="F275" t="s">
         <v>16</v>
@@ -9768,13 +9768,13 @@
         <v>7</v>
       </c>
       <c r="C276" t="s">
-        <v>331</v>
+        <v>371</v>
       </c>
       <c r="D276" t="s">
         <v>332</v>
       </c>
       <c r="E276" t="s">
-        <v>371</v>
+        <v>333</v>
       </c>
       <c r="F276" t="s">
         <v>16</v>
@@ -9788,13 +9788,13 @@
         <v>7</v>
       </c>
       <c r="C277" t="s">
-        <v>331</v>
+        <v>373</v>
       </c>
       <c r="D277" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="E277" t="s">
-        <v>374</v>
+        <v>333</v>
       </c>
       <c r="F277" t="s">
         <v>24</v>
@@ -9808,13 +9808,13 @@
         <v>7</v>
       </c>
       <c r="C278" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="D278" t="s">
         <v>332</v>
       </c>
       <c r="E278" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="F278" t="s">
         <v>16</v>
@@ -9828,13 +9828,13 @@
         <v>7</v>
       </c>
       <c r="C279" t="s">
-        <v>331</v>
+        <v>377</v>
       </c>
       <c r="D279" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E279" t="s">
-        <v>378</v>
+        <v>333</v>
       </c>
       <c r="F279" t="s">
         <v>24</v>
@@ -9848,13 +9848,13 @@
         <v>7</v>
       </c>
       <c r="C280" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="D280" t="s">
         <v>332</v>
       </c>
       <c r="E280" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="F280" t="s">
         <v>16</v>
@@ -9908,13 +9908,13 @@
         <v>7</v>
       </c>
       <c r="C283" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="D283" t="s">
         <v>332</v>
       </c>
       <c r="E283" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="F283" t="s">
         <v>16</v>
@@ -10008,13 +10008,13 @@
         <v>7</v>
       </c>
       <c r="C288" t="s">
-        <v>331</v>
+        <v>371</v>
       </c>
       <c r="D288" t="s">
         <v>332</v>
       </c>
       <c r="E288" t="s">
-        <v>371</v>
+        <v>333</v>
       </c>
       <c r="F288" t="s">
         <v>16</v>
@@ -10028,13 +10028,13 @@
         <v>7</v>
       </c>
       <c r="C289" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="D289" t="s">
         <v>332</v>
       </c>
       <c r="E289" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="F289" t="s">
         <v>16</v>
@@ -10088,13 +10088,13 @@
         <v>7</v>
       </c>
       <c r="C292" t="s">
-        <v>331</v>
+        <v>371</v>
       </c>
       <c r="D292" t="s">
         <v>332</v>
       </c>
       <c r="E292" t="s">
-        <v>371</v>
+        <v>333</v>
       </c>
       <c r="F292" t="s">
         <v>16</v>
@@ -10108,13 +10108,13 @@
         <v>7</v>
       </c>
       <c r="C293" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="D293" t="s">
         <v>332</v>
       </c>
       <c r="E293" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="F293" t="s">
         <v>16</v>
@@ -10248,13 +10248,13 @@
         <v>7</v>
       </c>
       <c r="C300" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="D300" t="s">
         <v>332</v>
       </c>
       <c r="E300" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="F300" t="s">
         <v>16</v>
@@ -10268,13 +10268,13 @@
         <v>7</v>
       </c>
       <c r="C301" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="D301" t="s">
         <v>332</v>
       </c>
       <c r="E301" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="F301" t="s">
         <v>16</v>
@@ -10288,13 +10288,13 @@
         <v>7</v>
       </c>
       <c r="C302" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="D302" t="s">
         <v>332</v>
       </c>
       <c r="E302" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="F302" t="s">
         <v>16</v>
@@ -10328,13 +10328,13 @@
         <v>7</v>
       </c>
       <c r="C304" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="D304" t="s">
         <v>332</v>
       </c>
       <c r="E304" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="F304" t="s">
         <v>16</v>
@@ -10388,13 +10388,13 @@
         <v>7</v>
       </c>
       <c r="C307" t="s">
-        <v>331</v>
+        <v>407</v>
       </c>
       <c r="D307" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="E307" t="s">
-        <v>407</v>
+        <v>333</v>
       </c>
       <c r="F307" t="s">
         <v>16</v>
@@ -10408,13 +10408,13 @@
         <v>7</v>
       </c>
       <c r="C308" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="D308" t="s">
         <v>332</v>
       </c>
       <c r="E308" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="F308" t="s">
         <v>16</v>
@@ -10708,13 +10708,13 @@
         <v>7</v>
       </c>
       <c r="C323" t="s">
-        <v>411</v>
+        <v>427</v>
       </c>
       <c r="D323" t="s">
         <v>412</v>
       </c>
       <c r="E323" t="s">
-        <v>427</v>
+        <v>413</v>
       </c>
       <c r="F323" t="s">
         <v>16</v>
@@ -11108,13 +11108,13 @@
         <v>7</v>
       </c>
       <c r="C343" t="s">
-        <v>411</v>
+        <v>450</v>
       </c>
       <c r="D343" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="E343" t="s">
-        <v>451</v>
+        <v>413</v>
       </c>
       <c r="F343" t="s">
         <v>24</v>
@@ -11128,13 +11128,13 @@
         <v>110</v>
       </c>
       <c r="C344" t="s">
-        <v>411</v>
+        <v>453</v>
       </c>
       <c r="D344" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="E344" t="s">
-        <v>453</v>
+        <v>413</v>
       </c>
       <c r="F344" t="s">
         <v>24</v>
@@ -11168,13 +11168,13 @@
         <v>110</v>
       </c>
       <c r="C346" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="D346" t="s">
         <v>456</v>
       </c>
       <c r="E346" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="F346" t="s">
         <v>16</v>
@@ -11368,13 +11368,13 @@
         <v>7</v>
       </c>
       <c r="C356" t="s">
-        <v>455</v>
+        <v>470</v>
       </c>
       <c r="D356" t="s">
         <v>456</v>
       </c>
       <c r="E356" t="s">
-        <v>470</v>
+        <v>457</v>
       </c>
       <c r="F356" t="s">
         <v>16</v>
@@ -11568,13 +11568,13 @@
         <v>7</v>
       </c>
       <c r="C366" t="s">
-        <v>455</v>
+        <v>481</v>
       </c>
       <c r="D366" t="s">
         <v>456</v>
       </c>
       <c r="E366" t="s">
-        <v>481</v>
+        <v>457</v>
       </c>
       <c r="F366" t="s">
         <v>16</v>
@@ -11588,13 +11588,13 @@
         <v>7</v>
       </c>
       <c r="C367" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="D367" t="s">
         <v>456</v>
       </c>
       <c r="E367" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="F367" t="s">
         <v>13</v>
@@ -11688,13 +11688,13 @@
         <v>7</v>
       </c>
       <c r="C372" t="s">
-        <v>455</v>
+        <v>489</v>
       </c>
       <c r="D372" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="E372" t="s">
-        <v>490</v>
+        <v>457</v>
       </c>
       <c r="F372" t="s">
         <v>19</v>
@@ -11728,13 +11728,13 @@
         <v>110</v>
       </c>
       <c r="C374" t="s">
-        <v>455</v>
+        <v>489</v>
       </c>
       <c r="D374" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="E374" t="s">
-        <v>490</v>
+        <v>457</v>
       </c>
       <c r="F374" t="s">
         <v>19</v>
@@ -11848,13 +11848,13 @@
         <v>7</v>
       </c>
       <c r="C380" t="s">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="D380" t="s">
         <v>498</v>
       </c>
       <c r="E380" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="F380" t="s">
         <v>13</v>
@@ -11968,13 +11968,13 @@
         <v>7</v>
       </c>
       <c r="C386" t="s">
-        <v>497</v>
+        <v>509</v>
       </c>
       <c r="D386" t="s">
         <v>498</v>
       </c>
       <c r="E386" t="s">
-        <v>509</v>
+        <v>499</v>
       </c>
       <c r="F386" t="s">
         <v>16</v>
@@ -11988,13 +11988,13 @@
         <v>7</v>
       </c>
       <c r="C387" t="s">
-        <v>497</v>
+        <v>511</v>
       </c>
       <c r="D387" t="s">
         <v>498</v>
       </c>
       <c r="E387" t="s">
-        <v>511</v>
+        <v>499</v>
       </c>
       <c r="F387" t="s">
         <v>19</v>
@@ -12028,13 +12028,13 @@
         <v>7</v>
       </c>
       <c r="C389" t="s">
-        <v>497</v>
+        <v>514</v>
       </c>
       <c r="D389" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="E389" t="s">
-        <v>515</v>
+        <v>499</v>
       </c>
       <c r="F389" t="s">
         <v>24</v>
@@ -12108,13 +12108,13 @@
         <v>7</v>
       </c>
       <c r="C393" t="s">
-        <v>497</v>
+        <v>520</v>
       </c>
       <c r="D393" t="s">
         <v>498</v>
       </c>
       <c r="E393" t="s">
-        <v>520</v>
+        <v>499</v>
       </c>
       <c r="F393" t="s">
         <v>16</v>
@@ -12148,13 +12148,13 @@
         <v>7</v>
       </c>
       <c r="C395" t="s">
-        <v>497</v>
+        <v>523</v>
       </c>
       <c r="D395" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="E395" t="s">
-        <v>524</v>
+        <v>499</v>
       </c>
       <c r="F395" t="s">
         <v>24</v>
@@ -12188,13 +12188,13 @@
         <v>7</v>
       </c>
       <c r="C397" t="s">
-        <v>497</v>
+        <v>527</v>
       </c>
       <c r="D397" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="E397" t="s">
-        <v>528</v>
+        <v>499</v>
       </c>
       <c r="F397" t="s">
         <v>24</v>
@@ -12248,13 +12248,13 @@
         <v>7</v>
       </c>
       <c r="C400" t="s">
-        <v>497</v>
+        <v>532</v>
       </c>
       <c r="D400" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="E400" t="s">
-        <v>533</v>
+        <v>499</v>
       </c>
       <c r="F400" t="s">
         <v>24</v>
@@ -12368,13 +12368,13 @@
         <v>7</v>
       </c>
       <c r="C406" t="s">
-        <v>497</v>
+        <v>540</v>
       </c>
       <c r="D406" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="E406" t="s">
-        <v>541</v>
+        <v>499</v>
       </c>
       <c r="F406" t="s">
         <v>24</v>
@@ -12388,13 +12388,13 @@
         <v>7</v>
       </c>
       <c r="C407" t="s">
-        <v>497</v>
+        <v>543</v>
       </c>
       <c r="D407" t="s">
         <v>498</v>
       </c>
       <c r="E407" t="s">
-        <v>543</v>
+        <v>499</v>
       </c>
       <c r="F407" t="s">
         <v>19</v>
@@ -12628,13 +12628,13 @@
         <v>7</v>
       </c>
       <c r="C419" t="s">
-        <v>554</v>
+        <v>559</v>
       </c>
       <c r="D419" t="s">
         <v>555</v>
       </c>
       <c r="E419" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="F419" t="s">
         <v>24</v>
@@ -12668,13 +12668,13 @@
         <v>7</v>
       </c>
       <c r="C421" t="s">
-        <v>554</v>
+        <v>562</v>
       </c>
       <c r="D421" t="s">
         <v>555</v>
       </c>
       <c r="E421" t="s">
-        <v>562</v>
+        <v>556</v>
       </c>
       <c r="F421" t="s">
         <v>19</v>
@@ -12808,13 +12808,13 @@
         <v>7</v>
       </c>
       <c r="C428" t="s">
-        <v>554</v>
+        <v>570</v>
       </c>
       <c r="D428" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="E428" t="s">
-        <v>571</v>
+        <v>556</v>
       </c>
       <c r="F428" t="s">
         <v>24</v>
@@ -12828,13 +12828,13 @@
         <v>7</v>
       </c>
       <c r="C429" t="s">
-        <v>554</v>
+        <v>573</v>
       </c>
       <c r="D429" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E429" t="s">
-        <v>574</v>
+        <v>556</v>
       </c>
       <c r="F429" t="s">
         <v>24</v>
@@ -12908,13 +12908,13 @@
         <v>7</v>
       </c>
       <c r="C433" t="s">
-        <v>554</v>
+        <v>579</v>
       </c>
       <c r="D433" t="s">
         <v>555</v>
       </c>
       <c r="E433" t="s">
-        <v>579</v>
+        <v>556</v>
       </c>
       <c r="F433" t="s">
         <v>24</v>
@@ -12968,13 +12968,13 @@
         <v>7</v>
       </c>
       <c r="C436" t="s">
-        <v>554</v>
+        <v>583</v>
       </c>
       <c r="D436" t="s">
         <v>555</v>
       </c>
       <c r="E436" t="s">
-        <v>583</v>
+        <v>556</v>
       </c>
       <c r="F436" t="s">
         <v>24</v>
@@ -12988,13 +12988,13 @@
         <v>7</v>
       </c>
       <c r="C437" t="s">
-        <v>554</v>
+        <v>585</v>
       </c>
       <c r="D437" t="s">
         <v>555</v>
       </c>
       <c r="E437" t="s">
-        <v>585</v>
+        <v>556</v>
       </c>
       <c r="F437" t="s">
         <v>19</v>
@@ -13048,13 +13048,13 @@
         <v>7</v>
       </c>
       <c r="C440" t="s">
-        <v>554</v>
+        <v>589</v>
       </c>
       <c r="D440" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="E440" t="s">
-        <v>590</v>
+        <v>556</v>
       </c>
       <c r="F440" t="s">
         <v>24</v>
@@ -13328,13 +13328,13 @@
         <v>7</v>
       </c>
       <c r="C454" t="s">
-        <v>554</v>
+        <v>605</v>
       </c>
       <c r="D454" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="E454" t="s">
-        <v>606</v>
+        <v>556</v>
       </c>
       <c r="F454" t="s">
         <v>19</v>
@@ -13528,13 +13528,13 @@
         <v>7</v>
       </c>
       <c r="C464" t="s">
-        <v>608</v>
+        <v>621</v>
       </c>
       <c r="D464" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="E464" t="s">
-        <v>622</v>
+        <v>610</v>
       </c>
       <c r="F464" t="s">
         <v>24</v>
@@ -13548,13 +13548,13 @@
         <v>7</v>
       </c>
       <c r="C465" t="s">
-        <v>608</v>
+        <v>624</v>
       </c>
       <c r="D465" t="s">
         <v>609</v>
       </c>
       <c r="E465" t="s">
-        <v>624</v>
+        <v>610</v>
       </c>
       <c r="F465" t="s">
         <v>24</v>
@@ -13568,13 +13568,13 @@
         <v>7</v>
       </c>
       <c r="C466" t="s">
-        <v>608</v>
+        <v>626</v>
       </c>
       <c r="D466" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="E466" t="s">
-        <v>626</v>
+        <v>610</v>
       </c>
       <c r="F466" t="s">
         <v>24</v>
@@ -13588,13 +13588,13 @@
         <v>7</v>
       </c>
       <c r="C467" t="s">
-        <v>608</v>
+        <v>628</v>
       </c>
       <c r="D467" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="E467" t="s">
-        <v>629</v>
+        <v>610</v>
       </c>
       <c r="F467" t="s">
         <v>24</v>
@@ -13628,13 +13628,13 @@
         <v>7</v>
       </c>
       <c r="C469" t="s">
-        <v>608</v>
+        <v>632</v>
       </c>
       <c r="D469" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="E469" t="s">
-        <v>633</v>
+        <v>610</v>
       </c>
       <c r="F469" t="s">
         <v>24</v>
@@ -13708,13 +13708,13 @@
         <v>7</v>
       </c>
       <c r="C473" t="s">
-        <v>608</v>
+        <v>638</v>
       </c>
       <c r="D473" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="E473" t="s">
-        <v>638</v>
+        <v>610</v>
       </c>
       <c r="F473" t="s">
         <v>24</v>
@@ -14008,13 +14008,13 @@
         <v>7</v>
       </c>
       <c r="C488" t="s">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="D488" t="s">
         <v>654</v>
       </c>
       <c r="E488" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="F488" t="s">
         <v>611</v>
@@ -14128,13 +14128,13 @@
         <v>7</v>
       </c>
       <c r="C494" t="s">
-        <v>653</v>
+        <v>632</v>
       </c>
       <c r="D494" t="s">
         <v>665</v>
       </c>
       <c r="E494" t="s">
-        <v>633</v>
+        <v>655</v>
       </c>
       <c r="F494" t="s">
         <v>13</v>
@@ -14148,13 +14148,13 @@
         <v>110</v>
       </c>
       <c r="C495" t="s">
-        <v>653</v>
+        <v>632</v>
       </c>
       <c r="D495" t="s">
         <v>665</v>
       </c>
       <c r="E495" t="s">
-        <v>633</v>
+        <v>655</v>
       </c>
       <c r="F495" t="s">
         <v>16</v>
@@ -14208,13 +14208,13 @@
         <v>7</v>
       </c>
       <c r="C498" t="s">
-        <v>653</v>
+        <v>670</v>
       </c>
       <c r="D498" t="s">
         <v>654</v>
       </c>
       <c r="E498" t="s">
-        <v>670</v>
+        <v>655</v>
       </c>
       <c r="F498" t="s">
         <v>611</v>
@@ -14288,13 +14288,13 @@
         <v>110</v>
       </c>
       <c r="C502" t="s">
-        <v>653</v>
+        <v>675</v>
       </c>
       <c r="D502" t="s">
         <v>654</v>
       </c>
       <c r="E502" t="s">
-        <v>675</v>
+        <v>655</v>
       </c>
       <c r="F502" t="s">
         <v>19</v>
@@ -14388,13 +14388,13 @@
         <v>7</v>
       </c>
       <c r="C507" t="s">
-        <v>653</v>
+        <v>681</v>
       </c>
       <c r="D507" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="E507" t="s">
-        <v>682</v>
+        <v>655</v>
       </c>
       <c r="F507" t="s">
         <v>24</v>
@@ -14408,13 +14408,13 @@
         <v>7</v>
       </c>
       <c r="C508" t="s">
-        <v>653</v>
+        <v>684</v>
       </c>
       <c r="D508" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="E508" t="s">
-        <v>685</v>
+        <v>655</v>
       </c>
       <c r="F508" t="s">
         <v>611</v>
@@ -14428,13 +14428,13 @@
         <v>110</v>
       </c>
       <c r="C509" t="s">
-        <v>653</v>
+        <v>684</v>
       </c>
       <c r="D509" t="s">
         <v>687</v>
       </c>
       <c r="E509" t="s">
-        <v>685</v>
+        <v>655</v>
       </c>
       <c r="F509" t="s">
         <v>19</v>
@@ -14448,13 +14448,13 @@
         <v>7</v>
       </c>
       <c r="C510" t="s">
-        <v>653</v>
+        <v>689</v>
       </c>
       <c r="D510" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="E510" t="s">
-        <v>690</v>
+        <v>655</v>
       </c>
       <c r="F510" t="s">
         <v>24</v>
@@ -14488,13 +14488,13 @@
         <v>7</v>
       </c>
       <c r="C512" t="s">
-        <v>653</v>
+        <v>693</v>
       </c>
       <c r="D512" t="s">
         <v>654</v>
       </c>
       <c r="E512" t="s">
-        <v>693</v>
+        <v>655</v>
       </c>
       <c r="F512" t="s">
         <v>16</v>
@@ -14668,13 +14668,13 @@
         <v>110</v>
       </c>
       <c r="C521" t="s">
-        <v>653</v>
+        <v>704</v>
       </c>
       <c r="D521" t="s">
         <v>654</v>
       </c>
       <c r="E521" t="s">
-        <v>704</v>
+        <v>655</v>
       </c>
       <c r="F521" t="s">
         <v>19</v>
@@ -14688,13 +14688,13 @@
         <v>110</v>
       </c>
       <c r="C522" t="s">
-        <v>653</v>
+        <v>706</v>
       </c>
       <c r="D522" t="s">
         <v>654</v>
       </c>
       <c r="E522" t="s">
-        <v>706</v>
+        <v>655</v>
       </c>
       <c r="F522" t="s">
         <v>13</v>
@@ -14708,13 +14708,13 @@
         <v>7</v>
       </c>
       <c r="C523" t="s">
-        <v>653</v>
+        <v>708</v>
       </c>
       <c r="D523" t="s">
         <v>654</v>
       </c>
       <c r="E523" t="s">
-        <v>708</v>
+        <v>655</v>
       </c>
       <c r="F523" t="s">
         <v>24</v>
@@ -14748,13 +14748,13 @@
         <v>7</v>
       </c>
       <c r="C525" t="s">
+        <v>657</v>
+      </c>
+      <c r="D525" t="s">
         <v>711</v>
       </c>
-      <c r="D525" t="s">
+      <c r="E525" t="s">
         <v>712</v>
-      </c>
-      <c r="E525" t="s">
-        <v>657</v>
       </c>
       <c r="F525" t="s">
         <v>713</v>
@@ -14768,13 +14768,13 @@
         <v>7</v>
       </c>
       <c r="C526" t="s">
+        <v>657</v>
+      </c>
+      <c r="D526" t="s">
         <v>711</v>
       </c>
-      <c r="D526" t="s">
+      <c r="E526" t="s">
         <v>712</v>
-      </c>
-      <c r="E526" t="s">
-        <v>657</v>
       </c>
       <c r="F526" t="s">
         <v>713</v>
@@ -14788,13 +14788,13 @@
         <v>7</v>
       </c>
       <c r="C527" t="s">
+        <v>657</v>
+      </c>
+      <c r="D527" t="s">
         <v>711</v>
       </c>
-      <c r="D527" t="s">
+      <c r="E527" t="s">
         <v>712</v>
-      </c>
-      <c r="E527" t="s">
-        <v>657</v>
       </c>
       <c r="F527" t="s">
         <v>713</v>
@@ -14808,13 +14808,13 @@
         <v>7</v>
       </c>
       <c r="C528" t="s">
+        <v>657</v>
+      </c>
+      <c r="D528" t="s">
         <v>711</v>
       </c>
-      <c r="D528" t="s">
+      <c r="E528" t="s">
         <v>712</v>
-      </c>
-      <c r="E528" t="s">
-        <v>657</v>
       </c>
       <c r="F528" t="s">
         <v>713</v>
@@ -14828,13 +14828,13 @@
         <v>7</v>
       </c>
       <c r="C529" t="s">
+        <v>718</v>
+      </c>
+      <c r="D529" t="s">
         <v>711</v>
       </c>
-      <c r="D529" t="s">
+      <c r="E529" t="s">
         <v>712</v>
-      </c>
-      <c r="E529" t="s">
-        <v>718</v>
       </c>
       <c r="F529" t="s">
         <v>16</v>
@@ -14848,13 +14848,13 @@
         <v>7</v>
       </c>
       <c r="C530" t="s">
-        <v>711</v>
+        <v>657</v>
       </c>
       <c r="D530" t="s">
         <v>720</v>
       </c>
       <c r="E530" t="s">
-        <v>657</v>
+        <v>712</v>
       </c>
       <c r="F530" t="s">
         <v>713</v>
@@ -14868,13 +14868,13 @@
         <v>7</v>
       </c>
       <c r="C531" t="s">
+        <v>657</v>
+      </c>
+      <c r="D531" t="s">
         <v>711</v>
       </c>
-      <c r="D531" t="s">
+      <c r="E531" t="s">
         <v>712</v>
-      </c>
-      <c r="E531" t="s">
-        <v>657</v>
       </c>
       <c r="F531" t="s">
         <v>713</v>
@@ -14888,13 +14888,13 @@
         <v>7</v>
       </c>
       <c r="C532" t="s">
+        <v>657</v>
+      </c>
+      <c r="D532" t="s">
         <v>711</v>
       </c>
-      <c r="D532" t="s">
+      <c r="E532" t="s">
         <v>712</v>
-      </c>
-      <c r="E532" t="s">
-        <v>657</v>
       </c>
       <c r="F532" t="s">
         <v>713</v>
@@ -14908,13 +14908,13 @@
         <v>7</v>
       </c>
       <c r="C533" t="s">
+        <v>657</v>
+      </c>
+      <c r="D533" t="s">
         <v>711</v>
       </c>
-      <c r="D533" t="s">
+      <c r="E533" t="s">
         <v>712</v>
-      </c>
-      <c r="E533" t="s">
-        <v>657</v>
       </c>
       <c r="F533" t="s">
         <v>713</v>
@@ -14928,13 +14928,13 @@
         <v>7</v>
       </c>
       <c r="C534" t="s">
+        <v>657</v>
+      </c>
+      <c r="D534" t="s">
         <v>711</v>
       </c>
-      <c r="D534" t="s">
+      <c r="E534" t="s">
         <v>712</v>
-      </c>
-      <c r="E534" t="s">
-        <v>657</v>
       </c>
       <c r="F534" t="s">
         <v>713</v>
@@ -14948,13 +14948,13 @@
         <v>7</v>
       </c>
       <c r="C535" t="s">
+        <v>657</v>
+      </c>
+      <c r="D535" t="s">
         <v>711</v>
       </c>
-      <c r="D535" t="s">
+      <c r="E535" t="s">
         <v>712</v>
-      </c>
-      <c r="E535" t="s">
-        <v>657</v>
       </c>
       <c r="F535" t="s">
         <v>713</v>
@@ -14968,13 +14968,13 @@
         <v>7</v>
       </c>
       <c r="C536" t="s">
+        <v>727</v>
+      </c>
+      <c r="D536" t="s">
         <v>711</v>
       </c>
-      <c r="D536" t="s">
+      <c r="E536" t="s">
         <v>712</v>
-      </c>
-      <c r="E536" t="s">
-        <v>727</v>
       </c>
       <c r="F536" t="s">
         <v>16</v>
@@ -14988,13 +14988,13 @@
         <v>7</v>
       </c>
       <c r="C537" t="s">
+        <v>729</v>
+      </c>
+      <c r="D537" t="s">
         <v>711</v>
       </c>
-      <c r="D537" t="s">
+      <c r="E537" t="s">
         <v>712</v>
-      </c>
-      <c r="E537" t="s">
-        <v>729</v>
       </c>
       <c r="F537" t="s">
         <v>16</v>
@@ -15008,13 +15008,13 @@
         <v>7</v>
       </c>
       <c r="C538" t="s">
+        <v>657</v>
+      </c>
+      <c r="D538" t="s">
         <v>711</v>
       </c>
-      <c r="D538" t="s">
+      <c r="E538" t="s">
         <v>712</v>
-      </c>
-      <c r="E538" t="s">
-        <v>657</v>
       </c>
       <c r="F538" t="s">
         <v>713</v>
@@ -15028,13 +15028,13 @@
         <v>7</v>
       </c>
       <c r="C539" t="s">
+        <v>657</v>
+      </c>
+      <c r="D539" t="s">
         <v>711</v>
       </c>
-      <c r="D539" t="s">
+      <c r="E539" t="s">
         <v>712</v>
-      </c>
-      <c r="E539" t="s">
-        <v>657</v>
       </c>
       <c r="F539" t="s">
         <v>713</v>
@@ -15048,13 +15048,13 @@
         <v>7</v>
       </c>
       <c r="C540" t="s">
-        <v>711</v>
+        <v>657</v>
       </c>
       <c r="D540" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="E540" t="s">
-        <v>657</v>
+        <v>712</v>
       </c>
       <c r="F540" t="s">
         <v>713</v>
@@ -15068,13 +15068,13 @@
         <v>7</v>
       </c>
       <c r="C541" t="s">
+        <v>657</v>
+      </c>
+      <c r="D541" t="s">
         <v>711</v>
       </c>
-      <c r="D541" t="s">
+      <c r="E541" t="s">
         <v>712</v>
-      </c>
-      <c r="E541" t="s">
-        <v>657</v>
       </c>
       <c r="F541" t="s">
         <v>713</v>
@@ -15088,13 +15088,13 @@
         <v>7</v>
       </c>
       <c r="C542" t="s">
+        <v>657</v>
+      </c>
+      <c r="D542" t="s">
         <v>711</v>
       </c>
-      <c r="D542" t="s">
+      <c r="E542" t="s">
         <v>712</v>
-      </c>
-      <c r="E542" t="s">
-        <v>657</v>
       </c>
       <c r="F542" t="s">
         <v>713</v>
@@ -15108,13 +15108,13 @@
         <v>7</v>
       </c>
       <c r="C543" t="s">
+        <v>657</v>
+      </c>
+      <c r="D543" t="s">
         <v>711</v>
       </c>
-      <c r="D543" t="s">
+      <c r="E543" t="s">
         <v>712</v>
-      </c>
-      <c r="E543" t="s">
-        <v>657</v>
       </c>
       <c r="F543" t="s">
         <v>713</v>
@@ -15128,13 +15128,13 @@
         <v>7</v>
       </c>
       <c r="C544" t="s">
+        <v>657</v>
+      </c>
+      <c r="D544" t="s">
         <v>711</v>
       </c>
-      <c r="D544" t="s">
+      <c r="E544" t="s">
         <v>712</v>
-      </c>
-      <c r="E544" t="s">
-        <v>657</v>
       </c>
       <c r="F544" t="s">
         <v>713</v>
@@ -15148,13 +15148,13 @@
         <v>7</v>
       </c>
       <c r="C545" t="s">
-        <v>711</v>
+        <v>657</v>
       </c>
       <c r="D545" t="s">
         <v>738</v>
       </c>
       <c r="E545" t="s">
-        <v>657</v>
+        <v>712</v>
       </c>
       <c r="F545" t="s">
         <v>13</v>
@@ -15168,13 +15168,13 @@
         <v>7</v>
       </c>
       <c r="C546" t="s">
+        <v>657</v>
+      </c>
+      <c r="D546" t="s">
         <v>711</v>
       </c>
-      <c r="D546" t="s">
+      <c r="E546" t="s">
         <v>712</v>
-      </c>
-      <c r="E546" t="s">
-        <v>657</v>
       </c>
       <c r="F546" t="s">
         <v>713</v>
@@ -15188,13 +15188,13 @@
         <v>7</v>
       </c>
       <c r="C547" t="s">
+        <v>657</v>
+      </c>
+      <c r="D547" t="s">
         <v>711</v>
       </c>
-      <c r="D547" t="s">
+      <c r="E547" t="s">
         <v>712</v>
-      </c>
-      <c r="E547" t="s">
-        <v>657</v>
       </c>
       <c r="F547" t="s">
         <v>16</v>
@@ -15228,13 +15228,13 @@
         <v>7</v>
       </c>
       <c r="C549" t="s">
-        <v>742</v>
+        <v>746</v>
       </c>
       <c r="D549" t="s">
         <v>743</v>
       </c>
       <c r="E549" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="F549" t="s">
         <v>713</v>
@@ -15248,13 +15248,13 @@
         <v>7</v>
       </c>
       <c r="C550" t="s">
-        <v>742</v>
+        <v>748</v>
       </c>
       <c r="D550" t="s">
         <v>743</v>
       </c>
       <c r="E550" t="s">
-        <v>748</v>
+        <v>744</v>
       </c>
       <c r="F550" t="s">
         <v>713</v>
@@ -15408,13 +15408,13 @@
         <v>7</v>
       </c>
       <c r="C558" t="s">
-        <v>742</v>
+        <v>758</v>
       </c>
       <c r="D558" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="E558" t="s">
-        <v>759</v>
+        <v>744</v>
       </c>
       <c r="F558" t="s">
         <v>24</v>
@@ -15448,13 +15448,13 @@
         <v>7</v>
       </c>
       <c r="C560" t="s">
-        <v>742</v>
+        <v>762</v>
       </c>
       <c r="D560" t="s">
         <v>743</v>
       </c>
       <c r="E560" t="s">
-        <v>762</v>
+        <v>744</v>
       </c>
       <c r="F560" t="s">
         <v>713</v>
@@ -15468,13 +15468,13 @@
         <v>7</v>
       </c>
       <c r="C561" t="s">
-        <v>742</v>
+        <v>762</v>
       </c>
       <c r="D561" t="s">
         <v>743</v>
       </c>
       <c r="E561" t="s">
-        <v>762</v>
+        <v>744</v>
       </c>
       <c r="F561" t="s">
         <v>713</v>
@@ -15628,13 +15628,13 @@
         <v>7</v>
       </c>
       <c r="C569" t="s">
-        <v>742</v>
+        <v>773</v>
       </c>
       <c r="D569" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="E569" t="s">
-        <v>774</v>
+        <v>744</v>
       </c>
       <c r="F569" t="s">
         <v>713</v>
@@ -15711,7 +15711,7 @@
         <v>779</v>
       </c>
       <c r="D573" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="E573" t="s">
         <v>780</v>
@@ -15808,13 +15808,13 @@
         <v>7</v>
       </c>
       <c r="C578" t="s">
-        <v>779</v>
+        <v>787</v>
       </c>
       <c r="D578" t="s">
         <v>782</v>
       </c>
       <c r="E578" t="s">
-        <v>787</v>
+        <v>780</v>
       </c>
       <c r="F578" t="s">
         <v>713</v>
@@ -15828,13 +15828,13 @@
         <v>7</v>
       </c>
       <c r="C579" t="s">
-        <v>779</v>
+        <v>789</v>
       </c>
       <c r="D579" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="E579" t="s">
-        <v>790</v>
+        <v>780</v>
       </c>
       <c r="F579" t="s">
         <v>24</v>
@@ -15848,13 +15848,13 @@
         <v>7</v>
       </c>
       <c r="C580" t="s">
-        <v>779</v>
+        <v>792</v>
       </c>
       <c r="D580" t="s">
         <v>782</v>
       </c>
       <c r="E580" t="s">
-        <v>792</v>
+        <v>780</v>
       </c>
       <c r="F580" t="s">
         <v>713</v>
@@ -15868,13 +15868,13 @@
         <v>7</v>
       </c>
       <c r="C581" t="s">
-        <v>779</v>
+        <v>794</v>
       </c>
       <c r="D581" t="s">
         <v>782</v>
       </c>
       <c r="E581" t="s">
-        <v>794</v>
+        <v>780</v>
       </c>
       <c r="F581" t="s">
         <v>16</v>
@@ -15908,13 +15908,13 @@
         <v>7</v>
       </c>
       <c r="C583" t="s">
-        <v>779</v>
+        <v>797</v>
       </c>
       <c r="D583" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="E583" t="s">
-        <v>798</v>
+        <v>780</v>
       </c>
       <c r="F583" t="s">
         <v>24</v>
@@ -15928,13 +15928,13 @@
         <v>7</v>
       </c>
       <c r="C584" t="s">
-        <v>779</v>
+        <v>800</v>
       </c>
       <c r="D584" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="E584" t="s">
-        <v>801</v>
+        <v>780</v>
       </c>
       <c r="F584" t="s">
         <v>24</v>
@@ -15968,13 +15968,13 @@
         <v>7</v>
       </c>
       <c r="C586" t="s">
-        <v>779</v>
+        <v>804</v>
       </c>
       <c r="D586" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="E586" t="s">
-        <v>805</v>
+        <v>780</v>
       </c>
       <c r="F586" t="s">
         <v>24</v>
@@ -15988,13 +15988,13 @@
         <v>7</v>
       </c>
       <c r="C587" t="s">
-        <v>779</v>
+        <v>807</v>
       </c>
       <c r="D587" t="s">
         <v>782</v>
       </c>
       <c r="E587" t="s">
-        <v>807</v>
+        <v>780</v>
       </c>
       <c r="F587" t="s">
         <v>13</v>
@@ -16008,13 +16008,13 @@
         <v>7</v>
       </c>
       <c r="C588" t="s">
-        <v>779</v>
+        <v>809</v>
       </c>
       <c r="D588" t="s">
         <v>782</v>
       </c>
       <c r="E588" t="s">
-        <v>809</v>
+        <v>780</v>
       </c>
       <c r="F588" t="s">
         <v>713</v>
@@ -16208,13 +16208,13 @@
         <v>7</v>
       </c>
       <c r="C598" t="s">
-        <v>820</v>
+        <v>824</v>
       </c>
       <c r="D598" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="E598" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="F598" t="s">
         <v>16</v>
@@ -16288,13 +16288,13 @@
         <v>7</v>
       </c>
       <c r="C602" t="s">
-        <v>820</v>
+        <v>830</v>
       </c>
       <c r="D602" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="E602" t="s">
-        <v>831</v>
+        <v>822</v>
       </c>
       <c r="F602" t="s">
         <v>24</v>
@@ -16308,13 +16308,13 @@
         <v>7</v>
       </c>
       <c r="C603" t="s">
-        <v>820</v>
+        <v>833</v>
       </c>
       <c r="D603" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="E603" t="s">
-        <v>834</v>
+        <v>822</v>
       </c>
       <c r="F603" t="s">
         <v>24</v>
@@ -16328,13 +16328,13 @@
         <v>7</v>
       </c>
       <c r="C604" t="s">
-        <v>820</v>
+        <v>836</v>
       </c>
       <c r="D604" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="E604" t="s">
-        <v>837</v>
+        <v>822</v>
       </c>
       <c r="F604" t="s">
         <v>713</v>
@@ -16348,13 +16348,13 @@
         <v>7</v>
       </c>
       <c r="C605" t="s">
-        <v>820</v>
+        <v>839</v>
       </c>
       <c r="D605" t="s">
         <v>821</v>
       </c>
       <c r="E605" t="s">
-        <v>839</v>
+        <v>822</v>
       </c>
       <c r="F605" t="s">
         <v>24</v>
@@ -16408,13 +16408,13 @@
         <v>7</v>
       </c>
       <c r="C608" t="s">
-        <v>820</v>
+        <v>843</v>
       </c>
       <c r="D608" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="E608" t="s">
-        <v>844</v>
+        <v>822</v>
       </c>
       <c r="F608" t="s">
         <v>24</v>
@@ -16428,13 +16428,13 @@
         <v>7</v>
       </c>
       <c r="C609" t="s">
-        <v>820</v>
+        <v>846</v>
       </c>
       <c r="D609" t="s">
         <v>807</v>
       </c>
       <c r="E609" t="s">
-        <v>846</v>
+        <v>822</v>
       </c>
       <c r="F609" t="s">
         <v>713</v>
@@ -16468,13 +16468,13 @@
         <v>7</v>
       </c>
       <c r="C611" t="s">
-        <v>820</v>
+        <v>824</v>
       </c>
       <c r="D611" t="s">
         <v>849</v>
       </c>
       <c r="E611" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="F611" t="s">
         <v>24</v>
@@ -16488,13 +16488,13 @@
         <v>7</v>
       </c>
       <c r="C612" t="s">
-        <v>820</v>
+        <v>851</v>
       </c>
       <c r="D612" t="s">
         <v>821</v>
       </c>
       <c r="E612" t="s">
-        <v>851</v>
+        <v>822</v>
       </c>
       <c r="F612" t="s">
         <v>16</v>
@@ -16528,13 +16528,13 @@
         <v>7</v>
       </c>
       <c r="C614" t="s">
-        <v>820</v>
+        <v>854</v>
       </c>
       <c r="D614" t="s">
         <v>821</v>
       </c>
       <c r="E614" t="s">
-        <v>854</v>
+        <v>822</v>
       </c>
       <c r="F614" t="s">
         <v>713</v>
@@ -16728,13 +16728,13 @@
         <v>7</v>
       </c>
       <c r="C624" t="s">
-        <v>864</v>
+        <v>868</v>
       </c>
       <c r="D624" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="E624" t="s">
-        <v>869</v>
+        <v>866</v>
       </c>
       <c r="F624" t="s">
         <v>24</v>
@@ -16828,13 +16828,13 @@
         <v>7</v>
       </c>
       <c r="C629" t="s">
-        <v>864</v>
+        <v>876</v>
       </c>
       <c r="D629" t="s">
         <v>865</v>
       </c>
       <c r="E629" t="s">
-        <v>876</v>
+        <v>866</v>
       </c>
       <c r="F629" t="s">
         <v>24</v>
@@ -16888,13 +16888,13 @@
         <v>7</v>
       </c>
       <c r="C632" t="s">
-        <v>864</v>
+        <v>876</v>
       </c>
       <c r="D632" t="s">
         <v>880</v>
       </c>
       <c r="E632" t="s">
-        <v>876</v>
+        <v>866</v>
       </c>
       <c r="F632" t="s">
         <v>24</v>
@@ -16908,13 +16908,13 @@
         <v>7</v>
       </c>
       <c r="C633" t="s">
-        <v>864</v>
+        <v>882</v>
       </c>
       <c r="D633" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="E633" t="s">
-        <v>883</v>
+        <v>866</v>
       </c>
       <c r="F633" t="s">
         <v>24</v>
@@ -16928,13 +16928,13 @@
         <v>7</v>
       </c>
       <c r="C634" t="s">
-        <v>864</v>
+        <v>885</v>
       </c>
       <c r="D634" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="E634" t="s">
-        <v>886</v>
+        <v>866</v>
       </c>
       <c r="F634" t="s">
         <v>24</v>
@@ -16968,13 +16968,13 @@
         <v>7</v>
       </c>
       <c r="C636" t="s">
-        <v>864</v>
+        <v>889</v>
       </c>
       <c r="D636" t="s">
         <v>865</v>
       </c>
       <c r="E636" t="s">
-        <v>889</v>
+        <v>866</v>
       </c>
       <c r="F636" t="s">
         <v>713</v>
@@ -16988,13 +16988,13 @@
         <v>7</v>
       </c>
       <c r="C637" t="s">
-        <v>864</v>
+        <v>891</v>
       </c>
       <c r="D637" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="E637" t="s">
-        <v>892</v>
+        <v>866</v>
       </c>
       <c r="F637" t="s">
         <v>24</v>
@@ -17068,13 +17068,13 @@
         <v>7</v>
       </c>
       <c r="C641" t="s">
-        <v>864</v>
+        <v>897</v>
       </c>
       <c r="D641" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="E641" t="s">
-        <v>898</v>
+        <v>866</v>
       </c>
       <c r="F641" t="s">
         <v>16</v>
@@ -17088,13 +17088,13 @@
         <v>7</v>
       </c>
       <c r="C642" t="s">
-        <v>864</v>
+        <v>900</v>
       </c>
       <c r="D642" t="s">
         <v>865</v>
       </c>
       <c r="E642" t="s">
-        <v>900</v>
+        <v>866</v>
       </c>
       <c r="F642" t="s">
         <v>16</v>
@@ -17108,13 +17108,13 @@
         <v>7</v>
       </c>
       <c r="C643" t="s">
-        <v>864</v>
+        <v>902</v>
       </c>
       <c r="D643" t="s">
         <v>865</v>
       </c>
       <c r="E643" t="s">
-        <v>902</v>
+        <v>866</v>
       </c>
       <c r="F643" t="s">
         <v>16</v>
@@ -17168,13 +17168,13 @@
         <v>7</v>
       </c>
       <c r="C646" t="s">
-        <v>864</v>
+        <v>906</v>
       </c>
       <c r="D646" t="s">
         <v>865</v>
       </c>
       <c r="E646" t="s">
-        <v>906</v>
+        <v>866</v>
       </c>
       <c r="F646" t="s">
         <v>24</v>
@@ -17248,13 +17248,13 @@
         <v>7</v>
       </c>
       <c r="C650" t="s">
-        <v>910</v>
+        <v>914</v>
       </c>
       <c r="D650" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="E650" t="s">
-        <v>915</v>
+        <v>912</v>
       </c>
       <c r="F650" t="s">
         <v>16</v>
@@ -17288,13 +17288,13 @@
         <v>7</v>
       </c>
       <c r="C652" t="s">
-        <v>910</v>
+        <v>919</v>
       </c>
       <c r="D652" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="E652" t="s">
-        <v>920</v>
+        <v>912</v>
       </c>
       <c r="F652" t="s">
         <v>713</v>
@@ -17308,13 +17308,13 @@
         <v>7</v>
       </c>
       <c r="C653" t="s">
-        <v>910</v>
+        <v>919</v>
       </c>
       <c r="D653" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="E653" t="s">
-        <v>920</v>
+        <v>912</v>
       </c>
       <c r="F653" t="s">
         <v>713</v>
@@ -17328,13 +17328,13 @@
         <v>7</v>
       </c>
       <c r="C654" t="s">
-        <v>910</v>
+        <v>902</v>
       </c>
       <c r="D654" t="s">
         <v>865</v>
       </c>
       <c r="E654" t="s">
-        <v>902</v>
+        <v>912</v>
       </c>
       <c r="F654" t="s">
         <v>16</v>
@@ -17348,13 +17348,13 @@
         <v>7</v>
       </c>
       <c r="C655" t="s">
-        <v>910</v>
+        <v>919</v>
       </c>
       <c r="D655" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="E655" t="s">
-        <v>920</v>
+        <v>912</v>
       </c>
       <c r="F655" t="s">
         <v>713</v>
@@ -17368,13 +17368,13 @@
         <v>7</v>
       </c>
       <c r="C656" t="s">
-        <v>910</v>
+        <v>919</v>
       </c>
       <c r="D656" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="E656" t="s">
-        <v>920</v>
+        <v>912</v>
       </c>
       <c r="F656" t="s">
         <v>713</v>
@@ -17388,13 +17388,13 @@
         <v>7</v>
       </c>
       <c r="C657" t="s">
-        <v>910</v>
+        <v>926</v>
       </c>
       <c r="D657" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="E657" t="s">
-        <v>927</v>
+        <v>912</v>
       </c>
       <c r="F657" t="s">
         <v>16</v>
@@ -17408,13 +17408,13 @@
         <v>7</v>
       </c>
       <c r="C658" t="s">
-        <v>910</v>
+        <v>929</v>
       </c>
       <c r="D658" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="E658" t="s">
-        <v>930</v>
+        <v>912</v>
       </c>
       <c r="F658" t="s">
         <v>24</v>
@@ -17428,13 +17428,13 @@
         <v>7</v>
       </c>
       <c r="C659" t="s">
-        <v>910</v>
+        <v>889</v>
       </c>
       <c r="D659" t="s">
         <v>932</v>
       </c>
       <c r="E659" t="s">
-        <v>889</v>
+        <v>912</v>
       </c>
       <c r="F659" t="s">
         <v>24</v>
@@ -17448,13 +17448,13 @@
         <v>7</v>
       </c>
       <c r="C660" t="s">
-        <v>910</v>
+        <v>934</v>
       </c>
       <c r="D660" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="E660" t="s">
-        <v>935</v>
+        <v>912</v>
       </c>
       <c r="F660" t="s">
         <v>24</v>
@@ -17468,13 +17468,13 @@
         <v>7</v>
       </c>
       <c r="C661" t="s">
-        <v>910</v>
+        <v>919</v>
       </c>
       <c r="D661" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="E661" t="s">
-        <v>920</v>
+        <v>912</v>
       </c>
       <c r="F661" t="s">
         <v>713</v>
@@ -17488,13 +17488,13 @@
         <v>7</v>
       </c>
       <c r="C662" t="s">
-        <v>910</v>
+        <v>919</v>
       </c>
       <c r="D662" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="E662" t="s">
-        <v>920</v>
+        <v>912</v>
       </c>
       <c r="F662" t="s">
         <v>24</v>
@@ -17508,13 +17508,13 @@
         <v>7</v>
       </c>
       <c r="C663" t="s">
-        <v>910</v>
+        <v>939</v>
       </c>
       <c r="D663" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="E663" t="s">
-        <v>940</v>
+        <v>912</v>
       </c>
       <c r="F663" t="s">
         <v>24</v>
@@ -17528,13 +17528,13 @@
         <v>7</v>
       </c>
       <c r="C664" t="s">
-        <v>910</v>
+        <v>902</v>
       </c>
       <c r="D664" t="s">
         <v>942</v>
       </c>
       <c r="E664" t="s">
-        <v>902</v>
+        <v>912</v>
       </c>
       <c r="F664" t="s">
         <v>16</v>
@@ -17548,13 +17548,13 @@
         <v>7</v>
       </c>
       <c r="C665" t="s">
-        <v>910</v>
+        <v>944</v>
       </c>
       <c r="D665" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="E665" t="s">
-        <v>944</v>
+        <v>912</v>
       </c>
       <c r="F665" t="s">
         <v>713</v>
@@ -17568,13 +17568,13 @@
         <v>7</v>
       </c>
       <c r="C666" t="s">
-        <v>910</v>
+        <v>944</v>
       </c>
       <c r="D666" t="s">
         <v>911</v>
       </c>
       <c r="E666" t="s">
-        <v>944</v>
+        <v>912</v>
       </c>
       <c r="F666" t="s">
         <v>24</v>
@@ -17588,13 +17588,13 @@
         <v>7</v>
       </c>
       <c r="C667" t="s">
-        <v>910</v>
+        <v>947</v>
       </c>
       <c r="D667" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="E667" t="s">
-        <v>948</v>
+        <v>912</v>
       </c>
       <c r="F667" t="s">
         <v>24</v>
@@ -17608,13 +17608,13 @@
         <v>7</v>
       </c>
       <c r="C668" t="s">
-        <v>910</v>
+        <v>919</v>
       </c>
       <c r="D668" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="E668" t="s">
-        <v>920</v>
+        <v>912</v>
       </c>
       <c r="F668" t="s">
         <v>16</v>
@@ -17628,13 +17628,13 @@
         <v>7</v>
       </c>
       <c r="C669" t="s">
-        <v>910</v>
+        <v>902</v>
       </c>
       <c r="D669" t="s">
         <v>932</v>
       </c>
       <c r="E669" t="s">
-        <v>902</v>
+        <v>912</v>
       </c>
       <c r="F669" t="s">
         <v>16</v>
@@ -17648,13 +17648,13 @@
         <v>7</v>
       </c>
       <c r="C670" t="s">
-        <v>910</v>
+        <v>919</v>
       </c>
       <c r="D670" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="E670" t="s">
-        <v>920</v>
+        <v>912</v>
       </c>
       <c r="F670" t="s">
         <v>713</v>
@@ -17688,13 +17688,13 @@
         <v>7</v>
       </c>
       <c r="C672" t="s">
-        <v>910</v>
+        <v>919</v>
       </c>
       <c r="D672" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="E672" t="s">
-        <v>920</v>
+        <v>912</v>
       </c>
       <c r="F672" t="s">
         <v>16</v>
@@ -17708,13 +17708,13 @@
         <v>7</v>
       </c>
       <c r="C673" t="s">
-        <v>910</v>
+        <v>919</v>
       </c>
       <c r="D673" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="E673" t="s">
-        <v>920</v>
+        <v>912</v>
       </c>
       <c r="F673" t="s">
         <v>713</v>
@@ -17728,13 +17728,13 @@
         <v>7</v>
       </c>
       <c r="C674" t="s">
-        <v>910</v>
+        <v>902</v>
       </c>
       <c r="D674" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="E674" t="s">
-        <v>902</v>
+        <v>912</v>
       </c>
       <c r="F674" t="s">
         <v>16</v>
@@ -17768,13 +17768,13 @@
         <v>7</v>
       </c>
       <c r="C676" t="s">
-        <v>910</v>
+        <v>959</v>
       </c>
       <c r="D676" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="E676" t="s">
-        <v>959</v>
+        <v>912</v>
       </c>
       <c r="F676" t="s">
         <v>16</v>
@@ -17788,13 +17788,13 @@
         <v>7</v>
       </c>
       <c r="C677" t="s">
-        <v>910</v>
+        <v>919</v>
       </c>
       <c r="D677" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="E677" t="s">
-        <v>920</v>
+        <v>912</v>
       </c>
       <c r="F677" t="s">
         <v>713</v>
@@ -17808,13 +17808,13 @@
         <v>7</v>
       </c>
       <c r="C678" t="s">
-        <v>910</v>
+        <v>919</v>
       </c>
       <c r="D678" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="E678" t="s">
-        <v>920</v>
+        <v>912</v>
       </c>
       <c r="F678" t="s">
         <v>713</v>
@@ -17828,13 +17828,13 @@
         <v>7</v>
       </c>
       <c r="C679" t="s">
-        <v>910</v>
+        <v>934</v>
       </c>
       <c r="D679" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="E679" t="s">
-        <v>935</v>
+        <v>912</v>
       </c>
       <c r="F679" t="s">
         <v>24</v>
@@ -17848,13 +17848,13 @@
         <v>7</v>
       </c>
       <c r="C680" t="s">
-        <v>910</v>
+        <v>919</v>
       </c>
       <c r="D680" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="E680" t="s">
-        <v>920</v>
+        <v>912</v>
       </c>
       <c r="F680" t="s">
         <v>713</v>
@@ -17868,13 +17868,13 @@
         <v>7</v>
       </c>
       <c r="C681" t="s">
-        <v>910</v>
+        <v>919</v>
       </c>
       <c r="D681" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="E681" t="s">
-        <v>920</v>
+        <v>912</v>
       </c>
       <c r="F681" t="s">
         <v>713</v>
@@ -17908,13 +17908,13 @@
         <v>7</v>
       </c>
       <c r="C683" t="s">
-        <v>966</v>
+        <v>970</v>
       </c>
       <c r="D683" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="E683" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="F683" t="s">
         <v>24</v>
@@ -17928,13 +17928,13 @@
         <v>7</v>
       </c>
       <c r="C684" t="s">
-        <v>966</v>
+        <v>973</v>
       </c>
       <c r="D684" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="E684" t="s">
-        <v>974</v>
+        <v>968</v>
       </c>
       <c r="F684" t="s">
         <v>713</v>
@@ -17948,13 +17948,13 @@
         <v>7</v>
       </c>
       <c r="C685" t="s">
-        <v>966</v>
+        <v>973</v>
       </c>
       <c r="D685" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="E685" t="s">
-        <v>974</v>
+        <v>968</v>
       </c>
       <c r="F685" t="s">
         <v>713</v>
@@ -17968,13 +17968,13 @@
         <v>7</v>
       </c>
       <c r="C686" t="s">
-        <v>966</v>
+        <v>973</v>
       </c>
       <c r="D686" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="E686" t="s">
-        <v>974</v>
+        <v>968</v>
       </c>
       <c r="F686" t="s">
         <v>713</v>
@@ -17988,13 +17988,13 @@
         <v>7</v>
       </c>
       <c r="C687" t="s">
-        <v>966</v>
+        <v>973</v>
       </c>
       <c r="D687" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="E687" t="s">
-        <v>974</v>
+        <v>968</v>
       </c>
       <c r="F687" t="s">
         <v>713</v>
@@ -18008,13 +18008,13 @@
         <v>7</v>
       </c>
       <c r="C688" t="s">
-        <v>966</v>
+        <v>973</v>
       </c>
       <c r="D688" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="E688" t="s">
-        <v>974</v>
+        <v>968</v>
       </c>
       <c r="F688" t="s">
         <v>713</v>
@@ -18028,13 +18028,13 @@
         <v>7</v>
       </c>
       <c r="C689" t="s">
-        <v>966</v>
+        <v>970</v>
       </c>
       <c r="D689" t="s">
         <v>980</v>
       </c>
       <c r="E689" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="F689" t="s">
         <v>24</v>
@@ -18048,13 +18048,13 @@
         <v>7</v>
       </c>
       <c r="C690" t="s">
-        <v>966</v>
+        <v>982</v>
       </c>
       <c r="D690" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="E690" t="s">
-        <v>983</v>
+        <v>968</v>
       </c>
       <c r="F690" t="s">
         <v>24</v>
@@ -18068,13 +18068,13 @@
         <v>7</v>
       </c>
       <c r="C691" t="s">
-        <v>966</v>
+        <v>973</v>
       </c>
       <c r="D691" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="E691" t="s">
-        <v>974</v>
+        <v>968</v>
       </c>
       <c r="F691" t="s">
         <v>13</v>
@@ -18088,13 +18088,13 @@
         <v>7</v>
       </c>
       <c r="C692" t="s">
-        <v>966</v>
+        <v>986</v>
       </c>
       <c r="D692" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="E692" t="s">
-        <v>986</v>
+        <v>968</v>
       </c>
       <c r="F692" t="s">
         <v>16</v>
@@ -18108,13 +18108,13 @@
         <v>7</v>
       </c>
       <c r="C693" t="s">
-        <v>966</v>
+        <v>988</v>
       </c>
       <c r="D693" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="E693" t="s">
-        <v>989</v>
+        <v>968</v>
       </c>
       <c r="F693" t="s">
         <v>24</v>
@@ -18128,13 +18128,13 @@
         <v>7</v>
       </c>
       <c r="C694" t="s">
-        <v>966</v>
+        <v>991</v>
       </c>
       <c r="D694" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="E694" t="s">
-        <v>992</v>
+        <v>968</v>
       </c>
       <c r="F694" t="s">
         <v>16</v>
@@ -18148,13 +18148,13 @@
         <v>7</v>
       </c>
       <c r="C695" t="s">
-        <v>966</v>
+        <v>994</v>
       </c>
       <c r="D695" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="E695" t="s">
-        <v>995</v>
+        <v>968</v>
       </c>
       <c r="F695" t="s">
         <v>24</v>
@@ -18168,13 +18168,13 @@
         <v>7</v>
       </c>
       <c r="C696" t="s">
-        <v>966</v>
+        <v>973</v>
       </c>
       <c r="D696" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="E696" t="s">
-        <v>974</v>
+        <v>968</v>
       </c>
       <c r="F696" t="s">
         <v>713</v>
@@ -18188,13 +18188,13 @@
         <v>7</v>
       </c>
       <c r="C697" t="s">
-        <v>966</v>
+        <v>998</v>
       </c>
       <c r="D697" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="E697" t="s">
-        <v>999</v>
+        <v>968</v>
       </c>
       <c r="F697" t="s">
         <v>24</v>
@@ -18208,13 +18208,13 @@
         <v>7</v>
       </c>
       <c r="C698" t="s">
-        <v>966</v>
+        <v>1001</v>
       </c>
       <c r="D698" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="E698" t="s">
-        <v>1002</v>
+        <v>968</v>
       </c>
       <c r="F698" t="s">
         <v>24</v>
@@ -18228,13 +18228,13 @@
         <v>7</v>
       </c>
       <c r="C699" t="s">
-        <v>966</v>
+        <v>973</v>
       </c>
       <c r="D699" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="E699" t="s">
-        <v>974</v>
+        <v>968</v>
       </c>
       <c r="F699" t="s">
         <v>16</v>
@@ -18248,13 +18248,13 @@
         <v>7</v>
       </c>
       <c r="C700" t="s">
-        <v>966</v>
+        <v>1005</v>
       </c>
       <c r="D700" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="E700" t="s">
-        <v>1006</v>
+        <v>968</v>
       </c>
       <c r="F700" t="s">
         <v>24</v>
@@ -18268,13 +18268,13 @@
         <v>7</v>
       </c>
       <c r="C701" t="s">
-        <v>966</v>
+        <v>973</v>
       </c>
       <c r="D701" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="E701" t="s">
-        <v>974</v>
+        <v>968</v>
       </c>
       <c r="F701" t="s">
         <v>16</v>
@@ -18288,13 +18288,13 @@
         <v>7</v>
       </c>
       <c r="C702" t="s">
-        <v>966</v>
+        <v>1009</v>
       </c>
       <c r="D702" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="E702" t="s">
-        <v>1010</v>
+        <v>968</v>
       </c>
       <c r="F702" t="s">
         <v>24</v>
@@ -18308,13 +18308,13 @@
         <v>7</v>
       </c>
       <c r="C703" t="s">
-        <v>966</v>
+        <v>1012</v>
       </c>
       <c r="D703" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="E703" t="s">
-        <v>1012</v>
+        <v>968</v>
       </c>
       <c r="F703" t="s">
         <v>24</v>
@@ -18328,13 +18328,13 @@
         <v>7</v>
       </c>
       <c r="C704" t="s">
-        <v>966</v>
+        <v>973</v>
       </c>
       <c r="D704" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="E704" t="s">
-        <v>974</v>
+        <v>968</v>
       </c>
       <c r="F704" t="s">
         <v>713</v>
@@ -18348,13 +18348,13 @@
         <v>7</v>
       </c>
       <c r="C705" t="s">
-        <v>966</v>
+        <v>1015</v>
       </c>
       <c r="D705" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="E705" t="s">
-        <v>1015</v>
+        <v>968</v>
       </c>
       <c r="F705" t="s">
         <v>16</v>
@@ -18368,13 +18368,13 @@
         <v>7</v>
       </c>
       <c r="C706" t="s">
-        <v>966</v>
+        <v>973</v>
       </c>
       <c r="D706" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="E706" t="s">
-        <v>974</v>
+        <v>968</v>
       </c>
       <c r="F706" t="s">
         <v>713</v>
@@ -18388,13 +18388,13 @@
         <v>7</v>
       </c>
       <c r="C707" t="s">
-        <v>966</v>
+        <v>973</v>
       </c>
       <c r="D707" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="E707" t="s">
-        <v>974</v>
+        <v>968</v>
       </c>
       <c r="F707" t="s">
         <v>16</v>
@@ -18408,13 +18408,13 @@
         <v>7</v>
       </c>
       <c r="C708" t="s">
-        <v>966</v>
+        <v>1019</v>
       </c>
       <c r="D708" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="E708" t="s">
-        <v>1019</v>
+        <v>968</v>
       </c>
       <c r="F708" t="s">
         <v>24</v>
@@ -18428,13 +18428,13 @@
         <v>7</v>
       </c>
       <c r="C709" t="s">
-        <v>966</v>
+        <v>973</v>
       </c>
       <c r="D709" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="E709" t="s">
-        <v>974</v>
+        <v>968</v>
       </c>
       <c r="F709" t="s">
         <v>713</v>
@@ -18448,13 +18448,13 @@
         <v>7</v>
       </c>
       <c r="C710" t="s">
-        <v>966</v>
+        <v>1022</v>
       </c>
       <c r="D710" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="E710" t="s">
-        <v>1023</v>
+        <v>968</v>
       </c>
       <c r="F710" t="s">
         <v>24</v>
@@ -18468,13 +18468,13 @@
         <v>7</v>
       </c>
       <c r="C711" t="s">
-        <v>966</v>
+        <v>973</v>
       </c>
       <c r="D711" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="E711" t="s">
-        <v>974</v>
+        <v>968</v>
       </c>
       <c r="F711" t="s">
         <v>713</v>
@@ -18488,13 +18488,13 @@
         <v>7</v>
       </c>
       <c r="C712" t="s">
-        <v>966</v>
+        <v>973</v>
       </c>
       <c r="D712" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="E712" t="s">
-        <v>974</v>
+        <v>968</v>
       </c>
       <c r="F712" t="s">
         <v>713</v>
@@ -18508,13 +18508,13 @@
         <v>7</v>
       </c>
       <c r="C713" t="s">
-        <v>966</v>
+        <v>982</v>
       </c>
       <c r="D713" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="E713" t="s">
-        <v>983</v>
+        <v>968</v>
       </c>
       <c r="F713" t="s">
         <v>24</v>
@@ -18528,13 +18528,13 @@
         <v>7</v>
       </c>
       <c r="C714" t="s">
-        <v>966</v>
+        <v>973</v>
       </c>
       <c r="D714" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="E714" t="s">
-        <v>974</v>
+        <v>968</v>
       </c>
       <c r="F714" t="s">
         <v>713</v>
@@ -18548,13 +18548,13 @@
         <v>7</v>
       </c>
       <c r="C715" t="s">
-        <v>966</v>
+        <v>998</v>
       </c>
       <c r="D715" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="E715" t="s">
-        <v>999</v>
+        <v>968</v>
       </c>
       <c r="F715" t="s">
         <v>24</v>
@@ -18568,13 +18568,13 @@
         <v>7</v>
       </c>
       <c r="C716" t="s">
-        <v>966</v>
+        <v>973</v>
       </c>
       <c r="D716" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="E716" t="s">
-        <v>974</v>
+        <v>968</v>
       </c>
       <c r="F716" t="s">
         <v>713</v>
@@ -18588,13 +18588,13 @@
         <v>7</v>
       </c>
       <c r="C717" t="s">
-        <v>966</v>
+        <v>973</v>
       </c>
       <c r="D717" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="E717" t="s">
-        <v>974</v>
+        <v>968</v>
       </c>
       <c r="F717" t="s">
         <v>713</v>
@@ -18628,13 +18628,13 @@
         <v>7</v>
       </c>
       <c r="C719" t="s">
-        <v>1032</v>
+        <v>1036</v>
       </c>
       <c r="D719" t="s">
         <v>1033</v>
       </c>
       <c r="E719" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="F719" t="s">
         <v>713</v>
@@ -18648,13 +18648,13 @@
         <v>7</v>
       </c>
       <c r="C720" t="s">
-        <v>1032</v>
+        <v>1036</v>
       </c>
       <c r="D720" t="s">
         <v>1033</v>
       </c>
       <c r="E720" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="F720" t="s">
         <v>713</v>
@@ -18668,13 +18668,13 @@
         <v>7</v>
       </c>
       <c r="C721" t="s">
-        <v>1032</v>
+        <v>1036</v>
       </c>
       <c r="D721" t="s">
         <v>1033</v>
       </c>
       <c r="E721" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="F721" t="s">
         <v>713</v>
@@ -18688,13 +18688,13 @@
         <v>7</v>
       </c>
       <c r="C722" t="s">
-        <v>1032</v>
+        <v>1036</v>
       </c>
       <c r="D722" t="s">
         <v>1033</v>
       </c>
       <c r="E722" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="F722" t="s">
         <v>713</v>
@@ -18708,13 +18708,13 @@
         <v>7</v>
       </c>
       <c r="C723" t="s">
-        <v>1032</v>
+        <v>1036</v>
       </c>
       <c r="D723" t="s">
         <v>1033</v>
       </c>
       <c r="E723" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="F723" t="s">
         <v>713</v>
@@ -18728,13 +18728,13 @@
         <v>7</v>
       </c>
       <c r="C724" t="s">
-        <v>1032</v>
+        <v>1036</v>
       </c>
       <c r="D724" t="s">
         <v>1033</v>
       </c>
       <c r="E724" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="F724" t="s">
         <v>16</v>
@@ -18748,13 +18748,13 @@
         <v>7</v>
       </c>
       <c r="C725" t="s">
-        <v>1032</v>
+        <v>1043</v>
       </c>
       <c r="D725" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="E725" t="s">
-        <v>1044</v>
+        <v>1034</v>
       </c>
       <c r="F725" t="s">
         <v>16</v>
@@ -18768,13 +18768,13 @@
         <v>7</v>
       </c>
       <c r="C726" t="s">
-        <v>1032</v>
+        <v>1046</v>
       </c>
       <c r="D726" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="E726" t="s">
-        <v>1047</v>
+        <v>1034</v>
       </c>
       <c r="F726" t="s">
         <v>16</v>
@@ -18788,13 +18788,13 @@
         <v>7</v>
       </c>
       <c r="C727" t="s">
-        <v>1032</v>
+        <v>1036</v>
       </c>
       <c r="D727" t="s">
         <v>1033</v>
       </c>
       <c r="E727" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="F727" t="s">
         <v>713</v>
@@ -18808,13 +18808,13 @@
         <v>7</v>
       </c>
       <c r="C728" t="s">
-        <v>1032</v>
+        <v>1036</v>
       </c>
       <c r="D728" t="s">
         <v>1033</v>
       </c>
       <c r="E728" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="F728" t="s">
         <v>713</v>
@@ -18828,13 +18828,13 @@
         <v>7</v>
       </c>
       <c r="C729" t="s">
-        <v>1032</v>
+        <v>1051</v>
       </c>
       <c r="D729" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="E729" t="s">
-        <v>1052</v>
+        <v>1034</v>
       </c>
       <c r="F729" t="s">
         <v>24</v>
@@ -18848,13 +18848,13 @@
         <v>7</v>
       </c>
       <c r="C730" t="s">
-        <v>1032</v>
+        <v>1036</v>
       </c>
       <c r="D730" t="s">
         <v>1033</v>
       </c>
       <c r="E730" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="F730" t="s">
         <v>13</v>
@@ -18868,13 +18868,13 @@
         <v>7</v>
       </c>
       <c r="C731" t="s">
-        <v>1032</v>
+        <v>1051</v>
       </c>
       <c r="D731" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="E731" t="s">
-        <v>1052</v>
+        <v>1034</v>
       </c>
       <c r="F731" t="s">
         <v>24</v>
@@ -18888,13 +18888,13 @@
         <v>7</v>
       </c>
       <c r="C732" t="s">
-        <v>1032</v>
+        <v>1056</v>
       </c>
       <c r="D732" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="E732" t="s">
-        <v>1057</v>
+        <v>1034</v>
       </c>
       <c r="F732" t="s">
         <v>24</v>
@@ -18908,13 +18908,13 @@
         <v>7</v>
       </c>
       <c r="C733" t="s">
-        <v>1032</v>
+        <v>1059</v>
       </c>
       <c r="D733" t="s">
         <v>1033</v>
       </c>
       <c r="E733" t="s">
-        <v>1059</v>
+        <v>1034</v>
       </c>
       <c r="F733" t="s">
         <v>24</v>
@@ -18928,13 +18928,13 @@
         <v>7</v>
       </c>
       <c r="C734" t="s">
-        <v>1032</v>
+        <v>1061</v>
       </c>
       <c r="D734" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="E734" t="s">
-        <v>1062</v>
+        <v>1034</v>
       </c>
       <c r="F734" t="s">
         <v>24</v>
@@ -18948,13 +18948,13 @@
         <v>7</v>
       </c>
       <c r="C735" t="s">
-        <v>1032</v>
+        <v>1036</v>
       </c>
       <c r="D735" t="s">
         <v>1033</v>
       </c>
       <c r="E735" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="F735" t="s">
         <v>713</v>
@@ -18968,13 +18968,13 @@
         <v>7</v>
       </c>
       <c r="C736" t="s">
-        <v>1032</v>
+        <v>1065</v>
       </c>
       <c r="D736" t="s">
         <v>1033</v>
       </c>
       <c r="E736" t="s">
-        <v>1065</v>
+        <v>1034</v>
       </c>
       <c r="F736" t="s">
         <v>713</v>
@@ -18988,13 +18988,13 @@
         <v>7</v>
       </c>
       <c r="C737" t="s">
-        <v>1032</v>
+        <v>1036</v>
       </c>
       <c r="D737" t="s">
         <v>1033</v>
       </c>
       <c r="E737" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="F737" t="s">
         <v>16</v>
@@ -19008,13 +19008,13 @@
         <v>7</v>
       </c>
       <c r="C738" t="s">
-        <v>1032</v>
+        <v>1068</v>
       </c>
       <c r="D738" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="E738" t="s">
-        <v>1068</v>
+        <v>1034</v>
       </c>
       <c r="F738" t="s">
         <v>16</v>
@@ -19028,13 +19028,13 @@
         <v>7</v>
       </c>
       <c r="C739" t="s">
-        <v>1032</v>
+        <v>1036</v>
       </c>
       <c r="D739" t="s">
         <v>1033</v>
       </c>
       <c r="E739" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="F739" t="s">
         <v>713</v>
@@ -19048,13 +19048,13 @@
         <v>7</v>
       </c>
       <c r="C740" t="s">
-        <v>1032</v>
+        <v>1036</v>
       </c>
       <c r="D740" t="s">
         <v>1033</v>
       </c>
       <c r="E740" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="F740" t="s">
         <v>713</v>
@@ -19068,13 +19068,13 @@
         <v>7</v>
       </c>
       <c r="C741" t="s">
-        <v>1032</v>
+        <v>1072</v>
       </c>
       <c r="D741" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="E741" t="s">
-        <v>1073</v>
+        <v>1034</v>
       </c>
       <c r="F741" t="s">
         <v>24</v>
@@ -19088,13 +19088,13 @@
         <v>7</v>
       </c>
       <c r="C742" t="s">
-        <v>1032</v>
+        <v>1075</v>
       </c>
       <c r="D742" t="s">
         <v>1033</v>
       </c>
       <c r="E742" t="s">
-        <v>1075</v>
+        <v>1034</v>
       </c>
       <c r="F742" t="s">
         <v>16</v>
@@ -19108,13 +19108,13 @@
         <v>7</v>
       </c>
       <c r="C743" t="s">
-        <v>1032</v>
+        <v>1036</v>
       </c>
       <c r="D743" t="s">
         <v>1033</v>
       </c>
       <c r="E743" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="F743" t="s">
         <v>713</v>
@@ -19148,13 +19148,13 @@
         <v>7</v>
       </c>
       <c r="C745" t="s">
-        <v>1032</v>
+        <v>1079</v>
       </c>
       <c r="D745" t="s">
         <v>1033</v>
       </c>
       <c r="E745" t="s">
-        <v>1079</v>
+        <v>1034</v>
       </c>
       <c r="F745" t="s">
         <v>24</v>
@@ -19168,13 +19168,13 @@
         <v>7</v>
       </c>
       <c r="C746" t="s">
-        <v>1032</v>
+        <v>1036</v>
       </c>
       <c r="D746" t="s">
         <v>1033</v>
       </c>
       <c r="E746" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="F746" t="s">
         <v>713</v>
@@ -19188,13 +19188,13 @@
         <v>7</v>
       </c>
       <c r="C747" t="s">
-        <v>1032</v>
+        <v>1036</v>
       </c>
       <c r="D747" t="s">
         <v>1033</v>
       </c>
       <c r="E747" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="F747" t="s">
         <v>713</v>
@@ -19208,13 +19208,13 @@
         <v>7</v>
       </c>
       <c r="C748" t="s">
-        <v>1032</v>
+        <v>1036</v>
       </c>
       <c r="D748" t="s">
         <v>1033</v>
       </c>
       <c r="E748" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="F748" t="s">
         <v>713</v>
@@ -19228,13 +19228,13 @@
         <v>7</v>
       </c>
       <c r="C749" t="s">
-        <v>1032</v>
+        <v>1036</v>
       </c>
       <c r="D749" t="s">
         <v>1033</v>
       </c>
       <c r="E749" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="F749" t="s">
         <v>713</v>
@@ -19268,13 +19268,13 @@
         <v>7</v>
       </c>
       <c r="C751" t="s">
-        <v>1085</v>
+        <v>1089</v>
       </c>
       <c r="D751" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="E751" t="s">
-        <v>1090</v>
+        <v>1087</v>
       </c>
       <c r="F751" t="s">
         <v>24</v>
@@ -19288,13 +19288,13 @@
         <v>7</v>
       </c>
       <c r="C752" t="s">
-        <v>1085</v>
+        <v>1092</v>
       </c>
       <c r="D752" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="E752" t="s">
-        <v>1093</v>
+        <v>1087</v>
       </c>
       <c r="F752" t="s">
         <v>713</v>
@@ -19308,13 +19308,13 @@
         <v>7</v>
       </c>
       <c r="C753" t="s">
-        <v>1085</v>
+        <v>1092</v>
       </c>
       <c r="D753" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="E753" t="s">
-        <v>1093</v>
+        <v>1087</v>
       </c>
       <c r="F753" t="s">
         <v>713</v>
@@ -19328,13 +19328,13 @@
         <v>7</v>
       </c>
       <c r="C754" t="s">
-        <v>1085</v>
+        <v>1092</v>
       </c>
       <c r="D754" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="E754" t="s">
-        <v>1093</v>
+        <v>1087</v>
       </c>
       <c r="F754" t="s">
         <v>713</v>
@@ -19348,13 +19348,13 @@
         <v>7</v>
       </c>
       <c r="C755" t="s">
-        <v>1085</v>
+        <v>1092</v>
       </c>
       <c r="D755" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="E755" t="s">
-        <v>1093</v>
+        <v>1087</v>
       </c>
       <c r="F755" t="s">
         <v>713</v>
@@ -19368,13 +19368,13 @@
         <v>7</v>
       </c>
       <c r="C756" t="s">
-        <v>1085</v>
+        <v>1092</v>
       </c>
       <c r="D756" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="E756" t="s">
-        <v>1093</v>
+        <v>1087</v>
       </c>
       <c r="F756" t="s">
         <v>713</v>
@@ -19388,13 +19388,13 @@
         <v>7</v>
       </c>
       <c r="C757" t="s">
-        <v>1085</v>
+        <v>1092</v>
       </c>
       <c r="D757" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="E757" t="s">
-        <v>1093</v>
+        <v>1087</v>
       </c>
       <c r="F757" t="s">
         <v>713</v>
@@ -19411,7 +19411,7 @@
         <v>1085</v>
       </c>
       <c r="D758" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="E758" t="s">
         <v>1087</v>
@@ -19428,13 +19428,13 @@
         <v>7</v>
       </c>
       <c r="C759" t="s">
-        <v>1085</v>
+        <v>1065</v>
       </c>
       <c r="D759" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="E759" t="s">
-        <v>1065</v>
+        <v>1087</v>
       </c>
       <c r="F759" t="s">
         <v>16</v>
@@ -19448,13 +19448,13 @@
         <v>7</v>
       </c>
       <c r="C760" t="s">
-        <v>1085</v>
+        <v>1092</v>
       </c>
       <c r="D760" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="E760" t="s">
-        <v>1093</v>
+        <v>1087</v>
       </c>
       <c r="F760" t="s">
         <v>713</v>
@@ -19468,13 +19468,13 @@
         <v>7</v>
       </c>
       <c r="C761" t="s">
-        <v>1085</v>
+        <v>1092</v>
       </c>
       <c r="D761" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="E761" t="s">
-        <v>1093</v>
+        <v>1087</v>
       </c>
       <c r="F761" t="s">
         <v>713</v>
@@ -19488,13 +19488,13 @@
         <v>7</v>
       </c>
       <c r="C762" t="s">
-        <v>1085</v>
+        <v>1065</v>
       </c>
       <c r="D762" t="s">
         <v>1104</v>
       </c>
       <c r="E762" t="s">
-        <v>1065</v>
+        <v>1087</v>
       </c>
       <c r="F762" t="s">
         <v>24</v>
@@ -19508,13 +19508,13 @@
         <v>7</v>
       </c>
       <c r="C763" t="s">
-        <v>1085</v>
+        <v>1092</v>
       </c>
       <c r="D763" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="E763" t="s">
-        <v>1093</v>
+        <v>1087</v>
       </c>
       <c r="F763" t="s">
         <v>713</v>
@@ -19528,13 +19528,13 @@
         <v>7</v>
       </c>
       <c r="C764" t="s">
-        <v>1085</v>
+        <v>1107</v>
       </c>
       <c r="D764" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="E764" t="s">
-        <v>1108</v>
+        <v>1087</v>
       </c>
       <c r="F764" t="s">
         <v>24</v>
@@ -19548,13 +19548,13 @@
         <v>7</v>
       </c>
       <c r="C765" t="s">
-        <v>1085</v>
+        <v>1092</v>
       </c>
       <c r="D765" t="s">
         <v>1086</v>
       </c>
       <c r="E765" t="s">
-        <v>1093</v>
+        <v>1087</v>
       </c>
       <c r="F765" t="s">
         <v>24</v>
@@ -19568,13 +19568,13 @@
         <v>7</v>
       </c>
       <c r="C766" t="s">
-        <v>1085</v>
+        <v>1111</v>
       </c>
       <c r="D766" t="s">
         <v>1104</v>
       </c>
       <c r="E766" t="s">
-        <v>1111</v>
+        <v>1087</v>
       </c>
       <c r="F766" t="s">
         <v>24</v>
@@ -19588,13 +19588,13 @@
         <v>7</v>
       </c>
       <c r="C767" t="s">
-        <v>1085</v>
+        <v>1113</v>
       </c>
       <c r="D767" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="E767" t="s">
-        <v>1114</v>
+        <v>1087</v>
       </c>
       <c r="F767" t="s">
         <v>24</v>
@@ -19608,13 +19608,13 @@
         <v>7</v>
       </c>
       <c r="C768" t="s">
-        <v>1085</v>
+        <v>1092</v>
       </c>
       <c r="D768" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="E768" t="s">
-        <v>1093</v>
+        <v>1087</v>
       </c>
       <c r="F768" t="s">
         <v>713</v>
@@ -19628,13 +19628,13 @@
         <v>7</v>
       </c>
       <c r="C769" t="s">
-        <v>1085</v>
+        <v>1092</v>
       </c>
       <c r="D769" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="E769" t="s">
-        <v>1093</v>
+        <v>1087</v>
       </c>
       <c r="F769" t="s">
         <v>713</v>
@@ -19648,13 +19648,13 @@
         <v>7</v>
       </c>
       <c r="C770" t="s">
-        <v>1085</v>
+        <v>1118</v>
       </c>
       <c r="D770" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="E770" t="s">
-        <v>1119</v>
+        <v>1087</v>
       </c>
       <c r="F770" t="s">
         <v>24</v>
@@ -19668,13 +19668,13 @@
         <v>7</v>
       </c>
       <c r="C771" t="s">
-        <v>1085</v>
+        <v>1092</v>
       </c>
       <c r="D771" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="E771" t="s">
-        <v>1093</v>
+        <v>1087</v>
       </c>
       <c r="F771" t="s">
         <v>713</v>
@@ -19688,13 +19688,13 @@
         <v>7</v>
       </c>
       <c r="C772" t="s">
-        <v>1085</v>
+        <v>1092</v>
       </c>
       <c r="D772" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="E772" t="s">
-        <v>1093</v>
+        <v>1087</v>
       </c>
       <c r="F772" t="s">
         <v>713</v>
@@ -19708,13 +19708,13 @@
         <v>7</v>
       </c>
       <c r="C773" t="s">
-        <v>1085</v>
+        <v>1092</v>
       </c>
       <c r="D773" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="E773" t="s">
-        <v>1093</v>
+        <v>1087</v>
       </c>
       <c r="F773" t="s">
         <v>713</v>
@@ -19728,13 +19728,13 @@
         <v>7</v>
       </c>
       <c r="C774" t="s">
-        <v>1085</v>
+        <v>1124</v>
       </c>
       <c r="D774" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="E774" t="s">
-        <v>1125</v>
+        <v>1087</v>
       </c>
       <c r="F774" t="s">
         <v>24</v>
@@ -19748,13 +19748,13 @@
         <v>7</v>
       </c>
       <c r="C775" t="s">
-        <v>1085</v>
+        <v>1092</v>
       </c>
       <c r="D775" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="E775" t="s">
-        <v>1093</v>
+        <v>1087</v>
       </c>
       <c r="F775" t="s">
         <v>713</v>
@@ -19788,13 +19788,13 @@
         <v>7</v>
       </c>
       <c r="C777" t="s">
-        <v>1128</v>
+        <v>1132</v>
       </c>
       <c r="D777" t="s">
         <v>1129</v>
       </c>
       <c r="E777" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="F777" t="s">
         <v>713</v>
@@ -19808,13 +19808,13 @@
         <v>7</v>
       </c>
       <c r="C778" t="s">
-        <v>1128</v>
+        <v>1134</v>
       </c>
       <c r="D778" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="E778" t="s">
-        <v>1135</v>
+        <v>1130</v>
       </c>
       <c r="F778" t="s">
         <v>24</v>
@@ -19828,13 +19828,13 @@
         <v>7</v>
       </c>
       <c r="C779" t="s">
-        <v>1128</v>
+        <v>1137</v>
       </c>
       <c r="D779" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="E779" t="s">
-        <v>1138</v>
+        <v>1130</v>
       </c>
       <c r="F779" t="s">
         <v>24</v>
@@ -19848,13 +19848,13 @@
         <v>7</v>
       </c>
       <c r="C780" t="s">
-        <v>1128</v>
+        <v>1132</v>
       </c>
       <c r="D780" t="s">
         <v>1129</v>
       </c>
       <c r="E780" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="F780" t="s">
         <v>713</v>
@@ -19868,13 +19868,13 @@
         <v>7</v>
       </c>
       <c r="C781" t="s">
-        <v>1128</v>
+        <v>1132</v>
       </c>
       <c r="D781" t="s">
         <v>1129</v>
       </c>
       <c r="E781" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="F781" t="s">
         <v>713</v>
@@ -19888,13 +19888,13 @@
         <v>7</v>
       </c>
       <c r="C782" t="s">
-        <v>1128</v>
+        <v>1142</v>
       </c>
       <c r="D782" t="s">
         <v>1129</v>
       </c>
       <c r="E782" t="s">
-        <v>1142</v>
+        <v>1130</v>
       </c>
       <c r="F782" t="s">
         <v>713</v>
@@ -19908,13 +19908,13 @@
         <v>7</v>
       </c>
       <c r="C783" t="s">
-        <v>1128</v>
+        <v>1132</v>
       </c>
       <c r="D783" t="s">
         <v>1129</v>
       </c>
       <c r="E783" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="F783" t="s">
         <v>713</v>
@@ -19928,13 +19928,13 @@
         <v>7</v>
       </c>
       <c r="C784" t="s">
-        <v>1128</v>
+        <v>1132</v>
       </c>
       <c r="D784" t="s">
         <v>1129</v>
       </c>
       <c r="E784" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="F784" t="s">
         <v>713</v>
@@ -19948,13 +19948,13 @@
         <v>7</v>
       </c>
       <c r="C785" t="s">
-        <v>1128</v>
+        <v>1132</v>
       </c>
       <c r="D785" t="s">
         <v>1129</v>
       </c>
       <c r="E785" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="F785" t="s">
         <v>713</v>
@@ -19968,13 +19968,13 @@
         <v>7</v>
       </c>
       <c r="C786" t="s">
-        <v>1128</v>
+        <v>1132</v>
       </c>
       <c r="D786" t="s">
         <v>1129</v>
       </c>
       <c r="E786" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="F786" t="s">
         <v>713</v>
@@ -19988,13 +19988,13 @@
         <v>7</v>
       </c>
       <c r="C787" t="s">
-        <v>1128</v>
+        <v>1132</v>
       </c>
       <c r="D787" t="s">
         <v>1129</v>
       </c>
       <c r="E787" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="F787" t="s">
         <v>713</v>
@@ -20008,13 +20008,13 @@
         <v>7</v>
       </c>
       <c r="C788" t="s">
-        <v>1128</v>
+        <v>1132</v>
       </c>
       <c r="D788" t="s">
         <v>1129</v>
       </c>
       <c r="E788" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="F788" t="s">
         <v>713</v>
@@ -20048,13 +20048,13 @@
         <v>7</v>
       </c>
       <c r="C790" t="s">
-        <v>1128</v>
+        <v>1132</v>
       </c>
       <c r="D790" t="s">
         <v>1129</v>
       </c>
       <c r="E790" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="F790" t="s">
         <v>713</v>
@@ -20068,13 +20068,13 @@
         <v>7</v>
       </c>
       <c r="C791" t="s">
-        <v>1128</v>
+        <v>1142</v>
       </c>
       <c r="D791" t="s">
         <v>1153</v>
       </c>
       <c r="E791" t="s">
-        <v>1142</v>
+        <v>1130</v>
       </c>
       <c r="F791" t="s">
         <v>24</v>
@@ -20088,13 +20088,13 @@
         <v>7</v>
       </c>
       <c r="C792" t="s">
-        <v>1128</v>
+        <v>1155</v>
       </c>
       <c r="D792" t="s">
         <v>1150</v>
       </c>
       <c r="E792" t="s">
-        <v>1155</v>
+        <v>1130</v>
       </c>
       <c r="F792" t="s">
         <v>24</v>
@@ -20108,13 +20108,13 @@
         <v>7</v>
       </c>
       <c r="C793" t="s">
-        <v>1128</v>
+        <v>1132</v>
       </c>
       <c r="D793" t="s">
         <v>1129</v>
       </c>
       <c r="E793" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="F793" t="s">
         <v>713</v>
@@ -20128,13 +20128,13 @@
         <v>7</v>
       </c>
       <c r="C794" t="s">
-        <v>1128</v>
+        <v>1132</v>
       </c>
       <c r="D794" t="s">
         <v>1158</v>
       </c>
       <c r="E794" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="F794" t="s">
         <v>24</v>
@@ -20148,13 +20148,13 @@
         <v>7</v>
       </c>
       <c r="C795" t="s">
-        <v>1128</v>
+        <v>1160</v>
       </c>
       <c r="D795" t="s">
         <v>1129</v>
       </c>
       <c r="E795" t="s">
-        <v>1160</v>
+        <v>1130</v>
       </c>
       <c r="F795" t="s">
         <v>24</v>
@@ -20168,13 +20168,13 @@
         <v>7</v>
       </c>
       <c r="C796" t="s">
-        <v>1128</v>
+        <v>1132</v>
       </c>
       <c r="D796" t="s">
         <v>1129</v>
       </c>
       <c r="E796" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="F796" t="s">
         <v>713</v>
@@ -20188,13 +20188,13 @@
         <v>7</v>
       </c>
       <c r="C797" t="s">
-        <v>1128</v>
+        <v>1163</v>
       </c>
       <c r="D797" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="E797" t="s">
-        <v>1164</v>
+        <v>1130</v>
       </c>
       <c r="F797" t="s">
         <v>24</v>
@@ -20208,13 +20208,13 @@
         <v>7</v>
       </c>
       <c r="C798" t="s">
-        <v>1128</v>
+        <v>1166</v>
       </c>
       <c r="D798" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="E798" t="s">
-        <v>1167</v>
+        <v>1130</v>
       </c>
       <c r="F798" t="s">
         <v>24</v>
@@ -20228,13 +20228,13 @@
         <v>7</v>
       </c>
       <c r="C799" t="s">
-        <v>1128</v>
+        <v>1132</v>
       </c>
       <c r="D799" t="s">
         <v>1129</v>
       </c>
       <c r="E799" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="F799" t="s">
         <v>713</v>
@@ -20248,13 +20248,13 @@
         <v>7</v>
       </c>
       <c r="C800" t="s">
-        <v>1128</v>
+        <v>1132</v>
       </c>
       <c r="D800" t="s">
         <v>1129</v>
       </c>
       <c r="E800" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="F800" t="s">
         <v>713</v>
@@ -20268,13 +20268,13 @@
         <v>7</v>
       </c>
       <c r="C801" t="s">
-        <v>1128</v>
+        <v>1132</v>
       </c>
       <c r="D801" t="s">
         <v>1129</v>
       </c>
       <c r="E801" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="F801" t="s">
         <v>713</v>
@@ -20288,13 +20288,13 @@
         <v>7</v>
       </c>
       <c r="C802" t="s">
-        <v>1128</v>
+        <v>1132</v>
       </c>
       <c r="D802" t="s">
         <v>1129</v>
       </c>
       <c r="E802" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="F802" t="s">
         <v>713</v>
@@ -20308,13 +20308,13 @@
         <v>7</v>
       </c>
       <c r="C803" t="s">
-        <v>1128</v>
+        <v>1132</v>
       </c>
       <c r="D803" t="s">
         <v>1129</v>
       </c>
       <c r="E803" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="F803" t="s">
         <v>713</v>
@@ -20328,13 +20328,13 @@
         <v>7</v>
       </c>
       <c r="C804" t="s">
-        <v>1128</v>
+        <v>1132</v>
       </c>
       <c r="D804" t="s">
         <v>1129</v>
       </c>
       <c r="E804" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="F804" t="s">
         <v>713</v>
@@ -20348,13 +20348,13 @@
         <v>7</v>
       </c>
       <c r="C805" t="s">
-        <v>1128</v>
+        <v>1132</v>
       </c>
       <c r="D805" t="s">
         <v>1129</v>
       </c>
       <c r="E805" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="F805" t="s">
         <v>713</v>
@@ -20368,13 +20368,13 @@
         <v>7</v>
       </c>
       <c r="C806" t="s">
-        <v>1128</v>
+        <v>1132</v>
       </c>
       <c r="D806" t="s">
         <v>1129</v>
       </c>
       <c r="E806" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="F806" t="s">
         <v>713</v>
@@ -20388,13 +20388,13 @@
         <v>7</v>
       </c>
       <c r="C807" t="s">
-        <v>1128</v>
+        <v>1132</v>
       </c>
       <c r="D807" t="s">
         <v>1129</v>
       </c>
       <c r="E807" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="F807" t="s">
         <v>713</v>
@@ -20468,13 +20468,13 @@
         <v>7</v>
       </c>
       <c r="C811" t="s">
-        <v>1178</v>
+        <v>1184</v>
       </c>
       <c r="D811" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="E811" t="s">
-        <v>1185</v>
+        <v>1180</v>
       </c>
       <c r="F811" t="s">
         <v>24</v>
@@ -20528,13 +20528,13 @@
         <v>7</v>
       </c>
       <c r="C814" t="s">
-        <v>1178</v>
+        <v>1184</v>
       </c>
       <c r="D814" t="s">
         <v>1179</v>
       </c>
       <c r="E814" t="s">
-        <v>1185</v>
+        <v>1180</v>
       </c>
       <c r="F814" t="s">
         <v>713</v>
@@ -20548,13 +20548,13 @@
         <v>7</v>
       </c>
       <c r="C815" t="s">
-        <v>1178</v>
+        <v>1190</v>
       </c>
       <c r="D815" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="E815" t="s">
-        <v>1191</v>
+        <v>1180</v>
       </c>
       <c r="F815" t="s">
         <v>24</v>
@@ -20668,13 +20668,13 @@
         <v>7</v>
       </c>
       <c r="C821" t="s">
-        <v>1178</v>
+        <v>1198</v>
       </c>
       <c r="D821" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="E821" t="s">
-        <v>1199</v>
+        <v>1180</v>
       </c>
       <c r="F821" t="s">
         <v>16</v>
@@ -20688,13 +20688,13 @@
         <v>7</v>
       </c>
       <c r="C822" t="s">
-        <v>1178</v>
+        <v>1201</v>
       </c>
       <c r="D822" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="E822" t="s">
-        <v>1202</v>
+        <v>1180</v>
       </c>
       <c r="F822" t="s">
         <v>713</v>
@@ -20708,13 +20708,13 @@
         <v>7</v>
       </c>
       <c r="C823" t="s">
-        <v>1178</v>
+        <v>1201</v>
       </c>
       <c r="D823" t="s">
         <v>1179</v>
       </c>
       <c r="E823" t="s">
-        <v>1202</v>
+        <v>1180</v>
       </c>
       <c r="F823" t="s">
         <v>713</v>
@@ -20728,13 +20728,13 @@
         <v>7</v>
       </c>
       <c r="C824" t="s">
-        <v>1178</v>
+        <v>1201</v>
       </c>
       <c r="D824" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="E824" t="s">
-        <v>1202</v>
+        <v>1180</v>
       </c>
       <c r="F824" t="s">
         <v>713</v>
@@ -20748,13 +20748,13 @@
         <v>7</v>
       </c>
       <c r="C825" t="s">
-        <v>1178</v>
+        <v>1201</v>
       </c>
       <c r="D825" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="E825" t="s">
-        <v>1202</v>
+        <v>1180</v>
       </c>
       <c r="F825" t="s">
         <v>713</v>
@@ -20768,13 +20768,13 @@
         <v>7</v>
       </c>
       <c r="C826" t="s">
-        <v>1178</v>
+        <v>1201</v>
       </c>
       <c r="D826" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="E826" t="s">
-        <v>1202</v>
+        <v>1180</v>
       </c>
       <c r="F826" t="s">
         <v>713</v>
@@ -20788,13 +20788,13 @@
         <v>7</v>
       </c>
       <c r="C827" t="s">
-        <v>1178</v>
+        <v>1201</v>
       </c>
       <c r="D827" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="E827" t="s">
-        <v>1202</v>
+        <v>1180</v>
       </c>
       <c r="F827" t="s">
         <v>713</v>
@@ -20808,13 +20808,13 @@
         <v>7</v>
       </c>
       <c r="C828" t="s">
-        <v>1178</v>
+        <v>1201</v>
       </c>
       <c r="D828" t="s">
         <v>1179</v>
       </c>
       <c r="E828" t="s">
-        <v>1202</v>
+        <v>1180</v>
       </c>
       <c r="F828" t="s">
         <v>713</v>
@@ -20848,13 +20848,13 @@
         <v>7</v>
       </c>
       <c r="C830" t="s">
-        <v>1178</v>
+        <v>1184</v>
       </c>
       <c r="D830" t="s">
         <v>1179</v>
       </c>
       <c r="E830" t="s">
-        <v>1185</v>
+        <v>1180</v>
       </c>
       <c r="F830" t="s">
         <v>713</v>
@@ -21048,13 +21048,13 @@
         <v>7</v>
       </c>
       <c r="C840" t="s">
-        <v>1220</v>
+        <v>1224</v>
       </c>
       <c r="D840" t="s">
         <v>1221</v>
       </c>
       <c r="E840" t="s">
-        <v>1224</v>
+        <v>1222</v>
       </c>
       <c r="F840" t="s">
         <v>713</v>
@@ -21068,13 +21068,13 @@
         <v>7</v>
       </c>
       <c r="C841" t="s">
-        <v>1220</v>
+        <v>1224</v>
       </c>
       <c r="D841" t="s">
         <v>1221</v>
       </c>
       <c r="E841" t="s">
-        <v>1224</v>
+        <v>1222</v>
       </c>
       <c r="F841" t="s">
         <v>713</v>
@@ -21088,13 +21088,13 @@
         <v>7</v>
       </c>
       <c r="C842" t="s">
-        <v>1220</v>
+        <v>1224</v>
       </c>
       <c r="D842" t="s">
         <v>1221</v>
       </c>
       <c r="E842" t="s">
-        <v>1224</v>
+        <v>1222</v>
       </c>
       <c r="F842" t="s">
         <v>713</v>
@@ -21108,13 +21108,13 @@
         <v>7</v>
       </c>
       <c r="C843" t="s">
-        <v>1220</v>
+        <v>1224</v>
       </c>
       <c r="D843" t="s">
         <v>1221</v>
       </c>
       <c r="E843" t="s">
-        <v>1224</v>
+        <v>1222</v>
       </c>
       <c r="F843" t="s">
         <v>713</v>
@@ -21128,13 +21128,13 @@
         <v>7</v>
       </c>
       <c r="C844" t="s">
-        <v>1220</v>
+        <v>1224</v>
       </c>
       <c r="D844" t="s">
         <v>1221</v>
       </c>
       <c r="E844" t="s">
-        <v>1224</v>
+        <v>1222</v>
       </c>
       <c r="F844" t="s">
         <v>713</v>
@@ -21148,13 +21148,13 @@
         <v>7</v>
       </c>
       <c r="C845" t="s">
-        <v>1220</v>
+        <v>1224</v>
       </c>
       <c r="D845" t="s">
         <v>1221</v>
       </c>
       <c r="E845" t="s">
-        <v>1224</v>
+        <v>1222</v>
       </c>
       <c r="F845" t="s">
         <v>713</v>
@@ -21168,13 +21168,13 @@
         <v>7</v>
       </c>
       <c r="C846" t="s">
-        <v>1220</v>
+        <v>1224</v>
       </c>
       <c r="D846" t="s">
         <v>1221</v>
       </c>
       <c r="E846" t="s">
-        <v>1224</v>
+        <v>1222</v>
       </c>
       <c r="F846" t="s">
         <v>713</v>
@@ -21188,13 +21188,13 @@
         <v>7</v>
       </c>
       <c r="C847" t="s">
-        <v>1220</v>
+        <v>1232</v>
       </c>
       <c r="D847" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="E847" t="s">
-        <v>1232</v>
+        <v>1222</v>
       </c>
       <c r="F847" t="s">
         <v>713</v>
@@ -21208,13 +21208,13 @@
         <v>7</v>
       </c>
       <c r="C848" t="s">
-        <v>1220</v>
+        <v>1232</v>
       </c>
       <c r="D848" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="E848" t="s">
-        <v>1232</v>
+        <v>1222</v>
       </c>
       <c r="F848" t="s">
         <v>713</v>
@@ -21228,13 +21228,13 @@
         <v>7</v>
       </c>
       <c r="C849" t="s">
-        <v>1220</v>
+        <v>1232</v>
       </c>
       <c r="D849" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="E849" t="s">
-        <v>1232</v>
+        <v>1222</v>
       </c>
       <c r="F849" t="s">
         <v>713</v>
@@ -21248,13 +21248,13 @@
         <v>7</v>
       </c>
       <c r="C850" t="s">
-        <v>1220</v>
+        <v>1232</v>
       </c>
       <c r="D850" t="s">
         <v>1236</v>
       </c>
       <c r="E850" t="s">
-        <v>1232</v>
+        <v>1222</v>
       </c>
       <c r="F850" t="s">
         <v>713</v>
@@ -21268,13 +21268,13 @@
         <v>7</v>
       </c>
       <c r="C851" t="s">
-        <v>1220</v>
+        <v>1232</v>
       </c>
       <c r="D851" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="E851" t="s">
-        <v>1232</v>
+        <v>1222</v>
       </c>
       <c r="F851" t="s">
         <v>713</v>
@@ -21288,13 +21288,13 @@
         <v>7</v>
       </c>
       <c r="C852" t="s">
-        <v>1220</v>
+        <v>1232</v>
       </c>
       <c r="D852" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="E852" t="s">
-        <v>1232</v>
+        <v>1222</v>
       </c>
       <c r="F852" t="s">
         <v>713</v>
@@ -21308,13 +21308,13 @@
         <v>7</v>
       </c>
       <c r="C853" t="s">
-        <v>1220</v>
+        <v>1224</v>
       </c>
       <c r="D853" t="s">
         <v>1221</v>
       </c>
       <c r="E853" t="s">
-        <v>1224</v>
+        <v>1222</v>
       </c>
       <c r="F853" t="s">
         <v>713</v>
@@ -21328,13 +21328,13 @@
         <v>7</v>
       </c>
       <c r="C854" t="s">
-        <v>1220</v>
+        <v>1224</v>
       </c>
       <c r="D854" t="s">
         <v>1221</v>
       </c>
       <c r="E854" t="s">
-        <v>1224</v>
+        <v>1222</v>
       </c>
       <c r="F854" t="s">
         <v>16</v>
@@ -21348,13 +21348,13 @@
         <v>7</v>
       </c>
       <c r="C855" t="s">
-        <v>1220</v>
+        <v>1224</v>
       </c>
       <c r="D855" t="s">
         <v>1221</v>
       </c>
       <c r="E855" t="s">
-        <v>1224</v>
+        <v>1222</v>
       </c>
       <c r="F855" t="s">
         <v>16</v>
@@ -21368,13 +21368,13 @@
         <v>7</v>
       </c>
       <c r="C856" t="s">
-        <v>1220</v>
+        <v>1224</v>
       </c>
       <c r="D856" t="s">
         <v>1221</v>
       </c>
       <c r="E856" t="s">
-        <v>1224</v>
+        <v>1222</v>
       </c>
       <c r="F856" t="s">
         <v>16</v>
@@ -21388,13 +21388,13 @@
         <v>7</v>
       </c>
       <c r="C857" t="s">
-        <v>1220</v>
+        <v>1224</v>
       </c>
       <c r="D857" t="s">
         <v>1221</v>
       </c>
       <c r="E857" t="s">
-        <v>1224</v>
+        <v>1222</v>
       </c>
       <c r="F857" t="s">
         <v>713</v>
@@ -21408,13 +21408,13 @@
         <v>7</v>
       </c>
       <c r="C858" t="s">
-        <v>1220</v>
+        <v>1224</v>
       </c>
       <c r="D858" t="s">
         <v>1221</v>
       </c>
       <c r="E858" t="s">
-        <v>1224</v>
+        <v>1222</v>
       </c>
       <c r="F858" t="s">
         <v>713</v>
@@ -21428,13 +21428,13 @@
         <v>7</v>
       </c>
       <c r="C859" t="s">
-        <v>1220</v>
+        <v>1224</v>
       </c>
       <c r="D859" t="s">
         <v>1221</v>
       </c>
       <c r="E859" t="s">
-        <v>1224</v>
+        <v>1222</v>
       </c>
       <c r="F859" t="s">
         <v>16</v>
@@ -21448,13 +21448,13 @@
         <v>7</v>
       </c>
       <c r="C860" t="s">
-        <v>1220</v>
+        <v>1224</v>
       </c>
       <c r="D860" t="s">
         <v>1221</v>
       </c>
       <c r="E860" t="s">
-        <v>1224</v>
+        <v>1222</v>
       </c>
       <c r="F860" t="s">
         <v>713</v>
@@ -21468,13 +21468,13 @@
         <v>7</v>
       </c>
       <c r="C861" t="s">
-        <v>1220</v>
+        <v>1224</v>
       </c>
       <c r="D861" t="s">
         <v>1221</v>
       </c>
       <c r="E861" t="s">
-        <v>1224</v>
+        <v>1222</v>
       </c>
       <c r="F861" t="s">
         <v>713</v>
@@ -21488,13 +21488,13 @@
         <v>7</v>
       </c>
       <c r="C862" t="s">
-        <v>1220</v>
+        <v>1224</v>
       </c>
       <c r="D862" t="s">
         <v>1221</v>
       </c>
       <c r="E862" t="s">
-        <v>1224</v>
+        <v>1222</v>
       </c>
       <c r="F862" t="s">
         <v>713</v>
@@ -21508,13 +21508,13 @@
         <v>7</v>
       </c>
       <c r="C863" t="s">
-        <v>1220</v>
+        <v>1224</v>
       </c>
       <c r="D863" t="s">
         <v>1221</v>
       </c>
       <c r="E863" t="s">
-        <v>1224</v>
+        <v>1222</v>
       </c>
       <c r="F863" t="s">
         <v>713</v>
@@ -21528,13 +21528,13 @@
         <v>7</v>
       </c>
       <c r="C864" t="s">
-        <v>1220</v>
+        <v>1224</v>
       </c>
       <c r="D864" t="s">
         <v>1221</v>
       </c>
       <c r="E864" t="s">
-        <v>1224</v>
+        <v>1222</v>
       </c>
       <c r="F864" t="s">
         <v>713</v>
@@ -21548,13 +21548,13 @@
         <v>7</v>
       </c>
       <c r="C865" t="s">
-        <v>1220</v>
+        <v>1224</v>
       </c>
       <c r="D865" t="s">
         <v>1221</v>
       </c>
       <c r="E865" t="s">
-        <v>1224</v>
+        <v>1222</v>
       </c>
       <c r="F865" t="s">
         <v>713</v>
@@ -21568,13 +21568,13 @@
         <v>7</v>
       </c>
       <c r="C866" t="s">
-        <v>1220</v>
+        <v>1224</v>
       </c>
       <c r="D866" t="s">
         <v>1221</v>
       </c>
       <c r="E866" t="s">
-        <v>1224</v>
+        <v>1222</v>
       </c>
       <c r="F866" t="s">
         <v>713</v>
@@ -22148,13 +22148,13 @@
         <v>7</v>
       </c>
       <c r="C895" t="s">
-        <v>1281</v>
+        <v>1289</v>
       </c>
       <c r="D895" t="s">
         <v>1282</v>
       </c>
       <c r="E895" t="s">
-        <v>1289</v>
+        <v>1283</v>
       </c>
       <c r="F895" t="s">
         <v>713</v>
@@ -22348,13 +22348,13 @@
         <v>7</v>
       </c>
       <c r="C905" t="s">
-        <v>1299</v>
+        <v>1302</v>
       </c>
       <c r="D905" t="s">
         <v>1282</v>
       </c>
       <c r="E905" t="s">
-        <v>1302</v>
+        <v>1300</v>
       </c>
       <c r="F905" t="s">
         <v>713</v>

--- a/api/2/clv2/xlsx/pt/HumanitarianPlan.xlsx
+++ b/api/2/clv2/xlsx/pt/HumanitarianPlan.xlsx
@@ -22,12 +22,12 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:plan-end-date</t>
+  </si>
+  <si>
     <t>codeforiati:plan-start-date</t>
   </si>
   <si>
-    <t>codeforiati:plan-end-date</t>
-  </si>
-  <si>
     <t>codeforiati:plan-year</t>
   </si>
   <si>
@@ -40,12 +40,12 @@
     <t>active</t>
   </si>
   <si>
+    <t>2025-12-31</t>
+  </si>
+  <si>
     <t>2025-01-01</t>
   </si>
   <si>
-    <t>2025-12-31</t>
-  </si>
-  <si>
     <t>2025</t>
   </si>
   <si>
@@ -217,12 +217,12 @@
     <t>HAFG24</t>
   </si>
   <si>
+    <t>2024-12-31</t>
+  </si>
+  <si>
     <t>2024-01-01</t>
   </si>
   <si>
-    <t>2024-12-31</t>
-  </si>
-  <si>
     <t>2024</t>
   </si>
   <si>
@@ -421,12 +421,12 @@
     <t>HAFG23</t>
   </si>
   <si>
+    <t>2023-12-31</t>
+  </si>
+  <si>
     <t>2023-01-01</t>
   </si>
   <si>
-    <t>2023-12-31</t>
-  </si>
-  <si>
     <t>2023</t>
   </si>
   <si>
@@ -493,21 +493,21 @@
     <t>OMNG2223</t>
   </si>
   <si>
+    <t>2023-05-31</t>
+  </si>
+  <si>
     <t>2022-12-01</t>
   </si>
   <si>
-    <t>2023-05-31</t>
-  </si>
-  <si>
     <t>OMOZ23</t>
   </si>
   <si>
+    <t>2023-09-30</t>
+  </si>
+  <si>
     <t>2023-03-01</t>
   </si>
   <si>
-    <t>2023-09-30</t>
-  </si>
-  <si>
     <t>HMOZ23</t>
   </si>
   <si>
@@ -553,12 +553,12 @@
     <t>RRSDN23</t>
   </si>
   <si>
+    <t>2023-10-31</t>
+  </si>
+  <si>
     <t>2023-05-01</t>
   </si>
   <si>
-    <t>2023-10-31</t>
-  </si>
-  <si>
     <t>HSDN23</t>
   </si>
   <si>
@@ -601,12 +601,12 @@
     <t>HAFG22</t>
   </si>
   <si>
+    <t>2022-12-31</t>
+  </si>
+  <si>
     <t>2022-01-01</t>
   </si>
   <si>
-    <t>2022-12-31</t>
-  </si>
-  <si>
     <t>2022</t>
   </si>
   <si>
@@ -631,12 +631,12 @@
     <t>OCUB2223</t>
   </si>
   <si>
+    <t>2023-03-31</t>
+  </si>
+  <si>
     <t>2022-10-20</t>
   </si>
   <si>
-    <t>2023-03-31</t>
-  </si>
-  <si>
     <t>RDRCRRP22</t>
   </si>
   <si>
@@ -652,12 +652,12 @@
     <t>FHTI2223</t>
   </si>
   <si>
+    <t>2023-04-15</t>
+  </si>
+  <si>
     <t>2022-10-16</t>
   </si>
   <si>
-    <t>2023-04-15</t>
-  </si>
-  <si>
     <t>FHTI22</t>
   </si>
   <si>
@@ -688,24 +688,24 @@
     <t>FMWI22</t>
   </si>
   <si>
+    <t>2022-05-31</t>
+  </si>
+  <si>
     <t>2022-02-26</t>
   </si>
   <si>
-    <t>2022-05-31</t>
-  </si>
-  <si>
     <t>HMLI22</t>
   </si>
   <si>
     <t>FMOZ22</t>
   </si>
   <si>
+    <t>2022-09-30</t>
+  </si>
+  <si>
     <t>2022-04-01</t>
   </si>
   <si>
-    <t>2022-09-30</t>
-  </si>
-  <si>
     <t>HMOZ22</t>
   </si>
   <si>
@@ -736,12 +736,12 @@
     <t>OPHL2122</t>
   </si>
   <si>
+    <t>2022-06-30</t>
+  </si>
+  <si>
     <t>2021-12-24</t>
   </si>
   <si>
-    <t>2022-06-30</t>
-  </si>
-  <si>
     <t>RREG22</t>
   </si>
   <si>
@@ -805,12 +805,12 @@
     <t>FAFG21</t>
   </si>
   <si>
+    <t>2021-12-31</t>
+  </si>
+  <si>
     <t>2021-09-01</t>
   </si>
   <si>
-    <t>2021-12-31</t>
-  </si>
-  <si>
     <t>2021</t>
   </si>
   <si>
@@ -862,12 +862,12 @@
     <t>FPSE21</t>
   </si>
   <si>
+    <t>2021-08-27</t>
+  </si>
+  <si>
     <t>2021-05-27</t>
   </si>
   <si>
-    <t>2021-08-27</t>
-  </si>
-  <si>
     <t>HETH21</t>
   </si>
   <si>
@@ -880,24 +880,24 @@
     <t>FHTI2122</t>
   </si>
   <si>
+    <t>2022-02-15</t>
+  </si>
+  <si>
     <t>2021-08-16</t>
   </si>
   <si>
-    <t>2022-02-15</t>
-  </si>
-  <si>
     <t>HHTI21</t>
   </si>
   <si>
     <t>FHND2021</t>
   </si>
   <si>
+    <t>2021-06-30</t>
+  </si>
+  <si>
     <t>2020-11-15</t>
   </si>
   <si>
-    <t>2021-06-30</t>
-  </si>
-  <si>
     <t>HHND21</t>
   </si>
   <si>
@@ -916,12 +916,12 @@
     <t>OLBN2122</t>
   </si>
   <si>
+    <t>2022-07-31</t>
+  </si>
+  <si>
     <t>2021-08-03</t>
   </si>
   <si>
-    <t>2022-07-31</t>
-  </si>
-  <si>
     <t>HLBY21</t>
   </si>
   <si>
@@ -1009,12 +1009,12 @@
     <t>HAFG20</t>
   </si>
   <si>
+    <t>2020-12-31</t>
+  </si>
+  <si>
     <t>2020-01-01</t>
   </si>
   <si>
-    <t>2020-12-31</t>
-  </si>
-  <si>
     <t>2020</t>
   </si>
   <si>
@@ -1081,12 +1081,12 @@
     <t>FDJI1920</t>
   </si>
   <si>
+    <t>2020-03-31</t>
+  </si>
+  <si>
     <t>2019-12-17</t>
   </si>
   <si>
-    <t>2020-03-31</t>
-  </si>
-  <si>
     <t>ODJI20</t>
   </si>
   <si>
@@ -1135,24 +1135,24 @@
     <t>FLBN20</t>
   </si>
   <si>
+    <t>2020-11-13</t>
+  </si>
+  <si>
     <t>2020-08-05</t>
   </si>
   <si>
-    <t>2020-11-13</t>
-  </si>
-  <si>
     <t>OLBN20</t>
   </si>
   <si>
     <t>FLSO1920</t>
   </si>
   <si>
+    <t>2020-04-30</t>
+  </si>
+  <si>
     <t>2019-11-01</t>
   </si>
   <si>
-    <t>2020-04-30</t>
-  </si>
-  <si>
     <t>OLBR20</t>
   </si>
   <si>
@@ -1249,12 +1249,12 @@
     <t>HAFG19</t>
   </si>
   <si>
+    <t>2019-12-31</t>
+  </si>
+  <si>
     <t>2019-01-01</t>
   </si>
   <si>
-    <t>2019-12-31</t>
-  </si>
-  <si>
     <t>2019</t>
   </si>
   <si>
@@ -1366,12 +1366,12 @@
     <t>FZWE1920</t>
   </si>
   <si>
+    <t>2020-04-29</t>
+  </si>
+  <si>
     <t>2019-02-01</t>
   </si>
   <si>
-    <t>2020-04-29</t>
-  </si>
-  <si>
     <t>FZWE1820</t>
   </si>
   <si>
@@ -1381,12 +1381,12 @@
     <t>HAFG18</t>
   </si>
   <si>
+    <t>2018-12-31</t>
+  </si>
+  <si>
     <t>2018-01-01</t>
   </si>
   <si>
-    <t>2018-12-31</t>
-  </si>
-  <si>
     <t>2018</t>
   </si>
   <si>
@@ -1483,12 +1483,12 @@
     <t>HSYR18</t>
   </si>
   <si>
+    <t>2018-12-30</t>
+  </si>
+  <si>
     <t>2018-11-30</t>
   </si>
   <si>
-    <t>2018-12-30</t>
-  </si>
-  <si>
     <t>RSYR18</t>
   </si>
   <si>
@@ -1507,12 +1507,12 @@
     <t>OEUR17</t>
   </si>
   <si>
+    <t>2017-12-31</t>
+  </si>
+  <si>
     <t>2017-01-01</t>
   </si>
   <si>
-    <t>2017-12-31</t>
-  </si>
-  <si>
     <t>2017</t>
   </si>
   <si>
@@ -1558,12 +1558,12 @@
     <t>FDMA17</t>
   </si>
   <si>
+    <t>2017-12-29</t>
+  </si>
+  <si>
     <t>2017-09-28</t>
   </si>
   <si>
-    <t>2017-12-29</t>
-  </si>
-  <si>
     <t>OPRK17</t>
   </si>
   <si>
@@ -1585,24 +1585,24 @@
     <t>FKEN17</t>
   </si>
   <si>
+    <t>2017-11-30</t>
+  </si>
+  <si>
     <t>2017-02-10</t>
   </si>
   <si>
-    <t>2017-11-30</t>
-  </si>
-  <si>
     <t>HLBY17</t>
   </si>
   <si>
     <t>FMDG17</t>
   </si>
   <si>
+    <t>2017-06-20</t>
+  </si>
+  <si>
     <t>2017-03-20</t>
   </si>
   <si>
-    <t>2017-06-20</t>
-  </si>
-  <si>
     <t>HMLI17</t>
   </si>
   <si>
@@ -1612,12 +1612,12 @@
     <t>FMOZ17</t>
   </si>
   <si>
+    <t>2017-05-31</t>
+  </si>
+  <si>
     <t>2017-02-28</t>
   </si>
   <si>
-    <t>2017-05-31</t>
-  </si>
-  <si>
     <t>HMMR17</t>
   </si>
   <si>
@@ -1636,12 +1636,12 @@
     <t>FPER17</t>
   </si>
   <si>
+    <t>2017-10-31</t>
+  </si>
+  <si>
     <t>2017-04-01</t>
   </si>
   <si>
-    <t>2017-10-31</t>
-  </si>
-  <si>
     <t>HCOG17</t>
   </si>
   <si>
@@ -1678,12 +1678,12 @@
     <t>OEUR16</t>
   </si>
   <si>
+    <t>2016-12-31</t>
+  </si>
+  <si>
     <t>2016-01-01</t>
   </si>
   <si>
-    <t>2016-12-31</t>
-  </si>
-  <si>
     <t>2016</t>
   </si>
   <si>
@@ -1726,21 +1726,21 @@
     <t>FECU16</t>
   </si>
   <si>
+    <t>2016-10-31</t>
+  </si>
+  <si>
     <t>2016-04-16</t>
   </si>
   <si>
-    <t>2016-10-31</t>
-  </si>
-  <si>
     <t>FFJI16</t>
   </si>
   <si>
+    <t>2016-05-30</t>
+  </si>
+  <si>
     <t>2016-02-20</t>
   </si>
   <si>
-    <t>2016-05-30</t>
-  </si>
-  <si>
     <t>HGMB16</t>
   </si>
   <si>
@@ -1783,12 +1783,12 @@
     <t>FIRQ16</t>
   </si>
   <si>
+    <t>2016-10-01</t>
+  </si>
+  <si>
     <t>2016-07-20</t>
   </si>
   <si>
-    <t>2016-10-01</t>
-  </si>
-  <si>
     <t>HMMR16</t>
   </si>
   <si>
@@ -1831,21 +1831,21 @@
     <t>HZWE1617</t>
   </si>
   <si>
+    <t>2017-03-31</t>
+  </si>
+  <si>
     <t>2016-04-01</t>
   </si>
   <si>
-    <t>2017-03-31</t>
-  </si>
-  <si>
     <t>HAFG15</t>
   </si>
   <si>
+    <t>2015-12-31</t>
+  </si>
+  <si>
     <t>2015-01-01</t>
   </si>
   <si>
-    <t>2015-12-31</t>
-  </si>
-  <si>
     <t>2015</t>
   </si>
   <si>
@@ -1879,12 +1879,12 @@
     <t>FGTM1415</t>
   </si>
   <si>
+    <t>2015-09-30</t>
+  </si>
+  <si>
     <t>2014-11-03</t>
   </si>
   <si>
-    <t>2015-09-30</t>
-  </si>
-  <si>
     <t>FHTI15</t>
   </si>
   <si>
@@ -1900,24 +1900,24 @@
     <t>FVUT15</t>
   </si>
   <si>
+    <t>2015-10-31</t>
+  </si>
+  <si>
     <t>2015-03-24</t>
   </si>
   <si>
-    <t>2015-10-31</t>
-  </si>
-  <si>
     <t>HIRQ15</t>
   </si>
   <si>
     <t>HLBY1415</t>
   </si>
   <si>
+    <t>2015-05-31</t>
+  </si>
+  <si>
     <t>2014-10-01</t>
   </si>
   <si>
-    <t>2015-05-31</t>
-  </si>
-  <si>
     <t>HMLI15</t>
   </si>
   <si>
@@ -1975,12 +1975,12 @@
     <t>HAFG14</t>
   </si>
   <si>
+    <t>2014-12-31</t>
+  </si>
+  <si>
     <t>2014-01-01</t>
   </si>
   <si>
-    <t>2014-12-31</t>
-  </si>
-  <si>
     <t>2014</t>
   </si>
   <si>
@@ -2059,21 +2059,21 @@
     <t>FPHL1314</t>
   </si>
   <si>
+    <t>2014-04-22</t>
+  </si>
+  <si>
     <t>2013-10-22</t>
   </si>
   <si>
-    <t>2014-04-22</t>
-  </si>
-  <si>
     <t>SPHL1314</t>
   </si>
   <si>
+    <t>2014-11-07</t>
+  </si>
+  <si>
     <t>2013-11-08</t>
   </si>
   <si>
-    <t>2014-11-07</t>
-  </si>
-  <si>
     <t>HPHL1314</t>
   </si>
   <si>
@@ -2083,12 +2083,12 @@
     <t>HPHL1314a</t>
   </si>
   <si>
+    <t>2014-08-31</t>
+  </si>
+  <si>
     <t>2013-10-01</t>
   </si>
   <si>
-    <t>2014-08-31</t>
-  </si>
-  <si>
     <t>SCOD14</t>
   </si>
   <si>
@@ -2242,12 +2242,12 @@
     <t>CKEN12</t>
   </si>
   <si>
+    <t>2012-12-31</t>
+  </si>
+  <si>
     <t>2012-01-01</t>
   </si>
   <si>
-    <t>2012-12-31</t>
-  </si>
-  <si>
     <t>2012</t>
   </si>
   <si>
@@ -2290,12 +2290,12 @@
     <t>FLSO1213</t>
   </si>
   <si>
+    <t>2013-03-25</t>
+  </si>
+  <si>
     <t>2012-09-18</t>
   </si>
   <si>
-    <t>2013-03-25</t>
-  </si>
-  <si>
     <t>CLBR12</t>
   </si>
   <si>
@@ -2335,12 +2335,12 @@
     <t>CSYR12</t>
   </si>
   <si>
+    <t>2012-12-05</t>
+  </si>
+  <si>
     <t>2012-06-05</t>
   </si>
   <si>
-    <t>2012-12-05</t>
-  </si>
-  <si>
     <t>CYEM12</t>
   </si>
   <si>
@@ -2383,12 +2383,12 @@
     <t>FSLV1112</t>
   </si>
   <si>
+    <t>2012-04-25</t>
+  </si>
+  <si>
     <t>2011-10-25</t>
   </si>
   <si>
-    <t>2012-04-25</t>
-  </si>
-  <si>
     <t>CHTI1011</t>
   </si>
   <si>
@@ -2407,33 +2407,33 @@
     <t>FNAM11</t>
   </si>
   <si>
+    <t>2011-10-11</t>
+  </si>
+  <si>
     <t>2011-04-11</t>
   </si>
   <si>
-    <t>2011-10-11</t>
-  </si>
-  <si>
     <t>FNIC1112</t>
   </si>
   <si>
+    <t>2012-04-26</t>
+  </si>
+  <si>
     <t>2011-10-27</t>
   </si>
   <si>
-    <t>2012-04-26</t>
-  </si>
-  <si>
     <t>CNER11</t>
   </si>
   <si>
     <t>FPAK1112</t>
   </si>
   <si>
+    <t>2012-06-30</t>
+  </si>
+  <si>
     <t>2011-09-15</t>
   </si>
   <si>
-    <t>2012-06-30</t>
-  </si>
-  <si>
     <t>FXLBYREG11</t>
   </si>
   <si>
@@ -2476,24 +2476,24 @@
     <t>CAFG10</t>
   </si>
   <si>
+    <t>2010-12-31</t>
+  </si>
+  <si>
     <t>2010-01-01</t>
   </si>
   <si>
-    <t>2010-12-31</t>
-  </si>
-  <si>
     <t>2010</t>
   </si>
   <si>
     <t>OBFA1011</t>
   </si>
   <si>
+    <t>2011-01-31</t>
+  </si>
+  <si>
     <t>2010-08-01</t>
   </si>
   <si>
-    <t>2011-01-31</t>
-  </si>
-  <si>
     <t>CCAF10</t>
   </si>
   <si>
@@ -2506,30 +2506,30 @@
     <t>FSLV0910</t>
   </si>
   <si>
+    <t>2010-05-31</t>
+  </si>
+  <si>
     <t>2009-11-01</t>
   </si>
   <si>
-    <t>2010-05-31</t>
-  </si>
-  <si>
     <t>FGTM10</t>
   </si>
   <si>
+    <t>2010-12-09</t>
+  </si>
+  <si>
     <t>2010-06-10</t>
   </si>
   <si>
-    <t>2010-12-09</t>
-  </si>
-  <si>
     <t>CGTM10</t>
   </si>
   <si>
+    <t>2010-08-11</t>
+  </si>
+  <si>
     <t>2010-02-12</t>
   </si>
   <si>
-    <t>2010-08-11</t>
-  </si>
-  <si>
     <t>FHTI10</t>
   </si>
   <si>
@@ -2545,12 +2545,12 @@
     <t>FKGZ1011</t>
   </si>
   <si>
+    <t>2011-06-30</t>
+  </si>
+  <si>
     <t>2010-06-01</t>
   </si>
   <si>
-    <t>2011-06-30</t>
-  </si>
-  <si>
     <t>CMNG1011</t>
   </si>
   <si>
@@ -2608,24 +2608,24 @@
     <t>CAFG09</t>
   </si>
   <si>
+    <t>2009-12-31</t>
+  </si>
+  <si>
     <t>2009-01-01</t>
   </si>
   <si>
-    <t>2009-12-31</t>
-  </si>
-  <si>
     <t>2009</t>
   </si>
   <si>
     <t>FBFA0910</t>
   </si>
   <si>
+    <t>2010-03-09</t>
+  </si>
+  <si>
     <t>2009-09-10</t>
   </si>
   <si>
-    <t>2010-03-09</t>
-  </si>
-  <si>
     <t>CCAF09</t>
   </si>
   <si>
@@ -2662,21 +2662,21 @@
     <t>FMDG09</t>
   </si>
   <si>
+    <t>2009-10-31</t>
+  </si>
+  <si>
     <t>2009-04-01</t>
   </si>
   <si>
-    <t>2009-10-31</t>
-  </si>
-  <si>
     <t>FNAM09</t>
   </si>
   <si>
+    <t>2009-09-30</t>
+  </si>
+  <si>
     <t>2009-03-20</t>
   </si>
   <si>
-    <t>2009-09-30</t>
-  </si>
-  <si>
     <t>ONPL09</t>
   </si>
   <si>
@@ -2689,12 +2689,12 @@
     <t>FPHL0910</t>
   </si>
   <si>
+    <t>2010-03-31</t>
+  </si>
+  <si>
     <t>2009-10-03</t>
   </si>
   <si>
-    <t>2010-03-31</t>
-  </si>
-  <si>
     <t>CSOM09</t>
   </si>
   <si>
@@ -2707,12 +2707,12 @@
     <t>OSYR0910</t>
   </si>
   <si>
+    <t>2010-06-14</t>
+  </si>
+  <si>
     <t>2009-07-15</t>
   </si>
   <si>
-    <t>2010-06-14</t>
-  </si>
-  <si>
     <t>OTJK09</t>
   </si>
   <si>
@@ -2746,24 +2746,24 @@
     <t>OAFG08</t>
   </si>
   <si>
+    <t>2008-06-30</t>
+  </si>
+  <si>
     <t>2008-02-01</t>
   </si>
   <si>
-    <t>2008-06-30</t>
-  </si>
-  <si>
     <t>2008</t>
   </si>
   <si>
     <t>OAFG0809</t>
   </si>
   <si>
+    <t>2009-06-30</t>
+  </si>
+  <si>
     <t>2008-07-01</t>
   </si>
   <si>
-    <t>2009-06-30</t>
-  </si>
-  <si>
     <t>FBOL08</t>
   </si>
   <si>
@@ -2773,12 +2773,12 @@
     <t>CCAF08</t>
   </si>
   <si>
+    <t>2008-12-31</t>
+  </si>
+  <si>
     <t>2008-01-01</t>
   </si>
   <si>
-    <t>2008-12-31</t>
-  </si>
-  <si>
     <t>CTCD08</t>
   </si>
   <si>
@@ -2794,21 +2794,21 @@
     <t>ODJI0809</t>
   </si>
   <si>
+    <t>2009-02-28</t>
+  </si>
+  <si>
     <t>2008-08-01</t>
   </si>
   <si>
-    <t>2009-02-28</t>
-  </si>
-  <si>
     <t>FGEO0809</t>
   </si>
   <si>
+    <t>2009-02-09</t>
+  </si>
+  <si>
     <t>2008-08-09</t>
   </si>
   <si>
-    <t>2009-02-09</t>
-  </si>
-  <si>
     <t>FHTI0809</t>
   </si>
   <si>
@@ -2818,12 +2818,12 @@
     <t>FHND0809</t>
   </si>
   <si>
+    <t>2009-04-30</t>
+  </si>
+  <si>
     <t>2008-11-01</t>
   </si>
   <si>
-    <t>2009-04-30</t>
-  </si>
-  <si>
     <t>CIRQ08</t>
   </si>
   <si>
@@ -2833,12 +2833,12 @@
     <t>FKGZ0809</t>
   </si>
   <si>
+    <t>2009-05-31</t>
+  </si>
+  <si>
     <t>2008-12-01</t>
   </si>
   <si>
-    <t>2009-05-31</t>
-  </si>
-  <si>
     <t>OLAO0809</t>
   </si>
   <si>
@@ -2857,12 +2857,12 @@
     <t>FMMR08</t>
   </si>
   <si>
+    <t>2008-11-30</t>
+  </si>
+  <si>
     <t>2008-05-01</t>
   </si>
   <si>
-    <t>2008-11-30</t>
-  </si>
-  <si>
     <t>ONPL08</t>
   </si>
   <si>
@@ -2914,33 +2914,33 @@
     <t>FBOL07</t>
   </si>
   <si>
+    <t>2007-08-21</t>
+  </si>
+  <si>
     <t>2007-02-22</t>
   </si>
   <si>
-    <t>2007-08-21</t>
-  </si>
-  <si>
     <t>2007</t>
   </si>
   <si>
     <t>FBFA0708</t>
   </si>
   <si>
+    <t>2008-01-31</t>
+  </si>
+  <si>
     <t>2007-11-01</t>
   </si>
   <si>
-    <t>2008-01-31</t>
-  </si>
-  <si>
     <t>CBDI07</t>
   </si>
   <si>
+    <t>2007-12-31</t>
+  </si>
+  <si>
     <t>2007-01-01</t>
   </si>
   <si>
-    <t>2007-12-31</t>
-  </si>
-  <si>
     <t>CCAF07</t>
   </si>
   <si>
@@ -2962,12 +2962,12 @@
     <t>FGHA0708</t>
   </si>
   <si>
+    <t>2008-03-31</t>
+  </si>
+  <si>
     <t>2007-09-01</t>
   </si>
   <si>
-    <t>2008-03-31</t>
-  </si>
-  <si>
     <t>CXGLR07</t>
   </si>
   <si>
@@ -2980,75 +2980,75 @@
     <t>FPRK07</t>
   </si>
   <si>
+    <t>2007-11-30</t>
+  </si>
+  <si>
     <t>2007-08-28</t>
   </si>
   <si>
-    <t>2007-11-30</t>
-  </si>
-  <si>
     <t>OLBN07</t>
   </si>
   <si>
+    <t>2007-09-03</t>
+  </si>
+  <si>
     <t>2007-06-04</t>
   </si>
   <si>
-    <t>2007-09-03</t>
-  </si>
-  <si>
     <t>FLSO0708</t>
   </si>
   <si>
+    <t>2008-01-28</t>
+  </si>
+  <si>
     <t>2007-07-28</t>
   </si>
   <si>
-    <t>2008-01-28</t>
-  </si>
-  <si>
     <t>CLBR07</t>
   </si>
   <si>
     <t>FMDG07</t>
   </si>
   <si>
+    <t>2007-09-15</t>
+  </si>
+  <si>
     <t>2007-03-15</t>
   </si>
   <si>
-    <t>2007-09-15</t>
-  </si>
-  <si>
     <t>FMOZ07</t>
   </si>
   <si>
+    <t>2007-06-30</t>
+  </si>
+  <si>
     <t>2007-03-01</t>
   </si>
   <si>
-    <t>2007-06-30</t>
-  </si>
-  <si>
     <t>ONPL07</t>
   </si>
   <si>
     <t>FNIC0708</t>
   </si>
   <si>
+    <t>2008-02-28</t>
+  </si>
+  <si>
     <t>2007-09-07</t>
   </si>
   <si>
-    <t>2008-02-28</t>
-  </si>
-  <si>
     <t>ORUS07</t>
   </si>
   <si>
     <t>FPAK07</t>
   </si>
   <si>
+    <t>2007-10-31</t>
+  </si>
+  <si>
     <t>2007-07-15</t>
   </si>
   <si>
-    <t>2007-10-31</t>
-  </si>
-  <si>
     <t>FPER0708</t>
   </si>
   <si>
@@ -3082,12 +3082,12 @@
     <t>FSWZ0708</t>
   </si>
   <si>
+    <t>2008-01-20</t>
+  </si>
+  <si>
     <t>2007-07-20</t>
   </si>
   <si>
-    <t>2008-01-20</t>
-  </si>
-  <si>
     <t>CTLS07</t>
   </si>
   <si>
@@ -3112,12 +3112,12 @@
     <t>OAFG06</t>
   </si>
   <si>
+    <t>2006-12-31</t>
+  </si>
+  <si>
     <t>2006-07-01</t>
   </si>
   <si>
-    <t>2006-12-31</t>
-  </si>
-  <si>
     <t>2006</t>
   </si>
   <si>
@@ -3145,21 +3145,21 @@
     <t>OETH06a</t>
   </si>
   <si>
+    <t>2006-11-25</t>
+  </si>
+  <si>
     <t>2006-08-25</t>
   </si>
   <si>
-    <t>2006-11-25</t>
-  </si>
-  <si>
     <t>OETH0607</t>
   </si>
   <si>
+    <t>2007-01-22</t>
+  </si>
+  <si>
     <t>2006-11-23</t>
   </si>
   <si>
-    <t>2007-01-22</t>
-  </si>
-  <si>
     <t>CXGLR06</t>
   </si>
   <si>
@@ -3169,12 +3169,12 @@
     <t>FGNB06</t>
   </si>
   <si>
+    <t>2006-11-30</t>
+  </si>
+  <si>
     <t>2006-05-01</t>
   </si>
   <si>
-    <t>2006-11-30</t>
-  </si>
-  <si>
     <t>CXHAF06</t>
   </si>
   <si>
@@ -3184,12 +3184,12 @@
     <t>FKEN0607</t>
   </si>
   <si>
+    <t>2007-04-15</t>
+  </si>
+  <si>
     <t>2006-10-16</t>
   </si>
   <si>
-    <t>2007-04-15</t>
-  </si>
-  <si>
     <t>FKEN06</t>
   </si>
   <si>
@@ -3199,12 +3199,12 @@
     <t>FLBN06</t>
   </si>
   <si>
+    <t>2006-10-23</t>
+  </si>
+  <si>
     <t>2006-07-24</t>
   </si>
   <si>
-    <t>2006-10-23</t>
-  </si>
-  <si>
     <t>CLBR06</t>
   </si>
   <si>
@@ -3232,12 +3232,12 @@
     <t>FSOM0607</t>
   </si>
   <si>
+    <t>2007-03-05</t>
+  </si>
+  <si>
     <t>2006-12-05</t>
   </si>
   <si>
-    <t>2007-03-05</t>
-  </si>
-  <si>
     <t>OLKA06</t>
   </si>
   <si>
@@ -3271,33 +3271,33 @@
     <t>FAGO05</t>
   </si>
   <si>
+    <t>2005-06-30</t>
+  </si>
+  <si>
     <t>2005-04-01</t>
   </si>
   <si>
-    <t>2005-06-30</t>
-  </si>
-  <si>
     <t>2005</t>
   </si>
   <si>
     <t>FBEN05</t>
   </si>
   <si>
+    <t>2005-10-31</t>
+  </si>
+  <si>
     <t>2005-05-01</t>
   </si>
   <si>
-    <t>2005-10-31</t>
-  </si>
-  <si>
     <t>CBDI05</t>
   </si>
   <si>
+    <t>2005-12-31</t>
+  </si>
+  <si>
     <t>2005-01-01</t>
   </si>
   <si>
-    <t>2005-12-31</t>
-  </si>
-  <si>
     <t>CCAF05</t>
   </si>
   <si>
@@ -3337,12 +3337,12 @@
     <t>FGUY05</t>
   </si>
   <si>
+    <t>2005-08-01</t>
+  </si>
+  <si>
     <t>2005-02-01</t>
   </si>
   <si>
-    <t>2005-08-01</t>
-  </si>
-  <si>
     <t>FXINDTSU05</t>
   </si>
   <si>
@@ -3355,12 +3355,12 @@
     <t>FNER05</t>
   </si>
   <si>
+    <t>2005-09-30</t>
+  </si>
+  <si>
     <t>2005-06-01</t>
   </si>
   <si>
-    <t>2005-09-30</t>
-  </si>
-  <si>
     <t>CCOG05</t>
   </si>
   <si>
@@ -3370,12 +3370,12 @@
     <t>FXSASIA0506</t>
   </si>
   <si>
+    <t>2006-04-10</t>
+  </si>
+  <si>
     <t>2005-10-11</t>
   </si>
   <si>
-    <t>2006-04-10</t>
-  </si>
-  <si>
     <t>CSDN05</t>
   </si>
   <si>
@@ -3388,24 +3388,24 @@
     <t>FXWAF0506</t>
   </si>
   <si>
+    <t>2006-05-31</t>
+  </si>
+  <si>
     <t>2005-11-01</t>
   </si>
   <si>
-    <t>2006-05-31</t>
-  </si>
-  <si>
     <t>CPSE05</t>
   </si>
   <si>
     <t>OAFG04</t>
   </si>
   <si>
+    <t>2004-12-31</t>
+  </si>
+  <si>
     <t>2004-09-01</t>
   </si>
   <si>
-    <t>2004-12-31</t>
-  </si>
-  <si>
     <t>2004</t>
   </si>
   <si>
@@ -3418,21 +3418,21 @@
     <t>FBGD0405</t>
   </si>
   <si>
+    <t>2005-01-31</t>
+  </si>
+  <si>
     <t>2004-08-01</t>
   </si>
   <si>
-    <t>2005-01-31</t>
-  </si>
-  <si>
     <t>FBOL0405</t>
   </si>
   <si>
+    <t>2005-05-31</t>
+  </si>
+  <si>
     <t>2004-11-01</t>
   </si>
   <si>
-    <t>2005-05-31</t>
-  </si>
-  <si>
     <t>CBDI04</t>
   </si>
   <si>
@@ -3505,21 +3505,21 @@
     <t>FMDG04</t>
   </si>
   <si>
+    <t>2004-06-19</t>
+  </si>
+  <si>
     <t>2004-03-19</t>
   </si>
   <si>
-    <t>2004-06-19</t>
-  </si>
-  <si>
     <t>FPHL0405</t>
   </si>
   <si>
+    <t>2005-03-15</t>
+  </si>
+  <si>
     <t>2004-12-15</t>
   </si>
   <si>
-    <t>2005-03-15</t>
-  </si>
-  <si>
     <t>CSLE04</t>
   </si>
   <si>
@@ -3550,12 +3550,12 @@
     <t>OAFG03</t>
   </si>
   <si>
+    <t>2003-12-31</t>
+  </si>
+  <si>
     <t>2003-01-01</t>
   </si>
   <si>
-    <t>2003-12-31</t>
-  </si>
-  <si>
     <t>2003</t>
   </si>
   <si>
@@ -3568,12 +3568,12 @@
     <t>FCAF03</t>
   </si>
   <si>
+    <t>2003-06-30</t>
+  </si>
+  <si>
     <t>2003-04-01</t>
   </si>
   <si>
-    <t>2003-06-30</t>
-  </si>
-  <si>
     <t>CRUS03</t>
   </si>
   <si>
@@ -3586,12 +3586,12 @@
     <t>FCIV0203</t>
   </si>
   <si>
+    <t>2003-01-31</t>
+  </si>
+  <si>
     <t>2002-11-01</t>
   </si>
   <si>
-    <t>2003-01-31</t>
-  </si>
-  <si>
     <t>CPRK03</t>
   </si>
   <si>
@@ -3610,21 +3610,21 @@
     <t>OHTI03</t>
   </si>
   <si>
+    <t>2003-08-31</t>
+  </si>
+  <si>
     <t>2003-03-01</t>
   </si>
   <si>
-    <t>2003-08-31</t>
-  </si>
-  <si>
     <t>CLSO0304</t>
   </si>
   <si>
+    <t>2004-06-30</t>
+  </si>
+  <si>
     <t>2003-07-01</t>
   </si>
   <si>
-    <t>2004-06-30</t>
-  </si>
-  <si>
     <t>CMWI03</t>
   </si>
   <si>
@@ -3676,12 +3676,12 @@
     <t>CAFG0102</t>
   </si>
   <si>
+    <t>2002-12-31</t>
+  </si>
+  <si>
     <t>2001-10-01</t>
   </si>
   <si>
-    <t>2002-12-31</t>
-  </si>
-  <si>
     <t>2002</t>
   </si>
   <si>
@@ -3778,12 +3778,12 @@
     <t>CAFG01</t>
   </si>
   <si>
+    <t>2001-09-30</t>
+  </si>
+  <si>
     <t>2001-01-01</t>
   </si>
   <si>
-    <t>2001-09-30</t>
-  </si>
-  <si>
     <t>2001</t>
   </si>
   <si>
@@ -3859,10 +3859,10 @@
     <t>CAGO00</t>
   </si>
   <si>
+    <t>2000-12-31</t>
+  </si>
+  <si>
     <t>2000-01-01</t>
-  </si>
-  <si>
-    <t>2000-12-31</t>
   </si>
   <si>
     <t>2000</t>
@@ -4328,10 +4328,10 @@
         <v>7</v>
       </c>
       <c r="C4" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D4" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E4" t="s">
         <v>10</v>
@@ -4528,10 +4528,10 @@
         <v>7</v>
       </c>
       <c r="C14" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D14" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E14" t="s">
         <v>10</v>
@@ -4548,10 +4548,10 @@
         <v>7</v>
       </c>
       <c r="C15" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="D15" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="E15" t="s">
         <v>10</v>
@@ -4588,10 +4588,10 @@
         <v>7</v>
       </c>
       <c r="C17" t="s">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="D17" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="E17" t="s">
         <v>10</v>
@@ -4628,10 +4628,10 @@
         <v>7</v>
       </c>
       <c r="C19" t="s">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="D19" t="s">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="E19" t="s">
         <v>10</v>
@@ -4648,10 +4648,10 @@
         <v>7</v>
       </c>
       <c r="C20" t="s">
+        <v>8</v>
+      </c>
+      <c r="D20" t="s">
         <v>38</v>
-      </c>
-      <c r="D20" t="s">
-        <v>9</v>
       </c>
       <c r="E20" t="s">
         <v>10</v>
@@ -4728,10 +4728,10 @@
         <v>7</v>
       </c>
       <c r="C24" t="s">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="D24" t="s">
-        <v>43</v>
+        <v>9</v>
       </c>
       <c r="E24" t="s">
         <v>10</v>
@@ -4928,10 +4928,10 @@
         <v>7</v>
       </c>
       <c r="C34" t="s">
+        <v>8</v>
+      </c>
+      <c r="D34" t="s">
         <v>54</v>
-      </c>
-      <c r="D34" t="s">
-        <v>9</v>
       </c>
       <c r="E34" t="s">
         <v>10</v>
@@ -5088,10 +5088,10 @@
         <v>7</v>
       </c>
       <c r="C42" t="s">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="D42" t="s">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="E42" t="s">
         <v>10</v>
@@ -5128,10 +5128,10 @@
         <v>7</v>
       </c>
       <c r="C44" t="s">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="D44" t="s">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="E44" t="s">
         <v>10</v>
@@ -5148,10 +5148,10 @@
         <v>7</v>
       </c>
       <c r="C45" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="D45" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="E45" t="s">
         <v>10</v>
@@ -5208,10 +5208,10 @@
         <v>7</v>
       </c>
       <c r="C48" t="s">
+        <v>67</v>
+      </c>
+      <c r="D48" t="s">
         <v>72</v>
-      </c>
-      <c r="D48" t="s">
-        <v>68</v>
       </c>
       <c r="E48" t="s">
         <v>69</v>
@@ -5248,10 +5248,10 @@
         <v>7</v>
       </c>
       <c r="C50" t="s">
+        <v>67</v>
+      </c>
+      <c r="D50" t="s">
         <v>75</v>
-      </c>
-      <c r="D50" t="s">
-        <v>68</v>
       </c>
       <c r="E50" t="s">
         <v>69</v>
@@ -5388,10 +5388,10 @@
         <v>7</v>
       </c>
       <c r="C57" t="s">
+        <v>67</v>
+      </c>
+      <c r="D57" t="s">
         <v>83</v>
-      </c>
-      <c r="D57" t="s">
-        <v>68</v>
       </c>
       <c r="E57" t="s">
         <v>69</v>
@@ -5468,10 +5468,10 @@
         <v>7</v>
       </c>
       <c r="C61" t="s">
+        <v>67</v>
+      </c>
+      <c r="D61" t="s">
         <v>88</v>
-      </c>
-      <c r="D61" t="s">
-        <v>68</v>
       </c>
       <c r="E61" t="s">
         <v>69</v>
@@ -5488,10 +5488,10 @@
         <v>7</v>
       </c>
       <c r="C62" t="s">
+        <v>67</v>
+      </c>
+      <c r="D62" t="s">
         <v>88</v>
-      </c>
-      <c r="D62" t="s">
-        <v>68</v>
       </c>
       <c r="E62" t="s">
         <v>69</v>
@@ -5508,10 +5508,10 @@
         <v>7</v>
       </c>
       <c r="C63" t="s">
-        <v>67</v>
+        <v>91</v>
       </c>
       <c r="D63" t="s">
-        <v>91</v>
+        <v>68</v>
       </c>
       <c r="E63" t="s">
         <v>69</v>
@@ -5528,10 +5528,10 @@
         <v>7</v>
       </c>
       <c r="C64" t="s">
-        <v>67</v>
+        <v>93</v>
       </c>
       <c r="D64" t="s">
-        <v>93</v>
+        <v>68</v>
       </c>
       <c r="E64" t="s">
         <v>69</v>
@@ -5548,10 +5548,10 @@
         <v>7</v>
       </c>
       <c r="C65" t="s">
+        <v>67</v>
+      </c>
+      <c r="D65" t="s">
         <v>95</v>
-      </c>
-      <c r="D65" t="s">
-        <v>68</v>
       </c>
       <c r="E65" t="s">
         <v>69</v>
@@ -5588,10 +5588,10 @@
         <v>7</v>
       </c>
       <c r="C67" t="s">
+        <v>93</v>
+      </c>
+      <c r="D67" t="s">
         <v>98</v>
-      </c>
-      <c r="D67" t="s">
-        <v>93</v>
       </c>
       <c r="E67" t="s">
         <v>69</v>
@@ -5608,10 +5608,10 @@
         <v>7</v>
       </c>
       <c r="C68" t="s">
+        <v>67</v>
+      </c>
+      <c r="D68" t="s">
         <v>100</v>
-      </c>
-      <c r="D68" t="s">
-        <v>68</v>
       </c>
       <c r="E68" t="s">
         <v>69</v>
@@ -5668,10 +5668,10 @@
         <v>7</v>
       </c>
       <c r="C71" t="s">
+        <v>67</v>
+      </c>
+      <c r="D71" t="s">
         <v>104</v>
-      </c>
-      <c r="D71" t="s">
-        <v>68</v>
       </c>
       <c r="E71" t="s">
         <v>69</v>
@@ -5728,10 +5728,10 @@
         <v>7</v>
       </c>
       <c r="C74" t="s">
+        <v>67</v>
+      </c>
+      <c r="D74" t="s">
         <v>108</v>
-      </c>
-      <c r="D74" t="s">
-        <v>68</v>
       </c>
       <c r="E74" t="s">
         <v>69</v>
@@ -5848,10 +5848,10 @@
         <v>7</v>
       </c>
       <c r="C80" t="s">
+        <v>67</v>
+      </c>
+      <c r="D80" t="s">
         <v>83</v>
-      </c>
-      <c r="D80" t="s">
-        <v>68</v>
       </c>
       <c r="E80" t="s">
         <v>69</v>
@@ -6108,10 +6108,10 @@
         <v>7</v>
       </c>
       <c r="C93" t="s">
+        <v>67</v>
+      </c>
+      <c r="D93" t="s">
         <v>129</v>
-      </c>
-      <c r="D93" t="s">
-        <v>68</v>
       </c>
       <c r="E93" t="s">
         <v>69</v>
@@ -6148,10 +6148,10 @@
         <v>7</v>
       </c>
       <c r="C95" t="s">
+        <v>67</v>
+      </c>
+      <c r="D95" t="s">
         <v>132</v>
-      </c>
-      <c r="D95" t="s">
-        <v>68</v>
       </c>
       <c r="E95" t="s">
         <v>69</v>
@@ -6168,10 +6168,10 @@
         <v>7</v>
       </c>
       <c r="C96" t="s">
+        <v>67</v>
+      </c>
+      <c r="D96" t="s">
         <v>132</v>
-      </c>
-      <c r="D96" t="s">
-        <v>68</v>
       </c>
       <c r="E96" t="s">
         <v>69</v>
@@ -6348,10 +6348,10 @@
         <v>7</v>
       </c>
       <c r="C105" t="s">
+        <v>135</v>
+      </c>
+      <c r="D105" t="s">
         <v>146</v>
-      </c>
-      <c r="D105" t="s">
-        <v>136</v>
       </c>
       <c r="E105" t="s">
         <v>137</v>
@@ -6508,10 +6508,10 @@
         <v>7</v>
       </c>
       <c r="C113" t="s">
+        <v>135</v>
+      </c>
+      <c r="D113" t="s">
         <v>155</v>
-      </c>
-      <c r="D113" t="s">
-        <v>136</v>
       </c>
       <c r="E113" t="s">
         <v>137</v>
@@ -6688,10 +6688,10 @@
         <v>7</v>
       </c>
       <c r="C122" t="s">
-        <v>135</v>
+        <v>162</v>
       </c>
       <c r="D122" t="s">
-        <v>163</v>
+        <v>136</v>
       </c>
       <c r="E122" t="s">
         <v>137</v>
@@ -6708,10 +6708,10 @@
         <v>7</v>
       </c>
       <c r="C123" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="D123" t="s">
-        <v>160</v>
+        <v>136</v>
       </c>
       <c r="E123" t="s">
         <v>137</v>
@@ -6928,10 +6928,10 @@
         <v>7</v>
       </c>
       <c r="C134" t="s">
+        <v>159</v>
+      </c>
+      <c r="D134" t="s">
         <v>183</v>
-      </c>
-      <c r="D134" t="s">
-        <v>160</v>
       </c>
       <c r="E134" t="s">
         <v>137</v>
@@ -6968,10 +6968,10 @@
         <v>7</v>
       </c>
       <c r="C136" t="s">
+        <v>159</v>
+      </c>
+      <c r="D136" t="s">
         <v>186</v>
-      </c>
-      <c r="D136" t="s">
-        <v>160</v>
       </c>
       <c r="E136" t="s">
         <v>137</v>
@@ -7388,10 +7388,10 @@
         <v>110</v>
       </c>
       <c r="C157" t="s">
-        <v>212</v>
+        <v>195</v>
       </c>
       <c r="D157" t="s">
-        <v>196</v>
+        <v>213</v>
       </c>
       <c r="E157" t="s">
         <v>197</v>
@@ -7468,10 +7468,10 @@
         <v>7</v>
       </c>
       <c r="C161" t="s">
-        <v>195</v>
+        <v>219</v>
       </c>
       <c r="D161" t="s">
-        <v>219</v>
+        <v>196</v>
       </c>
       <c r="E161" t="s">
         <v>197</v>
@@ -7708,10 +7708,10 @@
         <v>7</v>
       </c>
       <c r="C173" t="s">
+        <v>195</v>
+      </c>
+      <c r="D173" t="s">
         <v>236</v>
-      </c>
-      <c r="D173" t="s">
-        <v>196</v>
       </c>
       <c r="E173" t="s">
         <v>197</v>
@@ -7728,10 +7728,10 @@
         <v>110</v>
       </c>
       <c r="C174" t="s">
+        <v>238</v>
+      </c>
+      <c r="D174" t="s">
         <v>236</v>
-      </c>
-      <c r="D174" t="s">
-        <v>238</v>
       </c>
       <c r="E174" t="s">
         <v>197</v>
@@ -7908,10 +7908,10 @@
         <v>7</v>
       </c>
       <c r="C183" t="s">
+        <v>195</v>
+      </c>
+      <c r="D183" t="s">
         <v>250</v>
-      </c>
-      <c r="D183" t="s">
-        <v>196</v>
       </c>
       <c r="E183" t="s">
         <v>197</v>
@@ -8008,10 +8008,10 @@
         <v>7</v>
       </c>
       <c r="C188" t="s">
+        <v>195</v>
+      </c>
+      <c r="D188" t="s">
         <v>256</v>
-      </c>
-      <c r="D188" t="s">
-        <v>196</v>
       </c>
       <c r="E188" t="s">
         <v>197</v>
@@ -8048,10 +8048,10 @@
         <v>7</v>
       </c>
       <c r="C190" t="s">
+        <v>259</v>
+      </c>
+      <c r="D190" t="s">
         <v>256</v>
-      </c>
-      <c r="D190" t="s">
-        <v>259</v>
       </c>
       <c r="E190" t="s">
         <v>197</v>
@@ -8128,10 +8128,10 @@
         <v>7</v>
       </c>
       <c r="C194" t="s">
+        <v>263</v>
+      </c>
+      <c r="D194" t="s">
         <v>267</v>
-      </c>
-      <c r="D194" t="s">
-        <v>264</v>
       </c>
       <c r="E194" t="s">
         <v>265</v>
@@ -8148,10 +8148,10 @@
         <v>7</v>
       </c>
       <c r="C195" t="s">
+        <v>263</v>
+      </c>
+      <c r="D195" t="s">
         <v>267</v>
-      </c>
-      <c r="D195" t="s">
-        <v>264</v>
       </c>
       <c r="E195" t="s">
         <v>265</v>
@@ -8168,10 +8168,10 @@
         <v>7</v>
       </c>
       <c r="C196" t="s">
+        <v>263</v>
+      </c>
+      <c r="D196" t="s">
         <v>267</v>
-      </c>
-      <c r="D196" t="s">
-        <v>264</v>
       </c>
       <c r="E196" t="s">
         <v>265</v>
@@ -8188,10 +8188,10 @@
         <v>7</v>
       </c>
       <c r="C197" t="s">
+        <v>263</v>
+      </c>
+      <c r="D197" t="s">
         <v>267</v>
-      </c>
-      <c r="D197" t="s">
-        <v>264</v>
       </c>
       <c r="E197" t="s">
         <v>265</v>
@@ -8208,10 +8208,10 @@
         <v>7</v>
       </c>
       <c r="C198" t="s">
+        <v>263</v>
+      </c>
+      <c r="D198" t="s">
         <v>267</v>
-      </c>
-      <c r="D198" t="s">
-        <v>264</v>
       </c>
       <c r="E198" t="s">
         <v>265</v>
@@ -8228,10 +8228,10 @@
         <v>7</v>
       </c>
       <c r="C199" t="s">
+        <v>263</v>
+      </c>
+      <c r="D199" t="s">
         <v>267</v>
-      </c>
-      <c r="D199" t="s">
-        <v>264</v>
       </c>
       <c r="E199" t="s">
         <v>265</v>
@@ -8248,10 +8248,10 @@
         <v>7</v>
       </c>
       <c r="C200" t="s">
+        <v>263</v>
+      </c>
+      <c r="D200" t="s">
         <v>267</v>
-      </c>
-      <c r="D200" t="s">
-        <v>264</v>
       </c>
       <c r="E200" t="s">
         <v>265</v>
@@ -8268,10 +8268,10 @@
         <v>7</v>
       </c>
       <c r="C201" t="s">
+        <v>263</v>
+      </c>
+      <c r="D201" t="s">
         <v>267</v>
-      </c>
-      <c r="D201" t="s">
-        <v>264</v>
       </c>
       <c r="E201" t="s">
         <v>265</v>
@@ -8288,10 +8288,10 @@
         <v>7</v>
       </c>
       <c r="C202" t="s">
+        <v>263</v>
+      </c>
+      <c r="D202" t="s">
         <v>267</v>
-      </c>
-      <c r="D202" t="s">
-        <v>264</v>
       </c>
       <c r="E202" t="s">
         <v>265</v>
@@ -8308,10 +8308,10 @@
         <v>7</v>
       </c>
       <c r="C203" t="s">
+        <v>263</v>
+      </c>
+      <c r="D203" t="s">
         <v>267</v>
-      </c>
-      <c r="D203" t="s">
-        <v>264</v>
       </c>
       <c r="E203" t="s">
         <v>265</v>
@@ -8328,10 +8328,10 @@
         <v>7</v>
       </c>
       <c r="C204" t="s">
+        <v>263</v>
+      </c>
+      <c r="D204" t="s">
         <v>267</v>
-      </c>
-      <c r="D204" t="s">
-        <v>264</v>
       </c>
       <c r="E204" t="s">
         <v>265</v>
@@ -8348,10 +8348,10 @@
         <v>7</v>
       </c>
       <c r="C205" t="s">
+        <v>263</v>
+      </c>
+      <c r="D205" t="s">
         <v>279</v>
-      </c>
-      <c r="D205" t="s">
-        <v>264</v>
       </c>
       <c r="E205" t="s">
         <v>265</v>
@@ -8368,10 +8368,10 @@
         <v>110</v>
       </c>
       <c r="C206" t="s">
+        <v>195</v>
+      </c>
+      <c r="D206" t="s">
         <v>279</v>
-      </c>
-      <c r="D206" t="s">
-        <v>196</v>
       </c>
       <c r="E206" t="s">
         <v>265</v>
@@ -8408,10 +8408,10 @@
         <v>7</v>
       </c>
       <c r="C208" t="s">
+        <v>263</v>
+      </c>
+      <c r="D208" t="s">
         <v>267</v>
-      </c>
-      <c r="D208" t="s">
-        <v>264</v>
       </c>
       <c r="E208" t="s">
         <v>265</v>
@@ -8428,10 +8428,10 @@
         <v>7</v>
       </c>
       <c r="C209" t="s">
+        <v>263</v>
+      </c>
+      <c r="D209" t="s">
         <v>279</v>
-      </c>
-      <c r="D209" t="s">
-        <v>264</v>
       </c>
       <c r="E209" t="s">
         <v>265</v>
@@ -8448,10 +8448,10 @@
         <v>110</v>
       </c>
       <c r="C210" t="s">
+        <v>195</v>
+      </c>
+      <c r="D210" t="s">
         <v>279</v>
-      </c>
-      <c r="D210" t="s">
-        <v>196</v>
       </c>
       <c r="E210" t="s">
         <v>265</v>
@@ -8488,10 +8488,10 @@
         <v>7</v>
       </c>
       <c r="C212" t="s">
+        <v>263</v>
+      </c>
+      <c r="D212" t="s">
         <v>267</v>
-      </c>
-      <c r="D212" t="s">
-        <v>264</v>
       </c>
       <c r="E212" t="s">
         <v>265</v>
@@ -8528,10 +8528,10 @@
         <v>7</v>
       </c>
       <c r="C214" t="s">
+        <v>263</v>
+      </c>
+      <c r="D214" t="s">
         <v>279</v>
-      </c>
-      <c r="D214" t="s">
-        <v>264</v>
       </c>
       <c r="E214" t="s">
         <v>265</v>
@@ -8548,10 +8548,10 @@
         <v>110</v>
       </c>
       <c r="C215" t="s">
+        <v>195</v>
+      </c>
+      <c r="D215" t="s">
         <v>279</v>
-      </c>
-      <c r="D215" t="s">
-        <v>196</v>
       </c>
       <c r="E215" t="s">
         <v>265</v>
@@ -8568,10 +8568,10 @@
         <v>7</v>
       </c>
       <c r="C216" t="s">
+        <v>263</v>
+      </c>
+      <c r="D216" t="s">
         <v>267</v>
-      </c>
-      <c r="D216" t="s">
-        <v>264</v>
       </c>
       <c r="E216" t="s">
         <v>265</v>
@@ -8588,10 +8588,10 @@
         <v>7</v>
       </c>
       <c r="C217" t="s">
+        <v>263</v>
+      </c>
+      <c r="D217" t="s">
         <v>298</v>
-      </c>
-      <c r="D217" t="s">
-        <v>264</v>
       </c>
       <c r="E217" t="s">
         <v>265</v>
@@ -8628,10 +8628,10 @@
         <v>7</v>
       </c>
       <c r="C219" t="s">
+        <v>263</v>
+      </c>
+      <c r="D219" t="s">
         <v>267</v>
-      </c>
-      <c r="D219" t="s">
-        <v>264</v>
       </c>
       <c r="E219" t="s">
         <v>265</v>
@@ -8648,10 +8648,10 @@
         <v>110</v>
       </c>
       <c r="C220" t="s">
+        <v>224</v>
+      </c>
+      <c r="D220" t="s">
         <v>267</v>
-      </c>
-      <c r="D220" t="s">
-        <v>225</v>
       </c>
       <c r="E220" t="s">
         <v>265</v>
@@ -8668,10 +8668,10 @@
         <v>7</v>
       </c>
       <c r="C221" t="s">
+        <v>263</v>
+      </c>
+      <c r="D221" t="s">
         <v>267</v>
-      </c>
-      <c r="D221" t="s">
-        <v>264</v>
       </c>
       <c r="E221" t="s">
         <v>265</v>
@@ -8688,10 +8688,10 @@
         <v>7</v>
       </c>
       <c r="C222" t="s">
+        <v>263</v>
+      </c>
+      <c r="D222" t="s">
         <v>267</v>
-      </c>
-      <c r="D222" t="s">
-        <v>264</v>
       </c>
       <c r="E222" t="s">
         <v>265</v>
@@ -8708,10 +8708,10 @@
         <v>7</v>
       </c>
       <c r="C223" t="s">
+        <v>263</v>
+      </c>
+      <c r="D223" t="s">
         <v>267</v>
-      </c>
-      <c r="D223" t="s">
-        <v>264</v>
       </c>
       <c r="E223" t="s">
         <v>265</v>
@@ -8728,10 +8728,10 @@
         <v>7</v>
       </c>
       <c r="C224" t="s">
+        <v>263</v>
+      </c>
+      <c r="D224" t="s">
         <v>267</v>
-      </c>
-      <c r="D224" t="s">
-        <v>264</v>
       </c>
       <c r="E224" t="s">
         <v>265</v>
@@ -8748,10 +8748,10 @@
         <v>7</v>
       </c>
       <c r="C225" t="s">
+        <v>263</v>
+      </c>
+      <c r="D225" t="s">
         <v>309</v>
-      </c>
-      <c r="D225" t="s">
-        <v>264</v>
       </c>
       <c r="E225" t="s">
         <v>265</v>
@@ -8768,10 +8768,10 @@
         <v>7</v>
       </c>
       <c r="C226" t="s">
+        <v>263</v>
+      </c>
+      <c r="D226" t="s">
         <v>311</v>
-      </c>
-      <c r="D226" t="s">
-        <v>264</v>
       </c>
       <c r="E226" t="s">
         <v>265</v>
@@ -8788,10 +8788,10 @@
         <v>7</v>
       </c>
       <c r="C227" t="s">
+        <v>263</v>
+      </c>
+      <c r="D227" t="s">
         <v>267</v>
-      </c>
-      <c r="D227" t="s">
-        <v>264</v>
       </c>
       <c r="E227" t="s">
         <v>265</v>
@@ -8808,10 +8808,10 @@
         <v>7</v>
       </c>
       <c r="C228" t="s">
+        <v>263</v>
+      </c>
+      <c r="D228" t="s">
         <v>267</v>
-      </c>
-      <c r="D228" t="s">
-        <v>264</v>
       </c>
       <c r="E228" t="s">
         <v>265</v>
@@ -8828,10 +8828,10 @@
         <v>7</v>
       </c>
       <c r="C229" t="s">
+        <v>263</v>
+      </c>
+      <c r="D229" t="s">
         <v>311</v>
-      </c>
-      <c r="D229" t="s">
-        <v>264</v>
       </c>
       <c r="E229" t="s">
         <v>265</v>
@@ -8848,10 +8848,10 @@
         <v>110</v>
       </c>
       <c r="C230" t="s">
+        <v>263</v>
+      </c>
+      <c r="D230" t="s">
         <v>311</v>
-      </c>
-      <c r="D230" t="s">
-        <v>264</v>
       </c>
       <c r="E230" t="s">
         <v>265</v>
@@ -8868,10 +8868,10 @@
         <v>7</v>
       </c>
       <c r="C231" t="s">
+        <v>263</v>
+      </c>
+      <c r="D231" t="s">
         <v>267</v>
-      </c>
-      <c r="D231" t="s">
-        <v>264</v>
       </c>
       <c r="E231" t="s">
         <v>265</v>
@@ -8888,10 +8888,10 @@
         <v>7</v>
       </c>
       <c r="C232" t="s">
+        <v>263</v>
+      </c>
+      <c r="D232" t="s">
         <v>267</v>
-      </c>
-      <c r="D232" t="s">
-        <v>264</v>
       </c>
       <c r="E232" t="s">
         <v>265</v>
@@ -8908,10 +8908,10 @@
         <v>7</v>
       </c>
       <c r="C233" t="s">
+        <v>263</v>
+      </c>
+      <c r="D233" t="s">
         <v>267</v>
-      </c>
-      <c r="D233" t="s">
-        <v>264</v>
       </c>
       <c r="E233" t="s">
         <v>265</v>
@@ -8928,10 +8928,10 @@
         <v>7</v>
       </c>
       <c r="C234" t="s">
+        <v>263</v>
+      </c>
+      <c r="D234" t="s">
         <v>267</v>
-      </c>
-      <c r="D234" t="s">
-        <v>264</v>
       </c>
       <c r="E234" t="s">
         <v>265</v>
@@ -8948,10 +8948,10 @@
         <v>7</v>
       </c>
       <c r="C235" t="s">
+        <v>263</v>
+      </c>
+      <c r="D235" t="s">
         <v>267</v>
-      </c>
-      <c r="D235" t="s">
-        <v>264</v>
       </c>
       <c r="E235" t="s">
         <v>265</v>
@@ -8968,10 +8968,10 @@
         <v>7</v>
       </c>
       <c r="C236" t="s">
+        <v>263</v>
+      </c>
+      <c r="D236" t="s">
         <v>267</v>
-      </c>
-      <c r="D236" t="s">
-        <v>264</v>
       </c>
       <c r="E236" t="s">
         <v>265</v>
@@ -8988,10 +8988,10 @@
         <v>7</v>
       </c>
       <c r="C237" t="s">
+        <v>263</v>
+      </c>
+      <c r="D237" t="s">
         <v>267</v>
-      </c>
-      <c r="D237" t="s">
-        <v>264</v>
       </c>
       <c r="E237" t="s">
         <v>265</v>
@@ -9008,10 +9008,10 @@
         <v>7</v>
       </c>
       <c r="C238" t="s">
+        <v>263</v>
+      </c>
+      <c r="D238" t="s">
         <v>267</v>
-      </c>
-      <c r="D238" t="s">
-        <v>264</v>
       </c>
       <c r="E238" t="s">
         <v>265</v>
@@ -9028,10 +9028,10 @@
         <v>7</v>
       </c>
       <c r="C239" t="s">
+        <v>263</v>
+      </c>
+      <c r="D239" t="s">
         <v>267</v>
-      </c>
-      <c r="D239" t="s">
-        <v>264</v>
       </c>
       <c r="E239" t="s">
         <v>265</v>
@@ -9048,10 +9048,10 @@
         <v>7</v>
       </c>
       <c r="C240" t="s">
+        <v>263</v>
+      </c>
+      <c r="D240" t="s">
         <v>267</v>
-      </c>
-      <c r="D240" t="s">
-        <v>264</v>
       </c>
       <c r="E240" t="s">
         <v>265</v>
@@ -9068,10 +9068,10 @@
         <v>7</v>
       </c>
       <c r="C241" t="s">
+        <v>263</v>
+      </c>
+      <c r="D241" t="s">
         <v>267</v>
-      </c>
-      <c r="D241" t="s">
-        <v>264</v>
       </c>
       <c r="E241" t="s">
         <v>265</v>
@@ -9088,10 +9088,10 @@
         <v>7</v>
       </c>
       <c r="C242" t="s">
+        <v>263</v>
+      </c>
+      <c r="D242" t="s">
         <v>267</v>
-      </c>
-      <c r="D242" t="s">
-        <v>264</v>
       </c>
       <c r="E242" t="s">
         <v>265</v>
@@ -9108,10 +9108,10 @@
         <v>7</v>
       </c>
       <c r="C243" t="s">
+        <v>263</v>
+      </c>
+      <c r="D243" t="s">
         <v>267</v>
-      </c>
-      <c r="D243" t="s">
-        <v>264</v>
       </c>
       <c r="E243" t="s">
         <v>265</v>
@@ -9128,10 +9128,10 @@
         <v>7</v>
       </c>
       <c r="C244" t="s">
+        <v>263</v>
+      </c>
+      <c r="D244" t="s">
         <v>267</v>
-      </c>
-      <c r="D244" t="s">
-        <v>264</v>
       </c>
       <c r="E244" t="s">
         <v>265</v>
@@ -9168,10 +9168,10 @@
         <v>7</v>
       </c>
       <c r="C246" t="s">
+        <v>331</v>
+      </c>
+      <c r="D246" t="s">
         <v>335</v>
-      </c>
-      <c r="D246" t="s">
-        <v>332</v>
       </c>
       <c r="E246" t="s">
         <v>333</v>
@@ -9208,10 +9208,10 @@
         <v>7</v>
       </c>
       <c r="C248" t="s">
+        <v>331</v>
+      </c>
+      <c r="D248" t="s">
         <v>335</v>
-      </c>
-      <c r="D248" t="s">
-        <v>332</v>
       </c>
       <c r="E248" t="s">
         <v>333</v>
@@ -9288,10 +9288,10 @@
         <v>7</v>
       </c>
       <c r="C252" t="s">
+        <v>331</v>
+      </c>
+      <c r="D252" t="s">
         <v>342</v>
-      </c>
-      <c r="D252" t="s">
-        <v>332</v>
       </c>
       <c r="E252" t="s">
         <v>333</v>
@@ -9328,10 +9328,10 @@
         <v>7</v>
       </c>
       <c r="C254" t="s">
+        <v>267</v>
+      </c>
+      <c r="D254" t="s">
         <v>345</v>
-      </c>
-      <c r="D254" t="s">
-        <v>267</v>
       </c>
       <c r="E254" t="s">
         <v>333</v>
@@ -9388,10 +9388,10 @@
         <v>7</v>
       </c>
       <c r="C257" t="s">
+        <v>331</v>
+      </c>
+      <c r="D257" t="s">
         <v>335</v>
-      </c>
-      <c r="D257" t="s">
-        <v>332</v>
       </c>
       <c r="E257" t="s">
         <v>333</v>
@@ -9408,10 +9408,10 @@
         <v>7</v>
       </c>
       <c r="C258" t="s">
+        <v>331</v>
+      </c>
+      <c r="D258" t="s">
         <v>335</v>
-      </c>
-      <c r="D258" t="s">
-        <v>332</v>
       </c>
       <c r="E258" t="s">
         <v>333</v>
@@ -9428,10 +9428,10 @@
         <v>110</v>
       </c>
       <c r="C259" t="s">
+        <v>331</v>
+      </c>
+      <c r="D259" t="s">
         <v>351</v>
-      </c>
-      <c r="D259" t="s">
-        <v>332</v>
       </c>
       <c r="E259" t="s">
         <v>333</v>
@@ -9508,10 +9508,10 @@
         <v>7</v>
       </c>
       <c r="C263" t="s">
+        <v>331</v>
+      </c>
+      <c r="D263" t="s">
         <v>335</v>
-      </c>
-      <c r="D263" t="s">
-        <v>332</v>
       </c>
       <c r="E263" t="s">
         <v>333</v>
@@ -9528,10 +9528,10 @@
         <v>110</v>
       </c>
       <c r="C264" t="s">
+        <v>331</v>
+      </c>
+      <c r="D264" t="s">
         <v>335</v>
-      </c>
-      <c r="D264" t="s">
-        <v>332</v>
       </c>
       <c r="E264" t="s">
         <v>333</v>
@@ -9568,10 +9568,10 @@
         <v>7</v>
       </c>
       <c r="C266" t="s">
+        <v>331</v>
+      </c>
+      <c r="D266" t="s">
         <v>335</v>
-      </c>
-      <c r="D266" t="s">
-        <v>332</v>
       </c>
       <c r="E266" t="s">
         <v>333</v>
@@ -9608,10 +9608,10 @@
         <v>7</v>
       </c>
       <c r="C268" t="s">
+        <v>331</v>
+      </c>
+      <c r="D268" t="s">
         <v>335</v>
-      </c>
-      <c r="D268" t="s">
-        <v>332</v>
       </c>
       <c r="E268" t="s">
         <v>333</v>
@@ -9628,10 +9628,10 @@
         <v>7</v>
       </c>
       <c r="C269" t="s">
+        <v>331</v>
+      </c>
+      <c r="D269" t="s">
         <v>351</v>
-      </c>
-      <c r="D269" t="s">
-        <v>332</v>
       </c>
       <c r="E269" t="s">
         <v>333</v>
@@ -9648,10 +9648,10 @@
         <v>110</v>
       </c>
       <c r="C270" t="s">
+        <v>331</v>
+      </c>
+      <c r="D270" t="s">
         <v>335</v>
-      </c>
-      <c r="D270" t="s">
-        <v>332</v>
       </c>
       <c r="E270" t="s">
         <v>333</v>
@@ -9668,10 +9668,10 @@
         <v>7</v>
       </c>
       <c r="C271" t="s">
+        <v>331</v>
+      </c>
+      <c r="D271" t="s">
         <v>335</v>
-      </c>
-      <c r="D271" t="s">
-        <v>332</v>
       </c>
       <c r="E271" t="s">
         <v>333</v>
@@ -9708,10 +9708,10 @@
         <v>7</v>
       </c>
       <c r="C273" t="s">
+        <v>331</v>
+      </c>
+      <c r="D273" t="s">
         <v>335</v>
-      </c>
-      <c r="D273" t="s">
-        <v>332</v>
       </c>
       <c r="E273" t="s">
         <v>333</v>
@@ -9748,10 +9748,10 @@
         <v>7</v>
       </c>
       <c r="C275" t="s">
+        <v>331</v>
+      </c>
+      <c r="D275" t="s">
         <v>335</v>
-      </c>
-      <c r="D275" t="s">
-        <v>332</v>
       </c>
       <c r="E275" t="s">
         <v>333</v>
@@ -9768,10 +9768,10 @@
         <v>7</v>
       </c>
       <c r="C276" t="s">
+        <v>331</v>
+      </c>
+      <c r="D276" t="s">
         <v>371</v>
-      </c>
-      <c r="D276" t="s">
-        <v>332</v>
       </c>
       <c r="E276" t="s">
         <v>333</v>
@@ -9808,10 +9808,10 @@
         <v>7</v>
       </c>
       <c r="C278" t="s">
+        <v>331</v>
+      </c>
+      <c r="D278" t="s">
         <v>335</v>
-      </c>
-      <c r="D278" t="s">
-        <v>332</v>
       </c>
       <c r="E278" t="s">
         <v>333</v>
@@ -9848,10 +9848,10 @@
         <v>7</v>
       </c>
       <c r="C280" t="s">
+        <v>331</v>
+      </c>
+      <c r="D280" t="s">
         <v>335</v>
-      </c>
-      <c r="D280" t="s">
-        <v>332</v>
       </c>
       <c r="E280" t="s">
         <v>333</v>
@@ -9908,10 +9908,10 @@
         <v>7</v>
       </c>
       <c r="C283" t="s">
+        <v>331</v>
+      </c>
+      <c r="D283" t="s">
         <v>335</v>
-      </c>
-      <c r="D283" t="s">
-        <v>332</v>
       </c>
       <c r="E283" t="s">
         <v>333</v>
@@ -10008,10 +10008,10 @@
         <v>7</v>
       </c>
       <c r="C288" t="s">
+        <v>331</v>
+      </c>
+      <c r="D288" t="s">
         <v>371</v>
-      </c>
-      <c r="D288" t="s">
-        <v>332</v>
       </c>
       <c r="E288" t="s">
         <v>333</v>
@@ -10028,10 +10028,10 @@
         <v>7</v>
       </c>
       <c r="C289" t="s">
+        <v>331</v>
+      </c>
+      <c r="D289" t="s">
         <v>335</v>
-      </c>
-      <c r="D289" t="s">
-        <v>332</v>
       </c>
       <c r="E289" t="s">
         <v>333</v>
@@ -10088,10 +10088,10 @@
         <v>7</v>
       </c>
       <c r="C292" t="s">
+        <v>331</v>
+      </c>
+      <c r="D292" t="s">
         <v>371</v>
-      </c>
-      <c r="D292" t="s">
-        <v>332</v>
       </c>
       <c r="E292" t="s">
         <v>333</v>
@@ -10108,10 +10108,10 @@
         <v>7</v>
       </c>
       <c r="C293" t="s">
+        <v>331</v>
+      </c>
+      <c r="D293" t="s">
         <v>335</v>
-      </c>
-      <c r="D293" t="s">
-        <v>332</v>
       </c>
       <c r="E293" t="s">
         <v>333</v>
@@ -10248,10 +10248,10 @@
         <v>7</v>
       </c>
       <c r="C300" t="s">
+        <v>331</v>
+      </c>
+      <c r="D300" t="s">
         <v>335</v>
-      </c>
-      <c r="D300" t="s">
-        <v>332</v>
       </c>
       <c r="E300" t="s">
         <v>333</v>
@@ -10268,10 +10268,10 @@
         <v>7</v>
       </c>
       <c r="C301" t="s">
+        <v>331</v>
+      </c>
+      <c r="D301" t="s">
         <v>335</v>
-      </c>
-      <c r="D301" t="s">
-        <v>332</v>
       </c>
       <c r="E301" t="s">
         <v>333</v>
@@ -10288,10 +10288,10 @@
         <v>7</v>
       </c>
       <c r="C302" t="s">
+        <v>331</v>
+      </c>
+      <c r="D302" t="s">
         <v>335</v>
-      </c>
-      <c r="D302" t="s">
-        <v>332</v>
       </c>
       <c r="E302" t="s">
         <v>333</v>
@@ -10328,10 +10328,10 @@
         <v>7</v>
       </c>
       <c r="C304" t="s">
+        <v>331</v>
+      </c>
+      <c r="D304" t="s">
         <v>335</v>
-      </c>
-      <c r="D304" t="s">
-        <v>332</v>
       </c>
       <c r="E304" t="s">
         <v>333</v>
@@ -10388,10 +10388,10 @@
         <v>7</v>
       </c>
       <c r="C307" t="s">
+        <v>355</v>
+      </c>
+      <c r="D307" t="s">
         <v>407</v>
-      </c>
-      <c r="D307" t="s">
-        <v>356</v>
       </c>
       <c r="E307" t="s">
         <v>333</v>
@@ -10408,10 +10408,10 @@
         <v>7</v>
       </c>
       <c r="C308" t="s">
+        <v>331</v>
+      </c>
+      <c r="D308" t="s">
         <v>335</v>
-      </c>
-      <c r="D308" t="s">
-        <v>332</v>
       </c>
       <c r="E308" t="s">
         <v>333</v>
@@ -10708,10 +10708,10 @@
         <v>7</v>
       </c>
       <c r="C323" t="s">
+        <v>411</v>
+      </c>
+      <c r="D323" t="s">
         <v>427</v>
-      </c>
-      <c r="D323" t="s">
-        <v>412</v>
       </c>
       <c r="E323" t="s">
         <v>413</v>
@@ -10748,10 +10748,10 @@
         <v>7</v>
       </c>
       <c r="C325" t="s">
-        <v>411</v>
+        <v>430</v>
       </c>
       <c r="D325" t="s">
-        <v>430</v>
+        <v>412</v>
       </c>
       <c r="E325" t="s">
         <v>413</v>
@@ -10868,10 +10868,10 @@
         <v>7</v>
       </c>
       <c r="C331" t="s">
-        <v>411</v>
+        <v>437</v>
       </c>
       <c r="D331" t="s">
-        <v>437</v>
+        <v>412</v>
       </c>
       <c r="E331" t="s">
         <v>413</v>
@@ -11128,10 +11128,10 @@
         <v>110</v>
       </c>
       <c r="C344" t="s">
+        <v>450</v>
+      </c>
+      <c r="D344" t="s">
         <v>453</v>
-      </c>
-      <c r="D344" t="s">
-        <v>451</v>
       </c>
       <c r="E344" t="s">
         <v>413</v>
@@ -11168,10 +11168,10 @@
         <v>110</v>
       </c>
       <c r="C346" t="s">
+        <v>455</v>
+      </c>
+      <c r="D346" t="s">
         <v>459</v>
-      </c>
-      <c r="D346" t="s">
-        <v>456</v>
       </c>
       <c r="E346" t="s">
         <v>457</v>
@@ -11368,10 +11368,10 @@
         <v>7</v>
       </c>
       <c r="C356" t="s">
+        <v>455</v>
+      </c>
+      <c r="D356" t="s">
         <v>470</v>
-      </c>
-      <c r="D356" t="s">
-        <v>456</v>
       </c>
       <c r="E356" t="s">
         <v>457</v>
@@ -11568,10 +11568,10 @@
         <v>7</v>
       </c>
       <c r="C366" t="s">
+        <v>455</v>
+      </c>
+      <c r="D366" t="s">
         <v>481</v>
-      </c>
-      <c r="D366" t="s">
-        <v>456</v>
       </c>
       <c r="E366" t="s">
         <v>457</v>
@@ -11588,10 +11588,10 @@
         <v>7</v>
       </c>
       <c r="C367" t="s">
+        <v>455</v>
+      </c>
+      <c r="D367" t="s">
         <v>459</v>
-      </c>
-      <c r="D367" t="s">
-        <v>456</v>
       </c>
       <c r="E367" t="s">
         <v>457</v>
@@ -11668,10 +11668,10 @@
         <v>7</v>
       </c>
       <c r="C371" t="s">
-        <v>455</v>
+        <v>487</v>
       </c>
       <c r="D371" t="s">
-        <v>487</v>
+        <v>456</v>
       </c>
       <c r="E371" t="s">
         <v>457</v>
@@ -11848,10 +11848,10 @@
         <v>7</v>
       </c>
       <c r="C380" t="s">
+        <v>497</v>
+      </c>
+      <c r="D380" t="s">
         <v>502</v>
-      </c>
-      <c r="D380" t="s">
-        <v>498</v>
       </c>
       <c r="E380" t="s">
         <v>499</v>
@@ -11968,10 +11968,10 @@
         <v>7</v>
       </c>
       <c r="C386" t="s">
+        <v>497</v>
+      </c>
+      <c r="D386" t="s">
         <v>509</v>
-      </c>
-      <c r="D386" t="s">
-        <v>498</v>
       </c>
       <c r="E386" t="s">
         <v>499</v>
@@ -11988,10 +11988,10 @@
         <v>7</v>
       </c>
       <c r="C387" t="s">
+        <v>497</v>
+      </c>
+      <c r="D387" t="s">
         <v>511</v>
-      </c>
-      <c r="D387" t="s">
-        <v>498</v>
       </c>
       <c r="E387" t="s">
         <v>499</v>
@@ -12108,10 +12108,10 @@
         <v>7</v>
       </c>
       <c r="C393" t="s">
+        <v>497</v>
+      </c>
+      <c r="D393" t="s">
         <v>520</v>
-      </c>
-      <c r="D393" t="s">
-        <v>498</v>
       </c>
       <c r="E393" t="s">
         <v>499</v>
@@ -12388,10 +12388,10 @@
         <v>7</v>
       </c>
       <c r="C407" t="s">
+        <v>497</v>
+      </c>
+      <c r="D407" t="s">
         <v>543</v>
-      </c>
-      <c r="D407" t="s">
-        <v>498</v>
       </c>
       <c r="E407" t="s">
         <v>499</v>
@@ -12628,10 +12628,10 @@
         <v>7</v>
       </c>
       <c r="C419" t="s">
+        <v>554</v>
+      </c>
+      <c r="D419" t="s">
         <v>559</v>
-      </c>
-      <c r="D419" t="s">
-        <v>555</v>
       </c>
       <c r="E419" t="s">
         <v>556</v>
@@ -12668,10 +12668,10 @@
         <v>7</v>
       </c>
       <c r="C421" t="s">
+        <v>554</v>
+      </c>
+      <c r="D421" t="s">
         <v>562</v>
-      </c>
-      <c r="D421" t="s">
-        <v>555</v>
       </c>
       <c r="E421" t="s">
         <v>556</v>
@@ -12908,10 +12908,10 @@
         <v>7</v>
       </c>
       <c r="C433" t="s">
+        <v>554</v>
+      </c>
+      <c r="D433" t="s">
         <v>579</v>
-      </c>
-      <c r="D433" t="s">
-        <v>555</v>
       </c>
       <c r="E433" t="s">
         <v>556</v>
@@ -12968,10 +12968,10 @@
         <v>7</v>
       </c>
       <c r="C436" t="s">
+        <v>554</v>
+      </c>
+      <c r="D436" t="s">
         <v>583</v>
-      </c>
-      <c r="D436" t="s">
-        <v>555</v>
       </c>
       <c r="E436" t="s">
         <v>556</v>
@@ -12988,10 +12988,10 @@
         <v>7</v>
       </c>
       <c r="C437" t="s">
+        <v>554</v>
+      </c>
+      <c r="D437" t="s">
         <v>585</v>
-      </c>
-      <c r="D437" t="s">
-        <v>555</v>
       </c>
       <c r="E437" t="s">
         <v>556</v>
@@ -13548,10 +13548,10 @@
         <v>7</v>
       </c>
       <c r="C465" t="s">
+        <v>608</v>
+      </c>
+      <c r="D465" t="s">
         <v>624</v>
-      </c>
-      <c r="D465" t="s">
-        <v>609</v>
       </c>
       <c r="E465" t="s">
         <v>610</v>
@@ -13568,10 +13568,10 @@
         <v>7</v>
       </c>
       <c r="C466" t="s">
+        <v>621</v>
+      </c>
+      <c r="D466" t="s">
         <v>626</v>
-      </c>
-      <c r="D466" t="s">
-        <v>622</v>
       </c>
       <c r="E466" t="s">
         <v>610</v>
@@ -13708,10 +13708,10 @@
         <v>7</v>
       </c>
       <c r="C473" t="s">
+        <v>621</v>
+      </c>
+      <c r="D473" t="s">
         <v>638</v>
-      </c>
-      <c r="D473" t="s">
-        <v>622</v>
       </c>
       <c r="E473" t="s">
         <v>610</v>
@@ -14008,10 +14008,10 @@
         <v>7</v>
       </c>
       <c r="C488" t="s">
+        <v>653</v>
+      </c>
+      <c r="D488" t="s">
         <v>657</v>
-      </c>
-      <c r="D488" t="s">
-        <v>654</v>
       </c>
       <c r="E488" t="s">
         <v>655</v>
@@ -14088,10 +14088,10 @@
         <v>110</v>
       </c>
       <c r="C492" t="s">
-        <v>653</v>
+        <v>662</v>
       </c>
       <c r="D492" t="s">
-        <v>662</v>
+        <v>654</v>
       </c>
       <c r="E492" t="s">
         <v>655</v>
@@ -14128,10 +14128,10 @@
         <v>7</v>
       </c>
       <c r="C494" t="s">
-        <v>632</v>
+        <v>665</v>
       </c>
       <c r="D494" t="s">
-        <v>665</v>
+        <v>633</v>
       </c>
       <c r="E494" t="s">
         <v>655</v>
@@ -14148,10 +14148,10 @@
         <v>110</v>
       </c>
       <c r="C495" t="s">
-        <v>632</v>
+        <v>665</v>
       </c>
       <c r="D495" t="s">
-        <v>665</v>
+        <v>633</v>
       </c>
       <c r="E495" t="s">
         <v>655</v>
@@ -14208,10 +14208,10 @@
         <v>7</v>
       </c>
       <c r="C498" t="s">
+        <v>653</v>
+      </c>
+      <c r="D498" t="s">
         <v>670</v>
-      </c>
-      <c r="D498" t="s">
-        <v>654</v>
       </c>
       <c r="E498" t="s">
         <v>655</v>
@@ -14288,10 +14288,10 @@
         <v>110</v>
       </c>
       <c r="C502" t="s">
+        <v>653</v>
+      </c>
+      <c r="D502" t="s">
         <v>675</v>
-      </c>
-      <c r="D502" t="s">
-        <v>654</v>
       </c>
       <c r="E502" t="s">
         <v>655</v>
@@ -14428,10 +14428,10 @@
         <v>110</v>
       </c>
       <c r="C509" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="D509" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="E509" t="s">
         <v>655</v>
@@ -14488,10 +14488,10 @@
         <v>7</v>
       </c>
       <c r="C512" t="s">
+        <v>653</v>
+      </c>
+      <c r="D512" t="s">
         <v>693</v>
-      </c>
-      <c r="D512" t="s">
-        <v>654</v>
       </c>
       <c r="E512" t="s">
         <v>655</v>
@@ -14508,10 +14508,10 @@
         <v>110</v>
       </c>
       <c r="C513" t="s">
-        <v>653</v>
+        <v>695</v>
       </c>
       <c r="D513" t="s">
-        <v>695</v>
+        <v>654</v>
       </c>
       <c r="E513" t="s">
         <v>655</v>
@@ -14668,10 +14668,10 @@
         <v>110</v>
       </c>
       <c r="C521" t="s">
+        <v>653</v>
+      </c>
+      <c r="D521" t="s">
         <v>704</v>
-      </c>
-      <c r="D521" t="s">
-        <v>654</v>
       </c>
       <c r="E521" t="s">
         <v>655</v>
@@ -14688,10 +14688,10 @@
         <v>110</v>
       </c>
       <c r="C522" t="s">
+        <v>653</v>
+      </c>
+      <c r="D522" t="s">
         <v>706</v>
-      </c>
-      <c r="D522" t="s">
-        <v>654</v>
       </c>
       <c r="E522" t="s">
         <v>655</v>
@@ -14708,10 +14708,10 @@
         <v>7</v>
       </c>
       <c r="C523" t="s">
+        <v>653</v>
+      </c>
+      <c r="D523" t="s">
         <v>708</v>
-      </c>
-      <c r="D523" t="s">
-        <v>654</v>
       </c>
       <c r="E523" t="s">
         <v>655</v>
@@ -14748,10 +14748,10 @@
         <v>7</v>
       </c>
       <c r="C525" t="s">
+        <v>711</v>
+      </c>
+      <c r="D525" t="s">
         <v>657</v>
-      </c>
-      <c r="D525" t="s">
-        <v>711</v>
       </c>
       <c r="E525" t="s">
         <v>712</v>
@@ -14768,10 +14768,10 @@
         <v>7</v>
       </c>
       <c r="C526" t="s">
+        <v>711</v>
+      </c>
+      <c r="D526" t="s">
         <v>657</v>
-      </c>
-      <c r="D526" t="s">
-        <v>711</v>
       </c>
       <c r="E526" t="s">
         <v>712</v>
@@ -14788,10 +14788,10 @@
         <v>7</v>
       </c>
       <c r="C527" t="s">
+        <v>711</v>
+      </c>
+      <c r="D527" t="s">
         <v>657</v>
-      </c>
-      <c r="D527" t="s">
-        <v>711</v>
       </c>
       <c r="E527" t="s">
         <v>712</v>
@@ -14808,10 +14808,10 @@
         <v>7</v>
       </c>
       <c r="C528" t="s">
+        <v>711</v>
+      </c>
+      <c r="D528" t="s">
         <v>657</v>
-      </c>
-      <c r="D528" t="s">
-        <v>711</v>
       </c>
       <c r="E528" t="s">
         <v>712</v>
@@ -14828,10 +14828,10 @@
         <v>7</v>
       </c>
       <c r="C529" t="s">
+        <v>711</v>
+      </c>
+      <c r="D529" t="s">
         <v>718</v>
-      </c>
-      <c r="D529" t="s">
-        <v>711</v>
       </c>
       <c r="E529" t="s">
         <v>712</v>
@@ -14848,10 +14848,10 @@
         <v>7</v>
       </c>
       <c r="C530" t="s">
+        <v>720</v>
+      </c>
+      <c r="D530" t="s">
         <v>657</v>
-      </c>
-      <c r="D530" t="s">
-        <v>720</v>
       </c>
       <c r="E530" t="s">
         <v>712</v>
@@ -14868,10 +14868,10 @@
         <v>7</v>
       </c>
       <c r="C531" t="s">
+        <v>711</v>
+      </c>
+      <c r="D531" t="s">
         <v>657</v>
-      </c>
-      <c r="D531" t="s">
-        <v>711</v>
       </c>
       <c r="E531" t="s">
         <v>712</v>
@@ -14888,10 +14888,10 @@
         <v>7</v>
       </c>
       <c r="C532" t="s">
+        <v>711</v>
+      </c>
+      <c r="D532" t="s">
         <v>657</v>
-      </c>
-      <c r="D532" t="s">
-        <v>711</v>
       </c>
       <c r="E532" t="s">
         <v>712</v>
@@ -14908,10 +14908,10 @@
         <v>7</v>
       </c>
       <c r="C533" t="s">
+        <v>711</v>
+      </c>
+      <c r="D533" t="s">
         <v>657</v>
-      </c>
-      <c r="D533" t="s">
-        <v>711</v>
       </c>
       <c r="E533" t="s">
         <v>712</v>
@@ -14928,10 +14928,10 @@
         <v>7</v>
       </c>
       <c r="C534" t="s">
+        <v>711</v>
+      </c>
+      <c r="D534" t="s">
         <v>657</v>
-      </c>
-      <c r="D534" t="s">
-        <v>711</v>
       </c>
       <c r="E534" t="s">
         <v>712</v>
@@ -14948,10 +14948,10 @@
         <v>7</v>
       </c>
       <c r="C535" t="s">
+        <v>711</v>
+      </c>
+      <c r="D535" t="s">
         <v>657</v>
-      </c>
-      <c r="D535" t="s">
-        <v>711</v>
       </c>
       <c r="E535" t="s">
         <v>712</v>
@@ -14968,10 +14968,10 @@
         <v>7</v>
       </c>
       <c r="C536" t="s">
+        <v>711</v>
+      </c>
+      <c r="D536" t="s">
         <v>727</v>
-      </c>
-      <c r="D536" t="s">
-        <v>711</v>
       </c>
       <c r="E536" t="s">
         <v>712</v>
@@ -14988,10 +14988,10 @@
         <v>7</v>
       </c>
       <c r="C537" t="s">
+        <v>711</v>
+      </c>
+      <c r="D537" t="s">
         <v>729</v>
-      </c>
-      <c r="D537" t="s">
-        <v>711</v>
       </c>
       <c r="E537" t="s">
         <v>712</v>
@@ -15008,10 +15008,10 @@
         <v>7</v>
       </c>
       <c r="C538" t="s">
+        <v>711</v>
+      </c>
+      <c r="D538" t="s">
         <v>657</v>
-      </c>
-      <c r="D538" t="s">
-        <v>711</v>
       </c>
       <c r="E538" t="s">
         <v>712</v>
@@ -15028,10 +15028,10 @@
         <v>7</v>
       </c>
       <c r="C539" t="s">
+        <v>711</v>
+      </c>
+      <c r="D539" t="s">
         <v>657</v>
-      </c>
-      <c r="D539" t="s">
-        <v>711</v>
       </c>
       <c r="E539" t="s">
         <v>712</v>
@@ -15048,10 +15048,10 @@
         <v>7</v>
       </c>
       <c r="C540" t="s">
+        <v>689</v>
+      </c>
+      <c r="D540" t="s">
         <v>657</v>
-      </c>
-      <c r="D540" t="s">
-        <v>690</v>
       </c>
       <c r="E540" t="s">
         <v>712</v>
@@ -15068,10 +15068,10 @@
         <v>7</v>
       </c>
       <c r="C541" t="s">
+        <v>711</v>
+      </c>
+      <c r="D541" t="s">
         <v>657</v>
-      </c>
-      <c r="D541" t="s">
-        <v>711</v>
       </c>
       <c r="E541" t="s">
         <v>712</v>
@@ -15088,10 +15088,10 @@
         <v>7</v>
       </c>
       <c r="C542" t="s">
+        <v>711</v>
+      </c>
+      <c r="D542" t="s">
         <v>657</v>
-      </c>
-      <c r="D542" t="s">
-        <v>711</v>
       </c>
       <c r="E542" t="s">
         <v>712</v>
@@ -15108,10 +15108,10 @@
         <v>7</v>
       </c>
       <c r="C543" t="s">
+        <v>711</v>
+      </c>
+      <c r="D543" t="s">
         <v>657</v>
-      </c>
-      <c r="D543" t="s">
-        <v>711</v>
       </c>
       <c r="E543" t="s">
         <v>712</v>
@@ -15128,10 +15128,10 @@
         <v>7</v>
       </c>
       <c r="C544" t="s">
+        <v>711</v>
+      </c>
+      <c r="D544" t="s">
         <v>657</v>
-      </c>
-      <c r="D544" t="s">
-        <v>711</v>
       </c>
       <c r="E544" t="s">
         <v>712</v>
@@ -15148,10 +15148,10 @@
         <v>7</v>
       </c>
       <c r="C545" t="s">
+        <v>738</v>
+      </c>
+      <c r="D545" t="s">
         <v>657</v>
-      </c>
-      <c r="D545" t="s">
-        <v>738</v>
       </c>
       <c r="E545" t="s">
         <v>712</v>
@@ -15168,10 +15168,10 @@
         <v>7</v>
       </c>
       <c r="C546" t="s">
+        <v>711</v>
+      </c>
+      <c r="D546" t="s">
         <v>657</v>
-      </c>
-      <c r="D546" t="s">
-        <v>711</v>
       </c>
       <c r="E546" t="s">
         <v>712</v>
@@ -15188,10 +15188,10 @@
         <v>7</v>
       </c>
       <c r="C547" t="s">
+        <v>711</v>
+      </c>
+      <c r="D547" t="s">
         <v>657</v>
-      </c>
-      <c r="D547" t="s">
-        <v>711</v>
       </c>
       <c r="E547" t="s">
         <v>712</v>
@@ -15228,10 +15228,10 @@
         <v>7</v>
       </c>
       <c r="C549" t="s">
+        <v>742</v>
+      </c>
+      <c r="D549" t="s">
         <v>746</v>
-      </c>
-      <c r="D549" t="s">
-        <v>743</v>
       </c>
       <c r="E549" t="s">
         <v>744</v>
@@ -15248,10 +15248,10 @@
         <v>7</v>
       </c>
       <c r="C550" t="s">
+        <v>742</v>
+      </c>
+      <c r="D550" t="s">
         <v>748</v>
-      </c>
-      <c r="D550" t="s">
-        <v>743</v>
       </c>
       <c r="E550" t="s">
         <v>744</v>
@@ -15328,10 +15328,10 @@
         <v>7</v>
       </c>
       <c r="C554" t="s">
-        <v>742</v>
+        <v>753</v>
       </c>
       <c r="D554" t="s">
-        <v>753</v>
+        <v>743</v>
       </c>
       <c r="E554" t="s">
         <v>744</v>
@@ -15448,10 +15448,10 @@
         <v>7</v>
       </c>
       <c r="C560" t="s">
+        <v>742</v>
+      </c>
+      <c r="D560" t="s">
         <v>762</v>
-      </c>
-      <c r="D560" t="s">
-        <v>743</v>
       </c>
       <c r="E560" t="s">
         <v>744</v>
@@ -15468,10 +15468,10 @@
         <v>7</v>
       </c>
       <c r="C561" t="s">
+        <v>742</v>
+      </c>
+      <c r="D561" t="s">
         <v>762</v>
-      </c>
-      <c r="D561" t="s">
-        <v>743</v>
       </c>
       <c r="E561" t="s">
         <v>744</v>
@@ -15508,10 +15508,10 @@
         <v>7</v>
       </c>
       <c r="C563" t="s">
-        <v>742</v>
+        <v>766</v>
       </c>
       <c r="D563" t="s">
-        <v>766</v>
+        <v>743</v>
       </c>
       <c r="E563" t="s">
         <v>744</v>
@@ -15708,10 +15708,10 @@
         <v>7</v>
       </c>
       <c r="C573" t="s">
+        <v>711</v>
+      </c>
+      <c r="D573" t="s">
         <v>779</v>
-      </c>
-      <c r="D573" t="s">
-        <v>711</v>
       </c>
       <c r="E573" t="s">
         <v>780</v>
@@ -15728,10 +15728,10 @@
         <v>7</v>
       </c>
       <c r="C574" t="s">
+        <v>782</v>
+      </c>
+      <c r="D574" t="s">
         <v>779</v>
-      </c>
-      <c r="D574" t="s">
-        <v>782</v>
       </c>
       <c r="E574" t="s">
         <v>780</v>
@@ -15748,10 +15748,10 @@
         <v>7</v>
       </c>
       <c r="C575" t="s">
+        <v>782</v>
+      </c>
+      <c r="D575" t="s">
         <v>779</v>
-      </c>
-      <c r="D575" t="s">
-        <v>782</v>
       </c>
       <c r="E575" t="s">
         <v>780</v>
@@ -15768,10 +15768,10 @@
         <v>7</v>
       </c>
       <c r="C576" t="s">
+        <v>782</v>
+      </c>
+      <c r="D576" t="s">
         <v>779</v>
-      </c>
-      <c r="D576" t="s">
-        <v>782</v>
       </c>
       <c r="E576" t="s">
         <v>780</v>
@@ -15788,10 +15788,10 @@
         <v>7</v>
       </c>
       <c r="C577" t="s">
+        <v>742</v>
+      </c>
+      <c r="D577" t="s">
         <v>779</v>
-      </c>
-      <c r="D577" t="s">
-        <v>743</v>
       </c>
       <c r="E577" t="s">
         <v>780</v>
@@ -15808,10 +15808,10 @@
         <v>7</v>
       </c>
       <c r="C578" t="s">
+        <v>782</v>
+      </c>
+      <c r="D578" t="s">
         <v>787</v>
-      </c>
-      <c r="D578" t="s">
-        <v>782</v>
       </c>
       <c r="E578" t="s">
         <v>780</v>
@@ -15848,10 +15848,10 @@
         <v>7</v>
       </c>
       <c r="C580" t="s">
+        <v>782</v>
+      </c>
+      <c r="D580" t="s">
         <v>792</v>
-      </c>
-      <c r="D580" t="s">
-        <v>782</v>
       </c>
       <c r="E580" t="s">
         <v>780</v>
@@ -15868,10 +15868,10 @@
         <v>7</v>
       </c>
       <c r="C581" t="s">
+        <v>782</v>
+      </c>
+      <c r="D581" t="s">
         <v>794</v>
-      </c>
-      <c r="D581" t="s">
-        <v>782</v>
       </c>
       <c r="E581" t="s">
         <v>780</v>
@@ -15888,10 +15888,10 @@
         <v>7</v>
       </c>
       <c r="C582" t="s">
+        <v>782</v>
+      </c>
+      <c r="D582" t="s">
         <v>779</v>
-      </c>
-      <c r="D582" t="s">
-        <v>782</v>
       </c>
       <c r="E582" t="s">
         <v>780</v>
@@ -15948,10 +15948,10 @@
         <v>7</v>
       </c>
       <c r="C585" t="s">
+        <v>782</v>
+      </c>
+      <c r="D585" t="s">
         <v>779</v>
-      </c>
-      <c r="D585" t="s">
-        <v>782</v>
       </c>
       <c r="E585" t="s">
         <v>780</v>
@@ -15988,10 +15988,10 @@
         <v>7</v>
       </c>
       <c r="C587" t="s">
+        <v>782</v>
+      </c>
+      <c r="D587" t="s">
         <v>807</v>
-      </c>
-      <c r="D587" t="s">
-        <v>782</v>
       </c>
       <c r="E587" t="s">
         <v>780</v>
@@ -16008,10 +16008,10 @@
         <v>7</v>
       </c>
       <c r="C588" t="s">
+        <v>782</v>
+      </c>
+      <c r="D588" t="s">
         <v>809</v>
-      </c>
-      <c r="D588" t="s">
-        <v>782</v>
       </c>
       <c r="E588" t="s">
         <v>780</v>
@@ -16028,10 +16028,10 @@
         <v>7</v>
       </c>
       <c r="C589" t="s">
+        <v>782</v>
+      </c>
+      <c r="D589" t="s">
         <v>779</v>
-      </c>
-      <c r="D589" t="s">
-        <v>782</v>
       </c>
       <c r="E589" t="s">
         <v>780</v>
@@ -16048,10 +16048,10 @@
         <v>7</v>
       </c>
       <c r="C590" t="s">
+        <v>782</v>
+      </c>
+      <c r="D590" t="s">
         <v>779</v>
-      </c>
-      <c r="D590" t="s">
-        <v>782</v>
       </c>
       <c r="E590" t="s">
         <v>780</v>
@@ -16068,10 +16068,10 @@
         <v>7</v>
       </c>
       <c r="C591" t="s">
+        <v>782</v>
+      </c>
+      <c r="D591" t="s">
         <v>779</v>
-      </c>
-      <c r="D591" t="s">
-        <v>782</v>
       </c>
       <c r="E591" t="s">
         <v>780</v>
@@ -16088,10 +16088,10 @@
         <v>7</v>
       </c>
       <c r="C592" t="s">
+        <v>814</v>
+      </c>
+      <c r="D592" t="s">
         <v>779</v>
-      </c>
-      <c r="D592" t="s">
-        <v>814</v>
       </c>
       <c r="E592" t="s">
         <v>780</v>
@@ -16108,10 +16108,10 @@
         <v>7</v>
       </c>
       <c r="C593" t="s">
+        <v>782</v>
+      </c>
+      <c r="D593" t="s">
         <v>779</v>
-      </c>
-      <c r="D593" t="s">
-        <v>782</v>
       </c>
       <c r="E593" t="s">
         <v>780</v>
@@ -16128,10 +16128,10 @@
         <v>7</v>
       </c>
       <c r="C594" t="s">
+        <v>782</v>
+      </c>
+      <c r="D594" t="s">
         <v>779</v>
-      </c>
-      <c r="D594" t="s">
-        <v>782</v>
       </c>
       <c r="E594" t="s">
         <v>780</v>
@@ -16148,10 +16148,10 @@
         <v>7</v>
       </c>
       <c r="C595" t="s">
+        <v>782</v>
+      </c>
+      <c r="D595" t="s">
         <v>779</v>
-      </c>
-      <c r="D595" t="s">
-        <v>782</v>
       </c>
       <c r="E595" t="s">
         <v>780</v>
@@ -16168,10 +16168,10 @@
         <v>7</v>
       </c>
       <c r="C596" t="s">
+        <v>782</v>
+      </c>
+      <c r="D596" t="s">
         <v>779</v>
-      </c>
-      <c r="D596" t="s">
-        <v>782</v>
       </c>
       <c r="E596" t="s">
         <v>780</v>
@@ -16348,10 +16348,10 @@
         <v>7</v>
       </c>
       <c r="C605" t="s">
+        <v>820</v>
+      </c>
+      <c r="D605" t="s">
         <v>839</v>
-      </c>
-      <c r="D605" t="s">
-        <v>821</v>
       </c>
       <c r="E605" t="s">
         <v>822</v>
@@ -16428,10 +16428,10 @@
         <v>7</v>
       </c>
       <c r="C609" t="s">
+        <v>807</v>
+      </c>
+      <c r="D609" t="s">
         <v>846</v>
-      </c>
-      <c r="D609" t="s">
-        <v>807</v>
       </c>
       <c r="E609" t="s">
         <v>822</v>
@@ -16468,10 +16468,10 @@
         <v>7</v>
       </c>
       <c r="C611" t="s">
-        <v>824</v>
+        <v>849</v>
       </c>
       <c r="D611" t="s">
-        <v>849</v>
+        <v>825</v>
       </c>
       <c r="E611" t="s">
         <v>822</v>
@@ -16488,10 +16488,10 @@
         <v>7</v>
       </c>
       <c r="C612" t="s">
+        <v>820</v>
+      </c>
+      <c r="D612" t="s">
         <v>851</v>
-      </c>
-      <c r="D612" t="s">
-        <v>821</v>
       </c>
       <c r="E612" t="s">
         <v>822</v>
@@ -16528,10 +16528,10 @@
         <v>7</v>
       </c>
       <c r="C614" t="s">
+        <v>820</v>
+      </c>
+      <c r="D614" t="s">
         <v>854</v>
-      </c>
-      <c r="D614" t="s">
-        <v>821</v>
       </c>
       <c r="E614" t="s">
         <v>822</v>
@@ -16808,10 +16808,10 @@
         <v>7</v>
       </c>
       <c r="C628" t="s">
-        <v>864</v>
+        <v>874</v>
       </c>
       <c r="D628" t="s">
-        <v>874</v>
+        <v>865</v>
       </c>
       <c r="E628" t="s">
         <v>866</v>
@@ -16828,10 +16828,10 @@
         <v>7</v>
       </c>
       <c r="C629" t="s">
+        <v>864</v>
+      </c>
+      <c r="D629" t="s">
         <v>876</v>
-      </c>
-      <c r="D629" t="s">
-        <v>865</v>
       </c>
       <c r="E629" t="s">
         <v>866</v>
@@ -16888,10 +16888,10 @@
         <v>7</v>
       </c>
       <c r="C632" t="s">
+        <v>880</v>
+      </c>
+      <c r="D632" t="s">
         <v>876</v>
-      </c>
-      <c r="D632" t="s">
-        <v>880</v>
       </c>
       <c r="E632" t="s">
         <v>866</v>
@@ -16968,10 +16968,10 @@
         <v>7</v>
       </c>
       <c r="C636" t="s">
+        <v>864</v>
+      </c>
+      <c r="D636" t="s">
         <v>889</v>
-      </c>
-      <c r="D636" t="s">
-        <v>865</v>
       </c>
       <c r="E636" t="s">
         <v>866</v>
@@ -17088,10 +17088,10 @@
         <v>7</v>
       </c>
       <c r="C642" t="s">
+        <v>864</v>
+      </c>
+      <c r="D642" t="s">
         <v>900</v>
-      </c>
-      <c r="D642" t="s">
-        <v>865</v>
       </c>
       <c r="E642" t="s">
         <v>866</v>
@@ -17108,10 +17108,10 @@
         <v>7</v>
       </c>
       <c r="C643" t="s">
+        <v>864</v>
+      </c>
+      <c r="D643" t="s">
         <v>902</v>
-      </c>
-      <c r="D643" t="s">
-        <v>865</v>
       </c>
       <c r="E643" t="s">
         <v>866</v>
@@ -17168,10 +17168,10 @@
         <v>7</v>
       </c>
       <c r="C646" t="s">
+        <v>864</v>
+      </c>
+      <c r="D646" t="s">
         <v>906</v>
-      </c>
-      <c r="D646" t="s">
-        <v>865</v>
       </c>
       <c r="E646" t="s">
         <v>866</v>
@@ -17268,10 +17268,10 @@
         <v>7</v>
       </c>
       <c r="C651" t="s">
-        <v>910</v>
+        <v>917</v>
       </c>
       <c r="D651" t="s">
-        <v>917</v>
+        <v>911</v>
       </c>
       <c r="E651" t="s">
         <v>912</v>
@@ -17328,10 +17328,10 @@
         <v>7</v>
       </c>
       <c r="C654" t="s">
+        <v>864</v>
+      </c>
+      <c r="D654" t="s">
         <v>902</v>
-      </c>
-      <c r="D654" t="s">
-        <v>865</v>
       </c>
       <c r="E654" t="s">
         <v>912</v>
@@ -17428,10 +17428,10 @@
         <v>7</v>
       </c>
       <c r="C659" t="s">
+        <v>932</v>
+      </c>
+      <c r="D659" t="s">
         <v>889</v>
-      </c>
-      <c r="D659" t="s">
-        <v>932</v>
       </c>
       <c r="E659" t="s">
         <v>912</v>
@@ -17488,10 +17488,10 @@
         <v>7</v>
       </c>
       <c r="C662" t="s">
-        <v>919</v>
+        <v>915</v>
       </c>
       <c r="D662" t="s">
-        <v>914</v>
+        <v>920</v>
       </c>
       <c r="E662" t="s">
         <v>912</v>
@@ -17528,10 +17528,10 @@
         <v>7</v>
       </c>
       <c r="C664" t="s">
+        <v>942</v>
+      </c>
+      <c r="D664" t="s">
         <v>902</v>
-      </c>
-      <c r="D664" t="s">
-        <v>942</v>
       </c>
       <c r="E664" t="s">
         <v>912</v>
@@ -17548,10 +17548,10 @@
         <v>7</v>
       </c>
       <c r="C665" t="s">
+        <v>919</v>
+      </c>
+      <c r="D665" t="s">
         <v>944</v>
-      </c>
-      <c r="D665" t="s">
-        <v>920</v>
       </c>
       <c r="E665" t="s">
         <v>912</v>
@@ -17568,10 +17568,10 @@
         <v>7</v>
       </c>
       <c r="C666" t="s">
+        <v>910</v>
+      </c>
+      <c r="D666" t="s">
         <v>944</v>
-      </c>
-      <c r="D666" t="s">
-        <v>911</v>
       </c>
       <c r="E666" t="s">
         <v>912</v>
@@ -17628,10 +17628,10 @@
         <v>7</v>
       </c>
       <c r="C669" t="s">
+        <v>932</v>
+      </c>
+      <c r="D669" t="s">
         <v>902</v>
-      </c>
-      <c r="D669" t="s">
-        <v>932</v>
       </c>
       <c r="E669" t="s">
         <v>912</v>
@@ -17668,10 +17668,10 @@
         <v>7</v>
       </c>
       <c r="C671" t="s">
-        <v>910</v>
+        <v>953</v>
       </c>
       <c r="D671" t="s">
-        <v>953</v>
+        <v>911</v>
       </c>
       <c r="E671" t="s">
         <v>912</v>
@@ -17728,10 +17728,10 @@
         <v>7</v>
       </c>
       <c r="C674" t="s">
+        <v>934</v>
+      </c>
+      <c r="D674" t="s">
         <v>902</v>
-      </c>
-      <c r="D674" t="s">
-        <v>935</v>
       </c>
       <c r="E674" t="s">
         <v>912</v>
@@ -17748,10 +17748,10 @@
         <v>7</v>
       </c>
       <c r="C675" t="s">
-        <v>910</v>
+        <v>917</v>
       </c>
       <c r="D675" t="s">
-        <v>917</v>
+        <v>911</v>
       </c>
       <c r="E675" t="s">
         <v>912</v>
@@ -17768,10 +17768,10 @@
         <v>7</v>
       </c>
       <c r="C676" t="s">
+        <v>919</v>
+      </c>
+      <c r="D676" t="s">
         <v>959</v>
-      </c>
-      <c r="D676" t="s">
-        <v>920</v>
       </c>
       <c r="E676" t="s">
         <v>912</v>
@@ -18028,10 +18028,10 @@
         <v>7</v>
       </c>
       <c r="C689" t="s">
-        <v>970</v>
+        <v>980</v>
       </c>
       <c r="D689" t="s">
-        <v>980</v>
+        <v>971</v>
       </c>
       <c r="E689" t="s">
         <v>968</v>
@@ -18088,10 +18088,10 @@
         <v>7</v>
       </c>
       <c r="C692" t="s">
+        <v>919</v>
+      </c>
+      <c r="D692" t="s">
         <v>986</v>
-      </c>
-      <c r="D692" t="s">
-        <v>920</v>
       </c>
       <c r="E692" t="s">
         <v>968</v>
@@ -18308,10 +18308,10 @@
         <v>7</v>
       </c>
       <c r="C703" t="s">
+        <v>1005</v>
+      </c>
+      <c r="D703" t="s">
         <v>1012</v>
-      </c>
-      <c r="D703" t="s">
-        <v>1006</v>
       </c>
       <c r="E703" t="s">
         <v>968</v>
@@ -18348,10 +18348,10 @@
         <v>7</v>
       </c>
       <c r="C705" t="s">
+        <v>1001</v>
+      </c>
+      <c r="D705" t="s">
         <v>1015</v>
-      </c>
-      <c r="D705" t="s">
-        <v>1002</v>
       </c>
       <c r="E705" t="s">
         <v>968</v>
@@ -18388,10 +18388,10 @@
         <v>7</v>
       </c>
       <c r="C707" t="s">
-        <v>973</v>
+        <v>1001</v>
       </c>
       <c r="D707" t="s">
-        <v>1002</v>
+        <v>974</v>
       </c>
       <c r="E707" t="s">
         <v>968</v>
@@ -18408,10 +18408,10 @@
         <v>7</v>
       </c>
       <c r="C708" t="s">
+        <v>970</v>
+      </c>
+      <c r="D708" t="s">
         <v>1019</v>
-      </c>
-      <c r="D708" t="s">
-        <v>971</v>
       </c>
       <c r="E708" t="s">
         <v>968</v>
@@ -18468,10 +18468,10 @@
         <v>7</v>
       </c>
       <c r="C711" t="s">
-        <v>973</v>
+        <v>1001</v>
       </c>
       <c r="D711" t="s">
-        <v>1002</v>
+        <v>974</v>
       </c>
       <c r="E711" t="s">
         <v>968</v>
@@ -18548,10 +18548,10 @@
         <v>7</v>
       </c>
       <c r="C715" t="s">
-        <v>998</v>
+        <v>1001</v>
       </c>
       <c r="D715" t="s">
-        <v>1002</v>
+        <v>999</v>
       </c>
       <c r="E715" t="s">
         <v>968</v>
@@ -18628,10 +18628,10 @@
         <v>7</v>
       </c>
       <c r="C719" t="s">
+        <v>1032</v>
+      </c>
+      <c r="D719" t="s">
         <v>1036</v>
-      </c>
-      <c r="D719" t="s">
-        <v>1033</v>
       </c>
       <c r="E719" t="s">
         <v>1034</v>
@@ -18648,10 +18648,10 @@
         <v>7</v>
       </c>
       <c r="C720" t="s">
+        <v>1032</v>
+      </c>
+      <c r="D720" t="s">
         <v>1036</v>
-      </c>
-      <c r="D720" t="s">
-        <v>1033</v>
       </c>
       <c r="E720" t="s">
         <v>1034</v>
@@ -18668,10 +18668,10 @@
         <v>7</v>
       </c>
       <c r="C721" t="s">
+        <v>1032</v>
+      </c>
+      <c r="D721" t="s">
         <v>1036</v>
-      </c>
-      <c r="D721" t="s">
-        <v>1033</v>
       </c>
       <c r="E721" t="s">
         <v>1034</v>
@@ -18688,10 +18688,10 @@
         <v>7</v>
       </c>
       <c r="C722" t="s">
+        <v>1032</v>
+      </c>
+      <c r="D722" t="s">
         <v>1036</v>
-      </c>
-      <c r="D722" t="s">
-        <v>1033</v>
       </c>
       <c r="E722" t="s">
         <v>1034</v>
@@ -18708,10 +18708,10 @@
         <v>7</v>
       </c>
       <c r="C723" t="s">
+        <v>1032</v>
+      </c>
+      <c r="D723" t="s">
         <v>1036</v>
-      </c>
-      <c r="D723" t="s">
-        <v>1033</v>
       </c>
       <c r="E723" t="s">
         <v>1034</v>
@@ -18728,10 +18728,10 @@
         <v>7</v>
       </c>
       <c r="C724" t="s">
+        <v>1032</v>
+      </c>
+      <c r="D724" t="s">
         <v>1036</v>
-      </c>
-      <c r="D724" t="s">
-        <v>1033</v>
       </c>
       <c r="E724" t="s">
         <v>1034</v>
@@ -18788,10 +18788,10 @@
         <v>7</v>
       </c>
       <c r="C727" t="s">
+        <v>1032</v>
+      </c>
+      <c r="D727" t="s">
         <v>1036</v>
-      </c>
-      <c r="D727" t="s">
-        <v>1033</v>
       </c>
       <c r="E727" t="s">
         <v>1034</v>
@@ -18808,10 +18808,10 @@
         <v>7</v>
       </c>
       <c r="C728" t="s">
+        <v>1032</v>
+      </c>
+      <c r="D728" t="s">
         <v>1036</v>
-      </c>
-      <c r="D728" t="s">
-        <v>1033</v>
       </c>
       <c r="E728" t="s">
         <v>1034</v>
@@ -18848,10 +18848,10 @@
         <v>7</v>
       </c>
       <c r="C730" t="s">
+        <v>1032</v>
+      </c>
+      <c r="D730" t="s">
         <v>1036</v>
-      </c>
-      <c r="D730" t="s">
-        <v>1033</v>
       </c>
       <c r="E730" t="s">
         <v>1034</v>
@@ -18908,10 +18908,10 @@
         <v>7</v>
       </c>
       <c r="C733" t="s">
+        <v>1032</v>
+      </c>
+      <c r="D733" t="s">
         <v>1059</v>
-      </c>
-      <c r="D733" t="s">
-        <v>1033</v>
       </c>
       <c r="E733" t="s">
         <v>1034</v>
@@ -18948,10 +18948,10 @@
         <v>7</v>
       </c>
       <c r="C735" t="s">
+        <v>1032</v>
+      </c>
+      <c r="D735" t="s">
         <v>1036</v>
-      </c>
-      <c r="D735" t="s">
-        <v>1033</v>
       </c>
       <c r="E735" t="s">
         <v>1034</v>
@@ -18968,10 +18968,10 @@
         <v>7</v>
       </c>
       <c r="C736" t="s">
+        <v>1032</v>
+      </c>
+      <c r="D736" t="s">
         <v>1065</v>
-      </c>
-      <c r="D736" t="s">
-        <v>1033</v>
       </c>
       <c r="E736" t="s">
         <v>1034</v>
@@ -18988,10 +18988,10 @@
         <v>7</v>
       </c>
       <c r="C737" t="s">
+        <v>1032</v>
+      </c>
+      <c r="D737" t="s">
         <v>1036</v>
-      </c>
-      <c r="D737" t="s">
-        <v>1033</v>
       </c>
       <c r="E737" t="s">
         <v>1034</v>
@@ -19008,10 +19008,10 @@
         <v>7</v>
       </c>
       <c r="C738" t="s">
+        <v>973</v>
+      </c>
+      <c r="D738" t="s">
         <v>1068</v>
-      </c>
-      <c r="D738" t="s">
-        <v>974</v>
       </c>
       <c r="E738" t="s">
         <v>1034</v>
@@ -19028,10 +19028,10 @@
         <v>7</v>
       </c>
       <c r="C739" t="s">
+        <v>1032</v>
+      </c>
+      <c r="D739" t="s">
         <v>1036</v>
-      </c>
-      <c r="D739" t="s">
-        <v>1033</v>
       </c>
       <c r="E739" t="s">
         <v>1034</v>
@@ -19048,10 +19048,10 @@
         <v>7</v>
       </c>
       <c r="C740" t="s">
+        <v>1032</v>
+      </c>
+      <c r="D740" t="s">
         <v>1036</v>
-      </c>
-      <c r="D740" t="s">
-        <v>1033</v>
       </c>
       <c r="E740" t="s">
         <v>1034</v>
@@ -19088,10 +19088,10 @@
         <v>7</v>
       </c>
       <c r="C742" t="s">
+        <v>1032</v>
+      </c>
+      <c r="D742" t="s">
         <v>1075</v>
-      </c>
-      <c r="D742" t="s">
-        <v>1033</v>
       </c>
       <c r="E742" t="s">
         <v>1034</v>
@@ -19108,10 +19108,10 @@
         <v>7</v>
       </c>
       <c r="C743" t="s">
+        <v>1032</v>
+      </c>
+      <c r="D743" t="s">
         <v>1036</v>
-      </c>
-      <c r="D743" t="s">
-        <v>1033</v>
       </c>
       <c r="E743" t="s">
         <v>1034</v>
@@ -19148,10 +19148,10 @@
         <v>7</v>
       </c>
       <c r="C745" t="s">
+        <v>1032</v>
+      </c>
+      <c r="D745" t="s">
         <v>1079</v>
-      </c>
-      <c r="D745" t="s">
-        <v>1033</v>
       </c>
       <c r="E745" t="s">
         <v>1034</v>
@@ -19168,10 +19168,10 @@
         <v>7</v>
       </c>
       <c r="C746" t="s">
+        <v>1032</v>
+      </c>
+      <c r="D746" t="s">
         <v>1036</v>
-      </c>
-      <c r="D746" t="s">
-        <v>1033</v>
       </c>
       <c r="E746" t="s">
         <v>1034</v>
@@ -19188,10 +19188,10 @@
         <v>7</v>
       </c>
       <c r="C747" t="s">
+        <v>1032</v>
+      </c>
+      <c r="D747" t="s">
         <v>1036</v>
-      </c>
-      <c r="D747" t="s">
-        <v>1033</v>
       </c>
       <c r="E747" t="s">
         <v>1034</v>
@@ -19208,10 +19208,10 @@
         <v>7</v>
       </c>
       <c r="C748" t="s">
+        <v>1032</v>
+      </c>
+      <c r="D748" t="s">
         <v>1036</v>
-      </c>
-      <c r="D748" t="s">
-        <v>1033</v>
       </c>
       <c r="E748" t="s">
         <v>1034</v>
@@ -19228,10 +19228,10 @@
         <v>7</v>
       </c>
       <c r="C749" t="s">
+        <v>1032</v>
+      </c>
+      <c r="D749" t="s">
         <v>1036</v>
-      </c>
-      <c r="D749" t="s">
-        <v>1033</v>
       </c>
       <c r="E749" t="s">
         <v>1034</v>
@@ -19408,10 +19408,10 @@
         <v>7</v>
       </c>
       <c r="C758" t="s">
-        <v>1085</v>
+        <v>1089</v>
       </c>
       <c r="D758" t="s">
-        <v>1090</v>
+        <v>1086</v>
       </c>
       <c r="E758" t="s">
         <v>1087</v>
@@ -19428,10 +19428,10 @@
         <v>7</v>
       </c>
       <c r="C759" t="s">
+        <v>1092</v>
+      </c>
+      <c r="D759" t="s">
         <v>1065</v>
-      </c>
-      <c r="D759" t="s">
-        <v>1093</v>
       </c>
       <c r="E759" t="s">
         <v>1087</v>
@@ -19488,10 +19488,10 @@
         <v>7</v>
       </c>
       <c r="C762" t="s">
+        <v>1104</v>
+      </c>
+      <c r="D762" t="s">
         <v>1065</v>
-      </c>
-      <c r="D762" t="s">
-        <v>1104</v>
       </c>
       <c r="E762" t="s">
         <v>1087</v>
@@ -19548,10 +19548,10 @@
         <v>7</v>
       </c>
       <c r="C765" t="s">
-        <v>1092</v>
+        <v>1085</v>
       </c>
       <c r="D765" t="s">
-        <v>1086</v>
+        <v>1093</v>
       </c>
       <c r="E765" t="s">
         <v>1087</v>
@@ -19568,10 +19568,10 @@
         <v>7</v>
       </c>
       <c r="C766" t="s">
+        <v>1104</v>
+      </c>
+      <c r="D766" t="s">
         <v>1111</v>
-      </c>
-      <c r="D766" t="s">
-        <v>1104</v>
       </c>
       <c r="E766" t="s">
         <v>1087</v>
@@ -19788,10 +19788,10 @@
         <v>7</v>
       </c>
       <c r="C777" t="s">
+        <v>1128</v>
+      </c>
+      <c r="D777" t="s">
         <v>1132</v>
-      </c>
-      <c r="D777" t="s">
-        <v>1129</v>
       </c>
       <c r="E777" t="s">
         <v>1130</v>
@@ -19848,10 +19848,10 @@
         <v>7</v>
       </c>
       <c r="C780" t="s">
+        <v>1128</v>
+      </c>
+      <c r="D780" t="s">
         <v>1132</v>
-      </c>
-      <c r="D780" t="s">
-        <v>1129</v>
       </c>
       <c r="E780" t="s">
         <v>1130</v>
@@ -19868,10 +19868,10 @@
         <v>7</v>
       </c>
       <c r="C781" t="s">
+        <v>1128</v>
+      </c>
+      <c r="D781" t="s">
         <v>1132</v>
-      </c>
-      <c r="D781" t="s">
-        <v>1129</v>
       </c>
       <c r="E781" t="s">
         <v>1130</v>
@@ -19888,10 +19888,10 @@
         <v>7</v>
       </c>
       <c r="C782" t="s">
+        <v>1128</v>
+      </c>
+      <c r="D782" t="s">
         <v>1142</v>
-      </c>
-      <c r="D782" t="s">
-        <v>1129</v>
       </c>
       <c r="E782" t="s">
         <v>1130</v>
@@ -19908,10 +19908,10 @@
         <v>7</v>
       </c>
       <c r="C783" t="s">
+        <v>1128</v>
+      </c>
+      <c r="D783" t="s">
         <v>1132</v>
-      </c>
-      <c r="D783" t="s">
-        <v>1129</v>
       </c>
       <c r="E783" t="s">
         <v>1130</v>
@@ -19928,10 +19928,10 @@
         <v>7</v>
       </c>
       <c r="C784" t="s">
+        <v>1128</v>
+      </c>
+      <c r="D784" t="s">
         <v>1132</v>
-      </c>
-      <c r="D784" t="s">
-        <v>1129</v>
       </c>
       <c r="E784" t="s">
         <v>1130</v>
@@ -19948,10 +19948,10 @@
         <v>7</v>
       </c>
       <c r="C785" t="s">
+        <v>1128</v>
+      </c>
+      <c r="D785" t="s">
         <v>1132</v>
-      </c>
-      <c r="D785" t="s">
-        <v>1129</v>
       </c>
       <c r="E785" t="s">
         <v>1130</v>
@@ -19968,10 +19968,10 @@
         <v>7</v>
       </c>
       <c r="C786" t="s">
+        <v>1128</v>
+      </c>
+      <c r="D786" t="s">
         <v>1132</v>
-      </c>
-      <c r="D786" t="s">
-        <v>1129</v>
       </c>
       <c r="E786" t="s">
         <v>1130</v>
@@ -19988,10 +19988,10 @@
         <v>7</v>
       </c>
       <c r="C787" t="s">
+        <v>1128</v>
+      </c>
+      <c r="D787" t="s">
         <v>1132</v>
-      </c>
-      <c r="D787" t="s">
-        <v>1129</v>
       </c>
       <c r="E787" t="s">
         <v>1130</v>
@@ -20008,10 +20008,10 @@
         <v>7</v>
       </c>
       <c r="C788" t="s">
+        <v>1128</v>
+      </c>
+      <c r="D788" t="s">
         <v>1132</v>
-      </c>
-      <c r="D788" t="s">
-        <v>1129</v>
       </c>
       <c r="E788" t="s">
         <v>1130</v>
@@ -20028,10 +20028,10 @@
         <v>7</v>
       </c>
       <c r="C789" t="s">
-        <v>1128</v>
+        <v>1150</v>
       </c>
       <c r="D789" t="s">
-        <v>1150</v>
+        <v>1129</v>
       </c>
       <c r="E789" t="s">
         <v>1130</v>
@@ -20048,10 +20048,10 @@
         <v>7</v>
       </c>
       <c r="C790" t="s">
+        <v>1128</v>
+      </c>
+      <c r="D790" t="s">
         <v>1132</v>
-      </c>
-      <c r="D790" t="s">
-        <v>1129</v>
       </c>
       <c r="E790" t="s">
         <v>1130</v>
@@ -20068,10 +20068,10 @@
         <v>7</v>
       </c>
       <c r="C791" t="s">
+        <v>1153</v>
+      </c>
+      <c r="D791" t="s">
         <v>1142</v>
-      </c>
-      <c r="D791" t="s">
-        <v>1153</v>
       </c>
       <c r="E791" t="s">
         <v>1130</v>
@@ -20088,10 +20088,10 @@
         <v>7</v>
       </c>
       <c r="C792" t="s">
+        <v>1150</v>
+      </c>
+      <c r="D792" t="s">
         <v>1155</v>
-      </c>
-      <c r="D792" t="s">
-        <v>1150</v>
       </c>
       <c r="E792" t="s">
         <v>1130</v>
@@ -20108,10 +20108,10 @@
         <v>7</v>
       </c>
       <c r="C793" t="s">
+        <v>1128</v>
+      </c>
+      <c r="D793" t="s">
         <v>1132</v>
-      </c>
-      <c r="D793" t="s">
-        <v>1129</v>
       </c>
       <c r="E793" t="s">
         <v>1130</v>
@@ -20128,10 +20128,10 @@
         <v>7</v>
       </c>
       <c r="C794" t="s">
+        <v>1158</v>
+      </c>
+      <c r="D794" t="s">
         <v>1132</v>
-      </c>
-      <c r="D794" t="s">
-        <v>1158</v>
       </c>
       <c r="E794" t="s">
         <v>1130</v>
@@ -20148,10 +20148,10 @@
         <v>7</v>
       </c>
       <c r="C795" t="s">
+        <v>1128</v>
+      </c>
+      <c r="D795" t="s">
         <v>1160</v>
-      </c>
-      <c r="D795" t="s">
-        <v>1129</v>
       </c>
       <c r="E795" t="s">
         <v>1130</v>
@@ -20168,10 +20168,10 @@
         <v>7</v>
       </c>
       <c r="C796" t="s">
+        <v>1128</v>
+      </c>
+      <c r="D796" t="s">
         <v>1132</v>
-      </c>
-      <c r="D796" t="s">
-        <v>1129</v>
       </c>
       <c r="E796" t="s">
         <v>1130</v>
@@ -20228,10 +20228,10 @@
         <v>7</v>
       </c>
       <c r="C799" t="s">
+        <v>1128</v>
+      </c>
+      <c r="D799" t="s">
         <v>1132</v>
-      </c>
-      <c r="D799" t="s">
-        <v>1129</v>
       </c>
       <c r="E799" t="s">
         <v>1130</v>
@@ -20248,10 +20248,10 @@
         <v>7</v>
       </c>
       <c r="C800" t="s">
+        <v>1128</v>
+      </c>
+      <c r="D800" t="s">
         <v>1132</v>
-      </c>
-      <c r="D800" t="s">
-        <v>1129</v>
       </c>
       <c r="E800" t="s">
         <v>1130</v>
@@ -20268,10 +20268,10 @@
         <v>7</v>
       </c>
       <c r="C801" t="s">
+        <v>1128</v>
+      </c>
+      <c r="D801" t="s">
         <v>1132</v>
-      </c>
-      <c r="D801" t="s">
-        <v>1129</v>
       </c>
       <c r="E801" t="s">
         <v>1130</v>
@@ -20288,10 +20288,10 @@
         <v>7</v>
       </c>
       <c r="C802" t="s">
+        <v>1128</v>
+      </c>
+      <c r="D802" t="s">
         <v>1132</v>
-      </c>
-      <c r="D802" t="s">
-        <v>1129</v>
       </c>
       <c r="E802" t="s">
         <v>1130</v>
@@ -20308,10 +20308,10 @@
         <v>7</v>
       </c>
       <c r="C803" t="s">
+        <v>1128</v>
+      </c>
+      <c r="D803" t="s">
         <v>1132</v>
-      </c>
-      <c r="D803" t="s">
-        <v>1129</v>
       </c>
       <c r="E803" t="s">
         <v>1130</v>
@@ -20328,10 +20328,10 @@
         <v>7</v>
       </c>
       <c r="C804" t="s">
+        <v>1128</v>
+      </c>
+      <c r="D804" t="s">
         <v>1132</v>
-      </c>
-      <c r="D804" t="s">
-        <v>1129</v>
       </c>
       <c r="E804" t="s">
         <v>1130</v>
@@ -20348,10 +20348,10 @@
         <v>7</v>
       </c>
       <c r="C805" t="s">
+        <v>1128</v>
+      </c>
+      <c r="D805" t="s">
         <v>1132</v>
-      </c>
-      <c r="D805" t="s">
-        <v>1129</v>
       </c>
       <c r="E805" t="s">
         <v>1130</v>
@@ -20368,10 +20368,10 @@
         <v>7</v>
       </c>
       <c r="C806" t="s">
+        <v>1128</v>
+      </c>
+      <c r="D806" t="s">
         <v>1132</v>
-      </c>
-      <c r="D806" t="s">
-        <v>1129</v>
       </c>
       <c r="E806" t="s">
         <v>1130</v>
@@ -20388,10 +20388,10 @@
         <v>7</v>
       </c>
       <c r="C807" t="s">
+        <v>1128</v>
+      </c>
+      <c r="D807" t="s">
         <v>1132</v>
-      </c>
-      <c r="D807" t="s">
-        <v>1129</v>
       </c>
       <c r="E807" t="s">
         <v>1130</v>
@@ -20528,10 +20528,10 @@
         <v>7</v>
       </c>
       <c r="C814" t="s">
-        <v>1184</v>
+        <v>1178</v>
       </c>
       <c r="D814" t="s">
-        <v>1179</v>
+        <v>1185</v>
       </c>
       <c r="E814" t="s">
         <v>1180</v>
@@ -20708,10 +20708,10 @@
         <v>7</v>
       </c>
       <c r="C823" t="s">
-        <v>1201</v>
+        <v>1178</v>
       </c>
       <c r="D823" t="s">
-        <v>1179</v>
+        <v>1202</v>
       </c>
       <c r="E823" t="s">
         <v>1180</v>
@@ -20808,10 +20808,10 @@
         <v>7</v>
       </c>
       <c r="C828" t="s">
-        <v>1201</v>
+        <v>1178</v>
       </c>
       <c r="D828" t="s">
-        <v>1179</v>
+        <v>1202</v>
       </c>
       <c r="E828" t="s">
         <v>1180</v>
@@ -20848,10 +20848,10 @@
         <v>7</v>
       </c>
       <c r="C830" t="s">
-        <v>1184</v>
+        <v>1178</v>
       </c>
       <c r="D830" t="s">
-        <v>1179</v>
+        <v>1185</v>
       </c>
       <c r="E830" t="s">
         <v>1180</v>
@@ -21048,10 +21048,10 @@
         <v>7</v>
       </c>
       <c r="C840" t="s">
+        <v>1220</v>
+      </c>
+      <c r="D840" t="s">
         <v>1224</v>
-      </c>
-      <c r="D840" t="s">
-        <v>1221</v>
       </c>
       <c r="E840" t="s">
         <v>1222</v>
@@ -21068,10 +21068,10 @@
         <v>7</v>
       </c>
       <c r="C841" t="s">
+        <v>1220</v>
+      </c>
+      <c r="D841" t="s">
         <v>1224</v>
-      </c>
-      <c r="D841" t="s">
-        <v>1221</v>
       </c>
       <c r="E841" t="s">
         <v>1222</v>
@@ -21088,10 +21088,10 @@
         <v>7</v>
       </c>
       <c r="C842" t="s">
+        <v>1220</v>
+      </c>
+      <c r="D842" t="s">
         <v>1224</v>
-      </c>
-      <c r="D842" t="s">
-        <v>1221</v>
       </c>
       <c r="E842" t="s">
         <v>1222</v>
@@ -21108,10 +21108,10 @@
         <v>7</v>
       </c>
       <c r="C843" t="s">
+        <v>1220</v>
+      </c>
+      <c r="D843" t="s">
         <v>1224</v>
-      </c>
-      <c r="D843" t="s">
-        <v>1221</v>
       </c>
       <c r="E843" t="s">
         <v>1222</v>
@@ -21128,10 +21128,10 @@
         <v>7</v>
       </c>
       <c r="C844" t="s">
+        <v>1220</v>
+      </c>
+      <c r="D844" t="s">
         <v>1224</v>
-      </c>
-      <c r="D844" t="s">
-        <v>1221</v>
       </c>
       <c r="E844" t="s">
         <v>1222</v>
@@ -21148,10 +21148,10 @@
         <v>7</v>
       </c>
       <c r="C845" t="s">
+        <v>1220</v>
+      </c>
+      <c r="D845" t="s">
         <v>1224</v>
-      </c>
-      <c r="D845" t="s">
-        <v>1221</v>
       </c>
       <c r="E845" t="s">
         <v>1222</v>
@@ -21168,10 +21168,10 @@
         <v>7</v>
       </c>
       <c r="C846" t="s">
+        <v>1220</v>
+      </c>
+      <c r="D846" t="s">
         <v>1224</v>
-      </c>
-      <c r="D846" t="s">
-        <v>1221</v>
       </c>
       <c r="E846" t="s">
         <v>1222</v>
@@ -21188,10 +21188,10 @@
         <v>7</v>
       </c>
       <c r="C847" t="s">
+        <v>1184</v>
+      </c>
+      <c r="D847" t="s">
         <v>1232</v>
-      </c>
-      <c r="D847" t="s">
-        <v>1185</v>
       </c>
       <c r="E847" t="s">
         <v>1222</v>
@@ -21208,10 +21208,10 @@
         <v>7</v>
       </c>
       <c r="C848" t="s">
+        <v>1184</v>
+      </c>
+      <c r="D848" t="s">
         <v>1232</v>
-      </c>
-      <c r="D848" t="s">
-        <v>1185</v>
       </c>
       <c r="E848" t="s">
         <v>1222</v>
@@ -21228,10 +21228,10 @@
         <v>7</v>
       </c>
       <c r="C849" t="s">
+        <v>1184</v>
+      </c>
+      <c r="D849" t="s">
         <v>1232</v>
-      </c>
-      <c r="D849" t="s">
-        <v>1185</v>
       </c>
       <c r="E849" t="s">
         <v>1222</v>
@@ -21248,10 +21248,10 @@
         <v>7</v>
       </c>
       <c r="C850" t="s">
+        <v>1236</v>
+      </c>
+      <c r="D850" t="s">
         <v>1232</v>
-      </c>
-      <c r="D850" t="s">
-        <v>1236</v>
       </c>
       <c r="E850" t="s">
         <v>1222</v>
@@ -21268,10 +21268,10 @@
         <v>7</v>
       </c>
       <c r="C851" t="s">
+        <v>1184</v>
+      </c>
+      <c r="D851" t="s">
         <v>1232</v>
-      </c>
-      <c r="D851" t="s">
-        <v>1185</v>
       </c>
       <c r="E851" t="s">
         <v>1222</v>
@@ -21288,10 +21288,10 @@
         <v>7</v>
       </c>
       <c r="C852" t="s">
+        <v>1184</v>
+      </c>
+      <c r="D852" t="s">
         <v>1232</v>
-      </c>
-      <c r="D852" t="s">
-        <v>1185</v>
       </c>
       <c r="E852" t="s">
         <v>1222</v>
@@ -21308,10 +21308,10 @@
         <v>7</v>
       </c>
       <c r="C853" t="s">
+        <v>1220</v>
+      </c>
+      <c r="D853" t="s">
         <v>1224</v>
-      </c>
-      <c r="D853" t="s">
-        <v>1221</v>
       </c>
       <c r="E853" t="s">
         <v>1222</v>
@@ -21328,10 +21328,10 @@
         <v>7</v>
       </c>
       <c r="C854" t="s">
+        <v>1220</v>
+      </c>
+      <c r="D854" t="s">
         <v>1224</v>
-      </c>
-      <c r="D854" t="s">
-        <v>1221</v>
       </c>
       <c r="E854" t="s">
         <v>1222</v>
@@ -21348,10 +21348,10 @@
         <v>7</v>
       </c>
       <c r="C855" t="s">
+        <v>1220</v>
+      </c>
+      <c r="D855" t="s">
         <v>1224</v>
-      </c>
-      <c r="D855" t="s">
-        <v>1221</v>
       </c>
       <c r="E855" t="s">
         <v>1222</v>
@@ -21368,10 +21368,10 @@
         <v>7</v>
       </c>
       <c r="C856" t="s">
+        <v>1220</v>
+      </c>
+      <c r="D856" t="s">
         <v>1224</v>
-      </c>
-      <c r="D856" t="s">
-        <v>1221</v>
       </c>
       <c r="E856" t="s">
         <v>1222</v>
@@ -21388,10 +21388,10 @@
         <v>7</v>
       </c>
       <c r="C857" t="s">
+        <v>1220</v>
+      </c>
+      <c r="D857" t="s">
         <v>1224</v>
-      </c>
-      <c r="D857" t="s">
-        <v>1221</v>
       </c>
       <c r="E857" t="s">
         <v>1222</v>
@@ -21408,10 +21408,10 @@
         <v>7</v>
       </c>
       <c r="C858" t="s">
+        <v>1220</v>
+      </c>
+      <c r="D858" t="s">
         <v>1224</v>
-      </c>
-      <c r="D858" t="s">
-        <v>1221</v>
       </c>
       <c r="E858" t="s">
         <v>1222</v>
@@ -21428,10 +21428,10 @@
         <v>7</v>
       </c>
       <c r="C859" t="s">
+        <v>1220</v>
+      </c>
+      <c r="D859" t="s">
         <v>1224</v>
-      </c>
-      <c r="D859" t="s">
-        <v>1221</v>
       </c>
       <c r="E859" t="s">
         <v>1222</v>
@@ -21448,10 +21448,10 @@
         <v>7</v>
       </c>
       <c r="C860" t="s">
+        <v>1220</v>
+      </c>
+      <c r="D860" t="s">
         <v>1224</v>
-      </c>
-      <c r="D860" t="s">
-        <v>1221</v>
       </c>
       <c r="E860" t="s">
         <v>1222</v>
@@ -21468,10 +21468,10 @@
         <v>7</v>
       </c>
       <c r="C861" t="s">
+        <v>1220</v>
+      </c>
+      <c r="D861" t="s">
         <v>1224</v>
-      </c>
-      <c r="D861" t="s">
-        <v>1221</v>
       </c>
       <c r="E861" t="s">
         <v>1222</v>
@@ -21488,10 +21488,10 @@
         <v>7</v>
       </c>
       <c r="C862" t="s">
+        <v>1220</v>
+      </c>
+      <c r="D862" t="s">
         <v>1224</v>
-      </c>
-      <c r="D862" t="s">
-        <v>1221</v>
       </c>
       <c r="E862" t="s">
         <v>1222</v>
@@ -21508,10 +21508,10 @@
         <v>7</v>
       </c>
       <c r="C863" t="s">
+        <v>1220</v>
+      </c>
+      <c r="D863" t="s">
         <v>1224</v>
-      </c>
-      <c r="D863" t="s">
-        <v>1221</v>
       </c>
       <c r="E863" t="s">
         <v>1222</v>
@@ -21528,10 +21528,10 @@
         <v>7</v>
       </c>
       <c r="C864" t="s">
+        <v>1220</v>
+      </c>
+      <c r="D864" t="s">
         <v>1224</v>
-      </c>
-      <c r="D864" t="s">
-        <v>1221</v>
       </c>
       <c r="E864" t="s">
         <v>1222</v>
@@ -21548,10 +21548,10 @@
         <v>7</v>
       </c>
       <c r="C865" t="s">
+        <v>1220</v>
+      </c>
+      <c r="D865" t="s">
         <v>1224</v>
-      </c>
-      <c r="D865" t="s">
-        <v>1221</v>
       </c>
       <c r="E865" t="s">
         <v>1222</v>
@@ -21568,10 +21568,10 @@
         <v>7</v>
       </c>
       <c r="C866" t="s">
+        <v>1220</v>
+      </c>
+      <c r="D866" t="s">
         <v>1224</v>
-      </c>
-      <c r="D866" t="s">
-        <v>1221</v>
       </c>
       <c r="E866" t="s">
         <v>1222</v>
@@ -21608,10 +21608,10 @@
         <v>7</v>
       </c>
       <c r="C868" t="s">
-        <v>1254</v>
+        <v>1258</v>
       </c>
       <c r="D868" t="s">
-        <v>1258</v>
+        <v>1255</v>
       </c>
       <c r="E868" t="s">
         <v>1256</v>
@@ -21628,10 +21628,10 @@
         <v>7</v>
       </c>
       <c r="C869" t="s">
-        <v>1254</v>
+        <v>1258</v>
       </c>
       <c r="D869" t="s">
-        <v>1258</v>
+        <v>1255</v>
       </c>
       <c r="E869" t="s">
         <v>1256</v>
@@ -21648,10 +21648,10 @@
         <v>7</v>
       </c>
       <c r="C870" t="s">
-        <v>1254</v>
+        <v>1258</v>
       </c>
       <c r="D870" t="s">
-        <v>1258</v>
+        <v>1255</v>
       </c>
       <c r="E870" t="s">
         <v>1256</v>
@@ -21668,10 +21668,10 @@
         <v>7</v>
       </c>
       <c r="C871" t="s">
-        <v>1254</v>
+        <v>1258</v>
       </c>
       <c r="D871" t="s">
-        <v>1258</v>
+        <v>1255</v>
       </c>
       <c r="E871" t="s">
         <v>1256</v>
@@ -21688,10 +21688,10 @@
         <v>7</v>
       </c>
       <c r="C872" t="s">
-        <v>1254</v>
+        <v>1258</v>
       </c>
       <c r="D872" t="s">
-        <v>1258</v>
+        <v>1255</v>
       </c>
       <c r="E872" t="s">
         <v>1256</v>
@@ -21708,10 +21708,10 @@
         <v>7</v>
       </c>
       <c r="C873" t="s">
-        <v>1254</v>
+        <v>1258</v>
       </c>
       <c r="D873" t="s">
-        <v>1258</v>
+        <v>1255</v>
       </c>
       <c r="E873" t="s">
         <v>1256</v>
@@ -21728,10 +21728,10 @@
         <v>7</v>
       </c>
       <c r="C874" t="s">
-        <v>1254</v>
+        <v>1258</v>
       </c>
       <c r="D874" t="s">
-        <v>1258</v>
+        <v>1255</v>
       </c>
       <c r="E874" t="s">
         <v>1256</v>
@@ -21748,10 +21748,10 @@
         <v>7</v>
       </c>
       <c r="C875" t="s">
-        <v>1254</v>
+        <v>1258</v>
       </c>
       <c r="D875" t="s">
-        <v>1258</v>
+        <v>1255</v>
       </c>
       <c r="E875" t="s">
         <v>1256</v>
@@ -21768,10 +21768,10 @@
         <v>7</v>
       </c>
       <c r="C876" t="s">
-        <v>1254</v>
+        <v>1258</v>
       </c>
       <c r="D876" t="s">
-        <v>1258</v>
+        <v>1255</v>
       </c>
       <c r="E876" t="s">
         <v>1256</v>
@@ -21788,10 +21788,10 @@
         <v>7</v>
       </c>
       <c r="C877" t="s">
-        <v>1254</v>
+        <v>1258</v>
       </c>
       <c r="D877" t="s">
-        <v>1258</v>
+        <v>1255</v>
       </c>
       <c r="E877" t="s">
         <v>1256</v>
@@ -21808,10 +21808,10 @@
         <v>7</v>
       </c>
       <c r="C878" t="s">
-        <v>1254</v>
+        <v>1258</v>
       </c>
       <c r="D878" t="s">
-        <v>1258</v>
+        <v>1255</v>
       </c>
       <c r="E878" t="s">
         <v>1256</v>
@@ -21828,10 +21828,10 @@
         <v>7</v>
       </c>
       <c r="C879" t="s">
-        <v>1254</v>
+        <v>1258</v>
       </c>
       <c r="D879" t="s">
-        <v>1258</v>
+        <v>1255</v>
       </c>
       <c r="E879" t="s">
         <v>1256</v>
@@ -21848,10 +21848,10 @@
         <v>7</v>
       </c>
       <c r="C880" t="s">
-        <v>1254</v>
+        <v>1258</v>
       </c>
       <c r="D880" t="s">
-        <v>1258</v>
+        <v>1255</v>
       </c>
       <c r="E880" t="s">
         <v>1256</v>
@@ -21868,10 +21868,10 @@
         <v>7</v>
       </c>
       <c r="C881" t="s">
-        <v>1254</v>
+        <v>1258</v>
       </c>
       <c r="D881" t="s">
-        <v>1258</v>
+        <v>1255</v>
       </c>
       <c r="E881" t="s">
         <v>1256</v>
@@ -21888,10 +21888,10 @@
         <v>7</v>
       </c>
       <c r="C882" t="s">
-        <v>1254</v>
+        <v>1258</v>
       </c>
       <c r="D882" t="s">
-        <v>1258</v>
+        <v>1255</v>
       </c>
       <c r="E882" t="s">
         <v>1256</v>
@@ -21908,10 +21908,10 @@
         <v>7</v>
       </c>
       <c r="C883" t="s">
-        <v>1254</v>
+        <v>1258</v>
       </c>
       <c r="D883" t="s">
-        <v>1258</v>
+        <v>1255</v>
       </c>
       <c r="E883" t="s">
         <v>1256</v>
@@ -21928,10 +21928,10 @@
         <v>7</v>
       </c>
       <c r="C884" t="s">
-        <v>1254</v>
+        <v>1258</v>
       </c>
       <c r="D884" t="s">
-        <v>1258</v>
+        <v>1255</v>
       </c>
       <c r="E884" t="s">
         <v>1256</v>
@@ -21948,10 +21948,10 @@
         <v>7</v>
       </c>
       <c r="C885" t="s">
-        <v>1254</v>
+        <v>1258</v>
       </c>
       <c r="D885" t="s">
-        <v>1258</v>
+        <v>1255</v>
       </c>
       <c r="E885" t="s">
         <v>1256</v>
@@ -21968,10 +21968,10 @@
         <v>7</v>
       </c>
       <c r="C886" t="s">
-        <v>1254</v>
+        <v>1258</v>
       </c>
       <c r="D886" t="s">
-        <v>1258</v>
+        <v>1255</v>
       </c>
       <c r="E886" t="s">
         <v>1256</v>
@@ -21988,10 +21988,10 @@
         <v>7</v>
       </c>
       <c r="C887" t="s">
-        <v>1254</v>
+        <v>1258</v>
       </c>
       <c r="D887" t="s">
-        <v>1258</v>
+        <v>1255</v>
       </c>
       <c r="E887" t="s">
         <v>1256</v>
@@ -22008,10 +22008,10 @@
         <v>7</v>
       </c>
       <c r="C888" t="s">
-        <v>1254</v>
+        <v>1258</v>
       </c>
       <c r="D888" t="s">
-        <v>1258</v>
+        <v>1255</v>
       </c>
       <c r="E888" t="s">
         <v>1256</v>
@@ -22028,10 +22028,10 @@
         <v>7</v>
       </c>
       <c r="C889" t="s">
-        <v>1254</v>
+        <v>1258</v>
       </c>
       <c r="D889" t="s">
-        <v>1258</v>
+        <v>1255</v>
       </c>
       <c r="E889" t="s">
         <v>1256</v>
@@ -22148,10 +22148,10 @@
         <v>7</v>
       </c>
       <c r="C895" t="s">
+        <v>1281</v>
+      </c>
+      <c r="D895" t="s">
         <v>1289</v>
-      </c>
-      <c r="D895" t="s">
-        <v>1282</v>
       </c>
       <c r="E895" t="s">
         <v>1283</v>
@@ -22328,10 +22328,10 @@
         <v>7</v>
       </c>
       <c r="C904" t="s">
+        <v>1281</v>
+      </c>
+      <c r="D904" t="s">
         <v>1299</v>
-      </c>
-      <c r="D904" t="s">
-        <v>1282</v>
       </c>
       <c r="E904" t="s">
         <v>1300</v>
@@ -22348,10 +22348,10 @@
         <v>7</v>
       </c>
       <c r="C905" t="s">
+        <v>1281</v>
+      </c>
+      <c r="D905" t="s">
         <v>1302</v>
-      </c>
-      <c r="D905" t="s">
-        <v>1282</v>
       </c>
       <c r="E905" t="s">
         <v>1300</v>
@@ -22368,10 +22368,10 @@
         <v>7</v>
       </c>
       <c r="C906" t="s">
+        <v>1281</v>
+      </c>
+      <c r="D906" t="s">
         <v>1299</v>
-      </c>
-      <c r="D906" t="s">
-        <v>1282</v>
       </c>
       <c r="E906" t="s">
         <v>1300</v>

--- a/api/2/clv2/xlsx/pt/HumanitarianPlan.xlsx
+++ b/api/2/clv2/xlsx/pt/HumanitarianPlan.xlsx
@@ -25,12 +25,12 @@
     <t>codeforiati:plan-end-date</t>
   </si>
   <si>
+    <t>codeforiati:plan-year</t>
+  </si>
+  <si>
     <t>codeforiati:plan-start-date</t>
   </si>
   <si>
-    <t>codeforiati:plan-year</t>
-  </si>
-  <si>
     <t>codeforiati:plan-type</t>
   </si>
   <si>
@@ -43,12 +43,12 @@
     <t>2025-12-31</t>
   </si>
   <si>
+    <t>2025</t>
+  </si>
+  <si>
     <t>2025-01-01</t>
   </si>
   <si>
-    <t>2025</t>
-  </si>
-  <si>
     <t>Humanitarian needs and response plan</t>
   </si>
   <si>
@@ -220,12 +220,12 @@
     <t>2024-12-31</t>
   </si>
   <si>
+    <t>2024</t>
+  </si>
+  <si>
     <t>2024-01-01</t>
   </si>
   <si>
-    <t>2024</t>
-  </si>
-  <si>
     <t>RAFG_RRP24</t>
   </si>
   <si>
@@ -424,12 +424,12 @@
     <t>2023-12-31</t>
   </si>
   <si>
+    <t>2023</t>
+  </si>
+  <si>
     <t>2023-01-01</t>
   </si>
   <si>
-    <t>2023</t>
-  </si>
-  <si>
     <t>RAFG23</t>
   </si>
   <si>
@@ -604,12 +604,12 @@
     <t>2022-12-31</t>
   </si>
   <si>
+    <t>2022</t>
+  </si>
+  <si>
     <t>2022-01-01</t>
   </si>
   <si>
-    <t>2022</t>
-  </si>
-  <si>
     <t>RAFG22</t>
   </si>
   <si>
@@ -808,12 +808,12 @@
     <t>2021-12-31</t>
   </si>
   <si>
+    <t>2021</t>
+  </si>
+  <si>
     <t>2021-09-01</t>
   </si>
   <si>
-    <t>2021</t>
-  </si>
-  <si>
     <t>HAFG21</t>
   </si>
   <si>
@@ -1012,12 +1012,12 @@
     <t>2020-12-31</t>
   </si>
   <si>
+    <t>2020</t>
+  </si>
+  <si>
     <t>2020-01-01</t>
   </si>
   <si>
-    <t>2020</t>
-  </si>
-  <si>
     <t>OBGD20</t>
   </si>
   <si>
@@ -1252,12 +1252,12 @@
     <t>2019-12-31</t>
   </si>
   <si>
+    <t>2019</t>
+  </si>
+  <si>
     <t>2019-01-01</t>
   </si>
   <si>
-    <t>2019</t>
-  </si>
-  <si>
     <t>RBGD19</t>
   </si>
   <si>
@@ -1384,12 +1384,12 @@
     <t>2018-12-31</t>
   </si>
   <si>
+    <t>2018</t>
+  </si>
+  <si>
     <t>2018-01-01</t>
   </si>
   <si>
-    <t>2018</t>
-  </si>
-  <si>
     <t>OBGD18</t>
   </si>
   <si>
@@ -1510,12 +1510,12 @@
     <t>2017-12-31</t>
   </si>
   <si>
+    <t>2017</t>
+  </si>
+  <si>
     <t>2017-01-01</t>
   </si>
   <si>
-    <t>2017</t>
-  </si>
-  <si>
     <t>HAFG17</t>
   </si>
   <si>
@@ -1681,12 +1681,12 @@
     <t>2016-12-31</t>
   </si>
   <si>
+    <t>2016</t>
+  </si>
+  <si>
     <t>2016-01-01</t>
   </si>
   <si>
-    <t>2016</t>
-  </si>
-  <si>
     <t>HAFG16</t>
   </si>
   <si>
@@ -1843,12 +1843,12 @@
     <t>2015-12-31</t>
   </si>
   <si>
+    <t>2015</t>
+  </si>
+  <si>
     <t>2015-01-01</t>
   </si>
   <si>
-    <t>2015</t>
-  </si>
-  <si>
     <t>Strategic response plan</t>
   </si>
   <si>
@@ -1978,12 +1978,12 @@
     <t>2014-12-31</t>
   </si>
   <si>
+    <t>2014</t>
+  </si>
+  <si>
     <t>2014-01-01</t>
   </si>
   <si>
-    <t>2014</t>
-  </si>
-  <si>
     <t>HBFA1314</t>
   </si>
   <si>
@@ -2245,12 +2245,12 @@
     <t>2012-12-31</t>
   </si>
   <si>
+    <t>2012</t>
+  </si>
+  <si>
     <t>2012-01-01</t>
   </si>
   <si>
-    <t>2012</t>
-  </si>
-  <si>
     <t>CAFG1112</t>
   </si>
   <si>
@@ -2353,12 +2353,12 @@
     <t>CKEN1113</t>
   </si>
   <si>
+    <t>2011</t>
+  </si>
+  <si>
     <t>2011-01-01</t>
   </si>
   <si>
-    <t>2011</t>
-  </si>
-  <si>
     <t>CAFG11</t>
   </si>
   <si>
@@ -2479,12 +2479,12 @@
     <t>2010-12-31</t>
   </si>
   <si>
+    <t>2010</t>
+  </si>
+  <si>
     <t>2010-01-01</t>
   </si>
   <si>
-    <t>2010</t>
-  </si>
-  <si>
     <t>OBFA1011</t>
   </si>
   <si>
@@ -2611,12 +2611,12 @@
     <t>2009-12-31</t>
   </si>
   <si>
+    <t>2009</t>
+  </si>
+  <si>
     <t>2009-01-01</t>
   </si>
   <si>
-    <t>2009</t>
-  </si>
-  <si>
     <t>FBFA0910</t>
   </si>
   <si>
@@ -2749,12 +2749,12 @@
     <t>2008-06-30</t>
   </si>
   <si>
+    <t>2008</t>
+  </si>
+  <si>
     <t>2008-02-01</t>
   </si>
   <si>
-    <t>2008</t>
-  </si>
-  <si>
     <t>OAFG0809</t>
   </si>
   <si>
@@ -2917,12 +2917,12 @@
     <t>2007-08-21</t>
   </si>
   <si>
+    <t>2007</t>
+  </si>
+  <si>
     <t>2007-02-22</t>
   </si>
   <si>
-    <t>2007</t>
-  </si>
-  <si>
     <t>FBFA0708</t>
   </si>
   <si>
@@ -3115,12 +3115,12 @@
     <t>2006-12-31</t>
   </si>
   <si>
+    <t>2006</t>
+  </si>
+  <si>
     <t>2006-07-01</t>
   </si>
   <si>
-    <t>2006</t>
-  </si>
-  <si>
     <t>CBDI06</t>
   </si>
   <si>
@@ -3274,12 +3274,12 @@
     <t>2005-06-30</t>
   </si>
   <si>
+    <t>2005</t>
+  </si>
+  <si>
     <t>2005-04-01</t>
   </si>
   <si>
-    <t>2005</t>
-  </si>
-  <si>
     <t>FBEN05</t>
   </si>
   <si>
@@ -3403,12 +3403,12 @@
     <t>2004-12-31</t>
   </si>
   <si>
+    <t>2004</t>
+  </si>
+  <si>
     <t>2004-09-01</t>
   </si>
   <si>
-    <t>2004</t>
-  </si>
-  <si>
     <t>CAGO04</t>
   </si>
   <si>
@@ -3553,12 +3553,12 @@
     <t>2003-12-31</t>
   </si>
   <si>
+    <t>2003</t>
+  </si>
+  <si>
     <t>2003-01-01</t>
   </si>
   <si>
-    <t>2003</t>
-  </si>
-  <si>
     <t>CAGO03</t>
   </si>
   <si>
@@ -3679,12 +3679,12 @@
     <t>2002-12-31</t>
   </si>
   <si>
+    <t>2002</t>
+  </si>
+  <si>
     <t>2001-10-01</t>
   </si>
   <si>
-    <t>2002</t>
-  </si>
-  <si>
     <t>CAGO02</t>
   </si>
   <si>
@@ -3781,12 +3781,12 @@
     <t>2001-09-30</t>
   </si>
   <si>
+    <t>2001</t>
+  </si>
+  <si>
     <t>2001-01-01</t>
   </si>
   <si>
-    <t>2001</t>
-  </si>
-  <si>
     <t>CAGO01</t>
   </si>
   <si>
@@ -3862,12 +3862,12 @@
     <t>2000-12-31</t>
   </si>
   <si>
+    <t>2000</t>
+  </si>
+  <si>
     <t>2000-01-01</t>
   </si>
   <si>
-    <t>2000</t>
-  </si>
-  <si>
     <t>CBDI00</t>
   </si>
   <si>
@@ -3913,10 +3913,10 @@
     <t>CTLS9900</t>
   </si>
   <si>
+    <t>1999</t>
+  </si>
+  <si>
     <t>1999-10-01</t>
-  </si>
-  <si>
-    <t>1999</t>
   </si>
   <si>
     <t>CRUS9900</t>
@@ -4651,10 +4651,10 @@
         <v>8</v>
       </c>
       <c r="D20" t="s">
+        <v>9</v>
+      </c>
+      <c r="E20" t="s">
         <v>38</v>
-      </c>
-      <c r="E20" t="s">
-        <v>10</v>
       </c>
       <c r="F20" t="s">
         <v>11</v>
@@ -4931,10 +4931,10 @@
         <v>8</v>
       </c>
       <c r="D34" t="s">
+        <v>9</v>
+      </c>
+      <c r="E34" t="s">
         <v>54</v>
-      </c>
-      <c r="E34" t="s">
-        <v>10</v>
       </c>
       <c r="F34" t="s">
         <v>24</v>
@@ -5211,10 +5211,10 @@
         <v>67</v>
       </c>
       <c r="D48" t="s">
+        <v>68</v>
+      </c>
+      <c r="E48" t="s">
         <v>72</v>
-      </c>
-      <c r="E48" t="s">
-        <v>69</v>
       </c>
       <c r="F48" t="s">
         <v>16</v>
@@ -5251,10 +5251,10 @@
         <v>67</v>
       </c>
       <c r="D50" t="s">
+        <v>68</v>
+      </c>
+      <c r="E50" t="s">
         <v>75</v>
-      </c>
-      <c r="E50" t="s">
-        <v>69</v>
       </c>
       <c r="F50" t="s">
         <v>16</v>
@@ -5391,10 +5391,10 @@
         <v>67</v>
       </c>
       <c r="D57" t="s">
+        <v>68</v>
+      </c>
+      <c r="E57" t="s">
         <v>83</v>
-      </c>
-      <c r="E57" t="s">
-        <v>69</v>
       </c>
       <c r="F57" t="s">
         <v>24</v>
@@ -5471,10 +5471,10 @@
         <v>67</v>
       </c>
       <c r="D61" t="s">
+        <v>68</v>
+      </c>
+      <c r="E61" t="s">
         <v>88</v>
-      </c>
-      <c r="E61" t="s">
-        <v>69</v>
       </c>
       <c r="F61" t="s">
         <v>16</v>
@@ -5491,10 +5491,10 @@
         <v>67</v>
       </c>
       <c r="D62" t="s">
+        <v>68</v>
+      </c>
+      <c r="E62" t="s">
         <v>88</v>
-      </c>
-      <c r="E62" t="s">
-        <v>69</v>
       </c>
       <c r="F62" t="s">
         <v>24</v>
@@ -5551,10 +5551,10 @@
         <v>67</v>
       </c>
       <c r="D65" t="s">
+        <v>68</v>
+      </c>
+      <c r="E65" t="s">
         <v>95</v>
-      </c>
-      <c r="E65" t="s">
-        <v>69</v>
       </c>
       <c r="F65" t="s">
         <v>24</v>
@@ -5591,10 +5591,10 @@
         <v>93</v>
       </c>
       <c r="D67" t="s">
+        <v>68</v>
+      </c>
+      <c r="E67" t="s">
         <v>98</v>
-      </c>
-      <c r="E67" t="s">
-        <v>69</v>
       </c>
       <c r="F67" t="s">
         <v>16</v>
@@ -5611,10 +5611,10 @@
         <v>67</v>
       </c>
       <c r="D68" t="s">
+        <v>68</v>
+      </c>
+      <c r="E68" t="s">
         <v>100</v>
-      </c>
-      <c r="E68" t="s">
-        <v>69</v>
       </c>
       <c r="F68" t="s">
         <v>24</v>
@@ -5671,10 +5671,10 @@
         <v>67</v>
       </c>
       <c r="D71" t="s">
+        <v>68</v>
+      </c>
+      <c r="E71" t="s">
         <v>104</v>
-      </c>
-      <c r="E71" t="s">
-        <v>69</v>
       </c>
       <c r="F71" t="s">
         <v>16</v>
@@ -5731,10 +5731,10 @@
         <v>67</v>
       </c>
       <c r="D74" t="s">
+        <v>68</v>
+      </c>
+      <c r="E74" t="s">
         <v>108</v>
-      </c>
-      <c r="E74" t="s">
-        <v>69</v>
       </c>
       <c r="F74" t="s">
         <v>16</v>
@@ -5851,10 +5851,10 @@
         <v>67</v>
       </c>
       <c r="D80" t="s">
+        <v>68</v>
+      </c>
+      <c r="E80" t="s">
         <v>83</v>
-      </c>
-      <c r="E80" t="s">
-        <v>69</v>
       </c>
       <c r="F80" t="s">
         <v>24</v>
@@ -6111,10 +6111,10 @@
         <v>67</v>
       </c>
       <c r="D93" t="s">
+        <v>68</v>
+      </c>
+      <c r="E93" t="s">
         <v>129</v>
-      </c>
-      <c r="E93" t="s">
-        <v>69</v>
       </c>
       <c r="F93" t="s">
         <v>16</v>
@@ -6151,10 +6151,10 @@
         <v>67</v>
       </c>
       <c r="D95" t="s">
+        <v>68</v>
+      </c>
+      <c r="E95" t="s">
         <v>132</v>
-      </c>
-      <c r="E95" t="s">
-        <v>69</v>
       </c>
       <c r="F95" t="s">
         <v>24</v>
@@ -6171,10 +6171,10 @@
         <v>67</v>
       </c>
       <c r="D96" t="s">
+        <v>68</v>
+      </c>
+      <c r="E96" t="s">
         <v>132</v>
-      </c>
-      <c r="E96" t="s">
-        <v>69</v>
       </c>
       <c r="F96" t="s">
         <v>24</v>
@@ -6351,10 +6351,10 @@
         <v>135</v>
       </c>
       <c r="D105" t="s">
+        <v>136</v>
+      </c>
+      <c r="E105" t="s">
         <v>146</v>
-      </c>
-      <c r="E105" t="s">
-        <v>137</v>
       </c>
       <c r="F105" t="s">
         <v>24</v>
@@ -6511,10 +6511,10 @@
         <v>135</v>
       </c>
       <c r="D113" t="s">
+        <v>136</v>
+      </c>
+      <c r="E113" t="s">
         <v>155</v>
-      </c>
-      <c r="E113" t="s">
-        <v>137</v>
       </c>
       <c r="F113" t="s">
         <v>24</v>
@@ -6571,10 +6571,10 @@
         <v>159</v>
       </c>
       <c r="D116" t="s">
+        <v>136</v>
+      </c>
+      <c r="E116" t="s">
         <v>160</v>
-      </c>
-      <c r="E116" t="s">
-        <v>137</v>
       </c>
       <c r="F116" t="s">
         <v>16</v>
@@ -6591,10 +6591,10 @@
         <v>162</v>
       </c>
       <c r="D117" t="s">
+        <v>136</v>
+      </c>
+      <c r="E117" t="s">
         <v>163</v>
-      </c>
-      <c r="E117" t="s">
-        <v>137</v>
       </c>
       <c r="F117" t="s">
         <v>16</v>
@@ -6891,10 +6891,10 @@
         <v>179</v>
       </c>
       <c r="D132" t="s">
+        <v>136</v>
+      </c>
+      <c r="E132" t="s">
         <v>180</v>
-      </c>
-      <c r="E132" t="s">
-        <v>137</v>
       </c>
       <c r="F132" t="s">
         <v>13</v>
@@ -6931,10 +6931,10 @@
         <v>159</v>
       </c>
       <c r="D134" t="s">
+        <v>136</v>
+      </c>
+      <c r="E134" t="s">
         <v>183</v>
-      </c>
-      <c r="E134" t="s">
-        <v>137</v>
       </c>
       <c r="F134" t="s">
         <v>24</v>
@@ -6971,10 +6971,10 @@
         <v>159</v>
       </c>
       <c r="D136" t="s">
+        <v>136</v>
+      </c>
+      <c r="E136" t="s">
         <v>186</v>
-      </c>
-      <c r="E136" t="s">
-        <v>137</v>
       </c>
       <c r="F136" t="s">
         <v>24</v>
@@ -7271,10 +7271,10 @@
         <v>205</v>
       </c>
       <c r="D151" t="s">
+        <v>196</v>
+      </c>
+      <c r="E151" t="s">
         <v>206</v>
-      </c>
-      <c r="E151" t="s">
-        <v>197</v>
       </c>
       <c r="F151" t="s">
         <v>16</v>
@@ -7371,10 +7371,10 @@
         <v>212</v>
       </c>
       <c r="D156" t="s">
+        <v>196</v>
+      </c>
+      <c r="E156" t="s">
         <v>213</v>
-      </c>
-      <c r="E156" t="s">
-        <v>197</v>
       </c>
       <c r="F156" t="s">
         <v>24</v>
@@ -7391,10 +7391,10 @@
         <v>195</v>
       </c>
       <c r="D157" t="s">
+        <v>196</v>
+      </c>
+      <c r="E157" t="s">
         <v>213</v>
-      </c>
-      <c r="E157" t="s">
-        <v>197</v>
       </c>
       <c r="F157" t="s">
         <v>24</v>
@@ -7551,10 +7551,10 @@
         <v>224</v>
       </c>
       <c r="D165" t="s">
+        <v>196</v>
+      </c>
+      <c r="E165" t="s">
         <v>225</v>
-      </c>
-      <c r="E165" t="s">
-        <v>197</v>
       </c>
       <c r="F165" t="s">
         <v>24</v>
@@ -7591,10 +7591,10 @@
         <v>228</v>
       </c>
       <c r="D167" t="s">
+        <v>196</v>
+      </c>
+      <c r="E167" t="s">
         <v>229</v>
-      </c>
-      <c r="E167" t="s">
-        <v>197</v>
       </c>
       <c r="F167" t="s">
         <v>24</v>
@@ -7711,10 +7711,10 @@
         <v>195</v>
       </c>
       <c r="D173" t="s">
+        <v>196</v>
+      </c>
+      <c r="E173" t="s">
         <v>236</v>
-      </c>
-      <c r="E173" t="s">
-        <v>197</v>
       </c>
       <c r="F173" t="s">
         <v>16</v>
@@ -7731,10 +7731,10 @@
         <v>238</v>
       </c>
       <c r="D174" t="s">
+        <v>196</v>
+      </c>
+      <c r="E174" t="s">
         <v>236</v>
-      </c>
-      <c r="E174" t="s">
-        <v>197</v>
       </c>
       <c r="F174" t="s">
         <v>16</v>
@@ -7751,10 +7751,10 @@
         <v>240</v>
       </c>
       <c r="D175" t="s">
+        <v>196</v>
+      </c>
+      <c r="E175" t="s">
         <v>241</v>
-      </c>
-      <c r="E175" t="s">
-        <v>197</v>
       </c>
       <c r="F175" t="s">
         <v>16</v>
@@ -7911,10 +7911,10 @@
         <v>195</v>
       </c>
       <c r="D183" t="s">
+        <v>196</v>
+      </c>
+      <c r="E183" t="s">
         <v>250</v>
-      </c>
-      <c r="E183" t="s">
-        <v>197</v>
       </c>
       <c r="F183" t="s">
         <v>16</v>
@@ -8011,10 +8011,10 @@
         <v>195</v>
       </c>
       <c r="D188" t="s">
+        <v>196</v>
+      </c>
+      <c r="E188" t="s">
         <v>256</v>
-      </c>
-      <c r="E188" t="s">
-        <v>197</v>
       </c>
       <c r="F188" t="s">
         <v>24</v>
@@ -8051,10 +8051,10 @@
         <v>259</v>
       </c>
       <c r="D190" t="s">
+        <v>196</v>
+      </c>
+      <c r="E190" t="s">
         <v>256</v>
-      </c>
-      <c r="E190" t="s">
-        <v>197</v>
       </c>
       <c r="F190" t="s">
         <v>13</v>
@@ -8131,10 +8131,10 @@
         <v>263</v>
       </c>
       <c r="D194" t="s">
+        <v>264</v>
+      </c>
+      <c r="E194" t="s">
         <v>267</v>
-      </c>
-      <c r="E194" t="s">
-        <v>265</v>
       </c>
       <c r="F194" t="s">
         <v>19</v>
@@ -8151,10 +8151,10 @@
         <v>263</v>
       </c>
       <c r="D195" t="s">
+        <v>264</v>
+      </c>
+      <c r="E195" t="s">
         <v>267</v>
-      </c>
-      <c r="E195" t="s">
-        <v>265</v>
       </c>
       <c r="F195" t="s">
         <v>13</v>
@@ -8171,10 +8171,10 @@
         <v>263</v>
       </c>
       <c r="D196" t="s">
+        <v>264</v>
+      </c>
+      <c r="E196" t="s">
         <v>267</v>
-      </c>
-      <c r="E196" t="s">
-        <v>265</v>
       </c>
       <c r="F196" t="s">
         <v>19</v>
@@ -8191,10 +8191,10 @@
         <v>263</v>
       </c>
       <c r="D197" t="s">
+        <v>264</v>
+      </c>
+      <c r="E197" t="s">
         <v>267</v>
-      </c>
-      <c r="E197" t="s">
-        <v>265</v>
       </c>
       <c r="F197" t="s">
         <v>19</v>
@@ -8211,10 +8211,10 @@
         <v>263</v>
       </c>
       <c r="D198" t="s">
+        <v>264</v>
+      </c>
+      <c r="E198" t="s">
         <v>267</v>
-      </c>
-      <c r="E198" t="s">
-        <v>265</v>
       </c>
       <c r="F198" t="s">
         <v>13</v>
@@ -8231,10 +8231,10 @@
         <v>263</v>
       </c>
       <c r="D199" t="s">
+        <v>264</v>
+      </c>
+      <c r="E199" t="s">
         <v>267</v>
-      </c>
-      <c r="E199" t="s">
-        <v>265</v>
       </c>
       <c r="F199" t="s">
         <v>19</v>
@@ -8251,10 +8251,10 @@
         <v>263</v>
       </c>
       <c r="D200" t="s">
+        <v>264</v>
+      </c>
+      <c r="E200" t="s">
         <v>267</v>
-      </c>
-      <c r="E200" t="s">
-        <v>265</v>
       </c>
       <c r="F200" t="s">
         <v>19</v>
@@ -8271,10 +8271,10 @@
         <v>263</v>
       </c>
       <c r="D201" t="s">
+        <v>264</v>
+      </c>
+      <c r="E201" t="s">
         <v>267</v>
-      </c>
-      <c r="E201" t="s">
-        <v>265</v>
       </c>
       <c r="F201" t="s">
         <v>19</v>
@@ -8291,10 +8291,10 @@
         <v>263</v>
       </c>
       <c r="D202" t="s">
+        <v>264</v>
+      </c>
+      <c r="E202" t="s">
         <v>267</v>
-      </c>
-      <c r="E202" t="s">
-        <v>265</v>
       </c>
       <c r="F202" t="s">
         <v>19</v>
@@ -8311,10 +8311,10 @@
         <v>263</v>
       </c>
       <c r="D203" t="s">
+        <v>264</v>
+      </c>
+      <c r="E203" t="s">
         <v>267</v>
-      </c>
-      <c r="E203" t="s">
-        <v>265</v>
       </c>
       <c r="F203" t="s">
         <v>19</v>
@@ -8331,10 +8331,10 @@
         <v>263</v>
       </c>
       <c r="D204" t="s">
+        <v>264</v>
+      </c>
+      <c r="E204" t="s">
         <v>267</v>
-      </c>
-      <c r="E204" t="s">
-        <v>265</v>
       </c>
       <c r="F204" t="s">
         <v>13</v>
@@ -8351,10 +8351,10 @@
         <v>263</v>
       </c>
       <c r="D205" t="s">
+        <v>264</v>
+      </c>
+      <c r="E205" t="s">
         <v>279</v>
-      </c>
-      <c r="E205" t="s">
-        <v>265</v>
       </c>
       <c r="F205" t="s">
         <v>19</v>
@@ -8371,10 +8371,10 @@
         <v>195</v>
       </c>
       <c r="D206" t="s">
+        <v>264</v>
+      </c>
+      <c r="E206" t="s">
         <v>279</v>
-      </c>
-      <c r="E206" t="s">
-        <v>265</v>
       </c>
       <c r="F206" t="s">
         <v>19</v>
@@ -8391,10 +8391,10 @@
         <v>282</v>
       </c>
       <c r="D207" t="s">
+        <v>264</v>
+      </c>
+      <c r="E207" t="s">
         <v>283</v>
-      </c>
-      <c r="E207" t="s">
-        <v>265</v>
       </c>
       <c r="F207" t="s">
         <v>24</v>
@@ -8411,10 +8411,10 @@
         <v>263</v>
       </c>
       <c r="D208" t="s">
+        <v>264</v>
+      </c>
+      <c r="E208" t="s">
         <v>267</v>
-      </c>
-      <c r="E208" t="s">
-        <v>265</v>
       </c>
       <c r="F208" t="s">
         <v>19</v>
@@ -8431,10 +8431,10 @@
         <v>263</v>
       </c>
       <c r="D209" t="s">
+        <v>264</v>
+      </c>
+      <c r="E209" t="s">
         <v>279</v>
-      </c>
-      <c r="E209" t="s">
-        <v>265</v>
       </c>
       <c r="F209" t="s">
         <v>19</v>
@@ -8451,10 +8451,10 @@
         <v>195</v>
       </c>
       <c r="D210" t="s">
+        <v>264</v>
+      </c>
+      <c r="E210" t="s">
         <v>279</v>
-      </c>
-      <c r="E210" t="s">
-        <v>265</v>
       </c>
       <c r="F210" t="s">
         <v>19</v>
@@ -8471,10 +8471,10 @@
         <v>288</v>
       </c>
       <c r="D211" t="s">
+        <v>264</v>
+      </c>
+      <c r="E211" t="s">
         <v>289</v>
-      </c>
-      <c r="E211" t="s">
-        <v>265</v>
       </c>
       <c r="F211" t="s">
         <v>24</v>
@@ -8491,10 +8491,10 @@
         <v>263</v>
       </c>
       <c r="D212" t="s">
+        <v>264</v>
+      </c>
+      <c r="E212" t="s">
         <v>267</v>
-      </c>
-      <c r="E212" t="s">
-        <v>265</v>
       </c>
       <c r="F212" t="s">
         <v>19</v>
@@ -8511,10 +8511,10 @@
         <v>292</v>
       </c>
       <c r="D213" t="s">
+        <v>264</v>
+      </c>
+      <c r="E213" t="s">
         <v>293</v>
-      </c>
-      <c r="E213" t="s">
-        <v>265</v>
       </c>
       <c r="F213" t="s">
         <v>24</v>
@@ -8531,10 +8531,10 @@
         <v>263</v>
       </c>
       <c r="D214" t="s">
+        <v>264</v>
+      </c>
+      <c r="E214" t="s">
         <v>279</v>
-      </c>
-      <c r="E214" t="s">
-        <v>265</v>
       </c>
       <c r="F214" t="s">
         <v>19</v>
@@ -8551,10 +8551,10 @@
         <v>195</v>
       </c>
       <c r="D215" t="s">
+        <v>264</v>
+      </c>
+      <c r="E215" t="s">
         <v>279</v>
-      </c>
-      <c r="E215" t="s">
-        <v>265</v>
       </c>
       <c r="F215" t="s">
         <v>19</v>
@@ -8571,10 +8571,10 @@
         <v>263</v>
       </c>
       <c r="D216" t="s">
+        <v>264</v>
+      </c>
+      <c r="E216" t="s">
         <v>267</v>
-      </c>
-      <c r="E216" t="s">
-        <v>265</v>
       </c>
       <c r="F216" t="s">
         <v>19</v>
@@ -8591,10 +8591,10 @@
         <v>263</v>
       </c>
       <c r="D217" t="s">
+        <v>264</v>
+      </c>
+      <c r="E217" t="s">
         <v>298</v>
-      </c>
-      <c r="E217" t="s">
-        <v>265</v>
       </c>
       <c r="F217" t="s">
         <v>24</v>
@@ -8611,10 +8611,10 @@
         <v>300</v>
       </c>
       <c r="D218" t="s">
+        <v>264</v>
+      </c>
+      <c r="E218" t="s">
         <v>301</v>
-      </c>
-      <c r="E218" t="s">
-        <v>265</v>
       </c>
       <c r="F218" t="s">
         <v>16</v>
@@ -8631,10 +8631,10 @@
         <v>263</v>
       </c>
       <c r="D219" t="s">
+        <v>264</v>
+      </c>
+      <c r="E219" t="s">
         <v>267</v>
-      </c>
-      <c r="E219" t="s">
-        <v>265</v>
       </c>
       <c r="F219" t="s">
         <v>19</v>
@@ -8651,10 +8651,10 @@
         <v>224</v>
       </c>
       <c r="D220" t="s">
+        <v>264</v>
+      </c>
+      <c r="E220" t="s">
         <v>267</v>
-      </c>
-      <c r="E220" t="s">
-        <v>265</v>
       </c>
       <c r="F220" t="s">
         <v>24</v>
@@ -8671,10 +8671,10 @@
         <v>263</v>
       </c>
       <c r="D221" t="s">
+        <v>264</v>
+      </c>
+      <c r="E221" t="s">
         <v>267</v>
-      </c>
-      <c r="E221" t="s">
-        <v>265</v>
       </c>
       <c r="F221" t="s">
         <v>24</v>
@@ -8691,10 +8691,10 @@
         <v>263</v>
       </c>
       <c r="D222" t="s">
+        <v>264</v>
+      </c>
+      <c r="E222" t="s">
         <v>267</v>
-      </c>
-      <c r="E222" t="s">
-        <v>265</v>
       </c>
       <c r="F222" t="s">
         <v>19</v>
@@ -8711,10 +8711,10 @@
         <v>263</v>
       </c>
       <c r="D223" t="s">
+        <v>264</v>
+      </c>
+      <c r="E223" t="s">
         <v>267</v>
-      </c>
-      <c r="E223" t="s">
-        <v>265</v>
       </c>
       <c r="F223" t="s">
         <v>19</v>
@@ -8731,10 +8731,10 @@
         <v>263</v>
       </c>
       <c r="D224" t="s">
+        <v>264</v>
+      </c>
+      <c r="E224" t="s">
         <v>267</v>
-      </c>
-      <c r="E224" t="s">
-        <v>265</v>
       </c>
       <c r="F224" t="s">
         <v>19</v>
@@ -8751,10 +8751,10 @@
         <v>263</v>
       </c>
       <c r="D225" t="s">
+        <v>264</v>
+      </c>
+      <c r="E225" t="s">
         <v>309</v>
-      </c>
-      <c r="E225" t="s">
-        <v>265</v>
       </c>
       <c r="F225" t="s">
         <v>16</v>
@@ -8771,10 +8771,10 @@
         <v>263</v>
       </c>
       <c r="D226" t="s">
+        <v>264</v>
+      </c>
+      <c r="E226" t="s">
         <v>311</v>
-      </c>
-      <c r="E226" t="s">
-        <v>265</v>
       </c>
       <c r="F226" t="s">
         <v>16</v>
@@ -8791,10 +8791,10 @@
         <v>263</v>
       </c>
       <c r="D227" t="s">
+        <v>264</v>
+      </c>
+      <c r="E227" t="s">
         <v>267</v>
-      </c>
-      <c r="E227" t="s">
-        <v>265</v>
       </c>
       <c r="F227" t="s">
         <v>19</v>
@@ -8811,10 +8811,10 @@
         <v>263</v>
       </c>
       <c r="D228" t="s">
+        <v>264</v>
+      </c>
+      <c r="E228" t="s">
         <v>267</v>
-      </c>
-      <c r="E228" t="s">
-        <v>265</v>
       </c>
       <c r="F228" t="s">
         <v>19</v>
@@ -8831,10 +8831,10 @@
         <v>263</v>
       </c>
       <c r="D229" t="s">
+        <v>264</v>
+      </c>
+      <c r="E229" t="s">
         <v>311</v>
-      </c>
-      <c r="E229" t="s">
-        <v>265</v>
       </c>
       <c r="F229" t="s">
         <v>24</v>
@@ -8851,10 +8851,10 @@
         <v>263</v>
       </c>
       <c r="D230" t="s">
+        <v>264</v>
+      </c>
+      <c r="E230" t="s">
         <v>311</v>
-      </c>
-      <c r="E230" t="s">
-        <v>265</v>
       </c>
       <c r="F230" t="s">
         <v>16</v>
@@ -8871,10 +8871,10 @@
         <v>263</v>
       </c>
       <c r="D231" t="s">
+        <v>264</v>
+      </c>
+      <c r="E231" t="s">
         <v>267</v>
-      </c>
-      <c r="E231" t="s">
-        <v>265</v>
       </c>
       <c r="F231" t="s">
         <v>19</v>
@@ -8891,10 +8891,10 @@
         <v>263</v>
       </c>
       <c r="D232" t="s">
+        <v>264</v>
+      </c>
+      <c r="E232" t="s">
         <v>267</v>
-      </c>
-      <c r="E232" t="s">
-        <v>265</v>
       </c>
       <c r="F232" t="s">
         <v>19</v>
@@ -8911,10 +8911,10 @@
         <v>263</v>
       </c>
       <c r="D233" t="s">
+        <v>264</v>
+      </c>
+      <c r="E233" t="s">
         <v>267</v>
-      </c>
-      <c r="E233" t="s">
-        <v>265</v>
       </c>
       <c r="F233" t="s">
         <v>13</v>
@@ -8931,10 +8931,10 @@
         <v>263</v>
       </c>
       <c r="D234" t="s">
+        <v>264</v>
+      </c>
+      <c r="E234" t="s">
         <v>267</v>
-      </c>
-      <c r="E234" t="s">
-        <v>265</v>
       </c>
       <c r="F234" t="s">
         <v>13</v>
@@ -8951,10 +8951,10 @@
         <v>263</v>
       </c>
       <c r="D235" t="s">
+        <v>264</v>
+      </c>
+      <c r="E235" t="s">
         <v>267</v>
-      </c>
-      <c r="E235" t="s">
-        <v>265</v>
       </c>
       <c r="F235" t="s">
         <v>19</v>
@@ -8971,10 +8971,10 @@
         <v>263</v>
       </c>
       <c r="D236" t="s">
+        <v>264</v>
+      </c>
+      <c r="E236" t="s">
         <v>267</v>
-      </c>
-      <c r="E236" t="s">
-        <v>265</v>
       </c>
       <c r="F236" t="s">
         <v>19</v>
@@ -8991,10 +8991,10 @@
         <v>263</v>
       </c>
       <c r="D237" t="s">
+        <v>264</v>
+      </c>
+      <c r="E237" t="s">
         <v>267</v>
-      </c>
-      <c r="E237" t="s">
-        <v>265</v>
       </c>
       <c r="F237" t="s">
         <v>13</v>
@@ -9011,10 +9011,10 @@
         <v>263</v>
       </c>
       <c r="D238" t="s">
+        <v>264</v>
+      </c>
+      <c r="E238" t="s">
         <v>267</v>
-      </c>
-      <c r="E238" t="s">
-        <v>265</v>
       </c>
       <c r="F238" t="s">
         <v>19</v>
@@ -9031,10 +9031,10 @@
         <v>263</v>
       </c>
       <c r="D239" t="s">
+        <v>264</v>
+      </c>
+      <c r="E239" t="s">
         <v>267</v>
-      </c>
-      <c r="E239" t="s">
-        <v>265</v>
       </c>
       <c r="F239" t="s">
         <v>19</v>
@@ -9051,10 +9051,10 @@
         <v>263</v>
       </c>
       <c r="D240" t="s">
+        <v>264</v>
+      </c>
+      <c r="E240" t="s">
         <v>267</v>
-      </c>
-      <c r="E240" t="s">
-        <v>265</v>
       </c>
       <c r="F240" t="s">
         <v>13</v>
@@ -9071,10 +9071,10 @@
         <v>263</v>
       </c>
       <c r="D241" t="s">
+        <v>264</v>
+      </c>
+      <c r="E241" t="s">
         <v>267</v>
-      </c>
-      <c r="E241" t="s">
-        <v>265</v>
       </c>
       <c r="F241" t="s">
         <v>19</v>
@@ -9091,10 +9091,10 @@
         <v>263</v>
       </c>
       <c r="D242" t="s">
+        <v>264</v>
+      </c>
+      <c r="E242" t="s">
         <v>267</v>
-      </c>
-      <c r="E242" t="s">
-        <v>265</v>
       </c>
       <c r="F242" t="s">
         <v>19</v>
@@ -9111,10 +9111,10 @@
         <v>263</v>
       </c>
       <c r="D243" t="s">
+        <v>264</v>
+      </c>
+      <c r="E243" t="s">
         <v>267</v>
-      </c>
-      <c r="E243" t="s">
-        <v>265</v>
       </c>
       <c r="F243" t="s">
         <v>19</v>
@@ -9131,10 +9131,10 @@
         <v>263</v>
       </c>
       <c r="D244" t="s">
+        <v>264</v>
+      </c>
+      <c r="E244" t="s">
         <v>267</v>
-      </c>
-      <c r="E244" t="s">
-        <v>265</v>
       </c>
       <c r="F244" t="s">
         <v>19</v>
@@ -9171,10 +9171,10 @@
         <v>331</v>
       </c>
       <c r="D246" t="s">
+        <v>332</v>
+      </c>
+      <c r="E246" t="s">
         <v>335</v>
-      </c>
-      <c r="E246" t="s">
-        <v>333</v>
       </c>
       <c r="F246" t="s">
         <v>16</v>
@@ -9211,10 +9211,10 @@
         <v>331</v>
       </c>
       <c r="D248" t="s">
+        <v>332</v>
+      </c>
+      <c r="E248" t="s">
         <v>335</v>
-      </c>
-      <c r="E248" t="s">
-        <v>333</v>
       </c>
       <c r="F248" t="s">
         <v>16</v>
@@ -9291,10 +9291,10 @@
         <v>331</v>
       </c>
       <c r="D252" t="s">
+        <v>332</v>
+      </c>
+      <c r="E252" t="s">
         <v>342</v>
-      </c>
-      <c r="E252" t="s">
-        <v>333</v>
       </c>
       <c r="F252" t="s">
         <v>16</v>
@@ -9331,10 +9331,10 @@
         <v>267</v>
       </c>
       <c r="D254" t="s">
+        <v>332</v>
+      </c>
+      <c r="E254" t="s">
         <v>345</v>
-      </c>
-      <c r="E254" t="s">
-        <v>333</v>
       </c>
       <c r="F254" t="s">
         <v>19</v>
@@ -9391,10 +9391,10 @@
         <v>331</v>
       </c>
       <c r="D257" t="s">
+        <v>332</v>
+      </c>
+      <c r="E257" t="s">
         <v>335</v>
-      </c>
-      <c r="E257" t="s">
-        <v>333</v>
       </c>
       <c r="F257" t="s">
         <v>16</v>
@@ -9411,10 +9411,10 @@
         <v>331</v>
       </c>
       <c r="D258" t="s">
+        <v>332</v>
+      </c>
+      <c r="E258" t="s">
         <v>335</v>
-      </c>
-      <c r="E258" t="s">
-        <v>333</v>
       </c>
       <c r="F258" t="s">
         <v>16</v>
@@ -9431,10 +9431,10 @@
         <v>331</v>
       </c>
       <c r="D259" t="s">
+        <v>332</v>
+      </c>
+      <c r="E259" t="s">
         <v>351</v>
-      </c>
-      <c r="E259" t="s">
-        <v>333</v>
       </c>
       <c r="F259" t="s">
         <v>19</v>
@@ -9491,10 +9491,10 @@
         <v>355</v>
       </c>
       <c r="D262" t="s">
+        <v>332</v>
+      </c>
+      <c r="E262" t="s">
         <v>356</v>
-      </c>
-      <c r="E262" t="s">
-        <v>333</v>
       </c>
       <c r="F262" t="s">
         <v>24</v>
@@ -9511,10 +9511,10 @@
         <v>331</v>
       </c>
       <c r="D263" t="s">
+        <v>332</v>
+      </c>
+      <c r="E263" t="s">
         <v>335</v>
-      </c>
-      <c r="E263" t="s">
-        <v>333</v>
       </c>
       <c r="F263" t="s">
         <v>16</v>
@@ -9531,10 +9531,10 @@
         <v>331</v>
       </c>
       <c r="D264" t="s">
+        <v>332</v>
+      </c>
+      <c r="E264" t="s">
         <v>335</v>
-      </c>
-      <c r="E264" t="s">
-        <v>333</v>
       </c>
       <c r="F264" t="s">
         <v>16</v>
@@ -9571,10 +9571,10 @@
         <v>331</v>
       </c>
       <c r="D266" t="s">
+        <v>332</v>
+      </c>
+      <c r="E266" t="s">
         <v>335</v>
-      </c>
-      <c r="E266" t="s">
-        <v>333</v>
       </c>
       <c r="F266" t="s">
         <v>16</v>
@@ -9611,10 +9611,10 @@
         <v>331</v>
       </c>
       <c r="D268" t="s">
+        <v>332</v>
+      </c>
+      <c r="E268" t="s">
         <v>335</v>
-      </c>
-      <c r="E268" t="s">
-        <v>333</v>
       </c>
       <c r="F268" t="s">
         <v>16</v>
@@ -9631,10 +9631,10 @@
         <v>331</v>
       </c>
       <c r="D269" t="s">
+        <v>332</v>
+      </c>
+      <c r="E269" t="s">
         <v>351</v>
-      </c>
-      <c r="E269" t="s">
-        <v>333</v>
       </c>
       <c r="F269" t="s">
         <v>16</v>
@@ -9651,10 +9651,10 @@
         <v>331</v>
       </c>
       <c r="D270" t="s">
+        <v>332</v>
+      </c>
+      <c r="E270" t="s">
         <v>335</v>
-      </c>
-      <c r="E270" t="s">
-        <v>333</v>
       </c>
       <c r="F270" t="s">
         <v>16</v>
@@ -9671,10 +9671,10 @@
         <v>331</v>
       </c>
       <c r="D271" t="s">
+        <v>332</v>
+      </c>
+      <c r="E271" t="s">
         <v>335</v>
-      </c>
-      <c r="E271" t="s">
-        <v>333</v>
       </c>
       <c r="F271" t="s">
         <v>16</v>
@@ -9711,10 +9711,10 @@
         <v>331</v>
       </c>
       <c r="D273" t="s">
+        <v>332</v>
+      </c>
+      <c r="E273" t="s">
         <v>335</v>
-      </c>
-      <c r="E273" t="s">
-        <v>333</v>
       </c>
       <c r="F273" t="s">
         <v>16</v>
@@ -9751,10 +9751,10 @@
         <v>331</v>
       </c>
       <c r="D275" t="s">
+        <v>332</v>
+      </c>
+      <c r="E275" t="s">
         <v>335</v>
-      </c>
-      <c r="E275" t="s">
-        <v>333</v>
       </c>
       <c r="F275" t="s">
         <v>16</v>
@@ -9771,10 +9771,10 @@
         <v>331</v>
       </c>
       <c r="D276" t="s">
+        <v>332</v>
+      </c>
+      <c r="E276" t="s">
         <v>371</v>
-      </c>
-      <c r="E276" t="s">
-        <v>333</v>
       </c>
       <c r="F276" t="s">
         <v>16</v>
@@ -9791,10 +9791,10 @@
         <v>373</v>
       </c>
       <c r="D277" t="s">
+        <v>332</v>
+      </c>
+      <c r="E277" t="s">
         <v>374</v>
-      </c>
-      <c r="E277" t="s">
-        <v>333</v>
       </c>
       <c r="F277" t="s">
         <v>24</v>
@@ -9811,10 +9811,10 @@
         <v>331</v>
       </c>
       <c r="D278" t="s">
+        <v>332</v>
+      </c>
+      <c r="E278" t="s">
         <v>335</v>
-      </c>
-      <c r="E278" t="s">
-        <v>333</v>
       </c>
       <c r="F278" t="s">
         <v>16</v>
@@ -9831,10 +9831,10 @@
         <v>377</v>
       </c>
       <c r="D279" t="s">
+        <v>332</v>
+      </c>
+      <c r="E279" t="s">
         <v>378</v>
-      </c>
-      <c r="E279" t="s">
-        <v>333</v>
       </c>
       <c r="F279" t="s">
         <v>24</v>
@@ -9851,10 +9851,10 @@
         <v>331</v>
       </c>
       <c r="D280" t="s">
+        <v>332</v>
+      </c>
+      <c r="E280" t="s">
         <v>335</v>
-      </c>
-      <c r="E280" t="s">
-        <v>333</v>
       </c>
       <c r="F280" t="s">
         <v>16</v>
@@ -9911,10 +9911,10 @@
         <v>331</v>
       </c>
       <c r="D283" t="s">
+        <v>332</v>
+      </c>
+      <c r="E283" t="s">
         <v>335</v>
-      </c>
-      <c r="E283" t="s">
-        <v>333</v>
       </c>
       <c r="F283" t="s">
         <v>16</v>
@@ -10011,10 +10011,10 @@
         <v>331</v>
       </c>
       <c r="D288" t="s">
+        <v>332</v>
+      </c>
+      <c r="E288" t="s">
         <v>371</v>
-      </c>
-      <c r="E288" t="s">
-        <v>333</v>
       </c>
       <c r="F288" t="s">
         <v>16</v>
@@ -10031,10 +10031,10 @@
         <v>331</v>
       </c>
       <c r="D289" t="s">
+        <v>332</v>
+      </c>
+      <c r="E289" t="s">
         <v>335</v>
-      </c>
-      <c r="E289" t="s">
-        <v>333</v>
       </c>
       <c r="F289" t="s">
         <v>16</v>
@@ -10091,10 +10091,10 @@
         <v>331</v>
       </c>
       <c r="D292" t="s">
+        <v>332</v>
+      </c>
+      <c r="E292" t="s">
         <v>371</v>
-      </c>
-      <c r="E292" t="s">
-        <v>333</v>
       </c>
       <c r="F292" t="s">
         <v>16</v>
@@ -10111,10 +10111,10 @@
         <v>331</v>
       </c>
       <c r="D293" t="s">
+        <v>332</v>
+      </c>
+      <c r="E293" t="s">
         <v>335</v>
-      </c>
-      <c r="E293" t="s">
-        <v>333</v>
       </c>
       <c r="F293" t="s">
         <v>16</v>
@@ -10251,10 +10251,10 @@
         <v>331</v>
       </c>
       <c r="D300" t="s">
+        <v>332</v>
+      </c>
+      <c r="E300" t="s">
         <v>335</v>
-      </c>
-      <c r="E300" t="s">
-        <v>333</v>
       </c>
       <c r="F300" t="s">
         <v>16</v>
@@ -10271,10 +10271,10 @@
         <v>331</v>
       </c>
       <c r="D301" t="s">
+        <v>332</v>
+      </c>
+      <c r="E301" t="s">
         <v>335</v>
-      </c>
-      <c r="E301" t="s">
-        <v>333</v>
       </c>
       <c r="F301" t="s">
         <v>16</v>
@@ -10291,10 +10291,10 @@
         <v>331</v>
       </c>
       <c r="D302" t="s">
+        <v>332</v>
+      </c>
+      <c r="E302" t="s">
         <v>335</v>
-      </c>
-      <c r="E302" t="s">
-        <v>333</v>
       </c>
       <c r="F302" t="s">
         <v>16</v>
@@ -10331,10 +10331,10 @@
         <v>331</v>
       </c>
       <c r="D304" t="s">
+        <v>332</v>
+      </c>
+      <c r="E304" t="s">
         <v>335</v>
-      </c>
-      <c r="E304" t="s">
-        <v>333</v>
       </c>
       <c r="F304" t="s">
         <v>16</v>
@@ -10391,10 +10391,10 @@
         <v>355</v>
       </c>
       <c r="D307" t="s">
+        <v>332</v>
+      </c>
+      <c r="E307" t="s">
         <v>407</v>
-      </c>
-      <c r="E307" t="s">
-        <v>333</v>
       </c>
       <c r="F307" t="s">
         <v>16</v>
@@ -10411,10 +10411,10 @@
         <v>331</v>
       </c>
       <c r="D308" t="s">
+        <v>332</v>
+      </c>
+      <c r="E308" t="s">
         <v>335</v>
-      </c>
-      <c r="E308" t="s">
-        <v>333</v>
       </c>
       <c r="F308" t="s">
         <v>16</v>
@@ -10711,10 +10711,10 @@
         <v>411</v>
       </c>
       <c r="D323" t="s">
+        <v>412</v>
+      </c>
+      <c r="E323" t="s">
         <v>427</v>
-      </c>
-      <c r="E323" t="s">
-        <v>413</v>
       </c>
       <c r="F323" t="s">
         <v>16</v>
@@ -11111,10 +11111,10 @@
         <v>450</v>
       </c>
       <c r="D343" t="s">
+        <v>412</v>
+      </c>
+      <c r="E343" t="s">
         <v>451</v>
-      </c>
-      <c r="E343" t="s">
-        <v>413</v>
       </c>
       <c r="F343" t="s">
         <v>24</v>
@@ -11131,10 +11131,10 @@
         <v>450</v>
       </c>
       <c r="D344" t="s">
+        <v>412</v>
+      </c>
+      <c r="E344" t="s">
         <v>453</v>
-      </c>
-      <c r="E344" t="s">
-        <v>413</v>
       </c>
       <c r="F344" t="s">
         <v>24</v>
@@ -11171,10 +11171,10 @@
         <v>455</v>
       </c>
       <c r="D346" t="s">
+        <v>456</v>
+      </c>
+      <c r="E346" t="s">
         <v>459</v>
-      </c>
-      <c r="E346" t="s">
-        <v>457</v>
       </c>
       <c r="F346" t="s">
         <v>16</v>
@@ -11371,10 +11371,10 @@
         <v>455</v>
       </c>
       <c r="D356" t="s">
+        <v>456</v>
+      </c>
+      <c r="E356" t="s">
         <v>470</v>
-      </c>
-      <c r="E356" t="s">
-        <v>457</v>
       </c>
       <c r="F356" t="s">
         <v>16</v>
@@ -11571,10 +11571,10 @@
         <v>455</v>
       </c>
       <c r="D366" t="s">
+        <v>456</v>
+      </c>
+      <c r="E366" t="s">
         <v>481</v>
-      </c>
-      <c r="E366" t="s">
-        <v>457</v>
       </c>
       <c r="F366" t="s">
         <v>16</v>
@@ -11591,10 +11591,10 @@
         <v>455</v>
       </c>
       <c r="D367" t="s">
+        <v>456</v>
+      </c>
+      <c r="E367" t="s">
         <v>459</v>
-      </c>
-      <c r="E367" t="s">
-        <v>457</v>
       </c>
       <c r="F367" t="s">
         <v>13</v>
@@ -11691,10 +11691,10 @@
         <v>489</v>
       </c>
       <c r="D372" t="s">
+        <v>456</v>
+      </c>
+      <c r="E372" t="s">
         <v>490</v>
-      </c>
-      <c r="E372" t="s">
-        <v>457</v>
       </c>
       <c r="F372" t="s">
         <v>19</v>
@@ -11731,10 +11731,10 @@
         <v>489</v>
       </c>
       <c r="D374" t="s">
+        <v>456</v>
+      </c>
+      <c r="E374" t="s">
         <v>490</v>
-      </c>
-      <c r="E374" t="s">
-        <v>457</v>
       </c>
       <c r="F374" t="s">
         <v>19</v>
@@ -11851,10 +11851,10 @@
         <v>497</v>
       </c>
       <c r="D380" t="s">
+        <v>498</v>
+      </c>
+      <c r="E380" t="s">
         <v>502</v>
-      </c>
-      <c r="E380" t="s">
-        <v>499</v>
       </c>
       <c r="F380" t="s">
         <v>13</v>
@@ -11971,10 +11971,10 @@
         <v>497</v>
       </c>
       <c r="D386" t="s">
+        <v>498</v>
+      </c>
+      <c r="E386" t="s">
         <v>509</v>
-      </c>
-      <c r="E386" t="s">
-        <v>499</v>
       </c>
       <c r="F386" t="s">
         <v>16</v>
@@ -11991,10 +11991,10 @@
         <v>497</v>
       </c>
       <c r="D387" t="s">
+        <v>498</v>
+      </c>
+      <c r="E387" t="s">
         <v>511</v>
-      </c>
-      <c r="E387" t="s">
-        <v>499</v>
       </c>
       <c r="F387" t="s">
         <v>19</v>
@@ -12031,10 +12031,10 @@
         <v>514</v>
       </c>
       <c r="D389" t="s">
+        <v>498</v>
+      </c>
+      <c r="E389" t="s">
         <v>515</v>
-      </c>
-      <c r="E389" t="s">
-        <v>499</v>
       </c>
       <c r="F389" t="s">
         <v>24</v>
@@ -12111,10 +12111,10 @@
         <v>497</v>
       </c>
       <c r="D393" t="s">
+        <v>498</v>
+      </c>
+      <c r="E393" t="s">
         <v>520</v>
-      </c>
-      <c r="E393" t="s">
-        <v>499</v>
       </c>
       <c r="F393" t="s">
         <v>16</v>
@@ -12151,10 +12151,10 @@
         <v>523</v>
       </c>
       <c r="D395" t="s">
+        <v>498</v>
+      </c>
+      <c r="E395" t="s">
         <v>524</v>
-      </c>
-      <c r="E395" t="s">
-        <v>499</v>
       </c>
       <c r="F395" t="s">
         <v>24</v>
@@ -12191,10 +12191,10 @@
         <v>527</v>
       </c>
       <c r="D397" t="s">
+        <v>498</v>
+      </c>
+      <c r="E397" t="s">
         <v>528</v>
-      </c>
-      <c r="E397" t="s">
-        <v>499</v>
       </c>
       <c r="F397" t="s">
         <v>24</v>
@@ -12251,10 +12251,10 @@
         <v>532</v>
       </c>
       <c r="D400" t="s">
+        <v>498</v>
+      </c>
+      <c r="E400" t="s">
         <v>533</v>
-      </c>
-      <c r="E400" t="s">
-        <v>499</v>
       </c>
       <c r="F400" t="s">
         <v>24</v>
@@ -12371,10 +12371,10 @@
         <v>540</v>
       </c>
       <c r="D406" t="s">
+        <v>498</v>
+      </c>
+      <c r="E406" t="s">
         <v>541</v>
-      </c>
-      <c r="E406" t="s">
-        <v>499</v>
       </c>
       <c r="F406" t="s">
         <v>24</v>
@@ -12391,10 +12391,10 @@
         <v>497</v>
       </c>
       <c r="D407" t="s">
+        <v>498</v>
+      </c>
+      <c r="E407" t="s">
         <v>543</v>
-      </c>
-      <c r="E407" t="s">
-        <v>499</v>
       </c>
       <c r="F407" t="s">
         <v>19</v>
@@ -12631,10 +12631,10 @@
         <v>554</v>
       </c>
       <c r="D419" t="s">
+        <v>555</v>
+      </c>
+      <c r="E419" t="s">
         <v>559</v>
-      </c>
-      <c r="E419" t="s">
-        <v>556</v>
       </c>
       <c r="F419" t="s">
         <v>24</v>
@@ -12671,10 +12671,10 @@
         <v>554</v>
       </c>
       <c r="D421" t="s">
+        <v>555</v>
+      </c>
+      <c r="E421" t="s">
         <v>562</v>
-      </c>
-      <c r="E421" t="s">
-        <v>556</v>
       </c>
       <c r="F421" t="s">
         <v>19</v>
@@ -12811,10 +12811,10 @@
         <v>570</v>
       </c>
       <c r="D428" t="s">
+        <v>555</v>
+      </c>
+      <c r="E428" t="s">
         <v>571</v>
-      </c>
-      <c r="E428" t="s">
-        <v>556</v>
       </c>
       <c r="F428" t="s">
         <v>24</v>
@@ -12831,10 +12831,10 @@
         <v>573</v>
       </c>
       <c r="D429" t="s">
+        <v>555</v>
+      </c>
+      <c r="E429" t="s">
         <v>574</v>
-      </c>
-      <c r="E429" t="s">
-        <v>556</v>
       </c>
       <c r="F429" t="s">
         <v>24</v>
@@ -12911,10 +12911,10 @@
         <v>554</v>
       </c>
       <c r="D433" t="s">
+        <v>555</v>
+      </c>
+      <c r="E433" t="s">
         <v>579</v>
-      </c>
-      <c r="E433" t="s">
-        <v>556</v>
       </c>
       <c r="F433" t="s">
         <v>24</v>
@@ -12971,10 +12971,10 @@
         <v>554</v>
       </c>
       <c r="D436" t="s">
+        <v>555</v>
+      </c>
+      <c r="E436" t="s">
         <v>583</v>
-      </c>
-      <c r="E436" t="s">
-        <v>556</v>
       </c>
       <c r="F436" t="s">
         <v>24</v>
@@ -12991,10 +12991,10 @@
         <v>554</v>
       </c>
       <c r="D437" t="s">
+        <v>555</v>
+      </c>
+      <c r="E437" t="s">
         <v>585</v>
-      </c>
-      <c r="E437" t="s">
-        <v>556</v>
       </c>
       <c r="F437" t="s">
         <v>19</v>
@@ -13051,10 +13051,10 @@
         <v>589</v>
       </c>
       <c r="D440" t="s">
+        <v>555</v>
+      </c>
+      <c r="E440" t="s">
         <v>590</v>
-      </c>
-      <c r="E440" t="s">
-        <v>556</v>
       </c>
       <c r="F440" t="s">
         <v>24</v>
@@ -13331,10 +13331,10 @@
         <v>605</v>
       </c>
       <c r="D454" t="s">
+        <v>555</v>
+      </c>
+      <c r="E454" t="s">
         <v>606</v>
-      </c>
-      <c r="E454" t="s">
-        <v>556</v>
       </c>
       <c r="F454" t="s">
         <v>19</v>
@@ -13531,10 +13531,10 @@
         <v>621</v>
       </c>
       <c r="D464" t="s">
+        <v>609</v>
+      </c>
+      <c r="E464" t="s">
         <v>622</v>
-      </c>
-      <c r="E464" t="s">
-        <v>610</v>
       </c>
       <c r="F464" t="s">
         <v>24</v>
@@ -13551,10 +13551,10 @@
         <v>608</v>
       </c>
       <c r="D465" t="s">
+        <v>609</v>
+      </c>
+      <c r="E465" t="s">
         <v>624</v>
-      </c>
-      <c r="E465" t="s">
-        <v>610</v>
       </c>
       <c r="F465" t="s">
         <v>24</v>
@@ -13571,10 +13571,10 @@
         <v>621</v>
       </c>
       <c r="D466" t="s">
+        <v>609</v>
+      </c>
+      <c r="E466" t="s">
         <v>626</v>
-      </c>
-      <c r="E466" t="s">
-        <v>610</v>
       </c>
       <c r="F466" t="s">
         <v>24</v>
@@ -13591,10 +13591,10 @@
         <v>628</v>
       </c>
       <c r="D467" t="s">
+        <v>609</v>
+      </c>
+      <c r="E467" t="s">
         <v>629</v>
-      </c>
-      <c r="E467" t="s">
-        <v>610</v>
       </c>
       <c r="F467" t="s">
         <v>24</v>
@@ -13631,10 +13631,10 @@
         <v>632</v>
       </c>
       <c r="D469" t="s">
+        <v>609</v>
+      </c>
+      <c r="E469" t="s">
         <v>633</v>
-      </c>
-      <c r="E469" t="s">
-        <v>610</v>
       </c>
       <c r="F469" t="s">
         <v>24</v>
@@ -13711,10 +13711,10 @@
         <v>621</v>
       </c>
       <c r="D473" t="s">
+        <v>609</v>
+      </c>
+      <c r="E473" t="s">
         <v>638</v>
-      </c>
-      <c r="E473" t="s">
-        <v>610</v>
       </c>
       <c r="F473" t="s">
         <v>24</v>
@@ -14011,10 +14011,10 @@
         <v>653</v>
       </c>
       <c r="D488" t="s">
+        <v>654</v>
+      </c>
+      <c r="E488" t="s">
         <v>657</v>
-      </c>
-      <c r="E488" t="s">
-        <v>655</v>
       </c>
       <c r="F488" t="s">
         <v>611</v>
@@ -14131,10 +14131,10 @@
         <v>665</v>
       </c>
       <c r="D494" t="s">
+        <v>654</v>
+      </c>
+      <c r="E494" t="s">
         <v>633</v>
-      </c>
-      <c r="E494" t="s">
-        <v>655</v>
       </c>
       <c r="F494" t="s">
         <v>13</v>
@@ -14151,10 +14151,10 @@
         <v>665</v>
       </c>
       <c r="D495" t="s">
+        <v>654</v>
+      </c>
+      <c r="E495" t="s">
         <v>633</v>
-      </c>
-      <c r="E495" t="s">
-        <v>655</v>
       </c>
       <c r="F495" t="s">
         <v>16</v>
@@ -14211,10 +14211,10 @@
         <v>653</v>
       </c>
       <c r="D498" t="s">
+        <v>654</v>
+      </c>
+      <c r="E498" t="s">
         <v>670</v>
-      </c>
-      <c r="E498" t="s">
-        <v>655</v>
       </c>
       <c r="F498" t="s">
         <v>611</v>
@@ -14291,10 +14291,10 @@
         <v>653</v>
       </c>
       <c r="D502" t="s">
+        <v>654</v>
+      </c>
+      <c r="E502" t="s">
         <v>675</v>
-      </c>
-      <c r="E502" t="s">
-        <v>655</v>
       </c>
       <c r="F502" t="s">
         <v>19</v>
@@ -14391,10 +14391,10 @@
         <v>681</v>
       </c>
       <c r="D507" t="s">
+        <v>654</v>
+      </c>
+      <c r="E507" t="s">
         <v>682</v>
-      </c>
-      <c r="E507" t="s">
-        <v>655</v>
       </c>
       <c r="F507" t="s">
         <v>24</v>
@@ -14411,10 +14411,10 @@
         <v>684</v>
       </c>
       <c r="D508" t="s">
+        <v>654</v>
+      </c>
+      <c r="E508" t="s">
         <v>685</v>
-      </c>
-      <c r="E508" t="s">
-        <v>655</v>
       </c>
       <c r="F508" t="s">
         <v>611</v>
@@ -14431,10 +14431,10 @@
         <v>687</v>
       </c>
       <c r="D509" t="s">
+        <v>654</v>
+      </c>
+      <c r="E509" t="s">
         <v>685</v>
-      </c>
-      <c r="E509" t="s">
-        <v>655</v>
       </c>
       <c r="F509" t="s">
         <v>19</v>
@@ -14451,10 +14451,10 @@
         <v>689</v>
       </c>
       <c r="D510" t="s">
+        <v>654</v>
+      </c>
+      <c r="E510" t="s">
         <v>690</v>
-      </c>
-      <c r="E510" t="s">
-        <v>655</v>
       </c>
       <c r="F510" t="s">
         <v>24</v>
@@ -14491,10 +14491,10 @@
         <v>653</v>
       </c>
       <c r="D512" t="s">
+        <v>654</v>
+      </c>
+      <c r="E512" t="s">
         <v>693</v>
-      </c>
-      <c r="E512" t="s">
-        <v>655</v>
       </c>
       <c r="F512" t="s">
         <v>16</v>
@@ -14671,10 +14671,10 @@
         <v>653</v>
       </c>
       <c r="D521" t="s">
+        <v>654</v>
+      </c>
+      <c r="E521" t="s">
         <v>704</v>
-      </c>
-      <c r="E521" t="s">
-        <v>655</v>
       </c>
       <c r="F521" t="s">
         <v>19</v>
@@ -14691,10 +14691,10 @@
         <v>653</v>
       </c>
       <c r="D522" t="s">
+        <v>654</v>
+      </c>
+      <c r="E522" t="s">
         <v>706</v>
-      </c>
-      <c r="E522" t="s">
-        <v>655</v>
       </c>
       <c r="F522" t="s">
         <v>13</v>
@@ -14711,10 +14711,10 @@
         <v>653</v>
       </c>
       <c r="D523" t="s">
+        <v>654</v>
+      </c>
+      <c r="E523" t="s">
         <v>708</v>
-      </c>
-      <c r="E523" t="s">
-        <v>655</v>
       </c>
       <c r="F523" t="s">
         <v>24</v>
@@ -14751,10 +14751,10 @@
         <v>711</v>
       </c>
       <c r="D525" t="s">
+        <v>712</v>
+      </c>
+      <c r="E525" t="s">
         <v>657</v>
-      </c>
-      <c r="E525" t="s">
-        <v>712</v>
       </c>
       <c r="F525" t="s">
         <v>713</v>
@@ -14771,10 +14771,10 @@
         <v>711</v>
       </c>
       <c r="D526" t="s">
+        <v>712</v>
+      </c>
+      <c r="E526" t="s">
         <v>657</v>
-      </c>
-      <c r="E526" t="s">
-        <v>712</v>
       </c>
       <c r="F526" t="s">
         <v>713</v>
@@ -14791,10 +14791,10 @@
         <v>711</v>
       </c>
       <c r="D527" t="s">
+        <v>712</v>
+      </c>
+      <c r="E527" t="s">
         <v>657</v>
-      </c>
-      <c r="E527" t="s">
-        <v>712</v>
       </c>
       <c r="F527" t="s">
         <v>713</v>
@@ -14811,10 +14811,10 @@
         <v>711</v>
       </c>
       <c r="D528" t="s">
+        <v>712</v>
+      </c>
+      <c r="E528" t="s">
         <v>657</v>
-      </c>
-      <c r="E528" t="s">
-        <v>712</v>
       </c>
       <c r="F528" t="s">
         <v>713</v>
@@ -14831,10 +14831,10 @@
         <v>711</v>
       </c>
       <c r="D529" t="s">
+        <v>712</v>
+      </c>
+      <c r="E529" t="s">
         <v>718</v>
-      </c>
-      <c r="E529" t="s">
-        <v>712</v>
       </c>
       <c r="F529" t="s">
         <v>16</v>
@@ -14851,10 +14851,10 @@
         <v>720</v>
       </c>
       <c r="D530" t="s">
+        <v>712</v>
+      </c>
+      <c r="E530" t="s">
         <v>657</v>
-      </c>
-      <c r="E530" t="s">
-        <v>712</v>
       </c>
       <c r="F530" t="s">
         <v>713</v>
@@ -14871,10 +14871,10 @@
         <v>711</v>
       </c>
       <c r="D531" t="s">
+        <v>712</v>
+      </c>
+      <c r="E531" t="s">
         <v>657</v>
-      </c>
-      <c r="E531" t="s">
-        <v>712</v>
       </c>
       <c r="F531" t="s">
         <v>713</v>
@@ -14891,10 +14891,10 @@
         <v>711</v>
       </c>
       <c r="D532" t="s">
+        <v>712</v>
+      </c>
+      <c r="E532" t="s">
         <v>657</v>
-      </c>
-      <c r="E532" t="s">
-        <v>712</v>
       </c>
       <c r="F532" t="s">
         <v>713</v>
@@ -14911,10 +14911,10 @@
         <v>711</v>
       </c>
       <c r="D533" t="s">
+        <v>712</v>
+      </c>
+      <c r="E533" t="s">
         <v>657</v>
-      </c>
-      <c r="E533" t="s">
-        <v>712</v>
       </c>
       <c r="F533" t="s">
         <v>713</v>
@@ -14931,10 +14931,10 @@
         <v>711</v>
       </c>
       <c r="D534" t="s">
+        <v>712</v>
+      </c>
+      <c r="E534" t="s">
         <v>657</v>
-      </c>
-      <c r="E534" t="s">
-        <v>712</v>
       </c>
       <c r="F534" t="s">
         <v>713</v>
@@ -14951,10 +14951,10 @@
         <v>711</v>
       </c>
       <c r="D535" t="s">
+        <v>712</v>
+      </c>
+      <c r="E535" t="s">
         <v>657</v>
-      </c>
-      <c r="E535" t="s">
-        <v>712</v>
       </c>
       <c r="F535" t="s">
         <v>713</v>
@@ -14971,10 +14971,10 @@
         <v>711</v>
       </c>
       <c r="D536" t="s">
+        <v>712</v>
+      </c>
+      <c r="E536" t="s">
         <v>727</v>
-      </c>
-      <c r="E536" t="s">
-        <v>712</v>
       </c>
       <c r="F536" t="s">
         <v>16</v>
@@ -14991,10 +14991,10 @@
         <v>711</v>
       </c>
       <c r="D537" t="s">
+        <v>712</v>
+      </c>
+      <c r="E537" t="s">
         <v>729</v>
-      </c>
-      <c r="E537" t="s">
-        <v>712</v>
       </c>
       <c r="F537" t="s">
         <v>16</v>
@@ -15011,10 +15011,10 @@
         <v>711</v>
       </c>
       <c r="D538" t="s">
+        <v>712</v>
+      </c>
+      <c r="E538" t="s">
         <v>657</v>
-      </c>
-      <c r="E538" t="s">
-        <v>712</v>
       </c>
       <c r="F538" t="s">
         <v>713</v>
@@ -15031,10 +15031,10 @@
         <v>711</v>
       </c>
       <c r="D539" t="s">
+        <v>712</v>
+      </c>
+      <c r="E539" t="s">
         <v>657</v>
-      </c>
-      <c r="E539" t="s">
-        <v>712</v>
       </c>
       <c r="F539" t="s">
         <v>713</v>
@@ -15051,10 +15051,10 @@
         <v>689</v>
       </c>
       <c r="D540" t="s">
+        <v>712</v>
+      </c>
+      <c r="E540" t="s">
         <v>657</v>
-      </c>
-      <c r="E540" t="s">
-        <v>712</v>
       </c>
       <c r="F540" t="s">
         <v>713</v>
@@ -15071,10 +15071,10 @@
         <v>711</v>
       </c>
       <c r="D541" t="s">
+        <v>712</v>
+      </c>
+      <c r="E541" t="s">
         <v>657</v>
-      </c>
-      <c r="E541" t="s">
-        <v>712</v>
       </c>
       <c r="F541" t="s">
         <v>713</v>
@@ -15091,10 +15091,10 @@
         <v>711</v>
       </c>
       <c r="D542" t="s">
+        <v>712</v>
+      </c>
+      <c r="E542" t="s">
         <v>657</v>
-      </c>
-      <c r="E542" t="s">
-        <v>712</v>
       </c>
       <c r="F542" t="s">
         <v>713</v>
@@ -15111,10 +15111,10 @@
         <v>711</v>
       </c>
       <c r="D543" t="s">
+        <v>712</v>
+      </c>
+      <c r="E543" t="s">
         <v>657</v>
-      </c>
-      <c r="E543" t="s">
-        <v>712</v>
       </c>
       <c r="F543" t="s">
         <v>713</v>
@@ -15131,10 +15131,10 @@
         <v>711</v>
       </c>
       <c r="D544" t="s">
+        <v>712</v>
+      </c>
+      <c r="E544" t="s">
         <v>657</v>
-      </c>
-      <c r="E544" t="s">
-        <v>712</v>
       </c>
       <c r="F544" t="s">
         <v>713</v>
@@ -15151,10 +15151,10 @@
         <v>738</v>
       </c>
       <c r="D545" t="s">
+        <v>712</v>
+      </c>
+      <c r="E545" t="s">
         <v>657</v>
-      </c>
-      <c r="E545" t="s">
-        <v>712</v>
       </c>
       <c r="F545" t="s">
         <v>13</v>
@@ -15171,10 +15171,10 @@
         <v>711</v>
       </c>
       <c r="D546" t="s">
+        <v>712</v>
+      </c>
+      <c r="E546" t="s">
         <v>657</v>
-      </c>
-      <c r="E546" t="s">
-        <v>712</v>
       </c>
       <c r="F546" t="s">
         <v>713</v>
@@ -15191,10 +15191,10 @@
         <v>711</v>
       </c>
       <c r="D547" t="s">
+        <v>712</v>
+      </c>
+      <c r="E547" t="s">
         <v>657</v>
-      </c>
-      <c r="E547" t="s">
-        <v>712</v>
       </c>
       <c r="F547" t="s">
         <v>16</v>
@@ -15231,10 +15231,10 @@
         <v>742</v>
       </c>
       <c r="D549" t="s">
+        <v>743</v>
+      </c>
+      <c r="E549" t="s">
         <v>746</v>
-      </c>
-      <c r="E549" t="s">
-        <v>744</v>
       </c>
       <c r="F549" t="s">
         <v>713</v>
@@ -15251,10 +15251,10 @@
         <v>742</v>
       </c>
       <c r="D550" t="s">
+        <v>743</v>
+      </c>
+      <c r="E550" t="s">
         <v>748</v>
-      </c>
-      <c r="E550" t="s">
-        <v>744</v>
       </c>
       <c r="F550" t="s">
         <v>713</v>
@@ -15411,10 +15411,10 @@
         <v>758</v>
       </c>
       <c r="D558" t="s">
+        <v>743</v>
+      </c>
+      <c r="E558" t="s">
         <v>759</v>
-      </c>
-      <c r="E558" t="s">
-        <v>744</v>
       </c>
       <c r="F558" t="s">
         <v>24</v>
@@ -15451,10 +15451,10 @@
         <v>742</v>
       </c>
       <c r="D560" t="s">
+        <v>743</v>
+      </c>
+      <c r="E560" t="s">
         <v>762</v>
-      </c>
-      <c r="E560" t="s">
-        <v>744</v>
       </c>
       <c r="F560" t="s">
         <v>713</v>
@@ -15471,10 +15471,10 @@
         <v>742</v>
       </c>
       <c r="D561" t="s">
+        <v>743</v>
+      </c>
+      <c r="E561" t="s">
         <v>762</v>
-      </c>
-      <c r="E561" t="s">
-        <v>744</v>
       </c>
       <c r="F561" t="s">
         <v>713</v>
@@ -15631,10 +15631,10 @@
         <v>773</v>
       </c>
       <c r="D569" t="s">
+        <v>743</v>
+      </c>
+      <c r="E569" t="s">
         <v>774</v>
-      </c>
-      <c r="E569" t="s">
-        <v>744</v>
       </c>
       <c r="F569" t="s">
         <v>713</v>
@@ -15811,10 +15811,10 @@
         <v>782</v>
       </c>
       <c r="D578" t="s">
+        <v>779</v>
+      </c>
+      <c r="E578" t="s">
         <v>787</v>
-      </c>
-      <c r="E578" t="s">
-        <v>780</v>
       </c>
       <c r="F578" t="s">
         <v>713</v>
@@ -15831,10 +15831,10 @@
         <v>789</v>
       </c>
       <c r="D579" t="s">
+        <v>779</v>
+      </c>
+      <c r="E579" t="s">
         <v>790</v>
-      </c>
-      <c r="E579" t="s">
-        <v>780</v>
       </c>
       <c r="F579" t="s">
         <v>24</v>
@@ -15851,10 +15851,10 @@
         <v>782</v>
       </c>
       <c r="D580" t="s">
+        <v>779</v>
+      </c>
+      <c r="E580" t="s">
         <v>792</v>
-      </c>
-      <c r="E580" t="s">
-        <v>780</v>
       </c>
       <c r="F580" t="s">
         <v>713</v>
@@ -15871,10 +15871,10 @@
         <v>782</v>
       </c>
       <c r="D581" t="s">
+        <v>779</v>
+      </c>
+      <c r="E581" t="s">
         <v>794</v>
-      </c>
-      <c r="E581" t="s">
-        <v>780</v>
       </c>
       <c r="F581" t="s">
         <v>16</v>
@@ -15911,10 +15911,10 @@
         <v>797</v>
       </c>
       <c r="D583" t="s">
+        <v>779</v>
+      </c>
+      <c r="E583" t="s">
         <v>798</v>
-      </c>
-      <c r="E583" t="s">
-        <v>780</v>
       </c>
       <c r="F583" t="s">
         <v>24</v>
@@ -15931,10 +15931,10 @@
         <v>800</v>
       </c>
       <c r="D584" t="s">
+        <v>779</v>
+      </c>
+      <c r="E584" t="s">
         <v>801</v>
-      </c>
-      <c r="E584" t="s">
-        <v>780</v>
       </c>
       <c r="F584" t="s">
         <v>24</v>
@@ -15971,10 +15971,10 @@
         <v>804</v>
       </c>
       <c r="D586" t="s">
+        <v>779</v>
+      </c>
+      <c r="E586" t="s">
         <v>805</v>
-      </c>
-      <c r="E586" t="s">
-        <v>780</v>
       </c>
       <c r="F586" t="s">
         <v>24</v>
@@ -15991,10 +15991,10 @@
         <v>782</v>
       </c>
       <c r="D587" t="s">
+        <v>779</v>
+      </c>
+      <c r="E587" t="s">
         <v>807</v>
-      </c>
-      <c r="E587" t="s">
-        <v>780</v>
       </c>
       <c r="F587" t="s">
         <v>13</v>
@@ -16011,10 +16011,10 @@
         <v>782</v>
       </c>
       <c r="D588" t="s">
+        <v>779</v>
+      </c>
+      <c r="E588" t="s">
         <v>809</v>
-      </c>
-      <c r="E588" t="s">
-        <v>780</v>
       </c>
       <c r="F588" t="s">
         <v>713</v>
@@ -16211,10 +16211,10 @@
         <v>824</v>
       </c>
       <c r="D598" t="s">
+        <v>821</v>
+      </c>
+      <c r="E598" t="s">
         <v>825</v>
-      </c>
-      <c r="E598" t="s">
-        <v>822</v>
       </c>
       <c r="F598" t="s">
         <v>16</v>
@@ -16291,10 +16291,10 @@
         <v>830</v>
       </c>
       <c r="D602" t="s">
+        <v>821</v>
+      </c>
+      <c r="E602" t="s">
         <v>831</v>
-      </c>
-      <c r="E602" t="s">
-        <v>822</v>
       </c>
       <c r="F602" t="s">
         <v>24</v>
@@ -16311,10 +16311,10 @@
         <v>833</v>
       </c>
       <c r="D603" t="s">
+        <v>821</v>
+      </c>
+      <c r="E603" t="s">
         <v>834</v>
-      </c>
-      <c r="E603" t="s">
-        <v>822</v>
       </c>
       <c r="F603" t="s">
         <v>24</v>
@@ -16331,10 +16331,10 @@
         <v>836</v>
       </c>
       <c r="D604" t="s">
+        <v>821</v>
+      </c>
+      <c r="E604" t="s">
         <v>837</v>
-      </c>
-      <c r="E604" t="s">
-        <v>822</v>
       </c>
       <c r="F604" t="s">
         <v>713</v>
@@ -16351,10 +16351,10 @@
         <v>820</v>
       </c>
       <c r="D605" t="s">
+        <v>821</v>
+      </c>
+      <c r="E605" t="s">
         <v>839</v>
-      </c>
-      <c r="E605" t="s">
-        <v>822</v>
       </c>
       <c r="F605" t="s">
         <v>24</v>
@@ -16411,10 +16411,10 @@
         <v>843</v>
       </c>
       <c r="D608" t="s">
+        <v>821</v>
+      </c>
+      <c r="E608" t="s">
         <v>844</v>
-      </c>
-      <c r="E608" t="s">
-        <v>822</v>
       </c>
       <c r="F608" t="s">
         <v>24</v>
@@ -16431,10 +16431,10 @@
         <v>807</v>
       </c>
       <c r="D609" t="s">
+        <v>821</v>
+      </c>
+      <c r="E609" t="s">
         <v>846</v>
-      </c>
-      <c r="E609" t="s">
-        <v>822</v>
       </c>
       <c r="F609" t="s">
         <v>713</v>
@@ -16471,10 +16471,10 @@
         <v>849</v>
       </c>
       <c r="D611" t="s">
+        <v>821</v>
+      </c>
+      <c r="E611" t="s">
         <v>825</v>
-      </c>
-      <c r="E611" t="s">
-        <v>822</v>
       </c>
       <c r="F611" t="s">
         <v>24</v>
@@ -16491,10 +16491,10 @@
         <v>820</v>
       </c>
       <c r="D612" t="s">
+        <v>821</v>
+      </c>
+      <c r="E612" t="s">
         <v>851</v>
-      </c>
-      <c r="E612" t="s">
-        <v>822</v>
       </c>
       <c r="F612" t="s">
         <v>16</v>
@@ -16531,10 +16531,10 @@
         <v>820</v>
       </c>
       <c r="D614" t="s">
+        <v>821</v>
+      </c>
+      <c r="E614" t="s">
         <v>854</v>
-      </c>
-      <c r="E614" t="s">
-        <v>822</v>
       </c>
       <c r="F614" t="s">
         <v>713</v>
@@ -16731,10 +16731,10 @@
         <v>868</v>
       </c>
       <c r="D624" t="s">
+        <v>865</v>
+      </c>
+      <c r="E624" t="s">
         <v>869</v>
-      </c>
-      <c r="E624" t="s">
-        <v>866</v>
       </c>
       <c r="F624" t="s">
         <v>24</v>
@@ -16831,10 +16831,10 @@
         <v>864</v>
       </c>
       <c r="D629" t="s">
+        <v>865</v>
+      </c>
+      <c r="E629" t="s">
         <v>876</v>
-      </c>
-      <c r="E629" t="s">
-        <v>866</v>
       </c>
       <c r="F629" t="s">
         <v>24</v>
@@ -16891,10 +16891,10 @@
         <v>880</v>
       </c>
       <c r="D632" t="s">
+        <v>865</v>
+      </c>
+      <c r="E632" t="s">
         <v>876</v>
-      </c>
-      <c r="E632" t="s">
-        <v>866</v>
       </c>
       <c r="F632" t="s">
         <v>24</v>
@@ -16911,10 +16911,10 @@
         <v>882</v>
       </c>
       <c r="D633" t="s">
+        <v>865</v>
+      </c>
+      <c r="E633" t="s">
         <v>883</v>
-      </c>
-      <c r="E633" t="s">
-        <v>866</v>
       </c>
       <c r="F633" t="s">
         <v>24</v>
@@ -16931,10 +16931,10 @@
         <v>885</v>
       </c>
       <c r="D634" t="s">
+        <v>865</v>
+      </c>
+      <c r="E634" t="s">
         <v>886</v>
-      </c>
-      <c r="E634" t="s">
-        <v>866</v>
       </c>
       <c r="F634" t="s">
         <v>24</v>
@@ -16971,10 +16971,10 @@
         <v>864</v>
       </c>
       <c r="D636" t="s">
+        <v>865</v>
+      </c>
+      <c r="E636" t="s">
         <v>889</v>
-      </c>
-      <c r="E636" t="s">
-        <v>866</v>
       </c>
       <c r="F636" t="s">
         <v>713</v>
@@ -16991,10 +16991,10 @@
         <v>891</v>
       </c>
       <c r="D637" t="s">
+        <v>865</v>
+      </c>
+      <c r="E637" t="s">
         <v>892</v>
-      </c>
-      <c r="E637" t="s">
-        <v>866</v>
       </c>
       <c r="F637" t="s">
         <v>24</v>
@@ -17071,10 +17071,10 @@
         <v>897</v>
       </c>
       <c r="D641" t="s">
+        <v>865</v>
+      </c>
+      <c r="E641" t="s">
         <v>898</v>
-      </c>
-      <c r="E641" t="s">
-        <v>866</v>
       </c>
       <c r="F641" t="s">
         <v>16</v>
@@ -17091,10 +17091,10 @@
         <v>864</v>
       </c>
       <c r="D642" t="s">
+        <v>865</v>
+      </c>
+      <c r="E642" t="s">
         <v>900</v>
-      </c>
-      <c r="E642" t="s">
-        <v>866</v>
       </c>
       <c r="F642" t="s">
         <v>16</v>
@@ -17111,10 +17111,10 @@
         <v>864</v>
       </c>
       <c r="D643" t="s">
+        <v>865</v>
+      </c>
+      <c r="E643" t="s">
         <v>902</v>
-      </c>
-      <c r="E643" t="s">
-        <v>866</v>
       </c>
       <c r="F643" t="s">
         <v>16</v>
@@ -17171,10 +17171,10 @@
         <v>864</v>
       </c>
       <c r="D646" t="s">
+        <v>865</v>
+      </c>
+      <c r="E646" t="s">
         <v>906</v>
-      </c>
-      <c r="E646" t="s">
-        <v>866</v>
       </c>
       <c r="F646" t="s">
         <v>24</v>
@@ -17251,10 +17251,10 @@
         <v>914</v>
       </c>
       <c r="D650" t="s">
+        <v>911</v>
+      </c>
+      <c r="E650" t="s">
         <v>915</v>
-      </c>
-      <c r="E650" t="s">
-        <v>912</v>
       </c>
       <c r="F650" t="s">
         <v>16</v>
@@ -17291,10 +17291,10 @@
         <v>919</v>
       </c>
       <c r="D652" t="s">
+        <v>911</v>
+      </c>
+      <c r="E652" t="s">
         <v>920</v>
-      </c>
-      <c r="E652" t="s">
-        <v>912</v>
       </c>
       <c r="F652" t="s">
         <v>713</v>
@@ -17311,10 +17311,10 @@
         <v>919</v>
       </c>
       <c r="D653" t="s">
+        <v>911</v>
+      </c>
+      <c r="E653" t="s">
         <v>920</v>
-      </c>
-      <c r="E653" t="s">
-        <v>912</v>
       </c>
       <c r="F653" t="s">
         <v>713</v>
@@ -17331,10 +17331,10 @@
         <v>864</v>
       </c>
       <c r="D654" t="s">
+        <v>911</v>
+      </c>
+      <c r="E654" t="s">
         <v>902</v>
-      </c>
-      <c r="E654" t="s">
-        <v>912</v>
       </c>
       <c r="F654" t="s">
         <v>16</v>
@@ -17351,10 +17351,10 @@
         <v>919</v>
       </c>
       <c r="D655" t="s">
+        <v>911</v>
+      </c>
+      <c r="E655" t="s">
         <v>920</v>
-      </c>
-      <c r="E655" t="s">
-        <v>912</v>
       </c>
       <c r="F655" t="s">
         <v>713</v>
@@ -17371,10 +17371,10 @@
         <v>919</v>
       </c>
       <c r="D656" t="s">
+        <v>911</v>
+      </c>
+      <c r="E656" t="s">
         <v>920</v>
-      </c>
-      <c r="E656" t="s">
-        <v>912</v>
       </c>
       <c r="F656" t="s">
         <v>713</v>
@@ -17391,10 +17391,10 @@
         <v>926</v>
       </c>
       <c r="D657" t="s">
+        <v>911</v>
+      </c>
+      <c r="E657" t="s">
         <v>927</v>
-      </c>
-      <c r="E657" t="s">
-        <v>912</v>
       </c>
       <c r="F657" t="s">
         <v>16</v>
@@ -17411,10 +17411,10 @@
         <v>929</v>
       </c>
       <c r="D658" t="s">
+        <v>911</v>
+      </c>
+      <c r="E658" t="s">
         <v>930</v>
-      </c>
-      <c r="E658" t="s">
-        <v>912</v>
       </c>
       <c r="F658" t="s">
         <v>24</v>
@@ -17431,10 +17431,10 @@
         <v>932</v>
       </c>
       <c r="D659" t="s">
+        <v>911</v>
+      </c>
+      <c r="E659" t="s">
         <v>889</v>
-      </c>
-      <c r="E659" t="s">
-        <v>912</v>
       </c>
       <c r="F659" t="s">
         <v>24</v>
@@ -17451,10 +17451,10 @@
         <v>934</v>
       </c>
       <c r="D660" t="s">
+        <v>911</v>
+      </c>
+      <c r="E660" t="s">
         <v>935</v>
-      </c>
-      <c r="E660" t="s">
-        <v>912</v>
       </c>
       <c r="F660" t="s">
         <v>24</v>
@@ -17471,10 +17471,10 @@
         <v>919</v>
       </c>
       <c r="D661" t="s">
+        <v>911</v>
+      </c>
+      <c r="E661" t="s">
         <v>920</v>
-      </c>
-      <c r="E661" t="s">
-        <v>912</v>
       </c>
       <c r="F661" t="s">
         <v>713</v>
@@ -17491,10 +17491,10 @@
         <v>915</v>
       </c>
       <c r="D662" t="s">
+        <v>911</v>
+      </c>
+      <c r="E662" t="s">
         <v>920</v>
-      </c>
-      <c r="E662" t="s">
-        <v>912</v>
       </c>
       <c r="F662" t="s">
         <v>24</v>
@@ -17511,10 +17511,10 @@
         <v>939</v>
       </c>
       <c r="D663" t="s">
+        <v>911</v>
+      </c>
+      <c r="E663" t="s">
         <v>940</v>
-      </c>
-      <c r="E663" t="s">
-        <v>912</v>
       </c>
       <c r="F663" t="s">
         <v>24</v>
@@ -17531,10 +17531,10 @@
         <v>942</v>
       </c>
       <c r="D664" t="s">
+        <v>911</v>
+      </c>
+      <c r="E664" t="s">
         <v>902</v>
-      </c>
-      <c r="E664" t="s">
-        <v>912</v>
       </c>
       <c r="F664" t="s">
         <v>16</v>
@@ -17551,10 +17551,10 @@
         <v>919</v>
       </c>
       <c r="D665" t="s">
+        <v>911</v>
+      </c>
+      <c r="E665" t="s">
         <v>944</v>
-      </c>
-      <c r="E665" t="s">
-        <v>912</v>
       </c>
       <c r="F665" t="s">
         <v>713</v>
@@ -17571,10 +17571,10 @@
         <v>910</v>
       </c>
       <c r="D666" t="s">
+        <v>911</v>
+      </c>
+      <c r="E666" t="s">
         <v>944</v>
-      </c>
-      <c r="E666" t="s">
-        <v>912</v>
       </c>
       <c r="F666" t="s">
         <v>24</v>
@@ -17591,10 +17591,10 @@
         <v>947</v>
       </c>
       <c r="D667" t="s">
+        <v>911</v>
+      </c>
+      <c r="E667" t="s">
         <v>948</v>
-      </c>
-      <c r="E667" t="s">
-        <v>912</v>
       </c>
       <c r="F667" t="s">
         <v>24</v>
@@ -17611,10 +17611,10 @@
         <v>919</v>
       </c>
       <c r="D668" t="s">
+        <v>911</v>
+      </c>
+      <c r="E668" t="s">
         <v>920</v>
-      </c>
-      <c r="E668" t="s">
-        <v>912</v>
       </c>
       <c r="F668" t="s">
         <v>16</v>
@@ -17631,10 +17631,10 @@
         <v>932</v>
       </c>
       <c r="D669" t="s">
+        <v>911</v>
+      </c>
+      <c r="E669" t="s">
         <v>902</v>
-      </c>
-      <c r="E669" t="s">
-        <v>912</v>
       </c>
       <c r="F669" t="s">
         <v>16</v>
@@ -17651,10 +17651,10 @@
         <v>919</v>
       </c>
       <c r="D670" t="s">
+        <v>911</v>
+      </c>
+      <c r="E670" t="s">
         <v>920</v>
-      </c>
-      <c r="E670" t="s">
-        <v>912</v>
       </c>
       <c r="F670" t="s">
         <v>713</v>
@@ -17691,10 +17691,10 @@
         <v>919</v>
       </c>
       <c r="D672" t="s">
+        <v>911</v>
+      </c>
+      <c r="E672" t="s">
         <v>920</v>
-      </c>
-      <c r="E672" t="s">
-        <v>912</v>
       </c>
       <c r="F672" t="s">
         <v>16</v>
@@ -17711,10 +17711,10 @@
         <v>919</v>
       </c>
       <c r="D673" t="s">
+        <v>911</v>
+      </c>
+      <c r="E673" t="s">
         <v>920</v>
-      </c>
-      <c r="E673" t="s">
-        <v>912</v>
       </c>
       <c r="F673" t="s">
         <v>713</v>
@@ -17731,10 +17731,10 @@
         <v>934</v>
       </c>
       <c r="D674" t="s">
+        <v>911</v>
+      </c>
+      <c r="E674" t="s">
         <v>902</v>
-      </c>
-      <c r="E674" t="s">
-        <v>912</v>
       </c>
       <c r="F674" t="s">
         <v>16</v>
@@ -17771,10 +17771,10 @@
         <v>919</v>
       </c>
       <c r="D676" t="s">
+        <v>911</v>
+      </c>
+      <c r="E676" t="s">
         <v>959</v>
-      </c>
-      <c r="E676" t="s">
-        <v>912</v>
       </c>
       <c r="F676" t="s">
         <v>16</v>
@@ -17791,10 +17791,10 @@
         <v>919</v>
       </c>
       <c r="D677" t="s">
+        <v>911</v>
+      </c>
+      <c r="E677" t="s">
         <v>920</v>
-      </c>
-      <c r="E677" t="s">
-        <v>912</v>
       </c>
       <c r="F677" t="s">
         <v>713</v>
@@ -17811,10 +17811,10 @@
         <v>919</v>
       </c>
       <c r="D678" t="s">
+        <v>911</v>
+      </c>
+      <c r="E678" t="s">
         <v>920</v>
-      </c>
-      <c r="E678" t="s">
-        <v>912</v>
       </c>
       <c r="F678" t="s">
         <v>713</v>
@@ -17831,10 +17831,10 @@
         <v>934</v>
       </c>
       <c r="D679" t="s">
+        <v>911</v>
+      </c>
+      <c r="E679" t="s">
         <v>935</v>
-      </c>
-      <c r="E679" t="s">
-        <v>912</v>
       </c>
       <c r="F679" t="s">
         <v>24</v>
@@ -17851,10 +17851,10 @@
         <v>919</v>
       </c>
       <c r="D680" t="s">
+        <v>911</v>
+      </c>
+      <c r="E680" t="s">
         <v>920</v>
-      </c>
-      <c r="E680" t="s">
-        <v>912</v>
       </c>
       <c r="F680" t="s">
         <v>713</v>
@@ -17871,10 +17871,10 @@
         <v>919</v>
       </c>
       <c r="D681" t="s">
+        <v>911</v>
+      </c>
+      <c r="E681" t="s">
         <v>920</v>
-      </c>
-      <c r="E681" t="s">
-        <v>912</v>
       </c>
       <c r="F681" t="s">
         <v>713</v>
@@ -17911,10 +17911,10 @@
         <v>970</v>
       </c>
       <c r="D683" t="s">
+        <v>967</v>
+      </c>
+      <c r="E683" t="s">
         <v>971</v>
-      </c>
-      <c r="E683" t="s">
-        <v>968</v>
       </c>
       <c r="F683" t="s">
         <v>24</v>
@@ -17931,10 +17931,10 @@
         <v>973</v>
       </c>
       <c r="D684" t="s">
+        <v>967</v>
+      </c>
+      <c r="E684" t="s">
         <v>974</v>
-      </c>
-      <c r="E684" t="s">
-        <v>968</v>
       </c>
       <c r="F684" t="s">
         <v>713</v>
@@ -17951,10 +17951,10 @@
         <v>973</v>
       </c>
       <c r="D685" t="s">
+        <v>967</v>
+      </c>
+      <c r="E685" t="s">
         <v>974</v>
-      </c>
-      <c r="E685" t="s">
-        <v>968</v>
       </c>
       <c r="F685" t="s">
         <v>713</v>
@@ -17971,10 +17971,10 @@
         <v>973</v>
       </c>
       <c r="D686" t="s">
+        <v>967</v>
+      </c>
+      <c r="E686" t="s">
         <v>974</v>
-      </c>
-      <c r="E686" t="s">
-        <v>968</v>
       </c>
       <c r="F686" t="s">
         <v>713</v>
@@ -17991,10 +17991,10 @@
         <v>973</v>
       </c>
       <c r="D687" t="s">
+        <v>967</v>
+      </c>
+      <c r="E687" t="s">
         <v>974</v>
-      </c>
-      <c r="E687" t="s">
-        <v>968</v>
       </c>
       <c r="F687" t="s">
         <v>713</v>
@@ -18011,10 +18011,10 @@
         <v>973</v>
       </c>
       <c r="D688" t="s">
+        <v>967</v>
+      </c>
+      <c r="E688" t="s">
         <v>974</v>
-      </c>
-      <c r="E688" t="s">
-        <v>968</v>
       </c>
       <c r="F688" t="s">
         <v>713</v>
@@ -18031,10 +18031,10 @@
         <v>980</v>
       </c>
       <c r="D689" t="s">
+        <v>967</v>
+      </c>
+      <c r="E689" t="s">
         <v>971</v>
-      </c>
-      <c r="E689" t="s">
-        <v>968</v>
       </c>
       <c r="F689" t="s">
         <v>24</v>
@@ -18051,10 +18051,10 @@
         <v>982</v>
       </c>
       <c r="D690" t="s">
+        <v>967</v>
+      </c>
+      <c r="E690" t="s">
         <v>983</v>
-      </c>
-      <c r="E690" t="s">
-        <v>968</v>
       </c>
       <c r="F690" t="s">
         <v>24</v>
@@ -18071,10 +18071,10 @@
         <v>973</v>
       </c>
       <c r="D691" t="s">
+        <v>967</v>
+      </c>
+      <c r="E691" t="s">
         <v>974</v>
-      </c>
-      <c r="E691" t="s">
-        <v>968</v>
       </c>
       <c r="F691" t="s">
         <v>13</v>
@@ -18091,10 +18091,10 @@
         <v>919</v>
       </c>
       <c r="D692" t="s">
+        <v>967</v>
+      </c>
+      <c r="E692" t="s">
         <v>986</v>
-      </c>
-      <c r="E692" t="s">
-        <v>968</v>
       </c>
       <c r="F692" t="s">
         <v>16</v>
@@ -18111,10 +18111,10 @@
         <v>988</v>
       </c>
       <c r="D693" t="s">
+        <v>967</v>
+      </c>
+      <c r="E693" t="s">
         <v>989</v>
-      </c>
-      <c r="E693" t="s">
-        <v>968</v>
       </c>
       <c r="F693" t="s">
         <v>24</v>
@@ -18131,10 +18131,10 @@
         <v>991</v>
       </c>
       <c r="D694" t="s">
+        <v>967</v>
+      </c>
+      <c r="E694" t="s">
         <v>992</v>
-      </c>
-      <c r="E694" t="s">
-        <v>968</v>
       </c>
       <c r="F694" t="s">
         <v>16</v>
@@ -18151,10 +18151,10 @@
         <v>994</v>
       </c>
       <c r="D695" t="s">
+        <v>967</v>
+      </c>
+      <c r="E695" t="s">
         <v>995</v>
-      </c>
-      <c r="E695" t="s">
-        <v>968</v>
       </c>
       <c r="F695" t="s">
         <v>24</v>
@@ -18171,10 +18171,10 @@
         <v>973</v>
       </c>
       <c r="D696" t="s">
+        <v>967</v>
+      </c>
+      <c r="E696" t="s">
         <v>974</v>
-      </c>
-      <c r="E696" t="s">
-        <v>968</v>
       </c>
       <c r="F696" t="s">
         <v>713</v>
@@ -18191,10 +18191,10 @@
         <v>998</v>
       </c>
       <c r="D697" t="s">
+        <v>967</v>
+      </c>
+      <c r="E697" t="s">
         <v>999</v>
-      </c>
-      <c r="E697" t="s">
-        <v>968</v>
       </c>
       <c r="F697" t="s">
         <v>24</v>
@@ -18211,10 +18211,10 @@
         <v>1001</v>
       </c>
       <c r="D698" t="s">
+        <v>967</v>
+      </c>
+      <c r="E698" t="s">
         <v>1002</v>
-      </c>
-      <c r="E698" t="s">
-        <v>968</v>
       </c>
       <c r="F698" t="s">
         <v>24</v>
@@ -18231,10 +18231,10 @@
         <v>973</v>
       </c>
       <c r="D699" t="s">
+        <v>967</v>
+      </c>
+      <c r="E699" t="s">
         <v>974</v>
-      </c>
-      <c r="E699" t="s">
-        <v>968</v>
       </c>
       <c r="F699" t="s">
         <v>16</v>
@@ -18251,10 +18251,10 @@
         <v>1005</v>
       </c>
       <c r="D700" t="s">
+        <v>967</v>
+      </c>
+      <c r="E700" t="s">
         <v>1006</v>
-      </c>
-      <c r="E700" t="s">
-        <v>968</v>
       </c>
       <c r="F700" t="s">
         <v>24</v>
@@ -18271,10 +18271,10 @@
         <v>973</v>
       </c>
       <c r="D701" t="s">
+        <v>967</v>
+      </c>
+      <c r="E701" t="s">
         <v>974</v>
-      </c>
-      <c r="E701" t="s">
-        <v>968</v>
       </c>
       <c r="F701" t="s">
         <v>16</v>
@@ -18291,10 +18291,10 @@
         <v>1009</v>
       </c>
       <c r="D702" t="s">
+        <v>967</v>
+      </c>
+      <c r="E702" t="s">
         <v>1010</v>
-      </c>
-      <c r="E702" t="s">
-        <v>968</v>
       </c>
       <c r="F702" t="s">
         <v>24</v>
@@ -18311,10 +18311,10 @@
         <v>1005</v>
       </c>
       <c r="D703" t="s">
+        <v>967</v>
+      </c>
+      <c r="E703" t="s">
         <v>1012</v>
-      </c>
-      <c r="E703" t="s">
-        <v>968</v>
       </c>
       <c r="F703" t="s">
         <v>24</v>
@@ -18331,10 +18331,10 @@
         <v>973</v>
       </c>
       <c r="D704" t="s">
+        <v>967</v>
+      </c>
+      <c r="E704" t="s">
         <v>974</v>
-      </c>
-      <c r="E704" t="s">
-        <v>968</v>
       </c>
       <c r="F704" t="s">
         <v>713</v>
@@ -18351,10 +18351,10 @@
         <v>1001</v>
       </c>
       <c r="D705" t="s">
+        <v>967</v>
+      </c>
+      <c r="E705" t="s">
         <v>1015</v>
-      </c>
-      <c r="E705" t="s">
-        <v>968</v>
       </c>
       <c r="F705" t="s">
         <v>16</v>
@@ -18371,10 +18371,10 @@
         <v>973</v>
       </c>
       <c r="D706" t="s">
+        <v>967</v>
+      </c>
+      <c r="E706" t="s">
         <v>974</v>
-      </c>
-      <c r="E706" t="s">
-        <v>968</v>
       </c>
       <c r="F706" t="s">
         <v>713</v>
@@ -18391,10 +18391,10 @@
         <v>1001</v>
       </c>
       <c r="D707" t="s">
+        <v>967</v>
+      </c>
+      <c r="E707" t="s">
         <v>974</v>
-      </c>
-      <c r="E707" t="s">
-        <v>968</v>
       </c>
       <c r="F707" t="s">
         <v>16</v>
@@ -18411,10 +18411,10 @@
         <v>970</v>
       </c>
       <c r="D708" t="s">
+        <v>967</v>
+      </c>
+      <c r="E708" t="s">
         <v>1019</v>
-      </c>
-      <c r="E708" t="s">
-        <v>968</v>
       </c>
       <c r="F708" t="s">
         <v>24</v>
@@ -18431,10 +18431,10 @@
         <v>973</v>
       </c>
       <c r="D709" t="s">
+        <v>967</v>
+      </c>
+      <c r="E709" t="s">
         <v>974</v>
-      </c>
-      <c r="E709" t="s">
-        <v>968</v>
       </c>
       <c r="F709" t="s">
         <v>713</v>
@@ -18451,10 +18451,10 @@
         <v>1022</v>
       </c>
       <c r="D710" t="s">
+        <v>967</v>
+      </c>
+      <c r="E710" t="s">
         <v>1023</v>
-      </c>
-      <c r="E710" t="s">
-        <v>968</v>
       </c>
       <c r="F710" t="s">
         <v>24</v>
@@ -18471,10 +18471,10 @@
         <v>1001</v>
       </c>
       <c r="D711" t="s">
+        <v>967</v>
+      </c>
+      <c r="E711" t="s">
         <v>974</v>
-      </c>
-      <c r="E711" t="s">
-        <v>968</v>
       </c>
       <c r="F711" t="s">
         <v>713</v>
@@ -18491,10 +18491,10 @@
         <v>973</v>
       </c>
       <c r="D712" t="s">
+        <v>967</v>
+      </c>
+      <c r="E712" t="s">
         <v>974</v>
-      </c>
-      <c r="E712" t="s">
-        <v>968</v>
       </c>
       <c r="F712" t="s">
         <v>713</v>
@@ -18511,10 +18511,10 @@
         <v>982</v>
       </c>
       <c r="D713" t="s">
+        <v>967</v>
+      </c>
+      <c r="E713" t="s">
         <v>983</v>
-      </c>
-      <c r="E713" t="s">
-        <v>968</v>
       </c>
       <c r="F713" t="s">
         <v>24</v>
@@ -18531,10 +18531,10 @@
         <v>973</v>
       </c>
       <c r="D714" t="s">
+        <v>967</v>
+      </c>
+      <c r="E714" t="s">
         <v>974</v>
-      </c>
-      <c r="E714" t="s">
-        <v>968</v>
       </c>
       <c r="F714" t="s">
         <v>713</v>
@@ -18551,10 +18551,10 @@
         <v>1001</v>
       </c>
       <c r="D715" t="s">
+        <v>967</v>
+      </c>
+      <c r="E715" t="s">
         <v>999</v>
-      </c>
-      <c r="E715" t="s">
-        <v>968</v>
       </c>
       <c r="F715" t="s">
         <v>24</v>
@@ -18571,10 +18571,10 @@
         <v>973</v>
       </c>
       <c r="D716" t="s">
+        <v>967</v>
+      </c>
+      <c r="E716" t="s">
         <v>974</v>
-      </c>
-      <c r="E716" t="s">
-        <v>968</v>
       </c>
       <c r="F716" t="s">
         <v>713</v>
@@ -18591,10 +18591,10 @@
         <v>973</v>
       </c>
       <c r="D717" t="s">
+        <v>967</v>
+      </c>
+      <c r="E717" t="s">
         <v>974</v>
-      </c>
-      <c r="E717" t="s">
-        <v>968</v>
       </c>
       <c r="F717" t="s">
         <v>713</v>
@@ -18631,10 +18631,10 @@
         <v>1032</v>
       </c>
       <c r="D719" t="s">
+        <v>1033</v>
+      </c>
+      <c r="E719" t="s">
         <v>1036</v>
-      </c>
-      <c r="E719" t="s">
-        <v>1034</v>
       </c>
       <c r="F719" t="s">
         <v>713</v>
@@ -18651,10 +18651,10 @@
         <v>1032</v>
       </c>
       <c r="D720" t="s">
+        <v>1033</v>
+      </c>
+      <c r="E720" t="s">
         <v>1036</v>
-      </c>
-      <c r="E720" t="s">
-        <v>1034</v>
       </c>
       <c r="F720" t="s">
         <v>713</v>
@@ -18671,10 +18671,10 @@
         <v>1032</v>
       </c>
       <c r="D721" t="s">
+        <v>1033</v>
+      </c>
+      <c r="E721" t="s">
         <v>1036</v>
-      </c>
-      <c r="E721" t="s">
-        <v>1034</v>
       </c>
       <c r="F721" t="s">
         <v>713</v>
@@ -18691,10 +18691,10 @@
         <v>1032</v>
       </c>
       <c r="D722" t="s">
+        <v>1033</v>
+      </c>
+      <c r="E722" t="s">
         <v>1036</v>
-      </c>
-      <c r="E722" t="s">
-        <v>1034</v>
       </c>
       <c r="F722" t="s">
         <v>713</v>
@@ -18711,10 +18711,10 @@
         <v>1032</v>
       </c>
       <c r="D723" t="s">
+        <v>1033</v>
+      </c>
+      <c r="E723" t="s">
         <v>1036</v>
-      </c>
-      <c r="E723" t="s">
-        <v>1034</v>
       </c>
       <c r="F723" t="s">
         <v>713</v>
@@ -18731,10 +18731,10 @@
         <v>1032</v>
       </c>
       <c r="D724" t="s">
+        <v>1033</v>
+      </c>
+      <c r="E724" t="s">
         <v>1036</v>
-      </c>
-      <c r="E724" t="s">
-        <v>1034</v>
       </c>
       <c r="F724" t="s">
         <v>16</v>
@@ -18751,10 +18751,10 @@
         <v>1043</v>
       </c>
       <c r="D725" t="s">
+        <v>1033</v>
+      </c>
+      <c r="E725" t="s">
         <v>1044</v>
-      </c>
-      <c r="E725" t="s">
-        <v>1034</v>
       </c>
       <c r="F725" t="s">
         <v>16</v>
@@ -18771,10 +18771,10 @@
         <v>1046</v>
       </c>
       <c r="D726" t="s">
+        <v>1033</v>
+      </c>
+      <c r="E726" t="s">
         <v>1047</v>
-      </c>
-      <c r="E726" t="s">
-        <v>1034</v>
       </c>
       <c r="F726" t="s">
         <v>16</v>
@@ -18791,10 +18791,10 @@
         <v>1032</v>
       </c>
       <c r="D727" t="s">
+        <v>1033</v>
+      </c>
+      <c r="E727" t="s">
         <v>1036</v>
-      </c>
-      <c r="E727" t="s">
-        <v>1034</v>
       </c>
       <c r="F727" t="s">
         <v>713</v>
@@ -18811,10 +18811,10 @@
         <v>1032</v>
       </c>
       <c r="D728" t="s">
+        <v>1033</v>
+      </c>
+      <c r="E728" t="s">
         <v>1036</v>
-      </c>
-      <c r="E728" t="s">
-        <v>1034</v>
       </c>
       <c r="F728" t="s">
         <v>713</v>
@@ -18831,10 +18831,10 @@
         <v>1051</v>
       </c>
       <c r="D729" t="s">
+        <v>1033</v>
+      </c>
+      <c r="E729" t="s">
         <v>1052</v>
-      </c>
-      <c r="E729" t="s">
-        <v>1034</v>
       </c>
       <c r="F729" t="s">
         <v>24</v>
@@ -18851,10 +18851,10 @@
         <v>1032</v>
       </c>
       <c r="D730" t="s">
+        <v>1033</v>
+      </c>
+      <c r="E730" t="s">
         <v>1036</v>
-      </c>
-      <c r="E730" t="s">
-        <v>1034</v>
       </c>
       <c r="F730" t="s">
         <v>13</v>
@@ -18871,10 +18871,10 @@
         <v>1051</v>
       </c>
       <c r="D731" t="s">
+        <v>1033</v>
+      </c>
+      <c r="E731" t="s">
         <v>1052</v>
-      </c>
-      <c r="E731" t="s">
-        <v>1034</v>
       </c>
       <c r="F731" t="s">
         <v>24</v>
@@ -18891,10 +18891,10 @@
         <v>1056</v>
       </c>
       <c r="D732" t="s">
+        <v>1033</v>
+      </c>
+      <c r="E732" t="s">
         <v>1057</v>
-      </c>
-      <c r="E732" t="s">
-        <v>1034</v>
       </c>
       <c r="F732" t="s">
         <v>24</v>
@@ -18911,10 +18911,10 @@
         <v>1032</v>
       </c>
       <c r="D733" t="s">
+        <v>1033</v>
+      </c>
+      <c r="E733" t="s">
         <v>1059</v>
-      </c>
-      <c r="E733" t="s">
-        <v>1034</v>
       </c>
       <c r="F733" t="s">
         <v>24</v>
@@ -18931,10 +18931,10 @@
         <v>1061</v>
       </c>
       <c r="D734" t="s">
+        <v>1033</v>
+      </c>
+      <c r="E734" t="s">
         <v>1062</v>
-      </c>
-      <c r="E734" t="s">
-        <v>1034</v>
       </c>
       <c r="F734" t="s">
         <v>24</v>
@@ -18951,10 +18951,10 @@
         <v>1032</v>
       </c>
       <c r="D735" t="s">
+        <v>1033</v>
+      </c>
+      <c r="E735" t="s">
         <v>1036</v>
-      </c>
-      <c r="E735" t="s">
-        <v>1034</v>
       </c>
       <c r="F735" t="s">
         <v>713</v>
@@ -18971,10 +18971,10 @@
         <v>1032</v>
       </c>
       <c r="D736" t="s">
+        <v>1033</v>
+      </c>
+      <c r="E736" t="s">
         <v>1065</v>
-      </c>
-      <c r="E736" t="s">
-        <v>1034</v>
       </c>
       <c r="F736" t="s">
         <v>713</v>
@@ -18991,10 +18991,10 @@
         <v>1032</v>
       </c>
       <c r="D737" t="s">
+        <v>1033</v>
+      </c>
+      <c r="E737" t="s">
         <v>1036</v>
-      </c>
-      <c r="E737" t="s">
-        <v>1034</v>
       </c>
       <c r="F737" t="s">
         <v>16</v>
@@ -19011,10 +19011,10 @@
         <v>973</v>
       </c>
       <c r="D738" t="s">
+        <v>1033</v>
+      </c>
+      <c r="E738" t="s">
         <v>1068</v>
-      </c>
-      <c r="E738" t="s">
-        <v>1034</v>
       </c>
       <c r="F738" t="s">
         <v>16</v>
@@ -19031,10 +19031,10 @@
         <v>1032</v>
       </c>
       <c r="D739" t="s">
+        <v>1033</v>
+      </c>
+      <c r="E739" t="s">
         <v>1036</v>
-      </c>
-      <c r="E739" t="s">
-        <v>1034</v>
       </c>
       <c r="F739" t="s">
         <v>713</v>
@@ -19051,10 +19051,10 @@
         <v>1032</v>
       </c>
       <c r="D740" t="s">
+        <v>1033</v>
+      </c>
+      <c r="E740" t="s">
         <v>1036</v>
-      </c>
-      <c r="E740" t="s">
-        <v>1034</v>
       </c>
       <c r="F740" t="s">
         <v>713</v>
@@ -19071,10 +19071,10 @@
         <v>1072</v>
       </c>
       <c r="D741" t="s">
+        <v>1033</v>
+      </c>
+      <c r="E741" t="s">
         <v>1073</v>
-      </c>
-      <c r="E741" t="s">
-        <v>1034</v>
       </c>
       <c r="F741" t="s">
         <v>24</v>
@@ -19091,10 +19091,10 @@
         <v>1032</v>
       </c>
       <c r="D742" t="s">
+        <v>1033</v>
+      </c>
+      <c r="E742" t="s">
         <v>1075</v>
-      </c>
-      <c r="E742" t="s">
-        <v>1034</v>
       </c>
       <c r="F742" t="s">
         <v>16</v>
@@ -19111,10 +19111,10 @@
         <v>1032</v>
       </c>
       <c r="D743" t="s">
+        <v>1033</v>
+      </c>
+      <c r="E743" t="s">
         <v>1036</v>
-      </c>
-      <c r="E743" t="s">
-        <v>1034</v>
       </c>
       <c r="F743" t="s">
         <v>713</v>
@@ -19151,10 +19151,10 @@
         <v>1032</v>
       </c>
       <c r="D745" t="s">
+        <v>1033</v>
+      </c>
+      <c r="E745" t="s">
         <v>1079</v>
-      </c>
-      <c r="E745" t="s">
-        <v>1034</v>
       </c>
       <c r="F745" t="s">
         <v>24</v>
@@ -19171,10 +19171,10 @@
         <v>1032</v>
       </c>
       <c r="D746" t="s">
+        <v>1033</v>
+      </c>
+      <c r="E746" t="s">
         <v>1036</v>
-      </c>
-      <c r="E746" t="s">
-        <v>1034</v>
       </c>
       <c r="F746" t="s">
         <v>713</v>
@@ -19191,10 +19191,10 @@
         <v>1032</v>
       </c>
       <c r="D747" t="s">
+        <v>1033</v>
+      </c>
+      <c r="E747" t="s">
         <v>1036</v>
-      </c>
-      <c r="E747" t="s">
-        <v>1034</v>
       </c>
       <c r="F747" t="s">
         <v>713</v>
@@ -19211,10 +19211,10 @@
         <v>1032</v>
       </c>
       <c r="D748" t="s">
+        <v>1033</v>
+      </c>
+      <c r="E748" t="s">
         <v>1036</v>
-      </c>
-      <c r="E748" t="s">
-        <v>1034</v>
       </c>
       <c r="F748" t="s">
         <v>713</v>
@@ -19231,10 +19231,10 @@
         <v>1032</v>
       </c>
       <c r="D749" t="s">
+        <v>1033</v>
+      </c>
+      <c r="E749" t="s">
         <v>1036</v>
-      </c>
-      <c r="E749" t="s">
-        <v>1034</v>
       </c>
       <c r="F749" t="s">
         <v>713</v>
@@ -19271,10 +19271,10 @@
         <v>1089</v>
       </c>
       <c r="D751" t="s">
+        <v>1086</v>
+      </c>
+      <c r="E751" t="s">
         <v>1090</v>
-      </c>
-      <c r="E751" t="s">
-        <v>1087</v>
       </c>
       <c r="F751" t="s">
         <v>24</v>
@@ -19291,10 +19291,10 @@
         <v>1092</v>
       </c>
       <c r="D752" t="s">
+        <v>1086</v>
+      </c>
+      <c r="E752" t="s">
         <v>1093</v>
-      </c>
-      <c r="E752" t="s">
-        <v>1087</v>
       </c>
       <c r="F752" t="s">
         <v>713</v>
@@ -19311,10 +19311,10 @@
         <v>1092</v>
       </c>
       <c r="D753" t="s">
+        <v>1086</v>
+      </c>
+      <c r="E753" t="s">
         <v>1093</v>
-      </c>
-      <c r="E753" t="s">
-        <v>1087</v>
       </c>
       <c r="F753" t="s">
         <v>713</v>
@@ -19331,10 +19331,10 @@
         <v>1092</v>
       </c>
       <c r="D754" t="s">
+        <v>1086</v>
+      </c>
+      <c r="E754" t="s">
         <v>1093</v>
-      </c>
-      <c r="E754" t="s">
-        <v>1087</v>
       </c>
       <c r="F754" t="s">
         <v>713</v>
@@ -19351,10 +19351,10 @@
         <v>1092</v>
       </c>
       <c r="D755" t="s">
+        <v>1086</v>
+      </c>
+      <c r="E755" t="s">
         <v>1093</v>
-      </c>
-      <c r="E755" t="s">
-        <v>1087</v>
       </c>
       <c r="F755" t="s">
         <v>713</v>
@@ -19371,10 +19371,10 @@
         <v>1092</v>
       </c>
       <c r="D756" t="s">
+        <v>1086</v>
+      </c>
+      <c r="E756" t="s">
         <v>1093</v>
-      </c>
-      <c r="E756" t="s">
-        <v>1087</v>
       </c>
       <c r="F756" t="s">
         <v>713</v>
@@ -19391,10 +19391,10 @@
         <v>1092</v>
       </c>
       <c r="D757" t="s">
+        <v>1086</v>
+      </c>
+      <c r="E757" t="s">
         <v>1093</v>
-      </c>
-      <c r="E757" t="s">
-        <v>1087</v>
       </c>
       <c r="F757" t="s">
         <v>713</v>
@@ -19431,10 +19431,10 @@
         <v>1092</v>
       </c>
       <c r="D759" t="s">
+        <v>1086</v>
+      </c>
+      <c r="E759" t="s">
         <v>1065</v>
-      </c>
-      <c r="E759" t="s">
-        <v>1087</v>
       </c>
       <c r="F759" t="s">
         <v>16</v>
@@ -19451,10 +19451,10 @@
         <v>1092</v>
       </c>
       <c r="D760" t="s">
+        <v>1086</v>
+      </c>
+      <c r="E760" t="s">
         <v>1093</v>
-      </c>
-      <c r="E760" t="s">
-        <v>1087</v>
       </c>
       <c r="F760" t="s">
         <v>713</v>
@@ -19471,10 +19471,10 @@
         <v>1092</v>
       </c>
       <c r="D761" t="s">
+        <v>1086</v>
+      </c>
+      <c r="E761" t="s">
         <v>1093</v>
-      </c>
-      <c r="E761" t="s">
-        <v>1087</v>
       </c>
       <c r="F761" t="s">
         <v>713</v>
@@ -19491,10 +19491,10 @@
         <v>1104</v>
       </c>
       <c r="D762" t="s">
+        <v>1086</v>
+      </c>
+      <c r="E762" t="s">
         <v>1065</v>
-      </c>
-      <c r="E762" t="s">
-        <v>1087</v>
       </c>
       <c r="F762" t="s">
         <v>24</v>
@@ -19511,10 +19511,10 @@
         <v>1092</v>
       </c>
       <c r="D763" t="s">
+        <v>1086</v>
+      </c>
+      <c r="E763" t="s">
         <v>1093</v>
-      </c>
-      <c r="E763" t="s">
-        <v>1087</v>
       </c>
       <c r="F763" t="s">
         <v>713</v>
@@ -19531,10 +19531,10 @@
         <v>1107</v>
       </c>
       <c r="D764" t="s">
+        <v>1086</v>
+      </c>
+      <c r="E764" t="s">
         <v>1108</v>
-      </c>
-      <c r="E764" t="s">
-        <v>1087</v>
       </c>
       <c r="F764" t="s">
         <v>24</v>
@@ -19551,10 +19551,10 @@
         <v>1085</v>
       </c>
       <c r="D765" t="s">
+        <v>1086</v>
+      </c>
+      <c r="E765" t="s">
         <v>1093</v>
-      </c>
-      <c r="E765" t="s">
-        <v>1087</v>
       </c>
       <c r="F765" t="s">
         <v>24</v>
@@ -19571,10 +19571,10 @@
         <v>1104</v>
       </c>
       <c r="D766" t="s">
+        <v>1086</v>
+      </c>
+      <c r="E766" t="s">
         <v>1111</v>
-      </c>
-      <c r="E766" t="s">
-        <v>1087</v>
       </c>
       <c r="F766" t="s">
         <v>24</v>
@@ -19591,10 +19591,10 @@
         <v>1113</v>
       </c>
       <c r="D767" t="s">
+        <v>1086</v>
+      </c>
+      <c r="E767" t="s">
         <v>1114</v>
-      </c>
-      <c r="E767" t="s">
-        <v>1087</v>
       </c>
       <c r="F767" t="s">
         <v>24</v>
@@ -19611,10 +19611,10 @@
         <v>1092</v>
       </c>
       <c r="D768" t="s">
+        <v>1086</v>
+      </c>
+      <c r="E768" t="s">
         <v>1093</v>
-      </c>
-      <c r="E768" t="s">
-        <v>1087</v>
       </c>
       <c r="F768" t="s">
         <v>713</v>
@@ -19631,10 +19631,10 @@
         <v>1092</v>
       </c>
       <c r="D769" t="s">
+        <v>1086</v>
+      </c>
+      <c r="E769" t="s">
         <v>1093</v>
-      </c>
-      <c r="E769" t="s">
-        <v>1087</v>
       </c>
       <c r="F769" t="s">
         <v>713</v>
@@ -19651,10 +19651,10 @@
         <v>1118</v>
       </c>
       <c r="D770" t="s">
+        <v>1086</v>
+      </c>
+      <c r="E770" t="s">
         <v>1119</v>
-      </c>
-      <c r="E770" t="s">
-        <v>1087</v>
       </c>
       <c r="F770" t="s">
         <v>24</v>
@@ -19671,10 +19671,10 @@
         <v>1092</v>
       </c>
       <c r="D771" t="s">
+        <v>1086</v>
+      </c>
+      <c r="E771" t="s">
         <v>1093</v>
-      </c>
-      <c r="E771" t="s">
-        <v>1087</v>
       </c>
       <c r="F771" t="s">
         <v>713</v>
@@ -19691,10 +19691,10 @@
         <v>1092</v>
       </c>
       <c r="D772" t="s">
+        <v>1086</v>
+      </c>
+      <c r="E772" t="s">
         <v>1093</v>
-      </c>
-      <c r="E772" t="s">
-        <v>1087</v>
       </c>
       <c r="F772" t="s">
         <v>713</v>
@@ -19711,10 +19711,10 @@
         <v>1092</v>
       </c>
       <c r="D773" t="s">
+        <v>1086</v>
+      </c>
+      <c r="E773" t="s">
         <v>1093</v>
-      </c>
-      <c r="E773" t="s">
-        <v>1087</v>
       </c>
       <c r="F773" t="s">
         <v>713</v>
@@ -19731,10 +19731,10 @@
         <v>1124</v>
       </c>
       <c r="D774" t="s">
+        <v>1086</v>
+      </c>
+      <c r="E774" t="s">
         <v>1125</v>
-      </c>
-      <c r="E774" t="s">
-        <v>1087</v>
       </c>
       <c r="F774" t="s">
         <v>24</v>
@@ -19751,10 +19751,10 @@
         <v>1092</v>
       </c>
       <c r="D775" t="s">
+        <v>1086</v>
+      </c>
+      <c r="E775" t="s">
         <v>1093</v>
-      </c>
-      <c r="E775" t="s">
-        <v>1087</v>
       </c>
       <c r="F775" t="s">
         <v>713</v>
@@ -19791,10 +19791,10 @@
         <v>1128</v>
       </c>
       <c r="D777" t="s">
+        <v>1129</v>
+      </c>
+      <c r="E777" t="s">
         <v>1132</v>
-      </c>
-      <c r="E777" t="s">
-        <v>1130</v>
       </c>
       <c r="F777" t="s">
         <v>713</v>
@@ -19811,10 +19811,10 @@
         <v>1134</v>
       </c>
       <c r="D778" t="s">
+        <v>1129</v>
+      </c>
+      <c r="E778" t="s">
         <v>1135</v>
-      </c>
-      <c r="E778" t="s">
-        <v>1130</v>
       </c>
       <c r="F778" t="s">
         <v>24</v>
@@ -19831,10 +19831,10 @@
         <v>1137</v>
       </c>
       <c r="D779" t="s">
+        <v>1129</v>
+      </c>
+      <c r="E779" t="s">
         <v>1138</v>
-      </c>
-      <c r="E779" t="s">
-        <v>1130</v>
       </c>
       <c r="F779" t="s">
         <v>24</v>
@@ -19851,10 +19851,10 @@
         <v>1128</v>
       </c>
       <c r="D780" t="s">
+        <v>1129</v>
+      </c>
+      <c r="E780" t="s">
         <v>1132</v>
-      </c>
-      <c r="E780" t="s">
-        <v>1130</v>
       </c>
       <c r="F780" t="s">
         <v>713</v>
@@ -19871,10 +19871,10 @@
         <v>1128</v>
       </c>
       <c r="D781" t="s">
+        <v>1129</v>
+      </c>
+      <c r="E781" t="s">
         <v>1132</v>
-      </c>
-      <c r="E781" t="s">
-        <v>1130</v>
       </c>
       <c r="F781" t="s">
         <v>713</v>
@@ -19891,10 +19891,10 @@
         <v>1128</v>
       </c>
       <c r="D782" t="s">
+        <v>1129</v>
+      </c>
+      <c r="E782" t="s">
         <v>1142</v>
-      </c>
-      <c r="E782" t="s">
-        <v>1130</v>
       </c>
       <c r="F782" t="s">
         <v>713</v>
@@ -19911,10 +19911,10 @@
         <v>1128</v>
       </c>
       <c r="D783" t="s">
+        <v>1129</v>
+      </c>
+      <c r="E783" t="s">
         <v>1132</v>
-      </c>
-      <c r="E783" t="s">
-        <v>1130</v>
       </c>
       <c r="F783" t="s">
         <v>713</v>
@@ -19931,10 +19931,10 @@
         <v>1128</v>
       </c>
       <c r="D784" t="s">
+        <v>1129</v>
+      </c>
+      <c r="E784" t="s">
         <v>1132</v>
-      </c>
-      <c r="E784" t="s">
-        <v>1130</v>
       </c>
       <c r="F784" t="s">
         <v>713</v>
@@ -19951,10 +19951,10 @@
         <v>1128</v>
       </c>
       <c r="D785" t="s">
+        <v>1129</v>
+      </c>
+      <c r="E785" t="s">
         <v>1132</v>
-      </c>
-      <c r="E785" t="s">
-        <v>1130</v>
       </c>
       <c r="F785" t="s">
         <v>713</v>
@@ -19971,10 +19971,10 @@
         <v>1128</v>
       </c>
       <c r="D786" t="s">
+        <v>1129</v>
+      </c>
+      <c r="E786" t="s">
         <v>1132</v>
-      </c>
-      <c r="E786" t="s">
-        <v>1130</v>
       </c>
       <c r="F786" t="s">
         <v>713</v>
@@ -19991,10 +19991,10 @@
         <v>1128</v>
       </c>
       <c r="D787" t="s">
+        <v>1129</v>
+      </c>
+      <c r="E787" t="s">
         <v>1132</v>
-      </c>
-      <c r="E787" t="s">
-        <v>1130</v>
       </c>
       <c r="F787" t="s">
         <v>713</v>
@@ -20011,10 +20011,10 @@
         <v>1128</v>
       </c>
       <c r="D788" t="s">
+        <v>1129</v>
+      </c>
+      <c r="E788" t="s">
         <v>1132</v>
-      </c>
-      <c r="E788" t="s">
-        <v>1130</v>
       </c>
       <c r="F788" t="s">
         <v>713</v>
@@ -20051,10 +20051,10 @@
         <v>1128</v>
       </c>
       <c r="D790" t="s">
+        <v>1129</v>
+      </c>
+      <c r="E790" t="s">
         <v>1132</v>
-      </c>
-      <c r="E790" t="s">
-        <v>1130</v>
       </c>
       <c r="F790" t="s">
         <v>713</v>
@@ -20071,10 +20071,10 @@
         <v>1153</v>
       </c>
       <c r="D791" t="s">
+        <v>1129</v>
+      </c>
+      <c r="E791" t="s">
         <v>1142</v>
-      </c>
-      <c r="E791" t="s">
-        <v>1130</v>
       </c>
       <c r="F791" t="s">
         <v>24</v>
@@ -20091,10 +20091,10 @@
         <v>1150</v>
       </c>
       <c r="D792" t="s">
+        <v>1129</v>
+      </c>
+      <c r="E792" t="s">
         <v>1155</v>
-      </c>
-      <c r="E792" t="s">
-        <v>1130</v>
       </c>
       <c r="F792" t="s">
         <v>24</v>
@@ -20111,10 +20111,10 @@
         <v>1128</v>
       </c>
       <c r="D793" t="s">
+        <v>1129</v>
+      </c>
+      <c r="E793" t="s">
         <v>1132</v>
-      </c>
-      <c r="E793" t="s">
-        <v>1130</v>
       </c>
       <c r="F793" t="s">
         <v>713</v>
@@ -20131,10 +20131,10 @@
         <v>1158</v>
       </c>
       <c r="D794" t="s">
+        <v>1129</v>
+      </c>
+      <c r="E794" t="s">
         <v>1132</v>
-      </c>
-      <c r="E794" t="s">
-        <v>1130</v>
       </c>
       <c r="F794" t="s">
         <v>24</v>
@@ -20151,10 +20151,10 @@
         <v>1128</v>
       </c>
       <c r="D795" t="s">
+        <v>1129</v>
+      </c>
+      <c r="E795" t="s">
         <v>1160</v>
-      </c>
-      <c r="E795" t="s">
-        <v>1130</v>
       </c>
       <c r="F795" t="s">
         <v>24</v>
@@ -20171,10 +20171,10 @@
         <v>1128</v>
       </c>
       <c r="D796" t="s">
+        <v>1129</v>
+      </c>
+      <c r="E796" t="s">
         <v>1132</v>
-      </c>
-      <c r="E796" t="s">
-        <v>1130</v>
       </c>
       <c r="F796" t="s">
         <v>713</v>
@@ -20191,10 +20191,10 @@
         <v>1163</v>
       </c>
       <c r="D797" t="s">
+        <v>1129</v>
+      </c>
+      <c r="E797" t="s">
         <v>1164</v>
-      </c>
-      <c r="E797" t="s">
-        <v>1130</v>
       </c>
       <c r="F797" t="s">
         <v>24</v>
@@ -20211,10 +20211,10 @@
         <v>1166</v>
       </c>
       <c r="D798" t="s">
+        <v>1129</v>
+      </c>
+      <c r="E798" t="s">
         <v>1167</v>
-      </c>
-      <c r="E798" t="s">
-        <v>1130</v>
       </c>
       <c r="F798" t="s">
         <v>24</v>
@@ -20231,10 +20231,10 @@
         <v>1128</v>
       </c>
       <c r="D799" t="s">
+        <v>1129</v>
+      </c>
+      <c r="E799" t="s">
         <v>1132</v>
-      </c>
-      <c r="E799" t="s">
-        <v>1130</v>
       </c>
       <c r="F799" t="s">
         <v>713</v>
@@ -20251,10 +20251,10 @@
         <v>1128</v>
       </c>
       <c r="D800" t="s">
+        <v>1129</v>
+      </c>
+      <c r="E800" t="s">
         <v>1132</v>
-      </c>
-      <c r="E800" t="s">
-        <v>1130</v>
       </c>
       <c r="F800" t="s">
         <v>713</v>
@@ -20271,10 +20271,10 @@
         <v>1128</v>
       </c>
       <c r="D801" t="s">
+        <v>1129</v>
+      </c>
+      <c r="E801" t="s">
         <v>1132</v>
-      </c>
-      <c r="E801" t="s">
-        <v>1130</v>
       </c>
       <c r="F801" t="s">
         <v>713</v>
@@ -20291,10 +20291,10 @@
         <v>1128</v>
       </c>
       <c r="D802" t="s">
+        <v>1129</v>
+      </c>
+      <c r="E802" t="s">
         <v>1132</v>
-      </c>
-      <c r="E802" t="s">
-        <v>1130</v>
       </c>
       <c r="F802" t="s">
         <v>713</v>
@@ -20311,10 +20311,10 @@
         <v>1128</v>
       </c>
       <c r="D803" t="s">
+        <v>1129</v>
+      </c>
+      <c r="E803" t="s">
         <v>1132</v>
-      </c>
-      <c r="E803" t="s">
-        <v>1130</v>
       </c>
       <c r="F803" t="s">
         <v>713</v>
@@ -20331,10 +20331,10 @@
         <v>1128</v>
       </c>
       <c r="D804" t="s">
+        <v>1129</v>
+      </c>
+      <c r="E804" t="s">
         <v>1132</v>
-      </c>
-      <c r="E804" t="s">
-        <v>1130</v>
       </c>
       <c r="F804" t="s">
         <v>713</v>
@@ -20351,10 +20351,10 @@
         <v>1128</v>
       </c>
       <c r="D805" t="s">
+        <v>1129</v>
+      </c>
+      <c r="E805" t="s">
         <v>1132</v>
-      </c>
-      <c r="E805" t="s">
-        <v>1130</v>
       </c>
       <c r="F805" t="s">
         <v>713</v>
@@ -20371,10 +20371,10 @@
         <v>1128</v>
       </c>
       <c r="D806" t="s">
+        <v>1129</v>
+      </c>
+      <c r="E806" t="s">
         <v>1132</v>
-      </c>
-      <c r="E806" t="s">
-        <v>1130</v>
       </c>
       <c r="F806" t="s">
         <v>713</v>
@@ -20391,10 +20391,10 @@
         <v>1128</v>
       </c>
       <c r="D807" t="s">
+        <v>1129</v>
+      </c>
+      <c r="E807" t="s">
         <v>1132</v>
-      </c>
-      <c r="E807" t="s">
-        <v>1130</v>
       </c>
       <c r="F807" t="s">
         <v>713</v>
@@ -20471,10 +20471,10 @@
         <v>1184</v>
       </c>
       <c r="D811" t="s">
+        <v>1179</v>
+      </c>
+      <c r="E811" t="s">
         <v>1185</v>
-      </c>
-      <c r="E811" t="s">
-        <v>1180</v>
       </c>
       <c r="F811" t="s">
         <v>24</v>
@@ -20531,10 +20531,10 @@
         <v>1178</v>
       </c>
       <c r="D814" t="s">
+        <v>1179</v>
+      </c>
+      <c r="E814" t="s">
         <v>1185</v>
-      </c>
-      <c r="E814" t="s">
-        <v>1180</v>
       </c>
       <c r="F814" t="s">
         <v>713</v>
@@ -20551,10 +20551,10 @@
         <v>1190</v>
       </c>
       <c r="D815" t="s">
+        <v>1179</v>
+      </c>
+      <c r="E815" t="s">
         <v>1191</v>
-      </c>
-      <c r="E815" t="s">
-        <v>1180</v>
       </c>
       <c r="F815" t="s">
         <v>24</v>
@@ -20671,10 +20671,10 @@
         <v>1198</v>
       </c>
       <c r="D821" t="s">
+        <v>1179</v>
+      </c>
+      <c r="E821" t="s">
         <v>1199</v>
-      </c>
-      <c r="E821" t="s">
-        <v>1180</v>
       </c>
       <c r="F821" t="s">
         <v>16</v>
@@ -20691,10 +20691,10 @@
         <v>1201</v>
       </c>
       <c r="D822" t="s">
+        <v>1179</v>
+      </c>
+      <c r="E822" t="s">
         <v>1202</v>
-      </c>
-      <c r="E822" t="s">
-        <v>1180</v>
       </c>
       <c r="F822" t="s">
         <v>713</v>
@@ -20711,10 +20711,10 @@
         <v>1178</v>
       </c>
       <c r="D823" t="s">
+        <v>1179</v>
+      </c>
+      <c r="E823" t="s">
         <v>1202</v>
-      </c>
-      <c r="E823" t="s">
-        <v>1180</v>
       </c>
       <c r="F823" t="s">
         <v>713</v>
@@ -20731,10 +20731,10 @@
         <v>1201</v>
       </c>
       <c r="D824" t="s">
+        <v>1179</v>
+      </c>
+      <c r="E824" t="s">
         <v>1202</v>
-      </c>
-      <c r="E824" t="s">
-        <v>1180</v>
       </c>
       <c r="F824" t="s">
         <v>713</v>
@@ -20751,10 +20751,10 @@
         <v>1201</v>
       </c>
       <c r="D825" t="s">
+        <v>1179</v>
+      </c>
+      <c r="E825" t="s">
         <v>1202</v>
-      </c>
-      <c r="E825" t="s">
-        <v>1180</v>
       </c>
       <c r="F825" t="s">
         <v>713</v>
@@ -20771,10 +20771,10 @@
         <v>1201</v>
       </c>
       <c r="D826" t="s">
+        <v>1179</v>
+      </c>
+      <c r="E826" t="s">
         <v>1202</v>
-      </c>
-      <c r="E826" t="s">
-        <v>1180</v>
       </c>
       <c r="F826" t="s">
         <v>713</v>
@@ -20791,10 +20791,10 @@
         <v>1201</v>
       </c>
       <c r="D827" t="s">
+        <v>1179</v>
+      </c>
+      <c r="E827" t="s">
         <v>1202</v>
-      </c>
-      <c r="E827" t="s">
-        <v>1180</v>
       </c>
       <c r="F827" t="s">
         <v>713</v>
@@ -20811,10 +20811,10 @@
         <v>1178</v>
       </c>
       <c r="D828" t="s">
+        <v>1179</v>
+      </c>
+      <c r="E828" t="s">
         <v>1202</v>
-      </c>
-      <c r="E828" t="s">
-        <v>1180</v>
       </c>
       <c r="F828" t="s">
         <v>713</v>
@@ -20851,10 +20851,10 @@
         <v>1178</v>
       </c>
       <c r="D830" t="s">
+        <v>1179</v>
+      </c>
+      <c r="E830" t="s">
         <v>1185</v>
-      </c>
-      <c r="E830" t="s">
-        <v>1180</v>
       </c>
       <c r="F830" t="s">
         <v>713</v>
@@ -21051,10 +21051,10 @@
         <v>1220</v>
       </c>
       <c r="D840" t="s">
+        <v>1221</v>
+      </c>
+      <c r="E840" t="s">
         <v>1224</v>
-      </c>
-      <c r="E840" t="s">
-        <v>1222</v>
       </c>
       <c r="F840" t="s">
         <v>713</v>
@@ -21071,10 +21071,10 @@
         <v>1220</v>
       </c>
       <c r="D841" t="s">
+        <v>1221</v>
+      </c>
+      <c r="E841" t="s">
         <v>1224</v>
-      </c>
-      <c r="E841" t="s">
-        <v>1222</v>
       </c>
       <c r="F841" t="s">
         <v>713</v>
@@ -21091,10 +21091,10 @@
         <v>1220</v>
       </c>
       <c r="D842" t="s">
+        <v>1221</v>
+      </c>
+      <c r="E842" t="s">
         <v>1224</v>
-      </c>
-      <c r="E842" t="s">
-        <v>1222</v>
       </c>
       <c r="F842" t="s">
         <v>713</v>
@@ -21111,10 +21111,10 @@
         <v>1220</v>
       </c>
       <c r="D843" t="s">
+        <v>1221</v>
+      </c>
+      <c r="E843" t="s">
         <v>1224</v>
-      </c>
-      <c r="E843" t="s">
-        <v>1222</v>
       </c>
       <c r="F843" t="s">
         <v>713</v>
@@ -21131,10 +21131,10 @@
         <v>1220</v>
       </c>
       <c r="D844" t="s">
+        <v>1221</v>
+      </c>
+      <c r="E844" t="s">
         <v>1224</v>
-      </c>
-      <c r="E844" t="s">
-        <v>1222</v>
       </c>
       <c r="F844" t="s">
         <v>713</v>
@@ -21151,10 +21151,10 @@
         <v>1220</v>
       </c>
       <c r="D845" t="s">
+        <v>1221</v>
+      </c>
+      <c r="E845" t="s">
         <v>1224</v>
-      </c>
-      <c r="E845" t="s">
-        <v>1222</v>
       </c>
       <c r="F845" t="s">
         <v>713</v>
@@ -21171,10 +21171,10 @@
         <v>1220</v>
       </c>
       <c r="D846" t="s">
+        <v>1221</v>
+      </c>
+      <c r="E846" t="s">
         <v>1224</v>
-      </c>
-      <c r="E846" t="s">
-        <v>1222</v>
       </c>
       <c r="F846" t="s">
         <v>713</v>
@@ -21191,10 +21191,10 @@
         <v>1184</v>
       </c>
       <c r="D847" t="s">
+        <v>1221</v>
+      </c>
+      <c r="E847" t="s">
         <v>1232</v>
-      </c>
-      <c r="E847" t="s">
-        <v>1222</v>
       </c>
       <c r="F847" t="s">
         <v>713</v>
@@ -21211,10 +21211,10 @@
         <v>1184</v>
       </c>
       <c r="D848" t="s">
+        <v>1221</v>
+      </c>
+      <c r="E848" t="s">
         <v>1232</v>
-      </c>
-      <c r="E848" t="s">
-        <v>1222</v>
       </c>
       <c r="F848" t="s">
         <v>713</v>
@@ -21231,10 +21231,10 @@
         <v>1184</v>
       </c>
       <c r="D849" t="s">
+        <v>1221</v>
+      </c>
+      <c r="E849" t="s">
         <v>1232</v>
-      </c>
-      <c r="E849" t="s">
-        <v>1222</v>
       </c>
       <c r="F849" t="s">
         <v>713</v>
@@ -21251,10 +21251,10 @@
         <v>1236</v>
       </c>
       <c r="D850" t="s">
+        <v>1221</v>
+      </c>
+      <c r="E850" t="s">
         <v>1232</v>
-      </c>
-      <c r="E850" t="s">
-        <v>1222</v>
       </c>
       <c r="F850" t="s">
         <v>713</v>
@@ -21271,10 +21271,10 @@
         <v>1184</v>
       </c>
       <c r="D851" t="s">
+        <v>1221</v>
+      </c>
+      <c r="E851" t="s">
         <v>1232</v>
-      </c>
-      <c r="E851" t="s">
-        <v>1222</v>
       </c>
       <c r="F851" t="s">
         <v>713</v>
@@ -21291,10 +21291,10 @@
         <v>1184</v>
       </c>
       <c r="D852" t="s">
+        <v>1221</v>
+      </c>
+      <c r="E852" t="s">
         <v>1232</v>
-      </c>
-      <c r="E852" t="s">
-        <v>1222</v>
       </c>
       <c r="F852" t="s">
         <v>713</v>
@@ -21311,10 +21311,10 @@
         <v>1220</v>
       </c>
       <c r="D853" t="s">
+        <v>1221</v>
+      </c>
+      <c r="E853" t="s">
         <v>1224</v>
-      </c>
-      <c r="E853" t="s">
-        <v>1222</v>
       </c>
       <c r="F853" t="s">
         <v>713</v>
@@ -21331,10 +21331,10 @@
         <v>1220</v>
       </c>
       <c r="D854" t="s">
+        <v>1221</v>
+      </c>
+      <c r="E854" t="s">
         <v>1224</v>
-      </c>
-      <c r="E854" t="s">
-        <v>1222</v>
       </c>
       <c r="F854" t="s">
         <v>16</v>
@@ -21351,10 +21351,10 @@
         <v>1220</v>
       </c>
       <c r="D855" t="s">
+        <v>1221</v>
+      </c>
+      <c r="E855" t="s">
         <v>1224</v>
-      </c>
-      <c r="E855" t="s">
-        <v>1222</v>
       </c>
       <c r="F855" t="s">
         <v>16</v>
@@ -21371,10 +21371,10 @@
         <v>1220</v>
       </c>
       <c r="D856" t="s">
+        <v>1221</v>
+      </c>
+      <c r="E856" t="s">
         <v>1224</v>
-      </c>
-      <c r="E856" t="s">
-        <v>1222</v>
       </c>
       <c r="F856" t="s">
         <v>16</v>
@@ -21391,10 +21391,10 @@
         <v>1220</v>
       </c>
       <c r="D857" t="s">
+        <v>1221</v>
+      </c>
+      <c r="E857" t="s">
         <v>1224</v>
-      </c>
-      <c r="E857" t="s">
-        <v>1222</v>
       </c>
       <c r="F857" t="s">
         <v>713</v>
@@ -21411,10 +21411,10 @@
         <v>1220</v>
       </c>
       <c r="D858" t="s">
+        <v>1221</v>
+      </c>
+      <c r="E858" t="s">
         <v>1224</v>
-      </c>
-      <c r="E858" t="s">
-        <v>1222</v>
       </c>
       <c r="F858" t="s">
         <v>713</v>
@@ -21431,10 +21431,10 @@
         <v>1220</v>
       </c>
       <c r="D859" t="s">
+        <v>1221</v>
+      </c>
+      <c r="E859" t="s">
         <v>1224</v>
-      </c>
-      <c r="E859" t="s">
-        <v>1222</v>
       </c>
       <c r="F859" t="s">
         <v>16</v>
@@ -21451,10 +21451,10 @@
         <v>1220</v>
       </c>
       <c r="D860" t="s">
+        <v>1221</v>
+      </c>
+      <c r="E860" t="s">
         <v>1224</v>
-      </c>
-      <c r="E860" t="s">
-        <v>1222</v>
       </c>
       <c r="F860" t="s">
         <v>713</v>
@@ -21471,10 +21471,10 @@
         <v>1220</v>
       </c>
       <c r="D861" t="s">
+        <v>1221</v>
+      </c>
+      <c r="E861" t="s">
         <v>1224</v>
-      </c>
-      <c r="E861" t="s">
-        <v>1222</v>
       </c>
       <c r="F861" t="s">
         <v>713</v>
@@ -21491,10 +21491,10 @@
         <v>1220</v>
       </c>
       <c r="D862" t="s">
+        <v>1221</v>
+      </c>
+      <c r="E862" t="s">
         <v>1224</v>
-      </c>
-      <c r="E862" t="s">
-        <v>1222</v>
       </c>
       <c r="F862" t="s">
         <v>713</v>
@@ -21511,10 +21511,10 @@
         <v>1220</v>
       </c>
       <c r="D863" t="s">
+        <v>1221</v>
+      </c>
+      <c r="E863" t="s">
         <v>1224</v>
-      </c>
-      <c r="E863" t="s">
-        <v>1222</v>
       </c>
       <c r="F863" t="s">
         <v>713</v>
@@ -21531,10 +21531,10 @@
         <v>1220</v>
       </c>
       <c r="D864" t="s">
+        <v>1221</v>
+      </c>
+      <c r="E864" t="s">
         <v>1224</v>
-      </c>
-      <c r="E864" t="s">
-        <v>1222</v>
       </c>
       <c r="F864" t="s">
         <v>713</v>
@@ -21551,10 +21551,10 @@
         <v>1220</v>
       </c>
       <c r="D865" t="s">
+        <v>1221</v>
+      </c>
+      <c r="E865" t="s">
         <v>1224</v>
-      </c>
-      <c r="E865" t="s">
-        <v>1222</v>
       </c>
       <c r="F865" t="s">
         <v>713</v>
@@ -21571,10 +21571,10 @@
         <v>1220</v>
       </c>
       <c r="D866" t="s">
+        <v>1221</v>
+      </c>
+      <c r="E866" t="s">
         <v>1224</v>
-      </c>
-      <c r="E866" t="s">
-        <v>1222</v>
       </c>
       <c r="F866" t="s">
         <v>713</v>
@@ -22151,10 +22151,10 @@
         <v>1281</v>
       </c>
       <c r="D895" t="s">
+        <v>1282</v>
+      </c>
+      <c r="E895" t="s">
         <v>1289</v>
-      </c>
-      <c r="E895" t="s">
-        <v>1283</v>
       </c>
       <c r="F895" t="s">
         <v>713</v>
@@ -22351,10 +22351,10 @@
         <v>1281</v>
       </c>
       <c r="D905" t="s">
+        <v>1299</v>
+      </c>
+      <c r="E905" t="s">
         <v>1302</v>
-      </c>
-      <c r="E905" t="s">
-        <v>1300</v>
       </c>
       <c r="F905" t="s">
         <v>713</v>

--- a/api/2/clv2/xlsx/pt/HumanitarianPlan.xlsx
+++ b/api/2/clv2/xlsx/pt/HumanitarianPlan.xlsx
@@ -22,15 +22,15 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:plan-start-date</t>
+  </si>
+  <si>
     <t>codeforiati:plan-end-date</t>
   </si>
   <si>
     <t>codeforiati:plan-year</t>
   </si>
   <si>
-    <t>codeforiati:plan-start-date</t>
-  </si>
-  <si>
     <t>codeforiati:plan-type</t>
   </si>
   <si>
@@ -40,15 +40,15 @@
     <t>active</t>
   </si>
   <si>
+    <t>2025-01-01</t>
+  </si>
+  <si>
     <t>2025-12-31</t>
   </si>
   <si>
     <t>2025</t>
   </si>
   <si>
-    <t>2025-01-01</t>
-  </si>
-  <si>
     <t>Humanitarian needs and response plan</t>
   </si>
   <si>
@@ -217,15 +217,15 @@
     <t>HAFG24</t>
   </si>
   <si>
+    <t>2024-01-01</t>
+  </si>
+  <si>
     <t>2024-12-31</t>
   </si>
   <si>
     <t>2024</t>
   </si>
   <si>
-    <t>2024-01-01</t>
-  </si>
-  <si>
     <t>RAFG_RRP24</t>
   </si>
   <si>
@@ -421,15 +421,15 @@
     <t>HAFG23</t>
   </si>
   <si>
+    <t>2023-01-01</t>
+  </si>
+  <si>
     <t>2023-12-31</t>
   </si>
   <si>
     <t>2023</t>
   </si>
   <si>
-    <t>2023-01-01</t>
-  </si>
-  <si>
     <t>RAFG23</t>
   </si>
   <si>
@@ -493,21 +493,21 @@
     <t>OMNG2223</t>
   </si>
   <si>
+    <t>2022-12-01</t>
+  </si>
+  <si>
     <t>2023-05-31</t>
   </si>
   <si>
-    <t>2022-12-01</t>
-  </si>
-  <si>
     <t>OMOZ23</t>
   </si>
   <si>
+    <t>2023-03-01</t>
+  </si>
+  <si>
     <t>2023-09-30</t>
   </si>
   <si>
-    <t>2023-03-01</t>
-  </si>
-  <si>
     <t>HMOZ23</t>
   </si>
   <si>
@@ -553,12 +553,12 @@
     <t>RRSDN23</t>
   </si>
   <si>
+    <t>2023-05-01</t>
+  </si>
+  <si>
     <t>2023-10-31</t>
   </si>
   <si>
-    <t>2023-05-01</t>
-  </si>
-  <si>
     <t>HSDN23</t>
   </si>
   <si>
@@ -601,15 +601,15 @@
     <t>HAFG22</t>
   </si>
   <si>
+    <t>2022-01-01</t>
+  </si>
+  <si>
     <t>2022-12-31</t>
   </si>
   <si>
     <t>2022</t>
   </si>
   <si>
-    <t>2022-01-01</t>
-  </si>
-  <si>
     <t>RAFG22</t>
   </si>
   <si>
@@ -631,12 +631,12 @@
     <t>OCUB2223</t>
   </si>
   <si>
+    <t>2022-10-20</t>
+  </si>
+  <si>
     <t>2023-03-31</t>
   </si>
   <si>
-    <t>2022-10-20</t>
-  </si>
-  <si>
     <t>RDRCRRP22</t>
   </si>
   <si>
@@ -652,12 +652,12 @@
     <t>FHTI2223</t>
   </si>
   <si>
+    <t>2022-10-16</t>
+  </si>
+  <si>
     <t>2023-04-15</t>
   </si>
   <si>
-    <t>2022-10-16</t>
-  </si>
-  <si>
     <t>FHTI22</t>
   </si>
   <si>
@@ -688,24 +688,24 @@
     <t>FMWI22</t>
   </si>
   <si>
+    <t>2022-02-26</t>
+  </si>
+  <si>
     <t>2022-05-31</t>
   </si>
   <si>
-    <t>2022-02-26</t>
-  </si>
-  <si>
     <t>HMLI22</t>
   </si>
   <si>
     <t>FMOZ22</t>
   </si>
   <si>
+    <t>2022-04-01</t>
+  </si>
+  <si>
     <t>2022-09-30</t>
   </si>
   <si>
-    <t>2022-04-01</t>
-  </si>
-  <si>
     <t>HMOZ22</t>
   </si>
   <si>
@@ -736,12 +736,12 @@
     <t>OPHL2122</t>
   </si>
   <si>
+    <t>2021-12-24</t>
+  </si>
+  <si>
     <t>2022-06-30</t>
   </si>
   <si>
-    <t>2021-12-24</t>
-  </si>
-  <si>
     <t>RREG22</t>
   </si>
   <si>
@@ -805,15 +805,15 @@
     <t>FAFG21</t>
   </si>
   <si>
+    <t>2021-09-01</t>
+  </si>
+  <si>
     <t>2021-12-31</t>
   </si>
   <si>
     <t>2021</t>
   </si>
   <si>
-    <t>2021-09-01</t>
-  </si>
-  <si>
     <t>HAFG21</t>
   </si>
   <si>
@@ -862,12 +862,12 @@
     <t>FPSE21</t>
   </si>
   <si>
+    <t>2021-05-27</t>
+  </si>
+  <si>
     <t>2021-08-27</t>
   </si>
   <si>
-    <t>2021-05-27</t>
-  </si>
-  <si>
     <t>HETH21</t>
   </si>
   <si>
@@ -880,24 +880,24 @@
     <t>FHTI2122</t>
   </si>
   <si>
+    <t>2021-08-16</t>
+  </si>
+  <si>
     <t>2022-02-15</t>
   </si>
   <si>
-    <t>2021-08-16</t>
-  </si>
-  <si>
     <t>HHTI21</t>
   </si>
   <si>
     <t>FHND2021</t>
   </si>
   <si>
+    <t>2020-11-15</t>
+  </si>
+  <si>
     <t>2021-06-30</t>
   </si>
   <si>
-    <t>2020-11-15</t>
-  </si>
-  <si>
     <t>HHND21</t>
   </si>
   <si>
@@ -916,12 +916,12 @@
     <t>OLBN2122</t>
   </si>
   <si>
+    <t>2021-08-03</t>
+  </si>
+  <si>
     <t>2022-07-31</t>
   </si>
   <si>
-    <t>2021-08-03</t>
-  </si>
-  <si>
     <t>HLBY21</t>
   </si>
   <si>
@@ -1009,15 +1009,15 @@
     <t>HAFG20</t>
   </si>
   <si>
+    <t>2020-01-01</t>
+  </si>
+  <si>
     <t>2020-12-31</t>
   </si>
   <si>
     <t>2020</t>
   </si>
   <si>
-    <t>2020-01-01</t>
-  </si>
-  <si>
     <t>OBGD20</t>
   </si>
   <si>
@@ -1081,12 +1081,12 @@
     <t>FDJI1920</t>
   </si>
   <si>
+    <t>2019-12-17</t>
+  </si>
+  <si>
     <t>2020-03-31</t>
   </si>
   <si>
-    <t>2019-12-17</t>
-  </si>
-  <si>
     <t>ODJI20</t>
   </si>
   <si>
@@ -1135,24 +1135,24 @@
     <t>FLBN20</t>
   </si>
   <si>
+    <t>2020-08-05</t>
+  </si>
+  <si>
     <t>2020-11-13</t>
   </si>
   <si>
-    <t>2020-08-05</t>
-  </si>
-  <si>
     <t>OLBN20</t>
   </si>
   <si>
     <t>FLSO1920</t>
   </si>
   <si>
+    <t>2019-11-01</t>
+  </si>
+  <si>
     <t>2020-04-30</t>
   </si>
   <si>
-    <t>2019-11-01</t>
-  </si>
-  <si>
     <t>OLBR20</t>
   </si>
   <si>
@@ -1249,15 +1249,15 @@
     <t>HAFG19</t>
   </si>
   <si>
+    <t>2019-01-01</t>
+  </si>
+  <si>
     <t>2019-12-31</t>
   </si>
   <si>
     <t>2019</t>
   </si>
   <si>
-    <t>2019-01-01</t>
-  </si>
-  <si>
     <t>RBGD19</t>
   </si>
   <si>
@@ -1366,12 +1366,12 @@
     <t>FZWE1920</t>
   </si>
   <si>
+    <t>2019-02-01</t>
+  </si>
+  <si>
     <t>2020-04-29</t>
   </si>
   <si>
-    <t>2019-02-01</t>
-  </si>
-  <si>
     <t>FZWE1820</t>
   </si>
   <si>
@@ -1381,15 +1381,15 @@
     <t>HAFG18</t>
   </si>
   <si>
+    <t>2018-01-01</t>
+  </si>
+  <si>
     <t>2018-12-31</t>
   </si>
   <si>
     <t>2018</t>
   </si>
   <si>
-    <t>2018-01-01</t>
-  </si>
-  <si>
     <t>OBGD18</t>
   </si>
   <si>
@@ -1483,12 +1483,12 @@
     <t>HSYR18</t>
   </si>
   <si>
+    <t>2018-11-30</t>
+  </si>
+  <si>
     <t>2018-12-30</t>
   </si>
   <si>
-    <t>2018-11-30</t>
-  </si>
-  <si>
     <t>RSYR18</t>
   </si>
   <si>
@@ -1507,15 +1507,15 @@
     <t>OEUR17</t>
   </si>
   <si>
+    <t>2017-01-01</t>
+  </si>
+  <si>
     <t>2017-12-31</t>
   </si>
   <si>
     <t>2017</t>
   </si>
   <si>
-    <t>2017-01-01</t>
-  </si>
-  <si>
     <t>HAFG17</t>
   </si>
   <si>
@@ -1558,12 +1558,12 @@
     <t>FDMA17</t>
   </si>
   <si>
+    <t>2017-09-28</t>
+  </si>
+  <si>
     <t>2017-12-29</t>
   </si>
   <si>
-    <t>2017-09-28</t>
-  </si>
-  <si>
     <t>OPRK17</t>
   </si>
   <si>
@@ -1585,24 +1585,24 @@
     <t>FKEN17</t>
   </si>
   <si>
+    <t>2017-02-10</t>
+  </si>
+  <si>
     <t>2017-11-30</t>
   </si>
   <si>
-    <t>2017-02-10</t>
-  </si>
-  <si>
     <t>HLBY17</t>
   </si>
   <si>
     <t>FMDG17</t>
   </si>
   <si>
+    <t>2017-03-20</t>
+  </si>
+  <si>
     <t>2017-06-20</t>
   </si>
   <si>
-    <t>2017-03-20</t>
-  </si>
-  <si>
     <t>HMLI17</t>
   </si>
   <si>
@@ -1612,12 +1612,12 @@
     <t>FMOZ17</t>
   </si>
   <si>
+    <t>2017-02-28</t>
+  </si>
+  <si>
     <t>2017-05-31</t>
   </si>
   <si>
-    <t>2017-02-28</t>
-  </si>
-  <si>
     <t>HMMR17</t>
   </si>
   <si>
@@ -1636,12 +1636,12 @@
     <t>FPER17</t>
   </si>
   <si>
+    <t>2017-04-01</t>
+  </si>
+  <si>
     <t>2017-10-31</t>
   </si>
   <si>
-    <t>2017-04-01</t>
-  </si>
-  <si>
     <t>HCOG17</t>
   </si>
   <si>
@@ -1678,15 +1678,15 @@
     <t>OEUR16</t>
   </si>
   <si>
+    <t>2016-01-01</t>
+  </si>
+  <si>
     <t>2016-12-31</t>
   </si>
   <si>
     <t>2016</t>
   </si>
   <si>
-    <t>2016-01-01</t>
-  </si>
-  <si>
     <t>HAFG16</t>
   </si>
   <si>
@@ -1726,21 +1726,21 @@
     <t>FECU16</t>
   </si>
   <si>
+    <t>2016-04-16</t>
+  </si>
+  <si>
     <t>2016-10-31</t>
   </si>
   <si>
-    <t>2016-04-16</t>
-  </si>
-  <si>
     <t>FFJI16</t>
   </si>
   <si>
+    <t>2016-02-20</t>
+  </si>
+  <si>
     <t>2016-05-30</t>
   </si>
   <si>
-    <t>2016-02-20</t>
-  </si>
-  <si>
     <t>HGMB16</t>
   </si>
   <si>
@@ -1783,12 +1783,12 @@
     <t>FIRQ16</t>
   </si>
   <si>
+    <t>2016-07-20</t>
+  </si>
+  <si>
     <t>2016-10-01</t>
   </si>
   <si>
-    <t>2016-07-20</t>
-  </si>
-  <si>
     <t>HMMR16</t>
   </si>
   <si>
@@ -1831,24 +1831,24 @@
     <t>HZWE1617</t>
   </si>
   <si>
+    <t>2016-04-01</t>
+  </si>
+  <si>
     <t>2017-03-31</t>
   </si>
   <si>
-    <t>2016-04-01</t>
-  </si>
-  <si>
     <t>HAFG15</t>
   </si>
   <si>
+    <t>2015-01-01</t>
+  </si>
+  <si>
     <t>2015-12-31</t>
   </si>
   <si>
     <t>2015</t>
   </si>
   <si>
-    <t>2015-01-01</t>
-  </si>
-  <si>
     <t>Strategic response plan</t>
   </si>
   <si>
@@ -1879,12 +1879,12 @@
     <t>FGTM1415</t>
   </si>
   <si>
+    <t>2014-11-03</t>
+  </si>
+  <si>
     <t>2015-09-30</t>
   </si>
   <si>
-    <t>2014-11-03</t>
-  </si>
-  <si>
     <t>FHTI15</t>
   </si>
   <si>
@@ -1900,24 +1900,24 @@
     <t>FVUT15</t>
   </si>
   <si>
+    <t>2015-03-24</t>
+  </si>
+  <si>
     <t>2015-10-31</t>
   </si>
   <si>
-    <t>2015-03-24</t>
-  </si>
-  <si>
     <t>HIRQ15</t>
   </si>
   <si>
     <t>HLBY1415</t>
   </si>
   <si>
+    <t>2014-10-01</t>
+  </si>
+  <si>
     <t>2015-05-31</t>
   </si>
   <si>
-    <t>2014-10-01</t>
-  </si>
-  <si>
     <t>HMLI15</t>
   </si>
   <si>
@@ -1975,15 +1975,15 @@
     <t>HAFG14</t>
   </si>
   <si>
+    <t>2014-01-01</t>
+  </si>
+  <si>
     <t>2014-12-31</t>
   </si>
   <si>
     <t>2014</t>
   </si>
   <si>
-    <t>2014-01-01</t>
-  </si>
-  <si>
     <t>HBFA1314</t>
   </si>
   <si>
@@ -2059,21 +2059,21 @@
     <t>FPHL1314</t>
   </si>
   <si>
+    <t>2013-10-22</t>
+  </si>
+  <si>
     <t>2014-04-22</t>
   </si>
   <si>
-    <t>2013-10-22</t>
-  </si>
-  <si>
     <t>SPHL1314</t>
   </si>
   <si>
+    <t>2013-11-08</t>
+  </si>
+  <si>
     <t>2014-11-07</t>
   </si>
   <si>
-    <t>2013-11-08</t>
-  </si>
-  <si>
     <t>HPHL1314</t>
   </si>
   <si>
@@ -2083,12 +2083,12 @@
     <t>HPHL1314a</t>
   </si>
   <si>
+    <t>2013-10-01</t>
+  </si>
+  <si>
     <t>2014-08-31</t>
   </si>
   <si>
-    <t>2013-10-01</t>
-  </si>
-  <si>
     <t>SCOD14</t>
   </si>
   <si>
@@ -2242,15 +2242,15 @@
     <t>CKEN12</t>
   </si>
   <si>
+    <t>2012-01-01</t>
+  </si>
+  <si>
     <t>2012-12-31</t>
   </si>
   <si>
     <t>2012</t>
   </si>
   <si>
-    <t>2012-01-01</t>
-  </si>
-  <si>
     <t>CAFG1112</t>
   </si>
   <si>
@@ -2290,12 +2290,12 @@
     <t>FLSO1213</t>
   </si>
   <si>
+    <t>2012-09-18</t>
+  </si>
+  <si>
     <t>2013-03-25</t>
   </si>
   <si>
-    <t>2012-09-18</t>
-  </si>
-  <si>
     <t>CLBR12</t>
   </si>
   <si>
@@ -2335,12 +2335,12 @@
     <t>CSYR12</t>
   </si>
   <si>
+    <t>2012-06-05</t>
+  </si>
+  <si>
     <t>2012-12-05</t>
   </si>
   <si>
-    <t>2012-06-05</t>
-  </si>
-  <si>
     <t>CYEM12</t>
   </si>
   <si>
@@ -2353,12 +2353,12 @@
     <t>CKEN1113</t>
   </si>
   <si>
+    <t>2011-01-01</t>
+  </si>
+  <si>
     <t>2011</t>
   </si>
   <si>
-    <t>2011-01-01</t>
-  </si>
-  <si>
     <t>CAFG11</t>
   </si>
   <si>
@@ -2383,12 +2383,12 @@
     <t>FSLV1112</t>
   </si>
   <si>
+    <t>2011-10-25</t>
+  </si>
+  <si>
     <t>2012-04-25</t>
   </si>
   <si>
-    <t>2011-10-25</t>
-  </si>
-  <si>
     <t>CHTI1011</t>
   </si>
   <si>
@@ -2407,33 +2407,33 @@
     <t>FNAM11</t>
   </si>
   <si>
+    <t>2011-04-11</t>
+  </si>
+  <si>
     <t>2011-10-11</t>
   </si>
   <si>
-    <t>2011-04-11</t>
-  </si>
-  <si>
     <t>FNIC1112</t>
   </si>
   <si>
+    <t>2011-10-27</t>
+  </si>
+  <si>
     <t>2012-04-26</t>
   </si>
   <si>
-    <t>2011-10-27</t>
-  </si>
-  <si>
     <t>CNER11</t>
   </si>
   <si>
     <t>FPAK1112</t>
   </si>
   <si>
+    <t>2011-09-15</t>
+  </si>
+  <si>
     <t>2012-06-30</t>
   </si>
   <si>
-    <t>2011-09-15</t>
-  </si>
-  <si>
     <t>FXLBYREG11</t>
   </si>
   <si>
@@ -2476,24 +2476,24 @@
     <t>CAFG10</t>
   </si>
   <si>
+    <t>2010-01-01</t>
+  </si>
+  <si>
     <t>2010-12-31</t>
   </si>
   <si>
     <t>2010</t>
   </si>
   <si>
-    <t>2010-01-01</t>
-  </si>
-  <si>
     <t>OBFA1011</t>
   </si>
   <si>
+    <t>2010-08-01</t>
+  </si>
+  <si>
     <t>2011-01-31</t>
   </si>
   <si>
-    <t>2010-08-01</t>
-  </si>
-  <si>
     <t>CCAF10</t>
   </si>
   <si>
@@ -2506,30 +2506,30 @@
     <t>FSLV0910</t>
   </si>
   <si>
+    <t>2009-11-01</t>
+  </si>
+  <si>
     <t>2010-05-31</t>
   </si>
   <si>
-    <t>2009-11-01</t>
-  </si>
-  <si>
     <t>FGTM10</t>
   </si>
   <si>
+    <t>2010-06-10</t>
+  </si>
+  <si>
     <t>2010-12-09</t>
   </si>
   <si>
-    <t>2010-06-10</t>
-  </si>
-  <si>
     <t>CGTM10</t>
   </si>
   <si>
+    <t>2010-02-12</t>
+  </si>
+  <si>
     <t>2010-08-11</t>
   </si>
   <si>
-    <t>2010-02-12</t>
-  </si>
-  <si>
     <t>FHTI10</t>
   </si>
   <si>
@@ -2545,12 +2545,12 @@
     <t>FKGZ1011</t>
   </si>
   <si>
+    <t>2010-06-01</t>
+  </si>
+  <si>
     <t>2011-06-30</t>
   </si>
   <si>
-    <t>2010-06-01</t>
-  </si>
-  <si>
     <t>CMNG1011</t>
   </si>
   <si>
@@ -2608,24 +2608,24 @@
     <t>CAFG09</t>
   </si>
   <si>
+    <t>2009-01-01</t>
+  </si>
+  <si>
     <t>2009-12-31</t>
   </si>
   <si>
     <t>2009</t>
   </si>
   <si>
-    <t>2009-01-01</t>
-  </si>
-  <si>
     <t>FBFA0910</t>
   </si>
   <si>
+    <t>2009-09-10</t>
+  </si>
+  <si>
     <t>2010-03-09</t>
   </si>
   <si>
-    <t>2009-09-10</t>
-  </si>
-  <si>
     <t>CCAF09</t>
   </si>
   <si>
@@ -2662,21 +2662,21 @@
     <t>FMDG09</t>
   </si>
   <si>
+    <t>2009-04-01</t>
+  </si>
+  <si>
     <t>2009-10-31</t>
   </si>
   <si>
-    <t>2009-04-01</t>
-  </si>
-  <si>
     <t>FNAM09</t>
   </si>
   <si>
+    <t>2009-03-20</t>
+  </si>
+  <si>
     <t>2009-09-30</t>
   </si>
   <si>
-    <t>2009-03-20</t>
-  </si>
-  <si>
     <t>ONPL09</t>
   </si>
   <si>
@@ -2689,12 +2689,12 @@
     <t>FPHL0910</t>
   </si>
   <si>
+    <t>2009-10-03</t>
+  </si>
+  <si>
     <t>2010-03-31</t>
   </si>
   <si>
-    <t>2009-10-03</t>
-  </si>
-  <si>
     <t>CSOM09</t>
   </si>
   <si>
@@ -2707,12 +2707,12 @@
     <t>OSYR0910</t>
   </si>
   <si>
+    <t>2009-07-15</t>
+  </si>
+  <si>
     <t>2010-06-14</t>
   </si>
   <si>
-    <t>2009-07-15</t>
-  </si>
-  <si>
     <t>OTJK09</t>
   </si>
   <si>
@@ -2746,24 +2746,24 @@
     <t>OAFG08</t>
   </si>
   <si>
+    <t>2008-02-01</t>
+  </si>
+  <si>
     <t>2008-06-30</t>
   </si>
   <si>
     <t>2008</t>
   </si>
   <si>
-    <t>2008-02-01</t>
-  </si>
-  <si>
     <t>OAFG0809</t>
   </si>
   <si>
+    <t>2008-07-01</t>
+  </si>
+  <si>
     <t>2009-06-30</t>
   </si>
   <si>
-    <t>2008-07-01</t>
-  </si>
-  <si>
     <t>FBOL08</t>
   </si>
   <si>
@@ -2773,12 +2773,12 @@
     <t>CCAF08</t>
   </si>
   <si>
+    <t>2008-01-01</t>
+  </si>
+  <si>
     <t>2008-12-31</t>
   </si>
   <si>
-    <t>2008-01-01</t>
-  </si>
-  <si>
     <t>CTCD08</t>
   </si>
   <si>
@@ -2794,21 +2794,21 @@
     <t>ODJI0809</t>
   </si>
   <si>
+    <t>2008-08-01</t>
+  </si>
+  <si>
     <t>2009-02-28</t>
   </si>
   <si>
-    <t>2008-08-01</t>
-  </si>
-  <si>
     <t>FGEO0809</t>
   </si>
   <si>
+    <t>2008-08-09</t>
+  </si>
+  <si>
     <t>2009-02-09</t>
   </si>
   <si>
-    <t>2008-08-09</t>
-  </si>
-  <si>
     <t>FHTI0809</t>
   </si>
   <si>
@@ -2818,12 +2818,12 @@
     <t>FHND0809</t>
   </si>
   <si>
+    <t>2008-11-01</t>
+  </si>
+  <si>
     <t>2009-04-30</t>
   </si>
   <si>
-    <t>2008-11-01</t>
-  </si>
-  <si>
     <t>CIRQ08</t>
   </si>
   <si>
@@ -2833,12 +2833,12 @@
     <t>FKGZ0809</t>
   </si>
   <si>
+    <t>2008-12-01</t>
+  </si>
+  <si>
     <t>2009-05-31</t>
   </si>
   <si>
-    <t>2008-12-01</t>
-  </si>
-  <si>
     <t>OLAO0809</t>
   </si>
   <si>
@@ -2857,12 +2857,12 @@
     <t>FMMR08</t>
   </si>
   <si>
+    <t>2008-05-01</t>
+  </si>
+  <si>
     <t>2008-11-30</t>
   </si>
   <si>
-    <t>2008-05-01</t>
-  </si>
-  <si>
     <t>ONPL08</t>
   </si>
   <si>
@@ -2914,33 +2914,33 @@
     <t>FBOL07</t>
   </si>
   <si>
+    <t>2007-02-22</t>
+  </si>
+  <si>
     <t>2007-08-21</t>
   </si>
   <si>
     <t>2007</t>
   </si>
   <si>
-    <t>2007-02-22</t>
-  </si>
-  <si>
     <t>FBFA0708</t>
   </si>
   <si>
+    <t>2007-11-01</t>
+  </si>
+  <si>
     <t>2008-01-31</t>
   </si>
   <si>
-    <t>2007-11-01</t>
-  </si>
-  <si>
     <t>CBDI07</t>
   </si>
   <si>
+    <t>2007-01-01</t>
+  </si>
+  <si>
     <t>2007-12-31</t>
   </si>
   <si>
-    <t>2007-01-01</t>
-  </si>
-  <si>
     <t>CCAF07</t>
   </si>
   <si>
@@ -2962,12 +2962,12 @@
     <t>FGHA0708</t>
   </si>
   <si>
+    <t>2007-09-01</t>
+  </si>
+  <si>
     <t>2008-03-31</t>
   </si>
   <si>
-    <t>2007-09-01</t>
-  </si>
-  <si>
     <t>CXGLR07</t>
   </si>
   <si>
@@ -2980,75 +2980,75 @@
     <t>FPRK07</t>
   </si>
   <si>
+    <t>2007-08-28</t>
+  </si>
+  <si>
     <t>2007-11-30</t>
   </si>
   <si>
-    <t>2007-08-28</t>
-  </si>
-  <si>
     <t>OLBN07</t>
   </si>
   <si>
+    <t>2007-06-04</t>
+  </si>
+  <si>
     <t>2007-09-03</t>
   </si>
   <si>
-    <t>2007-06-04</t>
-  </si>
-  <si>
     <t>FLSO0708</t>
   </si>
   <si>
+    <t>2007-07-28</t>
+  </si>
+  <si>
     <t>2008-01-28</t>
   </si>
   <si>
-    <t>2007-07-28</t>
-  </si>
-  <si>
     <t>CLBR07</t>
   </si>
   <si>
     <t>FMDG07</t>
   </si>
   <si>
+    <t>2007-03-15</t>
+  </si>
+  <si>
     <t>2007-09-15</t>
   </si>
   <si>
-    <t>2007-03-15</t>
-  </si>
-  <si>
     <t>FMOZ07</t>
   </si>
   <si>
+    <t>2007-03-01</t>
+  </si>
+  <si>
     <t>2007-06-30</t>
   </si>
   <si>
-    <t>2007-03-01</t>
-  </si>
-  <si>
     <t>ONPL07</t>
   </si>
   <si>
     <t>FNIC0708</t>
   </si>
   <si>
+    <t>2007-09-07</t>
+  </si>
+  <si>
     <t>2008-02-28</t>
   </si>
   <si>
-    <t>2007-09-07</t>
-  </si>
-  <si>
     <t>ORUS07</t>
   </si>
   <si>
     <t>FPAK07</t>
   </si>
   <si>
+    <t>2007-07-15</t>
+  </si>
+  <si>
     <t>2007-10-31</t>
   </si>
   <si>
-    <t>2007-07-15</t>
-  </si>
-  <si>
     <t>FPER0708</t>
   </si>
   <si>
@@ -3082,12 +3082,12 @@
     <t>FSWZ0708</t>
   </si>
   <si>
+    <t>2007-07-20</t>
+  </si>
+  <si>
     <t>2008-01-20</t>
   </si>
   <si>
-    <t>2007-07-20</t>
-  </si>
-  <si>
     <t>CTLS07</t>
   </si>
   <si>
@@ -3112,15 +3112,15 @@
     <t>OAFG06</t>
   </si>
   <si>
+    <t>2006-07-01</t>
+  </si>
+  <si>
     <t>2006-12-31</t>
   </si>
   <si>
     <t>2006</t>
   </si>
   <si>
-    <t>2006-07-01</t>
-  </si>
-  <si>
     <t>CBDI06</t>
   </si>
   <si>
@@ -3145,21 +3145,21 @@
     <t>OETH06a</t>
   </si>
   <si>
+    <t>2006-08-25</t>
+  </si>
+  <si>
     <t>2006-11-25</t>
   </si>
   <si>
-    <t>2006-08-25</t>
-  </si>
-  <si>
     <t>OETH0607</t>
   </si>
   <si>
+    <t>2006-11-23</t>
+  </si>
+  <si>
     <t>2007-01-22</t>
   </si>
   <si>
-    <t>2006-11-23</t>
-  </si>
-  <si>
     <t>CXGLR06</t>
   </si>
   <si>
@@ -3169,12 +3169,12 @@
     <t>FGNB06</t>
   </si>
   <si>
+    <t>2006-05-01</t>
+  </si>
+  <si>
     <t>2006-11-30</t>
   </si>
   <si>
-    <t>2006-05-01</t>
-  </si>
-  <si>
     <t>CXHAF06</t>
   </si>
   <si>
@@ -3184,12 +3184,12 @@
     <t>FKEN0607</t>
   </si>
   <si>
+    <t>2006-10-16</t>
+  </si>
+  <si>
     <t>2007-04-15</t>
   </si>
   <si>
-    <t>2006-10-16</t>
-  </si>
-  <si>
     <t>FKEN06</t>
   </si>
   <si>
@@ -3199,12 +3199,12 @@
     <t>FLBN06</t>
   </si>
   <si>
+    <t>2006-07-24</t>
+  </si>
+  <si>
     <t>2006-10-23</t>
   </si>
   <si>
-    <t>2006-07-24</t>
-  </si>
-  <si>
     <t>CLBR06</t>
   </si>
   <si>
@@ -3232,12 +3232,12 @@
     <t>FSOM0607</t>
   </si>
   <si>
+    <t>2006-12-05</t>
+  </si>
+  <si>
     <t>2007-03-05</t>
   </si>
   <si>
-    <t>2006-12-05</t>
-  </si>
-  <si>
     <t>OLKA06</t>
   </si>
   <si>
@@ -3271,33 +3271,33 @@
     <t>FAGO05</t>
   </si>
   <si>
+    <t>2005-04-01</t>
+  </si>
+  <si>
     <t>2005-06-30</t>
   </si>
   <si>
     <t>2005</t>
   </si>
   <si>
-    <t>2005-04-01</t>
-  </si>
-  <si>
     <t>FBEN05</t>
   </si>
   <si>
+    <t>2005-05-01</t>
+  </si>
+  <si>
     <t>2005-10-31</t>
   </si>
   <si>
-    <t>2005-05-01</t>
-  </si>
-  <si>
     <t>CBDI05</t>
   </si>
   <si>
+    <t>2005-01-01</t>
+  </si>
+  <si>
     <t>2005-12-31</t>
   </si>
   <si>
-    <t>2005-01-01</t>
-  </si>
-  <si>
     <t>CCAF05</t>
   </si>
   <si>
@@ -3337,12 +3337,12 @@
     <t>FGUY05</t>
   </si>
   <si>
+    <t>2005-02-01</t>
+  </si>
+  <si>
     <t>2005-08-01</t>
   </si>
   <si>
-    <t>2005-02-01</t>
-  </si>
-  <si>
     <t>FXINDTSU05</t>
   </si>
   <si>
@@ -3355,12 +3355,12 @@
     <t>FNER05</t>
   </si>
   <si>
+    <t>2005-06-01</t>
+  </si>
+  <si>
     <t>2005-09-30</t>
   </si>
   <si>
-    <t>2005-06-01</t>
-  </si>
-  <si>
     <t>CCOG05</t>
   </si>
   <si>
@@ -3370,12 +3370,12 @@
     <t>FXSASIA0506</t>
   </si>
   <si>
+    <t>2005-10-11</t>
+  </si>
+  <si>
     <t>2006-04-10</t>
   </si>
   <si>
-    <t>2005-10-11</t>
-  </si>
-  <si>
     <t>CSDN05</t>
   </si>
   <si>
@@ -3388,27 +3388,27 @@
     <t>FXWAF0506</t>
   </si>
   <si>
+    <t>2005-11-01</t>
+  </si>
+  <si>
     <t>2006-05-31</t>
   </si>
   <si>
-    <t>2005-11-01</t>
-  </si>
-  <si>
     <t>CPSE05</t>
   </si>
   <si>
     <t>OAFG04</t>
   </si>
   <si>
+    <t>2004-09-01</t>
+  </si>
+  <si>
     <t>2004-12-31</t>
   </si>
   <si>
     <t>2004</t>
   </si>
   <si>
-    <t>2004-09-01</t>
-  </si>
-  <si>
     <t>CAGO04</t>
   </si>
   <si>
@@ -3418,21 +3418,21 @@
     <t>FBGD0405</t>
   </si>
   <si>
+    <t>2004-08-01</t>
+  </si>
+  <si>
     <t>2005-01-31</t>
   </si>
   <si>
-    <t>2004-08-01</t>
-  </si>
-  <si>
     <t>FBOL0405</t>
   </si>
   <si>
+    <t>2004-11-01</t>
+  </si>
+  <si>
     <t>2005-05-31</t>
   </si>
   <si>
-    <t>2004-11-01</t>
-  </si>
-  <si>
     <t>CBDI04</t>
   </si>
   <si>
@@ -3505,21 +3505,21 @@
     <t>FMDG04</t>
   </si>
   <si>
+    <t>2004-03-19</t>
+  </si>
+  <si>
     <t>2004-06-19</t>
   </si>
   <si>
-    <t>2004-03-19</t>
-  </si>
-  <si>
     <t>FPHL0405</t>
   </si>
   <si>
+    <t>2004-12-15</t>
+  </si>
+  <si>
     <t>2005-03-15</t>
   </si>
   <si>
-    <t>2004-12-15</t>
-  </si>
-  <si>
     <t>CSLE04</t>
   </si>
   <si>
@@ -3550,15 +3550,15 @@
     <t>OAFG03</t>
   </si>
   <si>
+    <t>2003-01-01</t>
+  </si>
+  <si>
     <t>2003-12-31</t>
   </si>
   <si>
     <t>2003</t>
   </si>
   <si>
-    <t>2003-01-01</t>
-  </si>
-  <si>
     <t>CAGO03</t>
   </si>
   <si>
@@ -3568,12 +3568,12 @@
     <t>FCAF03</t>
   </si>
   <si>
+    <t>2003-04-01</t>
+  </si>
+  <si>
     <t>2003-06-30</t>
   </si>
   <si>
-    <t>2003-04-01</t>
-  </si>
-  <si>
     <t>CRUS03</t>
   </si>
   <si>
@@ -3586,12 +3586,12 @@
     <t>FCIV0203</t>
   </si>
   <si>
+    <t>2002-11-01</t>
+  </si>
+  <si>
     <t>2003-01-31</t>
   </si>
   <si>
-    <t>2002-11-01</t>
-  </si>
-  <si>
     <t>CPRK03</t>
   </si>
   <si>
@@ -3610,21 +3610,21 @@
     <t>OHTI03</t>
   </si>
   <si>
+    <t>2003-03-01</t>
+  </si>
+  <si>
     <t>2003-08-31</t>
   </si>
   <si>
-    <t>2003-03-01</t>
-  </si>
-  <si>
     <t>CLSO0304</t>
   </si>
   <si>
+    <t>2003-07-01</t>
+  </si>
+  <si>
     <t>2004-06-30</t>
   </si>
   <si>
-    <t>2003-07-01</t>
-  </si>
-  <si>
     <t>CMWI03</t>
   </si>
   <si>
@@ -3676,15 +3676,15 @@
     <t>CAFG0102</t>
   </si>
   <si>
+    <t>2001-10-01</t>
+  </si>
+  <si>
     <t>2002-12-31</t>
   </si>
   <si>
     <t>2002</t>
   </si>
   <si>
-    <t>2001-10-01</t>
-  </si>
-  <si>
     <t>CAGO02</t>
   </si>
   <si>
@@ -3778,15 +3778,15 @@
     <t>CAFG01</t>
   </si>
   <si>
+    <t>2001-01-01</t>
+  </si>
+  <si>
     <t>2001-09-30</t>
   </si>
   <si>
     <t>2001</t>
   </si>
   <si>
-    <t>2001-01-01</t>
-  </si>
-  <si>
     <t>CAGO01</t>
   </si>
   <si>
@@ -3859,15 +3859,15 @@
     <t>CAGO00</t>
   </si>
   <si>
+    <t>2000-01-01</t>
+  </si>
+  <si>
     <t>2000-12-31</t>
   </si>
   <si>
     <t>2000</t>
   </si>
   <si>
-    <t>2000-01-01</t>
-  </si>
-  <si>
     <t>CBDI00</t>
   </si>
   <si>
@@ -3913,10 +3913,10 @@
     <t>CTLS9900</t>
   </si>
   <si>
+    <t>1999-10-01</t>
+  </si>
+  <si>
     <t>1999</t>
-  </si>
-  <si>
-    <t>1999-10-01</t>
   </si>
   <si>
     <t>CRUS9900</t>
@@ -4328,10 +4328,10 @@
         <v>7</v>
       </c>
       <c r="C4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" t="s">
         <v>15</v>
-      </c>
-      <c r="D4" t="s">
-        <v>9</v>
       </c>
       <c r="E4" t="s">
         <v>10</v>
@@ -4528,10 +4528,10 @@
         <v>7</v>
       </c>
       <c r="C14" t="s">
+        <v>8</v>
+      </c>
+      <c r="D14" t="s">
         <v>15</v>
-      </c>
-      <c r="D14" t="s">
-        <v>9</v>
       </c>
       <c r="E14" t="s">
         <v>10</v>
@@ -4548,10 +4548,10 @@
         <v>7</v>
       </c>
       <c r="C15" t="s">
+        <v>8</v>
+      </c>
+      <c r="D15" t="s">
         <v>30</v>
-      </c>
-      <c r="D15" t="s">
-        <v>9</v>
       </c>
       <c r="E15" t="s">
         <v>10</v>
@@ -4588,10 +4588,10 @@
         <v>7</v>
       </c>
       <c r="C17" t="s">
+        <v>8</v>
+      </c>
+      <c r="D17" t="s">
         <v>33</v>
-      </c>
-      <c r="D17" t="s">
-        <v>9</v>
       </c>
       <c r="E17" t="s">
         <v>10</v>
@@ -4628,10 +4628,10 @@
         <v>7</v>
       </c>
       <c r="C19" t="s">
+        <v>8</v>
+      </c>
+      <c r="D19" t="s">
         <v>36</v>
-      </c>
-      <c r="D19" t="s">
-        <v>9</v>
       </c>
       <c r="E19" t="s">
         <v>10</v>
@@ -4648,13 +4648,13 @@
         <v>7</v>
       </c>
       <c r="C20" t="s">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="D20" t="s">
         <v>9</v>
       </c>
       <c r="E20" t="s">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="F20" t="s">
         <v>11</v>
@@ -4728,10 +4728,10 @@
         <v>7</v>
       </c>
       <c r="C24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D24" t="s">
         <v>43</v>
-      </c>
-      <c r="D24" t="s">
-        <v>9</v>
       </c>
       <c r="E24" t="s">
         <v>10</v>
@@ -4928,13 +4928,13 @@
         <v>7</v>
       </c>
       <c r="C34" t="s">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="D34" t="s">
         <v>9</v>
       </c>
       <c r="E34" t="s">
-        <v>54</v>
+        <v>10</v>
       </c>
       <c r="F34" t="s">
         <v>24</v>
@@ -5088,10 +5088,10 @@
         <v>7</v>
       </c>
       <c r="C42" t="s">
+        <v>8</v>
+      </c>
+      <c r="D42" t="s">
         <v>36</v>
-      </c>
-      <c r="D42" t="s">
-        <v>9</v>
       </c>
       <c r="E42" t="s">
         <v>10</v>
@@ -5128,10 +5128,10 @@
         <v>7</v>
       </c>
       <c r="C44" t="s">
+        <v>8</v>
+      </c>
+      <c r="D44" t="s">
         <v>36</v>
-      </c>
-      <c r="D44" t="s">
-        <v>9</v>
       </c>
       <c r="E44" t="s">
         <v>10</v>
@@ -5148,10 +5148,10 @@
         <v>7</v>
       </c>
       <c r="C45" t="s">
+        <v>8</v>
+      </c>
+      <c r="D45" t="s">
         <v>30</v>
-      </c>
-      <c r="D45" t="s">
-        <v>9</v>
       </c>
       <c r="E45" t="s">
         <v>10</v>
@@ -5208,13 +5208,13 @@
         <v>7</v>
       </c>
       <c r="C48" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="D48" t="s">
         <v>68</v>
       </c>
       <c r="E48" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F48" t="s">
         <v>16</v>
@@ -5248,13 +5248,13 @@
         <v>7</v>
       </c>
       <c r="C50" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="D50" t="s">
         <v>68</v>
       </c>
       <c r="E50" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="F50" t="s">
         <v>16</v>
@@ -5388,13 +5388,13 @@
         <v>7</v>
       </c>
       <c r="C57" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="D57" t="s">
         <v>68</v>
       </c>
       <c r="E57" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="F57" t="s">
         <v>24</v>
@@ -5468,13 +5468,13 @@
         <v>7</v>
       </c>
       <c r="C61" t="s">
-        <v>67</v>
+        <v>88</v>
       </c>
       <c r="D61" t="s">
         <v>68</v>
       </c>
       <c r="E61" t="s">
-        <v>88</v>
+        <v>69</v>
       </c>
       <c r="F61" t="s">
         <v>16</v>
@@ -5488,13 +5488,13 @@
         <v>7</v>
       </c>
       <c r="C62" t="s">
-        <v>67</v>
+        <v>88</v>
       </c>
       <c r="D62" t="s">
         <v>68</v>
       </c>
       <c r="E62" t="s">
-        <v>88</v>
+        <v>69</v>
       </c>
       <c r="F62" t="s">
         <v>24</v>
@@ -5508,10 +5508,10 @@
         <v>7</v>
       </c>
       <c r="C63" t="s">
+        <v>67</v>
+      </c>
+      <c r="D63" t="s">
         <v>91</v>
-      </c>
-      <c r="D63" t="s">
-        <v>68</v>
       </c>
       <c r="E63" t="s">
         <v>69</v>
@@ -5528,10 +5528,10 @@
         <v>7</v>
       </c>
       <c r="C64" t="s">
+        <v>67</v>
+      </c>
+      <c r="D64" t="s">
         <v>93</v>
-      </c>
-      <c r="D64" t="s">
-        <v>68</v>
       </c>
       <c r="E64" t="s">
         <v>69</v>
@@ -5548,13 +5548,13 @@
         <v>7</v>
       </c>
       <c r="C65" t="s">
-        <v>67</v>
+        <v>95</v>
       </c>
       <c r="D65" t="s">
         <v>68</v>
       </c>
       <c r="E65" t="s">
-        <v>95</v>
+        <v>69</v>
       </c>
       <c r="F65" t="s">
         <v>24</v>
@@ -5588,13 +5588,13 @@
         <v>7</v>
       </c>
       <c r="C67" t="s">
+        <v>98</v>
+      </c>
+      <c r="D67" t="s">
         <v>93</v>
       </c>
-      <c r="D67" t="s">
-        <v>68</v>
-      </c>
       <c r="E67" t="s">
-        <v>98</v>
+        <v>69</v>
       </c>
       <c r="F67" t="s">
         <v>16</v>
@@ -5608,13 +5608,13 @@
         <v>7</v>
       </c>
       <c r="C68" t="s">
-        <v>67</v>
+        <v>100</v>
       </c>
       <c r="D68" t="s">
         <v>68</v>
       </c>
       <c r="E68" t="s">
-        <v>100</v>
+        <v>69</v>
       </c>
       <c r="F68" t="s">
         <v>24</v>
@@ -5668,13 +5668,13 @@
         <v>7</v>
       </c>
       <c r="C71" t="s">
-        <v>67</v>
+        <v>104</v>
       </c>
       <c r="D71" t="s">
         <v>68</v>
       </c>
       <c r="E71" t="s">
-        <v>104</v>
+        <v>69</v>
       </c>
       <c r="F71" t="s">
         <v>16</v>
@@ -5728,13 +5728,13 @@
         <v>7</v>
       </c>
       <c r="C74" t="s">
-        <v>67</v>
+        <v>108</v>
       </c>
       <c r="D74" t="s">
         <v>68</v>
       </c>
       <c r="E74" t="s">
-        <v>108</v>
+        <v>69</v>
       </c>
       <c r="F74" t="s">
         <v>16</v>
@@ -5848,13 +5848,13 @@
         <v>7</v>
       </c>
       <c r="C80" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="D80" t="s">
         <v>68</v>
       </c>
       <c r="E80" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="F80" t="s">
         <v>24</v>
@@ -6108,13 +6108,13 @@
         <v>7</v>
       </c>
       <c r="C93" t="s">
-        <v>67</v>
+        <v>129</v>
       </c>
       <c r="D93" t="s">
         <v>68</v>
       </c>
       <c r="E93" t="s">
-        <v>129</v>
+        <v>69</v>
       </c>
       <c r="F93" t="s">
         <v>16</v>
@@ -6148,13 +6148,13 @@
         <v>7</v>
       </c>
       <c r="C95" t="s">
-        <v>67</v>
+        <v>132</v>
       </c>
       <c r="D95" t="s">
         <v>68</v>
       </c>
       <c r="E95" t="s">
-        <v>132</v>
+        <v>69</v>
       </c>
       <c r="F95" t="s">
         <v>24</v>
@@ -6168,13 +6168,13 @@
         <v>7</v>
       </c>
       <c r="C96" t="s">
-        <v>67</v>
+        <v>132</v>
       </c>
       <c r="D96" t="s">
         <v>68</v>
       </c>
       <c r="E96" t="s">
-        <v>132</v>
+        <v>69</v>
       </c>
       <c r="F96" t="s">
         <v>24</v>
@@ -6348,13 +6348,13 @@
         <v>7</v>
       </c>
       <c r="C105" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="D105" t="s">
         <v>136</v>
       </c>
       <c r="E105" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="F105" t="s">
         <v>24</v>
@@ -6508,13 +6508,13 @@
         <v>7</v>
       </c>
       <c r="C113" t="s">
-        <v>135</v>
+        <v>155</v>
       </c>
       <c r="D113" t="s">
         <v>136</v>
       </c>
       <c r="E113" t="s">
-        <v>155</v>
+        <v>137</v>
       </c>
       <c r="F113" t="s">
         <v>24</v>
@@ -6571,10 +6571,10 @@
         <v>159</v>
       </c>
       <c r="D116" t="s">
-        <v>136</v>
+        <v>160</v>
       </c>
       <c r="E116" t="s">
-        <v>160</v>
+        <v>137</v>
       </c>
       <c r="F116" t="s">
         <v>16</v>
@@ -6591,10 +6591,10 @@
         <v>162</v>
       </c>
       <c r="D117" t="s">
-        <v>136</v>
+        <v>163</v>
       </c>
       <c r="E117" t="s">
-        <v>163</v>
+        <v>137</v>
       </c>
       <c r="F117" t="s">
         <v>16</v>
@@ -6688,10 +6688,10 @@
         <v>7</v>
       </c>
       <c r="C122" t="s">
-        <v>162</v>
+        <v>135</v>
       </c>
       <c r="D122" t="s">
-        <v>136</v>
+        <v>163</v>
       </c>
       <c r="E122" t="s">
         <v>137</v>
@@ -6708,10 +6708,10 @@
         <v>7</v>
       </c>
       <c r="C123" t="s">
-        <v>159</v>
+        <v>135</v>
       </c>
       <c r="D123" t="s">
-        <v>136</v>
+        <v>160</v>
       </c>
       <c r="E123" t="s">
         <v>137</v>
@@ -6891,10 +6891,10 @@
         <v>179</v>
       </c>
       <c r="D132" t="s">
-        <v>136</v>
+        <v>180</v>
       </c>
       <c r="E132" t="s">
-        <v>180</v>
+        <v>137</v>
       </c>
       <c r="F132" t="s">
         <v>13</v>
@@ -6928,13 +6928,13 @@
         <v>7</v>
       </c>
       <c r="C134" t="s">
-        <v>159</v>
+        <v>183</v>
       </c>
       <c r="D134" t="s">
-        <v>136</v>
+        <v>160</v>
       </c>
       <c r="E134" t="s">
-        <v>183</v>
+        <v>137</v>
       </c>
       <c r="F134" t="s">
         <v>24</v>
@@ -6968,13 +6968,13 @@
         <v>7</v>
       </c>
       <c r="C136" t="s">
-        <v>159</v>
+        <v>186</v>
       </c>
       <c r="D136" t="s">
-        <v>136</v>
+        <v>160</v>
       </c>
       <c r="E136" t="s">
-        <v>186</v>
+        <v>137</v>
       </c>
       <c r="F136" t="s">
         <v>24</v>
@@ -7271,10 +7271,10 @@
         <v>205</v>
       </c>
       <c r="D151" t="s">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c r="E151" t="s">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="F151" t="s">
         <v>16</v>
@@ -7371,10 +7371,10 @@
         <v>212</v>
       </c>
       <c r="D156" t="s">
-        <v>196</v>
+        <v>213</v>
       </c>
       <c r="E156" t="s">
-        <v>213</v>
+        <v>197</v>
       </c>
       <c r="F156" t="s">
         <v>24</v>
@@ -7388,13 +7388,13 @@
         <v>110</v>
       </c>
       <c r="C157" t="s">
-        <v>195</v>
+        <v>212</v>
       </c>
       <c r="D157" t="s">
         <v>196</v>
       </c>
       <c r="E157" t="s">
-        <v>213</v>
+        <v>197</v>
       </c>
       <c r="F157" t="s">
         <v>24</v>
@@ -7468,10 +7468,10 @@
         <v>7</v>
       </c>
       <c r="C161" t="s">
+        <v>195</v>
+      </c>
+      <c r="D161" t="s">
         <v>219</v>
-      </c>
-      <c r="D161" t="s">
-        <v>196</v>
       </c>
       <c r="E161" t="s">
         <v>197</v>
@@ -7551,10 +7551,10 @@
         <v>224</v>
       </c>
       <c r="D165" t="s">
-        <v>196</v>
+        <v>225</v>
       </c>
       <c r="E165" t="s">
-        <v>225</v>
+        <v>197</v>
       </c>
       <c r="F165" t="s">
         <v>24</v>
@@ -7591,10 +7591,10 @@
         <v>228</v>
       </c>
       <c r="D167" t="s">
-        <v>196</v>
+        <v>229</v>
       </c>
       <c r="E167" t="s">
-        <v>229</v>
+        <v>197</v>
       </c>
       <c r="F167" t="s">
         <v>24</v>
@@ -7708,13 +7708,13 @@
         <v>7</v>
       </c>
       <c r="C173" t="s">
-        <v>195</v>
+        <v>236</v>
       </c>
       <c r="D173" t="s">
         <v>196</v>
       </c>
       <c r="E173" t="s">
-        <v>236</v>
+        <v>197</v>
       </c>
       <c r="F173" t="s">
         <v>16</v>
@@ -7728,13 +7728,13 @@
         <v>110</v>
       </c>
       <c r="C174" t="s">
+        <v>236</v>
+      </c>
+      <c r="D174" t="s">
         <v>238</v>
       </c>
-      <c r="D174" t="s">
-        <v>196</v>
-      </c>
       <c r="E174" t="s">
-        <v>236</v>
+        <v>197</v>
       </c>
       <c r="F174" t="s">
         <v>16</v>
@@ -7751,10 +7751,10 @@
         <v>240</v>
       </c>
       <c r="D175" t="s">
-        <v>196</v>
+        <v>241</v>
       </c>
       <c r="E175" t="s">
-        <v>241</v>
+        <v>197</v>
       </c>
       <c r="F175" t="s">
         <v>16</v>
@@ -7908,13 +7908,13 @@
         <v>7</v>
       </c>
       <c r="C183" t="s">
-        <v>195</v>
+        <v>250</v>
       </c>
       <c r="D183" t="s">
         <v>196</v>
       </c>
       <c r="E183" t="s">
-        <v>250</v>
+        <v>197</v>
       </c>
       <c r="F183" t="s">
         <v>16</v>
@@ -8008,13 +8008,13 @@
         <v>7</v>
       </c>
       <c r="C188" t="s">
-        <v>195</v>
+        <v>256</v>
       </c>
       <c r="D188" t="s">
         <v>196</v>
       </c>
       <c r="E188" t="s">
-        <v>256</v>
+        <v>197</v>
       </c>
       <c r="F188" t="s">
         <v>24</v>
@@ -8048,13 +8048,13 @@
         <v>7</v>
       </c>
       <c r="C190" t="s">
+        <v>256</v>
+      </c>
+      <c r="D190" t="s">
         <v>259</v>
       </c>
-      <c r="D190" t="s">
-        <v>196</v>
-      </c>
       <c r="E190" t="s">
-        <v>256</v>
+        <v>197</v>
       </c>
       <c r="F190" t="s">
         <v>13</v>
@@ -8128,13 +8128,13 @@
         <v>7</v>
       </c>
       <c r="C194" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="D194" t="s">
         <v>264</v>
       </c>
       <c r="E194" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F194" t="s">
         <v>19</v>
@@ -8148,13 +8148,13 @@
         <v>7</v>
       </c>
       <c r="C195" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="D195" t="s">
         <v>264</v>
       </c>
       <c r="E195" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F195" t="s">
         <v>13</v>
@@ -8168,13 +8168,13 @@
         <v>7</v>
       </c>
       <c r="C196" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="D196" t="s">
         <v>264</v>
       </c>
       <c r="E196" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F196" t="s">
         <v>19</v>
@@ -8188,13 +8188,13 @@
         <v>7</v>
       </c>
       <c r="C197" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="D197" t="s">
         <v>264</v>
       </c>
       <c r="E197" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F197" t="s">
         <v>19</v>
@@ -8208,13 +8208,13 @@
         <v>7</v>
       </c>
       <c r="C198" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="D198" t="s">
         <v>264</v>
       </c>
       <c r="E198" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F198" t="s">
         <v>13</v>
@@ -8228,13 +8228,13 @@
         <v>7</v>
       </c>
       <c r="C199" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="D199" t="s">
         <v>264</v>
       </c>
       <c r="E199" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F199" t="s">
         <v>19</v>
@@ -8248,13 +8248,13 @@
         <v>7</v>
       </c>
       <c r="C200" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="D200" t="s">
         <v>264</v>
       </c>
       <c r="E200" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F200" t="s">
         <v>19</v>
@@ -8268,13 +8268,13 @@
         <v>7</v>
       </c>
       <c r="C201" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="D201" t="s">
         <v>264</v>
       </c>
       <c r="E201" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F201" t="s">
         <v>19</v>
@@ -8288,13 +8288,13 @@
         <v>7</v>
       </c>
       <c r="C202" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="D202" t="s">
         <v>264</v>
       </c>
       <c r="E202" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F202" t="s">
         <v>19</v>
@@ -8308,13 +8308,13 @@
         <v>7</v>
       </c>
       <c r="C203" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="D203" t="s">
         <v>264</v>
       </c>
       <c r="E203" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F203" t="s">
         <v>19</v>
@@ -8328,13 +8328,13 @@
         <v>7</v>
       </c>
       <c r="C204" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="D204" t="s">
         <v>264</v>
       </c>
       <c r="E204" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F204" t="s">
         <v>13</v>
@@ -8348,13 +8348,13 @@
         <v>7</v>
       </c>
       <c r="C205" t="s">
-        <v>263</v>
+        <v>279</v>
       </c>
       <c r="D205" t="s">
         <v>264</v>
       </c>
       <c r="E205" t="s">
-        <v>279</v>
+        <v>265</v>
       </c>
       <c r="F205" t="s">
         <v>19</v>
@@ -8368,13 +8368,13 @@
         <v>110</v>
       </c>
       <c r="C206" t="s">
-        <v>195</v>
+        <v>279</v>
       </c>
       <c r="D206" t="s">
-        <v>264</v>
+        <v>196</v>
       </c>
       <c r="E206" t="s">
-        <v>279</v>
+        <v>265</v>
       </c>
       <c r="F206" t="s">
         <v>19</v>
@@ -8391,10 +8391,10 @@
         <v>282</v>
       </c>
       <c r="D207" t="s">
-        <v>264</v>
+        <v>283</v>
       </c>
       <c r="E207" t="s">
-        <v>283</v>
+        <v>265</v>
       </c>
       <c r="F207" t="s">
         <v>24</v>
@@ -8408,13 +8408,13 @@
         <v>7</v>
       </c>
       <c r="C208" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="D208" t="s">
         <v>264</v>
       </c>
       <c r="E208" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F208" t="s">
         <v>19</v>
@@ -8428,13 +8428,13 @@
         <v>7</v>
       </c>
       <c r="C209" t="s">
-        <v>263</v>
+        <v>279</v>
       </c>
       <c r="D209" t="s">
         <v>264</v>
       </c>
       <c r="E209" t="s">
-        <v>279</v>
+        <v>265</v>
       </c>
       <c r="F209" t="s">
         <v>19</v>
@@ -8448,13 +8448,13 @@
         <v>110</v>
       </c>
       <c r="C210" t="s">
-        <v>195</v>
+        <v>279</v>
       </c>
       <c r="D210" t="s">
-        <v>264</v>
+        <v>196</v>
       </c>
       <c r="E210" t="s">
-        <v>279</v>
+        <v>265</v>
       </c>
       <c r="F210" t="s">
         <v>19</v>
@@ -8471,10 +8471,10 @@
         <v>288</v>
       </c>
       <c r="D211" t="s">
-        <v>264</v>
+        <v>289</v>
       </c>
       <c r="E211" t="s">
-        <v>289</v>
+        <v>265</v>
       </c>
       <c r="F211" t="s">
         <v>24</v>
@@ -8488,13 +8488,13 @@
         <v>7</v>
       </c>
       <c r="C212" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="D212" t="s">
         <v>264</v>
       </c>
       <c r="E212" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F212" t="s">
         <v>19</v>
@@ -8511,10 +8511,10 @@
         <v>292</v>
       </c>
       <c r="D213" t="s">
-        <v>264</v>
+        <v>293</v>
       </c>
       <c r="E213" t="s">
-        <v>293</v>
+        <v>265</v>
       </c>
       <c r="F213" t="s">
         <v>24</v>
@@ -8528,13 +8528,13 @@
         <v>7</v>
       </c>
       <c r="C214" t="s">
-        <v>263</v>
+        <v>279</v>
       </c>
       <c r="D214" t="s">
         <v>264</v>
       </c>
       <c r="E214" t="s">
-        <v>279</v>
+        <v>265</v>
       </c>
       <c r="F214" t="s">
         <v>19</v>
@@ -8548,13 +8548,13 @@
         <v>110</v>
       </c>
       <c r="C215" t="s">
-        <v>195</v>
+        <v>279</v>
       </c>
       <c r="D215" t="s">
-        <v>264</v>
+        <v>196</v>
       </c>
       <c r="E215" t="s">
-        <v>279</v>
+        <v>265</v>
       </c>
       <c r="F215" t="s">
         <v>19</v>
@@ -8568,13 +8568,13 @@
         <v>7</v>
       </c>
       <c r="C216" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="D216" t="s">
         <v>264</v>
       </c>
       <c r="E216" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F216" t="s">
         <v>19</v>
@@ -8588,13 +8588,13 @@
         <v>7</v>
       </c>
       <c r="C217" t="s">
-        <v>263</v>
+        <v>298</v>
       </c>
       <c r="D217" t="s">
         <v>264</v>
       </c>
       <c r="E217" t="s">
-        <v>298</v>
+        <v>265</v>
       </c>
       <c r="F217" t="s">
         <v>24</v>
@@ -8611,10 +8611,10 @@
         <v>300</v>
       </c>
       <c r="D218" t="s">
-        <v>264</v>
+        <v>301</v>
       </c>
       <c r="E218" t="s">
-        <v>301</v>
+        <v>265</v>
       </c>
       <c r="F218" t="s">
         <v>16</v>
@@ -8628,13 +8628,13 @@
         <v>7</v>
       </c>
       <c r="C219" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="D219" t="s">
         <v>264</v>
       </c>
       <c r="E219" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F219" t="s">
         <v>19</v>
@@ -8648,13 +8648,13 @@
         <v>110</v>
       </c>
       <c r="C220" t="s">
-        <v>224</v>
+        <v>267</v>
       </c>
       <c r="D220" t="s">
-        <v>264</v>
+        <v>225</v>
       </c>
       <c r="E220" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F220" t="s">
         <v>24</v>
@@ -8668,13 +8668,13 @@
         <v>7</v>
       </c>
       <c r="C221" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="D221" t="s">
         <v>264</v>
       </c>
       <c r="E221" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F221" t="s">
         <v>24</v>
@@ -8688,13 +8688,13 @@
         <v>7</v>
       </c>
       <c r="C222" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="D222" t="s">
         <v>264</v>
       </c>
       <c r="E222" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F222" t="s">
         <v>19</v>
@@ -8708,13 +8708,13 @@
         <v>7</v>
       </c>
       <c r="C223" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="D223" t="s">
         <v>264</v>
       </c>
       <c r="E223" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F223" t="s">
         <v>19</v>
@@ -8728,13 +8728,13 @@
         <v>7</v>
       </c>
       <c r="C224" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="D224" t="s">
         <v>264</v>
       </c>
       <c r="E224" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F224" t="s">
         <v>19</v>
@@ -8748,13 +8748,13 @@
         <v>7</v>
       </c>
       <c r="C225" t="s">
-        <v>263</v>
+        <v>309</v>
       </c>
       <c r="D225" t="s">
         <v>264</v>
       </c>
       <c r="E225" t="s">
-        <v>309</v>
+        <v>265</v>
       </c>
       <c r="F225" t="s">
         <v>16</v>
@@ -8768,13 +8768,13 @@
         <v>7</v>
       </c>
       <c r="C226" t="s">
-        <v>263</v>
+        <v>311</v>
       </c>
       <c r="D226" t="s">
         <v>264</v>
       </c>
       <c r="E226" t="s">
-        <v>311</v>
+        <v>265</v>
       </c>
       <c r="F226" t="s">
         <v>16</v>
@@ -8788,13 +8788,13 @@
         <v>7</v>
       </c>
       <c r="C227" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="D227" t="s">
         <v>264</v>
       </c>
       <c r="E227" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F227" t="s">
         <v>19</v>
@@ -8808,13 +8808,13 @@
         <v>7</v>
       </c>
       <c r="C228" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="D228" t="s">
         <v>264</v>
       </c>
       <c r="E228" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F228" t="s">
         <v>19</v>
@@ -8828,13 +8828,13 @@
         <v>7</v>
       </c>
       <c r="C229" t="s">
-        <v>263</v>
+        <v>311</v>
       </c>
       <c r="D229" t="s">
         <v>264</v>
       </c>
       <c r="E229" t="s">
-        <v>311</v>
+        <v>265</v>
       </c>
       <c r="F229" t="s">
         <v>24</v>
@@ -8848,13 +8848,13 @@
         <v>110</v>
       </c>
       <c r="C230" t="s">
-        <v>263</v>
+        <v>311</v>
       </c>
       <c r="D230" t="s">
         <v>264</v>
       </c>
       <c r="E230" t="s">
-        <v>311</v>
+        <v>265</v>
       </c>
       <c r="F230" t="s">
         <v>16</v>
@@ -8868,13 +8868,13 @@
         <v>7</v>
       </c>
       <c r="C231" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="D231" t="s">
         <v>264</v>
       </c>
       <c r="E231" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F231" t="s">
         <v>19</v>
@@ -8888,13 +8888,13 @@
         <v>7</v>
       </c>
       <c r="C232" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="D232" t="s">
         <v>264</v>
       </c>
       <c r="E232" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F232" t="s">
         <v>19</v>
@@ -8908,13 +8908,13 @@
         <v>7</v>
       </c>
       <c r="C233" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="D233" t="s">
         <v>264</v>
       </c>
       <c r="E233" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F233" t="s">
         <v>13</v>
@@ -8928,13 +8928,13 @@
         <v>7</v>
       </c>
       <c r="C234" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="D234" t="s">
         <v>264</v>
       </c>
       <c r="E234" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F234" t="s">
         <v>13</v>
@@ -8948,13 +8948,13 @@
         <v>7</v>
       </c>
       <c r="C235" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="D235" t="s">
         <v>264</v>
       </c>
       <c r="E235" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F235" t="s">
         <v>19</v>
@@ -8968,13 +8968,13 @@
         <v>7</v>
       </c>
       <c r="C236" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="D236" t="s">
         <v>264</v>
       </c>
       <c r="E236" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F236" t="s">
         <v>19</v>
@@ -8988,13 +8988,13 @@
         <v>7</v>
       </c>
       <c r="C237" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="D237" t="s">
         <v>264</v>
       </c>
       <c r="E237" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F237" t="s">
         <v>13</v>
@@ -9008,13 +9008,13 @@
         <v>7</v>
       </c>
       <c r="C238" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="D238" t="s">
         <v>264</v>
       </c>
       <c r="E238" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F238" t="s">
         <v>19</v>
@@ -9028,13 +9028,13 @@
         <v>7</v>
       </c>
       <c r="C239" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="D239" t="s">
         <v>264</v>
       </c>
       <c r="E239" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F239" t="s">
         <v>19</v>
@@ -9048,13 +9048,13 @@
         <v>7</v>
       </c>
       <c r="C240" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="D240" t="s">
         <v>264</v>
       </c>
       <c r="E240" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F240" t="s">
         <v>13</v>
@@ -9068,13 +9068,13 @@
         <v>7</v>
       </c>
       <c r="C241" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="D241" t="s">
         <v>264</v>
       </c>
       <c r="E241" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F241" t="s">
         <v>19</v>
@@ -9088,13 +9088,13 @@
         <v>7</v>
       </c>
       <c r="C242" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="D242" t="s">
         <v>264</v>
       </c>
       <c r="E242" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F242" t="s">
         <v>19</v>
@@ -9108,13 +9108,13 @@
         <v>7</v>
       </c>
       <c r="C243" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="D243" t="s">
         <v>264</v>
       </c>
       <c r="E243" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F243" t="s">
         <v>19</v>
@@ -9128,13 +9128,13 @@
         <v>7</v>
       </c>
       <c r="C244" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="D244" t="s">
         <v>264</v>
       </c>
       <c r="E244" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F244" t="s">
         <v>19</v>
@@ -9168,13 +9168,13 @@
         <v>7</v>
       </c>
       <c r="C246" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="D246" t="s">
         <v>332</v>
       </c>
       <c r="E246" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="F246" t="s">
         <v>16</v>
@@ -9208,13 +9208,13 @@
         <v>7</v>
       </c>
       <c r="C248" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="D248" t="s">
         <v>332</v>
       </c>
       <c r="E248" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="F248" t="s">
         <v>16</v>
@@ -9288,13 +9288,13 @@
         <v>7</v>
       </c>
       <c r="C252" t="s">
-        <v>331</v>
+        <v>342</v>
       </c>
       <c r="D252" t="s">
         <v>332</v>
       </c>
       <c r="E252" t="s">
-        <v>342</v>
+        <v>333</v>
       </c>
       <c r="F252" t="s">
         <v>16</v>
@@ -9328,13 +9328,13 @@
         <v>7</v>
       </c>
       <c r="C254" t="s">
+        <v>345</v>
+      </c>
+      <c r="D254" t="s">
         <v>267</v>
       </c>
-      <c r="D254" t="s">
-        <v>332</v>
-      </c>
       <c r="E254" t="s">
-        <v>345</v>
+        <v>333</v>
       </c>
       <c r="F254" t="s">
         <v>19</v>
@@ -9388,13 +9388,13 @@
         <v>7</v>
       </c>
       <c r="C257" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="D257" t="s">
         <v>332</v>
       </c>
       <c r="E257" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="F257" t="s">
         <v>16</v>
@@ -9408,13 +9408,13 @@
         <v>7</v>
       </c>
       <c r="C258" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="D258" t="s">
         <v>332</v>
       </c>
       <c r="E258" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="F258" t="s">
         <v>16</v>
@@ -9428,13 +9428,13 @@
         <v>110</v>
       </c>
       <c r="C259" t="s">
-        <v>331</v>
+        <v>351</v>
       </c>
       <c r="D259" t="s">
         <v>332</v>
       </c>
       <c r="E259" t="s">
-        <v>351</v>
+        <v>333</v>
       </c>
       <c r="F259" t="s">
         <v>19</v>
@@ -9491,10 +9491,10 @@
         <v>355</v>
       </c>
       <c r="D262" t="s">
-        <v>332</v>
+        <v>356</v>
       </c>
       <c r="E262" t="s">
-        <v>356</v>
+        <v>333</v>
       </c>
       <c r="F262" t="s">
         <v>24</v>
@@ -9508,13 +9508,13 @@
         <v>7</v>
       </c>
       <c r="C263" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="D263" t="s">
         <v>332</v>
       </c>
       <c r="E263" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="F263" t="s">
         <v>16</v>
@@ -9528,13 +9528,13 @@
         <v>110</v>
       </c>
       <c r="C264" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="D264" t="s">
         <v>332</v>
       </c>
       <c r="E264" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="F264" t="s">
         <v>16</v>
@@ -9568,13 +9568,13 @@
         <v>7</v>
       </c>
       <c r="C266" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="D266" t="s">
         <v>332</v>
       </c>
       <c r="E266" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="F266" t="s">
         <v>16</v>
@@ -9608,13 +9608,13 @@
         <v>7</v>
       </c>
       <c r="C268" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="D268" t="s">
         <v>332</v>
       </c>
       <c r="E268" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="F268" t="s">
         <v>16</v>
@@ -9628,13 +9628,13 @@
         <v>7</v>
       </c>
       <c r="C269" t="s">
-        <v>331</v>
+        <v>351</v>
       </c>
       <c r="D269" t="s">
         <v>332</v>
       </c>
       <c r="E269" t="s">
-        <v>351</v>
+        <v>333</v>
       </c>
       <c r="F269" t="s">
         <v>16</v>
@@ -9648,13 +9648,13 @@
         <v>110</v>
       </c>
       <c r="C270" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="D270" t="s">
         <v>332</v>
       </c>
       <c r="E270" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="F270" t="s">
         <v>16</v>
@@ -9668,13 +9668,13 @@
         <v>7</v>
       </c>
       <c r="C271" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="D271" t="s">
         <v>332</v>
       </c>
       <c r="E271" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="F271" t="s">
         <v>16</v>
@@ -9708,13 +9708,13 @@
         <v>7</v>
       </c>
       <c r="C273" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="D273" t="s">
         <v>332</v>
       </c>
       <c r="E273" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="F273" t="s">
         <v>16</v>
@@ -9748,13 +9748,13 @@
         <v>7</v>
       </c>
       <c r="C275" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="D275" t="s">
         <v>332</v>
       </c>
       <c r="E275" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="F275" t="s">
         <v>16</v>
@@ -9768,13 +9768,13 @@
         <v>7</v>
       </c>
       <c r="C276" t="s">
-        <v>331</v>
+        <v>371</v>
       </c>
       <c r="D276" t="s">
         <v>332</v>
       </c>
       <c r="E276" t="s">
-        <v>371</v>
+        <v>333</v>
       </c>
       <c r="F276" t="s">
         <v>16</v>
@@ -9791,10 +9791,10 @@
         <v>373</v>
       </c>
       <c r="D277" t="s">
-        <v>332</v>
+        <v>374</v>
       </c>
       <c r="E277" t="s">
-        <v>374</v>
+        <v>333</v>
       </c>
       <c r="F277" t="s">
         <v>24</v>
@@ -9808,13 +9808,13 @@
         <v>7</v>
       </c>
       <c r="C278" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="D278" t="s">
         <v>332</v>
       </c>
       <c r="E278" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="F278" t="s">
         <v>16</v>
@@ -9831,10 +9831,10 @@
         <v>377</v>
       </c>
       <c r="D279" t="s">
-        <v>332</v>
+        <v>378</v>
       </c>
       <c r="E279" t="s">
-        <v>378</v>
+        <v>333</v>
       </c>
       <c r="F279" t="s">
         <v>24</v>
@@ -9848,13 +9848,13 @@
         <v>7</v>
       </c>
       <c r="C280" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="D280" t="s">
         <v>332</v>
       </c>
       <c r="E280" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="F280" t="s">
         <v>16</v>
@@ -9908,13 +9908,13 @@
         <v>7</v>
       </c>
       <c r="C283" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="D283" t="s">
         <v>332</v>
       </c>
       <c r="E283" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="F283" t="s">
         <v>16</v>
@@ -10008,13 +10008,13 @@
         <v>7</v>
       </c>
       <c r="C288" t="s">
-        <v>331</v>
+        <v>371</v>
       </c>
       <c r="D288" t="s">
         <v>332</v>
       </c>
       <c r="E288" t="s">
-        <v>371</v>
+        <v>333</v>
       </c>
       <c r="F288" t="s">
         <v>16</v>
@@ -10028,13 +10028,13 @@
         <v>7</v>
       </c>
       <c r="C289" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="D289" t="s">
         <v>332</v>
       </c>
       <c r="E289" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="F289" t="s">
         <v>16</v>
@@ -10088,13 +10088,13 @@
         <v>7</v>
       </c>
       <c r="C292" t="s">
-        <v>331</v>
+        <v>371</v>
       </c>
       <c r="D292" t="s">
         <v>332</v>
       </c>
       <c r="E292" t="s">
-        <v>371</v>
+        <v>333</v>
       </c>
       <c r="F292" t="s">
         <v>16</v>
@@ -10108,13 +10108,13 @@
         <v>7</v>
       </c>
       <c r="C293" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="D293" t="s">
         <v>332</v>
       </c>
       <c r="E293" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="F293" t="s">
         <v>16</v>
@@ -10248,13 +10248,13 @@
         <v>7</v>
       </c>
       <c r="C300" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="D300" t="s">
         <v>332</v>
       </c>
       <c r="E300" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="F300" t="s">
         <v>16</v>
@@ -10268,13 +10268,13 @@
         <v>7</v>
       </c>
       <c r="C301" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="D301" t="s">
         <v>332</v>
       </c>
       <c r="E301" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="F301" t="s">
         <v>16</v>
@@ -10288,13 +10288,13 @@
         <v>7</v>
       </c>
       <c r="C302" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="D302" t="s">
         <v>332</v>
       </c>
       <c r="E302" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="F302" t="s">
         <v>16</v>
@@ -10328,13 +10328,13 @@
         <v>7</v>
       </c>
       <c r="C304" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="D304" t="s">
         <v>332</v>
       </c>
       <c r="E304" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="F304" t="s">
         <v>16</v>
@@ -10388,13 +10388,13 @@
         <v>7</v>
       </c>
       <c r="C307" t="s">
-        <v>355</v>
+        <v>407</v>
       </c>
       <c r="D307" t="s">
-        <v>332</v>
+        <v>356</v>
       </c>
       <c r="E307" t="s">
-        <v>407</v>
+        <v>333</v>
       </c>
       <c r="F307" t="s">
         <v>16</v>
@@ -10408,13 +10408,13 @@
         <v>7</v>
       </c>
       <c r="C308" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="D308" t="s">
         <v>332</v>
       </c>
       <c r="E308" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="F308" t="s">
         <v>16</v>
@@ -10708,13 +10708,13 @@
         <v>7</v>
       </c>
       <c r="C323" t="s">
-        <v>411</v>
+        <v>427</v>
       </c>
       <c r="D323" t="s">
         <v>412</v>
       </c>
       <c r="E323" t="s">
-        <v>427</v>
+        <v>413</v>
       </c>
       <c r="F323" t="s">
         <v>16</v>
@@ -10748,10 +10748,10 @@
         <v>7</v>
       </c>
       <c r="C325" t="s">
+        <v>411</v>
+      </c>
+      <c r="D325" t="s">
         <v>430</v>
-      </c>
-      <c r="D325" t="s">
-        <v>412</v>
       </c>
       <c r="E325" t="s">
         <v>413</v>
@@ -10868,10 +10868,10 @@
         <v>7</v>
       </c>
       <c r="C331" t="s">
+        <v>411</v>
+      </c>
+      <c r="D331" t="s">
         <v>437</v>
-      </c>
-      <c r="D331" t="s">
-        <v>412</v>
       </c>
       <c r="E331" t="s">
         <v>413</v>
@@ -11111,10 +11111,10 @@
         <v>450</v>
       </c>
       <c r="D343" t="s">
-        <v>412</v>
+        <v>451</v>
       </c>
       <c r="E343" t="s">
-        <v>451</v>
+        <v>413</v>
       </c>
       <c r="F343" t="s">
         <v>24</v>
@@ -11128,13 +11128,13 @@
         <v>110</v>
       </c>
       <c r="C344" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="D344" t="s">
-        <v>412</v>
+        <v>451</v>
       </c>
       <c r="E344" t="s">
-        <v>453</v>
+        <v>413</v>
       </c>
       <c r="F344" t="s">
         <v>24</v>
@@ -11168,13 +11168,13 @@
         <v>110</v>
       </c>
       <c r="C346" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="D346" t="s">
         <v>456</v>
       </c>
       <c r="E346" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="F346" t="s">
         <v>16</v>
@@ -11368,13 +11368,13 @@
         <v>7</v>
       </c>
       <c r="C356" t="s">
-        <v>455</v>
+        <v>470</v>
       </c>
       <c r="D356" t="s">
         <v>456</v>
       </c>
       <c r="E356" t="s">
-        <v>470</v>
+        <v>457</v>
       </c>
       <c r="F356" t="s">
         <v>16</v>
@@ -11568,13 +11568,13 @@
         <v>7</v>
       </c>
       <c r="C366" t="s">
-        <v>455</v>
+        <v>481</v>
       </c>
       <c r="D366" t="s">
         <v>456</v>
       </c>
       <c r="E366" t="s">
-        <v>481</v>
+        <v>457</v>
       </c>
       <c r="F366" t="s">
         <v>16</v>
@@ -11588,13 +11588,13 @@
         <v>7</v>
       </c>
       <c r="C367" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="D367" t="s">
         <v>456</v>
       </c>
       <c r="E367" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="F367" t="s">
         <v>13</v>
@@ -11668,10 +11668,10 @@
         <v>7</v>
       </c>
       <c r="C371" t="s">
+        <v>455</v>
+      </c>
+      <c r="D371" t="s">
         <v>487</v>
-      </c>
-      <c r="D371" t="s">
-        <v>456</v>
       </c>
       <c r="E371" t="s">
         <v>457</v>
@@ -11691,10 +11691,10 @@
         <v>489</v>
       </c>
       <c r="D372" t="s">
-        <v>456</v>
+        <v>490</v>
       </c>
       <c r="E372" t="s">
-        <v>490</v>
+        <v>457</v>
       </c>
       <c r="F372" t="s">
         <v>19</v>
@@ -11731,10 +11731,10 @@
         <v>489</v>
       </c>
       <c r="D374" t="s">
-        <v>456</v>
+        <v>490</v>
       </c>
       <c r="E374" t="s">
-        <v>490</v>
+        <v>457</v>
       </c>
       <c r="F374" t="s">
         <v>19</v>
@@ -11848,13 +11848,13 @@
         <v>7</v>
       </c>
       <c r="C380" t="s">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="D380" t="s">
         <v>498</v>
       </c>
       <c r="E380" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="F380" t="s">
         <v>13</v>
@@ -11968,13 +11968,13 @@
         <v>7</v>
       </c>
       <c r="C386" t="s">
-        <v>497</v>
+        <v>509</v>
       </c>
       <c r="D386" t="s">
         <v>498</v>
       </c>
       <c r="E386" t="s">
-        <v>509</v>
+        <v>499</v>
       </c>
       <c r="F386" t="s">
         <v>16</v>
@@ -11988,13 +11988,13 @@
         <v>7</v>
       </c>
       <c r="C387" t="s">
-        <v>497</v>
+        <v>511</v>
       </c>
       <c r="D387" t="s">
         <v>498</v>
       </c>
       <c r="E387" t="s">
-        <v>511</v>
+        <v>499</v>
       </c>
       <c r="F387" t="s">
         <v>19</v>
@@ -12031,10 +12031,10 @@
         <v>514</v>
       </c>
       <c r="D389" t="s">
-        <v>498</v>
+        <v>515</v>
       </c>
       <c r="E389" t="s">
-        <v>515</v>
+        <v>499</v>
       </c>
       <c r="F389" t="s">
         <v>24</v>
@@ -12108,13 +12108,13 @@
         <v>7</v>
       </c>
       <c r="C393" t="s">
-        <v>497</v>
+        <v>520</v>
       </c>
       <c r="D393" t="s">
         <v>498</v>
       </c>
       <c r="E393" t="s">
-        <v>520</v>
+        <v>499</v>
       </c>
       <c r="F393" t="s">
         <v>16</v>
@@ -12151,10 +12151,10 @@
         <v>523</v>
       </c>
       <c r="D395" t="s">
-        <v>498</v>
+        <v>524</v>
       </c>
       <c r="E395" t="s">
-        <v>524</v>
+        <v>499</v>
       </c>
       <c r="F395" t="s">
         <v>24</v>
@@ -12191,10 +12191,10 @@
         <v>527</v>
       </c>
       <c r="D397" t="s">
-        <v>498</v>
+        <v>528</v>
       </c>
       <c r="E397" t="s">
-        <v>528</v>
+        <v>499</v>
       </c>
       <c r="F397" t="s">
         <v>24</v>
@@ -12251,10 +12251,10 @@
         <v>532</v>
       </c>
       <c r="D400" t="s">
-        <v>498</v>
+        <v>533</v>
       </c>
       <c r="E400" t="s">
-        <v>533</v>
+        <v>499</v>
       </c>
       <c r="F400" t="s">
         <v>24</v>
@@ -12371,10 +12371,10 @@
         <v>540</v>
       </c>
       <c r="D406" t="s">
-        <v>498</v>
+        <v>541</v>
       </c>
       <c r="E406" t="s">
-        <v>541</v>
+        <v>499</v>
       </c>
       <c r="F406" t="s">
         <v>24</v>
@@ -12388,13 +12388,13 @@
         <v>7</v>
       </c>
       <c r="C407" t="s">
-        <v>497</v>
+        <v>543</v>
       </c>
       <c r="D407" t="s">
         <v>498</v>
       </c>
       <c r="E407" t="s">
-        <v>543</v>
+        <v>499</v>
       </c>
       <c r="F407" t="s">
         <v>19</v>
@@ -12628,13 +12628,13 @@
         <v>7</v>
       </c>
       <c r="C419" t="s">
-        <v>554</v>
+        <v>559</v>
       </c>
       <c r="D419" t="s">
         <v>555</v>
       </c>
       <c r="E419" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="F419" t="s">
         <v>24</v>
@@ -12668,13 +12668,13 @@
         <v>7</v>
       </c>
       <c r="C421" t="s">
-        <v>554</v>
+        <v>562</v>
       </c>
       <c r="D421" t="s">
         <v>555</v>
       </c>
       <c r="E421" t="s">
-        <v>562</v>
+        <v>556</v>
       </c>
       <c r="F421" t="s">
         <v>19</v>
@@ -12811,10 +12811,10 @@
         <v>570</v>
       </c>
       <c r="D428" t="s">
-        <v>555</v>
+        <v>571</v>
       </c>
       <c r="E428" t="s">
-        <v>571</v>
+        <v>556</v>
       </c>
       <c r="F428" t="s">
         <v>24</v>
@@ -12831,10 +12831,10 @@
         <v>573</v>
       </c>
       <c r="D429" t="s">
-        <v>555</v>
+        <v>574</v>
       </c>
       <c r="E429" t="s">
-        <v>574</v>
+        <v>556</v>
       </c>
       <c r="F429" t="s">
         <v>24</v>
@@ -12908,13 +12908,13 @@
         <v>7</v>
       </c>
       <c r="C433" t="s">
-        <v>554</v>
+        <v>579</v>
       </c>
       <c r="D433" t="s">
         <v>555</v>
       </c>
       <c r="E433" t="s">
-        <v>579</v>
+        <v>556</v>
       </c>
       <c r="F433" t="s">
         <v>24</v>
@@ -12968,13 +12968,13 @@
         <v>7</v>
       </c>
       <c r="C436" t="s">
-        <v>554</v>
+        <v>583</v>
       </c>
       <c r="D436" t="s">
         <v>555</v>
       </c>
       <c r="E436" t="s">
-        <v>583</v>
+        <v>556</v>
       </c>
       <c r="F436" t="s">
         <v>24</v>
@@ -12988,13 +12988,13 @@
         <v>7</v>
       </c>
       <c r="C437" t="s">
-        <v>554</v>
+        <v>585</v>
       </c>
       <c r="D437" t="s">
         <v>555</v>
       </c>
       <c r="E437" t="s">
-        <v>585</v>
+        <v>556</v>
       </c>
       <c r="F437" t="s">
         <v>19</v>
@@ -13051,10 +13051,10 @@
         <v>589</v>
       </c>
       <c r="D440" t="s">
-        <v>555</v>
+        <v>590</v>
       </c>
       <c r="E440" t="s">
-        <v>590</v>
+        <v>556</v>
       </c>
       <c r="F440" t="s">
         <v>24</v>
@@ -13331,10 +13331,10 @@
         <v>605</v>
       </c>
       <c r="D454" t="s">
-        <v>555</v>
+        <v>606</v>
       </c>
       <c r="E454" t="s">
-        <v>606</v>
+        <v>556</v>
       </c>
       <c r="F454" t="s">
         <v>19</v>
@@ -13531,10 +13531,10 @@
         <v>621</v>
       </c>
       <c r="D464" t="s">
-        <v>609</v>
+        <v>622</v>
       </c>
       <c r="E464" t="s">
-        <v>622</v>
+        <v>610</v>
       </c>
       <c r="F464" t="s">
         <v>24</v>
@@ -13548,13 +13548,13 @@
         <v>7</v>
       </c>
       <c r="C465" t="s">
-        <v>608</v>
+        <v>624</v>
       </c>
       <c r="D465" t="s">
         <v>609</v>
       </c>
       <c r="E465" t="s">
-        <v>624</v>
+        <v>610</v>
       </c>
       <c r="F465" t="s">
         <v>24</v>
@@ -13568,13 +13568,13 @@
         <v>7</v>
       </c>
       <c r="C466" t="s">
-        <v>621</v>
+        <v>626</v>
       </c>
       <c r="D466" t="s">
-        <v>609</v>
+        <v>622</v>
       </c>
       <c r="E466" t="s">
-        <v>626</v>
+        <v>610</v>
       </c>
       <c r="F466" t="s">
         <v>24</v>
@@ -13591,10 +13591,10 @@
         <v>628</v>
       </c>
       <c r="D467" t="s">
-        <v>609</v>
+        <v>629</v>
       </c>
       <c r="E467" t="s">
-        <v>629</v>
+        <v>610</v>
       </c>
       <c r="F467" t="s">
         <v>24</v>
@@ -13631,10 +13631,10 @@
         <v>632</v>
       </c>
       <c r="D469" t="s">
-        <v>609</v>
+        <v>633</v>
       </c>
       <c r="E469" t="s">
-        <v>633</v>
+        <v>610</v>
       </c>
       <c r="F469" t="s">
         <v>24</v>
@@ -13708,13 +13708,13 @@
         <v>7</v>
       </c>
       <c r="C473" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="D473" t="s">
-        <v>609</v>
+        <v>622</v>
       </c>
       <c r="E473" t="s">
-        <v>638</v>
+        <v>610</v>
       </c>
       <c r="F473" t="s">
         <v>24</v>
@@ -14008,13 +14008,13 @@
         <v>7</v>
       </c>
       <c r="C488" t="s">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="D488" t="s">
         <v>654</v>
       </c>
       <c r="E488" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="F488" t="s">
         <v>611</v>
@@ -14088,10 +14088,10 @@
         <v>110</v>
       </c>
       <c r="C492" t="s">
+        <v>653</v>
+      </c>
+      <c r="D492" t="s">
         <v>662</v>
-      </c>
-      <c r="D492" t="s">
-        <v>654</v>
       </c>
       <c r="E492" t="s">
         <v>655</v>
@@ -14128,13 +14128,13 @@
         <v>7</v>
       </c>
       <c r="C494" t="s">
+        <v>632</v>
+      </c>
+      <c r="D494" t="s">
         <v>665</v>
       </c>
-      <c r="D494" t="s">
-        <v>654</v>
-      </c>
       <c r="E494" t="s">
-        <v>633</v>
+        <v>655</v>
       </c>
       <c r="F494" t="s">
         <v>13</v>
@@ -14148,13 +14148,13 @@
         <v>110</v>
       </c>
       <c r="C495" t="s">
+        <v>632</v>
+      </c>
+      <c r="D495" t="s">
         <v>665</v>
       </c>
-      <c r="D495" t="s">
-        <v>654</v>
-      </c>
       <c r="E495" t="s">
-        <v>633</v>
+        <v>655</v>
       </c>
       <c r="F495" t="s">
         <v>16</v>
@@ -14208,13 +14208,13 @@
         <v>7</v>
       </c>
       <c r="C498" t="s">
-        <v>653</v>
+        <v>670</v>
       </c>
       <c r="D498" t="s">
         <v>654</v>
       </c>
       <c r="E498" t="s">
-        <v>670</v>
+        <v>655</v>
       </c>
       <c r="F498" t="s">
         <v>611</v>
@@ -14288,13 +14288,13 @@
         <v>110</v>
       </c>
       <c r="C502" t="s">
-        <v>653</v>
+        <v>675</v>
       </c>
       <c r="D502" t="s">
         <v>654</v>
       </c>
       <c r="E502" t="s">
-        <v>675</v>
+        <v>655</v>
       </c>
       <c r="F502" t="s">
         <v>19</v>
@@ -14391,10 +14391,10 @@
         <v>681</v>
       </c>
       <c r="D507" t="s">
-        <v>654</v>
+        <v>682</v>
       </c>
       <c r="E507" t="s">
-        <v>682</v>
+        <v>655</v>
       </c>
       <c r="F507" t="s">
         <v>24</v>
@@ -14411,10 +14411,10 @@
         <v>684</v>
       </c>
       <c r="D508" t="s">
-        <v>654</v>
+        <v>685</v>
       </c>
       <c r="E508" t="s">
-        <v>685</v>
+        <v>655</v>
       </c>
       <c r="F508" t="s">
         <v>611</v>
@@ -14428,13 +14428,13 @@
         <v>110</v>
       </c>
       <c r="C509" t="s">
+        <v>684</v>
+      </c>
+      <c r="D509" t="s">
         <v>687</v>
       </c>
-      <c r="D509" t="s">
-        <v>654</v>
-      </c>
       <c r="E509" t="s">
-        <v>685</v>
+        <v>655</v>
       </c>
       <c r="F509" t="s">
         <v>19</v>
@@ -14451,10 +14451,10 @@
         <v>689</v>
       </c>
       <c r="D510" t="s">
-        <v>654</v>
+        <v>690</v>
       </c>
       <c r="E510" t="s">
-        <v>690</v>
+        <v>655</v>
       </c>
       <c r="F510" t="s">
         <v>24</v>
@@ -14488,13 +14488,13 @@
         <v>7</v>
       </c>
       <c r="C512" t="s">
-        <v>653</v>
+        <v>693</v>
       </c>
       <c r="D512" t="s">
         <v>654</v>
       </c>
       <c r="E512" t="s">
-        <v>693</v>
+        <v>655</v>
       </c>
       <c r="F512" t="s">
         <v>16</v>
@@ -14508,10 +14508,10 @@
         <v>110</v>
       </c>
       <c r="C513" t="s">
+        <v>653</v>
+      </c>
+      <c r="D513" t="s">
         <v>695</v>
-      </c>
-      <c r="D513" t="s">
-        <v>654</v>
       </c>
       <c r="E513" t="s">
         <v>655</v>
@@ -14668,13 +14668,13 @@
         <v>110</v>
       </c>
       <c r="C521" t="s">
-        <v>653</v>
+        <v>704</v>
       </c>
       <c r="D521" t="s">
         <v>654</v>
       </c>
       <c r="E521" t="s">
-        <v>704</v>
+        <v>655</v>
       </c>
       <c r="F521" t="s">
         <v>19</v>
@@ -14688,13 +14688,13 @@
         <v>110</v>
       </c>
       <c r="C522" t="s">
-        <v>653</v>
+        <v>706</v>
       </c>
       <c r="D522" t="s">
         <v>654</v>
       </c>
       <c r="E522" t="s">
-        <v>706</v>
+        <v>655</v>
       </c>
       <c r="F522" t="s">
         <v>13</v>
@@ -14708,13 +14708,13 @@
         <v>7</v>
       </c>
       <c r="C523" t="s">
-        <v>653</v>
+        <v>708</v>
       </c>
       <c r="D523" t="s">
         <v>654</v>
       </c>
       <c r="E523" t="s">
-        <v>708</v>
+        <v>655</v>
       </c>
       <c r="F523" t="s">
         <v>24</v>
@@ -14748,13 +14748,13 @@
         <v>7</v>
       </c>
       <c r="C525" t="s">
+        <v>657</v>
+      </c>
+      <c r="D525" t="s">
         <v>711</v>
       </c>
-      <c r="D525" t="s">
+      <c r="E525" t="s">
         <v>712</v>
-      </c>
-      <c r="E525" t="s">
-        <v>657</v>
       </c>
       <c r="F525" t="s">
         <v>713</v>
@@ -14768,13 +14768,13 @@
         <v>7</v>
       </c>
       <c r="C526" t="s">
+        <v>657</v>
+      </c>
+      <c r="D526" t="s">
         <v>711</v>
       </c>
-      <c r="D526" t="s">
+      <c r="E526" t="s">
         <v>712</v>
-      </c>
-      <c r="E526" t="s">
-        <v>657</v>
       </c>
       <c r="F526" t="s">
         <v>713</v>
@@ -14788,13 +14788,13 @@
         <v>7</v>
       </c>
       <c r="C527" t="s">
+        <v>657</v>
+      </c>
+      <c r="D527" t="s">
         <v>711</v>
       </c>
-      <c r="D527" t="s">
+      <c r="E527" t="s">
         <v>712</v>
-      </c>
-      <c r="E527" t="s">
-        <v>657</v>
       </c>
       <c r="F527" t="s">
         <v>713</v>
@@ -14808,13 +14808,13 @@
         <v>7</v>
       </c>
       <c r="C528" t="s">
+        <v>657</v>
+      </c>
+      <c r="D528" t="s">
         <v>711</v>
       </c>
-      <c r="D528" t="s">
+      <c r="E528" t="s">
         <v>712</v>
-      </c>
-      <c r="E528" t="s">
-        <v>657</v>
       </c>
       <c r="F528" t="s">
         <v>713</v>
@@ -14828,13 +14828,13 @@
         <v>7</v>
       </c>
       <c r="C529" t="s">
+        <v>718</v>
+      </c>
+      <c r="D529" t="s">
         <v>711</v>
       </c>
-      <c r="D529" t="s">
+      <c r="E529" t="s">
         <v>712</v>
-      </c>
-      <c r="E529" t="s">
-        <v>718</v>
       </c>
       <c r="F529" t="s">
         <v>16</v>
@@ -14848,13 +14848,13 @@
         <v>7</v>
       </c>
       <c r="C530" t="s">
+        <v>657</v>
+      </c>
+      <c r="D530" t="s">
         <v>720</v>
       </c>
-      <c r="D530" t="s">
+      <c r="E530" t="s">
         <v>712</v>
-      </c>
-      <c r="E530" t="s">
-        <v>657</v>
       </c>
       <c r="F530" t="s">
         <v>713</v>
@@ -14868,13 +14868,13 @@
         <v>7</v>
       </c>
       <c r="C531" t="s">
+        <v>657</v>
+      </c>
+      <c r="D531" t="s">
         <v>711</v>
       </c>
-      <c r="D531" t="s">
+      <c r="E531" t="s">
         <v>712</v>
-      </c>
-      <c r="E531" t="s">
-        <v>657</v>
       </c>
       <c r="F531" t="s">
         <v>713</v>
@@ -14888,13 +14888,13 @@
         <v>7</v>
       </c>
       <c r="C532" t="s">
+        <v>657</v>
+      </c>
+      <c r="D532" t="s">
         <v>711</v>
       </c>
-      <c r="D532" t="s">
+      <c r="E532" t="s">
         <v>712</v>
-      </c>
-      <c r="E532" t="s">
-        <v>657</v>
       </c>
       <c r="F532" t="s">
         <v>713</v>
@@ -14908,13 +14908,13 @@
         <v>7</v>
       </c>
       <c r="C533" t="s">
+        <v>657</v>
+      </c>
+      <c r="D533" t="s">
         <v>711</v>
       </c>
-      <c r="D533" t="s">
+      <c r="E533" t="s">
         <v>712</v>
-      </c>
-      <c r="E533" t="s">
-        <v>657</v>
       </c>
       <c r="F533" t="s">
         <v>713</v>
@@ -14928,13 +14928,13 @@
         <v>7</v>
       </c>
       <c r="C534" t="s">
+        <v>657</v>
+      </c>
+      <c r="D534" t="s">
         <v>711</v>
       </c>
-      <c r="D534" t="s">
+      <c r="E534" t="s">
         <v>712</v>
-      </c>
-      <c r="E534" t="s">
-        <v>657</v>
       </c>
       <c r="F534" t="s">
         <v>713</v>
@@ -14948,13 +14948,13 @@
         <v>7</v>
       </c>
       <c r="C535" t="s">
+        <v>657</v>
+      </c>
+      <c r="D535" t="s">
         <v>711</v>
       </c>
-      <c r="D535" t="s">
+      <c r="E535" t="s">
         <v>712</v>
-      </c>
-      <c r="E535" t="s">
-        <v>657</v>
       </c>
       <c r="F535" t="s">
         <v>713</v>
@@ -14968,13 +14968,13 @@
         <v>7</v>
       </c>
       <c r="C536" t="s">
+        <v>727</v>
+      </c>
+      <c r="D536" t="s">
         <v>711</v>
       </c>
-      <c r="D536" t="s">
+      <c r="E536" t="s">
         <v>712</v>
-      </c>
-      <c r="E536" t="s">
-        <v>727</v>
       </c>
       <c r="F536" t="s">
         <v>16</v>
@@ -14988,13 +14988,13 @@
         <v>7</v>
       </c>
       <c r="C537" t="s">
+        <v>729</v>
+      </c>
+      <c r="D537" t="s">
         <v>711</v>
       </c>
-      <c r="D537" t="s">
+      <c r="E537" t="s">
         <v>712</v>
-      </c>
-      <c r="E537" t="s">
-        <v>729</v>
       </c>
       <c r="F537" t="s">
         <v>16</v>
@@ -15008,13 +15008,13 @@
         <v>7</v>
       </c>
       <c r="C538" t="s">
+        <v>657</v>
+      </c>
+      <c r="D538" t="s">
         <v>711</v>
       </c>
-      <c r="D538" t="s">
+      <c r="E538" t="s">
         <v>712</v>
-      </c>
-      <c r="E538" t="s">
-        <v>657</v>
       </c>
       <c r="F538" t="s">
         <v>713</v>
@@ -15028,13 +15028,13 @@
         <v>7</v>
       </c>
       <c r="C539" t="s">
+        <v>657</v>
+      </c>
+      <c r="D539" t="s">
         <v>711</v>
       </c>
-      <c r="D539" t="s">
+      <c r="E539" t="s">
         <v>712</v>
-      </c>
-      <c r="E539" t="s">
-        <v>657</v>
       </c>
       <c r="F539" t="s">
         <v>713</v>
@@ -15048,13 +15048,13 @@
         <v>7</v>
       </c>
       <c r="C540" t="s">
-        <v>689</v>
+        <v>657</v>
       </c>
       <c r="D540" t="s">
+        <v>690</v>
+      </c>
+      <c r="E540" t="s">
         <v>712</v>
-      </c>
-      <c r="E540" t="s">
-        <v>657</v>
       </c>
       <c r="F540" t="s">
         <v>713</v>
@@ -15068,13 +15068,13 @@
         <v>7</v>
       </c>
       <c r="C541" t="s">
+        <v>657</v>
+      </c>
+      <c r="D541" t="s">
         <v>711</v>
       </c>
-      <c r="D541" t="s">
+      <c r="E541" t="s">
         <v>712</v>
-      </c>
-      <c r="E541" t="s">
-        <v>657</v>
       </c>
       <c r="F541" t="s">
         <v>713</v>
@@ -15088,13 +15088,13 @@
         <v>7</v>
       </c>
       <c r="C542" t="s">
+        <v>657</v>
+      </c>
+      <c r="D542" t="s">
         <v>711</v>
       </c>
-      <c r="D542" t="s">
+      <c r="E542" t="s">
         <v>712</v>
-      </c>
-      <c r="E542" t="s">
-        <v>657</v>
       </c>
       <c r="F542" t="s">
         <v>713</v>
@@ -15108,13 +15108,13 @@
         <v>7</v>
       </c>
       <c r="C543" t="s">
+        <v>657</v>
+      </c>
+      <c r="D543" t="s">
         <v>711</v>
       </c>
-      <c r="D543" t="s">
+      <c r="E543" t="s">
         <v>712</v>
-      </c>
-      <c r="E543" t="s">
-        <v>657</v>
       </c>
       <c r="F543" t="s">
         <v>713</v>
@@ -15128,13 +15128,13 @@
         <v>7</v>
       </c>
       <c r="C544" t="s">
+        <v>657</v>
+      </c>
+      <c r="D544" t="s">
         <v>711</v>
       </c>
-      <c r="D544" t="s">
+      <c r="E544" t="s">
         <v>712</v>
-      </c>
-      <c r="E544" t="s">
-        <v>657</v>
       </c>
       <c r="F544" t="s">
         <v>713</v>
@@ -15148,13 +15148,13 @@
         <v>7</v>
       </c>
       <c r="C545" t="s">
+        <v>657</v>
+      </c>
+      <c r="D545" t="s">
         <v>738</v>
       </c>
-      <c r="D545" t="s">
+      <c r="E545" t="s">
         <v>712</v>
-      </c>
-      <c r="E545" t="s">
-        <v>657</v>
       </c>
       <c r="F545" t="s">
         <v>13</v>
@@ -15168,13 +15168,13 @@
         <v>7</v>
       </c>
       <c r="C546" t="s">
+        <v>657</v>
+      </c>
+      <c r="D546" t="s">
         <v>711</v>
       </c>
-      <c r="D546" t="s">
+      <c r="E546" t="s">
         <v>712</v>
-      </c>
-      <c r="E546" t="s">
-        <v>657</v>
       </c>
       <c r="F546" t="s">
         <v>713</v>
@@ -15188,13 +15188,13 @@
         <v>7</v>
       </c>
       <c r="C547" t="s">
+        <v>657</v>
+      </c>
+      <c r="D547" t="s">
         <v>711</v>
       </c>
-      <c r="D547" t="s">
+      <c r="E547" t="s">
         <v>712</v>
-      </c>
-      <c r="E547" t="s">
-        <v>657</v>
       </c>
       <c r="F547" t="s">
         <v>16</v>
@@ -15228,13 +15228,13 @@
         <v>7</v>
       </c>
       <c r="C549" t="s">
-        <v>742</v>
+        <v>746</v>
       </c>
       <c r="D549" t="s">
         <v>743</v>
       </c>
       <c r="E549" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="F549" t="s">
         <v>713</v>
@@ -15248,13 +15248,13 @@
         <v>7</v>
       </c>
       <c r="C550" t="s">
-        <v>742</v>
+        <v>748</v>
       </c>
       <c r="D550" t="s">
         <v>743</v>
       </c>
       <c r="E550" t="s">
-        <v>748</v>
+        <v>744</v>
       </c>
       <c r="F550" t="s">
         <v>713</v>
@@ -15328,10 +15328,10 @@
         <v>7</v>
       </c>
       <c r="C554" t="s">
+        <v>742</v>
+      </c>
+      <c r="D554" t="s">
         <v>753</v>
-      </c>
-      <c r="D554" t="s">
-        <v>743</v>
       </c>
       <c r="E554" t="s">
         <v>744</v>
@@ -15411,10 +15411,10 @@
         <v>758</v>
       </c>
       <c r="D558" t="s">
-        <v>743</v>
+        <v>759</v>
       </c>
       <c r="E558" t="s">
-        <v>759</v>
+        <v>744</v>
       </c>
       <c r="F558" t="s">
         <v>24</v>
@@ -15448,13 +15448,13 @@
         <v>7</v>
       </c>
       <c r="C560" t="s">
-        <v>742</v>
+        <v>762</v>
       </c>
       <c r="D560" t="s">
         <v>743</v>
       </c>
       <c r="E560" t="s">
-        <v>762</v>
+        <v>744</v>
       </c>
       <c r="F560" t="s">
         <v>713</v>
@@ -15468,13 +15468,13 @@
         <v>7</v>
       </c>
       <c r="C561" t="s">
-        <v>742</v>
+        <v>762</v>
       </c>
       <c r="D561" t="s">
         <v>743</v>
       </c>
       <c r="E561" t="s">
-        <v>762</v>
+        <v>744</v>
       </c>
       <c r="F561" t="s">
         <v>713</v>
@@ -15508,10 +15508,10 @@
         <v>7</v>
       </c>
       <c r="C563" t="s">
+        <v>742</v>
+      </c>
+      <c r="D563" t="s">
         <v>766</v>
-      </c>
-      <c r="D563" t="s">
-        <v>743</v>
       </c>
       <c r="E563" t="s">
         <v>744</v>
@@ -15631,10 +15631,10 @@
         <v>773</v>
       </c>
       <c r="D569" t="s">
-        <v>743</v>
+        <v>774</v>
       </c>
       <c r="E569" t="s">
-        <v>774</v>
+        <v>744</v>
       </c>
       <c r="F569" t="s">
         <v>713</v>
@@ -15708,10 +15708,10 @@
         <v>7</v>
       </c>
       <c r="C573" t="s">
+        <v>779</v>
+      </c>
+      <c r="D573" t="s">
         <v>711</v>
-      </c>
-      <c r="D573" t="s">
-        <v>779</v>
       </c>
       <c r="E573" t="s">
         <v>780</v>
@@ -15728,10 +15728,10 @@
         <v>7</v>
       </c>
       <c r="C574" t="s">
+        <v>779</v>
+      </c>
+      <c r="D574" t="s">
         <v>782</v>
-      </c>
-      <c r="D574" t="s">
-        <v>779</v>
       </c>
       <c r="E574" t="s">
         <v>780</v>
@@ -15748,10 +15748,10 @@
         <v>7</v>
       </c>
       <c r="C575" t="s">
+        <v>779</v>
+      </c>
+      <c r="D575" t="s">
         <v>782</v>
-      </c>
-      <c r="D575" t="s">
-        <v>779</v>
       </c>
       <c r="E575" t="s">
         <v>780</v>
@@ -15768,10 +15768,10 @@
         <v>7</v>
       </c>
       <c r="C576" t="s">
+        <v>779</v>
+      </c>
+      <c r="D576" t="s">
         <v>782</v>
-      </c>
-      <c r="D576" t="s">
-        <v>779</v>
       </c>
       <c r="E576" t="s">
         <v>780</v>
@@ -15788,10 +15788,10 @@
         <v>7</v>
       </c>
       <c r="C577" t="s">
-        <v>742</v>
+        <v>779</v>
       </c>
       <c r="D577" t="s">
-        <v>779</v>
+        <v>743</v>
       </c>
       <c r="E577" t="s">
         <v>780</v>
@@ -15808,13 +15808,13 @@
         <v>7</v>
       </c>
       <c r="C578" t="s">
+        <v>787</v>
+      </c>
+      <c r="D578" t="s">
         <v>782</v>
       </c>
-      <c r="D578" t="s">
-        <v>779</v>
-      </c>
       <c r="E578" t="s">
-        <v>787</v>
+        <v>780</v>
       </c>
       <c r="F578" t="s">
         <v>713</v>
@@ -15831,10 +15831,10 @@
         <v>789</v>
       </c>
       <c r="D579" t="s">
-        <v>779</v>
+        <v>790</v>
       </c>
       <c r="E579" t="s">
-        <v>790</v>
+        <v>780</v>
       </c>
       <c r="F579" t="s">
         <v>24</v>
@@ -15848,13 +15848,13 @@
         <v>7</v>
       </c>
       <c r="C580" t="s">
+        <v>792</v>
+      </c>
+      <c r="D580" t="s">
         <v>782</v>
       </c>
-      <c r="D580" t="s">
-        <v>779</v>
-      </c>
       <c r="E580" t="s">
-        <v>792</v>
+        <v>780</v>
       </c>
       <c r="F580" t="s">
         <v>713</v>
@@ -15868,13 +15868,13 @@
         <v>7</v>
       </c>
       <c r="C581" t="s">
+        <v>794</v>
+      </c>
+      <c r="D581" t="s">
         <v>782</v>
       </c>
-      <c r="D581" t="s">
-        <v>779</v>
-      </c>
       <c r="E581" t="s">
-        <v>794</v>
+        <v>780</v>
       </c>
       <c r="F581" t="s">
         <v>16</v>
@@ -15888,10 +15888,10 @@
         <v>7</v>
       </c>
       <c r="C582" t="s">
+        <v>779</v>
+      </c>
+      <c r="D582" t="s">
         <v>782</v>
-      </c>
-      <c r="D582" t="s">
-        <v>779</v>
       </c>
       <c r="E582" t="s">
         <v>780</v>
@@ -15911,10 +15911,10 @@
         <v>797</v>
       </c>
       <c r="D583" t="s">
-        <v>779</v>
+        <v>798</v>
       </c>
       <c r="E583" t="s">
-        <v>798</v>
+        <v>780</v>
       </c>
       <c r="F583" t="s">
         <v>24</v>
@@ -15931,10 +15931,10 @@
         <v>800</v>
       </c>
       <c r="D584" t="s">
-        <v>779</v>
+        <v>801</v>
       </c>
       <c r="E584" t="s">
-        <v>801</v>
+        <v>780</v>
       </c>
       <c r="F584" t="s">
         <v>24</v>
@@ -15948,10 +15948,10 @@
         <v>7</v>
       </c>
       <c r="C585" t="s">
+        <v>779</v>
+      </c>
+      <c r="D585" t="s">
         <v>782</v>
-      </c>
-      <c r="D585" t="s">
-        <v>779</v>
       </c>
       <c r="E585" t="s">
         <v>780</v>
@@ -15971,10 +15971,10 @@
         <v>804</v>
       </c>
       <c r="D586" t="s">
-        <v>779</v>
+        <v>805</v>
       </c>
       <c r="E586" t="s">
-        <v>805</v>
+        <v>780</v>
       </c>
       <c r="F586" t="s">
         <v>24</v>
@@ -15988,13 +15988,13 @@
         <v>7</v>
       </c>
       <c r="C587" t="s">
+        <v>807</v>
+      </c>
+      <c r="D587" t="s">
         <v>782</v>
       </c>
-      <c r="D587" t="s">
-        <v>779</v>
-      </c>
       <c r="E587" t="s">
-        <v>807</v>
+        <v>780</v>
       </c>
       <c r="F587" t="s">
         <v>13</v>
@@ -16008,13 +16008,13 @@
         <v>7</v>
       </c>
       <c r="C588" t="s">
+        <v>809</v>
+      </c>
+      <c r="D588" t="s">
         <v>782</v>
       </c>
-      <c r="D588" t="s">
-        <v>779</v>
-      </c>
       <c r="E588" t="s">
-        <v>809</v>
+        <v>780</v>
       </c>
       <c r="F588" t="s">
         <v>713</v>
@@ -16028,10 +16028,10 @@
         <v>7</v>
       </c>
       <c r="C589" t="s">
+        <v>779</v>
+      </c>
+      <c r="D589" t="s">
         <v>782</v>
-      </c>
-      <c r="D589" t="s">
-        <v>779</v>
       </c>
       <c r="E589" t="s">
         <v>780</v>
@@ -16048,10 +16048,10 @@
         <v>7</v>
       </c>
       <c r="C590" t="s">
+        <v>779</v>
+      </c>
+      <c r="D590" t="s">
         <v>782</v>
-      </c>
-      <c r="D590" t="s">
-        <v>779</v>
       </c>
       <c r="E590" t="s">
         <v>780</v>
@@ -16068,10 +16068,10 @@
         <v>7</v>
       </c>
       <c r="C591" t="s">
+        <v>779</v>
+      </c>
+      <c r="D591" t="s">
         <v>782</v>
-      </c>
-      <c r="D591" t="s">
-        <v>779</v>
       </c>
       <c r="E591" t="s">
         <v>780</v>
@@ -16088,10 +16088,10 @@
         <v>7</v>
       </c>
       <c r="C592" t="s">
+        <v>779</v>
+      </c>
+      <c r="D592" t="s">
         <v>814</v>
-      </c>
-      <c r="D592" t="s">
-        <v>779</v>
       </c>
       <c r="E592" t="s">
         <v>780</v>
@@ -16108,10 +16108,10 @@
         <v>7</v>
       </c>
       <c r="C593" t="s">
+        <v>779</v>
+      </c>
+      <c r="D593" t="s">
         <v>782</v>
-      </c>
-      <c r="D593" t="s">
-        <v>779</v>
       </c>
       <c r="E593" t="s">
         <v>780</v>
@@ -16128,10 +16128,10 @@
         <v>7</v>
       </c>
       <c r="C594" t="s">
+        <v>779</v>
+      </c>
+      <c r="D594" t="s">
         <v>782</v>
-      </c>
-      <c r="D594" t="s">
-        <v>779</v>
       </c>
       <c r="E594" t="s">
         <v>780</v>
@@ -16148,10 +16148,10 @@
         <v>7</v>
       </c>
       <c r="C595" t="s">
+        <v>779</v>
+      </c>
+      <c r="D595" t="s">
         <v>782</v>
-      </c>
-      <c r="D595" t="s">
-        <v>779</v>
       </c>
       <c r="E595" t="s">
         <v>780</v>
@@ -16168,10 +16168,10 @@
         <v>7</v>
       </c>
       <c r="C596" t="s">
+        <v>779</v>
+      </c>
+      <c r="D596" t="s">
         <v>782</v>
-      </c>
-      <c r="D596" t="s">
-        <v>779</v>
       </c>
       <c r="E596" t="s">
         <v>780</v>
@@ -16211,10 +16211,10 @@
         <v>824</v>
       </c>
       <c r="D598" t="s">
-        <v>821</v>
+        <v>825</v>
       </c>
       <c r="E598" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="F598" t="s">
         <v>16</v>
@@ -16291,10 +16291,10 @@
         <v>830</v>
       </c>
       <c r="D602" t="s">
-        <v>821</v>
+        <v>831</v>
       </c>
       <c r="E602" t="s">
-        <v>831</v>
+        <v>822</v>
       </c>
       <c r="F602" t="s">
         <v>24</v>
@@ -16311,10 +16311,10 @@
         <v>833</v>
       </c>
       <c r="D603" t="s">
-        <v>821</v>
+        <v>834</v>
       </c>
       <c r="E603" t="s">
-        <v>834</v>
+        <v>822</v>
       </c>
       <c r="F603" t="s">
         <v>24</v>
@@ -16331,10 +16331,10 @@
         <v>836</v>
       </c>
       <c r="D604" t="s">
-        <v>821</v>
+        <v>837</v>
       </c>
       <c r="E604" t="s">
-        <v>837</v>
+        <v>822</v>
       </c>
       <c r="F604" t="s">
         <v>713</v>
@@ -16348,13 +16348,13 @@
         <v>7</v>
       </c>
       <c r="C605" t="s">
-        <v>820</v>
+        <v>839</v>
       </c>
       <c r="D605" t="s">
         <v>821</v>
       </c>
       <c r="E605" t="s">
-        <v>839</v>
+        <v>822</v>
       </c>
       <c r="F605" t="s">
         <v>24</v>
@@ -16411,10 +16411,10 @@
         <v>843</v>
       </c>
       <c r="D608" t="s">
-        <v>821</v>
+        <v>844</v>
       </c>
       <c r="E608" t="s">
-        <v>844</v>
+        <v>822</v>
       </c>
       <c r="F608" t="s">
         <v>24</v>
@@ -16428,13 +16428,13 @@
         <v>7</v>
       </c>
       <c r="C609" t="s">
+        <v>846</v>
+      </c>
+      <c r="D609" t="s">
         <v>807</v>
       </c>
-      <c r="D609" t="s">
-        <v>821</v>
-      </c>
       <c r="E609" t="s">
-        <v>846</v>
+        <v>822</v>
       </c>
       <c r="F609" t="s">
         <v>713</v>
@@ -16468,13 +16468,13 @@
         <v>7</v>
       </c>
       <c r="C611" t="s">
+        <v>824</v>
+      </c>
+      <c r="D611" t="s">
         <v>849</v>
       </c>
-      <c r="D611" t="s">
-        <v>821</v>
-      </c>
       <c r="E611" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="F611" t="s">
         <v>24</v>
@@ -16488,13 +16488,13 @@
         <v>7</v>
       </c>
       <c r="C612" t="s">
-        <v>820</v>
+        <v>851</v>
       </c>
       <c r="D612" t="s">
         <v>821</v>
       </c>
       <c r="E612" t="s">
-        <v>851</v>
+        <v>822</v>
       </c>
       <c r="F612" t="s">
         <v>16</v>
@@ -16528,13 +16528,13 @@
         <v>7</v>
       </c>
       <c r="C614" t="s">
-        <v>820</v>
+        <v>854</v>
       </c>
       <c r="D614" t="s">
         <v>821</v>
       </c>
       <c r="E614" t="s">
-        <v>854</v>
+        <v>822</v>
       </c>
       <c r="F614" t="s">
         <v>713</v>
@@ -16731,10 +16731,10 @@
         <v>868</v>
       </c>
       <c r="D624" t="s">
-        <v>865</v>
+        <v>869</v>
       </c>
       <c r="E624" t="s">
-        <v>869</v>
+        <v>866</v>
       </c>
       <c r="F624" t="s">
         <v>24</v>
@@ -16808,10 +16808,10 @@
         <v>7</v>
       </c>
       <c r="C628" t="s">
+        <v>864</v>
+      </c>
+      <c r="D628" t="s">
         <v>874</v>
-      </c>
-      <c r="D628" t="s">
-        <v>865</v>
       </c>
       <c r="E628" t="s">
         <v>866</v>
@@ -16828,13 +16828,13 @@
         <v>7</v>
       </c>
       <c r="C629" t="s">
-        <v>864</v>
+        <v>876</v>
       </c>
       <c r="D629" t="s">
         <v>865</v>
       </c>
       <c r="E629" t="s">
-        <v>876</v>
+        <v>866</v>
       </c>
       <c r="F629" t="s">
         <v>24</v>
@@ -16888,13 +16888,13 @@
         <v>7</v>
       </c>
       <c r="C632" t="s">
+        <v>876</v>
+      </c>
+      <c r="D632" t="s">
         <v>880</v>
       </c>
-      <c r="D632" t="s">
-        <v>865</v>
-      </c>
       <c r="E632" t="s">
-        <v>876</v>
+        <v>866</v>
       </c>
       <c r="F632" t="s">
         <v>24</v>
@@ -16911,10 +16911,10 @@
         <v>882</v>
       </c>
       <c r="D633" t="s">
-        <v>865</v>
+        <v>883</v>
       </c>
       <c r="E633" t="s">
-        <v>883</v>
+        <v>866</v>
       </c>
       <c r="F633" t="s">
         <v>24</v>
@@ -16931,10 +16931,10 @@
         <v>885</v>
       </c>
       <c r="D634" t="s">
-        <v>865</v>
+        <v>886</v>
       </c>
       <c r="E634" t="s">
-        <v>886</v>
+        <v>866</v>
       </c>
       <c r="F634" t="s">
         <v>24</v>
@@ -16968,13 +16968,13 @@
         <v>7</v>
       </c>
       <c r="C636" t="s">
-        <v>864</v>
+        <v>889</v>
       </c>
       <c r="D636" t="s">
         <v>865</v>
       </c>
       <c r="E636" t="s">
-        <v>889</v>
+        <v>866</v>
       </c>
       <c r="F636" t="s">
         <v>713</v>
@@ -16991,10 +16991,10 @@
         <v>891</v>
       </c>
       <c r="D637" t="s">
-        <v>865</v>
+        <v>892</v>
       </c>
       <c r="E637" t="s">
-        <v>892</v>
+        <v>866</v>
       </c>
       <c r="F637" t="s">
         <v>24</v>
@@ -17071,10 +17071,10 @@
         <v>897</v>
       </c>
       <c r="D641" t="s">
-        <v>865</v>
+        <v>898</v>
       </c>
       <c r="E641" t="s">
-        <v>898</v>
+        <v>866</v>
       </c>
       <c r="F641" t="s">
         <v>16</v>
@@ -17088,13 +17088,13 @@
         <v>7</v>
       </c>
       <c r="C642" t="s">
-        <v>864</v>
+        <v>900</v>
       </c>
       <c r="D642" t="s">
         <v>865</v>
       </c>
       <c r="E642" t="s">
-        <v>900</v>
+        <v>866</v>
       </c>
       <c r="F642" t="s">
         <v>16</v>
@@ -17108,13 +17108,13 @@
         <v>7</v>
       </c>
       <c r="C643" t="s">
-        <v>864</v>
+        <v>902</v>
       </c>
       <c r="D643" t="s">
         <v>865</v>
       </c>
       <c r="E643" t="s">
-        <v>902</v>
+        <v>866</v>
       </c>
       <c r="F643" t="s">
         <v>16</v>
@@ -17168,13 +17168,13 @@
         <v>7</v>
       </c>
       <c r="C646" t="s">
-        <v>864</v>
+        <v>906</v>
       </c>
       <c r="D646" t="s">
         <v>865</v>
       </c>
       <c r="E646" t="s">
-        <v>906</v>
+        <v>866</v>
       </c>
       <c r="F646" t="s">
         <v>24</v>
@@ -17251,10 +17251,10 @@
         <v>914</v>
       </c>
       <c r="D650" t="s">
-        <v>911</v>
+        <v>915</v>
       </c>
       <c r="E650" t="s">
-        <v>915</v>
+        <v>912</v>
       </c>
       <c r="F650" t="s">
         <v>16</v>
@@ -17268,10 +17268,10 @@
         <v>7</v>
       </c>
       <c r="C651" t="s">
+        <v>910</v>
+      </c>
+      <c r="D651" t="s">
         <v>917</v>
-      </c>
-      <c r="D651" t="s">
-        <v>911</v>
       </c>
       <c r="E651" t="s">
         <v>912</v>
@@ -17291,10 +17291,10 @@
         <v>919</v>
       </c>
       <c r="D652" t="s">
-        <v>911</v>
+        <v>920</v>
       </c>
       <c r="E652" t="s">
-        <v>920</v>
+        <v>912</v>
       </c>
       <c r="F652" t="s">
         <v>713</v>
@@ -17311,10 +17311,10 @@
         <v>919</v>
       </c>
       <c r="D653" t="s">
-        <v>911</v>
+        <v>920</v>
       </c>
       <c r="E653" t="s">
-        <v>920</v>
+        <v>912</v>
       </c>
       <c r="F653" t="s">
         <v>713</v>
@@ -17328,13 +17328,13 @@
         <v>7</v>
       </c>
       <c r="C654" t="s">
-        <v>864</v>
+        <v>902</v>
       </c>
       <c r="D654" t="s">
-        <v>911</v>
+        <v>865</v>
       </c>
       <c r="E654" t="s">
-        <v>902</v>
+        <v>912</v>
       </c>
       <c r="F654" t="s">
         <v>16</v>
@@ -17351,10 +17351,10 @@
         <v>919</v>
       </c>
       <c r="D655" t="s">
-        <v>911</v>
+        <v>920</v>
       </c>
       <c r="E655" t="s">
-        <v>920</v>
+        <v>912</v>
       </c>
       <c r="F655" t="s">
         <v>713</v>
@@ -17371,10 +17371,10 @@
         <v>919</v>
       </c>
       <c r="D656" t="s">
-        <v>911</v>
+        <v>920</v>
       </c>
       <c r="E656" t="s">
-        <v>920</v>
+        <v>912</v>
       </c>
       <c r="F656" t="s">
         <v>713</v>
@@ -17391,10 +17391,10 @@
         <v>926</v>
       </c>
       <c r="D657" t="s">
-        <v>911</v>
+        <v>927</v>
       </c>
       <c r="E657" t="s">
-        <v>927</v>
+        <v>912</v>
       </c>
       <c r="F657" t="s">
         <v>16</v>
@@ -17411,10 +17411,10 @@
         <v>929</v>
       </c>
       <c r="D658" t="s">
-        <v>911</v>
+        <v>930</v>
       </c>
       <c r="E658" t="s">
-        <v>930</v>
+        <v>912</v>
       </c>
       <c r="F658" t="s">
         <v>24</v>
@@ -17428,13 +17428,13 @@
         <v>7</v>
       </c>
       <c r="C659" t="s">
+        <v>889</v>
+      </c>
+      <c r="D659" t="s">
         <v>932</v>
       </c>
-      <c r="D659" t="s">
-        <v>911</v>
-      </c>
       <c r="E659" t="s">
-        <v>889</v>
+        <v>912</v>
       </c>
       <c r="F659" t="s">
         <v>24</v>
@@ -17451,10 +17451,10 @@
         <v>934</v>
       </c>
       <c r="D660" t="s">
-        <v>911</v>
+        <v>935</v>
       </c>
       <c r="E660" t="s">
-        <v>935</v>
+        <v>912</v>
       </c>
       <c r="F660" t="s">
         <v>24</v>
@@ -17471,10 +17471,10 @@
         <v>919</v>
       </c>
       <c r="D661" t="s">
-        <v>911</v>
+        <v>920</v>
       </c>
       <c r="E661" t="s">
-        <v>920</v>
+        <v>912</v>
       </c>
       <c r="F661" t="s">
         <v>713</v>
@@ -17488,13 +17488,13 @@
         <v>7</v>
       </c>
       <c r="C662" t="s">
-        <v>915</v>
+        <v>919</v>
       </c>
       <c r="D662" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E662" t="s">
-        <v>920</v>
+        <v>912</v>
       </c>
       <c r="F662" t="s">
         <v>24</v>
@@ -17511,10 +17511,10 @@
         <v>939</v>
       </c>
       <c r="D663" t="s">
-        <v>911</v>
+        <v>940</v>
       </c>
       <c r="E663" t="s">
-        <v>940</v>
+        <v>912</v>
       </c>
       <c r="F663" t="s">
         <v>24</v>
@@ -17528,13 +17528,13 @@
         <v>7</v>
       </c>
       <c r="C664" t="s">
+        <v>902</v>
+      </c>
+      <c r="D664" t="s">
         <v>942</v>
       </c>
-      <c r="D664" t="s">
-        <v>911</v>
-      </c>
       <c r="E664" t="s">
-        <v>902</v>
+        <v>912</v>
       </c>
       <c r="F664" t="s">
         <v>16</v>
@@ -17548,13 +17548,13 @@
         <v>7</v>
       </c>
       <c r="C665" t="s">
-        <v>919</v>
+        <v>944</v>
       </c>
       <c r="D665" t="s">
-        <v>911</v>
+        <v>920</v>
       </c>
       <c r="E665" t="s">
-        <v>944</v>
+        <v>912</v>
       </c>
       <c r="F665" t="s">
         <v>713</v>
@@ -17568,13 +17568,13 @@
         <v>7</v>
       </c>
       <c r="C666" t="s">
-        <v>910</v>
+        <v>944</v>
       </c>
       <c r="D666" t="s">
         <v>911</v>
       </c>
       <c r="E666" t="s">
-        <v>944</v>
+        <v>912</v>
       </c>
       <c r="F666" t="s">
         <v>24</v>
@@ -17591,10 +17591,10 @@
         <v>947</v>
       </c>
       <c r="D667" t="s">
-        <v>911</v>
+        <v>948</v>
       </c>
       <c r="E667" t="s">
-        <v>948</v>
+        <v>912</v>
       </c>
       <c r="F667" t="s">
         <v>24</v>
@@ -17611,10 +17611,10 @@
         <v>919</v>
       </c>
       <c r="D668" t="s">
-        <v>911</v>
+        <v>920</v>
       </c>
       <c r="E668" t="s">
-        <v>920</v>
+        <v>912</v>
       </c>
       <c r="F668" t="s">
         <v>16</v>
@@ -17628,13 +17628,13 @@
         <v>7</v>
       </c>
       <c r="C669" t="s">
+        <v>902</v>
+      </c>
+      <c r="D669" t="s">
         <v>932</v>
       </c>
-      <c r="D669" t="s">
-        <v>911</v>
-      </c>
       <c r="E669" t="s">
-        <v>902</v>
+        <v>912</v>
       </c>
       <c r="F669" t="s">
         <v>16</v>
@@ -17651,10 +17651,10 @@
         <v>919</v>
       </c>
       <c r="D670" t="s">
-        <v>911</v>
+        <v>920</v>
       </c>
       <c r="E670" t="s">
-        <v>920</v>
+        <v>912</v>
       </c>
       <c r="F670" t="s">
         <v>713</v>
@@ -17668,10 +17668,10 @@
         <v>7</v>
       </c>
       <c r="C671" t="s">
+        <v>910</v>
+      </c>
+      <c r="D671" t="s">
         <v>953</v>
-      </c>
-      <c r="D671" t="s">
-        <v>911</v>
       </c>
       <c r="E671" t="s">
         <v>912</v>
@@ -17691,10 +17691,10 @@
         <v>919</v>
       </c>
       <c r="D672" t="s">
-        <v>911</v>
+        <v>920</v>
       </c>
       <c r="E672" t="s">
-        <v>920</v>
+        <v>912</v>
       </c>
       <c r="F672" t="s">
         <v>16</v>
@@ -17711,10 +17711,10 @@
         <v>919</v>
       </c>
       <c r="D673" t="s">
-        <v>911</v>
+        <v>920</v>
       </c>
       <c r="E673" t="s">
-        <v>920</v>
+        <v>912</v>
       </c>
       <c r="F673" t="s">
         <v>713</v>
@@ -17728,13 +17728,13 @@
         <v>7</v>
       </c>
       <c r="C674" t="s">
-        <v>934</v>
+        <v>902</v>
       </c>
       <c r="D674" t="s">
-        <v>911</v>
+        <v>935</v>
       </c>
       <c r="E674" t="s">
-        <v>902</v>
+        <v>912</v>
       </c>
       <c r="F674" t="s">
         <v>16</v>
@@ -17748,10 +17748,10 @@
         <v>7</v>
       </c>
       <c r="C675" t="s">
+        <v>910</v>
+      </c>
+      <c r="D675" t="s">
         <v>917</v>
-      </c>
-      <c r="D675" t="s">
-        <v>911</v>
       </c>
       <c r="E675" t="s">
         <v>912</v>
@@ -17768,13 +17768,13 @@
         <v>7</v>
       </c>
       <c r="C676" t="s">
-        <v>919</v>
+        <v>959</v>
       </c>
       <c r="D676" t="s">
-        <v>911</v>
+        <v>920</v>
       </c>
       <c r="E676" t="s">
-        <v>959</v>
+        <v>912</v>
       </c>
       <c r="F676" t="s">
         <v>16</v>
@@ -17791,10 +17791,10 @@
         <v>919</v>
       </c>
       <c r="D677" t="s">
-        <v>911</v>
+        <v>920</v>
       </c>
       <c r="E677" t="s">
-        <v>920</v>
+        <v>912</v>
       </c>
       <c r="F677" t="s">
         <v>713</v>
@@ -17811,10 +17811,10 @@
         <v>919</v>
       </c>
       <c r="D678" t="s">
-        <v>911</v>
+        <v>920</v>
       </c>
       <c r="E678" t="s">
-        <v>920</v>
+        <v>912</v>
       </c>
       <c r="F678" t="s">
         <v>713</v>
@@ -17831,10 +17831,10 @@
         <v>934</v>
       </c>
       <c r="D679" t="s">
-        <v>911</v>
+        <v>935</v>
       </c>
       <c r="E679" t="s">
-        <v>935</v>
+        <v>912</v>
       </c>
       <c r="F679" t="s">
         <v>24</v>
@@ -17851,10 +17851,10 @@
         <v>919</v>
       </c>
       <c r="D680" t="s">
-        <v>911</v>
+        <v>920</v>
       </c>
       <c r="E680" t="s">
-        <v>920</v>
+        <v>912</v>
       </c>
       <c r="F680" t="s">
         <v>713</v>
@@ -17871,10 +17871,10 @@
         <v>919</v>
       </c>
       <c r="D681" t="s">
-        <v>911</v>
+        <v>920</v>
       </c>
       <c r="E681" t="s">
-        <v>920</v>
+        <v>912</v>
       </c>
       <c r="F681" t="s">
         <v>713</v>
@@ -17911,10 +17911,10 @@
         <v>970</v>
       </c>
       <c r="D683" t="s">
-        <v>967</v>
+        <v>971</v>
       </c>
       <c r="E683" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="F683" t="s">
         <v>24</v>
@@ -17931,10 +17931,10 @@
         <v>973</v>
       </c>
       <c r="D684" t="s">
-        <v>967</v>
+        <v>974</v>
       </c>
       <c r="E684" t="s">
-        <v>974</v>
+        <v>968</v>
       </c>
       <c r="F684" t="s">
         <v>713</v>
@@ -17951,10 +17951,10 @@
         <v>973</v>
       </c>
       <c r="D685" t="s">
-        <v>967</v>
+        <v>974</v>
       </c>
       <c r="E685" t="s">
-        <v>974</v>
+        <v>968</v>
       </c>
       <c r="F685" t="s">
         <v>713</v>
@@ -17971,10 +17971,10 @@
         <v>973</v>
       </c>
       <c r="D686" t="s">
-        <v>967</v>
+        <v>974</v>
       </c>
       <c r="E686" t="s">
-        <v>974</v>
+        <v>968</v>
       </c>
       <c r="F686" t="s">
         <v>713</v>
@@ -17991,10 +17991,10 @@
         <v>973</v>
       </c>
       <c r="D687" t="s">
-        <v>967</v>
+        <v>974</v>
       </c>
       <c r="E687" t="s">
-        <v>974</v>
+        <v>968</v>
       </c>
       <c r="F687" t="s">
         <v>713</v>
@@ -18011,10 +18011,10 @@
         <v>973</v>
       </c>
       <c r="D688" t="s">
-        <v>967</v>
+        <v>974</v>
       </c>
       <c r="E688" t="s">
-        <v>974</v>
+        <v>968</v>
       </c>
       <c r="F688" t="s">
         <v>713</v>
@@ -18028,13 +18028,13 @@
         <v>7</v>
       </c>
       <c r="C689" t="s">
+        <v>970</v>
+      </c>
+      <c r="D689" t="s">
         <v>980</v>
       </c>
-      <c r="D689" t="s">
-        <v>967</v>
-      </c>
       <c r="E689" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="F689" t="s">
         <v>24</v>
@@ -18051,10 +18051,10 @@
         <v>982</v>
       </c>
       <c r="D690" t="s">
-        <v>967</v>
+        <v>983</v>
       </c>
       <c r="E690" t="s">
-        <v>983</v>
+        <v>968</v>
       </c>
       <c r="F690" t="s">
         <v>24</v>
@@ -18071,10 +18071,10 @@
         <v>973</v>
       </c>
       <c r="D691" t="s">
-        <v>967</v>
+        <v>974</v>
       </c>
       <c r="E691" t="s">
-        <v>974</v>
+        <v>968</v>
       </c>
       <c r="F691" t="s">
         <v>13</v>
@@ -18088,13 +18088,13 @@
         <v>7</v>
       </c>
       <c r="C692" t="s">
-        <v>919</v>
+        <v>986</v>
       </c>
       <c r="D692" t="s">
-        <v>967</v>
+        <v>920</v>
       </c>
       <c r="E692" t="s">
-        <v>986</v>
+        <v>968</v>
       </c>
       <c r="F692" t="s">
         <v>16</v>
@@ -18111,10 +18111,10 @@
         <v>988</v>
       </c>
       <c r="D693" t="s">
-        <v>967</v>
+        <v>989</v>
       </c>
       <c r="E693" t="s">
-        <v>989</v>
+        <v>968</v>
       </c>
       <c r="F693" t="s">
         <v>24</v>
@@ -18131,10 +18131,10 @@
         <v>991</v>
       </c>
       <c r="D694" t="s">
-        <v>967</v>
+        <v>992</v>
       </c>
       <c r="E694" t="s">
-        <v>992</v>
+        <v>968</v>
       </c>
       <c r="F694" t="s">
         <v>16</v>
@@ -18151,10 +18151,10 @@
         <v>994</v>
       </c>
       <c r="D695" t="s">
-        <v>967</v>
+        <v>995</v>
       </c>
       <c r="E695" t="s">
-        <v>995</v>
+        <v>968</v>
       </c>
       <c r="F695" t="s">
         <v>24</v>
@@ -18171,10 +18171,10 @@
         <v>973</v>
       </c>
       <c r="D696" t="s">
-        <v>967</v>
+        <v>974</v>
       </c>
       <c r="E696" t="s">
-        <v>974</v>
+        <v>968</v>
       </c>
       <c r="F696" t="s">
         <v>713</v>
@@ -18191,10 +18191,10 @@
         <v>998</v>
       </c>
       <c r="D697" t="s">
-        <v>967</v>
+        <v>999</v>
       </c>
       <c r="E697" t="s">
-        <v>999</v>
+        <v>968</v>
       </c>
       <c r="F697" t="s">
         <v>24</v>
@@ -18211,10 +18211,10 @@
         <v>1001</v>
       </c>
       <c r="D698" t="s">
-        <v>967</v>
+        <v>1002</v>
       </c>
       <c r="E698" t="s">
-        <v>1002</v>
+        <v>968</v>
       </c>
       <c r="F698" t="s">
         <v>24</v>
@@ -18231,10 +18231,10 @@
         <v>973</v>
       </c>
       <c r="D699" t="s">
-        <v>967</v>
+        <v>974</v>
       </c>
       <c r="E699" t="s">
-        <v>974</v>
+        <v>968</v>
       </c>
       <c r="F699" t="s">
         <v>16</v>
@@ -18251,10 +18251,10 @@
         <v>1005</v>
       </c>
       <c r="D700" t="s">
-        <v>967</v>
+        <v>1006</v>
       </c>
       <c r="E700" t="s">
-        <v>1006</v>
+        <v>968</v>
       </c>
       <c r="F700" t="s">
         <v>24</v>
@@ -18271,10 +18271,10 @@
         <v>973</v>
       </c>
       <c r="D701" t="s">
-        <v>967</v>
+        <v>974</v>
       </c>
       <c r="E701" t="s">
-        <v>974</v>
+        <v>968</v>
       </c>
       <c r="F701" t="s">
         <v>16</v>
@@ -18291,10 +18291,10 @@
         <v>1009</v>
       </c>
       <c r="D702" t="s">
-        <v>967</v>
+        <v>1010</v>
       </c>
       <c r="E702" t="s">
-        <v>1010</v>
+        <v>968</v>
       </c>
       <c r="F702" t="s">
         <v>24</v>
@@ -18308,13 +18308,13 @@
         <v>7</v>
       </c>
       <c r="C703" t="s">
-        <v>1005</v>
+        <v>1012</v>
       </c>
       <c r="D703" t="s">
-        <v>967</v>
+        <v>1006</v>
       </c>
       <c r="E703" t="s">
-        <v>1012</v>
+        <v>968</v>
       </c>
       <c r="F703" t="s">
         <v>24</v>
@@ -18331,10 +18331,10 @@
         <v>973</v>
       </c>
       <c r="D704" t="s">
-        <v>967</v>
+        <v>974</v>
       </c>
       <c r="E704" t="s">
-        <v>974</v>
+        <v>968</v>
       </c>
       <c r="F704" t="s">
         <v>713</v>
@@ -18348,13 +18348,13 @@
         <v>7</v>
       </c>
       <c r="C705" t="s">
-        <v>1001</v>
+        <v>1015</v>
       </c>
       <c r="D705" t="s">
-        <v>967</v>
+        <v>1002</v>
       </c>
       <c r="E705" t="s">
-        <v>1015</v>
+        <v>968</v>
       </c>
       <c r="F705" t="s">
         <v>16</v>
@@ -18371,10 +18371,10 @@
         <v>973</v>
       </c>
       <c r="D706" t="s">
-        <v>967</v>
+        <v>974</v>
       </c>
       <c r="E706" t="s">
-        <v>974</v>
+        <v>968</v>
       </c>
       <c r="F706" t="s">
         <v>713</v>
@@ -18388,13 +18388,13 @@
         <v>7</v>
       </c>
       <c r="C707" t="s">
-        <v>1001</v>
+        <v>973</v>
       </c>
       <c r="D707" t="s">
-        <v>967</v>
+        <v>1002</v>
       </c>
       <c r="E707" t="s">
-        <v>974</v>
+        <v>968</v>
       </c>
       <c r="F707" t="s">
         <v>16</v>
@@ -18408,13 +18408,13 @@
         <v>7</v>
       </c>
       <c r="C708" t="s">
-        <v>970</v>
+        <v>1019</v>
       </c>
       <c r="D708" t="s">
-        <v>967</v>
+        <v>971</v>
       </c>
       <c r="E708" t="s">
-        <v>1019</v>
+        <v>968</v>
       </c>
       <c r="F708" t="s">
         <v>24</v>
@@ -18431,10 +18431,10 @@
         <v>973</v>
       </c>
       <c r="D709" t="s">
-        <v>967</v>
+        <v>974</v>
       </c>
       <c r="E709" t="s">
-        <v>974</v>
+        <v>968</v>
       </c>
       <c r="F709" t="s">
         <v>713</v>
@@ -18451,10 +18451,10 @@
         <v>1022</v>
       </c>
       <c r="D710" t="s">
-        <v>967</v>
+        <v>1023</v>
       </c>
       <c r="E710" t="s">
-        <v>1023</v>
+        <v>968</v>
       </c>
       <c r="F710" t="s">
         <v>24</v>
@@ -18468,13 +18468,13 @@
         <v>7</v>
       </c>
       <c r="C711" t="s">
-        <v>1001</v>
+        <v>973</v>
       </c>
       <c r="D711" t="s">
-        <v>967</v>
+        <v>1002</v>
       </c>
       <c r="E711" t="s">
-        <v>974</v>
+        <v>968</v>
       </c>
       <c r="F711" t="s">
         <v>713</v>
@@ -18491,10 +18491,10 @@
         <v>973</v>
       </c>
       <c r="D712" t="s">
-        <v>967</v>
+        <v>974</v>
       </c>
       <c r="E712" t="s">
-        <v>974</v>
+        <v>968</v>
       </c>
       <c r="F712" t="s">
         <v>713</v>
@@ -18511,10 +18511,10 @@
         <v>982</v>
       </c>
       <c r="D713" t="s">
-        <v>967</v>
+        <v>983</v>
       </c>
       <c r="E713" t="s">
-        <v>983</v>
+        <v>968</v>
       </c>
       <c r="F713" t="s">
         <v>24</v>
@@ -18531,10 +18531,10 @@
         <v>973</v>
       </c>
       <c r="D714" t="s">
-        <v>967</v>
+        <v>974</v>
       </c>
       <c r="E714" t="s">
-        <v>974</v>
+        <v>968</v>
       </c>
       <c r="F714" t="s">
         <v>713</v>
@@ -18548,13 +18548,13 @@
         <v>7</v>
       </c>
       <c r="C715" t="s">
-        <v>1001</v>
+        <v>998</v>
       </c>
       <c r="D715" t="s">
-        <v>967</v>
+        <v>1002</v>
       </c>
       <c r="E715" t="s">
-        <v>999</v>
+        <v>968</v>
       </c>
       <c r="F715" t="s">
         <v>24</v>
@@ -18571,10 +18571,10 @@
         <v>973</v>
       </c>
       <c r="D716" t="s">
-        <v>967</v>
+        <v>974</v>
       </c>
       <c r="E716" t="s">
-        <v>974</v>
+        <v>968</v>
       </c>
       <c r="F716" t="s">
         <v>713</v>
@@ -18591,10 +18591,10 @@
         <v>973</v>
       </c>
       <c r="D717" t="s">
-        <v>967</v>
+        <v>974</v>
       </c>
       <c r="E717" t="s">
-        <v>974</v>
+        <v>968</v>
       </c>
       <c r="F717" t="s">
         <v>713</v>
@@ -18628,13 +18628,13 @@
         <v>7</v>
       </c>
       <c r="C719" t="s">
-        <v>1032</v>
+        <v>1036</v>
       </c>
       <c r="D719" t="s">
         <v>1033</v>
       </c>
       <c r="E719" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="F719" t="s">
         <v>713</v>
@@ -18648,13 +18648,13 @@
         <v>7</v>
       </c>
       <c r="C720" t="s">
-        <v>1032</v>
+        <v>1036</v>
       </c>
       <c r="D720" t="s">
         <v>1033</v>
       </c>
       <c r="E720" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="F720" t="s">
         <v>713</v>
@@ -18668,13 +18668,13 @@
         <v>7</v>
       </c>
       <c r="C721" t="s">
-        <v>1032</v>
+        <v>1036</v>
       </c>
       <c r="D721" t="s">
         <v>1033</v>
       </c>
       <c r="E721" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="F721" t="s">
         <v>713</v>
@@ -18688,13 +18688,13 @@
         <v>7</v>
       </c>
       <c r="C722" t="s">
-        <v>1032</v>
+        <v>1036</v>
       </c>
       <c r="D722" t="s">
         <v>1033</v>
       </c>
       <c r="E722" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="F722" t="s">
         <v>713</v>
@@ -18708,13 +18708,13 @@
         <v>7</v>
       </c>
       <c r="C723" t="s">
-        <v>1032</v>
+        <v>1036</v>
       </c>
       <c r="D723" t="s">
         <v>1033</v>
       </c>
       <c r="E723" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="F723" t="s">
         <v>713</v>
@@ -18728,13 +18728,13 @@
         <v>7</v>
       </c>
       <c r="C724" t="s">
-        <v>1032</v>
+        <v>1036</v>
       </c>
       <c r="D724" t="s">
         <v>1033</v>
       </c>
       <c r="E724" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="F724" t="s">
         <v>16</v>
@@ -18751,10 +18751,10 @@
         <v>1043</v>
       </c>
       <c r="D725" t="s">
-        <v>1033</v>
+        <v>1044</v>
       </c>
       <c r="E725" t="s">
-        <v>1044</v>
+        <v>1034</v>
       </c>
       <c r="F725" t="s">
         <v>16</v>
@@ -18771,10 +18771,10 @@
         <v>1046</v>
       </c>
       <c r="D726" t="s">
-        <v>1033</v>
+        <v>1047</v>
       </c>
       <c r="E726" t="s">
-        <v>1047</v>
+        <v>1034</v>
       </c>
       <c r="F726" t="s">
         <v>16</v>
@@ -18788,13 +18788,13 @@
         <v>7</v>
       </c>
       <c r="C727" t="s">
-        <v>1032</v>
+        <v>1036</v>
       </c>
       <c r="D727" t="s">
         <v>1033</v>
       </c>
       <c r="E727" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="F727" t="s">
         <v>713</v>
@@ -18808,13 +18808,13 @@
         <v>7</v>
       </c>
       <c r="C728" t="s">
-        <v>1032</v>
+        <v>1036</v>
       </c>
       <c r="D728" t="s">
         <v>1033</v>
       </c>
       <c r="E728" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="F728" t="s">
         <v>713</v>
@@ -18831,10 +18831,10 @@
         <v>1051</v>
       </c>
       <c r="D729" t="s">
-        <v>1033</v>
+        <v>1052</v>
       </c>
       <c r="E729" t="s">
-        <v>1052</v>
+        <v>1034</v>
       </c>
       <c r="F729" t="s">
         <v>24</v>
@@ -18848,13 +18848,13 @@
         <v>7</v>
       </c>
       <c r="C730" t="s">
-        <v>1032</v>
+        <v>1036</v>
       </c>
       <c r="D730" t="s">
         <v>1033</v>
       </c>
       <c r="E730" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="F730" t="s">
         <v>13</v>
@@ -18871,10 +18871,10 @@
         <v>1051</v>
       </c>
       <c r="D731" t="s">
-        <v>1033</v>
+        <v>1052</v>
       </c>
       <c r="E731" t="s">
-        <v>1052</v>
+        <v>1034</v>
       </c>
       <c r="F731" t="s">
         <v>24</v>
@@ -18891,10 +18891,10 @@
         <v>1056</v>
       </c>
       <c r="D732" t="s">
-        <v>1033</v>
+        <v>1057</v>
       </c>
       <c r="E732" t="s">
-        <v>1057</v>
+        <v>1034</v>
       </c>
       <c r="F732" t="s">
         <v>24</v>
@@ -18908,13 +18908,13 @@
         <v>7</v>
       </c>
       <c r="C733" t="s">
-        <v>1032</v>
+        <v>1059</v>
       </c>
       <c r="D733" t="s">
         <v>1033</v>
       </c>
       <c r="E733" t="s">
-        <v>1059</v>
+        <v>1034</v>
       </c>
       <c r="F733" t="s">
         <v>24</v>
@@ -18931,10 +18931,10 @@
         <v>1061</v>
       </c>
       <c r="D734" t="s">
-        <v>1033</v>
+        <v>1062</v>
       </c>
       <c r="E734" t="s">
-        <v>1062</v>
+        <v>1034</v>
       </c>
       <c r="F734" t="s">
         <v>24</v>
@@ -18948,13 +18948,13 @@
         <v>7</v>
       </c>
       <c r="C735" t="s">
-        <v>1032</v>
+        <v>1036</v>
       </c>
       <c r="D735" t="s">
         <v>1033</v>
       </c>
       <c r="E735" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="F735" t="s">
         <v>713</v>
@@ -18968,13 +18968,13 @@
         <v>7</v>
       </c>
       <c r="C736" t="s">
-        <v>1032</v>
+        <v>1065</v>
       </c>
       <c r="D736" t="s">
         <v>1033</v>
       </c>
       <c r="E736" t="s">
-        <v>1065</v>
+        <v>1034</v>
       </c>
       <c r="F736" t="s">
         <v>713</v>
@@ -18988,13 +18988,13 @@
         <v>7</v>
       </c>
       <c r="C737" t="s">
-        <v>1032</v>
+        <v>1036</v>
       </c>
       <c r="D737" t="s">
         <v>1033</v>
       </c>
       <c r="E737" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="F737" t="s">
         <v>16</v>
@@ -19008,13 +19008,13 @@
         <v>7</v>
       </c>
       <c r="C738" t="s">
-        <v>973</v>
+        <v>1068</v>
       </c>
       <c r="D738" t="s">
-        <v>1033</v>
+        <v>974</v>
       </c>
       <c r="E738" t="s">
-        <v>1068</v>
+        <v>1034</v>
       </c>
       <c r="F738" t="s">
         <v>16</v>
@@ -19028,13 +19028,13 @@
         <v>7</v>
       </c>
       <c r="C739" t="s">
-        <v>1032</v>
+        <v>1036</v>
       </c>
       <c r="D739" t="s">
         <v>1033</v>
       </c>
       <c r="E739" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="F739" t="s">
         <v>713</v>
@@ -19048,13 +19048,13 @@
         <v>7</v>
       </c>
       <c r="C740" t="s">
-        <v>1032</v>
+        <v>1036</v>
       </c>
       <c r="D740" t="s">
         <v>1033</v>
       </c>
       <c r="E740" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="F740" t="s">
         <v>713</v>
@@ -19071,10 +19071,10 @@
         <v>1072</v>
       </c>
       <c r="D741" t="s">
-        <v>1033</v>
+        <v>1073</v>
       </c>
       <c r="E741" t="s">
-        <v>1073</v>
+        <v>1034</v>
       </c>
       <c r="F741" t="s">
         <v>24</v>
@@ -19088,13 +19088,13 @@
         <v>7</v>
       </c>
       <c r="C742" t="s">
-        <v>1032</v>
+        <v>1075</v>
       </c>
       <c r="D742" t="s">
         <v>1033</v>
       </c>
       <c r="E742" t="s">
-        <v>1075</v>
+        <v>1034</v>
       </c>
       <c r="F742" t="s">
         <v>16</v>
@@ -19108,13 +19108,13 @@
         <v>7</v>
       </c>
       <c r="C743" t="s">
-        <v>1032</v>
+        <v>1036</v>
       </c>
       <c r="D743" t="s">
         <v>1033</v>
       </c>
       <c r="E743" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="F743" t="s">
         <v>713</v>
@@ -19148,13 +19148,13 @@
         <v>7</v>
       </c>
       <c r="C745" t="s">
-        <v>1032</v>
+        <v>1079</v>
       </c>
       <c r="D745" t="s">
         <v>1033</v>
       </c>
       <c r="E745" t="s">
-        <v>1079</v>
+        <v>1034</v>
       </c>
       <c r="F745" t="s">
         <v>24</v>
@@ -19168,13 +19168,13 @@
         <v>7</v>
       </c>
       <c r="C746" t="s">
-        <v>1032</v>
+        <v>1036</v>
       </c>
       <c r="D746" t="s">
         <v>1033</v>
       </c>
       <c r="E746" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="F746" t="s">
         <v>713</v>
@@ -19188,13 +19188,13 @@
         <v>7</v>
       </c>
       <c r="C747" t="s">
-        <v>1032</v>
+        <v>1036</v>
       </c>
       <c r="D747" t="s">
         <v>1033</v>
       </c>
       <c r="E747" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="F747" t="s">
         <v>713</v>
@@ -19208,13 +19208,13 @@
         <v>7</v>
       </c>
       <c r="C748" t="s">
-        <v>1032</v>
+        <v>1036</v>
       </c>
       <c r="D748" t="s">
         <v>1033</v>
       </c>
       <c r="E748" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="F748" t="s">
         <v>713</v>
@@ -19228,13 +19228,13 @@
         <v>7</v>
       </c>
       <c r="C749" t="s">
-        <v>1032</v>
+        <v>1036</v>
       </c>
       <c r="D749" t="s">
         <v>1033</v>
       </c>
       <c r="E749" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="F749" t="s">
         <v>713</v>
@@ -19271,10 +19271,10 @@
         <v>1089</v>
       </c>
       <c r="D751" t="s">
-        <v>1086</v>
+        <v>1090</v>
       </c>
       <c r="E751" t="s">
-        <v>1090</v>
+        <v>1087</v>
       </c>
       <c r="F751" t="s">
         <v>24</v>
@@ -19291,10 +19291,10 @@
         <v>1092</v>
       </c>
       <c r="D752" t="s">
-        <v>1086</v>
+        <v>1093</v>
       </c>
       <c r="E752" t="s">
-        <v>1093</v>
+        <v>1087</v>
       </c>
       <c r="F752" t="s">
         <v>713</v>
@@ -19311,10 +19311,10 @@
         <v>1092</v>
       </c>
       <c r="D753" t="s">
-        <v>1086</v>
+        <v>1093</v>
       </c>
       <c r="E753" t="s">
-        <v>1093</v>
+        <v>1087</v>
       </c>
       <c r="F753" t="s">
         <v>713</v>
@@ -19331,10 +19331,10 @@
         <v>1092</v>
       </c>
       <c r="D754" t="s">
-        <v>1086</v>
+        <v>1093</v>
       </c>
       <c r="E754" t="s">
-        <v>1093</v>
+        <v>1087</v>
       </c>
       <c r="F754" t="s">
         <v>713</v>
@@ -19351,10 +19351,10 @@
         <v>1092</v>
       </c>
       <c r="D755" t="s">
-        <v>1086</v>
+        <v>1093</v>
       </c>
       <c r="E755" t="s">
-        <v>1093</v>
+        <v>1087</v>
       </c>
       <c r="F755" t="s">
         <v>713</v>
@@ -19371,10 +19371,10 @@
         <v>1092</v>
       </c>
       <c r="D756" t="s">
-        <v>1086</v>
+        <v>1093</v>
       </c>
       <c r="E756" t="s">
-        <v>1093</v>
+        <v>1087</v>
       </c>
       <c r="F756" t="s">
         <v>713</v>
@@ -19391,10 +19391,10 @@
         <v>1092</v>
       </c>
       <c r="D757" t="s">
-        <v>1086</v>
+        <v>1093</v>
       </c>
       <c r="E757" t="s">
-        <v>1093</v>
+        <v>1087</v>
       </c>
       <c r="F757" t="s">
         <v>713</v>
@@ -19408,10 +19408,10 @@
         <v>7</v>
       </c>
       <c r="C758" t="s">
-        <v>1089</v>
+        <v>1085</v>
       </c>
       <c r="D758" t="s">
-        <v>1086</v>
+        <v>1090</v>
       </c>
       <c r="E758" t="s">
         <v>1087</v>
@@ -19428,13 +19428,13 @@
         <v>7</v>
       </c>
       <c r="C759" t="s">
-        <v>1092</v>
+        <v>1065</v>
       </c>
       <c r="D759" t="s">
-        <v>1086</v>
+        <v>1093</v>
       </c>
       <c r="E759" t="s">
-        <v>1065</v>
+        <v>1087</v>
       </c>
       <c r="F759" t="s">
         <v>16</v>
@@ -19451,10 +19451,10 @@
         <v>1092</v>
       </c>
       <c r="D760" t="s">
-        <v>1086</v>
+        <v>1093</v>
       </c>
       <c r="E760" t="s">
-        <v>1093</v>
+        <v>1087</v>
       </c>
       <c r="F760" t="s">
         <v>713</v>
@@ -19471,10 +19471,10 @@
         <v>1092</v>
       </c>
       <c r="D761" t="s">
-        <v>1086</v>
+        <v>1093</v>
       </c>
       <c r="E761" t="s">
-        <v>1093</v>
+        <v>1087</v>
       </c>
       <c r="F761" t="s">
         <v>713</v>
@@ -19488,13 +19488,13 @@
         <v>7</v>
       </c>
       <c r="C762" t="s">
+        <v>1065</v>
+      </c>
+      <c r="D762" t="s">
         <v>1104</v>
       </c>
-      <c r="D762" t="s">
-        <v>1086</v>
-      </c>
       <c r="E762" t="s">
-        <v>1065</v>
+        <v>1087</v>
       </c>
       <c r="F762" t="s">
         <v>24</v>
@@ -19511,10 +19511,10 @@
         <v>1092</v>
       </c>
       <c r="D763" t="s">
-        <v>1086</v>
+        <v>1093</v>
       </c>
       <c r="E763" t="s">
-        <v>1093</v>
+        <v>1087</v>
       </c>
       <c r="F763" t="s">
         <v>713</v>
@@ -19531,10 +19531,10 @@
         <v>1107</v>
       </c>
       <c r="D764" t="s">
-        <v>1086</v>
+        <v>1108</v>
       </c>
       <c r="E764" t="s">
-        <v>1108</v>
+        <v>1087</v>
       </c>
       <c r="F764" t="s">
         <v>24</v>
@@ -19548,13 +19548,13 @@
         <v>7</v>
       </c>
       <c r="C765" t="s">
-        <v>1085</v>
+        <v>1092</v>
       </c>
       <c r="D765" t="s">
         <v>1086</v>
       </c>
       <c r="E765" t="s">
-        <v>1093</v>
+        <v>1087</v>
       </c>
       <c r="F765" t="s">
         <v>24</v>
@@ -19568,13 +19568,13 @@
         <v>7</v>
       </c>
       <c r="C766" t="s">
+        <v>1111</v>
+      </c>
+      <c r="D766" t="s">
         <v>1104</v>
       </c>
-      <c r="D766" t="s">
-        <v>1086</v>
-      </c>
       <c r="E766" t="s">
-        <v>1111</v>
+        <v>1087</v>
       </c>
       <c r="F766" t="s">
         <v>24</v>
@@ -19591,10 +19591,10 @@
         <v>1113</v>
       </c>
       <c r="D767" t="s">
-        <v>1086</v>
+        <v>1114</v>
       </c>
       <c r="E767" t="s">
-        <v>1114</v>
+        <v>1087</v>
       </c>
       <c r="F767" t="s">
         <v>24</v>
@@ -19611,10 +19611,10 @@
         <v>1092</v>
       </c>
       <c r="D768" t="s">
-        <v>1086</v>
+        <v>1093</v>
       </c>
       <c r="E768" t="s">
-        <v>1093</v>
+        <v>1087</v>
       </c>
       <c r="F768" t="s">
         <v>713</v>
@@ -19631,10 +19631,10 @@
         <v>1092</v>
       </c>
       <c r="D769" t="s">
-        <v>1086</v>
+        <v>1093</v>
       </c>
       <c r="E769" t="s">
-        <v>1093</v>
+        <v>1087</v>
       </c>
       <c r="F769" t="s">
         <v>713</v>
@@ -19651,10 +19651,10 @@
         <v>1118</v>
       </c>
       <c r="D770" t="s">
-        <v>1086</v>
+        <v>1119</v>
       </c>
       <c r="E770" t="s">
-        <v>1119</v>
+        <v>1087</v>
       </c>
       <c r="F770" t="s">
         <v>24</v>
@@ -19671,10 +19671,10 @@
         <v>1092</v>
       </c>
       <c r="D771" t="s">
-        <v>1086</v>
+        <v>1093</v>
       </c>
       <c r="E771" t="s">
-        <v>1093</v>
+        <v>1087</v>
       </c>
       <c r="F771" t="s">
         <v>713</v>
@@ -19691,10 +19691,10 @@
         <v>1092</v>
       </c>
       <c r="D772" t="s">
-        <v>1086</v>
+        <v>1093</v>
       </c>
       <c r="E772" t="s">
-        <v>1093</v>
+        <v>1087</v>
       </c>
       <c r="F772" t="s">
         <v>713</v>
@@ -19711,10 +19711,10 @@
         <v>1092</v>
       </c>
       <c r="D773" t="s">
-        <v>1086</v>
+        <v>1093</v>
       </c>
       <c r="E773" t="s">
-        <v>1093</v>
+        <v>1087</v>
       </c>
       <c r="F773" t="s">
         <v>713</v>
@@ -19731,10 +19731,10 @@
         <v>1124</v>
       </c>
       <c r="D774" t="s">
-        <v>1086</v>
+        <v>1125</v>
       </c>
       <c r="E774" t="s">
-        <v>1125</v>
+        <v>1087</v>
       </c>
       <c r="F774" t="s">
         <v>24</v>
@@ -19751,10 +19751,10 @@
         <v>1092</v>
       </c>
       <c r="D775" t="s">
-        <v>1086</v>
+        <v>1093</v>
       </c>
       <c r="E775" t="s">
-        <v>1093</v>
+        <v>1087</v>
       </c>
       <c r="F775" t="s">
         <v>713</v>
@@ -19788,13 +19788,13 @@
         <v>7</v>
       </c>
       <c r="C777" t="s">
-        <v>1128</v>
+        <v>1132</v>
       </c>
       <c r="D777" t="s">
         <v>1129</v>
       </c>
       <c r="E777" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="F777" t="s">
         <v>713</v>
@@ -19811,10 +19811,10 @@
         <v>1134</v>
       </c>
       <c r="D778" t="s">
-        <v>1129</v>
+        <v>1135</v>
       </c>
       <c r="E778" t="s">
-        <v>1135</v>
+        <v>1130</v>
       </c>
       <c r="F778" t="s">
         <v>24</v>
@@ -19831,10 +19831,10 @@
         <v>1137</v>
       </c>
       <c r="D779" t="s">
-        <v>1129</v>
+        <v>1138</v>
       </c>
       <c r="E779" t="s">
-        <v>1138</v>
+        <v>1130</v>
       </c>
       <c r="F779" t="s">
         <v>24</v>
@@ -19848,13 +19848,13 @@
         <v>7</v>
       </c>
       <c r="C780" t="s">
-        <v>1128</v>
+        <v>1132</v>
       </c>
       <c r="D780" t="s">
         <v>1129</v>
       </c>
       <c r="E780" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="F780" t="s">
         <v>713</v>
@@ -19868,13 +19868,13 @@
         <v>7</v>
       </c>
       <c r="C781" t="s">
-        <v>1128</v>
+        <v>1132</v>
       </c>
       <c r="D781" t="s">
         <v>1129</v>
       </c>
       <c r="E781" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="F781" t="s">
         <v>713</v>
@@ -19888,13 +19888,13 @@
         <v>7</v>
       </c>
       <c r="C782" t="s">
-        <v>1128</v>
+        <v>1142</v>
       </c>
       <c r="D782" t="s">
         <v>1129</v>
       </c>
       <c r="E782" t="s">
-        <v>1142</v>
+        <v>1130</v>
       </c>
       <c r="F782" t="s">
         <v>713</v>
@@ -19908,13 +19908,13 @@
         <v>7</v>
       </c>
       <c r="C783" t="s">
-        <v>1128</v>
+        <v>1132</v>
       </c>
       <c r="D783" t="s">
         <v>1129</v>
       </c>
       <c r="E783" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="F783" t="s">
         <v>713</v>
@@ -19928,13 +19928,13 @@
         <v>7</v>
       </c>
       <c r="C784" t="s">
-        <v>1128</v>
+        <v>1132</v>
       </c>
       <c r="D784" t="s">
         <v>1129</v>
       </c>
       <c r="E784" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="F784" t="s">
         <v>713</v>
@@ -19948,13 +19948,13 @@
         <v>7</v>
       </c>
       <c r="C785" t="s">
-        <v>1128</v>
+        <v>1132</v>
       </c>
       <c r="D785" t="s">
         <v>1129</v>
       </c>
       <c r="E785" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="F785" t="s">
         <v>713</v>
@@ -19968,13 +19968,13 @@
         <v>7</v>
       </c>
       <c r="C786" t="s">
-        <v>1128</v>
+        <v>1132</v>
       </c>
       <c r="D786" t="s">
         <v>1129</v>
       </c>
       <c r="E786" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="F786" t="s">
         <v>713</v>
@@ -19988,13 +19988,13 @@
         <v>7</v>
       </c>
       <c r="C787" t="s">
-        <v>1128</v>
+        <v>1132</v>
       </c>
       <c r="D787" t="s">
         <v>1129</v>
       </c>
       <c r="E787" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="F787" t="s">
         <v>713</v>
@@ -20008,13 +20008,13 @@
         <v>7</v>
       </c>
       <c r="C788" t="s">
-        <v>1128</v>
+        <v>1132</v>
       </c>
       <c r="D788" t="s">
         <v>1129</v>
       </c>
       <c r="E788" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="F788" t="s">
         <v>713</v>
@@ -20028,10 +20028,10 @@
         <v>7</v>
       </c>
       <c r="C789" t="s">
+        <v>1128</v>
+      </c>
+      <c r="D789" t="s">
         <v>1150</v>
-      </c>
-      <c r="D789" t="s">
-        <v>1129</v>
       </c>
       <c r="E789" t="s">
         <v>1130</v>
@@ -20048,13 +20048,13 @@
         <v>7</v>
       </c>
       <c r="C790" t="s">
-        <v>1128</v>
+        <v>1132</v>
       </c>
       <c r="D790" t="s">
         <v>1129</v>
       </c>
       <c r="E790" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="F790" t="s">
         <v>713</v>
@@ -20068,13 +20068,13 @@
         <v>7</v>
       </c>
       <c r="C791" t="s">
+        <v>1142</v>
+      </c>
+      <c r="D791" t="s">
         <v>1153</v>
       </c>
-      <c r="D791" t="s">
-        <v>1129</v>
-      </c>
       <c r="E791" t="s">
-        <v>1142</v>
+        <v>1130</v>
       </c>
       <c r="F791" t="s">
         <v>24</v>
@@ -20088,13 +20088,13 @@
         <v>7</v>
       </c>
       <c r="C792" t="s">
+        <v>1155</v>
+      </c>
+      <c r="D792" t="s">
         <v>1150</v>
       </c>
-      <c r="D792" t="s">
-        <v>1129</v>
-      </c>
       <c r="E792" t="s">
-        <v>1155</v>
+        <v>1130</v>
       </c>
       <c r="F792" t="s">
         <v>24</v>
@@ -20108,13 +20108,13 @@
         <v>7</v>
       </c>
       <c r="C793" t="s">
-        <v>1128</v>
+        <v>1132</v>
       </c>
       <c r="D793" t="s">
         <v>1129</v>
       </c>
       <c r="E793" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="F793" t="s">
         <v>713</v>
@@ -20128,13 +20128,13 @@
         <v>7</v>
       </c>
       <c r="C794" t="s">
+        <v>1132</v>
+      </c>
+      <c r="D794" t="s">
         <v>1158</v>
       </c>
-      <c r="D794" t="s">
-        <v>1129</v>
-      </c>
       <c r="E794" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="F794" t="s">
         <v>24</v>
@@ -20148,13 +20148,13 @@
         <v>7</v>
       </c>
       <c r="C795" t="s">
-        <v>1128</v>
+        <v>1160</v>
       </c>
       <c r="D795" t="s">
         <v>1129</v>
       </c>
       <c r="E795" t="s">
-        <v>1160</v>
+        <v>1130</v>
       </c>
       <c r="F795" t="s">
         <v>24</v>
@@ -20168,13 +20168,13 @@
         <v>7</v>
       </c>
       <c r="C796" t="s">
-        <v>1128</v>
+        <v>1132</v>
       </c>
       <c r="D796" t="s">
         <v>1129</v>
       </c>
       <c r="E796" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="F796" t="s">
         <v>713</v>
@@ -20191,10 +20191,10 @@
         <v>1163</v>
       </c>
       <c r="D797" t="s">
-        <v>1129</v>
+        <v>1164</v>
       </c>
       <c r="E797" t="s">
-        <v>1164</v>
+        <v>1130</v>
       </c>
       <c r="F797" t="s">
         <v>24</v>
@@ -20211,10 +20211,10 @@
         <v>1166</v>
       </c>
       <c r="D798" t="s">
-        <v>1129</v>
+        <v>1167</v>
       </c>
       <c r="E798" t="s">
-        <v>1167</v>
+        <v>1130</v>
       </c>
       <c r="F798" t="s">
         <v>24</v>
@@ -20228,13 +20228,13 @@
         <v>7</v>
       </c>
       <c r="C799" t="s">
-        <v>1128</v>
+        <v>1132</v>
       </c>
       <c r="D799" t="s">
         <v>1129</v>
       </c>
       <c r="E799" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="F799" t="s">
         <v>713</v>
@@ -20248,13 +20248,13 @@
         <v>7</v>
       </c>
       <c r="C800" t="s">
-        <v>1128</v>
+        <v>1132</v>
       </c>
       <c r="D800" t="s">
         <v>1129</v>
       </c>
       <c r="E800" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="F800" t="s">
         <v>713</v>
@@ -20268,13 +20268,13 @@
         <v>7</v>
       </c>
       <c r="C801" t="s">
-        <v>1128</v>
+        <v>1132</v>
       </c>
       <c r="D801" t="s">
         <v>1129</v>
       </c>
       <c r="E801" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="F801" t="s">
         <v>713</v>
@@ -20288,13 +20288,13 @@
         <v>7</v>
       </c>
       <c r="C802" t="s">
-        <v>1128</v>
+        <v>1132</v>
       </c>
       <c r="D802" t="s">
         <v>1129</v>
       </c>
       <c r="E802" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="F802" t="s">
         <v>713</v>
@@ -20308,13 +20308,13 @@
         <v>7</v>
       </c>
       <c r="C803" t="s">
-        <v>1128</v>
+        <v>1132</v>
       </c>
       <c r="D803" t="s">
         <v>1129</v>
       </c>
       <c r="E803" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="F803" t="s">
         <v>713</v>
@@ -20328,13 +20328,13 @@
         <v>7</v>
       </c>
       <c r="C804" t="s">
-        <v>1128</v>
+        <v>1132</v>
       </c>
       <c r="D804" t="s">
         <v>1129</v>
       </c>
       <c r="E804" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="F804" t="s">
         <v>713</v>
@@ -20348,13 +20348,13 @@
         <v>7</v>
       </c>
       <c r="C805" t="s">
-        <v>1128</v>
+        <v>1132</v>
       </c>
       <c r="D805" t="s">
         <v>1129</v>
       </c>
       <c r="E805" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="F805" t="s">
         <v>713</v>
@@ -20368,13 +20368,13 @@
         <v>7</v>
       </c>
       <c r="C806" t="s">
-        <v>1128</v>
+        <v>1132</v>
       </c>
       <c r="D806" t="s">
         <v>1129</v>
       </c>
       <c r="E806" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="F806" t="s">
         <v>713</v>
@@ -20388,13 +20388,13 @@
         <v>7</v>
       </c>
       <c r="C807" t="s">
-        <v>1128</v>
+        <v>1132</v>
       </c>
       <c r="D807" t="s">
         <v>1129</v>
       </c>
       <c r="E807" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="F807" t="s">
         <v>713</v>
@@ -20471,10 +20471,10 @@
         <v>1184</v>
       </c>
       <c r="D811" t="s">
-        <v>1179</v>
+        <v>1185</v>
       </c>
       <c r="E811" t="s">
-        <v>1185</v>
+        <v>1180</v>
       </c>
       <c r="F811" t="s">
         <v>24</v>
@@ -20528,13 +20528,13 @@
         <v>7</v>
       </c>
       <c r="C814" t="s">
-        <v>1178</v>
+        <v>1184</v>
       </c>
       <c r="D814" t="s">
         <v>1179</v>
       </c>
       <c r="E814" t="s">
-        <v>1185</v>
+        <v>1180</v>
       </c>
       <c r="F814" t="s">
         <v>713</v>
@@ -20551,10 +20551,10 @@
         <v>1190</v>
       </c>
       <c r="D815" t="s">
-        <v>1179</v>
+        <v>1191</v>
       </c>
       <c r="E815" t="s">
-        <v>1191</v>
+        <v>1180</v>
       </c>
       <c r="F815" t="s">
         <v>24</v>
@@ -20671,10 +20671,10 @@
         <v>1198</v>
       </c>
       <c r="D821" t="s">
-        <v>1179</v>
+        <v>1199</v>
       </c>
       <c r="E821" t="s">
-        <v>1199</v>
+        <v>1180</v>
       </c>
       <c r="F821" t="s">
         <v>16</v>
@@ -20691,10 +20691,10 @@
         <v>1201</v>
       </c>
       <c r="D822" t="s">
-        <v>1179</v>
+        <v>1202</v>
       </c>
       <c r="E822" t="s">
-        <v>1202</v>
+        <v>1180</v>
       </c>
       <c r="F822" t="s">
         <v>713</v>
@@ -20708,13 +20708,13 @@
         <v>7</v>
       </c>
       <c r="C823" t="s">
-        <v>1178</v>
+        <v>1201</v>
       </c>
       <c r="D823" t="s">
         <v>1179</v>
       </c>
       <c r="E823" t="s">
-        <v>1202</v>
+        <v>1180</v>
       </c>
       <c r="F823" t="s">
         <v>713</v>
@@ -20731,10 +20731,10 @@
         <v>1201</v>
       </c>
       <c r="D824" t="s">
-        <v>1179</v>
+        <v>1202</v>
       </c>
       <c r="E824" t="s">
-        <v>1202</v>
+        <v>1180</v>
       </c>
       <c r="F824" t="s">
         <v>713</v>
@@ -20751,10 +20751,10 @@
         <v>1201</v>
       </c>
       <c r="D825" t="s">
-        <v>1179</v>
+        <v>1202</v>
       </c>
       <c r="E825" t="s">
-        <v>1202</v>
+        <v>1180</v>
       </c>
       <c r="F825" t="s">
         <v>713</v>
@@ -20771,10 +20771,10 @@
         <v>1201</v>
       </c>
       <c r="D826" t="s">
-        <v>1179</v>
+        <v>1202</v>
       </c>
       <c r="E826" t="s">
-        <v>1202</v>
+        <v>1180</v>
       </c>
       <c r="F826" t="s">
         <v>713</v>
@@ -20791,10 +20791,10 @@
         <v>1201</v>
       </c>
       <c r="D827" t="s">
-        <v>1179</v>
+        <v>1202</v>
       </c>
       <c r="E827" t="s">
-        <v>1202</v>
+        <v>1180</v>
       </c>
       <c r="F827" t="s">
         <v>713</v>
@@ -20808,13 +20808,13 @@
         <v>7</v>
       </c>
       <c r="C828" t="s">
-        <v>1178</v>
+        <v>1201</v>
       </c>
       <c r="D828" t="s">
         <v>1179</v>
       </c>
       <c r="E828" t="s">
-        <v>1202</v>
+        <v>1180</v>
       </c>
       <c r="F828" t="s">
         <v>713</v>
@@ -20848,13 +20848,13 @@
         <v>7</v>
       </c>
       <c r="C830" t="s">
-        <v>1178</v>
+        <v>1184</v>
       </c>
       <c r="D830" t="s">
         <v>1179</v>
       </c>
       <c r="E830" t="s">
-        <v>1185</v>
+        <v>1180</v>
       </c>
       <c r="F830" t="s">
         <v>713</v>
@@ -21048,13 +21048,13 @@
         <v>7</v>
       </c>
       <c r="C840" t="s">
-        <v>1220</v>
+        <v>1224</v>
       </c>
       <c r="D840" t="s">
         <v>1221</v>
       </c>
       <c r="E840" t="s">
-        <v>1224</v>
+        <v>1222</v>
       </c>
       <c r="F840" t="s">
         <v>713</v>
@@ -21068,13 +21068,13 @@
         <v>7</v>
       </c>
       <c r="C841" t="s">
-        <v>1220</v>
+        <v>1224</v>
       </c>
       <c r="D841" t="s">
         <v>1221</v>
       </c>
       <c r="E841" t="s">
-        <v>1224</v>
+        <v>1222</v>
       </c>
       <c r="F841" t="s">
         <v>713</v>
@@ -21088,13 +21088,13 @@
         <v>7</v>
       </c>
       <c r="C842" t="s">
-        <v>1220</v>
+        <v>1224</v>
       </c>
       <c r="D842" t="s">
         <v>1221</v>
       </c>
       <c r="E842" t="s">
-        <v>1224</v>
+        <v>1222</v>
       </c>
       <c r="F842" t="s">
         <v>713</v>
@@ -21108,13 +21108,13 @@
         <v>7</v>
       </c>
       <c r="C843" t="s">
-        <v>1220</v>
+        <v>1224</v>
       </c>
       <c r="D843" t="s">
         <v>1221</v>
       </c>
       <c r="E843" t="s">
-        <v>1224</v>
+        <v>1222</v>
       </c>
       <c r="F843" t="s">
         <v>713</v>
@@ -21128,13 +21128,13 @@
         <v>7</v>
       </c>
       <c r="C844" t="s">
-        <v>1220</v>
+        <v>1224</v>
       </c>
       <c r="D844" t="s">
         <v>1221</v>
       </c>
       <c r="E844" t="s">
-        <v>1224</v>
+        <v>1222</v>
       </c>
       <c r="F844" t="s">
         <v>713</v>
@@ -21148,13 +21148,13 @@
         <v>7</v>
       </c>
       <c r="C845" t="s">
-        <v>1220</v>
+        <v>1224</v>
       </c>
       <c r="D845" t="s">
         <v>1221</v>
       </c>
       <c r="E845" t="s">
-        <v>1224</v>
+        <v>1222</v>
       </c>
       <c r="F845" t="s">
         <v>713</v>
@@ -21168,13 +21168,13 @@
         <v>7</v>
       </c>
       <c r="C846" t="s">
-        <v>1220</v>
+        <v>1224</v>
       </c>
       <c r="D846" t="s">
         <v>1221</v>
       </c>
       <c r="E846" t="s">
-        <v>1224</v>
+        <v>1222</v>
       </c>
       <c r="F846" t="s">
         <v>713</v>
@@ -21188,13 +21188,13 @@
         <v>7</v>
       </c>
       <c r="C847" t="s">
-        <v>1184</v>
+        <v>1232</v>
       </c>
       <c r="D847" t="s">
-        <v>1221</v>
+        <v>1185</v>
       </c>
       <c r="E847" t="s">
-        <v>1232</v>
+        <v>1222</v>
       </c>
       <c r="F847" t="s">
         <v>713</v>
@@ -21208,13 +21208,13 @@
         <v>7</v>
       </c>
       <c r="C848" t="s">
-        <v>1184</v>
+        <v>1232</v>
       </c>
       <c r="D848" t="s">
-        <v>1221</v>
+        <v>1185</v>
       </c>
       <c r="E848" t="s">
-        <v>1232</v>
+        <v>1222</v>
       </c>
       <c r="F848" t="s">
         <v>713</v>
@@ -21228,13 +21228,13 @@
         <v>7</v>
       </c>
       <c r="C849" t="s">
-        <v>1184</v>
+        <v>1232</v>
       </c>
       <c r="D849" t="s">
-        <v>1221</v>
+        <v>1185</v>
       </c>
       <c r="E849" t="s">
-        <v>1232</v>
+        <v>1222</v>
       </c>
       <c r="F849" t="s">
         <v>713</v>
@@ -21248,13 +21248,13 @@
         <v>7</v>
       </c>
       <c r="C850" t="s">
+        <v>1232</v>
+      </c>
+      <c r="D850" t="s">
         <v>1236</v>
       </c>
-      <c r="D850" t="s">
-        <v>1221</v>
-      </c>
       <c r="E850" t="s">
-        <v>1232</v>
+        <v>1222</v>
       </c>
       <c r="F850" t="s">
         <v>713</v>
@@ -21268,13 +21268,13 @@
         <v>7</v>
       </c>
       <c r="C851" t="s">
-        <v>1184</v>
+        <v>1232</v>
       </c>
       <c r="D851" t="s">
-        <v>1221</v>
+        <v>1185</v>
       </c>
       <c r="E851" t="s">
-        <v>1232</v>
+        <v>1222</v>
       </c>
       <c r="F851" t="s">
         <v>713</v>
@@ -21288,13 +21288,13 @@
         <v>7</v>
       </c>
       <c r="C852" t="s">
-        <v>1184</v>
+        <v>1232</v>
       </c>
       <c r="D852" t="s">
-        <v>1221</v>
+        <v>1185</v>
       </c>
       <c r="E852" t="s">
-        <v>1232</v>
+        <v>1222</v>
       </c>
       <c r="F852" t="s">
         <v>713</v>
@@ -21308,13 +21308,13 @@
         <v>7</v>
       </c>
       <c r="C853" t="s">
-        <v>1220</v>
+        <v>1224</v>
       </c>
       <c r="D853" t="s">
         <v>1221</v>
       </c>
       <c r="E853" t="s">
-        <v>1224</v>
+        <v>1222</v>
       </c>
       <c r="F853" t="s">
         <v>713</v>
@@ -21328,13 +21328,13 @@
         <v>7</v>
       </c>
       <c r="C854" t="s">
-        <v>1220</v>
+        <v>1224</v>
       </c>
       <c r="D854" t="s">
         <v>1221</v>
       </c>
       <c r="E854" t="s">
-        <v>1224</v>
+        <v>1222</v>
       </c>
       <c r="F854" t="s">
         <v>16</v>
@@ -21348,13 +21348,13 @@
         <v>7</v>
       </c>
       <c r="C855" t="s">
-        <v>1220</v>
+        <v>1224</v>
       </c>
       <c r="D855" t="s">
         <v>1221</v>
       </c>
       <c r="E855" t="s">
-        <v>1224</v>
+        <v>1222</v>
       </c>
       <c r="F855" t="s">
         <v>16</v>
@@ -21368,13 +21368,13 @@
         <v>7</v>
       </c>
       <c r="C856" t="s">
-        <v>1220</v>
+        <v>1224</v>
       </c>
       <c r="D856" t="s">
         <v>1221</v>
       </c>
       <c r="E856" t="s">
-        <v>1224</v>
+        <v>1222</v>
       </c>
       <c r="F856" t="s">
         <v>16</v>
@@ -21388,13 +21388,13 @@
         <v>7</v>
       </c>
       <c r="C857" t="s">
-        <v>1220</v>
+        <v>1224</v>
       </c>
       <c r="D857" t="s">
         <v>1221</v>
       </c>
       <c r="E857" t="s">
-        <v>1224</v>
+        <v>1222</v>
       </c>
       <c r="F857" t="s">
         <v>713</v>
@@ -21408,13 +21408,13 @@
         <v>7</v>
       </c>
       <c r="C858" t="s">
-        <v>1220</v>
+        <v>1224</v>
       </c>
       <c r="D858" t="s">
         <v>1221</v>
       </c>
       <c r="E858" t="s">
-        <v>1224</v>
+        <v>1222</v>
       </c>
       <c r="F858" t="s">
         <v>713</v>
@@ -21428,13 +21428,13 @@
         <v>7</v>
       </c>
       <c r="C859" t="s">
-        <v>1220</v>
+        <v>1224</v>
       </c>
       <c r="D859" t="s">
         <v>1221</v>
       </c>
       <c r="E859" t="s">
-        <v>1224</v>
+        <v>1222</v>
       </c>
       <c r="F859" t="s">
         <v>16</v>
@@ -21448,13 +21448,13 @@
         <v>7</v>
       </c>
       <c r="C860" t="s">
-        <v>1220</v>
+        <v>1224</v>
       </c>
       <c r="D860" t="s">
         <v>1221</v>
       </c>
       <c r="E860" t="s">
-        <v>1224</v>
+        <v>1222</v>
       </c>
       <c r="F860" t="s">
         <v>713</v>
@@ -21468,13 +21468,13 @@
         <v>7</v>
       </c>
       <c r="C861" t="s">
-        <v>1220</v>
+        <v>1224</v>
       </c>
       <c r="D861" t="s">
         <v>1221</v>
       </c>
       <c r="E861" t="s">
-        <v>1224</v>
+        <v>1222</v>
       </c>
       <c r="F861" t="s">
         <v>713</v>
@@ -21488,13 +21488,13 @@
         <v>7</v>
       </c>
       <c r="C862" t="s">
-        <v>1220</v>
+        <v>1224</v>
       </c>
       <c r="D862" t="s">
         <v>1221</v>
       </c>
       <c r="E862" t="s">
-        <v>1224</v>
+        <v>1222</v>
       </c>
       <c r="F862" t="s">
         <v>713</v>
@@ -21508,13 +21508,13 @@
         <v>7</v>
       </c>
       <c r="C863" t="s">
-        <v>1220</v>
+        <v>1224</v>
       </c>
       <c r="D863" t="s">
         <v>1221</v>
       </c>
       <c r="E863" t="s">
-        <v>1224</v>
+        <v>1222</v>
       </c>
       <c r="F863" t="s">
         <v>713</v>
@@ -21528,13 +21528,13 @@
         <v>7</v>
       </c>
       <c r="C864" t="s">
-        <v>1220</v>
+        <v>1224</v>
       </c>
       <c r="D864" t="s">
         <v>1221</v>
       </c>
       <c r="E864" t="s">
-        <v>1224</v>
+        <v>1222</v>
       </c>
       <c r="F864" t="s">
         <v>713</v>
@@ -21548,13 +21548,13 @@
         <v>7</v>
       </c>
       <c r="C865" t="s">
-        <v>1220</v>
+        <v>1224</v>
       </c>
       <c r="D865" t="s">
         <v>1221</v>
       </c>
       <c r="E865" t="s">
-        <v>1224</v>
+        <v>1222</v>
       </c>
       <c r="F865" t="s">
         <v>713</v>
@@ -21568,13 +21568,13 @@
         <v>7</v>
       </c>
       <c r="C866" t="s">
-        <v>1220</v>
+        <v>1224</v>
       </c>
       <c r="D866" t="s">
         <v>1221</v>
       </c>
       <c r="E866" t="s">
-        <v>1224</v>
+        <v>1222</v>
       </c>
       <c r="F866" t="s">
         <v>713</v>
@@ -21608,10 +21608,10 @@
         <v>7</v>
       </c>
       <c r="C868" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D868" t="s">
         <v>1258</v>
-      </c>
-      <c r="D868" t="s">
-        <v>1255</v>
       </c>
       <c r="E868" t="s">
         <v>1256</v>
@@ -21628,10 +21628,10 @@
         <v>7</v>
       </c>
       <c r="C869" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D869" t="s">
         <v>1258</v>
-      </c>
-      <c r="D869" t="s">
-        <v>1255</v>
       </c>
       <c r="E869" t="s">
         <v>1256</v>
@@ -21648,10 +21648,10 @@
         <v>7</v>
       </c>
       <c r="C870" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D870" t="s">
         <v>1258</v>
-      </c>
-      <c r="D870" t="s">
-        <v>1255</v>
       </c>
       <c r="E870" t="s">
         <v>1256</v>
@@ -21668,10 +21668,10 @@
         <v>7</v>
       </c>
       <c r="C871" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D871" t="s">
         <v>1258</v>
-      </c>
-      <c r="D871" t="s">
-        <v>1255</v>
       </c>
       <c r="E871" t="s">
         <v>1256</v>
@@ -21688,10 +21688,10 @@
         <v>7</v>
       </c>
       <c r="C872" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D872" t="s">
         <v>1258</v>
-      </c>
-      <c r="D872" t="s">
-        <v>1255</v>
       </c>
       <c r="E872" t="s">
         <v>1256</v>
@@ -21708,10 +21708,10 @@
         <v>7</v>
       </c>
       <c r="C873" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D873" t="s">
         <v>1258</v>
-      </c>
-      <c r="D873" t="s">
-        <v>1255</v>
       </c>
       <c r="E873" t="s">
         <v>1256</v>
@@ -21728,10 +21728,10 @@
         <v>7</v>
       </c>
       <c r="C874" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D874" t="s">
         <v>1258</v>
-      </c>
-      <c r="D874" t="s">
-        <v>1255</v>
       </c>
       <c r="E874" t="s">
         <v>1256</v>
@@ -21748,10 +21748,10 @@
         <v>7</v>
       </c>
       <c r="C875" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D875" t="s">
         <v>1258</v>
-      </c>
-      <c r="D875" t="s">
-        <v>1255</v>
       </c>
       <c r="E875" t="s">
         <v>1256</v>
@@ -21768,10 +21768,10 @@
         <v>7</v>
       </c>
       <c r="C876" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D876" t="s">
         <v>1258</v>
-      </c>
-      <c r="D876" t="s">
-        <v>1255</v>
       </c>
       <c r="E876" t="s">
         <v>1256</v>
@@ -21788,10 +21788,10 @@
         <v>7</v>
       </c>
       <c r="C877" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D877" t="s">
         <v>1258</v>
-      </c>
-      <c r="D877" t="s">
-        <v>1255</v>
       </c>
       <c r="E877" t="s">
         <v>1256</v>
@@ -21808,10 +21808,10 @@
         <v>7</v>
       </c>
       <c r="C878" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D878" t="s">
         <v>1258</v>
-      </c>
-      <c r="D878" t="s">
-        <v>1255</v>
       </c>
       <c r="E878" t="s">
         <v>1256</v>
@@ -21828,10 +21828,10 @@
         <v>7</v>
       </c>
       <c r="C879" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D879" t="s">
         <v>1258</v>
-      </c>
-      <c r="D879" t="s">
-        <v>1255</v>
       </c>
       <c r="E879" t="s">
         <v>1256</v>
@@ -21848,10 +21848,10 @@
         <v>7</v>
       </c>
       <c r="C880" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D880" t="s">
         <v>1258</v>
-      </c>
-      <c r="D880" t="s">
-        <v>1255</v>
       </c>
       <c r="E880" t="s">
         <v>1256</v>
@@ -21868,10 +21868,10 @@
         <v>7</v>
       </c>
       <c r="C881" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D881" t="s">
         <v>1258</v>
-      </c>
-      <c r="D881" t="s">
-        <v>1255</v>
       </c>
       <c r="E881" t="s">
         <v>1256</v>
@@ -21888,10 +21888,10 @@
         <v>7</v>
       </c>
       <c r="C882" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D882" t="s">
         <v>1258</v>
-      </c>
-      <c r="D882" t="s">
-        <v>1255</v>
       </c>
       <c r="E882" t="s">
         <v>1256</v>
@@ -21908,10 +21908,10 @@
         <v>7</v>
       </c>
       <c r="C883" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D883" t="s">
         <v>1258</v>
-      </c>
-      <c r="D883" t="s">
-        <v>1255</v>
       </c>
       <c r="E883" t="s">
         <v>1256</v>
@@ -21928,10 +21928,10 @@
         <v>7</v>
       </c>
       <c r="C884" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D884" t="s">
         <v>1258</v>
-      </c>
-      <c r="D884" t="s">
-        <v>1255</v>
       </c>
       <c r="E884" t="s">
         <v>1256</v>
@@ -21948,10 +21948,10 @@
         <v>7</v>
       </c>
       <c r="C885" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D885" t="s">
         <v>1258</v>
-      </c>
-      <c r="D885" t="s">
-        <v>1255</v>
       </c>
       <c r="E885" t="s">
         <v>1256</v>
@@ -21968,10 +21968,10 @@
         <v>7</v>
       </c>
       <c r="C886" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D886" t="s">
         <v>1258</v>
-      </c>
-      <c r="D886" t="s">
-        <v>1255</v>
       </c>
       <c r="E886" t="s">
         <v>1256</v>
@@ -21988,10 +21988,10 @@
         <v>7</v>
       </c>
       <c r="C887" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D887" t="s">
         <v>1258</v>
-      </c>
-      <c r="D887" t="s">
-        <v>1255</v>
       </c>
       <c r="E887" t="s">
         <v>1256</v>
@@ -22008,10 +22008,10 @@
         <v>7</v>
       </c>
       <c r="C888" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D888" t="s">
         <v>1258</v>
-      </c>
-      <c r="D888" t="s">
-        <v>1255</v>
       </c>
       <c r="E888" t="s">
         <v>1256</v>
@@ -22028,10 +22028,10 @@
         <v>7</v>
       </c>
       <c r="C889" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D889" t="s">
         <v>1258</v>
-      </c>
-      <c r="D889" t="s">
-        <v>1255</v>
       </c>
       <c r="E889" t="s">
         <v>1256</v>
@@ -22148,13 +22148,13 @@
         <v>7</v>
       </c>
       <c r="C895" t="s">
-        <v>1281</v>
+        <v>1289</v>
       </c>
       <c r="D895" t="s">
         <v>1282</v>
       </c>
       <c r="E895" t="s">
-        <v>1289</v>
+        <v>1283</v>
       </c>
       <c r="F895" t="s">
         <v>713</v>
@@ -22328,10 +22328,10 @@
         <v>7</v>
       </c>
       <c r="C904" t="s">
-        <v>1281</v>
+        <v>1299</v>
       </c>
       <c r="D904" t="s">
-        <v>1299</v>
+        <v>1282</v>
       </c>
       <c r="E904" t="s">
         <v>1300</v>
@@ -22348,13 +22348,13 @@
         <v>7</v>
       </c>
       <c r="C905" t="s">
-        <v>1281</v>
+        <v>1302</v>
       </c>
       <c r="D905" t="s">
-        <v>1299</v>
+        <v>1282</v>
       </c>
       <c r="E905" t="s">
-        <v>1302</v>
+        <v>1300</v>
       </c>
       <c r="F905" t="s">
         <v>713</v>
@@ -22368,10 +22368,10 @@
         <v>7</v>
       </c>
       <c r="C906" t="s">
-        <v>1281</v>
+        <v>1299</v>
       </c>
       <c r="D906" t="s">
-        <v>1299</v>
+        <v>1282</v>
       </c>
       <c r="E906" t="s">
         <v>1300</v>

--- a/api/2/clv2/xlsx/pt/HumanitarianPlan.xlsx
+++ b/api/2/clv2/xlsx/pt/HumanitarianPlan.xlsx
@@ -25,15 +25,15 @@
     <t>codeforiati:plan-type</t>
   </si>
   <si>
+    <t>codeforiati:plan-end-date</t>
+  </si>
+  <si>
     <t>codeforiati:plan-start-date</t>
   </si>
   <si>
     <t>codeforiati:plan-year</t>
   </si>
   <si>
-    <t>codeforiati:plan-end-date</t>
-  </si>
-  <si>
     <t>HAFG25</t>
   </si>
   <si>
@@ -43,15 +43,15 @@
     <t>Humanitarian needs and response plan</t>
   </si>
   <si>
+    <t>2025-12-31</t>
+  </si>
+  <si>
     <t>2025-01-01</t>
   </si>
   <si>
     <t>2025</t>
   </si>
   <si>
-    <t>2025-12-31</t>
-  </si>
-  <si>
     <t>RIRNPAK25</t>
   </si>
   <si>
@@ -217,15 +217,15 @@
     <t>HAFG24</t>
   </si>
   <si>
+    <t>2024-12-31</t>
+  </si>
+  <si>
     <t>2024-01-01</t>
   </si>
   <si>
     <t>2024</t>
   </si>
   <si>
-    <t>2024-12-31</t>
-  </si>
-  <si>
     <t>RAFG_RRP24</t>
   </si>
   <si>
@@ -421,15 +421,15 @@
     <t>HAFG23</t>
   </si>
   <si>
+    <t>2023-12-31</t>
+  </si>
+  <si>
     <t>2023-01-01</t>
   </si>
   <si>
     <t>2023</t>
   </si>
   <si>
-    <t>2023-12-31</t>
-  </si>
-  <si>
     <t>RAFG23</t>
   </si>
   <si>
@@ -493,21 +493,21 @@
     <t>OMNG2223</t>
   </si>
   <si>
+    <t>2023-05-31</t>
+  </si>
+  <si>
     <t>2022-12-01</t>
   </si>
   <si>
-    <t>2023-05-31</t>
-  </si>
-  <si>
     <t>OMOZ23</t>
   </si>
   <si>
+    <t>2023-09-30</t>
+  </si>
+  <si>
     <t>2023-03-01</t>
   </si>
   <si>
-    <t>2023-09-30</t>
-  </si>
-  <si>
     <t>HMOZ23</t>
   </si>
   <si>
@@ -553,12 +553,12 @@
     <t>RRSDN23</t>
   </si>
   <si>
+    <t>2023-10-31</t>
+  </si>
+  <si>
     <t>2023-05-01</t>
   </si>
   <si>
-    <t>2023-10-31</t>
-  </si>
-  <si>
     <t>HSDN23</t>
   </si>
   <si>
@@ -601,15 +601,15 @@
     <t>HAFG22</t>
   </si>
   <si>
+    <t>2022-12-31</t>
+  </si>
+  <si>
     <t>2022-01-01</t>
   </si>
   <si>
     <t>2022</t>
   </si>
   <si>
-    <t>2022-12-31</t>
-  </si>
-  <si>
     <t>RAFG22</t>
   </si>
   <si>
@@ -631,12 +631,12 @@
     <t>OCUB2223</t>
   </si>
   <si>
+    <t>2023-03-31</t>
+  </si>
+  <si>
     <t>2022-10-20</t>
   </si>
   <si>
-    <t>2023-03-31</t>
-  </si>
-  <si>
     <t>RDRCRRP22</t>
   </si>
   <si>
@@ -652,12 +652,12 @@
     <t>FHTI2223</t>
   </si>
   <si>
+    <t>2023-04-15</t>
+  </si>
+  <si>
     <t>2022-10-16</t>
   </si>
   <si>
-    <t>2023-04-15</t>
-  </si>
-  <si>
     <t>FHTI22</t>
   </si>
   <si>
@@ -688,24 +688,24 @@
     <t>FMWI22</t>
   </si>
   <si>
+    <t>2022-05-31</t>
+  </si>
+  <si>
     <t>2022-02-26</t>
   </si>
   <si>
-    <t>2022-05-31</t>
-  </si>
-  <si>
     <t>HMLI22</t>
   </si>
   <si>
     <t>FMOZ22</t>
   </si>
   <si>
+    <t>2022-09-30</t>
+  </si>
+  <si>
     <t>2022-04-01</t>
   </si>
   <si>
-    <t>2022-09-30</t>
-  </si>
-  <si>
     <t>HMOZ22</t>
   </si>
   <si>
@@ -736,12 +736,12 @@
     <t>OPHL2122</t>
   </si>
   <si>
+    <t>2022-06-30</t>
+  </si>
+  <si>
     <t>2021-12-24</t>
   </si>
   <si>
-    <t>2022-06-30</t>
-  </si>
-  <si>
     <t>RREG22</t>
   </si>
   <si>
@@ -805,15 +805,15 @@
     <t>FAFG21</t>
   </si>
   <si>
+    <t>2021-12-31</t>
+  </si>
+  <si>
     <t>2021-09-01</t>
   </si>
   <si>
     <t>2021</t>
   </si>
   <si>
-    <t>2021-12-31</t>
-  </si>
-  <si>
     <t>HAFG21</t>
   </si>
   <si>
@@ -862,12 +862,12 @@
     <t>FPSE21</t>
   </si>
   <si>
+    <t>2021-08-27</t>
+  </si>
+  <si>
     <t>2021-05-27</t>
   </si>
   <si>
-    <t>2021-08-27</t>
-  </si>
-  <si>
     <t>HETH21</t>
   </si>
   <si>
@@ -880,24 +880,24 @@
     <t>FHTI2122</t>
   </si>
   <si>
+    <t>2022-02-15</t>
+  </si>
+  <si>
     <t>2021-08-16</t>
   </si>
   <si>
-    <t>2022-02-15</t>
-  </si>
-  <si>
     <t>HHTI21</t>
   </si>
   <si>
     <t>FHND2021</t>
   </si>
   <si>
+    <t>2021-06-30</t>
+  </si>
+  <si>
     <t>2020-11-15</t>
   </si>
   <si>
-    <t>2021-06-30</t>
-  </si>
-  <si>
     <t>HHND21</t>
   </si>
   <si>
@@ -916,12 +916,12 @@
     <t>OLBN2122</t>
   </si>
   <si>
+    <t>2022-07-31</t>
+  </si>
+  <si>
     <t>2021-08-03</t>
   </si>
   <si>
-    <t>2022-07-31</t>
-  </si>
-  <si>
     <t>HLBY21</t>
   </si>
   <si>
@@ -1009,15 +1009,15 @@
     <t>HAFG20</t>
   </si>
   <si>
+    <t>2020-12-31</t>
+  </si>
+  <si>
     <t>2020-01-01</t>
   </si>
   <si>
     <t>2020</t>
   </si>
   <si>
-    <t>2020-12-31</t>
-  </si>
-  <si>
     <t>OBGD20</t>
   </si>
   <si>
@@ -1081,12 +1081,12 @@
     <t>FDJI1920</t>
   </si>
   <si>
+    <t>2020-03-31</t>
+  </si>
+  <si>
     <t>2019-12-17</t>
   </si>
   <si>
-    <t>2020-03-31</t>
-  </si>
-  <si>
     <t>ODJI20</t>
   </si>
   <si>
@@ -1135,24 +1135,24 @@
     <t>FLBN20</t>
   </si>
   <si>
+    <t>2020-11-13</t>
+  </si>
+  <si>
     <t>2020-08-05</t>
   </si>
   <si>
-    <t>2020-11-13</t>
-  </si>
-  <si>
     <t>OLBN20</t>
   </si>
   <si>
     <t>FLSO1920</t>
   </si>
   <si>
+    <t>2020-04-30</t>
+  </si>
+  <si>
     <t>2019-11-01</t>
   </si>
   <si>
-    <t>2020-04-30</t>
-  </si>
-  <si>
     <t>OLBR20</t>
   </si>
   <si>
@@ -1249,15 +1249,15 @@
     <t>HAFG19</t>
   </si>
   <si>
+    <t>2019-12-31</t>
+  </si>
+  <si>
     <t>2019-01-01</t>
   </si>
   <si>
     <t>2019</t>
   </si>
   <si>
-    <t>2019-12-31</t>
-  </si>
-  <si>
     <t>RBGD19</t>
   </si>
   <si>
@@ -1366,12 +1366,12 @@
     <t>FZWE1920</t>
   </si>
   <si>
+    <t>2020-04-29</t>
+  </si>
+  <si>
     <t>2019-02-01</t>
   </si>
   <si>
-    <t>2020-04-29</t>
-  </si>
-  <si>
     <t>FZWE1820</t>
   </si>
   <si>
@@ -1381,15 +1381,15 @@
     <t>HAFG18</t>
   </si>
   <si>
+    <t>2018-12-31</t>
+  </si>
+  <si>
     <t>2018-01-01</t>
   </si>
   <si>
     <t>2018</t>
   </si>
   <si>
-    <t>2018-12-31</t>
-  </si>
-  <si>
     <t>OBGD18</t>
   </si>
   <si>
@@ -1483,12 +1483,12 @@
     <t>HSYR18</t>
   </si>
   <si>
+    <t>2018-12-30</t>
+  </si>
+  <si>
     <t>2018-11-30</t>
   </si>
   <si>
-    <t>2018-12-30</t>
-  </si>
-  <si>
     <t>RSYR18</t>
   </si>
   <si>
@@ -1507,15 +1507,15 @@
     <t>OEUR17</t>
   </si>
   <si>
+    <t>2017-12-31</t>
+  </si>
+  <si>
     <t>2017-01-01</t>
   </si>
   <si>
     <t>2017</t>
   </si>
   <si>
-    <t>2017-12-31</t>
-  </si>
-  <si>
     <t>HAFG17</t>
   </si>
   <si>
@@ -1558,12 +1558,12 @@
     <t>FDMA17</t>
   </si>
   <si>
+    <t>2017-12-29</t>
+  </si>
+  <si>
     <t>2017-09-28</t>
   </si>
   <si>
-    <t>2017-12-29</t>
-  </si>
-  <si>
     <t>OPRK17</t>
   </si>
   <si>
@@ -1585,24 +1585,24 @@
     <t>FKEN17</t>
   </si>
   <si>
+    <t>2017-11-30</t>
+  </si>
+  <si>
     <t>2017-02-10</t>
   </si>
   <si>
-    <t>2017-11-30</t>
-  </si>
-  <si>
     <t>HLBY17</t>
   </si>
   <si>
     <t>FMDG17</t>
   </si>
   <si>
+    <t>2017-06-20</t>
+  </si>
+  <si>
     <t>2017-03-20</t>
   </si>
   <si>
-    <t>2017-06-20</t>
-  </si>
-  <si>
     <t>HMLI17</t>
   </si>
   <si>
@@ -1612,12 +1612,12 @@
     <t>FMOZ17</t>
   </si>
   <si>
+    <t>2017-05-31</t>
+  </si>
+  <si>
     <t>2017-02-28</t>
   </si>
   <si>
-    <t>2017-05-31</t>
-  </si>
-  <si>
     <t>HMMR17</t>
   </si>
   <si>
@@ -1636,12 +1636,12 @@
     <t>FPER17</t>
   </si>
   <si>
+    <t>2017-10-31</t>
+  </si>
+  <si>
     <t>2017-04-01</t>
   </si>
   <si>
-    <t>2017-10-31</t>
-  </si>
-  <si>
     <t>HCOG17</t>
   </si>
   <si>
@@ -1678,15 +1678,15 @@
     <t>OEUR16</t>
   </si>
   <si>
+    <t>2016-12-31</t>
+  </si>
+  <si>
     <t>2016-01-01</t>
   </si>
   <si>
     <t>2016</t>
   </si>
   <si>
-    <t>2016-12-31</t>
-  </si>
-  <si>
     <t>HAFG16</t>
   </si>
   <si>
@@ -1726,21 +1726,21 @@
     <t>FECU16</t>
   </si>
   <si>
+    <t>2016-10-31</t>
+  </si>
+  <si>
     <t>2016-04-16</t>
   </si>
   <si>
-    <t>2016-10-31</t>
-  </si>
-  <si>
     <t>FFJI16</t>
   </si>
   <si>
+    <t>2016-05-30</t>
+  </si>
+  <si>
     <t>2016-02-20</t>
   </si>
   <si>
-    <t>2016-05-30</t>
-  </si>
-  <si>
     <t>HGMB16</t>
   </si>
   <si>
@@ -1783,12 +1783,12 @@
     <t>FIRQ16</t>
   </si>
   <si>
+    <t>2016-10-01</t>
+  </si>
+  <si>
     <t>2016-07-20</t>
   </si>
   <si>
-    <t>2016-10-01</t>
-  </si>
-  <si>
     <t>HMMR16</t>
   </si>
   <si>
@@ -1831,27 +1831,27 @@
     <t>HZWE1617</t>
   </si>
   <si>
+    <t>2017-03-31</t>
+  </si>
+  <si>
     <t>2016-04-01</t>
   </si>
   <si>
-    <t>2017-03-31</t>
-  </si>
-  <si>
     <t>HAFG15</t>
   </si>
   <si>
     <t>Strategic response plan</t>
   </si>
   <si>
+    <t>2015-12-31</t>
+  </si>
+  <si>
     <t>2015-01-01</t>
   </si>
   <si>
     <t>2015</t>
   </si>
   <si>
-    <t>2015-12-31</t>
-  </si>
-  <si>
     <t>HBFA15</t>
   </si>
   <si>
@@ -1879,12 +1879,12 @@
     <t>FGTM1415</t>
   </si>
   <si>
+    <t>2015-09-30</t>
+  </si>
+  <si>
     <t>2014-11-03</t>
   </si>
   <si>
-    <t>2015-09-30</t>
-  </si>
-  <si>
     <t>FHTI15</t>
   </si>
   <si>
@@ -1900,24 +1900,24 @@
     <t>FVUT15</t>
   </si>
   <si>
+    <t>2015-10-31</t>
+  </si>
+  <si>
     <t>2015-03-24</t>
   </si>
   <si>
-    <t>2015-10-31</t>
-  </si>
-  <si>
     <t>HIRQ15</t>
   </si>
   <si>
     <t>HLBY1415</t>
   </si>
   <si>
+    <t>2015-05-31</t>
+  </si>
+  <si>
     <t>2014-10-01</t>
   </si>
   <si>
-    <t>2015-05-31</t>
-  </si>
-  <si>
     <t>HMLI15</t>
   </si>
   <si>
@@ -1975,15 +1975,15 @@
     <t>HAFG14</t>
   </si>
   <si>
+    <t>2014-12-31</t>
+  </si>
+  <si>
     <t>2014-01-01</t>
   </si>
   <si>
     <t>2014</t>
   </si>
   <si>
-    <t>2014-12-31</t>
-  </si>
-  <si>
     <t>HBFA1314</t>
   </si>
   <si>
@@ -2059,21 +2059,21 @@
     <t>FPHL1314</t>
   </si>
   <si>
+    <t>2014-04-22</t>
+  </si>
+  <si>
     <t>2013-10-22</t>
   </si>
   <si>
-    <t>2014-04-22</t>
-  </si>
-  <si>
     <t>SPHL1314</t>
   </si>
   <si>
+    <t>2014-11-07</t>
+  </si>
+  <si>
     <t>2013-11-08</t>
   </si>
   <si>
-    <t>2014-11-07</t>
-  </si>
-  <si>
     <t>HPHL1314</t>
   </si>
   <si>
@@ -2083,12 +2083,12 @@
     <t>HPHL1314a</t>
   </si>
   <si>
+    <t>2014-08-31</t>
+  </si>
+  <si>
     <t>2013-10-01</t>
   </si>
   <si>
-    <t>2014-08-31</t>
-  </si>
-  <si>
     <t>SCOD14</t>
   </si>
   <si>
@@ -2152,12 +2152,12 @@
     <t>Consolidated appeals process</t>
   </si>
   <si>
+    <t>2013-12-31</t>
+  </si>
+  <si>
     <t>2013</t>
   </si>
   <si>
-    <t>2013-12-31</t>
-  </si>
-  <si>
     <t>CBFA13</t>
   </si>
   <si>
@@ -2242,15 +2242,15 @@
     <t>CKEN12</t>
   </si>
   <si>
+    <t>2012-12-31</t>
+  </si>
+  <si>
     <t>2012-01-01</t>
   </si>
   <si>
     <t>2012</t>
   </si>
   <si>
-    <t>2012-12-31</t>
-  </si>
-  <si>
     <t>CAFG1112</t>
   </si>
   <si>
@@ -2290,12 +2290,12 @@
     <t>FLSO1213</t>
   </si>
   <si>
+    <t>2013-03-25</t>
+  </si>
+  <si>
     <t>2012-09-18</t>
   </si>
   <si>
-    <t>2013-03-25</t>
-  </si>
-  <si>
     <t>CLBR12</t>
   </si>
   <si>
@@ -2335,12 +2335,12 @@
     <t>CSYR12</t>
   </si>
   <si>
+    <t>2012-12-05</t>
+  </si>
+  <si>
     <t>2012-06-05</t>
   </si>
   <si>
-    <t>2012-12-05</t>
-  </si>
-  <si>
     <t>CYEM12</t>
   </si>
   <si>
@@ -2383,12 +2383,12 @@
     <t>FSLV1112</t>
   </si>
   <si>
+    <t>2012-04-25</t>
+  </si>
+  <si>
     <t>2011-10-25</t>
   </si>
   <si>
-    <t>2012-04-25</t>
-  </si>
-  <si>
     <t>CHTI1011</t>
   </si>
   <si>
@@ -2407,33 +2407,33 @@
     <t>FNAM11</t>
   </si>
   <si>
+    <t>2011-10-11</t>
+  </si>
+  <si>
     <t>2011-04-11</t>
   </si>
   <si>
-    <t>2011-10-11</t>
-  </si>
-  <si>
     <t>FNIC1112</t>
   </si>
   <si>
+    <t>2012-04-26</t>
+  </si>
+  <si>
     <t>2011-10-27</t>
   </si>
   <si>
-    <t>2012-04-26</t>
-  </si>
-  <si>
     <t>CNER11</t>
   </si>
   <si>
     <t>FPAK1112</t>
   </si>
   <si>
+    <t>2012-06-30</t>
+  </si>
+  <si>
     <t>2011-09-15</t>
   </si>
   <si>
-    <t>2012-06-30</t>
-  </si>
-  <si>
     <t>FXLBYREG11</t>
   </si>
   <si>
@@ -2476,24 +2476,24 @@
     <t>CAFG10</t>
   </si>
   <si>
+    <t>2010-12-31</t>
+  </si>
+  <si>
     <t>2010-01-01</t>
   </si>
   <si>
     <t>2010</t>
   </si>
   <si>
-    <t>2010-12-31</t>
-  </si>
-  <si>
     <t>OBFA1011</t>
   </si>
   <si>
+    <t>2011-01-31</t>
+  </si>
+  <si>
     <t>2010-08-01</t>
   </si>
   <si>
-    <t>2011-01-31</t>
-  </si>
-  <si>
     <t>CCAF10</t>
   </si>
   <si>
@@ -2506,30 +2506,30 @@
     <t>FSLV0910</t>
   </si>
   <si>
+    <t>2010-05-31</t>
+  </si>
+  <si>
     <t>2009-11-01</t>
   </si>
   <si>
-    <t>2010-05-31</t>
-  </si>
-  <si>
     <t>FGTM10</t>
   </si>
   <si>
+    <t>2010-12-09</t>
+  </si>
+  <si>
     <t>2010-06-10</t>
   </si>
   <si>
-    <t>2010-12-09</t>
-  </si>
-  <si>
     <t>CGTM10</t>
   </si>
   <si>
+    <t>2010-08-11</t>
+  </si>
+  <si>
     <t>2010-02-12</t>
   </si>
   <si>
-    <t>2010-08-11</t>
-  </si>
-  <si>
     <t>FHTI10</t>
   </si>
   <si>
@@ -2545,12 +2545,12 @@
     <t>FKGZ1011</t>
   </si>
   <si>
+    <t>2011-06-30</t>
+  </si>
+  <si>
     <t>2010-06-01</t>
   </si>
   <si>
-    <t>2011-06-30</t>
-  </si>
-  <si>
     <t>CMNG1011</t>
   </si>
   <si>
@@ -2608,24 +2608,24 @@
     <t>CAFG09</t>
   </si>
   <si>
+    <t>2009-12-31</t>
+  </si>
+  <si>
     <t>2009-01-01</t>
   </si>
   <si>
     <t>2009</t>
   </si>
   <si>
-    <t>2009-12-31</t>
-  </si>
-  <si>
     <t>FBFA0910</t>
   </si>
   <si>
+    <t>2010-03-09</t>
+  </si>
+  <si>
     <t>2009-09-10</t>
   </si>
   <si>
-    <t>2010-03-09</t>
-  </si>
-  <si>
     <t>CCAF09</t>
   </si>
   <si>
@@ -2662,21 +2662,21 @@
     <t>FMDG09</t>
   </si>
   <si>
+    <t>2009-10-31</t>
+  </si>
+  <si>
     <t>2009-04-01</t>
   </si>
   <si>
-    <t>2009-10-31</t>
-  </si>
-  <si>
     <t>FNAM09</t>
   </si>
   <si>
+    <t>2009-09-30</t>
+  </si>
+  <si>
     <t>2009-03-20</t>
   </si>
   <si>
-    <t>2009-09-30</t>
-  </si>
-  <si>
     <t>ONPL09</t>
   </si>
   <si>
@@ -2689,12 +2689,12 @@
     <t>FPHL0910</t>
   </si>
   <si>
+    <t>2010-03-31</t>
+  </si>
+  <si>
     <t>2009-10-03</t>
   </si>
   <si>
-    <t>2010-03-31</t>
-  </si>
-  <si>
     <t>CSOM09</t>
   </si>
   <si>
@@ -2707,12 +2707,12 @@
     <t>OSYR0910</t>
   </si>
   <si>
+    <t>2010-06-14</t>
+  </si>
+  <si>
     <t>2009-07-15</t>
   </si>
   <si>
-    <t>2010-06-14</t>
-  </si>
-  <si>
     <t>OTJK09</t>
   </si>
   <si>
@@ -2746,24 +2746,24 @@
     <t>OAFG08</t>
   </si>
   <si>
+    <t>2008-06-30</t>
+  </si>
+  <si>
     <t>2008-02-01</t>
   </si>
   <si>
     <t>2008</t>
   </si>
   <si>
-    <t>2008-06-30</t>
-  </si>
-  <si>
     <t>OAFG0809</t>
   </si>
   <si>
+    <t>2009-06-30</t>
+  </si>
+  <si>
     <t>2008-07-01</t>
   </si>
   <si>
-    <t>2009-06-30</t>
-  </si>
-  <si>
     <t>FBOL08</t>
   </si>
   <si>
@@ -2773,12 +2773,12 @@
     <t>CCAF08</t>
   </si>
   <si>
+    <t>2008-12-31</t>
+  </si>
+  <si>
     <t>2008-01-01</t>
   </si>
   <si>
-    <t>2008-12-31</t>
-  </si>
-  <si>
     <t>CTCD08</t>
   </si>
   <si>
@@ -2794,21 +2794,21 @@
     <t>ODJI0809</t>
   </si>
   <si>
+    <t>2009-02-28</t>
+  </si>
+  <si>
     <t>2008-08-01</t>
   </si>
   <si>
-    <t>2009-02-28</t>
-  </si>
-  <si>
     <t>FGEO0809</t>
   </si>
   <si>
+    <t>2009-02-09</t>
+  </si>
+  <si>
     <t>2008-08-09</t>
   </si>
   <si>
-    <t>2009-02-09</t>
-  </si>
-  <si>
     <t>FHTI0809</t>
   </si>
   <si>
@@ -2818,12 +2818,12 @@
     <t>FHND0809</t>
   </si>
   <si>
+    <t>2009-04-30</t>
+  </si>
+  <si>
     <t>2008-11-01</t>
   </si>
   <si>
-    <t>2009-04-30</t>
-  </si>
-  <si>
     <t>CIRQ08</t>
   </si>
   <si>
@@ -2833,12 +2833,12 @@
     <t>FKGZ0809</t>
   </si>
   <si>
+    <t>2009-05-31</t>
+  </si>
+  <si>
     <t>2008-12-01</t>
   </si>
   <si>
-    <t>2009-05-31</t>
-  </si>
-  <si>
     <t>OLAO0809</t>
   </si>
   <si>
@@ -2857,12 +2857,12 @@
     <t>FMMR08</t>
   </si>
   <si>
+    <t>2008-11-30</t>
+  </si>
+  <si>
     <t>2008-05-01</t>
   </si>
   <si>
-    <t>2008-11-30</t>
-  </si>
-  <si>
     <t>ONPL08</t>
   </si>
   <si>
@@ -2914,33 +2914,33 @@
     <t>FBOL07</t>
   </si>
   <si>
+    <t>2007-08-21</t>
+  </si>
+  <si>
     <t>2007-02-22</t>
   </si>
   <si>
     <t>2007</t>
   </si>
   <si>
-    <t>2007-08-21</t>
-  </si>
-  <si>
     <t>FBFA0708</t>
   </si>
   <si>
+    <t>2008-01-31</t>
+  </si>
+  <si>
     <t>2007-11-01</t>
   </si>
   <si>
-    <t>2008-01-31</t>
-  </si>
-  <si>
     <t>CBDI07</t>
   </si>
   <si>
+    <t>2007-12-31</t>
+  </si>
+  <si>
     <t>2007-01-01</t>
   </si>
   <si>
-    <t>2007-12-31</t>
-  </si>
-  <si>
     <t>CCAF07</t>
   </si>
   <si>
@@ -2962,12 +2962,12 @@
     <t>FGHA0708</t>
   </si>
   <si>
+    <t>2008-03-31</t>
+  </si>
+  <si>
     <t>2007-09-01</t>
   </si>
   <si>
-    <t>2008-03-31</t>
-  </si>
-  <si>
     <t>CXGLR07</t>
   </si>
   <si>
@@ -2980,75 +2980,75 @@
     <t>FPRK07</t>
   </si>
   <si>
+    <t>2007-11-30</t>
+  </si>
+  <si>
     <t>2007-08-28</t>
   </si>
   <si>
-    <t>2007-11-30</t>
-  </si>
-  <si>
     <t>OLBN07</t>
   </si>
   <si>
+    <t>2007-09-03</t>
+  </si>
+  <si>
     <t>2007-06-04</t>
   </si>
   <si>
-    <t>2007-09-03</t>
-  </si>
-  <si>
     <t>FLSO0708</t>
   </si>
   <si>
+    <t>2008-01-28</t>
+  </si>
+  <si>
     <t>2007-07-28</t>
   </si>
   <si>
-    <t>2008-01-28</t>
-  </si>
-  <si>
     <t>CLBR07</t>
   </si>
   <si>
     <t>FMDG07</t>
   </si>
   <si>
+    <t>2007-09-15</t>
+  </si>
+  <si>
     <t>2007-03-15</t>
   </si>
   <si>
-    <t>2007-09-15</t>
-  </si>
-  <si>
     <t>FMOZ07</t>
   </si>
   <si>
+    <t>2007-06-30</t>
+  </si>
+  <si>
     <t>2007-03-01</t>
   </si>
   <si>
-    <t>2007-06-30</t>
-  </si>
-  <si>
     <t>ONPL07</t>
   </si>
   <si>
     <t>FNIC0708</t>
   </si>
   <si>
+    <t>2008-02-28</t>
+  </si>
+  <si>
     <t>2007-09-07</t>
   </si>
   <si>
-    <t>2008-02-28</t>
-  </si>
-  <si>
     <t>ORUS07</t>
   </si>
   <si>
     <t>FPAK07</t>
   </si>
   <si>
+    <t>2007-10-31</t>
+  </si>
+  <si>
     <t>2007-07-15</t>
   </si>
   <si>
-    <t>2007-10-31</t>
-  </si>
-  <si>
     <t>FPER0708</t>
   </si>
   <si>
@@ -3082,12 +3082,12 @@
     <t>FSWZ0708</t>
   </si>
   <si>
+    <t>2008-01-20</t>
+  </si>
+  <si>
     <t>2007-07-20</t>
   </si>
   <si>
-    <t>2008-01-20</t>
-  </si>
-  <si>
     <t>CTLS07</t>
   </si>
   <si>
@@ -3112,15 +3112,15 @@
     <t>OAFG06</t>
   </si>
   <si>
+    <t>2006-12-31</t>
+  </si>
+  <si>
     <t>2006-07-01</t>
   </si>
   <si>
     <t>2006</t>
   </si>
   <si>
-    <t>2006-12-31</t>
-  </si>
-  <si>
     <t>CBDI06</t>
   </si>
   <si>
@@ -3145,21 +3145,21 @@
     <t>OETH06a</t>
   </si>
   <si>
+    <t>2006-11-25</t>
+  </si>
+  <si>
     <t>2006-08-25</t>
   </si>
   <si>
-    <t>2006-11-25</t>
-  </si>
-  <si>
     <t>OETH0607</t>
   </si>
   <si>
+    <t>2007-01-22</t>
+  </si>
+  <si>
     <t>2006-11-23</t>
   </si>
   <si>
-    <t>2007-01-22</t>
-  </si>
-  <si>
     <t>CXGLR06</t>
   </si>
   <si>
@@ -3169,12 +3169,12 @@
     <t>FGNB06</t>
   </si>
   <si>
+    <t>2006-11-30</t>
+  </si>
+  <si>
     <t>2006-05-01</t>
   </si>
   <si>
-    <t>2006-11-30</t>
-  </si>
-  <si>
     <t>CXHAF06</t>
   </si>
   <si>
@@ -3184,12 +3184,12 @@
     <t>FKEN0607</t>
   </si>
   <si>
+    <t>2007-04-15</t>
+  </si>
+  <si>
     <t>2006-10-16</t>
   </si>
   <si>
-    <t>2007-04-15</t>
-  </si>
-  <si>
     <t>FKEN06</t>
   </si>
   <si>
@@ -3199,12 +3199,12 @@
     <t>FLBN06</t>
   </si>
   <si>
+    <t>2006-10-23</t>
+  </si>
+  <si>
     <t>2006-07-24</t>
   </si>
   <si>
-    <t>2006-10-23</t>
-  </si>
-  <si>
     <t>CLBR06</t>
   </si>
   <si>
@@ -3232,12 +3232,12 @@
     <t>FSOM0607</t>
   </si>
   <si>
+    <t>2007-03-05</t>
+  </si>
+  <si>
     <t>2006-12-05</t>
   </si>
   <si>
-    <t>2007-03-05</t>
-  </si>
-  <si>
     <t>OLKA06</t>
   </si>
   <si>
@@ -3271,33 +3271,33 @@
     <t>FAGO05</t>
   </si>
   <si>
+    <t>2005-06-30</t>
+  </si>
+  <si>
     <t>2005-04-01</t>
   </si>
   <si>
     <t>2005</t>
   </si>
   <si>
-    <t>2005-06-30</t>
-  </si>
-  <si>
     <t>FBEN05</t>
   </si>
   <si>
+    <t>2005-10-31</t>
+  </si>
+  <si>
     <t>2005-05-01</t>
   </si>
   <si>
-    <t>2005-10-31</t>
-  </si>
-  <si>
     <t>CBDI05</t>
   </si>
   <si>
+    <t>2005-12-31</t>
+  </si>
+  <si>
     <t>2005-01-01</t>
   </si>
   <si>
-    <t>2005-12-31</t>
-  </si>
-  <si>
     <t>CCAF05</t>
   </si>
   <si>
@@ -3337,12 +3337,12 @@
     <t>FGUY05</t>
   </si>
   <si>
+    <t>2005-08-01</t>
+  </si>
+  <si>
     <t>2005-02-01</t>
   </si>
   <si>
-    <t>2005-08-01</t>
-  </si>
-  <si>
     <t>FXINDTSU05</t>
   </si>
   <si>
@@ -3355,12 +3355,12 @@
     <t>FNER05</t>
   </si>
   <si>
+    <t>2005-09-30</t>
+  </si>
+  <si>
     <t>2005-06-01</t>
   </si>
   <si>
-    <t>2005-09-30</t>
-  </si>
-  <si>
     <t>CCOG05</t>
   </si>
   <si>
@@ -3370,12 +3370,12 @@
     <t>FXSASIA0506</t>
   </si>
   <si>
+    <t>2006-04-10</t>
+  </si>
+  <si>
     <t>2005-10-11</t>
   </si>
   <si>
-    <t>2006-04-10</t>
-  </si>
-  <si>
     <t>CSDN05</t>
   </si>
   <si>
@@ -3388,27 +3388,27 @@
     <t>FXWAF0506</t>
   </si>
   <si>
+    <t>2006-05-31</t>
+  </si>
+  <si>
     <t>2005-11-01</t>
   </si>
   <si>
-    <t>2006-05-31</t>
-  </si>
-  <si>
     <t>CPSE05</t>
   </si>
   <si>
     <t>OAFG04</t>
   </si>
   <si>
+    <t>2004-12-31</t>
+  </si>
+  <si>
     <t>2004-09-01</t>
   </si>
   <si>
     <t>2004</t>
   </si>
   <si>
-    <t>2004-12-31</t>
-  </si>
-  <si>
     <t>CAGO04</t>
   </si>
   <si>
@@ -3418,21 +3418,21 @@
     <t>FBGD0405</t>
   </si>
   <si>
+    <t>2005-01-31</t>
+  </si>
+  <si>
     <t>2004-08-01</t>
   </si>
   <si>
-    <t>2005-01-31</t>
-  </si>
-  <si>
     <t>FBOL0405</t>
   </si>
   <si>
+    <t>2005-05-31</t>
+  </si>
+  <si>
     <t>2004-11-01</t>
   </si>
   <si>
-    <t>2005-05-31</t>
-  </si>
-  <si>
     <t>CBDI04</t>
   </si>
   <si>
@@ -3505,21 +3505,21 @@
     <t>FMDG04</t>
   </si>
   <si>
+    <t>2004-06-19</t>
+  </si>
+  <si>
     <t>2004-03-19</t>
   </si>
   <si>
-    <t>2004-06-19</t>
-  </si>
-  <si>
     <t>FPHL0405</t>
   </si>
   <si>
+    <t>2005-03-15</t>
+  </si>
+  <si>
     <t>2004-12-15</t>
   </si>
   <si>
-    <t>2005-03-15</t>
-  </si>
-  <si>
     <t>CSLE04</t>
   </si>
   <si>
@@ -3550,15 +3550,15 @@
     <t>OAFG03</t>
   </si>
   <si>
+    <t>2003-12-31</t>
+  </si>
+  <si>
     <t>2003-01-01</t>
   </si>
   <si>
     <t>2003</t>
   </si>
   <si>
-    <t>2003-12-31</t>
-  </si>
-  <si>
     <t>CAGO03</t>
   </si>
   <si>
@@ -3571,12 +3571,12 @@
     <t>FCAF03</t>
   </si>
   <si>
+    <t>2003-06-30</t>
+  </si>
+  <si>
     <t>2003-04-01</t>
   </si>
   <si>
-    <t>2003-06-30</t>
-  </si>
-  <si>
     <t>CRUS03</t>
   </si>
   <si>
@@ -3589,12 +3589,12 @@
     <t>FCIV0203</t>
   </si>
   <si>
+    <t>2003-01-31</t>
+  </si>
+  <si>
     <t>2002-11-01</t>
   </si>
   <si>
-    <t>2003-01-31</t>
-  </si>
-  <si>
     <t>CPRK03</t>
   </si>
   <si>
@@ -3613,21 +3613,21 @@
     <t>OHTI03</t>
   </si>
   <si>
+    <t>2003-08-31</t>
+  </si>
+  <si>
     <t>2003-03-01</t>
   </si>
   <si>
-    <t>2003-08-31</t>
-  </si>
-  <si>
     <t>CLSO0304</t>
   </si>
   <si>
+    <t>2004-06-30</t>
+  </si>
+  <si>
     <t>2003-07-01</t>
   </si>
   <si>
-    <t>2004-06-30</t>
-  </si>
-  <si>
     <t>CMWI03</t>
   </si>
   <si>
@@ -3679,15 +3679,15 @@
     <t>CAFG0102</t>
   </si>
   <si>
+    <t>2002-12-31</t>
+  </si>
+  <si>
     <t>2001-10-01</t>
   </si>
   <si>
     <t>2002</t>
   </si>
   <si>
-    <t>2002-12-31</t>
-  </si>
-  <si>
     <t>CAGO02</t>
   </si>
   <si>
@@ -3781,15 +3781,15 @@
     <t>CAFG01</t>
   </si>
   <si>
+    <t>2001-09-30</t>
+  </si>
+  <si>
     <t>2001-01-01</t>
   </si>
   <si>
     <t>2001</t>
   </si>
   <si>
-    <t>2001-09-30</t>
-  </si>
-  <si>
     <t>CAGO01</t>
   </si>
   <si>
@@ -3862,13 +3862,13 @@
     <t>CAGO00</t>
   </si>
   <si>
+    <t>2000-12-31</t>
+  </si>
+  <si>
     <t>2000-01-01</t>
   </si>
   <si>
     <t>2000</t>
-  </si>
-  <si>
-    <t>2000-12-31</t>
   </si>
   <si>
     <t>CBDI00</t>
@@ -4337,13 +4337,13 @@
         <v>15</v>
       </c>
       <c r="D4" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E4" t="s">
         <v>10</v>
       </c>
       <c r="F4" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -4537,13 +4537,13 @@
         <v>24</v>
       </c>
       <c r="D14" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E14" t="s">
         <v>10</v>
       </c>
       <c r="F14" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -4557,13 +4557,13 @@
         <v>24</v>
       </c>
       <c r="D15" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="E15" t="s">
         <v>10</v>
       </c>
       <c r="F15" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -4597,13 +4597,13 @@
         <v>24</v>
       </c>
       <c r="D17" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="E17" t="s">
         <v>10</v>
       </c>
       <c r="F17" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -4637,13 +4637,13 @@
         <v>24</v>
       </c>
       <c r="D19" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="E19" t="s">
         <v>10</v>
       </c>
       <c r="F19" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -4657,10 +4657,10 @@
         <v>8</v>
       </c>
       <c r="D20" t="s">
+        <v>9</v>
+      </c>
+      <c r="E20" t="s">
         <v>38</v>
-      </c>
-      <c r="E20" t="s">
-        <v>10</v>
       </c>
       <c r="F20" t="s">
         <v>11</v>
@@ -4737,13 +4737,13 @@
         <v>15</v>
       </c>
       <c r="D24" t="s">
-        <v>9</v>
+        <v>43</v>
       </c>
       <c r="E24" t="s">
         <v>10</v>
       </c>
       <c r="F24" t="s">
-        <v>43</v>
+        <v>11</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -4937,10 +4937,10 @@
         <v>24</v>
       </c>
       <c r="D34" t="s">
+        <v>9</v>
+      </c>
+      <c r="E34" t="s">
         <v>54</v>
-      </c>
-      <c r="E34" t="s">
-        <v>10</v>
       </c>
       <c r="F34" t="s">
         <v>11</v>
@@ -5097,13 +5097,13 @@
         <v>15</v>
       </c>
       <c r="D42" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="E42" t="s">
         <v>10</v>
       </c>
       <c r="F42" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
     </row>
     <row r="43" spans="1:6">
@@ -5137,13 +5137,13 @@
         <v>24</v>
       </c>
       <c r="D44" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="E44" t="s">
         <v>10</v>
       </c>
       <c r="F44" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
     </row>
     <row r="45" spans="1:6">
@@ -5157,13 +5157,13 @@
         <v>24</v>
       </c>
       <c r="D45" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="E45" t="s">
         <v>10</v>
       </c>
       <c r="F45" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
     </row>
     <row r="46" spans="1:6">
@@ -5217,10 +5217,10 @@
         <v>15</v>
       </c>
       <c r="D48" t="s">
+        <v>67</v>
+      </c>
+      <c r="E48" t="s">
         <v>72</v>
-      </c>
-      <c r="E48" t="s">
-        <v>68</v>
       </c>
       <c r="F48" t="s">
         <v>69</v>
@@ -5257,10 +5257,10 @@
         <v>15</v>
       </c>
       <c r="D50" t="s">
+        <v>67</v>
+      </c>
+      <c r="E50" t="s">
         <v>75</v>
-      </c>
-      <c r="E50" t="s">
-        <v>68</v>
       </c>
       <c r="F50" t="s">
         <v>69</v>
@@ -5397,10 +5397,10 @@
         <v>24</v>
       </c>
       <c r="D57" t="s">
+        <v>67</v>
+      </c>
+      <c r="E57" t="s">
         <v>83</v>
-      </c>
-      <c r="E57" t="s">
-        <v>68</v>
       </c>
       <c r="F57" t="s">
         <v>69</v>
@@ -5477,10 +5477,10 @@
         <v>15</v>
       </c>
       <c r="D61" t="s">
+        <v>67</v>
+      </c>
+      <c r="E61" t="s">
         <v>88</v>
-      </c>
-      <c r="E61" t="s">
-        <v>68</v>
       </c>
       <c r="F61" t="s">
         <v>69</v>
@@ -5497,10 +5497,10 @@
         <v>24</v>
       </c>
       <c r="D62" t="s">
+        <v>67</v>
+      </c>
+      <c r="E62" t="s">
         <v>88</v>
-      </c>
-      <c r="E62" t="s">
-        <v>68</v>
       </c>
       <c r="F62" t="s">
         <v>69</v>
@@ -5517,13 +5517,13 @@
         <v>24</v>
       </c>
       <c r="D63" t="s">
-        <v>67</v>
+        <v>91</v>
       </c>
       <c r="E63" t="s">
         <v>68</v>
       </c>
       <c r="F63" t="s">
-        <v>91</v>
+        <v>69</v>
       </c>
     </row>
     <row r="64" spans="1:6">
@@ -5537,13 +5537,13 @@
         <v>24</v>
       </c>
       <c r="D64" t="s">
-        <v>67</v>
+        <v>93</v>
       </c>
       <c r="E64" t="s">
         <v>68</v>
       </c>
       <c r="F64" t="s">
-        <v>93</v>
+        <v>69</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -5557,10 +5557,10 @@
         <v>24</v>
       </c>
       <c r="D65" t="s">
+        <v>67</v>
+      </c>
+      <c r="E65" t="s">
         <v>95</v>
-      </c>
-      <c r="E65" t="s">
-        <v>68</v>
       </c>
       <c r="F65" t="s">
         <v>69</v>
@@ -5597,13 +5597,13 @@
         <v>15</v>
       </c>
       <c r="D67" t="s">
+        <v>93</v>
+      </c>
+      <c r="E67" t="s">
         <v>98</v>
       </c>
-      <c r="E67" t="s">
-        <v>68</v>
-      </c>
       <c r="F67" t="s">
-        <v>93</v>
+        <v>69</v>
       </c>
     </row>
     <row r="68" spans="1:6">
@@ -5617,10 +5617,10 @@
         <v>24</v>
       </c>
       <c r="D68" t="s">
+        <v>67</v>
+      </c>
+      <c r="E68" t="s">
         <v>100</v>
-      </c>
-      <c r="E68" t="s">
-        <v>68</v>
       </c>
       <c r="F68" t="s">
         <v>69</v>
@@ -5677,10 +5677,10 @@
         <v>15</v>
       </c>
       <c r="D71" t="s">
+        <v>67</v>
+      </c>
+      <c r="E71" t="s">
         <v>104</v>
-      </c>
-      <c r="E71" t="s">
-        <v>68</v>
       </c>
       <c r="F71" t="s">
         <v>69</v>
@@ -5737,10 +5737,10 @@
         <v>15</v>
       </c>
       <c r="D74" t="s">
+        <v>67</v>
+      </c>
+      <c r="E74" t="s">
         <v>108</v>
-      </c>
-      <c r="E74" t="s">
-        <v>68</v>
       </c>
       <c r="F74" t="s">
         <v>69</v>
@@ -5857,10 +5857,10 @@
         <v>24</v>
       </c>
       <c r="D80" t="s">
+        <v>67</v>
+      </c>
+      <c r="E80" t="s">
         <v>83</v>
-      </c>
-      <c r="E80" t="s">
-        <v>68</v>
       </c>
       <c r="F80" t="s">
         <v>69</v>
@@ -6117,10 +6117,10 @@
         <v>15</v>
       </c>
       <c r="D93" t="s">
+        <v>67</v>
+      </c>
+      <c r="E93" t="s">
         <v>129</v>
-      </c>
-      <c r="E93" t="s">
-        <v>68</v>
       </c>
       <c r="F93" t="s">
         <v>69</v>
@@ -6157,10 +6157,10 @@
         <v>24</v>
       </c>
       <c r="D95" t="s">
+        <v>67</v>
+      </c>
+      <c r="E95" t="s">
         <v>132</v>
-      </c>
-      <c r="E95" t="s">
-        <v>68</v>
       </c>
       <c r="F95" t="s">
         <v>69</v>
@@ -6177,10 +6177,10 @@
         <v>24</v>
       </c>
       <c r="D96" t="s">
+        <v>67</v>
+      </c>
+      <c r="E96" t="s">
         <v>132</v>
-      </c>
-      <c r="E96" t="s">
-        <v>68</v>
       </c>
       <c r="F96" t="s">
         <v>69</v>
@@ -6357,10 +6357,10 @@
         <v>24</v>
       </c>
       <c r="D105" t="s">
+        <v>135</v>
+      </c>
+      <c r="E105" t="s">
         <v>146</v>
-      </c>
-      <c r="E105" t="s">
-        <v>136</v>
       </c>
       <c r="F105" t="s">
         <v>137</v>
@@ -6517,10 +6517,10 @@
         <v>24</v>
       </c>
       <c r="D113" t="s">
+        <v>135</v>
+      </c>
+      <c r="E113" t="s">
         <v>155</v>
-      </c>
-      <c r="E113" t="s">
-        <v>136</v>
       </c>
       <c r="F113" t="s">
         <v>137</v>
@@ -6580,10 +6580,10 @@
         <v>159</v>
       </c>
       <c r="E116" t="s">
-        <v>136</v>
+        <v>160</v>
       </c>
       <c r="F116" t="s">
-        <v>160</v>
+        <v>137</v>
       </c>
     </row>
     <row r="117" spans="1:6">
@@ -6600,10 +6600,10 @@
         <v>162</v>
       </c>
       <c r="E117" t="s">
-        <v>136</v>
+        <v>163</v>
       </c>
       <c r="F117" t="s">
-        <v>163</v>
+        <v>137</v>
       </c>
     </row>
     <row r="118" spans="1:6">
@@ -6697,13 +6697,13 @@
         <v>19</v>
       </c>
       <c r="D122" t="s">
-        <v>135</v>
+        <v>162</v>
       </c>
       <c r="E122" t="s">
         <v>136</v>
       </c>
       <c r="F122" t="s">
-        <v>163</v>
+        <v>137</v>
       </c>
     </row>
     <row r="123" spans="1:6">
@@ -6717,13 +6717,13 @@
         <v>15</v>
       </c>
       <c r="D123" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="E123" t="s">
         <v>136</v>
       </c>
       <c r="F123" t="s">
-        <v>160</v>
+        <v>137</v>
       </c>
     </row>
     <row r="124" spans="1:6">
@@ -6900,10 +6900,10 @@
         <v>179</v>
       </c>
       <c r="E132" t="s">
-        <v>136</v>
+        <v>180</v>
       </c>
       <c r="F132" t="s">
-        <v>180</v>
+        <v>137</v>
       </c>
     </row>
     <row r="133" spans="1:6">
@@ -6937,13 +6937,13 @@
         <v>24</v>
       </c>
       <c r="D134" t="s">
+        <v>159</v>
+      </c>
+      <c r="E134" t="s">
         <v>183</v>
       </c>
-      <c r="E134" t="s">
-        <v>136</v>
-      </c>
       <c r="F134" t="s">
-        <v>160</v>
+        <v>137</v>
       </c>
     </row>
     <row r="135" spans="1:6">
@@ -6977,13 +6977,13 @@
         <v>24</v>
       </c>
       <c r="D136" t="s">
+        <v>159</v>
+      </c>
+      <c r="E136" t="s">
         <v>186</v>
       </c>
-      <c r="E136" t="s">
-        <v>136</v>
-      </c>
       <c r="F136" t="s">
-        <v>160</v>
+        <v>137</v>
       </c>
     </row>
     <row r="137" spans="1:6">
@@ -7280,10 +7280,10 @@
         <v>205</v>
       </c>
       <c r="E151" t="s">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c r="F151" t="s">
-        <v>206</v>
+        <v>197</v>
       </c>
     </row>
     <row r="152" spans="1:6">
@@ -7380,10 +7380,10 @@
         <v>212</v>
       </c>
       <c r="E156" t="s">
-        <v>196</v>
+        <v>213</v>
       </c>
       <c r="F156" t="s">
-        <v>213</v>
+        <v>197</v>
       </c>
     </row>
     <row r="157" spans="1:6">
@@ -7397,10 +7397,10 @@
         <v>24</v>
       </c>
       <c r="D157" t="s">
-        <v>212</v>
+        <v>195</v>
       </c>
       <c r="E157" t="s">
-        <v>196</v>
+        <v>213</v>
       </c>
       <c r="F157" t="s">
         <v>197</v>
@@ -7477,13 +7477,13 @@
         <v>24</v>
       </c>
       <c r="D161" t="s">
-        <v>195</v>
+        <v>219</v>
       </c>
       <c r="E161" t="s">
         <v>196</v>
       </c>
       <c r="F161" t="s">
-        <v>219</v>
+        <v>197</v>
       </c>
     </row>
     <row r="162" spans="1:6">
@@ -7560,10 +7560,10 @@
         <v>224</v>
       </c>
       <c r="E165" t="s">
-        <v>196</v>
+        <v>225</v>
       </c>
       <c r="F165" t="s">
-        <v>225</v>
+        <v>197</v>
       </c>
     </row>
     <row r="166" spans="1:6">
@@ -7600,10 +7600,10 @@
         <v>228</v>
       </c>
       <c r="E167" t="s">
-        <v>196</v>
+        <v>229</v>
       </c>
       <c r="F167" t="s">
-        <v>229</v>
+        <v>197</v>
       </c>
     </row>
     <row r="168" spans="1:6">
@@ -7717,10 +7717,10 @@
         <v>15</v>
       </c>
       <c r="D173" t="s">
+        <v>195</v>
+      </c>
+      <c r="E173" t="s">
         <v>236</v>
-      </c>
-      <c r="E173" t="s">
-        <v>196</v>
       </c>
       <c r="F173" t="s">
         <v>197</v>
@@ -7737,13 +7737,13 @@
         <v>15</v>
       </c>
       <c r="D174" t="s">
+        <v>238</v>
+      </c>
+      <c r="E174" t="s">
         <v>236</v>
       </c>
-      <c r="E174" t="s">
-        <v>196</v>
-      </c>
       <c r="F174" t="s">
-        <v>238</v>
+        <v>197</v>
       </c>
     </row>
     <row r="175" spans="1:6">
@@ -7760,10 +7760,10 @@
         <v>240</v>
       </c>
       <c r="E175" t="s">
-        <v>196</v>
+        <v>241</v>
       </c>
       <c r="F175" t="s">
-        <v>241</v>
+        <v>197</v>
       </c>
     </row>
     <row r="176" spans="1:6">
@@ -7917,10 +7917,10 @@
         <v>15</v>
       </c>
       <c r="D183" t="s">
+        <v>195</v>
+      </c>
+      <c r="E183" t="s">
         <v>250</v>
-      </c>
-      <c r="E183" t="s">
-        <v>196</v>
       </c>
       <c r="F183" t="s">
         <v>197</v>
@@ -8017,10 +8017,10 @@
         <v>24</v>
       </c>
       <c r="D188" t="s">
+        <v>195</v>
+      </c>
+      <c r="E188" t="s">
         <v>256</v>
-      </c>
-      <c r="E188" t="s">
-        <v>196</v>
       </c>
       <c r="F188" t="s">
         <v>197</v>
@@ -8057,13 +8057,13 @@
         <v>13</v>
       </c>
       <c r="D190" t="s">
+        <v>259</v>
+      </c>
+      <c r="E190" t="s">
         <v>256</v>
       </c>
-      <c r="E190" t="s">
-        <v>196</v>
-      </c>
       <c r="F190" t="s">
-        <v>259</v>
+        <v>197</v>
       </c>
     </row>
     <row r="191" spans="1:6">
@@ -8137,10 +8137,10 @@
         <v>19</v>
       </c>
       <c r="D194" t="s">
+        <v>263</v>
+      </c>
+      <c r="E194" t="s">
         <v>267</v>
-      </c>
-      <c r="E194" t="s">
-        <v>264</v>
       </c>
       <c r="F194" t="s">
         <v>265</v>
@@ -8157,10 +8157,10 @@
         <v>13</v>
       </c>
       <c r="D195" t="s">
+        <v>263</v>
+      </c>
+      <c r="E195" t="s">
         <v>267</v>
-      </c>
-      <c r="E195" t="s">
-        <v>264</v>
       </c>
       <c r="F195" t="s">
         <v>265</v>
@@ -8177,10 +8177,10 @@
         <v>19</v>
       </c>
       <c r="D196" t="s">
+        <v>263</v>
+      </c>
+      <c r="E196" t="s">
         <v>267</v>
-      </c>
-      <c r="E196" t="s">
-        <v>264</v>
       </c>
       <c r="F196" t="s">
         <v>265</v>
@@ -8197,10 +8197,10 @@
         <v>19</v>
       </c>
       <c r="D197" t="s">
+        <v>263</v>
+      </c>
+      <c r="E197" t="s">
         <v>267</v>
-      </c>
-      <c r="E197" t="s">
-        <v>264</v>
       </c>
       <c r="F197" t="s">
         <v>265</v>
@@ -8217,10 +8217,10 @@
         <v>13</v>
       </c>
       <c r="D198" t="s">
+        <v>263</v>
+      </c>
+      <c r="E198" t="s">
         <v>267</v>
-      </c>
-      <c r="E198" t="s">
-        <v>264</v>
       </c>
       <c r="F198" t="s">
         <v>265</v>
@@ -8237,10 +8237,10 @@
         <v>19</v>
       </c>
       <c r="D199" t="s">
+        <v>263</v>
+      </c>
+      <c r="E199" t="s">
         <v>267</v>
-      </c>
-      <c r="E199" t="s">
-        <v>264</v>
       </c>
       <c r="F199" t="s">
         <v>265</v>
@@ -8257,10 +8257,10 @@
         <v>19</v>
       </c>
       <c r="D200" t="s">
+        <v>263</v>
+      </c>
+      <c r="E200" t="s">
         <v>267</v>
-      </c>
-      <c r="E200" t="s">
-        <v>264</v>
       </c>
       <c r="F200" t="s">
         <v>265</v>
@@ -8277,10 +8277,10 @@
         <v>19</v>
       </c>
       <c r="D201" t="s">
+        <v>263</v>
+      </c>
+      <c r="E201" t="s">
         <v>267</v>
-      </c>
-      <c r="E201" t="s">
-        <v>264</v>
       </c>
       <c r="F201" t="s">
         <v>265</v>
@@ -8297,10 +8297,10 @@
         <v>19</v>
       </c>
       <c r="D202" t="s">
+        <v>263</v>
+      </c>
+      <c r="E202" t="s">
         <v>267</v>
-      </c>
-      <c r="E202" t="s">
-        <v>264</v>
       </c>
       <c r="F202" t="s">
         <v>265</v>
@@ -8317,10 +8317,10 @@
         <v>19</v>
       </c>
       <c r="D203" t="s">
+        <v>263</v>
+      </c>
+      <c r="E203" t="s">
         <v>267</v>
-      </c>
-      <c r="E203" t="s">
-        <v>264</v>
       </c>
       <c r="F203" t="s">
         <v>265</v>
@@ -8337,10 +8337,10 @@
         <v>13</v>
       </c>
       <c r="D204" t="s">
+        <v>263</v>
+      </c>
+      <c r="E204" t="s">
         <v>267</v>
-      </c>
-      <c r="E204" t="s">
-        <v>264</v>
       </c>
       <c r="F204" t="s">
         <v>265</v>
@@ -8357,10 +8357,10 @@
         <v>19</v>
       </c>
       <c r="D205" t="s">
+        <v>263</v>
+      </c>
+      <c r="E205" t="s">
         <v>279</v>
-      </c>
-      <c r="E205" t="s">
-        <v>264</v>
       </c>
       <c r="F205" t="s">
         <v>265</v>
@@ -8377,13 +8377,13 @@
         <v>19</v>
       </c>
       <c r="D206" t="s">
+        <v>195</v>
+      </c>
+      <c r="E206" t="s">
         <v>279</v>
       </c>
-      <c r="E206" t="s">
-        <v>264</v>
-      </c>
       <c r="F206" t="s">
-        <v>197</v>
+        <v>265</v>
       </c>
     </row>
     <row r="207" spans="1:6">
@@ -8400,10 +8400,10 @@
         <v>282</v>
       </c>
       <c r="E207" t="s">
-        <v>264</v>
+        <v>283</v>
       </c>
       <c r="F207" t="s">
-        <v>283</v>
+        <v>265</v>
       </c>
     </row>
     <row r="208" spans="1:6">
@@ -8417,10 +8417,10 @@
         <v>19</v>
       </c>
       <c r="D208" t="s">
+        <v>263</v>
+      </c>
+      <c r="E208" t="s">
         <v>267</v>
-      </c>
-      <c r="E208" t="s">
-        <v>264</v>
       </c>
       <c r="F208" t="s">
         <v>265</v>
@@ -8437,10 +8437,10 @@
         <v>19</v>
       </c>
       <c r="D209" t="s">
+        <v>263</v>
+      </c>
+      <c r="E209" t="s">
         <v>279</v>
-      </c>
-      <c r="E209" t="s">
-        <v>264</v>
       </c>
       <c r="F209" t="s">
         <v>265</v>
@@ -8457,13 +8457,13 @@
         <v>19</v>
       </c>
       <c r="D210" t="s">
+        <v>195</v>
+      </c>
+      <c r="E210" t="s">
         <v>279</v>
       </c>
-      <c r="E210" t="s">
-        <v>264</v>
-      </c>
       <c r="F210" t="s">
-        <v>197</v>
+        <v>265</v>
       </c>
     </row>
     <row r="211" spans="1:6">
@@ -8480,10 +8480,10 @@
         <v>288</v>
       </c>
       <c r="E211" t="s">
-        <v>264</v>
+        <v>289</v>
       </c>
       <c r="F211" t="s">
-        <v>289</v>
+        <v>265</v>
       </c>
     </row>
     <row r="212" spans="1:6">
@@ -8497,10 +8497,10 @@
         <v>19</v>
       </c>
       <c r="D212" t="s">
+        <v>263</v>
+      </c>
+      <c r="E212" t="s">
         <v>267</v>
-      </c>
-      <c r="E212" t="s">
-        <v>264</v>
       </c>
       <c r="F212" t="s">
         <v>265</v>
@@ -8520,10 +8520,10 @@
         <v>292</v>
       </c>
       <c r="E213" t="s">
-        <v>264</v>
+        <v>293</v>
       </c>
       <c r="F213" t="s">
-        <v>293</v>
+        <v>265</v>
       </c>
     </row>
     <row r="214" spans="1:6">
@@ -8537,10 +8537,10 @@
         <v>19</v>
       </c>
       <c r="D214" t="s">
+        <v>263</v>
+      </c>
+      <c r="E214" t="s">
         <v>279</v>
-      </c>
-      <c r="E214" t="s">
-        <v>264</v>
       </c>
       <c r="F214" t="s">
         <v>265</v>
@@ -8557,13 +8557,13 @@
         <v>19</v>
       </c>
       <c r="D215" t="s">
+        <v>195</v>
+      </c>
+      <c r="E215" t="s">
         <v>279</v>
       </c>
-      <c r="E215" t="s">
-        <v>264</v>
-      </c>
       <c r="F215" t="s">
-        <v>197</v>
+        <v>265</v>
       </c>
     </row>
     <row r="216" spans="1:6">
@@ -8577,10 +8577,10 @@
         <v>19</v>
       </c>
       <c r="D216" t="s">
+        <v>263</v>
+      </c>
+      <c r="E216" t="s">
         <v>267</v>
-      </c>
-      <c r="E216" t="s">
-        <v>264</v>
       </c>
       <c r="F216" t="s">
         <v>265</v>
@@ -8597,10 +8597,10 @@
         <v>24</v>
       </c>
       <c r="D217" t="s">
+        <v>263</v>
+      </c>
+      <c r="E217" t="s">
         <v>298</v>
-      </c>
-      <c r="E217" t="s">
-        <v>264</v>
       </c>
       <c r="F217" t="s">
         <v>265</v>
@@ -8620,10 +8620,10 @@
         <v>300</v>
       </c>
       <c r="E218" t="s">
-        <v>264</v>
+        <v>301</v>
       </c>
       <c r="F218" t="s">
-        <v>301</v>
+        <v>265</v>
       </c>
     </row>
     <row r="219" spans="1:6">
@@ -8637,10 +8637,10 @@
         <v>19</v>
       </c>
       <c r="D219" t="s">
+        <v>263</v>
+      </c>
+      <c r="E219" t="s">
         <v>267</v>
-      </c>
-      <c r="E219" t="s">
-        <v>264</v>
       </c>
       <c r="F219" t="s">
         <v>265</v>
@@ -8657,13 +8657,13 @@
         <v>24</v>
       </c>
       <c r="D220" t="s">
+        <v>224</v>
+      </c>
+      <c r="E220" t="s">
         <v>267</v>
       </c>
-      <c r="E220" t="s">
-        <v>264</v>
-      </c>
       <c r="F220" t="s">
-        <v>225</v>
+        <v>265</v>
       </c>
     </row>
     <row r="221" spans="1:6">
@@ -8677,10 +8677,10 @@
         <v>24</v>
       </c>
       <c r="D221" t="s">
+        <v>263</v>
+      </c>
+      <c r="E221" t="s">
         <v>267</v>
-      </c>
-      <c r="E221" t="s">
-        <v>264</v>
       </c>
       <c r="F221" t="s">
         <v>265</v>
@@ -8697,10 +8697,10 @@
         <v>19</v>
       </c>
       <c r="D222" t="s">
+        <v>263</v>
+      </c>
+      <c r="E222" t="s">
         <v>267</v>
-      </c>
-      <c r="E222" t="s">
-        <v>264</v>
       </c>
       <c r="F222" t="s">
         <v>265</v>
@@ -8717,10 +8717,10 @@
         <v>19</v>
       </c>
       <c r="D223" t="s">
+        <v>263</v>
+      </c>
+      <c r="E223" t="s">
         <v>267</v>
-      </c>
-      <c r="E223" t="s">
-        <v>264</v>
       </c>
       <c r="F223" t="s">
         <v>265</v>
@@ -8737,10 +8737,10 @@
         <v>19</v>
       </c>
       <c r="D224" t="s">
+        <v>263</v>
+      </c>
+      <c r="E224" t="s">
         <v>267</v>
-      </c>
-      <c r="E224" t="s">
-        <v>264</v>
       </c>
       <c r="F224" t="s">
         <v>265</v>
@@ -8757,10 +8757,10 @@
         <v>15</v>
       </c>
       <c r="D225" t="s">
+        <v>263</v>
+      </c>
+      <c r="E225" t="s">
         <v>309</v>
-      </c>
-      <c r="E225" t="s">
-        <v>264</v>
       </c>
       <c r="F225" t="s">
         <v>265</v>
@@ -8777,10 +8777,10 @@
         <v>15</v>
       </c>
       <c r="D226" t="s">
+        <v>263</v>
+      </c>
+      <c r="E226" t="s">
         <v>311</v>
-      </c>
-      <c r="E226" t="s">
-        <v>264</v>
       </c>
       <c r="F226" t="s">
         <v>265</v>
@@ -8797,10 +8797,10 @@
         <v>19</v>
       </c>
       <c r="D227" t="s">
+        <v>263</v>
+      </c>
+      <c r="E227" t="s">
         <v>267</v>
-      </c>
-      <c r="E227" t="s">
-        <v>264</v>
       </c>
       <c r="F227" t="s">
         <v>265</v>
@@ -8817,10 +8817,10 @@
         <v>19</v>
       </c>
       <c r="D228" t="s">
+        <v>263</v>
+      </c>
+      <c r="E228" t="s">
         <v>267</v>
-      </c>
-      <c r="E228" t="s">
-        <v>264</v>
       </c>
       <c r="F228" t="s">
         <v>265</v>
@@ -8837,10 +8837,10 @@
         <v>24</v>
       </c>
       <c r="D229" t="s">
+        <v>263</v>
+      </c>
+      <c r="E229" t="s">
         <v>311</v>
-      </c>
-      <c r="E229" t="s">
-        <v>264</v>
       </c>
       <c r="F229" t="s">
         <v>265</v>
@@ -8857,10 +8857,10 @@
         <v>15</v>
       </c>
       <c r="D230" t="s">
+        <v>263</v>
+      </c>
+      <c r="E230" t="s">
         <v>311</v>
-      </c>
-      <c r="E230" t="s">
-        <v>264</v>
       </c>
       <c r="F230" t="s">
         <v>265</v>
@@ -8877,10 +8877,10 @@
         <v>19</v>
       </c>
       <c r="D231" t="s">
+        <v>263</v>
+      </c>
+      <c r="E231" t="s">
         <v>267</v>
-      </c>
-      <c r="E231" t="s">
-        <v>264</v>
       </c>
       <c r="F231" t="s">
         <v>265</v>
@@ -8897,10 +8897,10 @@
         <v>19</v>
       </c>
       <c r="D232" t="s">
+        <v>263</v>
+      </c>
+      <c r="E232" t="s">
         <v>267</v>
-      </c>
-      <c r="E232" t="s">
-        <v>264</v>
       </c>
       <c r="F232" t="s">
         <v>265</v>
@@ -8917,10 +8917,10 @@
         <v>13</v>
       </c>
       <c r="D233" t="s">
+        <v>263</v>
+      </c>
+      <c r="E233" t="s">
         <v>267</v>
-      </c>
-      <c r="E233" t="s">
-        <v>264</v>
       </c>
       <c r="F233" t="s">
         <v>265</v>
@@ -8937,10 +8937,10 @@
         <v>13</v>
       </c>
       <c r="D234" t="s">
+        <v>263</v>
+      </c>
+      <c r="E234" t="s">
         <v>267</v>
-      </c>
-      <c r="E234" t="s">
-        <v>264</v>
       </c>
       <c r="F234" t="s">
         <v>265</v>
@@ -8957,10 +8957,10 @@
         <v>19</v>
       </c>
       <c r="D235" t="s">
+        <v>263</v>
+      </c>
+      <c r="E235" t="s">
         <v>267</v>
-      </c>
-      <c r="E235" t="s">
-        <v>264</v>
       </c>
       <c r="F235" t="s">
         <v>265</v>
@@ -8977,10 +8977,10 @@
         <v>19</v>
       </c>
       <c r="D236" t="s">
+        <v>263</v>
+      </c>
+      <c r="E236" t="s">
         <v>267</v>
-      </c>
-      <c r="E236" t="s">
-        <v>264</v>
       </c>
       <c r="F236" t="s">
         <v>265</v>
@@ -8997,10 +8997,10 @@
         <v>13</v>
       </c>
       <c r="D237" t="s">
+        <v>263</v>
+      </c>
+      <c r="E237" t="s">
         <v>267</v>
-      </c>
-      <c r="E237" t="s">
-        <v>264</v>
       </c>
       <c r="F237" t="s">
         <v>265</v>
@@ -9017,10 +9017,10 @@
         <v>19</v>
       </c>
       <c r="D238" t="s">
+        <v>263</v>
+      </c>
+      <c r="E238" t="s">
         <v>267</v>
-      </c>
-      <c r="E238" t="s">
-        <v>264</v>
       </c>
       <c r="F238" t="s">
         <v>265</v>
@@ -9037,10 +9037,10 @@
         <v>19</v>
       </c>
       <c r="D239" t="s">
+        <v>263</v>
+      </c>
+      <c r="E239" t="s">
         <v>267</v>
-      </c>
-      <c r="E239" t="s">
-        <v>264</v>
       </c>
       <c r="F239" t="s">
         <v>265</v>
@@ -9057,10 +9057,10 @@
         <v>13</v>
       </c>
       <c r="D240" t="s">
+        <v>263</v>
+      </c>
+      <c r="E240" t="s">
         <v>267</v>
-      </c>
-      <c r="E240" t="s">
-        <v>264</v>
       </c>
       <c r="F240" t="s">
         <v>265</v>
@@ -9077,10 +9077,10 @@
         <v>19</v>
       </c>
       <c r="D241" t="s">
+        <v>263</v>
+      </c>
+      <c r="E241" t="s">
         <v>267</v>
-      </c>
-      <c r="E241" t="s">
-        <v>264</v>
       </c>
       <c r="F241" t="s">
         <v>265</v>
@@ -9097,10 +9097,10 @@
         <v>19</v>
       </c>
       <c r="D242" t="s">
+        <v>263</v>
+      </c>
+      <c r="E242" t="s">
         <v>267</v>
-      </c>
-      <c r="E242" t="s">
-        <v>264</v>
       </c>
       <c r="F242" t="s">
         <v>265</v>
@@ -9117,10 +9117,10 @@
         <v>19</v>
       </c>
       <c r="D243" t="s">
+        <v>263</v>
+      </c>
+      <c r="E243" t="s">
         <v>267</v>
-      </c>
-      <c r="E243" t="s">
-        <v>264</v>
       </c>
       <c r="F243" t="s">
         <v>265</v>
@@ -9137,10 +9137,10 @@
         <v>19</v>
       </c>
       <c r="D244" t="s">
+        <v>263</v>
+      </c>
+      <c r="E244" t="s">
         <v>267</v>
-      </c>
-      <c r="E244" t="s">
-        <v>264</v>
       </c>
       <c r="F244" t="s">
         <v>265</v>
@@ -9177,10 +9177,10 @@
         <v>15</v>
       </c>
       <c r="D246" t="s">
+        <v>331</v>
+      </c>
+      <c r="E246" t="s">
         <v>335</v>
-      </c>
-      <c r="E246" t="s">
-        <v>332</v>
       </c>
       <c r="F246" t="s">
         <v>333</v>
@@ -9217,10 +9217,10 @@
         <v>15</v>
       </c>
       <c r="D248" t="s">
+        <v>331</v>
+      </c>
+      <c r="E248" t="s">
         <v>335</v>
-      </c>
-      <c r="E248" t="s">
-        <v>332</v>
       </c>
       <c r="F248" t="s">
         <v>333</v>
@@ -9297,10 +9297,10 @@
         <v>15</v>
       </c>
       <c r="D252" t="s">
+        <v>331</v>
+      </c>
+      <c r="E252" t="s">
         <v>342</v>
-      </c>
-      <c r="E252" t="s">
-        <v>332</v>
       </c>
       <c r="F252" t="s">
         <v>333</v>
@@ -9337,13 +9337,13 @@
         <v>19</v>
       </c>
       <c r="D254" t="s">
+        <v>267</v>
+      </c>
+      <c r="E254" t="s">
         <v>345</v>
       </c>
-      <c r="E254" t="s">
-        <v>332</v>
-      </c>
       <c r="F254" t="s">
-        <v>267</v>
+        <v>333</v>
       </c>
     </row>
     <row r="255" spans="1:6">
@@ -9397,10 +9397,10 @@
         <v>15</v>
       </c>
       <c r="D257" t="s">
+        <v>331</v>
+      </c>
+      <c r="E257" t="s">
         <v>335</v>
-      </c>
-      <c r="E257" t="s">
-        <v>332</v>
       </c>
       <c r="F257" t="s">
         <v>333</v>
@@ -9417,10 +9417,10 @@
         <v>15</v>
       </c>
       <c r="D258" t="s">
+        <v>331</v>
+      </c>
+      <c r="E258" t="s">
         <v>335</v>
-      </c>
-      <c r="E258" t="s">
-        <v>332</v>
       </c>
       <c r="F258" t="s">
         <v>333</v>
@@ -9437,10 +9437,10 @@
         <v>19</v>
       </c>
       <c r="D259" t="s">
+        <v>331</v>
+      </c>
+      <c r="E259" t="s">
         <v>351</v>
-      </c>
-      <c r="E259" t="s">
-        <v>332</v>
       </c>
       <c r="F259" t="s">
         <v>333</v>
@@ -9500,10 +9500,10 @@
         <v>355</v>
       </c>
       <c r="E262" t="s">
-        <v>332</v>
+        <v>356</v>
       </c>
       <c r="F262" t="s">
-        <v>356</v>
+        <v>333</v>
       </c>
     </row>
     <row r="263" spans="1:6">
@@ -9517,10 +9517,10 @@
         <v>15</v>
       </c>
       <c r="D263" t="s">
+        <v>331</v>
+      </c>
+      <c r="E263" t="s">
         <v>335</v>
-      </c>
-      <c r="E263" t="s">
-        <v>332</v>
       </c>
       <c r="F263" t="s">
         <v>333</v>
@@ -9537,10 +9537,10 @@
         <v>15</v>
       </c>
       <c r="D264" t="s">
+        <v>331</v>
+      </c>
+      <c r="E264" t="s">
         <v>335</v>
-      </c>
-      <c r="E264" t="s">
-        <v>332</v>
       </c>
       <c r="F264" t="s">
         <v>333</v>
@@ -9577,10 +9577,10 @@
         <v>15</v>
       </c>
       <c r="D266" t="s">
+        <v>331</v>
+      </c>
+      <c r="E266" t="s">
         <v>335</v>
-      </c>
-      <c r="E266" t="s">
-        <v>332</v>
       </c>
       <c r="F266" t="s">
         <v>333</v>
@@ -9617,10 +9617,10 @@
         <v>15</v>
       </c>
       <c r="D268" t="s">
+        <v>331</v>
+      </c>
+      <c r="E268" t="s">
         <v>335</v>
-      </c>
-      <c r="E268" t="s">
-        <v>332</v>
       </c>
       <c r="F268" t="s">
         <v>333</v>
@@ -9637,10 +9637,10 @@
         <v>15</v>
       </c>
       <c r="D269" t="s">
+        <v>331</v>
+      </c>
+      <c r="E269" t="s">
         <v>351</v>
-      </c>
-      <c r="E269" t="s">
-        <v>332</v>
       </c>
       <c r="F269" t="s">
         <v>333</v>
@@ -9657,10 +9657,10 @@
         <v>15</v>
       </c>
       <c r="D270" t="s">
+        <v>331</v>
+      </c>
+      <c r="E270" t="s">
         <v>335</v>
-      </c>
-      <c r="E270" t="s">
-        <v>332</v>
       </c>
       <c r="F270" t="s">
         <v>333</v>
@@ -9677,10 +9677,10 @@
         <v>15</v>
       </c>
       <c r="D271" t="s">
+        <v>331</v>
+      </c>
+      <c r="E271" t="s">
         <v>335</v>
-      </c>
-      <c r="E271" t="s">
-        <v>332</v>
       </c>
       <c r="F271" t="s">
         <v>333</v>
@@ -9717,10 +9717,10 @@
         <v>15</v>
       </c>
       <c r="D273" t="s">
+        <v>331</v>
+      </c>
+      <c r="E273" t="s">
         <v>335</v>
-      </c>
-      <c r="E273" t="s">
-        <v>332</v>
       </c>
       <c r="F273" t="s">
         <v>333</v>
@@ -9757,10 +9757,10 @@
         <v>15</v>
       </c>
       <c r="D275" t="s">
+        <v>331</v>
+      </c>
+      <c r="E275" t="s">
         <v>335</v>
-      </c>
-      <c r="E275" t="s">
-        <v>332</v>
       </c>
       <c r="F275" t="s">
         <v>333</v>
@@ -9777,10 +9777,10 @@
         <v>15</v>
       </c>
       <c r="D276" t="s">
+        <v>331</v>
+      </c>
+      <c r="E276" t="s">
         <v>371</v>
-      </c>
-      <c r="E276" t="s">
-        <v>332</v>
       </c>
       <c r="F276" t="s">
         <v>333</v>
@@ -9800,10 +9800,10 @@
         <v>373</v>
       </c>
       <c r="E277" t="s">
-        <v>332</v>
+        <v>374</v>
       </c>
       <c r="F277" t="s">
-        <v>374</v>
+        <v>333</v>
       </c>
     </row>
     <row r="278" spans="1:6">
@@ -9817,10 +9817,10 @@
         <v>15</v>
       </c>
       <c r="D278" t="s">
+        <v>331</v>
+      </c>
+      <c r="E278" t="s">
         <v>335</v>
-      </c>
-      <c r="E278" t="s">
-        <v>332</v>
       </c>
       <c r="F278" t="s">
         <v>333</v>
@@ -9840,10 +9840,10 @@
         <v>377</v>
       </c>
       <c r="E279" t="s">
-        <v>332</v>
+        <v>378</v>
       </c>
       <c r="F279" t="s">
-        <v>378</v>
+        <v>333</v>
       </c>
     </row>
     <row r="280" spans="1:6">
@@ -9857,10 +9857,10 @@
         <v>15</v>
       </c>
       <c r="D280" t="s">
+        <v>331</v>
+      </c>
+      <c r="E280" t="s">
         <v>335</v>
-      </c>
-      <c r="E280" t="s">
-        <v>332</v>
       </c>
       <c r="F280" t="s">
         <v>333</v>
@@ -9917,10 +9917,10 @@
         <v>15</v>
       </c>
       <c r="D283" t="s">
+        <v>331</v>
+      </c>
+      <c r="E283" t="s">
         <v>335</v>
-      </c>
-      <c r="E283" t="s">
-        <v>332</v>
       </c>
       <c r="F283" t="s">
         <v>333</v>
@@ -10017,10 +10017,10 @@
         <v>15</v>
       </c>
       <c r="D288" t="s">
+        <v>331</v>
+      </c>
+      <c r="E288" t="s">
         <v>371</v>
-      </c>
-      <c r="E288" t="s">
-        <v>332</v>
       </c>
       <c r="F288" t="s">
         <v>333</v>
@@ -10037,10 +10037,10 @@
         <v>15</v>
       </c>
       <c r="D289" t="s">
+        <v>331</v>
+      </c>
+      <c r="E289" t="s">
         <v>335</v>
-      </c>
-      <c r="E289" t="s">
-        <v>332</v>
       </c>
       <c r="F289" t="s">
         <v>333</v>
@@ -10097,10 +10097,10 @@
         <v>15</v>
       </c>
       <c r="D292" t="s">
+        <v>331</v>
+      </c>
+      <c r="E292" t="s">
         <v>371</v>
-      </c>
-      <c r="E292" t="s">
-        <v>332</v>
       </c>
       <c r="F292" t="s">
         <v>333</v>
@@ -10117,10 +10117,10 @@
         <v>15</v>
       </c>
       <c r="D293" t="s">
+        <v>331</v>
+      </c>
+      <c r="E293" t="s">
         <v>335</v>
-      </c>
-      <c r="E293" t="s">
-        <v>332</v>
       </c>
       <c r="F293" t="s">
         <v>333</v>
@@ -10257,10 +10257,10 @@
         <v>15</v>
       </c>
       <c r="D300" t="s">
+        <v>331</v>
+      </c>
+      <c r="E300" t="s">
         <v>335</v>
-      </c>
-      <c r="E300" t="s">
-        <v>332</v>
       </c>
       <c r="F300" t="s">
         <v>333</v>
@@ -10277,10 +10277,10 @@
         <v>15</v>
       </c>
       <c r="D301" t="s">
+        <v>331</v>
+      </c>
+      <c r="E301" t="s">
         <v>335</v>
-      </c>
-      <c r="E301" t="s">
-        <v>332</v>
       </c>
       <c r="F301" t="s">
         <v>333</v>
@@ -10297,10 +10297,10 @@
         <v>15</v>
       </c>
       <c r="D302" t="s">
+        <v>331</v>
+      </c>
+      <c r="E302" t="s">
         <v>335</v>
-      </c>
-      <c r="E302" t="s">
-        <v>332</v>
       </c>
       <c r="F302" t="s">
         <v>333</v>
@@ -10337,10 +10337,10 @@
         <v>15</v>
       </c>
       <c r="D304" t="s">
+        <v>331</v>
+      </c>
+      <c r="E304" t="s">
         <v>335</v>
-      </c>
-      <c r="E304" t="s">
-        <v>332</v>
       </c>
       <c r="F304" t="s">
         <v>333</v>
@@ -10397,13 +10397,13 @@
         <v>15</v>
       </c>
       <c r="D307" t="s">
+        <v>355</v>
+      </c>
+      <c r="E307" t="s">
         <v>407</v>
       </c>
-      <c r="E307" t="s">
-        <v>332</v>
-      </c>
       <c r="F307" t="s">
-        <v>356</v>
+        <v>333</v>
       </c>
     </row>
     <row r="308" spans="1:6">
@@ -10417,10 +10417,10 @@
         <v>15</v>
       </c>
       <c r="D308" t="s">
+        <v>331</v>
+      </c>
+      <c r="E308" t="s">
         <v>335</v>
-      </c>
-      <c r="E308" t="s">
-        <v>332</v>
       </c>
       <c r="F308" t="s">
         <v>333</v>
@@ -10717,10 +10717,10 @@
         <v>15</v>
       </c>
       <c r="D323" t="s">
+        <v>411</v>
+      </c>
+      <c r="E323" t="s">
         <v>427</v>
-      </c>
-      <c r="E323" t="s">
-        <v>412</v>
       </c>
       <c r="F323" t="s">
         <v>413</v>
@@ -10757,13 +10757,13 @@
         <v>24</v>
       </c>
       <c r="D325" t="s">
-        <v>411</v>
+        <v>430</v>
       </c>
       <c r="E325" t="s">
         <v>412</v>
       </c>
       <c r="F325" t="s">
-        <v>430</v>
+        <v>413</v>
       </c>
     </row>
     <row r="326" spans="1:6">
@@ -10877,13 +10877,13 @@
         <v>19</v>
       </c>
       <c r="D331" t="s">
-        <v>411</v>
+        <v>437</v>
       </c>
       <c r="E331" t="s">
         <v>412</v>
       </c>
       <c r="F331" t="s">
-        <v>437</v>
+        <v>413</v>
       </c>
     </row>
     <row r="332" spans="1:6">
@@ -11120,10 +11120,10 @@
         <v>450</v>
       </c>
       <c r="E343" t="s">
-        <v>412</v>
+        <v>451</v>
       </c>
       <c r="F343" t="s">
-        <v>451</v>
+        <v>413</v>
       </c>
     </row>
     <row r="344" spans="1:6">
@@ -11137,13 +11137,13 @@
         <v>24</v>
       </c>
       <c r="D344" t="s">
+        <v>450</v>
+      </c>
+      <c r="E344" t="s">
         <v>453</v>
       </c>
-      <c r="E344" t="s">
-        <v>412</v>
-      </c>
       <c r="F344" t="s">
-        <v>451</v>
+        <v>413</v>
       </c>
     </row>
     <row r="345" spans="1:6">
@@ -11177,10 +11177,10 @@
         <v>15</v>
       </c>
       <c r="D346" t="s">
+        <v>455</v>
+      </c>
+      <c r="E346" t="s">
         <v>459</v>
-      </c>
-      <c r="E346" t="s">
-        <v>456</v>
       </c>
       <c r="F346" t="s">
         <v>457</v>
@@ -11377,10 +11377,10 @@
         <v>15</v>
       </c>
       <c r="D356" t="s">
+        <v>455</v>
+      </c>
+      <c r="E356" t="s">
         <v>470</v>
-      </c>
-      <c r="E356" t="s">
-        <v>456</v>
       </c>
       <c r="F356" t="s">
         <v>457</v>
@@ -11577,10 +11577,10 @@
         <v>15</v>
       </c>
       <c r="D366" t="s">
+        <v>455</v>
+      </c>
+      <c r="E366" t="s">
         <v>481</v>
-      </c>
-      <c r="E366" t="s">
-        <v>456</v>
       </c>
       <c r="F366" t="s">
         <v>457</v>
@@ -11597,10 +11597,10 @@
         <v>13</v>
       </c>
       <c r="D367" t="s">
+        <v>455</v>
+      </c>
+      <c r="E367" t="s">
         <v>459</v>
-      </c>
-      <c r="E367" t="s">
-        <v>456</v>
       </c>
       <c r="F367" t="s">
         <v>457</v>
@@ -11677,13 +11677,13 @@
         <v>19</v>
       </c>
       <c r="D371" t="s">
-        <v>455</v>
+        <v>487</v>
       </c>
       <c r="E371" t="s">
         <v>456</v>
       </c>
       <c r="F371" t="s">
-        <v>487</v>
+        <v>457</v>
       </c>
     </row>
     <row r="372" spans="1:6">
@@ -11700,10 +11700,10 @@
         <v>489</v>
       </c>
       <c r="E372" t="s">
-        <v>456</v>
+        <v>490</v>
       </c>
       <c r="F372" t="s">
-        <v>490</v>
+        <v>457</v>
       </c>
     </row>
     <row r="373" spans="1:6">
@@ -11740,10 +11740,10 @@
         <v>489</v>
       </c>
       <c r="E374" t="s">
-        <v>456</v>
+        <v>490</v>
       </c>
       <c r="F374" t="s">
-        <v>490</v>
+        <v>457</v>
       </c>
     </row>
     <row r="375" spans="1:6">
@@ -11857,10 +11857,10 @@
         <v>13</v>
       </c>
       <c r="D380" t="s">
+        <v>497</v>
+      </c>
+      <c r="E380" t="s">
         <v>502</v>
-      </c>
-      <c r="E380" t="s">
-        <v>498</v>
       </c>
       <c r="F380" t="s">
         <v>499</v>
@@ -11977,10 +11977,10 @@
         <v>15</v>
       </c>
       <c r="D386" t="s">
+        <v>497</v>
+      </c>
+      <c r="E386" t="s">
         <v>509</v>
-      </c>
-      <c r="E386" t="s">
-        <v>498</v>
       </c>
       <c r="F386" t="s">
         <v>499</v>
@@ -11997,10 +11997,10 @@
         <v>19</v>
       </c>
       <c r="D387" t="s">
+        <v>497</v>
+      </c>
+      <c r="E387" t="s">
         <v>511</v>
-      </c>
-      <c r="E387" t="s">
-        <v>498</v>
       </c>
       <c r="F387" t="s">
         <v>499</v>
@@ -12040,10 +12040,10 @@
         <v>514</v>
       </c>
       <c r="E389" t="s">
-        <v>498</v>
+        <v>515</v>
       </c>
       <c r="F389" t="s">
-        <v>515</v>
+        <v>499</v>
       </c>
     </row>
     <row r="390" spans="1:6">
@@ -12117,10 +12117,10 @@
         <v>15</v>
       </c>
       <c r="D393" t="s">
+        <v>497</v>
+      </c>
+      <c r="E393" t="s">
         <v>520</v>
-      </c>
-      <c r="E393" t="s">
-        <v>498</v>
       </c>
       <c r="F393" t="s">
         <v>499</v>
@@ -12160,10 +12160,10 @@
         <v>523</v>
       </c>
       <c r="E395" t="s">
-        <v>498</v>
+        <v>524</v>
       </c>
       <c r="F395" t="s">
-        <v>524</v>
+        <v>499</v>
       </c>
     </row>
     <row r="396" spans="1:6">
@@ -12200,10 +12200,10 @@
         <v>527</v>
       </c>
       <c r="E397" t="s">
-        <v>498</v>
+        <v>528</v>
       </c>
       <c r="F397" t="s">
-        <v>528</v>
+        <v>499</v>
       </c>
     </row>
     <row r="398" spans="1:6">
@@ -12260,10 +12260,10 @@
         <v>532</v>
       </c>
       <c r="E400" t="s">
-        <v>498</v>
+        <v>533</v>
       </c>
       <c r="F400" t="s">
-        <v>533</v>
+        <v>499</v>
       </c>
     </row>
     <row r="401" spans="1:6">
@@ -12380,10 +12380,10 @@
         <v>540</v>
       </c>
       <c r="E406" t="s">
-        <v>498</v>
+        <v>541</v>
       </c>
       <c r="F406" t="s">
-        <v>541</v>
+        <v>499</v>
       </c>
     </row>
     <row r="407" spans="1:6">
@@ -12397,10 +12397,10 @@
         <v>19</v>
       </c>
       <c r="D407" t="s">
+        <v>497</v>
+      </c>
+      <c r="E407" t="s">
         <v>543</v>
-      </c>
-      <c r="E407" t="s">
-        <v>498</v>
       </c>
       <c r="F407" t="s">
         <v>499</v>
@@ -12637,10 +12637,10 @@
         <v>24</v>
       </c>
       <c r="D419" t="s">
+        <v>554</v>
+      </c>
+      <c r="E419" t="s">
         <v>559</v>
-      </c>
-      <c r="E419" t="s">
-        <v>555</v>
       </c>
       <c r="F419" t="s">
         <v>556</v>
@@ -12677,10 +12677,10 @@
         <v>19</v>
       </c>
       <c r="D421" t="s">
+        <v>554</v>
+      </c>
+      <c r="E421" t="s">
         <v>562</v>
-      </c>
-      <c r="E421" t="s">
-        <v>555</v>
       </c>
       <c r="F421" t="s">
         <v>556</v>
@@ -12820,10 +12820,10 @@
         <v>570</v>
       </c>
       <c r="E428" t="s">
-        <v>555</v>
+        <v>571</v>
       </c>
       <c r="F428" t="s">
-        <v>571</v>
+        <v>556</v>
       </c>
     </row>
     <row r="429" spans="1:6">
@@ -12840,10 +12840,10 @@
         <v>573</v>
       </c>
       <c r="E429" t="s">
-        <v>555</v>
+        <v>574</v>
       </c>
       <c r="F429" t="s">
-        <v>574</v>
+        <v>556</v>
       </c>
     </row>
     <row r="430" spans="1:6">
@@ -12917,10 +12917,10 @@
         <v>24</v>
       </c>
       <c r="D433" t="s">
+        <v>554</v>
+      </c>
+      <c r="E433" t="s">
         <v>579</v>
-      </c>
-      <c r="E433" t="s">
-        <v>555</v>
       </c>
       <c r="F433" t="s">
         <v>556</v>
@@ -12977,10 +12977,10 @@
         <v>24</v>
       </c>
       <c r="D436" t="s">
+        <v>554</v>
+      </c>
+      <c r="E436" t="s">
         <v>583</v>
-      </c>
-      <c r="E436" t="s">
-        <v>555</v>
       </c>
       <c r="F436" t="s">
         <v>556</v>
@@ -12997,10 +12997,10 @@
         <v>19</v>
       </c>
       <c r="D437" t="s">
+        <v>554</v>
+      </c>
+      <c r="E437" t="s">
         <v>585</v>
-      </c>
-      <c r="E437" t="s">
-        <v>555</v>
       </c>
       <c r="F437" t="s">
         <v>556</v>
@@ -13060,10 +13060,10 @@
         <v>589</v>
       </c>
       <c r="E440" t="s">
-        <v>555</v>
+        <v>590</v>
       </c>
       <c r="F440" t="s">
-        <v>590</v>
+        <v>556</v>
       </c>
     </row>
     <row r="441" spans="1:6">
@@ -13340,10 +13340,10 @@
         <v>605</v>
       </c>
       <c r="E454" t="s">
-        <v>555</v>
+        <v>606</v>
       </c>
       <c r="F454" t="s">
-        <v>606</v>
+        <v>556</v>
       </c>
     </row>
     <row r="455" spans="1:6">
@@ -13540,10 +13540,10 @@
         <v>621</v>
       </c>
       <c r="E464" t="s">
-        <v>610</v>
+        <v>622</v>
       </c>
       <c r="F464" t="s">
-        <v>622</v>
+        <v>611</v>
       </c>
     </row>
     <row r="465" spans="1:6">
@@ -13557,10 +13557,10 @@
         <v>24</v>
       </c>
       <c r="D465" t="s">
+        <v>609</v>
+      </c>
+      <c r="E465" t="s">
         <v>624</v>
-      </c>
-      <c r="E465" t="s">
-        <v>610</v>
       </c>
       <c r="F465" t="s">
         <v>611</v>
@@ -13577,13 +13577,13 @@
         <v>24</v>
       </c>
       <c r="D466" t="s">
+        <v>621</v>
+      </c>
+      <c r="E466" t="s">
         <v>626</v>
       </c>
-      <c r="E466" t="s">
-        <v>610</v>
-      </c>
       <c r="F466" t="s">
-        <v>622</v>
+        <v>611</v>
       </c>
     </row>
     <row r="467" spans="1:6">
@@ -13600,10 +13600,10 @@
         <v>628</v>
       </c>
       <c r="E467" t="s">
-        <v>610</v>
+        <v>629</v>
       </c>
       <c r="F467" t="s">
-        <v>629</v>
+        <v>611</v>
       </c>
     </row>
     <row r="468" spans="1:6">
@@ -13640,10 +13640,10 @@
         <v>632</v>
       </c>
       <c r="E469" t="s">
-        <v>610</v>
+        <v>633</v>
       </c>
       <c r="F469" t="s">
-        <v>633</v>
+        <v>611</v>
       </c>
     </row>
     <row r="470" spans="1:6">
@@ -13717,13 +13717,13 @@
         <v>24</v>
       </c>
       <c r="D473" t="s">
+        <v>621</v>
+      </c>
+      <c r="E473" t="s">
         <v>638</v>
       </c>
-      <c r="E473" t="s">
-        <v>610</v>
-      </c>
       <c r="F473" t="s">
-        <v>622</v>
+        <v>611</v>
       </c>
     </row>
     <row r="474" spans="1:6">
@@ -14017,10 +14017,10 @@
         <v>608</v>
       </c>
       <c r="D488" t="s">
+        <v>653</v>
+      </c>
+      <c r="E488" t="s">
         <v>657</v>
-      </c>
-      <c r="E488" t="s">
-        <v>654</v>
       </c>
       <c r="F488" t="s">
         <v>655</v>
@@ -14097,13 +14097,13 @@
         <v>19</v>
       </c>
       <c r="D492" t="s">
-        <v>653</v>
+        <v>662</v>
       </c>
       <c r="E492" t="s">
         <v>654</v>
       </c>
       <c r="F492" t="s">
-        <v>662</v>
+        <v>655</v>
       </c>
     </row>
     <row r="493" spans="1:6">
@@ -14137,13 +14137,13 @@
         <v>13</v>
       </c>
       <c r="D494" t="s">
-        <v>632</v>
+        <v>665</v>
       </c>
       <c r="E494" t="s">
-        <v>654</v>
+        <v>633</v>
       </c>
       <c r="F494" t="s">
-        <v>665</v>
+        <v>655</v>
       </c>
     </row>
     <row r="495" spans="1:6">
@@ -14157,13 +14157,13 @@
         <v>15</v>
       </c>
       <c r="D495" t="s">
-        <v>632</v>
+        <v>665</v>
       </c>
       <c r="E495" t="s">
-        <v>654</v>
+        <v>633</v>
       </c>
       <c r="F495" t="s">
-        <v>665</v>
+        <v>655</v>
       </c>
     </row>
     <row r="496" spans="1:6">
@@ -14217,10 +14217,10 @@
         <v>608</v>
       </c>
       <c r="D498" t="s">
+        <v>653</v>
+      </c>
+      <c r="E498" t="s">
         <v>670</v>
-      </c>
-      <c r="E498" t="s">
-        <v>654</v>
       </c>
       <c r="F498" t="s">
         <v>655</v>
@@ -14297,10 +14297,10 @@
         <v>19</v>
       </c>
       <c r="D502" t="s">
+        <v>653</v>
+      </c>
+      <c r="E502" t="s">
         <v>675</v>
-      </c>
-      <c r="E502" t="s">
-        <v>654</v>
       </c>
       <c r="F502" t="s">
         <v>655</v>
@@ -14400,10 +14400,10 @@
         <v>681</v>
       </c>
       <c r="E507" t="s">
-        <v>654</v>
+        <v>682</v>
       </c>
       <c r="F507" t="s">
-        <v>682</v>
+        <v>655</v>
       </c>
     </row>
     <row r="508" spans="1:6">
@@ -14420,10 +14420,10 @@
         <v>684</v>
       </c>
       <c r="E508" t="s">
-        <v>654</v>
+        <v>685</v>
       </c>
       <c r="F508" t="s">
-        <v>685</v>
+        <v>655</v>
       </c>
     </row>
     <row r="509" spans="1:6">
@@ -14437,13 +14437,13 @@
         <v>19</v>
       </c>
       <c r="D509" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="E509" t="s">
-        <v>654</v>
+        <v>685</v>
       </c>
       <c r="F509" t="s">
-        <v>687</v>
+        <v>655</v>
       </c>
     </row>
     <row r="510" spans="1:6">
@@ -14460,10 +14460,10 @@
         <v>689</v>
       </c>
       <c r="E510" t="s">
-        <v>654</v>
+        <v>690</v>
       </c>
       <c r="F510" t="s">
-        <v>690</v>
+        <v>655</v>
       </c>
     </row>
     <row r="511" spans="1:6">
@@ -14497,10 +14497,10 @@
         <v>15</v>
       </c>
       <c r="D512" t="s">
+        <v>653</v>
+      </c>
+      <c r="E512" t="s">
         <v>693</v>
-      </c>
-      <c r="E512" t="s">
-        <v>654</v>
       </c>
       <c r="F512" t="s">
         <v>655</v>
@@ -14517,13 +14517,13 @@
         <v>19</v>
       </c>
       <c r="D513" t="s">
-        <v>653</v>
+        <v>695</v>
       </c>
       <c r="E513" t="s">
         <v>654</v>
       </c>
       <c r="F513" t="s">
-        <v>695</v>
+        <v>655</v>
       </c>
     </row>
     <row r="514" spans="1:6">
@@ -14677,10 +14677,10 @@
         <v>19</v>
       </c>
       <c r="D521" t="s">
+        <v>653</v>
+      </c>
+      <c r="E521" t="s">
         <v>704</v>
-      </c>
-      <c r="E521" t="s">
-        <v>654</v>
       </c>
       <c r="F521" t="s">
         <v>655</v>
@@ -14697,10 +14697,10 @@
         <v>13</v>
       </c>
       <c r="D522" t="s">
+        <v>653</v>
+      </c>
+      <c r="E522" t="s">
         <v>706</v>
-      </c>
-      <c r="E522" t="s">
-        <v>654</v>
       </c>
       <c r="F522" t="s">
         <v>655</v>
@@ -14717,10 +14717,10 @@
         <v>24</v>
       </c>
       <c r="D523" t="s">
+        <v>653</v>
+      </c>
+      <c r="E523" t="s">
         <v>708</v>
-      </c>
-      <c r="E523" t="s">
-        <v>654</v>
       </c>
       <c r="F523" t="s">
         <v>655</v>
@@ -14757,10 +14757,10 @@
         <v>711</v>
       </c>
       <c r="D525" t="s">
+        <v>712</v>
+      </c>
+      <c r="E525" t="s">
         <v>657</v>
-      </c>
-      <c r="E525" t="s">
-        <v>712</v>
       </c>
       <c r="F525" t="s">
         <v>713</v>
@@ -14777,10 +14777,10 @@
         <v>711</v>
       </c>
       <c r="D526" t="s">
+        <v>712</v>
+      </c>
+      <c r="E526" t="s">
         <v>657</v>
-      </c>
-      <c r="E526" t="s">
-        <v>712</v>
       </c>
       <c r="F526" t="s">
         <v>713</v>
@@ -14797,10 +14797,10 @@
         <v>711</v>
       </c>
       <c r="D527" t="s">
+        <v>712</v>
+      </c>
+      <c r="E527" t="s">
         <v>657</v>
-      </c>
-      <c r="E527" t="s">
-        <v>712</v>
       </c>
       <c r="F527" t="s">
         <v>713</v>
@@ -14817,10 +14817,10 @@
         <v>711</v>
       </c>
       <c r="D528" t="s">
+        <v>712</v>
+      </c>
+      <c r="E528" t="s">
         <v>657</v>
-      </c>
-      <c r="E528" t="s">
-        <v>712</v>
       </c>
       <c r="F528" t="s">
         <v>713</v>
@@ -14837,10 +14837,10 @@
         <v>15</v>
       </c>
       <c r="D529" t="s">
+        <v>712</v>
+      </c>
+      <c r="E529" t="s">
         <v>718</v>
-      </c>
-      <c r="E529" t="s">
-        <v>712</v>
       </c>
       <c r="F529" t="s">
         <v>713</v>
@@ -14857,13 +14857,13 @@
         <v>711</v>
       </c>
       <c r="D530" t="s">
+        <v>720</v>
+      </c>
+      <c r="E530" t="s">
         <v>657</v>
       </c>
-      <c r="E530" t="s">
-        <v>712</v>
-      </c>
       <c r="F530" t="s">
-        <v>720</v>
+        <v>713</v>
       </c>
     </row>
     <row r="531" spans="1:6">
@@ -14877,10 +14877,10 @@
         <v>711</v>
       </c>
       <c r="D531" t="s">
+        <v>712</v>
+      </c>
+      <c r="E531" t="s">
         <v>657</v>
-      </c>
-      <c r="E531" t="s">
-        <v>712</v>
       </c>
       <c r="F531" t="s">
         <v>713</v>
@@ -14897,10 +14897,10 @@
         <v>711</v>
       </c>
       <c r="D532" t="s">
+        <v>712</v>
+      </c>
+      <c r="E532" t="s">
         <v>657</v>
-      </c>
-      <c r="E532" t="s">
-        <v>712</v>
       </c>
       <c r="F532" t="s">
         <v>713</v>
@@ -14917,10 +14917,10 @@
         <v>711</v>
       </c>
       <c r="D533" t="s">
+        <v>712</v>
+      </c>
+      <c r="E533" t="s">
         <v>657</v>
-      </c>
-      <c r="E533" t="s">
-        <v>712</v>
       </c>
       <c r="F533" t="s">
         <v>713</v>
@@ -14937,10 +14937,10 @@
         <v>711</v>
       </c>
       <c r="D534" t="s">
+        <v>712</v>
+      </c>
+      <c r="E534" t="s">
         <v>657</v>
-      </c>
-      <c r="E534" t="s">
-        <v>712</v>
       </c>
       <c r="F534" t="s">
         <v>713</v>
@@ -14957,10 +14957,10 @@
         <v>711</v>
       </c>
       <c r="D535" t="s">
+        <v>712</v>
+      </c>
+      <c r="E535" t="s">
         <v>657</v>
-      </c>
-      <c r="E535" t="s">
-        <v>712</v>
       </c>
       <c r="F535" t="s">
         <v>713</v>
@@ -14977,10 +14977,10 @@
         <v>15</v>
       </c>
       <c r="D536" t="s">
+        <v>712</v>
+      </c>
+      <c r="E536" t="s">
         <v>727</v>
-      </c>
-      <c r="E536" t="s">
-        <v>712</v>
       </c>
       <c r="F536" t="s">
         <v>713</v>
@@ -14997,10 +14997,10 @@
         <v>15</v>
       </c>
       <c r="D537" t="s">
+        <v>712</v>
+      </c>
+      <c r="E537" t="s">
         <v>729</v>
-      </c>
-      <c r="E537" t="s">
-        <v>712</v>
       </c>
       <c r="F537" t="s">
         <v>713</v>
@@ -15017,10 +15017,10 @@
         <v>711</v>
       </c>
       <c r="D538" t="s">
+        <v>712</v>
+      </c>
+      <c r="E538" t="s">
         <v>657</v>
-      </c>
-      <c r="E538" t="s">
-        <v>712</v>
       </c>
       <c r="F538" t="s">
         <v>713</v>
@@ -15037,10 +15037,10 @@
         <v>711</v>
       </c>
       <c r="D539" t="s">
+        <v>712</v>
+      </c>
+      <c r="E539" t="s">
         <v>657</v>
-      </c>
-      <c r="E539" t="s">
-        <v>712</v>
       </c>
       <c r="F539" t="s">
         <v>713</v>
@@ -15057,13 +15057,13 @@
         <v>711</v>
       </c>
       <c r="D540" t="s">
+        <v>689</v>
+      </c>
+      <c r="E540" t="s">
         <v>657</v>
       </c>
-      <c r="E540" t="s">
-        <v>712</v>
-      </c>
       <c r="F540" t="s">
-        <v>690</v>
+        <v>713</v>
       </c>
     </row>
     <row r="541" spans="1:6">
@@ -15077,10 +15077,10 @@
         <v>711</v>
       </c>
       <c r="D541" t="s">
+        <v>712</v>
+      </c>
+      <c r="E541" t="s">
         <v>657</v>
-      </c>
-      <c r="E541" t="s">
-        <v>712</v>
       </c>
       <c r="F541" t="s">
         <v>713</v>
@@ -15097,10 +15097,10 @@
         <v>711</v>
       </c>
       <c r="D542" t="s">
+        <v>712</v>
+      </c>
+      <c r="E542" t="s">
         <v>657</v>
-      </c>
-      <c r="E542" t="s">
-        <v>712</v>
       </c>
       <c r="F542" t="s">
         <v>713</v>
@@ -15117,10 +15117,10 @@
         <v>711</v>
       </c>
       <c r="D543" t="s">
+        <v>712</v>
+      </c>
+      <c r="E543" t="s">
         <v>657</v>
-      </c>
-      <c r="E543" t="s">
-        <v>712</v>
       </c>
       <c r="F543" t="s">
         <v>713</v>
@@ -15137,10 +15137,10 @@
         <v>711</v>
       </c>
       <c r="D544" t="s">
+        <v>712</v>
+      </c>
+      <c r="E544" t="s">
         <v>657</v>
-      </c>
-      <c r="E544" t="s">
-        <v>712</v>
       </c>
       <c r="F544" t="s">
         <v>713</v>
@@ -15157,13 +15157,13 @@
         <v>13</v>
       </c>
       <c r="D545" t="s">
+        <v>738</v>
+      </c>
+      <c r="E545" t="s">
         <v>657</v>
       </c>
-      <c r="E545" t="s">
-        <v>712</v>
-      </c>
       <c r="F545" t="s">
-        <v>738</v>
+        <v>713</v>
       </c>
     </row>
     <row r="546" spans="1:6">
@@ -15177,10 +15177,10 @@
         <v>711</v>
       </c>
       <c r="D546" t="s">
+        <v>712</v>
+      </c>
+      <c r="E546" t="s">
         <v>657</v>
-      </c>
-      <c r="E546" t="s">
-        <v>712</v>
       </c>
       <c r="F546" t="s">
         <v>713</v>
@@ -15197,10 +15197,10 @@
         <v>15</v>
       </c>
       <c r="D547" t="s">
+        <v>712</v>
+      </c>
+      <c r="E547" t="s">
         <v>657</v>
-      </c>
-      <c r="E547" t="s">
-        <v>712</v>
       </c>
       <c r="F547" t="s">
         <v>713</v>
@@ -15237,10 +15237,10 @@
         <v>711</v>
       </c>
       <c r="D549" t="s">
+        <v>742</v>
+      </c>
+      <c r="E549" t="s">
         <v>746</v>
-      </c>
-      <c r="E549" t="s">
-        <v>743</v>
       </c>
       <c r="F549" t="s">
         <v>744</v>
@@ -15257,10 +15257,10 @@
         <v>711</v>
       </c>
       <c r="D550" t="s">
+        <v>742</v>
+      </c>
+      <c r="E550" t="s">
         <v>748</v>
-      </c>
-      <c r="E550" t="s">
-        <v>743</v>
       </c>
       <c r="F550" t="s">
         <v>744</v>
@@ -15337,13 +15337,13 @@
         <v>711</v>
       </c>
       <c r="D554" t="s">
-        <v>742</v>
+        <v>753</v>
       </c>
       <c r="E554" t="s">
         <v>743</v>
       </c>
       <c r="F554" t="s">
-        <v>753</v>
+        <v>744</v>
       </c>
     </row>
     <row r="555" spans="1:6">
@@ -15420,10 +15420,10 @@
         <v>758</v>
       </c>
       <c r="E558" t="s">
-        <v>743</v>
+        <v>759</v>
       </c>
       <c r="F558" t="s">
-        <v>759</v>
+        <v>744</v>
       </c>
     </row>
     <row r="559" spans="1:6">
@@ -15457,10 +15457,10 @@
         <v>711</v>
       </c>
       <c r="D560" t="s">
+        <v>742</v>
+      </c>
+      <c r="E560" t="s">
         <v>762</v>
-      </c>
-      <c r="E560" t="s">
-        <v>743</v>
       </c>
       <c r="F560" t="s">
         <v>744</v>
@@ -15477,10 +15477,10 @@
         <v>711</v>
       </c>
       <c r="D561" t="s">
+        <v>742</v>
+      </c>
+      <c r="E561" t="s">
         <v>762</v>
-      </c>
-      <c r="E561" t="s">
-        <v>743</v>
       </c>
       <c r="F561" t="s">
         <v>744</v>
@@ -15517,13 +15517,13 @@
         <v>15</v>
       </c>
       <c r="D563" t="s">
-        <v>742</v>
+        <v>766</v>
       </c>
       <c r="E563" t="s">
         <v>743</v>
       </c>
       <c r="F563" t="s">
-        <v>766</v>
+        <v>744</v>
       </c>
     </row>
     <row r="564" spans="1:6">
@@ -15640,10 +15640,10 @@
         <v>773</v>
       </c>
       <c r="E569" t="s">
-        <v>743</v>
+        <v>774</v>
       </c>
       <c r="F569" t="s">
-        <v>774</v>
+        <v>744</v>
       </c>
     </row>
     <row r="570" spans="1:6">
@@ -15717,13 +15717,13 @@
         <v>711</v>
       </c>
       <c r="D573" t="s">
+        <v>712</v>
+      </c>
+      <c r="E573" t="s">
         <v>779</v>
       </c>
-      <c r="E573" t="s">
+      <c r="F573" t="s">
         <v>780</v>
-      </c>
-      <c r="F573" t="s">
-        <v>713</v>
       </c>
     </row>
     <row r="574" spans="1:6">
@@ -15737,13 +15737,13 @@
         <v>711</v>
       </c>
       <c r="D574" t="s">
+        <v>782</v>
+      </c>
+      <c r="E574" t="s">
         <v>779</v>
       </c>
-      <c r="E574" t="s">
+      <c r="F574" t="s">
         <v>780</v>
-      </c>
-      <c r="F574" t="s">
-        <v>782</v>
       </c>
     </row>
     <row r="575" spans="1:6">
@@ -15757,13 +15757,13 @@
         <v>711</v>
       </c>
       <c r="D575" t="s">
+        <v>782</v>
+      </c>
+      <c r="E575" t="s">
         <v>779</v>
       </c>
-      <c r="E575" t="s">
+      <c r="F575" t="s">
         <v>780</v>
-      </c>
-      <c r="F575" t="s">
-        <v>782</v>
       </c>
     </row>
     <row r="576" spans="1:6">
@@ -15777,13 +15777,13 @@
         <v>711</v>
       </c>
       <c r="D576" t="s">
+        <v>782</v>
+      </c>
+      <c r="E576" t="s">
         <v>779</v>
       </c>
-      <c r="E576" t="s">
+      <c r="F576" t="s">
         <v>780</v>
-      </c>
-      <c r="F576" t="s">
-        <v>782</v>
       </c>
     </row>
     <row r="577" spans="1:6">
@@ -15797,13 +15797,13 @@
         <v>711</v>
       </c>
       <c r="D577" t="s">
+        <v>742</v>
+      </c>
+      <c r="E577" t="s">
         <v>779</v>
       </c>
-      <c r="E577" t="s">
+      <c r="F577" t="s">
         <v>780</v>
-      </c>
-      <c r="F577" t="s">
-        <v>744</v>
       </c>
     </row>
     <row r="578" spans="1:6">
@@ -15817,13 +15817,13 @@
         <v>711</v>
       </c>
       <c r="D578" t="s">
+        <v>782</v>
+      </c>
+      <c r="E578" t="s">
         <v>787</v>
       </c>
-      <c r="E578" t="s">
+      <c r="F578" t="s">
         <v>780</v>
-      </c>
-      <c r="F578" t="s">
-        <v>782</v>
       </c>
     </row>
     <row r="579" spans="1:6">
@@ -15840,10 +15840,10 @@
         <v>789</v>
       </c>
       <c r="E579" t="s">
+        <v>790</v>
+      </c>
+      <c r="F579" t="s">
         <v>780</v>
-      </c>
-      <c r="F579" t="s">
-        <v>790</v>
       </c>
     </row>
     <row r="580" spans="1:6">
@@ -15857,13 +15857,13 @@
         <v>711</v>
       </c>
       <c r="D580" t="s">
+        <v>782</v>
+      </c>
+      <c r="E580" t="s">
         <v>792</v>
       </c>
-      <c r="E580" t="s">
+      <c r="F580" t="s">
         <v>780</v>
-      </c>
-      <c r="F580" t="s">
-        <v>782</v>
       </c>
     </row>
     <row r="581" spans="1:6">
@@ -15877,13 +15877,13 @@
         <v>15</v>
       </c>
       <c r="D581" t="s">
+        <v>782</v>
+      </c>
+      <c r="E581" t="s">
         <v>794</v>
       </c>
-      <c r="E581" t="s">
+      <c r="F581" t="s">
         <v>780</v>
-      </c>
-      <c r="F581" t="s">
-        <v>782</v>
       </c>
     </row>
     <row r="582" spans="1:6">
@@ -15897,13 +15897,13 @@
         <v>15</v>
       </c>
       <c r="D582" t="s">
+        <v>782</v>
+      </c>
+      <c r="E582" t="s">
         <v>779</v>
       </c>
-      <c r="E582" t="s">
+      <c r="F582" t="s">
         <v>780</v>
-      </c>
-      <c r="F582" t="s">
-        <v>782</v>
       </c>
     </row>
     <row r="583" spans="1:6">
@@ -15920,10 +15920,10 @@
         <v>797</v>
       </c>
       <c r="E583" t="s">
+        <v>798</v>
+      </c>
+      <c r="F583" t="s">
         <v>780</v>
-      </c>
-      <c r="F583" t="s">
-        <v>798</v>
       </c>
     </row>
     <row r="584" spans="1:6">
@@ -15940,10 +15940,10 @@
         <v>800</v>
       </c>
       <c r="E584" t="s">
+        <v>801</v>
+      </c>
+      <c r="F584" t="s">
         <v>780</v>
-      </c>
-      <c r="F584" t="s">
-        <v>801</v>
       </c>
     </row>
     <row r="585" spans="1:6">
@@ -15957,13 +15957,13 @@
         <v>711</v>
       </c>
       <c r="D585" t="s">
+        <v>782</v>
+      </c>
+      <c r="E585" t="s">
         <v>779</v>
       </c>
-      <c r="E585" t="s">
+      <c r="F585" t="s">
         <v>780</v>
-      </c>
-      <c r="F585" t="s">
-        <v>782</v>
       </c>
     </row>
     <row r="586" spans="1:6">
@@ -15980,10 +15980,10 @@
         <v>804</v>
       </c>
       <c r="E586" t="s">
+        <v>805</v>
+      </c>
+      <c r="F586" t="s">
         <v>780</v>
-      </c>
-      <c r="F586" t="s">
-        <v>805</v>
       </c>
     </row>
     <row r="587" spans="1:6">
@@ -15997,13 +15997,13 @@
         <v>13</v>
       </c>
       <c r="D587" t="s">
+        <v>782</v>
+      </c>
+      <c r="E587" t="s">
         <v>807</v>
       </c>
-      <c r="E587" t="s">
+      <c r="F587" t="s">
         <v>780</v>
-      </c>
-      <c r="F587" t="s">
-        <v>782</v>
       </c>
     </row>
     <row r="588" spans="1:6">
@@ -16017,13 +16017,13 @@
         <v>711</v>
       </c>
       <c r="D588" t="s">
+        <v>782</v>
+      </c>
+      <c r="E588" t="s">
         <v>809</v>
       </c>
-      <c r="E588" t="s">
+      <c r="F588" t="s">
         <v>780</v>
-      </c>
-      <c r="F588" t="s">
-        <v>782</v>
       </c>
     </row>
     <row r="589" spans="1:6">
@@ -16037,13 +16037,13 @@
         <v>711</v>
       </c>
       <c r="D589" t="s">
+        <v>782</v>
+      </c>
+      <c r="E589" t="s">
         <v>779</v>
       </c>
-      <c r="E589" t="s">
+      <c r="F589" t="s">
         <v>780</v>
-      </c>
-      <c r="F589" t="s">
-        <v>782</v>
       </c>
     </row>
     <row r="590" spans="1:6">
@@ -16057,13 +16057,13 @@
         <v>24</v>
       </c>
       <c r="D590" t="s">
+        <v>782</v>
+      </c>
+      <c r="E590" t="s">
         <v>779</v>
       </c>
-      <c r="E590" t="s">
+      <c r="F590" t="s">
         <v>780</v>
-      </c>
-      <c r="F590" t="s">
-        <v>782</v>
       </c>
     </row>
     <row r="591" spans="1:6">
@@ -16077,13 +16077,13 @@
         <v>15</v>
       </c>
       <c r="D591" t="s">
+        <v>782</v>
+      </c>
+      <c r="E591" t="s">
         <v>779</v>
       </c>
-      <c r="E591" t="s">
+      <c r="F591" t="s">
         <v>780</v>
-      </c>
-      <c r="F591" t="s">
-        <v>782</v>
       </c>
     </row>
     <row r="592" spans="1:6">
@@ -16097,13 +16097,13 @@
         <v>711</v>
       </c>
       <c r="D592" t="s">
+        <v>814</v>
+      </c>
+      <c r="E592" t="s">
         <v>779</v>
       </c>
-      <c r="E592" t="s">
+      <c r="F592" t="s">
         <v>780</v>
-      </c>
-      <c r="F592" t="s">
-        <v>814</v>
       </c>
     </row>
     <row r="593" spans="1:6">
@@ -16117,13 +16117,13 @@
         <v>13</v>
       </c>
       <c r="D593" t="s">
+        <v>782</v>
+      </c>
+      <c r="E593" t="s">
         <v>779</v>
       </c>
-      <c r="E593" t="s">
+      <c r="F593" t="s">
         <v>780</v>
-      </c>
-      <c r="F593" t="s">
-        <v>782</v>
       </c>
     </row>
     <row r="594" spans="1:6">
@@ -16137,13 +16137,13 @@
         <v>711</v>
       </c>
       <c r="D594" t="s">
+        <v>782</v>
+      </c>
+      <c r="E594" t="s">
         <v>779</v>
       </c>
-      <c r="E594" t="s">
+      <c r="F594" t="s">
         <v>780</v>
-      </c>
-      <c r="F594" t="s">
-        <v>782</v>
       </c>
     </row>
     <row r="595" spans="1:6">
@@ -16157,13 +16157,13 @@
         <v>711</v>
       </c>
       <c r="D595" t="s">
+        <v>782</v>
+      </c>
+      <c r="E595" t="s">
         <v>779</v>
       </c>
-      <c r="E595" t="s">
+      <c r="F595" t="s">
         <v>780</v>
-      </c>
-      <c r="F595" t="s">
-        <v>782</v>
       </c>
     </row>
     <row r="596" spans="1:6">
@@ -16177,13 +16177,13 @@
         <v>711</v>
       </c>
       <c r="D596" t="s">
+        <v>782</v>
+      </c>
+      <c r="E596" t="s">
         <v>779</v>
       </c>
-      <c r="E596" t="s">
+      <c r="F596" t="s">
         <v>780</v>
-      </c>
-      <c r="F596" t="s">
-        <v>782</v>
       </c>
     </row>
     <row r="597" spans="1:6">
@@ -16220,10 +16220,10 @@
         <v>824</v>
       </c>
       <c r="E598" t="s">
-        <v>821</v>
+        <v>825</v>
       </c>
       <c r="F598" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
     </row>
     <row r="599" spans="1:6">
@@ -16300,10 +16300,10 @@
         <v>830</v>
       </c>
       <c r="E602" t="s">
-        <v>821</v>
+        <v>831</v>
       </c>
       <c r="F602" t="s">
-        <v>831</v>
+        <v>822</v>
       </c>
     </row>
     <row r="603" spans="1:6">
@@ -16320,10 +16320,10 @@
         <v>833</v>
       </c>
       <c r="E603" t="s">
-        <v>821</v>
+        <v>834</v>
       </c>
       <c r="F603" t="s">
-        <v>834</v>
+        <v>822</v>
       </c>
     </row>
     <row r="604" spans="1:6">
@@ -16340,10 +16340,10 @@
         <v>836</v>
       </c>
       <c r="E604" t="s">
-        <v>821</v>
+        <v>837</v>
       </c>
       <c r="F604" t="s">
-        <v>837</v>
+        <v>822</v>
       </c>
     </row>
     <row r="605" spans="1:6">
@@ -16357,10 +16357,10 @@
         <v>24</v>
       </c>
       <c r="D605" t="s">
+        <v>820</v>
+      </c>
+      <c r="E605" t="s">
         <v>839</v>
-      </c>
-      <c r="E605" t="s">
-        <v>821</v>
       </c>
       <c r="F605" t="s">
         <v>822</v>
@@ -16420,10 +16420,10 @@
         <v>843</v>
       </c>
       <c r="E608" t="s">
-        <v>821</v>
+        <v>844</v>
       </c>
       <c r="F608" t="s">
-        <v>844</v>
+        <v>822</v>
       </c>
     </row>
     <row r="609" spans="1:6">
@@ -16437,13 +16437,13 @@
         <v>711</v>
       </c>
       <c r="D609" t="s">
+        <v>807</v>
+      </c>
+      <c r="E609" t="s">
         <v>846</v>
       </c>
-      <c r="E609" t="s">
-        <v>821</v>
-      </c>
       <c r="F609" t="s">
-        <v>807</v>
+        <v>822</v>
       </c>
     </row>
     <row r="610" spans="1:6">
@@ -16477,13 +16477,13 @@
         <v>24</v>
       </c>
       <c r="D611" t="s">
-        <v>824</v>
+        <v>849</v>
       </c>
       <c r="E611" t="s">
-        <v>821</v>
+        <v>825</v>
       </c>
       <c r="F611" t="s">
-        <v>849</v>
+        <v>822</v>
       </c>
     </row>
     <row r="612" spans="1:6">
@@ -16497,10 +16497,10 @@
         <v>15</v>
       </c>
       <c r="D612" t="s">
+        <v>820</v>
+      </c>
+      <c r="E612" t="s">
         <v>851</v>
-      </c>
-      <c r="E612" t="s">
-        <v>821</v>
       </c>
       <c r="F612" t="s">
         <v>822</v>
@@ -16537,10 +16537,10 @@
         <v>711</v>
       </c>
       <c r="D614" t="s">
+        <v>820</v>
+      </c>
+      <c r="E614" t="s">
         <v>854</v>
-      </c>
-      <c r="E614" t="s">
-        <v>821</v>
       </c>
       <c r="F614" t="s">
         <v>822</v>
@@ -16740,10 +16740,10 @@
         <v>868</v>
       </c>
       <c r="E624" t="s">
-        <v>865</v>
+        <v>869</v>
       </c>
       <c r="F624" t="s">
-        <v>869</v>
+        <v>866</v>
       </c>
     </row>
     <row r="625" spans="1:6">
@@ -16817,13 +16817,13 @@
         <v>711</v>
       </c>
       <c r="D628" t="s">
-        <v>864</v>
+        <v>874</v>
       </c>
       <c r="E628" t="s">
         <v>865</v>
       </c>
       <c r="F628" t="s">
-        <v>874</v>
+        <v>866</v>
       </c>
     </row>
     <row r="629" spans="1:6">
@@ -16837,10 +16837,10 @@
         <v>24</v>
       </c>
       <c r="D629" t="s">
+        <v>864</v>
+      </c>
+      <c r="E629" t="s">
         <v>876</v>
-      </c>
-      <c r="E629" t="s">
-        <v>865</v>
       </c>
       <c r="F629" t="s">
         <v>866</v>
@@ -16897,13 +16897,13 @@
         <v>24</v>
       </c>
       <c r="D632" t="s">
+        <v>880</v>
+      </c>
+      <c r="E632" t="s">
         <v>876</v>
       </c>
-      <c r="E632" t="s">
-        <v>865</v>
-      </c>
       <c r="F632" t="s">
-        <v>880</v>
+        <v>866</v>
       </c>
     </row>
     <row r="633" spans="1:6">
@@ -16920,10 +16920,10 @@
         <v>882</v>
       </c>
       <c r="E633" t="s">
-        <v>865</v>
+        <v>883</v>
       </c>
       <c r="F633" t="s">
-        <v>883</v>
+        <v>866</v>
       </c>
     </row>
     <row r="634" spans="1:6">
@@ -16940,10 +16940,10 @@
         <v>885</v>
       </c>
       <c r="E634" t="s">
-        <v>865</v>
+        <v>886</v>
       </c>
       <c r="F634" t="s">
-        <v>886</v>
+        <v>866</v>
       </c>
     </row>
     <row r="635" spans="1:6">
@@ -16977,10 +16977,10 @@
         <v>711</v>
       </c>
       <c r="D636" t="s">
+        <v>864</v>
+      </c>
+      <c r="E636" t="s">
         <v>889</v>
-      </c>
-      <c r="E636" t="s">
-        <v>865</v>
       </c>
       <c r="F636" t="s">
         <v>866</v>
@@ -17000,10 +17000,10 @@
         <v>891</v>
       </c>
       <c r="E637" t="s">
-        <v>865</v>
+        <v>892</v>
       </c>
       <c r="F637" t="s">
-        <v>892</v>
+        <v>866</v>
       </c>
     </row>
     <row r="638" spans="1:6">
@@ -17080,10 +17080,10 @@
         <v>897</v>
       </c>
       <c r="E641" t="s">
-        <v>865</v>
+        <v>898</v>
       </c>
       <c r="F641" t="s">
-        <v>898</v>
+        <v>866</v>
       </c>
     </row>
     <row r="642" spans="1:6">
@@ -17097,10 +17097,10 @@
         <v>15</v>
       </c>
       <c r="D642" t="s">
+        <v>864</v>
+      </c>
+      <c r="E642" t="s">
         <v>900</v>
-      </c>
-      <c r="E642" t="s">
-        <v>865</v>
       </c>
       <c r="F642" t="s">
         <v>866</v>
@@ -17117,10 +17117,10 @@
         <v>15</v>
       </c>
       <c r="D643" t="s">
+        <v>864</v>
+      </c>
+      <c r="E643" t="s">
         <v>902</v>
-      </c>
-      <c r="E643" t="s">
-        <v>865</v>
       </c>
       <c r="F643" t="s">
         <v>866</v>
@@ -17177,10 +17177,10 @@
         <v>24</v>
       </c>
       <c r="D646" t="s">
+        <v>864</v>
+      </c>
+      <c r="E646" t="s">
         <v>906</v>
-      </c>
-      <c r="E646" t="s">
-        <v>865</v>
       </c>
       <c r="F646" t="s">
         <v>866</v>
@@ -17260,10 +17260,10 @@
         <v>914</v>
       </c>
       <c r="E650" t="s">
-        <v>911</v>
+        <v>915</v>
       </c>
       <c r="F650" t="s">
-        <v>915</v>
+        <v>912</v>
       </c>
     </row>
     <row r="651" spans="1:6">
@@ -17277,13 +17277,13 @@
         <v>24</v>
       </c>
       <c r="D651" t="s">
-        <v>910</v>
+        <v>917</v>
       </c>
       <c r="E651" t="s">
         <v>911</v>
       </c>
       <c r="F651" t="s">
-        <v>917</v>
+        <v>912</v>
       </c>
     </row>
     <row r="652" spans="1:6">
@@ -17300,10 +17300,10 @@
         <v>919</v>
       </c>
       <c r="E652" t="s">
-        <v>911</v>
+        <v>920</v>
       </c>
       <c r="F652" t="s">
-        <v>920</v>
+        <v>912</v>
       </c>
     </row>
     <row r="653" spans="1:6">
@@ -17320,10 +17320,10 @@
         <v>919</v>
       </c>
       <c r="E653" t="s">
-        <v>911</v>
+        <v>920</v>
       </c>
       <c r="F653" t="s">
-        <v>920</v>
+        <v>912</v>
       </c>
     </row>
     <row r="654" spans="1:6">
@@ -17337,13 +17337,13 @@
         <v>15</v>
       </c>
       <c r="D654" t="s">
+        <v>864</v>
+      </c>
+      <c r="E654" t="s">
         <v>902</v>
       </c>
-      <c r="E654" t="s">
-        <v>911</v>
-      </c>
       <c r="F654" t="s">
-        <v>866</v>
+        <v>912</v>
       </c>
     </row>
     <row r="655" spans="1:6">
@@ -17360,10 +17360,10 @@
         <v>919</v>
       </c>
       <c r="E655" t="s">
-        <v>911</v>
+        <v>920</v>
       </c>
       <c r="F655" t="s">
-        <v>920</v>
+        <v>912</v>
       </c>
     </row>
     <row r="656" spans="1:6">
@@ -17380,10 +17380,10 @@
         <v>919</v>
       </c>
       <c r="E656" t="s">
-        <v>911</v>
+        <v>920</v>
       </c>
       <c r="F656" t="s">
-        <v>920</v>
+        <v>912</v>
       </c>
     </row>
     <row r="657" spans="1:6">
@@ -17400,10 +17400,10 @@
         <v>926</v>
       </c>
       <c r="E657" t="s">
-        <v>911</v>
+        <v>927</v>
       </c>
       <c r="F657" t="s">
-        <v>927</v>
+        <v>912</v>
       </c>
     </row>
     <row r="658" spans="1:6">
@@ -17420,10 +17420,10 @@
         <v>929</v>
       </c>
       <c r="E658" t="s">
-        <v>911</v>
+        <v>930</v>
       </c>
       <c r="F658" t="s">
-        <v>930</v>
+        <v>912</v>
       </c>
     </row>
     <row r="659" spans="1:6">
@@ -17437,13 +17437,13 @@
         <v>24</v>
       </c>
       <c r="D659" t="s">
+        <v>932</v>
+      </c>
+      <c r="E659" t="s">
         <v>889</v>
       </c>
-      <c r="E659" t="s">
-        <v>911</v>
-      </c>
       <c r="F659" t="s">
-        <v>932</v>
+        <v>912</v>
       </c>
     </row>
     <row r="660" spans="1:6">
@@ -17460,10 +17460,10 @@
         <v>934</v>
       </c>
       <c r="E660" t="s">
-        <v>911</v>
+        <v>935</v>
       </c>
       <c r="F660" t="s">
-        <v>935</v>
+        <v>912</v>
       </c>
     </row>
     <row r="661" spans="1:6">
@@ -17480,10 +17480,10 @@
         <v>919</v>
       </c>
       <c r="E661" t="s">
-        <v>911</v>
+        <v>920</v>
       </c>
       <c r="F661" t="s">
-        <v>920</v>
+        <v>912</v>
       </c>
     </row>
     <row r="662" spans="1:6">
@@ -17497,13 +17497,13 @@
         <v>24</v>
       </c>
       <c r="D662" t="s">
-        <v>919</v>
+        <v>915</v>
       </c>
       <c r="E662" t="s">
-        <v>911</v>
+        <v>920</v>
       </c>
       <c r="F662" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
     </row>
     <row r="663" spans="1:6">
@@ -17520,10 +17520,10 @@
         <v>939</v>
       </c>
       <c r="E663" t="s">
-        <v>911</v>
+        <v>940</v>
       </c>
       <c r="F663" t="s">
-        <v>940</v>
+        <v>912</v>
       </c>
     </row>
     <row r="664" spans="1:6">
@@ -17537,13 +17537,13 @@
         <v>15</v>
       </c>
       <c r="D664" t="s">
+        <v>942</v>
+      </c>
+      <c r="E664" t="s">
         <v>902</v>
       </c>
-      <c r="E664" t="s">
-        <v>911</v>
-      </c>
       <c r="F664" t="s">
-        <v>942</v>
+        <v>912</v>
       </c>
     </row>
     <row r="665" spans="1:6">
@@ -17557,13 +17557,13 @@
         <v>711</v>
       </c>
       <c r="D665" t="s">
+        <v>919</v>
+      </c>
+      <c r="E665" t="s">
         <v>944</v>
       </c>
-      <c r="E665" t="s">
-        <v>911</v>
-      </c>
       <c r="F665" t="s">
-        <v>920</v>
+        <v>912</v>
       </c>
     </row>
     <row r="666" spans="1:6">
@@ -17577,10 +17577,10 @@
         <v>24</v>
       </c>
       <c r="D666" t="s">
+        <v>910</v>
+      </c>
+      <c r="E666" t="s">
         <v>944</v>
-      </c>
-      <c r="E666" t="s">
-        <v>911</v>
       </c>
       <c r="F666" t="s">
         <v>912</v>
@@ -17600,10 +17600,10 @@
         <v>947</v>
       </c>
       <c r="E667" t="s">
-        <v>911</v>
+        <v>948</v>
       </c>
       <c r="F667" t="s">
-        <v>948</v>
+        <v>912</v>
       </c>
     </row>
     <row r="668" spans="1:6">
@@ -17620,10 +17620,10 @@
         <v>919</v>
       </c>
       <c r="E668" t="s">
-        <v>911</v>
+        <v>920</v>
       </c>
       <c r="F668" t="s">
-        <v>920</v>
+        <v>912</v>
       </c>
     </row>
     <row r="669" spans="1:6">
@@ -17637,13 +17637,13 @@
         <v>15</v>
       </c>
       <c r="D669" t="s">
+        <v>932</v>
+      </c>
+      <c r="E669" t="s">
         <v>902</v>
       </c>
-      <c r="E669" t="s">
-        <v>911</v>
-      </c>
       <c r="F669" t="s">
-        <v>932</v>
+        <v>912</v>
       </c>
     </row>
     <row r="670" spans="1:6">
@@ -17660,10 +17660,10 @@
         <v>919</v>
       </c>
       <c r="E670" t="s">
-        <v>911</v>
+        <v>920</v>
       </c>
       <c r="F670" t="s">
-        <v>920</v>
+        <v>912</v>
       </c>
     </row>
     <row r="671" spans="1:6">
@@ -17677,13 +17677,13 @@
         <v>24</v>
       </c>
       <c r="D671" t="s">
-        <v>910</v>
+        <v>953</v>
       </c>
       <c r="E671" t="s">
         <v>911</v>
       </c>
       <c r="F671" t="s">
-        <v>953</v>
+        <v>912</v>
       </c>
     </row>
     <row r="672" spans="1:6">
@@ -17700,10 +17700,10 @@
         <v>919</v>
       </c>
       <c r="E672" t="s">
-        <v>911</v>
+        <v>920</v>
       </c>
       <c r="F672" t="s">
-        <v>920</v>
+        <v>912</v>
       </c>
     </row>
     <row r="673" spans="1:6">
@@ -17720,10 +17720,10 @@
         <v>919</v>
       </c>
       <c r="E673" t="s">
-        <v>911</v>
+        <v>920</v>
       </c>
       <c r="F673" t="s">
-        <v>920</v>
+        <v>912</v>
       </c>
     </row>
     <row r="674" spans="1:6">
@@ -17737,13 +17737,13 @@
         <v>15</v>
       </c>
       <c r="D674" t="s">
+        <v>934</v>
+      </c>
+      <c r="E674" t="s">
         <v>902</v>
       </c>
-      <c r="E674" t="s">
-        <v>911</v>
-      </c>
       <c r="F674" t="s">
-        <v>935</v>
+        <v>912</v>
       </c>
     </row>
     <row r="675" spans="1:6">
@@ -17757,13 +17757,13 @@
         <v>24</v>
       </c>
       <c r="D675" t="s">
-        <v>910</v>
+        <v>917</v>
       </c>
       <c r="E675" t="s">
         <v>911</v>
       </c>
       <c r="F675" t="s">
-        <v>917</v>
+        <v>912</v>
       </c>
     </row>
     <row r="676" spans="1:6">
@@ -17777,13 +17777,13 @@
         <v>15</v>
       </c>
       <c r="D676" t="s">
+        <v>919</v>
+      </c>
+      <c r="E676" t="s">
         <v>959</v>
       </c>
-      <c r="E676" t="s">
-        <v>911</v>
-      </c>
       <c r="F676" t="s">
-        <v>920</v>
+        <v>912</v>
       </c>
     </row>
     <row r="677" spans="1:6">
@@ -17800,10 +17800,10 @@
         <v>919</v>
       </c>
       <c r="E677" t="s">
-        <v>911</v>
+        <v>920</v>
       </c>
       <c r="F677" t="s">
-        <v>920</v>
+        <v>912</v>
       </c>
     </row>
     <row r="678" spans="1:6">
@@ -17820,10 +17820,10 @@
         <v>919</v>
       </c>
       <c r="E678" t="s">
-        <v>911</v>
+        <v>920</v>
       </c>
       <c r="F678" t="s">
-        <v>920</v>
+        <v>912</v>
       </c>
     </row>
     <row r="679" spans="1:6">
@@ -17840,10 +17840,10 @@
         <v>934</v>
       </c>
       <c r="E679" t="s">
-        <v>911</v>
+        <v>935</v>
       </c>
       <c r="F679" t="s">
-        <v>935</v>
+        <v>912</v>
       </c>
     </row>
     <row r="680" spans="1:6">
@@ -17860,10 +17860,10 @@
         <v>919</v>
       </c>
       <c r="E680" t="s">
-        <v>911</v>
+        <v>920</v>
       </c>
       <c r="F680" t="s">
-        <v>920</v>
+        <v>912</v>
       </c>
     </row>
     <row r="681" spans="1:6">
@@ -17880,10 +17880,10 @@
         <v>919</v>
       </c>
       <c r="E681" t="s">
-        <v>911</v>
+        <v>920</v>
       </c>
       <c r="F681" t="s">
-        <v>920</v>
+        <v>912</v>
       </c>
     </row>
     <row r="682" spans="1:6">
@@ -17920,10 +17920,10 @@
         <v>970</v>
       </c>
       <c r="E683" t="s">
-        <v>967</v>
+        <v>971</v>
       </c>
       <c r="F683" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
     </row>
     <row r="684" spans="1:6">
@@ -17940,10 +17940,10 @@
         <v>973</v>
       </c>
       <c r="E684" t="s">
-        <v>967</v>
+        <v>974</v>
       </c>
       <c r="F684" t="s">
-        <v>974</v>
+        <v>968</v>
       </c>
     </row>
     <row r="685" spans="1:6">
@@ -17960,10 +17960,10 @@
         <v>973</v>
       </c>
       <c r="E685" t="s">
-        <v>967</v>
+        <v>974</v>
       </c>
       <c r="F685" t="s">
-        <v>974</v>
+        <v>968</v>
       </c>
     </row>
     <row r="686" spans="1:6">
@@ -17980,10 +17980,10 @@
         <v>973</v>
       </c>
       <c r="E686" t="s">
-        <v>967</v>
+        <v>974</v>
       </c>
       <c r="F686" t="s">
-        <v>974</v>
+        <v>968</v>
       </c>
     </row>
     <row r="687" spans="1:6">
@@ -18000,10 +18000,10 @@
         <v>973</v>
       </c>
       <c r="E687" t="s">
-        <v>967</v>
+        <v>974</v>
       </c>
       <c r="F687" t="s">
-        <v>974</v>
+        <v>968</v>
       </c>
     </row>
     <row r="688" spans="1:6">
@@ -18020,10 +18020,10 @@
         <v>973</v>
       </c>
       <c r="E688" t="s">
-        <v>967</v>
+        <v>974</v>
       </c>
       <c r="F688" t="s">
-        <v>974</v>
+        <v>968</v>
       </c>
     </row>
     <row r="689" spans="1:6">
@@ -18037,13 +18037,13 @@
         <v>24</v>
       </c>
       <c r="D689" t="s">
-        <v>970</v>
+        <v>980</v>
       </c>
       <c r="E689" t="s">
-        <v>967</v>
+        <v>971</v>
       </c>
       <c r="F689" t="s">
-        <v>980</v>
+        <v>968</v>
       </c>
     </row>
     <row r="690" spans="1:6">
@@ -18060,10 +18060,10 @@
         <v>982</v>
       </c>
       <c r="E690" t="s">
-        <v>967</v>
+        <v>983</v>
       </c>
       <c r="F690" t="s">
-        <v>983</v>
+        <v>968</v>
       </c>
     </row>
     <row r="691" spans="1:6">
@@ -18080,10 +18080,10 @@
         <v>973</v>
       </c>
       <c r="E691" t="s">
-        <v>967</v>
+        <v>974</v>
       </c>
       <c r="F691" t="s">
-        <v>974</v>
+        <v>968</v>
       </c>
     </row>
     <row r="692" spans="1:6">
@@ -18097,13 +18097,13 @@
         <v>15</v>
       </c>
       <c r="D692" t="s">
+        <v>919</v>
+      </c>
+      <c r="E692" t="s">
         <v>986</v>
       </c>
-      <c r="E692" t="s">
-        <v>967</v>
-      </c>
       <c r="F692" t="s">
-        <v>920</v>
+        <v>968</v>
       </c>
     </row>
     <row r="693" spans="1:6">
@@ -18120,10 +18120,10 @@
         <v>988</v>
       </c>
       <c r="E693" t="s">
-        <v>967</v>
+        <v>989</v>
       </c>
       <c r="F693" t="s">
-        <v>989</v>
+        <v>968</v>
       </c>
     </row>
     <row r="694" spans="1:6">
@@ -18140,10 +18140,10 @@
         <v>991</v>
       </c>
       <c r="E694" t="s">
-        <v>967</v>
+        <v>992</v>
       </c>
       <c r="F694" t="s">
-        <v>992</v>
+        <v>968</v>
       </c>
     </row>
     <row r="695" spans="1:6">
@@ -18160,10 +18160,10 @@
         <v>994</v>
       </c>
       <c r="E695" t="s">
-        <v>967</v>
+        <v>995</v>
       </c>
       <c r="F695" t="s">
-        <v>995</v>
+        <v>968</v>
       </c>
     </row>
     <row r="696" spans="1:6">
@@ -18180,10 +18180,10 @@
         <v>973</v>
       </c>
       <c r="E696" t="s">
-        <v>967</v>
+        <v>974</v>
       </c>
       <c r="F696" t="s">
-        <v>974</v>
+        <v>968</v>
       </c>
     </row>
     <row r="697" spans="1:6">
@@ -18200,10 +18200,10 @@
         <v>998</v>
       </c>
       <c r="E697" t="s">
-        <v>967</v>
+        <v>999</v>
       </c>
       <c r="F697" t="s">
-        <v>999</v>
+        <v>968</v>
       </c>
     </row>
     <row r="698" spans="1:6">
@@ -18220,10 +18220,10 @@
         <v>1001</v>
       </c>
       <c r="E698" t="s">
-        <v>967</v>
+        <v>1002</v>
       </c>
       <c r="F698" t="s">
-        <v>1002</v>
+        <v>968</v>
       </c>
     </row>
     <row r="699" spans="1:6">
@@ -18240,10 +18240,10 @@
         <v>973</v>
       </c>
       <c r="E699" t="s">
-        <v>967</v>
+        <v>974</v>
       </c>
       <c r="F699" t="s">
-        <v>974</v>
+        <v>968</v>
       </c>
     </row>
     <row r="700" spans="1:6">
@@ -18260,10 +18260,10 @@
         <v>1005</v>
       </c>
       <c r="E700" t="s">
-        <v>967</v>
+        <v>1006</v>
       </c>
       <c r="F700" t="s">
-        <v>1006</v>
+        <v>968</v>
       </c>
     </row>
     <row r="701" spans="1:6">
@@ -18280,10 +18280,10 @@
         <v>973</v>
       </c>
       <c r="E701" t="s">
-        <v>967</v>
+        <v>974</v>
       </c>
       <c r="F701" t="s">
-        <v>974</v>
+        <v>968</v>
       </c>
     </row>
     <row r="702" spans="1:6">
@@ -18300,10 +18300,10 @@
         <v>1009</v>
       </c>
       <c r="E702" t="s">
-        <v>967</v>
+        <v>1010</v>
       </c>
       <c r="F702" t="s">
-        <v>1010</v>
+        <v>968</v>
       </c>
     </row>
     <row r="703" spans="1:6">
@@ -18317,13 +18317,13 @@
         <v>24</v>
       </c>
       <c r="D703" t="s">
+        <v>1005</v>
+      </c>
+      <c r="E703" t="s">
         <v>1012</v>
       </c>
-      <c r="E703" t="s">
-        <v>967</v>
-      </c>
       <c r="F703" t="s">
-        <v>1006</v>
+        <v>968</v>
       </c>
     </row>
     <row r="704" spans="1:6">
@@ -18340,10 +18340,10 @@
         <v>973</v>
       </c>
       <c r="E704" t="s">
-        <v>967</v>
+        <v>974</v>
       </c>
       <c r="F704" t="s">
-        <v>974</v>
+        <v>968</v>
       </c>
     </row>
     <row r="705" spans="1:6">
@@ -18357,13 +18357,13 @@
         <v>15</v>
       </c>
       <c r="D705" t="s">
+        <v>1001</v>
+      </c>
+      <c r="E705" t="s">
         <v>1015</v>
       </c>
-      <c r="E705" t="s">
-        <v>967</v>
-      </c>
       <c r="F705" t="s">
-        <v>1002</v>
+        <v>968</v>
       </c>
     </row>
     <row r="706" spans="1:6">
@@ -18380,10 +18380,10 @@
         <v>973</v>
       </c>
       <c r="E706" t="s">
-        <v>967</v>
+        <v>974</v>
       </c>
       <c r="F706" t="s">
-        <v>974</v>
+        <v>968</v>
       </c>
     </row>
     <row r="707" spans="1:6">
@@ -18397,13 +18397,13 @@
         <v>15</v>
       </c>
       <c r="D707" t="s">
-        <v>973</v>
+        <v>1001</v>
       </c>
       <c r="E707" t="s">
-        <v>967</v>
+        <v>974</v>
       </c>
       <c r="F707" t="s">
-        <v>1002</v>
+        <v>968</v>
       </c>
     </row>
     <row r="708" spans="1:6">
@@ -18417,13 +18417,13 @@
         <v>24</v>
       </c>
       <c r="D708" t="s">
+        <v>970</v>
+      </c>
+      <c r="E708" t="s">
         <v>1019</v>
       </c>
-      <c r="E708" t="s">
-        <v>967</v>
-      </c>
       <c r="F708" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
     </row>
     <row r="709" spans="1:6">
@@ -18440,10 +18440,10 @@
         <v>973</v>
       </c>
       <c r="E709" t="s">
-        <v>967</v>
+        <v>974</v>
       </c>
       <c r="F709" t="s">
-        <v>974</v>
+        <v>968</v>
       </c>
     </row>
     <row r="710" spans="1:6">
@@ -18460,10 +18460,10 @@
         <v>1022</v>
       </c>
       <c r="E710" t="s">
-        <v>967</v>
+        <v>1023</v>
       </c>
       <c r="F710" t="s">
-        <v>1023</v>
+        <v>968</v>
       </c>
     </row>
     <row r="711" spans="1:6">
@@ -18477,13 +18477,13 @@
         <v>711</v>
       </c>
       <c r="D711" t="s">
-        <v>973</v>
+        <v>1001</v>
       </c>
       <c r="E711" t="s">
-        <v>967</v>
+        <v>974</v>
       </c>
       <c r="F711" t="s">
-        <v>1002</v>
+        <v>968</v>
       </c>
     </row>
     <row r="712" spans="1:6">
@@ -18500,10 +18500,10 @@
         <v>973</v>
       </c>
       <c r="E712" t="s">
-        <v>967</v>
+        <v>974</v>
       </c>
       <c r="F712" t="s">
-        <v>974</v>
+        <v>968</v>
       </c>
     </row>
     <row r="713" spans="1:6">
@@ -18520,10 +18520,10 @@
         <v>982</v>
       </c>
       <c r="E713" t="s">
-        <v>967</v>
+        <v>983</v>
       </c>
       <c r="F713" t="s">
-        <v>983</v>
+        <v>968</v>
       </c>
     </row>
     <row r="714" spans="1:6">
@@ -18540,10 +18540,10 @@
         <v>973</v>
       </c>
       <c r="E714" t="s">
-        <v>967</v>
+        <v>974</v>
       </c>
       <c r="F714" t="s">
-        <v>974</v>
+        <v>968</v>
       </c>
     </row>
     <row r="715" spans="1:6">
@@ -18557,13 +18557,13 @@
         <v>24</v>
       </c>
       <c r="D715" t="s">
-        <v>998</v>
+        <v>1001</v>
       </c>
       <c r="E715" t="s">
-        <v>967</v>
+        <v>999</v>
       </c>
       <c r="F715" t="s">
-        <v>1002</v>
+        <v>968</v>
       </c>
     </row>
     <row r="716" spans="1:6">
@@ -18580,10 +18580,10 @@
         <v>973</v>
       </c>
       <c r="E716" t="s">
-        <v>967</v>
+        <v>974</v>
       </c>
       <c r="F716" t="s">
-        <v>974</v>
+        <v>968</v>
       </c>
     </row>
     <row r="717" spans="1:6">
@@ -18600,10 +18600,10 @@
         <v>973</v>
       </c>
       <c r="E717" t="s">
-        <v>967</v>
+        <v>974</v>
       </c>
       <c r="F717" t="s">
-        <v>974</v>
+        <v>968</v>
       </c>
     </row>
     <row r="718" spans="1:6">
@@ -18637,10 +18637,10 @@
         <v>711</v>
       </c>
       <c r="D719" t="s">
+        <v>1032</v>
+      </c>
+      <c r="E719" t="s">
         <v>1036</v>
-      </c>
-      <c r="E719" t="s">
-        <v>1033</v>
       </c>
       <c r="F719" t="s">
         <v>1034</v>
@@ -18657,10 +18657,10 @@
         <v>711</v>
       </c>
       <c r="D720" t="s">
+        <v>1032</v>
+      </c>
+      <c r="E720" t="s">
         <v>1036</v>
-      </c>
-      <c r="E720" t="s">
-        <v>1033</v>
       </c>
       <c r="F720" t="s">
         <v>1034</v>
@@ -18677,10 +18677,10 @@
         <v>711</v>
       </c>
       <c r="D721" t="s">
+        <v>1032</v>
+      </c>
+      <c r="E721" t="s">
         <v>1036</v>
-      </c>
-      <c r="E721" t="s">
-        <v>1033</v>
       </c>
       <c r="F721" t="s">
         <v>1034</v>
@@ -18697,10 +18697,10 @@
         <v>711</v>
       </c>
       <c r="D722" t="s">
+        <v>1032</v>
+      </c>
+      <c r="E722" t="s">
         <v>1036</v>
-      </c>
-      <c r="E722" t="s">
-        <v>1033</v>
       </c>
       <c r="F722" t="s">
         <v>1034</v>
@@ -18717,10 +18717,10 @@
         <v>711</v>
       </c>
       <c r="D723" t="s">
+        <v>1032</v>
+      </c>
+      <c r="E723" t="s">
         <v>1036</v>
-      </c>
-      <c r="E723" t="s">
-        <v>1033</v>
       </c>
       <c r="F723" t="s">
         <v>1034</v>
@@ -18737,10 +18737,10 @@
         <v>15</v>
       </c>
       <c r="D724" t="s">
+        <v>1032</v>
+      </c>
+      <c r="E724" t="s">
         <v>1036</v>
-      </c>
-      <c r="E724" t="s">
-        <v>1033</v>
       </c>
       <c r="F724" t="s">
         <v>1034</v>
@@ -18760,10 +18760,10 @@
         <v>1043</v>
       </c>
       <c r="E725" t="s">
-        <v>1033</v>
+        <v>1044</v>
       </c>
       <c r="F725" t="s">
-        <v>1044</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="726" spans="1:6">
@@ -18780,10 +18780,10 @@
         <v>1046</v>
       </c>
       <c r="E726" t="s">
-        <v>1033</v>
+        <v>1047</v>
       </c>
       <c r="F726" t="s">
-        <v>1047</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="727" spans="1:6">
@@ -18797,10 +18797,10 @@
         <v>711</v>
       </c>
       <c r="D727" t="s">
+        <v>1032</v>
+      </c>
+      <c r="E727" t="s">
         <v>1036</v>
-      </c>
-      <c r="E727" t="s">
-        <v>1033</v>
       </c>
       <c r="F727" t="s">
         <v>1034</v>
@@ -18817,10 +18817,10 @@
         <v>711</v>
       </c>
       <c r="D728" t="s">
+        <v>1032</v>
+      </c>
+      <c r="E728" t="s">
         <v>1036</v>
-      </c>
-      <c r="E728" t="s">
-        <v>1033</v>
       </c>
       <c r="F728" t="s">
         <v>1034</v>
@@ -18840,10 +18840,10 @@
         <v>1051</v>
       </c>
       <c r="E729" t="s">
-        <v>1033</v>
+        <v>1052</v>
       </c>
       <c r="F729" t="s">
-        <v>1052</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="730" spans="1:6">
@@ -18857,10 +18857,10 @@
         <v>13</v>
       </c>
       <c r="D730" t="s">
+        <v>1032</v>
+      </c>
+      <c r="E730" t="s">
         <v>1036</v>
-      </c>
-      <c r="E730" t="s">
-        <v>1033</v>
       </c>
       <c r="F730" t="s">
         <v>1034</v>
@@ -18880,10 +18880,10 @@
         <v>1051</v>
       </c>
       <c r="E731" t="s">
-        <v>1033</v>
+        <v>1052</v>
       </c>
       <c r="F731" t="s">
-        <v>1052</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="732" spans="1:6">
@@ -18900,10 +18900,10 @@
         <v>1056</v>
       </c>
       <c r="E732" t="s">
-        <v>1033</v>
+        <v>1057</v>
       </c>
       <c r="F732" t="s">
-        <v>1057</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="733" spans="1:6">
@@ -18917,10 +18917,10 @@
         <v>24</v>
       </c>
       <c r="D733" t="s">
+        <v>1032</v>
+      </c>
+      <c r="E733" t="s">
         <v>1059</v>
-      </c>
-      <c r="E733" t="s">
-        <v>1033</v>
       </c>
       <c r="F733" t="s">
         <v>1034</v>
@@ -18940,10 +18940,10 @@
         <v>1061</v>
       </c>
       <c r="E734" t="s">
-        <v>1033</v>
+        <v>1062</v>
       </c>
       <c r="F734" t="s">
-        <v>1062</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="735" spans="1:6">
@@ -18957,10 +18957,10 @@
         <v>711</v>
       </c>
       <c r="D735" t="s">
+        <v>1032</v>
+      </c>
+      <c r="E735" t="s">
         <v>1036</v>
-      </c>
-      <c r="E735" t="s">
-        <v>1033</v>
       </c>
       <c r="F735" t="s">
         <v>1034</v>
@@ -18977,10 +18977,10 @@
         <v>711</v>
       </c>
       <c r="D736" t="s">
+        <v>1032</v>
+      </c>
+      <c r="E736" t="s">
         <v>1065</v>
-      </c>
-      <c r="E736" t="s">
-        <v>1033</v>
       </c>
       <c r="F736" t="s">
         <v>1034</v>
@@ -18997,10 +18997,10 @@
         <v>15</v>
       </c>
       <c r="D737" t="s">
+        <v>1032</v>
+      </c>
+      <c r="E737" t="s">
         <v>1036</v>
-      </c>
-      <c r="E737" t="s">
-        <v>1033</v>
       </c>
       <c r="F737" t="s">
         <v>1034</v>
@@ -19017,13 +19017,13 @@
         <v>15</v>
       </c>
       <c r="D738" t="s">
+        <v>973</v>
+      </c>
+      <c r="E738" t="s">
         <v>1068</v>
       </c>
-      <c r="E738" t="s">
-        <v>1033</v>
-      </c>
       <c r="F738" t="s">
-        <v>974</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="739" spans="1:6">
@@ -19037,10 +19037,10 @@
         <v>711</v>
       </c>
       <c r="D739" t="s">
+        <v>1032</v>
+      </c>
+      <c r="E739" t="s">
         <v>1036</v>
-      </c>
-      <c r="E739" t="s">
-        <v>1033</v>
       </c>
       <c r="F739" t="s">
         <v>1034</v>
@@ -19057,10 +19057,10 @@
         <v>711</v>
       </c>
       <c r="D740" t="s">
+        <v>1032</v>
+      </c>
+      <c r="E740" t="s">
         <v>1036</v>
-      </c>
-      <c r="E740" t="s">
-        <v>1033</v>
       </c>
       <c r="F740" t="s">
         <v>1034</v>
@@ -19080,10 +19080,10 @@
         <v>1072</v>
       </c>
       <c r="E741" t="s">
-        <v>1033</v>
+        <v>1073</v>
       </c>
       <c r="F741" t="s">
-        <v>1073</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="742" spans="1:6">
@@ -19097,10 +19097,10 @@
         <v>15</v>
       </c>
       <c r="D742" t="s">
+        <v>1032</v>
+      </c>
+      <c r="E742" t="s">
         <v>1075</v>
-      </c>
-      <c r="E742" t="s">
-        <v>1033</v>
       </c>
       <c r="F742" t="s">
         <v>1034</v>
@@ -19117,10 +19117,10 @@
         <v>711</v>
       </c>
       <c r="D743" t="s">
+        <v>1032</v>
+      </c>
+      <c r="E743" t="s">
         <v>1036</v>
-      </c>
-      <c r="E743" t="s">
-        <v>1033</v>
       </c>
       <c r="F743" t="s">
         <v>1034</v>
@@ -19157,10 +19157,10 @@
         <v>24</v>
       </c>
       <c r="D745" t="s">
+        <v>1032</v>
+      </c>
+      <c r="E745" t="s">
         <v>1079</v>
-      </c>
-      <c r="E745" t="s">
-        <v>1033</v>
       </c>
       <c r="F745" t="s">
         <v>1034</v>
@@ -19177,10 +19177,10 @@
         <v>711</v>
       </c>
       <c r="D746" t="s">
+        <v>1032</v>
+      </c>
+      <c r="E746" t="s">
         <v>1036</v>
-      </c>
-      <c r="E746" t="s">
-        <v>1033</v>
       </c>
       <c r="F746" t="s">
         <v>1034</v>
@@ -19197,10 +19197,10 @@
         <v>711</v>
       </c>
       <c r="D747" t="s">
+        <v>1032</v>
+      </c>
+      <c r="E747" t="s">
         <v>1036</v>
-      </c>
-      <c r="E747" t="s">
-        <v>1033</v>
       </c>
       <c r="F747" t="s">
         <v>1034</v>
@@ -19217,10 +19217,10 @@
         <v>711</v>
       </c>
       <c r="D748" t="s">
+        <v>1032</v>
+      </c>
+      <c r="E748" t="s">
         <v>1036</v>
-      </c>
-      <c r="E748" t="s">
-        <v>1033</v>
       </c>
       <c r="F748" t="s">
         <v>1034</v>
@@ -19237,10 +19237,10 @@
         <v>711</v>
       </c>
       <c r="D749" t="s">
+        <v>1032</v>
+      </c>
+      <c r="E749" t="s">
         <v>1036</v>
-      </c>
-      <c r="E749" t="s">
-        <v>1033</v>
       </c>
       <c r="F749" t="s">
         <v>1034</v>
@@ -19280,10 +19280,10 @@
         <v>1089</v>
       </c>
       <c r="E751" t="s">
-        <v>1086</v>
+        <v>1090</v>
       </c>
       <c r="F751" t="s">
-        <v>1090</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="752" spans="1:6">
@@ -19300,10 +19300,10 @@
         <v>1092</v>
       </c>
       <c r="E752" t="s">
-        <v>1086</v>
+        <v>1093</v>
       </c>
       <c r="F752" t="s">
-        <v>1093</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="753" spans="1:6">
@@ -19320,10 +19320,10 @@
         <v>1092</v>
       </c>
       <c r="E753" t="s">
-        <v>1086</v>
+        <v>1093</v>
       </c>
       <c r="F753" t="s">
-        <v>1093</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="754" spans="1:6">
@@ -19340,10 +19340,10 @@
         <v>1092</v>
       </c>
       <c r="E754" t="s">
-        <v>1086</v>
+        <v>1093</v>
       </c>
       <c r="F754" t="s">
-        <v>1093</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="755" spans="1:6">
@@ -19360,10 +19360,10 @@
         <v>1092</v>
       </c>
       <c r="E755" t="s">
-        <v>1086</v>
+        <v>1093</v>
       </c>
       <c r="F755" t="s">
-        <v>1093</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="756" spans="1:6">
@@ -19380,10 +19380,10 @@
         <v>1092</v>
       </c>
       <c r="E756" t="s">
-        <v>1086</v>
+        <v>1093</v>
       </c>
       <c r="F756" t="s">
-        <v>1093</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="757" spans="1:6">
@@ -19400,10 +19400,10 @@
         <v>1092</v>
       </c>
       <c r="E757" t="s">
-        <v>1086</v>
+        <v>1093</v>
       </c>
       <c r="F757" t="s">
-        <v>1093</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="758" spans="1:6">
@@ -19417,13 +19417,13 @@
         <v>24</v>
       </c>
       <c r="D758" t="s">
-        <v>1085</v>
+        <v>1089</v>
       </c>
       <c r="E758" t="s">
         <v>1086</v>
       </c>
       <c r="F758" t="s">
-        <v>1090</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="759" spans="1:6">
@@ -19437,13 +19437,13 @@
         <v>15</v>
       </c>
       <c r="D759" t="s">
+        <v>1092</v>
+      </c>
+      <c r="E759" t="s">
         <v>1065</v>
       </c>
-      <c r="E759" t="s">
-        <v>1086</v>
-      </c>
       <c r="F759" t="s">
-        <v>1093</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="760" spans="1:6">
@@ -19460,10 +19460,10 @@
         <v>1092</v>
       </c>
       <c r="E760" t="s">
-        <v>1086</v>
+        <v>1093</v>
       </c>
       <c r="F760" t="s">
-        <v>1093</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="761" spans="1:6">
@@ -19480,10 +19480,10 @@
         <v>1092</v>
       </c>
       <c r="E761" t="s">
-        <v>1086</v>
+        <v>1093</v>
       </c>
       <c r="F761" t="s">
-        <v>1093</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="762" spans="1:6">
@@ -19497,13 +19497,13 @@
         <v>24</v>
       </c>
       <c r="D762" t="s">
+        <v>1104</v>
+      </c>
+      <c r="E762" t="s">
         <v>1065</v>
       </c>
-      <c r="E762" t="s">
-        <v>1086</v>
-      </c>
       <c r="F762" t="s">
-        <v>1104</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="763" spans="1:6">
@@ -19520,10 +19520,10 @@
         <v>1092</v>
       </c>
       <c r="E763" t="s">
-        <v>1086</v>
+        <v>1093</v>
       </c>
       <c r="F763" t="s">
-        <v>1093</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="764" spans="1:6">
@@ -19540,10 +19540,10 @@
         <v>1107</v>
       </c>
       <c r="E764" t="s">
-        <v>1086</v>
+        <v>1108</v>
       </c>
       <c r="F764" t="s">
-        <v>1108</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="765" spans="1:6">
@@ -19557,10 +19557,10 @@
         <v>24</v>
       </c>
       <c r="D765" t="s">
-        <v>1092</v>
+        <v>1085</v>
       </c>
       <c r="E765" t="s">
-        <v>1086</v>
+        <v>1093</v>
       </c>
       <c r="F765" t="s">
         <v>1087</v>
@@ -19577,13 +19577,13 @@
         <v>24</v>
       </c>
       <c r="D766" t="s">
+        <v>1104</v>
+      </c>
+      <c r="E766" t="s">
         <v>1111</v>
       </c>
-      <c r="E766" t="s">
-        <v>1086</v>
-      </c>
       <c r="F766" t="s">
-        <v>1104</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="767" spans="1:6">
@@ -19600,10 +19600,10 @@
         <v>1113</v>
       </c>
       <c r="E767" t="s">
-        <v>1086</v>
+        <v>1114</v>
       </c>
       <c r="F767" t="s">
-        <v>1114</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="768" spans="1:6">
@@ -19620,10 +19620,10 @@
         <v>1092</v>
       </c>
       <c r="E768" t="s">
-        <v>1086</v>
+        <v>1093</v>
       </c>
       <c r="F768" t="s">
-        <v>1093</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="769" spans="1:6">
@@ -19640,10 +19640,10 @@
         <v>1092</v>
       </c>
       <c r="E769" t="s">
-        <v>1086</v>
+        <v>1093</v>
       </c>
       <c r="F769" t="s">
-        <v>1093</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="770" spans="1:6">
@@ -19660,10 +19660,10 @@
         <v>1118</v>
       </c>
       <c r="E770" t="s">
-        <v>1086</v>
+        <v>1119</v>
       </c>
       <c r="F770" t="s">
-        <v>1119</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="771" spans="1:6">
@@ -19680,10 +19680,10 @@
         <v>1092</v>
       </c>
       <c r="E771" t="s">
-        <v>1086</v>
+        <v>1093</v>
       </c>
       <c r="F771" t="s">
-        <v>1093</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="772" spans="1:6">
@@ -19700,10 +19700,10 @@
         <v>1092</v>
       </c>
       <c r="E772" t="s">
-        <v>1086</v>
+        <v>1093</v>
       </c>
       <c r="F772" t="s">
-        <v>1093</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="773" spans="1:6">
@@ -19720,10 +19720,10 @@
         <v>1092</v>
       </c>
       <c r="E773" t="s">
-        <v>1086</v>
+        <v>1093</v>
       </c>
       <c r="F773" t="s">
-        <v>1093</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="774" spans="1:6">
@@ -19740,10 +19740,10 @@
         <v>1124</v>
       </c>
       <c r="E774" t="s">
-        <v>1086</v>
+        <v>1125</v>
       </c>
       <c r="F774" t="s">
-        <v>1125</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="775" spans="1:6">
@@ -19760,10 +19760,10 @@
         <v>1092</v>
       </c>
       <c r="E775" t="s">
-        <v>1086</v>
+        <v>1093</v>
       </c>
       <c r="F775" t="s">
-        <v>1093</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="776" spans="1:6">
@@ -19797,10 +19797,10 @@
         <v>711</v>
       </c>
       <c r="D777" t="s">
+        <v>1128</v>
+      </c>
+      <c r="E777" t="s">
         <v>1132</v>
-      </c>
-      <c r="E777" t="s">
-        <v>1129</v>
       </c>
       <c r="F777" t="s">
         <v>1130</v>
@@ -19820,10 +19820,10 @@
         <v>1134</v>
       </c>
       <c r="E778" t="s">
-        <v>1129</v>
+        <v>1135</v>
       </c>
       <c r="F778" t="s">
-        <v>1135</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="779" spans="1:6">
@@ -19840,10 +19840,10 @@
         <v>1137</v>
       </c>
       <c r="E779" t="s">
-        <v>1129</v>
+        <v>1138</v>
       </c>
       <c r="F779" t="s">
-        <v>1138</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="780" spans="1:6">
@@ -19857,10 +19857,10 @@
         <v>711</v>
       </c>
       <c r="D780" t="s">
+        <v>1128</v>
+      </c>
+      <c r="E780" t="s">
         <v>1132</v>
-      </c>
-      <c r="E780" t="s">
-        <v>1129</v>
       </c>
       <c r="F780" t="s">
         <v>1130</v>
@@ -19877,10 +19877,10 @@
         <v>711</v>
       </c>
       <c r="D781" t="s">
+        <v>1128</v>
+      </c>
+      <c r="E781" t="s">
         <v>1132</v>
-      </c>
-      <c r="E781" t="s">
-        <v>1129</v>
       </c>
       <c r="F781" t="s">
         <v>1130</v>
@@ -19897,10 +19897,10 @@
         <v>711</v>
       </c>
       <c r="D782" t="s">
+        <v>1128</v>
+      </c>
+      <c r="E782" t="s">
         <v>1142</v>
-      </c>
-      <c r="E782" t="s">
-        <v>1129</v>
       </c>
       <c r="F782" t="s">
         <v>1130</v>
@@ -19917,10 +19917,10 @@
         <v>711</v>
       </c>
       <c r="D783" t="s">
+        <v>1128</v>
+      </c>
+      <c r="E783" t="s">
         <v>1132</v>
-      </c>
-      <c r="E783" t="s">
-        <v>1129</v>
       </c>
       <c r="F783" t="s">
         <v>1130</v>
@@ -19937,10 +19937,10 @@
         <v>711</v>
       </c>
       <c r="D784" t="s">
+        <v>1128</v>
+      </c>
+      <c r="E784" t="s">
         <v>1132</v>
-      </c>
-      <c r="E784" t="s">
-        <v>1129</v>
       </c>
       <c r="F784" t="s">
         <v>1130</v>
@@ -19957,10 +19957,10 @@
         <v>711</v>
       </c>
       <c r="D785" t="s">
+        <v>1128</v>
+      </c>
+      <c r="E785" t="s">
         <v>1132</v>
-      </c>
-      <c r="E785" t="s">
-        <v>1129</v>
       </c>
       <c r="F785" t="s">
         <v>1130</v>
@@ -19977,10 +19977,10 @@
         <v>711</v>
       </c>
       <c r="D786" t="s">
+        <v>1128</v>
+      </c>
+      <c r="E786" t="s">
         <v>1132</v>
-      </c>
-      <c r="E786" t="s">
-        <v>1129</v>
       </c>
       <c r="F786" t="s">
         <v>1130</v>
@@ -19997,10 +19997,10 @@
         <v>711</v>
       </c>
       <c r="D787" t="s">
+        <v>1128</v>
+      </c>
+      <c r="E787" t="s">
         <v>1132</v>
-      </c>
-      <c r="E787" t="s">
-        <v>1129</v>
       </c>
       <c r="F787" t="s">
         <v>1130</v>
@@ -20017,10 +20017,10 @@
         <v>711</v>
       </c>
       <c r="D788" t="s">
+        <v>1128</v>
+      </c>
+      <c r="E788" t="s">
         <v>1132</v>
-      </c>
-      <c r="E788" t="s">
-        <v>1129</v>
       </c>
       <c r="F788" t="s">
         <v>1130</v>
@@ -20037,13 +20037,13 @@
         <v>24</v>
       </c>
       <c r="D789" t="s">
-        <v>1128</v>
+        <v>1150</v>
       </c>
       <c r="E789" t="s">
         <v>1129</v>
       </c>
       <c r="F789" t="s">
-        <v>1150</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="790" spans="1:6">
@@ -20057,10 +20057,10 @@
         <v>711</v>
       </c>
       <c r="D790" t="s">
+        <v>1128</v>
+      </c>
+      <c r="E790" t="s">
         <v>1132</v>
-      </c>
-      <c r="E790" t="s">
-        <v>1129</v>
       </c>
       <c r="F790" t="s">
         <v>1130</v>
@@ -20077,13 +20077,13 @@
         <v>24</v>
       </c>
       <c r="D791" t="s">
+        <v>1153</v>
+      </c>
+      <c r="E791" t="s">
         <v>1142</v>
       </c>
-      <c r="E791" t="s">
-        <v>1129</v>
-      </c>
       <c r="F791" t="s">
-        <v>1153</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="792" spans="1:6">
@@ -20097,13 +20097,13 @@
         <v>24</v>
       </c>
       <c r="D792" t="s">
+        <v>1150</v>
+      </c>
+      <c r="E792" t="s">
         <v>1155</v>
       </c>
-      <c r="E792" t="s">
-        <v>1129</v>
-      </c>
       <c r="F792" t="s">
-        <v>1150</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="793" spans="1:6">
@@ -20117,10 +20117,10 @@
         <v>711</v>
       </c>
       <c r="D793" t="s">
+        <v>1128</v>
+      </c>
+      <c r="E793" t="s">
         <v>1132</v>
-      </c>
-      <c r="E793" t="s">
-        <v>1129</v>
       </c>
       <c r="F793" t="s">
         <v>1130</v>
@@ -20137,13 +20137,13 @@
         <v>24</v>
       </c>
       <c r="D794" t="s">
+        <v>1158</v>
+      </c>
+      <c r="E794" t="s">
         <v>1132</v>
       </c>
-      <c r="E794" t="s">
-        <v>1129</v>
-      </c>
       <c r="F794" t="s">
-        <v>1158</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="795" spans="1:6">
@@ -20157,10 +20157,10 @@
         <v>24</v>
       </c>
       <c r="D795" t="s">
+        <v>1128</v>
+      </c>
+      <c r="E795" t="s">
         <v>1160</v>
-      </c>
-      <c r="E795" t="s">
-        <v>1129</v>
       </c>
       <c r="F795" t="s">
         <v>1130</v>
@@ -20177,10 +20177,10 @@
         <v>711</v>
       </c>
       <c r="D796" t="s">
+        <v>1128</v>
+      </c>
+      <c r="E796" t="s">
         <v>1132</v>
-      </c>
-      <c r="E796" t="s">
-        <v>1129</v>
       </c>
       <c r="F796" t="s">
         <v>1130</v>
@@ -20200,10 +20200,10 @@
         <v>1163</v>
       </c>
       <c r="E797" t="s">
-        <v>1129</v>
+        <v>1164</v>
       </c>
       <c r="F797" t="s">
-        <v>1164</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="798" spans="1:6">
@@ -20220,10 +20220,10 @@
         <v>1166</v>
       </c>
       <c r="E798" t="s">
-        <v>1129</v>
+        <v>1167</v>
       </c>
       <c r="F798" t="s">
-        <v>1167</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="799" spans="1:6">
@@ -20237,10 +20237,10 @@
         <v>711</v>
       </c>
       <c r="D799" t="s">
+        <v>1128</v>
+      </c>
+      <c r="E799" t="s">
         <v>1132</v>
-      </c>
-      <c r="E799" t="s">
-        <v>1129</v>
       </c>
       <c r="F799" t="s">
         <v>1130</v>
@@ -20257,10 +20257,10 @@
         <v>711</v>
       </c>
       <c r="D800" t="s">
+        <v>1128</v>
+      </c>
+      <c r="E800" t="s">
         <v>1132</v>
-      </c>
-      <c r="E800" t="s">
-        <v>1129</v>
       </c>
       <c r="F800" t="s">
         <v>1130</v>
@@ -20277,10 +20277,10 @@
         <v>711</v>
       </c>
       <c r="D801" t="s">
+        <v>1128</v>
+      </c>
+      <c r="E801" t="s">
         <v>1132</v>
-      </c>
-      <c r="E801" t="s">
-        <v>1129</v>
       </c>
       <c r="F801" t="s">
         <v>1130</v>
@@ -20297,10 +20297,10 @@
         <v>711</v>
       </c>
       <c r="D802" t="s">
+        <v>1128</v>
+      </c>
+      <c r="E802" t="s">
         <v>1132</v>
-      </c>
-      <c r="E802" t="s">
-        <v>1129</v>
       </c>
       <c r="F802" t="s">
         <v>1130</v>
@@ -20317,10 +20317,10 @@
         <v>711</v>
       </c>
       <c r="D803" t="s">
+        <v>1128</v>
+      </c>
+      <c r="E803" t="s">
         <v>1132</v>
-      </c>
-      <c r="E803" t="s">
-        <v>1129</v>
       </c>
       <c r="F803" t="s">
         <v>1130</v>
@@ -20337,10 +20337,10 @@
         <v>711</v>
       </c>
       <c r="D804" t="s">
+        <v>1128</v>
+      </c>
+      <c r="E804" t="s">
         <v>1132</v>
-      </c>
-      <c r="E804" t="s">
-        <v>1129</v>
       </c>
       <c r="F804" t="s">
         <v>1130</v>
@@ -20357,10 +20357,10 @@
         <v>711</v>
       </c>
       <c r="D805" t="s">
+        <v>1128</v>
+      </c>
+      <c r="E805" t="s">
         <v>1132</v>
-      </c>
-      <c r="E805" t="s">
-        <v>1129</v>
       </c>
       <c r="F805" t="s">
         <v>1130</v>
@@ -20377,10 +20377,10 @@
         <v>711</v>
       </c>
       <c r="D806" t="s">
+        <v>1128</v>
+      </c>
+      <c r="E806" t="s">
         <v>1132</v>
-      </c>
-      <c r="E806" t="s">
-        <v>1129</v>
       </c>
       <c r="F806" t="s">
         <v>1130</v>
@@ -20397,10 +20397,10 @@
         <v>711</v>
       </c>
       <c r="D807" t="s">
+        <v>1128</v>
+      </c>
+      <c r="E807" t="s">
         <v>1132</v>
-      </c>
-      <c r="E807" t="s">
-        <v>1129</v>
       </c>
       <c r="F807" t="s">
         <v>1130</v>
@@ -20480,10 +20480,10 @@
         <v>1185</v>
       </c>
       <c r="E811" t="s">
-        <v>1179</v>
+        <v>1186</v>
       </c>
       <c r="F811" t="s">
-        <v>1186</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="812" spans="1:6">
@@ -20537,10 +20537,10 @@
         <v>711</v>
       </c>
       <c r="D814" t="s">
-        <v>1185</v>
+        <v>1178</v>
       </c>
       <c r="E814" t="s">
-        <v>1179</v>
+        <v>1186</v>
       </c>
       <c r="F814" t="s">
         <v>1180</v>
@@ -20560,10 +20560,10 @@
         <v>1191</v>
       </c>
       <c r="E815" t="s">
-        <v>1179</v>
+        <v>1192</v>
       </c>
       <c r="F815" t="s">
-        <v>1192</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="816" spans="1:6">
@@ -20680,10 +20680,10 @@
         <v>1199</v>
       </c>
       <c r="E821" t="s">
-        <v>1179</v>
+        <v>1200</v>
       </c>
       <c r="F821" t="s">
-        <v>1200</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="822" spans="1:6">
@@ -20700,10 +20700,10 @@
         <v>1202</v>
       </c>
       <c r="E822" t="s">
-        <v>1179</v>
+        <v>1203</v>
       </c>
       <c r="F822" t="s">
-        <v>1203</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="823" spans="1:6">
@@ -20717,10 +20717,10 @@
         <v>1182</v>
       </c>
       <c r="D823" t="s">
-        <v>1202</v>
+        <v>1178</v>
       </c>
       <c r="E823" t="s">
-        <v>1179</v>
+        <v>1203</v>
       </c>
       <c r="F823" t="s">
         <v>1180</v>
@@ -20740,10 +20740,10 @@
         <v>1202</v>
       </c>
       <c r="E824" t="s">
-        <v>1179</v>
+        <v>1203</v>
       </c>
       <c r="F824" t="s">
-        <v>1203</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="825" spans="1:6">
@@ -20760,10 +20760,10 @@
         <v>1202</v>
       </c>
       <c r="E825" t="s">
-        <v>1179</v>
+        <v>1203</v>
       </c>
       <c r="F825" t="s">
-        <v>1203</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="826" spans="1:6">
@@ -20780,10 +20780,10 @@
         <v>1202</v>
       </c>
       <c r="E826" t="s">
-        <v>1179</v>
+        <v>1203</v>
       </c>
       <c r="F826" t="s">
-        <v>1203</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="827" spans="1:6">
@@ -20800,10 +20800,10 @@
         <v>1202</v>
       </c>
       <c r="E827" t="s">
-        <v>1179</v>
+        <v>1203</v>
       </c>
       <c r="F827" t="s">
-        <v>1203</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="828" spans="1:6">
@@ -20817,10 +20817,10 @@
         <v>1182</v>
       </c>
       <c r="D828" t="s">
-        <v>1202</v>
+        <v>1178</v>
       </c>
       <c r="E828" t="s">
-        <v>1179</v>
+        <v>1203</v>
       </c>
       <c r="F828" t="s">
         <v>1180</v>
@@ -20857,10 +20857,10 @@
         <v>1182</v>
       </c>
       <c r="D830" t="s">
-        <v>1185</v>
+        <v>1178</v>
       </c>
       <c r="E830" t="s">
-        <v>1179</v>
+        <v>1186</v>
       </c>
       <c r="F830" t="s">
         <v>1180</v>
@@ -21057,10 +21057,10 @@
         <v>1182</v>
       </c>
       <c r="D840" t="s">
+        <v>1221</v>
+      </c>
+      <c r="E840" t="s">
         <v>1225</v>
-      </c>
-      <c r="E840" t="s">
-        <v>1222</v>
       </c>
       <c r="F840" t="s">
         <v>1223</v>
@@ -21077,10 +21077,10 @@
         <v>1182</v>
       </c>
       <c r="D841" t="s">
+        <v>1221</v>
+      </c>
+      <c r="E841" t="s">
         <v>1225</v>
-      </c>
-      <c r="E841" t="s">
-        <v>1222</v>
       </c>
       <c r="F841" t="s">
         <v>1223</v>
@@ -21097,10 +21097,10 @@
         <v>1182</v>
       </c>
       <c r="D842" t="s">
+        <v>1221</v>
+      </c>
+      <c r="E842" t="s">
         <v>1225</v>
-      </c>
-      <c r="E842" t="s">
-        <v>1222</v>
       </c>
       <c r="F842" t="s">
         <v>1223</v>
@@ -21117,10 +21117,10 @@
         <v>1182</v>
       </c>
       <c r="D843" t="s">
+        <v>1221</v>
+      </c>
+      <c r="E843" t="s">
         <v>1225</v>
-      </c>
-      <c r="E843" t="s">
-        <v>1222</v>
       </c>
       <c r="F843" t="s">
         <v>1223</v>
@@ -21137,10 +21137,10 @@
         <v>1182</v>
       </c>
       <c r="D844" t="s">
+        <v>1221</v>
+      </c>
+      <c r="E844" t="s">
         <v>1225</v>
-      </c>
-      <c r="E844" t="s">
-        <v>1222</v>
       </c>
       <c r="F844" t="s">
         <v>1223</v>
@@ -21157,10 +21157,10 @@
         <v>711</v>
       </c>
       <c r="D845" t="s">
+        <v>1221</v>
+      </c>
+      <c r="E845" t="s">
         <v>1225</v>
-      </c>
-      <c r="E845" t="s">
-        <v>1222</v>
       </c>
       <c r="F845" t="s">
         <v>1223</v>
@@ -21177,10 +21177,10 @@
         <v>1182</v>
       </c>
       <c r="D846" t="s">
+        <v>1221</v>
+      </c>
+      <c r="E846" t="s">
         <v>1225</v>
-      </c>
-      <c r="E846" t="s">
-        <v>1222</v>
       </c>
       <c r="F846" t="s">
         <v>1223</v>
@@ -21197,13 +21197,13 @@
         <v>1182</v>
       </c>
       <c r="D847" t="s">
+        <v>1185</v>
+      </c>
+      <c r="E847" t="s">
         <v>1233</v>
       </c>
-      <c r="E847" t="s">
-        <v>1222</v>
-      </c>
       <c r="F847" t="s">
-        <v>1186</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="848" spans="1:6">
@@ -21217,13 +21217,13 @@
         <v>1182</v>
       </c>
       <c r="D848" t="s">
+        <v>1185</v>
+      </c>
+      <c r="E848" t="s">
         <v>1233</v>
       </c>
-      <c r="E848" t="s">
-        <v>1222</v>
-      </c>
       <c r="F848" t="s">
-        <v>1186</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="849" spans="1:6">
@@ -21237,13 +21237,13 @@
         <v>711</v>
       </c>
       <c r="D849" t="s">
+        <v>1185</v>
+      </c>
+      <c r="E849" t="s">
         <v>1233</v>
       </c>
-      <c r="E849" t="s">
-        <v>1222</v>
-      </c>
       <c r="F849" t="s">
-        <v>1186</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="850" spans="1:6">
@@ -21257,13 +21257,13 @@
         <v>1182</v>
       </c>
       <c r="D850" t="s">
+        <v>1237</v>
+      </c>
+      <c r="E850" t="s">
         <v>1233</v>
       </c>
-      <c r="E850" t="s">
-        <v>1222</v>
-      </c>
       <c r="F850" t="s">
-        <v>1237</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="851" spans="1:6">
@@ -21277,13 +21277,13 @@
         <v>1182</v>
       </c>
       <c r="D851" t="s">
+        <v>1185</v>
+      </c>
+      <c r="E851" t="s">
         <v>1233</v>
       </c>
-      <c r="E851" t="s">
-        <v>1222</v>
-      </c>
       <c r="F851" t="s">
-        <v>1186</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="852" spans="1:6">
@@ -21297,13 +21297,13 @@
         <v>1182</v>
       </c>
       <c r="D852" t="s">
+        <v>1185</v>
+      </c>
+      <c r="E852" t="s">
         <v>1233</v>
       </c>
-      <c r="E852" t="s">
-        <v>1222</v>
-      </c>
       <c r="F852" t="s">
-        <v>1186</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="853" spans="1:6">
@@ -21317,10 +21317,10 @@
         <v>1182</v>
       </c>
       <c r="D853" t="s">
+        <v>1221</v>
+      </c>
+      <c r="E853" t="s">
         <v>1225</v>
-      </c>
-      <c r="E853" t="s">
-        <v>1222</v>
       </c>
       <c r="F853" t="s">
         <v>1223</v>
@@ -21337,10 +21337,10 @@
         <v>15</v>
       </c>
       <c r="D854" t="s">
+        <v>1221</v>
+      </c>
+      <c r="E854" t="s">
         <v>1225</v>
-      </c>
-      <c r="E854" t="s">
-        <v>1222</v>
       </c>
       <c r="F854" t="s">
         <v>1223</v>
@@ -21357,10 +21357,10 @@
         <v>15</v>
       </c>
       <c r="D855" t="s">
+        <v>1221</v>
+      </c>
+      <c r="E855" t="s">
         <v>1225</v>
-      </c>
-      <c r="E855" t="s">
-        <v>1222</v>
       </c>
       <c r="F855" t="s">
         <v>1223</v>
@@ -21377,10 +21377,10 @@
         <v>15</v>
       </c>
       <c r="D856" t="s">
+        <v>1221</v>
+      </c>
+      <c r="E856" t="s">
         <v>1225</v>
-      </c>
-      <c r="E856" t="s">
-        <v>1222</v>
       </c>
       <c r="F856" t="s">
         <v>1223</v>
@@ -21397,10 +21397,10 @@
         <v>1182</v>
       </c>
       <c r="D857" t="s">
+        <v>1221</v>
+      </c>
+      <c r="E857" t="s">
         <v>1225</v>
-      </c>
-      <c r="E857" t="s">
-        <v>1222</v>
       </c>
       <c r="F857" t="s">
         <v>1223</v>
@@ -21417,10 +21417,10 @@
         <v>1182</v>
       </c>
       <c r="D858" t="s">
+        <v>1221</v>
+      </c>
+      <c r="E858" t="s">
         <v>1225</v>
-      </c>
-      <c r="E858" t="s">
-        <v>1222</v>
       </c>
       <c r="F858" t="s">
         <v>1223</v>
@@ -21437,10 +21437,10 @@
         <v>15</v>
       </c>
       <c r="D859" t="s">
+        <v>1221</v>
+      </c>
+      <c r="E859" t="s">
         <v>1225</v>
-      </c>
-      <c r="E859" t="s">
-        <v>1222</v>
       </c>
       <c r="F859" t="s">
         <v>1223</v>
@@ -21457,10 +21457,10 @@
         <v>1182</v>
       </c>
       <c r="D860" t="s">
+        <v>1221</v>
+      </c>
+      <c r="E860" t="s">
         <v>1225</v>
-      </c>
-      <c r="E860" t="s">
-        <v>1222</v>
       </c>
       <c r="F860" t="s">
         <v>1223</v>
@@ -21477,10 +21477,10 @@
         <v>1182</v>
       </c>
       <c r="D861" t="s">
+        <v>1221</v>
+      </c>
+      <c r="E861" t="s">
         <v>1225</v>
-      </c>
-      <c r="E861" t="s">
-        <v>1222</v>
       </c>
       <c r="F861" t="s">
         <v>1223</v>
@@ -21497,10 +21497,10 @@
         <v>711</v>
       </c>
       <c r="D862" t="s">
+        <v>1221</v>
+      </c>
+      <c r="E862" t="s">
         <v>1225</v>
-      </c>
-      <c r="E862" t="s">
-        <v>1222</v>
       </c>
       <c r="F862" t="s">
         <v>1223</v>
@@ -21517,10 +21517,10 @@
         <v>1182</v>
       </c>
       <c r="D863" t="s">
+        <v>1221</v>
+      </c>
+      <c r="E863" t="s">
         <v>1225</v>
-      </c>
-      <c r="E863" t="s">
-        <v>1222</v>
       </c>
       <c r="F863" t="s">
         <v>1223</v>
@@ -21537,10 +21537,10 @@
         <v>1182</v>
       </c>
       <c r="D864" t="s">
+        <v>1221</v>
+      </c>
+      <c r="E864" t="s">
         <v>1225</v>
-      </c>
-      <c r="E864" t="s">
-        <v>1222</v>
       </c>
       <c r="F864" t="s">
         <v>1223</v>
@@ -21557,10 +21557,10 @@
         <v>1182</v>
       </c>
       <c r="D865" t="s">
+        <v>1221</v>
+      </c>
+      <c r="E865" t="s">
         <v>1225</v>
-      </c>
-      <c r="E865" t="s">
-        <v>1222</v>
       </c>
       <c r="F865" t="s">
         <v>1223</v>
@@ -21577,10 +21577,10 @@
         <v>711</v>
       </c>
       <c r="D866" t="s">
+        <v>1221</v>
+      </c>
+      <c r="E866" t="s">
         <v>1225</v>
-      </c>
-      <c r="E866" t="s">
-        <v>1222</v>
       </c>
       <c r="F866" t="s">
         <v>1223</v>
@@ -21617,13 +21617,13 @@
         <v>1182</v>
       </c>
       <c r="D868" t="s">
-        <v>1255</v>
+        <v>1259</v>
       </c>
       <c r="E868" t="s">
         <v>1256</v>
       </c>
       <c r="F868" t="s">
-        <v>1259</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="869" spans="1:6">
@@ -21637,13 +21637,13 @@
         <v>1182</v>
       </c>
       <c r="D869" t="s">
-        <v>1255</v>
+        <v>1259</v>
       </c>
       <c r="E869" t="s">
         <v>1256</v>
       </c>
       <c r="F869" t="s">
-        <v>1259</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="870" spans="1:6">
@@ -21657,13 +21657,13 @@
         <v>1182</v>
       </c>
       <c r="D870" t="s">
-        <v>1255</v>
+        <v>1259</v>
       </c>
       <c r="E870" t="s">
         <v>1256</v>
       </c>
       <c r="F870" t="s">
-        <v>1259</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="871" spans="1:6">
@@ -21677,13 +21677,13 @@
         <v>1182</v>
       </c>
       <c r="D871" t="s">
-        <v>1255</v>
+        <v>1259</v>
       </c>
       <c r="E871" t="s">
         <v>1256</v>
       </c>
       <c r="F871" t="s">
-        <v>1259</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="872" spans="1:6">
@@ -21697,13 +21697,13 @@
         <v>15</v>
       </c>
       <c r="D872" t="s">
-        <v>1255</v>
+        <v>1259</v>
       </c>
       <c r="E872" t="s">
         <v>1256</v>
       </c>
       <c r="F872" t="s">
-        <v>1259</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="873" spans="1:6">
@@ -21717,13 +21717,13 @@
         <v>15</v>
       </c>
       <c r="D873" t="s">
-        <v>1255</v>
+        <v>1259</v>
       </c>
       <c r="E873" t="s">
         <v>1256</v>
       </c>
       <c r="F873" t="s">
-        <v>1259</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="874" spans="1:6">
@@ -21737,13 +21737,13 @@
         <v>1182</v>
       </c>
       <c r="D874" t="s">
-        <v>1255</v>
+        <v>1259</v>
       </c>
       <c r="E874" t="s">
         <v>1256</v>
       </c>
       <c r="F874" t="s">
-        <v>1259</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="875" spans="1:6">
@@ -21757,13 +21757,13 @@
         <v>1182</v>
       </c>
       <c r="D875" t="s">
-        <v>1255</v>
+        <v>1259</v>
       </c>
       <c r="E875" t="s">
         <v>1256</v>
       </c>
       <c r="F875" t="s">
-        <v>1259</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="876" spans="1:6">
@@ -21777,13 +21777,13 @@
         <v>711</v>
       </c>
       <c r="D876" t="s">
-        <v>1255</v>
+        <v>1259</v>
       </c>
       <c r="E876" t="s">
         <v>1256</v>
       </c>
       <c r="F876" t="s">
-        <v>1259</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="877" spans="1:6">
@@ -21797,13 +21797,13 @@
         <v>15</v>
       </c>
       <c r="D877" t="s">
-        <v>1255</v>
+        <v>1259</v>
       </c>
       <c r="E877" t="s">
         <v>1256</v>
       </c>
       <c r="F877" t="s">
-        <v>1259</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="878" spans="1:6">
@@ -21817,13 +21817,13 @@
         <v>1182</v>
       </c>
       <c r="D878" t="s">
-        <v>1255</v>
+        <v>1259</v>
       </c>
       <c r="E878" t="s">
         <v>1256</v>
       </c>
       <c r="F878" t="s">
-        <v>1259</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="879" spans="1:6">
@@ -21837,13 +21837,13 @@
         <v>1182</v>
       </c>
       <c r="D879" t="s">
-        <v>1255</v>
+        <v>1259</v>
       </c>
       <c r="E879" t="s">
         <v>1256</v>
       </c>
       <c r="F879" t="s">
-        <v>1259</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="880" spans="1:6">
@@ -21857,13 +21857,13 @@
         <v>1182</v>
       </c>
       <c r="D880" t="s">
-        <v>1255</v>
+        <v>1259</v>
       </c>
       <c r="E880" t="s">
         <v>1256</v>
       </c>
       <c r="F880" t="s">
-        <v>1259</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="881" spans="1:6">
@@ -21877,13 +21877,13 @@
         <v>1182</v>
       </c>
       <c r="D881" t="s">
-        <v>1255</v>
+        <v>1259</v>
       </c>
       <c r="E881" t="s">
         <v>1256</v>
       </c>
       <c r="F881" t="s">
-        <v>1259</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="882" spans="1:6">
@@ -21897,13 +21897,13 @@
         <v>1182</v>
       </c>
       <c r="D882" t="s">
-        <v>1255</v>
+        <v>1259</v>
       </c>
       <c r="E882" t="s">
         <v>1256</v>
       </c>
       <c r="F882" t="s">
-        <v>1259</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="883" spans="1:6">
@@ -21917,13 +21917,13 @@
         <v>711</v>
       </c>
       <c r="D883" t="s">
-        <v>1255</v>
+        <v>1259</v>
       </c>
       <c r="E883" t="s">
         <v>1256</v>
       </c>
       <c r="F883" t="s">
-        <v>1259</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="884" spans="1:6">
@@ -21937,13 +21937,13 @@
         <v>1182</v>
       </c>
       <c r="D884" t="s">
-        <v>1255</v>
+        <v>1259</v>
       </c>
       <c r="E884" t="s">
         <v>1256</v>
       </c>
       <c r="F884" t="s">
-        <v>1259</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="885" spans="1:6">
@@ -21957,13 +21957,13 @@
         <v>1182</v>
       </c>
       <c r="D885" t="s">
-        <v>1255</v>
+        <v>1259</v>
       </c>
       <c r="E885" t="s">
         <v>1256</v>
       </c>
       <c r="F885" t="s">
-        <v>1259</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="886" spans="1:6">
@@ -21977,13 +21977,13 @@
         <v>1182</v>
       </c>
       <c r="D886" t="s">
-        <v>1255</v>
+        <v>1259</v>
       </c>
       <c r="E886" t="s">
         <v>1256</v>
       </c>
       <c r="F886" t="s">
-        <v>1259</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="887" spans="1:6">
@@ -21997,13 +21997,13 @@
         <v>15</v>
       </c>
       <c r="D887" t="s">
-        <v>1255</v>
+        <v>1259</v>
       </c>
       <c r="E887" t="s">
         <v>1256</v>
       </c>
       <c r="F887" t="s">
-        <v>1259</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="888" spans="1:6">
@@ -22017,13 +22017,13 @@
         <v>1182</v>
       </c>
       <c r="D888" t="s">
-        <v>1255</v>
+        <v>1259</v>
       </c>
       <c r="E888" t="s">
         <v>1256</v>
       </c>
       <c r="F888" t="s">
-        <v>1259</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="889" spans="1:6">
@@ -22037,13 +22037,13 @@
         <v>711</v>
       </c>
       <c r="D889" t="s">
-        <v>1255</v>
+        <v>1259</v>
       </c>
       <c r="E889" t="s">
         <v>1256</v>
       </c>
       <c r="F889" t="s">
-        <v>1259</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="890" spans="1:6">
@@ -22157,10 +22157,10 @@
         <v>1182</v>
       </c>
       <c r="D895" t="s">
+        <v>1282</v>
+      </c>
+      <c r="E895" t="s">
         <v>1290</v>
-      </c>
-      <c r="E895" t="s">
-        <v>1283</v>
       </c>
       <c r="F895" t="s">
         <v>1284</v>
@@ -22177,10 +22177,10 @@
         <v>711</v>
       </c>
       <c r="D896" t="s">
+        <v>1282</v>
+      </c>
+      <c r="E896" t="s">
         <v>1290</v>
-      </c>
-      <c r="E896" t="s">
-        <v>1283</v>
       </c>
       <c r="F896" t="s">
         <v>1284</v>
@@ -22357,13 +22357,13 @@
         <v>1182</v>
       </c>
       <c r="D905" t="s">
+        <v>1282</v>
+      </c>
+      <c r="E905" t="s">
         <v>1301</v>
       </c>
-      <c r="E905" t="s">
+      <c r="F905" t="s">
         <v>1302</v>
-      </c>
-      <c r="F905" t="s">
-        <v>1284</v>
       </c>
     </row>
     <row r="906" spans="1:6">
@@ -22377,13 +22377,13 @@
         <v>1182</v>
       </c>
       <c r="D906" t="s">
+        <v>1282</v>
+      </c>
+      <c r="E906" t="s">
         <v>1304</v>
       </c>
-      <c r="E906" t="s">
+      <c r="F906" t="s">
         <v>1302</v>
-      </c>
-      <c r="F906" t="s">
-        <v>1284</v>
       </c>
     </row>
     <row r="907" spans="1:6">
@@ -22397,13 +22397,13 @@
         <v>1182</v>
       </c>
       <c r="D907" t="s">
+        <v>1282</v>
+      </c>
+      <c r="E907" t="s">
         <v>1301</v>
       </c>
-      <c r="E907" t="s">
+      <c r="F907" t="s">
         <v>1302</v>
-      </c>
-      <c r="F907" t="s">
-        <v>1284</v>
       </c>
     </row>
   </sheetData>

--- a/api/2/clv2/xlsx/pt/HumanitarianPlan.xlsx
+++ b/api/2/clv2/xlsx/pt/HumanitarianPlan.xlsx
@@ -22,12 +22,12 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:plan-year</t>
+  </si>
+  <si>
     <t>codeforiati:plan-start-date</t>
   </si>
   <si>
-    <t>codeforiati:plan-year</t>
-  </si>
-  <si>
     <t>codeforiati:plan-type</t>
   </si>
   <si>
@@ -40,12 +40,12 @@
     <t>active</t>
   </si>
   <si>
+    <t>2025</t>
+  </si>
+  <si>
     <t>2025-01-01</t>
   </si>
   <si>
-    <t>2025</t>
-  </si>
-  <si>
     <t>Humanitarian needs and response plan</t>
   </si>
   <si>
@@ -223,12 +223,12 @@
     <t>HAFG24</t>
   </si>
   <si>
+    <t>2024</t>
+  </si>
+  <si>
     <t>2024-01-01</t>
   </si>
   <si>
-    <t>2024</t>
-  </si>
-  <si>
     <t>2024-12-31</t>
   </si>
   <si>
@@ -427,12 +427,12 @@
     <t>HAFG23</t>
   </si>
   <si>
+    <t>2023</t>
+  </si>
+  <si>
     <t>2023-01-01</t>
   </si>
   <si>
-    <t>2023</t>
-  </si>
-  <si>
     <t>2023-12-31</t>
   </si>
   <si>
@@ -607,12 +607,12 @@
     <t>HAFG22</t>
   </si>
   <si>
+    <t>2022</t>
+  </si>
+  <si>
     <t>2022-01-01</t>
   </si>
   <si>
-    <t>2022</t>
-  </si>
-  <si>
     <t>2022-12-31</t>
   </si>
   <si>
@@ -811,12 +811,12 @@
     <t>FAFG21</t>
   </si>
   <si>
+    <t>2021</t>
+  </si>
+  <si>
     <t>2021-09-01</t>
   </si>
   <si>
-    <t>2021</t>
-  </si>
-  <si>
     <t>2021-12-31</t>
   </si>
   <si>
@@ -1015,12 +1015,12 @@
     <t>HAFG20</t>
   </si>
   <si>
+    <t>2020</t>
+  </si>
+  <si>
     <t>2020-01-01</t>
   </si>
   <si>
-    <t>2020</t>
-  </si>
-  <si>
     <t>2020-12-31</t>
   </si>
   <si>
@@ -1255,12 +1255,12 @@
     <t>HAFG19</t>
   </si>
   <si>
+    <t>2019</t>
+  </si>
+  <si>
     <t>2019-01-01</t>
   </si>
   <si>
-    <t>2019</t>
-  </si>
-  <si>
     <t>2019-12-31</t>
   </si>
   <si>
@@ -1387,12 +1387,12 @@
     <t>HAFG18</t>
   </si>
   <si>
+    <t>2018</t>
+  </si>
+  <si>
     <t>2018-01-01</t>
   </si>
   <si>
-    <t>2018</t>
-  </si>
-  <si>
     <t>2018-12-31</t>
   </si>
   <si>
@@ -1513,12 +1513,12 @@
     <t>OEUR17</t>
   </si>
   <si>
+    <t>2017</t>
+  </si>
+  <si>
     <t>2017-01-01</t>
   </si>
   <si>
-    <t>2017</t>
-  </si>
-  <si>
     <t>2017-12-31</t>
   </si>
   <si>
@@ -1690,12 +1690,12 @@
     <t>OEUR16</t>
   </si>
   <si>
+    <t>2016</t>
+  </si>
+  <si>
     <t>2016-01-01</t>
   </si>
   <si>
-    <t>2016</t>
-  </si>
-  <si>
     <t>2016-12-31</t>
   </si>
   <si>
@@ -1858,12 +1858,12 @@
     <t>HAFG15</t>
   </si>
   <si>
+    <t>2015</t>
+  </si>
+  <si>
     <t>2015-01-01</t>
   </si>
   <si>
-    <t>2015</t>
-  </si>
-  <si>
     <t>Strategic response plan</t>
   </si>
   <si>
@@ -1996,12 +1996,12 @@
     <t>HAFG14</t>
   </si>
   <si>
+    <t>2014</t>
+  </si>
+  <si>
     <t>2014-01-01</t>
   </si>
   <si>
-    <t>2014</t>
-  </si>
-  <si>
     <t>2014-12-31</t>
   </si>
   <si>
@@ -2266,12 +2266,12 @@
     <t>CKEN12</t>
   </si>
   <si>
+    <t>2012</t>
+  </si>
+  <si>
     <t>2012-01-01</t>
   </si>
   <si>
-    <t>2012</t>
-  </si>
-  <si>
     <t>2012-12-31</t>
   </si>
   <si>
@@ -2377,12 +2377,12 @@
     <t>CKEN1113</t>
   </si>
   <si>
+    <t>2011</t>
+  </si>
+  <si>
     <t>2011-01-01</t>
   </si>
   <si>
-    <t>2011</t>
-  </si>
-  <si>
     <t>CAFG11</t>
   </si>
   <si>
@@ -2500,12 +2500,12 @@
     <t>CAFG10</t>
   </si>
   <si>
+    <t>2010</t>
+  </si>
+  <si>
     <t>2010-01-01</t>
   </si>
   <si>
-    <t>2010</t>
-  </si>
-  <si>
     <t>2010-12-31</t>
   </si>
   <si>
@@ -2644,12 +2644,12 @@
     <t>CAFG09</t>
   </si>
   <si>
+    <t>2009</t>
+  </si>
+  <si>
     <t>2009-01-01</t>
   </si>
   <si>
-    <t>2009</t>
-  </si>
-  <si>
     <t>2009-12-31</t>
   </si>
   <si>
@@ -2788,12 +2788,12 @@
     <t>OAFG08</t>
   </si>
   <si>
+    <t>2008</t>
+  </si>
+  <si>
     <t>2008-02-01</t>
   </si>
   <si>
-    <t>2008</t>
-  </si>
-  <si>
     <t>2008-06-30</t>
   </si>
   <si>
@@ -2962,12 +2962,12 @@
     <t>FBOL07</t>
   </si>
   <si>
+    <t>2007</t>
+  </si>
+  <si>
     <t>2007-02-22</t>
   </si>
   <si>
-    <t>2007</t>
-  </si>
-  <si>
     <t>2007-08-21</t>
   </si>
   <si>
@@ -3166,12 +3166,12 @@
     <t>OAFG06</t>
   </si>
   <si>
+    <t>2006</t>
+  </si>
+  <si>
     <t>2006-07-01</t>
   </si>
   <si>
-    <t>2006</t>
-  </si>
-  <si>
     <t>2006-12-31</t>
   </si>
   <si>
@@ -3328,12 +3328,12 @@
     <t>FAGO05</t>
   </si>
   <si>
+    <t>2005</t>
+  </si>
+  <si>
     <t>2005-04-01</t>
   </si>
   <si>
-    <t>2005</t>
-  </si>
-  <si>
     <t>2005-06-30</t>
   </si>
   <si>
@@ -3466,12 +3466,12 @@
     <t>OAFG04</t>
   </si>
   <si>
+    <t>2004</t>
+  </si>
+  <si>
     <t>2004-09-01</t>
   </si>
   <si>
-    <t>2004</t>
-  </si>
-  <si>
     <t>2004-12-31</t>
   </si>
   <si>
@@ -3619,12 +3619,12 @@
     <t>OAFG03</t>
   </si>
   <si>
+    <t>2003</t>
+  </si>
+  <si>
     <t>2003-01-01</t>
   </si>
   <si>
-    <t>2003</t>
-  </si>
-  <si>
     <t>2003-12-31</t>
   </si>
   <si>
@@ -3763,12 +3763,12 @@
     <t>CAFG0102</t>
   </si>
   <si>
+    <t>2002</t>
+  </si>
+  <si>
     <t>2001-10-01</t>
   </si>
   <si>
-    <t>2002</t>
-  </si>
-  <si>
     <t>2002-12-31</t>
   </si>
   <si>
@@ -3871,12 +3871,12 @@
     <t>CAFG01</t>
   </si>
   <si>
+    <t>2001</t>
+  </si>
+  <si>
     <t>2001-01-01</t>
   </si>
   <si>
-    <t>2001</t>
-  </si>
-  <si>
     <t>2001-09-30</t>
   </si>
   <si>
@@ -3955,10 +3955,10 @@
     <t>CAGO00</t>
   </si>
   <si>
+    <t>2000</t>
+  </si>
+  <si>
     <t>2000-01-01</t>
-  </si>
-  <si>
-    <t>2000</t>
   </si>
   <si>
     <t>2000-12-31</t>
@@ -4747,10 +4747,10 @@
         <v>7</v>
       </c>
       <c r="C20" t="s">
+        <v>8</v>
+      </c>
+      <c r="D20" t="s">
         <v>38</v>
-      </c>
-      <c r="D20" t="s">
-        <v>9</v>
       </c>
       <c r="E20" t="s">
         <v>10</v>
@@ -5027,10 +5027,10 @@
         <v>7</v>
       </c>
       <c r="C34" t="s">
+        <v>8</v>
+      </c>
+      <c r="D34" t="s">
         <v>54</v>
-      </c>
-      <c r="D34" t="s">
-        <v>9</v>
       </c>
       <c r="E34" t="s">
         <v>24</v>
@@ -5207,10 +5207,10 @@
         <v>7</v>
       </c>
       <c r="C43" t="s">
+        <v>8</v>
+      </c>
+      <c r="D43" t="s">
         <v>64</v>
-      </c>
-      <c r="D43" t="s">
-        <v>9</v>
       </c>
       <c r="E43" t="s">
         <v>15</v>
@@ -5327,10 +5327,10 @@
         <v>7</v>
       </c>
       <c r="C49" t="s">
+        <v>69</v>
+      </c>
+      <c r="D49" t="s">
         <v>74</v>
-      </c>
-      <c r="D49" t="s">
-        <v>70</v>
       </c>
       <c r="E49" t="s">
         <v>15</v>
@@ -5367,10 +5367,10 @@
         <v>7</v>
       </c>
       <c r="C51" t="s">
+        <v>69</v>
+      </c>
+      <c r="D51" t="s">
         <v>77</v>
-      </c>
-      <c r="D51" t="s">
-        <v>70</v>
       </c>
       <c r="E51" t="s">
         <v>15</v>
@@ -5507,10 +5507,10 @@
         <v>7</v>
       </c>
       <c r="C58" t="s">
+        <v>69</v>
+      </c>
+      <c r="D58" t="s">
         <v>85</v>
-      </c>
-      <c r="D58" t="s">
-        <v>70</v>
       </c>
       <c r="E58" t="s">
         <v>24</v>
@@ -5587,10 +5587,10 @@
         <v>7</v>
       </c>
       <c r="C62" t="s">
+        <v>69</v>
+      </c>
+      <c r="D62" t="s">
         <v>90</v>
-      </c>
-      <c r="D62" t="s">
-        <v>70</v>
       </c>
       <c r="E62" t="s">
         <v>15</v>
@@ -5607,10 +5607,10 @@
         <v>7</v>
       </c>
       <c r="C63" t="s">
+        <v>69</v>
+      </c>
+      <c r="D63" t="s">
         <v>90</v>
-      </c>
-      <c r="D63" t="s">
-        <v>70</v>
       </c>
       <c r="E63" t="s">
         <v>24</v>
@@ -5667,10 +5667,10 @@
         <v>7</v>
       </c>
       <c r="C66" t="s">
+        <v>69</v>
+      </c>
+      <c r="D66" t="s">
         <v>97</v>
-      </c>
-      <c r="D66" t="s">
-        <v>70</v>
       </c>
       <c r="E66" t="s">
         <v>24</v>
@@ -5707,10 +5707,10 @@
         <v>7</v>
       </c>
       <c r="C68" t="s">
+        <v>69</v>
+      </c>
+      <c r="D68" t="s">
         <v>100</v>
-      </c>
-      <c r="D68" t="s">
-        <v>70</v>
       </c>
       <c r="E68" t="s">
         <v>15</v>
@@ -5727,10 +5727,10 @@
         <v>7</v>
       </c>
       <c r="C69" t="s">
+        <v>69</v>
+      </c>
+      <c r="D69" t="s">
         <v>102</v>
-      </c>
-      <c r="D69" t="s">
-        <v>70</v>
       </c>
       <c r="E69" t="s">
         <v>24</v>
@@ -5787,10 +5787,10 @@
         <v>7</v>
       </c>
       <c r="C72" t="s">
+        <v>69</v>
+      </c>
+      <c r="D72" t="s">
         <v>106</v>
-      </c>
-      <c r="D72" t="s">
-        <v>70</v>
       </c>
       <c r="E72" t="s">
         <v>15</v>
@@ -5847,10 +5847,10 @@
         <v>7</v>
       </c>
       <c r="C75" t="s">
+        <v>69</v>
+      </c>
+      <c r="D75" t="s">
         <v>110</v>
-      </c>
-      <c r="D75" t="s">
-        <v>70</v>
       </c>
       <c r="E75" t="s">
         <v>15</v>
@@ -5967,10 +5967,10 @@
         <v>7</v>
       </c>
       <c r="C81" t="s">
+        <v>69</v>
+      </c>
+      <c r="D81" t="s">
         <v>85</v>
-      </c>
-      <c r="D81" t="s">
-        <v>70</v>
       </c>
       <c r="E81" t="s">
         <v>24</v>
@@ -6227,10 +6227,10 @@
         <v>7</v>
       </c>
       <c r="C94" t="s">
+        <v>69</v>
+      </c>
+      <c r="D94" t="s">
         <v>131</v>
-      </c>
-      <c r="D94" t="s">
-        <v>70</v>
       </c>
       <c r="E94" t="s">
         <v>15</v>
@@ -6267,10 +6267,10 @@
         <v>7</v>
       </c>
       <c r="C96" t="s">
+        <v>69</v>
+      </c>
+      <c r="D96" t="s">
         <v>134</v>
-      </c>
-      <c r="D96" t="s">
-        <v>70</v>
       </c>
       <c r="E96" t="s">
         <v>24</v>
@@ -6287,10 +6287,10 @@
         <v>7</v>
       </c>
       <c r="C97" t="s">
+        <v>69</v>
+      </c>
+      <c r="D97" t="s">
         <v>134</v>
-      </c>
-      <c r="D97" t="s">
-        <v>70</v>
       </c>
       <c r="E97" t="s">
         <v>24</v>
@@ -6467,10 +6467,10 @@
         <v>7</v>
       </c>
       <c r="C106" t="s">
+        <v>137</v>
+      </c>
+      <c r="D106" t="s">
         <v>148</v>
-      </c>
-      <c r="D106" t="s">
-        <v>138</v>
       </c>
       <c r="E106" t="s">
         <v>24</v>
@@ -6627,10 +6627,10 @@
         <v>7</v>
       </c>
       <c r="C114" t="s">
+        <v>137</v>
+      </c>
+      <c r="D114" t="s">
         <v>157</v>
-      </c>
-      <c r="D114" t="s">
-        <v>138</v>
       </c>
       <c r="E114" t="s">
         <v>24</v>
@@ -6687,10 +6687,10 @@
         <v>7</v>
       </c>
       <c r="C117" t="s">
+        <v>137</v>
+      </c>
+      <c r="D117" t="s">
         <v>161</v>
-      </c>
-      <c r="D117" t="s">
-        <v>138</v>
       </c>
       <c r="E117" t="s">
         <v>15</v>
@@ -6707,10 +6707,10 @@
         <v>7</v>
       </c>
       <c r="C118" t="s">
+        <v>137</v>
+      </c>
+      <c r="D118" t="s">
         <v>164</v>
-      </c>
-      <c r="D118" t="s">
-        <v>138</v>
       </c>
       <c r="E118" t="s">
         <v>15</v>
@@ -7007,10 +7007,10 @@
         <v>7</v>
       </c>
       <c r="C133" t="s">
+        <v>137</v>
+      </c>
+      <c r="D133" t="s">
         <v>181</v>
-      </c>
-      <c r="D133" t="s">
-        <v>138</v>
       </c>
       <c r="E133" t="s">
         <v>13</v>
@@ -7047,10 +7047,10 @@
         <v>7</v>
       </c>
       <c r="C135" t="s">
+        <v>137</v>
+      </c>
+      <c r="D135" t="s">
         <v>185</v>
-      </c>
-      <c r="D135" t="s">
-        <v>138</v>
       </c>
       <c r="E135" t="s">
         <v>24</v>
@@ -7087,10 +7087,10 @@
         <v>7</v>
       </c>
       <c r="C137" t="s">
+        <v>137</v>
+      </c>
+      <c r="D137" t="s">
         <v>188</v>
-      </c>
-      <c r="D137" t="s">
-        <v>138</v>
       </c>
       <c r="E137" t="s">
         <v>24</v>
@@ -7387,10 +7387,10 @@
         <v>7</v>
       </c>
       <c r="C152" t="s">
+        <v>197</v>
+      </c>
+      <c r="D152" t="s">
         <v>207</v>
-      </c>
-      <c r="D152" t="s">
-        <v>198</v>
       </c>
       <c r="E152" t="s">
         <v>15</v>
@@ -7487,10 +7487,10 @@
         <v>7</v>
       </c>
       <c r="C157" t="s">
+        <v>197</v>
+      </c>
+      <c r="D157" t="s">
         <v>214</v>
-      </c>
-      <c r="D157" t="s">
-        <v>198</v>
       </c>
       <c r="E157" t="s">
         <v>24</v>
@@ -7507,10 +7507,10 @@
         <v>112</v>
       </c>
       <c r="C158" t="s">
+        <v>197</v>
+      </c>
+      <c r="D158" t="s">
         <v>214</v>
-      </c>
-      <c r="D158" t="s">
-        <v>198</v>
       </c>
       <c r="E158" t="s">
         <v>24</v>
@@ -7667,10 +7667,10 @@
         <v>7</v>
       </c>
       <c r="C166" t="s">
+        <v>197</v>
+      </c>
+      <c r="D166" t="s">
         <v>226</v>
-      </c>
-      <c r="D166" t="s">
-        <v>198</v>
       </c>
       <c r="E166" t="s">
         <v>24</v>
@@ -7707,10 +7707,10 @@
         <v>7</v>
       </c>
       <c r="C168" t="s">
+        <v>197</v>
+      </c>
+      <c r="D168" t="s">
         <v>230</v>
-      </c>
-      <c r="D168" t="s">
-        <v>198</v>
       </c>
       <c r="E168" t="s">
         <v>24</v>
@@ -7827,10 +7827,10 @@
         <v>7</v>
       </c>
       <c r="C174" t="s">
+        <v>197</v>
+      </c>
+      <c r="D174" t="s">
         <v>238</v>
-      </c>
-      <c r="D174" t="s">
-        <v>198</v>
       </c>
       <c r="E174" t="s">
         <v>15</v>
@@ -7847,10 +7847,10 @@
         <v>112</v>
       </c>
       <c r="C175" t="s">
+        <v>197</v>
+      </c>
+      <c r="D175" t="s">
         <v>238</v>
-      </c>
-      <c r="D175" t="s">
-        <v>198</v>
       </c>
       <c r="E175" t="s">
         <v>15</v>
@@ -7867,10 +7867,10 @@
         <v>7</v>
       </c>
       <c r="C176" t="s">
+        <v>197</v>
+      </c>
+      <c r="D176" t="s">
         <v>242</v>
-      </c>
-      <c r="D176" t="s">
-        <v>198</v>
       </c>
       <c r="E176" t="s">
         <v>15</v>
@@ -8027,10 +8027,10 @@
         <v>7</v>
       </c>
       <c r="C184" t="s">
+        <v>197</v>
+      </c>
+      <c r="D184" t="s">
         <v>252</v>
-      </c>
-      <c r="D184" t="s">
-        <v>198</v>
       </c>
       <c r="E184" t="s">
         <v>15</v>
@@ -8127,10 +8127,10 @@
         <v>7</v>
       </c>
       <c r="C189" t="s">
+        <v>197</v>
+      </c>
+      <c r="D189" t="s">
         <v>258</v>
-      </c>
-      <c r="D189" t="s">
-        <v>198</v>
       </c>
       <c r="E189" t="s">
         <v>24</v>
@@ -8167,10 +8167,10 @@
         <v>7</v>
       </c>
       <c r="C191" t="s">
+        <v>197</v>
+      </c>
+      <c r="D191" t="s">
         <v>258</v>
-      </c>
-      <c r="D191" t="s">
-        <v>198</v>
       </c>
       <c r="E191" t="s">
         <v>13</v>
@@ -8247,10 +8247,10 @@
         <v>7</v>
       </c>
       <c r="C195" t="s">
+        <v>265</v>
+      </c>
+      <c r="D195" t="s">
         <v>269</v>
-      </c>
-      <c r="D195" t="s">
-        <v>266</v>
       </c>
       <c r="E195" t="s">
         <v>19</v>
@@ -8267,10 +8267,10 @@
         <v>7</v>
       </c>
       <c r="C196" t="s">
+        <v>265</v>
+      </c>
+      <c r="D196" t="s">
         <v>269</v>
-      </c>
-      <c r="D196" t="s">
-        <v>266</v>
       </c>
       <c r="E196" t="s">
         <v>13</v>
@@ -8287,10 +8287,10 @@
         <v>7</v>
       </c>
       <c r="C197" t="s">
+        <v>265</v>
+      </c>
+      <c r="D197" t="s">
         <v>269</v>
-      </c>
-      <c r="D197" t="s">
-        <v>266</v>
       </c>
       <c r="E197" t="s">
         <v>19</v>
@@ -8307,10 +8307,10 @@
         <v>7</v>
       </c>
       <c r="C198" t="s">
+        <v>265</v>
+      </c>
+      <c r="D198" t="s">
         <v>269</v>
-      </c>
-      <c r="D198" t="s">
-        <v>266</v>
       </c>
       <c r="E198" t="s">
         <v>19</v>
@@ -8327,10 +8327,10 @@
         <v>7</v>
       </c>
       <c r="C199" t="s">
+        <v>265</v>
+      </c>
+      <c r="D199" t="s">
         <v>269</v>
-      </c>
-      <c r="D199" t="s">
-        <v>266</v>
       </c>
       <c r="E199" t="s">
         <v>13</v>
@@ -8347,10 +8347,10 @@
         <v>7</v>
       </c>
       <c r="C200" t="s">
+        <v>265</v>
+      </c>
+      <c r="D200" t="s">
         <v>269</v>
-      </c>
-      <c r="D200" t="s">
-        <v>266</v>
       </c>
       <c r="E200" t="s">
         <v>19</v>
@@ -8367,10 +8367,10 @@
         <v>7</v>
       </c>
       <c r="C201" t="s">
+        <v>265</v>
+      </c>
+      <c r="D201" t="s">
         <v>269</v>
-      </c>
-      <c r="D201" t="s">
-        <v>266</v>
       </c>
       <c r="E201" t="s">
         <v>19</v>
@@ -8387,10 +8387,10 @@
         <v>7</v>
       </c>
       <c r="C202" t="s">
+        <v>265</v>
+      </c>
+      <c r="D202" t="s">
         <v>269</v>
-      </c>
-      <c r="D202" t="s">
-        <v>266</v>
       </c>
       <c r="E202" t="s">
         <v>19</v>
@@ -8407,10 +8407,10 @@
         <v>7</v>
       </c>
       <c r="C203" t="s">
+        <v>265</v>
+      </c>
+      <c r="D203" t="s">
         <v>269</v>
-      </c>
-      <c r="D203" t="s">
-        <v>266</v>
       </c>
       <c r="E203" t="s">
         <v>19</v>
@@ -8427,10 +8427,10 @@
         <v>7</v>
       </c>
       <c r="C204" t="s">
+        <v>265</v>
+      </c>
+      <c r="D204" t="s">
         <v>269</v>
-      </c>
-      <c r="D204" t="s">
-        <v>266</v>
       </c>
       <c r="E204" t="s">
         <v>19</v>
@@ -8447,10 +8447,10 @@
         <v>7</v>
       </c>
       <c r="C205" t="s">
+        <v>265</v>
+      </c>
+      <c r="D205" t="s">
         <v>269</v>
-      </c>
-      <c r="D205" t="s">
-        <v>266</v>
       </c>
       <c r="E205" t="s">
         <v>13</v>
@@ -8467,10 +8467,10 @@
         <v>7</v>
       </c>
       <c r="C206" t="s">
+        <v>265</v>
+      </c>
+      <c r="D206" t="s">
         <v>281</v>
-      </c>
-      <c r="D206" t="s">
-        <v>266</v>
       </c>
       <c r="E206" t="s">
         <v>19</v>
@@ -8487,10 +8487,10 @@
         <v>112</v>
       </c>
       <c r="C207" t="s">
+        <v>265</v>
+      </c>
+      <c r="D207" t="s">
         <v>281</v>
-      </c>
-      <c r="D207" t="s">
-        <v>266</v>
       </c>
       <c r="E207" t="s">
         <v>19</v>
@@ -8507,10 +8507,10 @@
         <v>7</v>
       </c>
       <c r="C208" t="s">
+        <v>265</v>
+      </c>
+      <c r="D208" t="s">
         <v>284</v>
-      </c>
-      <c r="D208" t="s">
-        <v>266</v>
       </c>
       <c r="E208" t="s">
         <v>24</v>
@@ -8527,10 +8527,10 @@
         <v>7</v>
       </c>
       <c r="C209" t="s">
+        <v>265</v>
+      </c>
+      <c r="D209" t="s">
         <v>269</v>
-      </c>
-      <c r="D209" t="s">
-        <v>266</v>
       </c>
       <c r="E209" t="s">
         <v>19</v>
@@ -8547,10 +8547,10 @@
         <v>7</v>
       </c>
       <c r="C210" t="s">
+        <v>265</v>
+      </c>
+      <c r="D210" t="s">
         <v>281</v>
-      </c>
-      <c r="D210" t="s">
-        <v>266</v>
       </c>
       <c r="E210" t="s">
         <v>19</v>
@@ -8567,10 +8567,10 @@
         <v>112</v>
       </c>
       <c r="C211" t="s">
+        <v>265</v>
+      </c>
+      <c r="D211" t="s">
         <v>281</v>
-      </c>
-      <c r="D211" t="s">
-        <v>266</v>
       </c>
       <c r="E211" t="s">
         <v>19</v>
@@ -8587,10 +8587,10 @@
         <v>7</v>
       </c>
       <c r="C212" t="s">
+        <v>265</v>
+      </c>
+      <c r="D212" t="s">
         <v>290</v>
-      </c>
-      <c r="D212" t="s">
-        <v>266</v>
       </c>
       <c r="E212" t="s">
         <v>24</v>
@@ -8607,10 +8607,10 @@
         <v>7</v>
       </c>
       <c r="C213" t="s">
+        <v>265</v>
+      </c>
+      <c r="D213" t="s">
         <v>269</v>
-      </c>
-      <c r="D213" t="s">
-        <v>266</v>
       </c>
       <c r="E213" t="s">
         <v>19</v>
@@ -8627,10 +8627,10 @@
         <v>7</v>
       </c>
       <c r="C214" t="s">
+        <v>265</v>
+      </c>
+      <c r="D214" t="s">
         <v>294</v>
-      </c>
-      <c r="D214" t="s">
-        <v>266</v>
       </c>
       <c r="E214" t="s">
         <v>24</v>
@@ -8647,10 +8647,10 @@
         <v>7</v>
       </c>
       <c r="C215" t="s">
+        <v>265</v>
+      </c>
+      <c r="D215" t="s">
         <v>281</v>
-      </c>
-      <c r="D215" t="s">
-        <v>266</v>
       </c>
       <c r="E215" t="s">
         <v>19</v>
@@ -8667,10 +8667,10 @@
         <v>112</v>
       </c>
       <c r="C216" t="s">
+        <v>265</v>
+      </c>
+      <c r="D216" t="s">
         <v>281</v>
-      </c>
-      <c r="D216" t="s">
-        <v>266</v>
       </c>
       <c r="E216" t="s">
         <v>19</v>
@@ -8687,10 +8687,10 @@
         <v>7</v>
       </c>
       <c r="C217" t="s">
+        <v>265</v>
+      </c>
+      <c r="D217" t="s">
         <v>269</v>
-      </c>
-      <c r="D217" t="s">
-        <v>266</v>
       </c>
       <c r="E217" t="s">
         <v>19</v>
@@ -8707,10 +8707,10 @@
         <v>7</v>
       </c>
       <c r="C218" t="s">
+        <v>265</v>
+      </c>
+      <c r="D218" t="s">
         <v>300</v>
-      </c>
-      <c r="D218" t="s">
-        <v>266</v>
       </c>
       <c r="E218" t="s">
         <v>24</v>
@@ -8727,10 +8727,10 @@
         <v>7</v>
       </c>
       <c r="C219" t="s">
+        <v>265</v>
+      </c>
+      <c r="D219" t="s">
         <v>302</v>
-      </c>
-      <c r="D219" t="s">
-        <v>266</v>
       </c>
       <c r="E219" t="s">
         <v>15</v>
@@ -8747,10 +8747,10 @@
         <v>7</v>
       </c>
       <c r="C220" t="s">
+        <v>265</v>
+      </c>
+      <c r="D220" t="s">
         <v>269</v>
-      </c>
-      <c r="D220" t="s">
-        <v>266</v>
       </c>
       <c r="E220" t="s">
         <v>19</v>
@@ -8767,10 +8767,10 @@
         <v>112</v>
       </c>
       <c r="C221" t="s">
+        <v>265</v>
+      </c>
+      <c r="D221" t="s">
         <v>269</v>
-      </c>
-      <c r="D221" t="s">
-        <v>266</v>
       </c>
       <c r="E221" t="s">
         <v>24</v>
@@ -8787,10 +8787,10 @@
         <v>7</v>
       </c>
       <c r="C222" t="s">
+        <v>265</v>
+      </c>
+      <c r="D222" t="s">
         <v>269</v>
-      </c>
-      <c r="D222" t="s">
-        <v>266</v>
       </c>
       <c r="E222" t="s">
         <v>24</v>
@@ -8807,10 +8807,10 @@
         <v>7</v>
       </c>
       <c r="C223" t="s">
+        <v>265</v>
+      </c>
+      <c r="D223" t="s">
         <v>269</v>
-      </c>
-      <c r="D223" t="s">
-        <v>266</v>
       </c>
       <c r="E223" t="s">
         <v>19</v>
@@ -8827,10 +8827,10 @@
         <v>7</v>
       </c>
       <c r="C224" t="s">
+        <v>265</v>
+      </c>
+      <c r="D224" t="s">
         <v>269</v>
-      </c>
-      <c r="D224" t="s">
-        <v>266</v>
       </c>
       <c r="E224" t="s">
         <v>19</v>
@@ -8847,10 +8847,10 @@
         <v>7</v>
       </c>
       <c r="C225" t="s">
+        <v>265</v>
+      </c>
+      <c r="D225" t="s">
         <v>269</v>
-      </c>
-      <c r="D225" t="s">
-        <v>266</v>
       </c>
       <c r="E225" t="s">
         <v>19</v>
@@ -8867,10 +8867,10 @@
         <v>7</v>
       </c>
       <c r="C226" t="s">
+        <v>265</v>
+      </c>
+      <c r="D226" t="s">
         <v>311</v>
-      </c>
-      <c r="D226" t="s">
-        <v>266</v>
       </c>
       <c r="E226" t="s">
         <v>15</v>
@@ -8887,10 +8887,10 @@
         <v>7</v>
       </c>
       <c r="C227" t="s">
+        <v>265</v>
+      </c>
+      <c r="D227" t="s">
         <v>313</v>
-      </c>
-      <c r="D227" t="s">
-        <v>266</v>
       </c>
       <c r="E227" t="s">
         <v>15</v>
@@ -8907,10 +8907,10 @@
         <v>7</v>
       </c>
       <c r="C228" t="s">
+        <v>265</v>
+      </c>
+      <c r="D228" t="s">
         <v>269</v>
-      </c>
-      <c r="D228" t="s">
-        <v>266</v>
       </c>
       <c r="E228" t="s">
         <v>19</v>
@@ -8927,10 +8927,10 @@
         <v>7</v>
       </c>
       <c r="C229" t="s">
+        <v>265</v>
+      </c>
+      <c r="D229" t="s">
         <v>269</v>
-      </c>
-      <c r="D229" t="s">
-        <v>266</v>
       </c>
       <c r="E229" t="s">
         <v>19</v>
@@ -8947,10 +8947,10 @@
         <v>7</v>
       </c>
       <c r="C230" t="s">
+        <v>265</v>
+      </c>
+      <c r="D230" t="s">
         <v>313</v>
-      </c>
-      <c r="D230" t="s">
-        <v>266</v>
       </c>
       <c r="E230" t="s">
         <v>24</v>
@@ -8967,10 +8967,10 @@
         <v>112</v>
       </c>
       <c r="C231" t="s">
+        <v>265</v>
+      </c>
+      <c r="D231" t="s">
         <v>313</v>
-      </c>
-      <c r="D231" t="s">
-        <v>266</v>
       </c>
       <c r="E231" t="s">
         <v>15</v>
@@ -8987,10 +8987,10 @@
         <v>7</v>
       </c>
       <c r="C232" t="s">
+        <v>265</v>
+      </c>
+      <c r="D232" t="s">
         <v>269</v>
-      </c>
-      <c r="D232" t="s">
-        <v>266</v>
       </c>
       <c r="E232" t="s">
         <v>19</v>
@@ -9007,10 +9007,10 @@
         <v>7</v>
       </c>
       <c r="C233" t="s">
+        <v>265</v>
+      </c>
+      <c r="D233" t="s">
         <v>269</v>
-      </c>
-      <c r="D233" t="s">
-        <v>266</v>
       </c>
       <c r="E233" t="s">
         <v>19</v>
@@ -9027,10 +9027,10 @@
         <v>7</v>
       </c>
       <c r="C234" t="s">
+        <v>265</v>
+      </c>
+      <c r="D234" t="s">
         <v>269</v>
-      </c>
-      <c r="D234" t="s">
-        <v>266</v>
       </c>
       <c r="E234" t="s">
         <v>13</v>
@@ -9047,10 +9047,10 @@
         <v>7</v>
       </c>
       <c r="C235" t="s">
+        <v>265</v>
+      </c>
+      <c r="D235" t="s">
         <v>269</v>
-      </c>
-      <c r="D235" t="s">
-        <v>266</v>
       </c>
       <c r="E235" t="s">
         <v>13</v>
@@ -9067,10 +9067,10 @@
         <v>7</v>
       </c>
       <c r="C236" t="s">
+        <v>265</v>
+      </c>
+      <c r="D236" t="s">
         <v>269</v>
-      </c>
-      <c r="D236" t="s">
-        <v>266</v>
       </c>
       <c r="E236" t="s">
         <v>19</v>
@@ -9087,10 +9087,10 @@
         <v>7</v>
       </c>
       <c r="C237" t="s">
+        <v>265</v>
+      </c>
+      <c r="D237" t="s">
         <v>269</v>
-      </c>
-      <c r="D237" t="s">
-        <v>266</v>
       </c>
       <c r="E237" t="s">
         <v>19</v>
@@ -9107,10 +9107,10 @@
         <v>7</v>
       </c>
       <c r="C238" t="s">
+        <v>265</v>
+      </c>
+      <c r="D238" t="s">
         <v>269</v>
-      </c>
-      <c r="D238" t="s">
-        <v>266</v>
       </c>
       <c r="E238" t="s">
         <v>13</v>
@@ -9127,10 +9127,10 @@
         <v>7</v>
       </c>
       <c r="C239" t="s">
+        <v>265</v>
+      </c>
+      <c r="D239" t="s">
         <v>269</v>
-      </c>
-      <c r="D239" t="s">
-        <v>266</v>
       </c>
       <c r="E239" t="s">
         <v>19</v>
@@ -9147,10 +9147,10 @@
         <v>7</v>
       </c>
       <c r="C240" t="s">
+        <v>265</v>
+      </c>
+      <c r="D240" t="s">
         <v>269</v>
-      </c>
-      <c r="D240" t="s">
-        <v>266</v>
       </c>
       <c r="E240" t="s">
         <v>19</v>
@@ -9167,10 +9167,10 @@
         <v>7</v>
       </c>
       <c r="C241" t="s">
+        <v>265</v>
+      </c>
+      <c r="D241" t="s">
         <v>269</v>
-      </c>
-      <c r="D241" t="s">
-        <v>266</v>
       </c>
       <c r="E241" t="s">
         <v>13</v>
@@ -9187,10 +9187,10 @@
         <v>7</v>
       </c>
       <c r="C242" t="s">
+        <v>265</v>
+      </c>
+      <c r="D242" t="s">
         <v>269</v>
-      </c>
-      <c r="D242" t="s">
-        <v>266</v>
       </c>
       <c r="E242" t="s">
         <v>19</v>
@@ -9207,10 +9207,10 @@
         <v>7</v>
       </c>
       <c r="C243" t="s">
+        <v>265</v>
+      </c>
+      <c r="D243" t="s">
         <v>269</v>
-      </c>
-      <c r="D243" t="s">
-        <v>266</v>
       </c>
       <c r="E243" t="s">
         <v>19</v>
@@ -9227,10 +9227,10 @@
         <v>7</v>
       </c>
       <c r="C244" t="s">
+        <v>265</v>
+      </c>
+      <c r="D244" t="s">
         <v>269</v>
-      </c>
-      <c r="D244" t="s">
-        <v>266</v>
       </c>
       <c r="E244" t="s">
         <v>19</v>
@@ -9247,10 +9247,10 @@
         <v>7</v>
       </c>
       <c r="C245" t="s">
+        <v>265</v>
+      </c>
+      <c r="D245" t="s">
         <v>269</v>
-      </c>
-      <c r="D245" t="s">
-        <v>266</v>
       </c>
       <c r="E245" t="s">
         <v>19</v>
@@ -9287,10 +9287,10 @@
         <v>7</v>
       </c>
       <c r="C247" t="s">
+        <v>333</v>
+      </c>
+      <c r="D247" t="s">
         <v>337</v>
-      </c>
-      <c r="D247" t="s">
-        <v>334</v>
       </c>
       <c r="E247" t="s">
         <v>15</v>
@@ -9327,10 +9327,10 @@
         <v>7</v>
       </c>
       <c r="C249" t="s">
+        <v>333</v>
+      </c>
+      <c r="D249" t="s">
         <v>337</v>
-      </c>
-      <c r="D249" t="s">
-        <v>334</v>
       </c>
       <c r="E249" t="s">
         <v>15</v>
@@ -9407,10 +9407,10 @@
         <v>7</v>
       </c>
       <c r="C253" t="s">
+        <v>333</v>
+      </c>
+      <c r="D253" t="s">
         <v>344</v>
-      </c>
-      <c r="D253" t="s">
-        <v>334</v>
       </c>
       <c r="E253" t="s">
         <v>15</v>
@@ -9447,10 +9447,10 @@
         <v>7</v>
       </c>
       <c r="C255" t="s">
+        <v>333</v>
+      </c>
+      <c r="D255" t="s">
         <v>347</v>
-      </c>
-      <c r="D255" t="s">
-        <v>334</v>
       </c>
       <c r="E255" t="s">
         <v>19</v>
@@ -9507,10 +9507,10 @@
         <v>7</v>
       </c>
       <c r="C258" t="s">
+        <v>333</v>
+      </c>
+      <c r="D258" t="s">
         <v>337</v>
-      </c>
-      <c r="D258" t="s">
-        <v>334</v>
       </c>
       <c r="E258" t="s">
         <v>15</v>
@@ -9527,10 +9527,10 @@
         <v>7</v>
       </c>
       <c r="C259" t="s">
+        <v>333</v>
+      </c>
+      <c r="D259" t="s">
         <v>337</v>
-      </c>
-      <c r="D259" t="s">
-        <v>334</v>
       </c>
       <c r="E259" t="s">
         <v>15</v>
@@ -9547,10 +9547,10 @@
         <v>112</v>
       </c>
       <c r="C260" t="s">
+        <v>333</v>
+      </c>
+      <c r="D260" t="s">
         <v>353</v>
-      </c>
-      <c r="D260" t="s">
-        <v>334</v>
       </c>
       <c r="E260" t="s">
         <v>19</v>
@@ -9607,10 +9607,10 @@
         <v>7</v>
       </c>
       <c r="C263" t="s">
+        <v>333</v>
+      </c>
+      <c r="D263" t="s">
         <v>357</v>
-      </c>
-      <c r="D263" t="s">
-        <v>334</v>
       </c>
       <c r="E263" t="s">
         <v>24</v>
@@ -9627,10 +9627,10 @@
         <v>7</v>
       </c>
       <c r="C264" t="s">
+        <v>333</v>
+      </c>
+      <c r="D264" t="s">
         <v>337</v>
-      </c>
-      <c r="D264" t="s">
-        <v>334</v>
       </c>
       <c r="E264" t="s">
         <v>15</v>
@@ -9647,10 +9647,10 @@
         <v>112</v>
       </c>
       <c r="C265" t="s">
+        <v>333</v>
+      </c>
+      <c r="D265" t="s">
         <v>337</v>
-      </c>
-      <c r="D265" t="s">
-        <v>334</v>
       </c>
       <c r="E265" t="s">
         <v>15</v>
@@ -9687,10 +9687,10 @@
         <v>7</v>
       </c>
       <c r="C267" t="s">
+        <v>333</v>
+      </c>
+      <c r="D267" t="s">
         <v>337</v>
-      </c>
-      <c r="D267" t="s">
-        <v>334</v>
       </c>
       <c r="E267" t="s">
         <v>15</v>
@@ -9727,10 +9727,10 @@
         <v>7</v>
       </c>
       <c r="C269" t="s">
+        <v>333</v>
+      </c>
+      <c r="D269" t="s">
         <v>337</v>
-      </c>
-      <c r="D269" t="s">
-        <v>334</v>
       </c>
       <c r="E269" t="s">
         <v>15</v>
@@ -9747,10 +9747,10 @@
         <v>7</v>
       </c>
       <c r="C270" t="s">
+        <v>333</v>
+      </c>
+      <c r="D270" t="s">
         <v>353</v>
-      </c>
-      <c r="D270" t="s">
-        <v>334</v>
       </c>
       <c r="E270" t="s">
         <v>15</v>
@@ -9767,10 +9767,10 @@
         <v>112</v>
       </c>
       <c r="C271" t="s">
+        <v>333</v>
+      </c>
+      <c r="D271" t="s">
         <v>337</v>
-      </c>
-      <c r="D271" t="s">
-        <v>334</v>
       </c>
       <c r="E271" t="s">
         <v>15</v>
@@ -9787,10 +9787,10 @@
         <v>7</v>
       </c>
       <c r="C272" t="s">
+        <v>333</v>
+      </c>
+      <c r="D272" t="s">
         <v>337</v>
-      </c>
-      <c r="D272" t="s">
-        <v>334</v>
       </c>
       <c r="E272" t="s">
         <v>15</v>
@@ -9827,10 +9827,10 @@
         <v>7</v>
       </c>
       <c r="C274" t="s">
+        <v>333</v>
+      </c>
+      <c r="D274" t="s">
         <v>337</v>
-      </c>
-      <c r="D274" t="s">
-        <v>334</v>
       </c>
       <c r="E274" t="s">
         <v>15</v>
@@ -9867,10 +9867,10 @@
         <v>7</v>
       </c>
       <c r="C276" t="s">
+        <v>333</v>
+      </c>
+      <c r="D276" t="s">
         <v>337</v>
-      </c>
-      <c r="D276" t="s">
-        <v>334</v>
       </c>
       <c r="E276" t="s">
         <v>15</v>
@@ -9887,10 +9887,10 @@
         <v>7</v>
       </c>
       <c r="C277" t="s">
+        <v>333</v>
+      </c>
+      <c r="D277" t="s">
         <v>373</v>
-      </c>
-      <c r="D277" t="s">
-        <v>334</v>
       </c>
       <c r="E277" t="s">
         <v>15</v>
@@ -9907,10 +9907,10 @@
         <v>7</v>
       </c>
       <c r="C278" t="s">
+        <v>333</v>
+      </c>
+      <c r="D278" t="s">
         <v>375</v>
-      </c>
-      <c r="D278" t="s">
-        <v>334</v>
       </c>
       <c r="E278" t="s">
         <v>24</v>
@@ -9927,10 +9927,10 @@
         <v>7</v>
       </c>
       <c r="C279" t="s">
+        <v>333</v>
+      </c>
+      <c r="D279" t="s">
         <v>337</v>
-      </c>
-      <c r="D279" t="s">
-        <v>334</v>
       </c>
       <c r="E279" t="s">
         <v>15</v>
@@ -9947,10 +9947,10 @@
         <v>7</v>
       </c>
       <c r="C280" t="s">
+        <v>333</v>
+      </c>
+      <c r="D280" t="s">
         <v>379</v>
-      </c>
-      <c r="D280" t="s">
-        <v>334</v>
       </c>
       <c r="E280" t="s">
         <v>24</v>
@@ -9967,10 +9967,10 @@
         <v>7</v>
       </c>
       <c r="C281" t="s">
+        <v>333</v>
+      </c>
+      <c r="D281" t="s">
         <v>337</v>
-      </c>
-      <c r="D281" t="s">
-        <v>334</v>
       </c>
       <c r="E281" t="s">
         <v>15</v>
@@ -10027,10 +10027,10 @@
         <v>7</v>
       </c>
       <c r="C284" t="s">
+        <v>333</v>
+      </c>
+      <c r="D284" t="s">
         <v>337</v>
-      </c>
-      <c r="D284" t="s">
-        <v>334</v>
       </c>
       <c r="E284" t="s">
         <v>15</v>
@@ -10127,10 +10127,10 @@
         <v>7</v>
       </c>
       <c r="C289" t="s">
+        <v>333</v>
+      </c>
+      <c r="D289" t="s">
         <v>373</v>
-      </c>
-      <c r="D289" t="s">
-        <v>334</v>
       </c>
       <c r="E289" t="s">
         <v>15</v>
@@ -10147,10 +10147,10 @@
         <v>7</v>
       </c>
       <c r="C290" t="s">
+        <v>333</v>
+      </c>
+      <c r="D290" t="s">
         <v>337</v>
-      </c>
-      <c r="D290" t="s">
-        <v>334</v>
       </c>
       <c r="E290" t="s">
         <v>15</v>
@@ -10207,10 +10207,10 @@
         <v>7</v>
       </c>
       <c r="C293" t="s">
+        <v>333</v>
+      </c>
+      <c r="D293" t="s">
         <v>373</v>
-      </c>
-      <c r="D293" t="s">
-        <v>334</v>
       </c>
       <c r="E293" t="s">
         <v>15</v>
@@ -10227,10 +10227,10 @@
         <v>7</v>
       </c>
       <c r="C294" t="s">
+        <v>333</v>
+      </c>
+      <c r="D294" t="s">
         <v>337</v>
-      </c>
-      <c r="D294" t="s">
-        <v>334</v>
       </c>
       <c r="E294" t="s">
         <v>15</v>
@@ -10367,10 +10367,10 @@
         <v>7</v>
       </c>
       <c r="C301" t="s">
+        <v>333</v>
+      </c>
+      <c r="D301" t="s">
         <v>337</v>
-      </c>
-      <c r="D301" t="s">
-        <v>334</v>
       </c>
       <c r="E301" t="s">
         <v>15</v>
@@ -10387,10 +10387,10 @@
         <v>7</v>
       </c>
       <c r="C302" t="s">
+        <v>333</v>
+      </c>
+      <c r="D302" t="s">
         <v>337</v>
-      </c>
-      <c r="D302" t="s">
-        <v>334</v>
       </c>
       <c r="E302" t="s">
         <v>15</v>
@@ -10407,10 +10407,10 @@
         <v>7</v>
       </c>
       <c r="C303" t="s">
+        <v>333</v>
+      </c>
+      <c r="D303" t="s">
         <v>337</v>
-      </c>
-      <c r="D303" t="s">
-        <v>334</v>
       </c>
       <c r="E303" t="s">
         <v>15</v>
@@ -10447,10 +10447,10 @@
         <v>7</v>
       </c>
       <c r="C305" t="s">
+        <v>333</v>
+      </c>
+      <c r="D305" t="s">
         <v>337</v>
-      </c>
-      <c r="D305" t="s">
-        <v>334</v>
       </c>
       <c r="E305" t="s">
         <v>15</v>
@@ -10507,10 +10507,10 @@
         <v>7</v>
       </c>
       <c r="C308" t="s">
+        <v>333</v>
+      </c>
+      <c r="D308" t="s">
         <v>409</v>
-      </c>
-      <c r="D308" t="s">
-        <v>334</v>
       </c>
       <c r="E308" t="s">
         <v>15</v>
@@ -10527,10 +10527,10 @@
         <v>7</v>
       </c>
       <c r="C309" t="s">
+        <v>333</v>
+      </c>
+      <c r="D309" t="s">
         <v>337</v>
-      </c>
-      <c r="D309" t="s">
-        <v>334</v>
       </c>
       <c r="E309" t="s">
         <v>15</v>
@@ -10827,10 +10827,10 @@
         <v>7</v>
       </c>
       <c r="C324" t="s">
+        <v>413</v>
+      </c>
+      <c r="D324" t="s">
         <v>429</v>
-      </c>
-      <c r="D324" t="s">
-        <v>414</v>
       </c>
       <c r="E324" t="s">
         <v>15</v>
@@ -11227,10 +11227,10 @@
         <v>7</v>
       </c>
       <c r="C344" t="s">
+        <v>413</v>
+      </c>
+      <c r="D344" t="s">
         <v>452</v>
-      </c>
-      <c r="D344" t="s">
-        <v>414</v>
       </c>
       <c r="E344" t="s">
         <v>24</v>
@@ -11247,10 +11247,10 @@
         <v>112</v>
       </c>
       <c r="C345" t="s">
+        <v>413</v>
+      </c>
+      <c r="D345" t="s">
         <v>455</v>
-      </c>
-      <c r="D345" t="s">
-        <v>414</v>
       </c>
       <c r="E345" t="s">
         <v>24</v>
@@ -11287,10 +11287,10 @@
         <v>112</v>
       </c>
       <c r="C347" t="s">
+        <v>457</v>
+      </c>
+      <c r="D347" t="s">
         <v>461</v>
-      </c>
-      <c r="D347" t="s">
-        <v>458</v>
       </c>
       <c r="E347" t="s">
         <v>15</v>
@@ -11487,10 +11487,10 @@
         <v>7</v>
       </c>
       <c r="C357" t="s">
+        <v>457</v>
+      </c>
+      <c r="D357" t="s">
         <v>472</v>
-      </c>
-      <c r="D357" t="s">
-        <v>458</v>
       </c>
       <c r="E357" t="s">
         <v>15</v>
@@ -11687,10 +11687,10 @@
         <v>7</v>
       </c>
       <c r="C367" t="s">
+        <v>457</v>
+      </c>
+      <c r="D367" t="s">
         <v>483</v>
-      </c>
-      <c r="D367" t="s">
-        <v>458</v>
       </c>
       <c r="E367" t="s">
         <v>15</v>
@@ -11707,10 +11707,10 @@
         <v>7</v>
       </c>
       <c r="C368" t="s">
+        <v>457</v>
+      </c>
+      <c r="D368" t="s">
         <v>461</v>
-      </c>
-      <c r="D368" t="s">
-        <v>458</v>
       </c>
       <c r="E368" t="s">
         <v>13</v>
@@ -11807,10 +11807,10 @@
         <v>7</v>
       </c>
       <c r="C373" t="s">
+        <v>457</v>
+      </c>
+      <c r="D373" t="s">
         <v>491</v>
-      </c>
-      <c r="D373" t="s">
-        <v>458</v>
       </c>
       <c r="E373" t="s">
         <v>19</v>
@@ -11847,10 +11847,10 @@
         <v>112</v>
       </c>
       <c r="C375" t="s">
+        <v>457</v>
+      </c>
+      <c r="D375" t="s">
         <v>491</v>
-      </c>
-      <c r="D375" t="s">
-        <v>458</v>
       </c>
       <c r="E375" t="s">
         <v>19</v>
@@ -11967,10 +11967,10 @@
         <v>112</v>
       </c>
       <c r="C381" t="s">
+        <v>499</v>
+      </c>
+      <c r="D381" t="s">
         <v>504</v>
-      </c>
-      <c r="D381" t="s">
-        <v>500</v>
       </c>
       <c r="E381" t="s">
         <v>13</v>
@@ -12087,10 +12087,10 @@
         <v>7</v>
       </c>
       <c r="C387" t="s">
+        <v>499</v>
+      </c>
+      <c r="D387" t="s">
         <v>511</v>
-      </c>
-      <c r="D387" t="s">
-        <v>500</v>
       </c>
       <c r="E387" t="s">
         <v>15</v>
@@ -12107,10 +12107,10 @@
         <v>7</v>
       </c>
       <c r="C388" t="s">
+        <v>499</v>
+      </c>
+      <c r="D388" t="s">
         <v>513</v>
-      </c>
-      <c r="D388" t="s">
-        <v>500</v>
       </c>
       <c r="E388" t="s">
         <v>19</v>
@@ -12147,10 +12147,10 @@
         <v>7</v>
       </c>
       <c r="C390" t="s">
+        <v>499</v>
+      </c>
+      <c r="D390" t="s">
         <v>516</v>
-      </c>
-      <c r="D390" t="s">
-        <v>500</v>
       </c>
       <c r="E390" t="s">
         <v>24</v>
@@ -12227,10 +12227,10 @@
         <v>112</v>
       </c>
       <c r="C394" t="s">
+        <v>499</v>
+      </c>
+      <c r="D394" t="s">
         <v>522</v>
-      </c>
-      <c r="D394" t="s">
-        <v>500</v>
       </c>
       <c r="E394" t="s">
         <v>15</v>
@@ -12267,10 +12267,10 @@
         <v>7</v>
       </c>
       <c r="C396" t="s">
+        <v>499</v>
+      </c>
+      <c r="D396" t="s">
         <v>525</v>
-      </c>
-      <c r="D396" t="s">
-        <v>500</v>
       </c>
       <c r="E396" t="s">
         <v>24</v>
@@ -12307,10 +12307,10 @@
         <v>7</v>
       </c>
       <c r="C398" t="s">
+        <v>499</v>
+      </c>
+      <c r="D398" t="s">
         <v>529</v>
-      </c>
-      <c r="D398" t="s">
-        <v>500</v>
       </c>
       <c r="E398" t="s">
         <v>24</v>
@@ -12367,10 +12367,10 @@
         <v>7</v>
       </c>
       <c r="C401" t="s">
+        <v>499</v>
+      </c>
+      <c r="D401" t="s">
         <v>534</v>
-      </c>
-      <c r="D401" t="s">
-        <v>500</v>
       </c>
       <c r="E401" t="s">
         <v>24</v>
@@ -12487,10 +12487,10 @@
         <v>7</v>
       </c>
       <c r="C407" t="s">
+        <v>499</v>
+      </c>
+      <c r="D407" t="s">
         <v>542</v>
-      </c>
-      <c r="D407" t="s">
-        <v>500</v>
       </c>
       <c r="E407" t="s">
         <v>24</v>
@@ -12507,10 +12507,10 @@
         <v>7</v>
       </c>
       <c r="C408" t="s">
+        <v>499</v>
+      </c>
+      <c r="D408" t="s">
         <v>545</v>
-      </c>
-      <c r="D408" t="s">
-        <v>500</v>
       </c>
       <c r="E408" t="s">
         <v>19</v>
@@ -12527,10 +12527,10 @@
         <v>7</v>
       </c>
       <c r="C409" t="s">
+        <v>499</v>
+      </c>
+      <c r="D409" t="s">
         <v>522</v>
-      </c>
-      <c r="D409" t="s">
-        <v>500</v>
       </c>
       <c r="E409" t="s">
         <v>13</v>
@@ -12547,10 +12547,10 @@
         <v>7</v>
       </c>
       <c r="C410" t="s">
+        <v>499</v>
+      </c>
+      <c r="D410" t="s">
         <v>504</v>
-      </c>
-      <c r="D410" t="s">
-        <v>500</v>
       </c>
       <c r="E410" t="s">
         <v>13</v>
@@ -12787,10 +12787,10 @@
         <v>7</v>
       </c>
       <c r="C422" t="s">
+        <v>558</v>
+      </c>
+      <c r="D422" t="s">
         <v>563</v>
-      </c>
-      <c r="D422" t="s">
-        <v>559</v>
       </c>
       <c r="E422" t="s">
         <v>24</v>
@@ -12827,10 +12827,10 @@
         <v>7</v>
       </c>
       <c r="C424" t="s">
+        <v>558</v>
+      </c>
+      <c r="D424" t="s">
         <v>566</v>
-      </c>
-      <c r="D424" t="s">
-        <v>559</v>
       </c>
       <c r="E424" t="s">
         <v>19</v>
@@ -12967,10 +12967,10 @@
         <v>7</v>
       </c>
       <c r="C431" t="s">
+        <v>558</v>
+      </c>
+      <c r="D431" t="s">
         <v>574</v>
-      </c>
-      <c r="D431" t="s">
-        <v>559</v>
       </c>
       <c r="E431" t="s">
         <v>24</v>
@@ -12987,10 +12987,10 @@
         <v>7</v>
       </c>
       <c r="C432" t="s">
+        <v>558</v>
+      </c>
+      <c r="D432" t="s">
         <v>577</v>
-      </c>
-      <c r="D432" t="s">
-        <v>559</v>
       </c>
       <c r="E432" t="s">
         <v>24</v>
@@ -13067,10 +13067,10 @@
         <v>7</v>
       </c>
       <c r="C436" t="s">
+        <v>558</v>
+      </c>
+      <c r="D436" t="s">
         <v>583</v>
-      </c>
-      <c r="D436" t="s">
-        <v>559</v>
       </c>
       <c r="E436" t="s">
         <v>24</v>
@@ -13127,10 +13127,10 @@
         <v>7</v>
       </c>
       <c r="C439" t="s">
+        <v>558</v>
+      </c>
+      <c r="D439" t="s">
         <v>587</v>
-      </c>
-      <c r="D439" t="s">
-        <v>559</v>
       </c>
       <c r="E439" t="s">
         <v>24</v>
@@ -13147,10 +13147,10 @@
         <v>7</v>
       </c>
       <c r="C440" t="s">
+        <v>558</v>
+      </c>
+      <c r="D440" t="s">
         <v>589</v>
-      </c>
-      <c r="D440" t="s">
-        <v>559</v>
       </c>
       <c r="E440" t="s">
         <v>19</v>
@@ -13207,10 +13207,10 @@
         <v>7</v>
       </c>
       <c r="C443" t="s">
+        <v>558</v>
+      </c>
+      <c r="D443" t="s">
         <v>593</v>
-      </c>
-      <c r="D443" t="s">
-        <v>559</v>
       </c>
       <c r="E443" t="s">
         <v>24</v>
@@ -13527,10 +13527,10 @@
         <v>7</v>
       </c>
       <c r="C459" t="s">
+        <v>558</v>
+      </c>
+      <c r="D459" t="s">
         <v>611</v>
-      </c>
-      <c r="D459" t="s">
-        <v>559</v>
       </c>
       <c r="E459" t="s">
         <v>19</v>
@@ -13727,10 +13727,10 @@
         <v>7</v>
       </c>
       <c r="C469" t="s">
+        <v>614</v>
+      </c>
+      <c r="D469" t="s">
         <v>627</v>
-      </c>
-      <c r="D469" t="s">
-        <v>615</v>
       </c>
       <c r="E469" t="s">
         <v>24</v>
@@ -13747,10 +13747,10 @@
         <v>7</v>
       </c>
       <c r="C470" t="s">
+        <v>614</v>
+      </c>
+      <c r="D470" t="s">
         <v>630</v>
-      </c>
-      <c r="D470" t="s">
-        <v>615</v>
       </c>
       <c r="E470" t="s">
         <v>24</v>
@@ -13767,10 +13767,10 @@
         <v>7</v>
       </c>
       <c r="C471" t="s">
+        <v>614</v>
+      </c>
+      <c r="D471" t="s">
         <v>632</v>
-      </c>
-      <c r="D471" t="s">
-        <v>615</v>
       </c>
       <c r="E471" t="s">
         <v>24</v>
@@ -13787,10 +13787,10 @@
         <v>7</v>
       </c>
       <c r="C472" t="s">
+        <v>614</v>
+      </c>
+      <c r="D472" t="s">
         <v>634</v>
-      </c>
-      <c r="D472" t="s">
-        <v>615</v>
       </c>
       <c r="E472" t="s">
         <v>24</v>
@@ -13827,10 +13827,10 @@
         <v>7</v>
       </c>
       <c r="C474" t="s">
+        <v>614</v>
+      </c>
+      <c r="D474" t="s">
         <v>638</v>
-      </c>
-      <c r="D474" t="s">
-        <v>615</v>
       </c>
       <c r="E474" t="s">
         <v>24</v>
@@ -13907,10 +13907,10 @@
         <v>7</v>
       </c>
       <c r="C478" t="s">
+        <v>614</v>
+      </c>
+      <c r="D478" t="s">
         <v>644</v>
-      </c>
-      <c r="D478" t="s">
-        <v>615</v>
       </c>
       <c r="E478" t="s">
         <v>24</v>
@@ -14227,10 +14227,10 @@
         <v>7</v>
       </c>
       <c r="C494" t="s">
+        <v>660</v>
+      </c>
+      <c r="D494" t="s">
         <v>664</v>
-      </c>
-      <c r="D494" t="s">
-        <v>661</v>
       </c>
       <c r="E494" t="s">
         <v>616</v>
@@ -14347,10 +14347,10 @@
         <v>7</v>
       </c>
       <c r="C500" t="s">
+        <v>660</v>
+      </c>
+      <c r="D500" t="s">
         <v>638</v>
-      </c>
-      <c r="D500" t="s">
-        <v>661</v>
       </c>
       <c r="E500" t="s">
         <v>13</v>
@@ -14367,10 +14367,10 @@
         <v>112</v>
       </c>
       <c r="C501" t="s">
+        <v>660</v>
+      </c>
+      <c r="D501" t="s">
         <v>638</v>
-      </c>
-      <c r="D501" t="s">
-        <v>661</v>
       </c>
       <c r="E501" t="s">
         <v>15</v>
@@ -14427,10 +14427,10 @@
         <v>7</v>
       </c>
       <c r="C504" t="s">
+        <v>660</v>
+      </c>
+      <c r="D504" t="s">
         <v>677</v>
-      </c>
-      <c r="D504" t="s">
-        <v>661</v>
       </c>
       <c r="E504" t="s">
         <v>616</v>
@@ -14507,10 +14507,10 @@
         <v>112</v>
       </c>
       <c r="C508" t="s">
+        <v>660</v>
+      </c>
+      <c r="D508" t="s">
         <v>682</v>
-      </c>
-      <c r="D508" t="s">
-        <v>661</v>
       </c>
       <c r="E508" t="s">
         <v>19</v>
@@ -14607,10 +14607,10 @@
         <v>7</v>
       </c>
       <c r="C513" t="s">
+        <v>660</v>
+      </c>
+      <c r="D513" t="s">
         <v>688</v>
-      </c>
-      <c r="D513" t="s">
-        <v>661</v>
       </c>
       <c r="E513" t="s">
         <v>24</v>
@@ -14627,10 +14627,10 @@
         <v>7</v>
       </c>
       <c r="C514" t="s">
+        <v>660</v>
+      </c>
+      <c r="D514" t="s">
         <v>691</v>
-      </c>
-      <c r="D514" t="s">
-        <v>661</v>
       </c>
       <c r="E514" t="s">
         <v>616</v>
@@ -14647,10 +14647,10 @@
         <v>112</v>
       </c>
       <c r="C515" t="s">
+        <v>660</v>
+      </c>
+      <c r="D515" t="s">
         <v>691</v>
-      </c>
-      <c r="D515" t="s">
-        <v>661</v>
       </c>
       <c r="E515" t="s">
         <v>19</v>
@@ -14667,10 +14667,10 @@
         <v>7</v>
       </c>
       <c r="C516" t="s">
+        <v>660</v>
+      </c>
+      <c r="D516" t="s">
         <v>696</v>
-      </c>
-      <c r="D516" t="s">
-        <v>661</v>
       </c>
       <c r="E516" t="s">
         <v>24</v>
@@ -14707,10 +14707,10 @@
         <v>7</v>
       </c>
       <c r="C518" t="s">
+        <v>660</v>
+      </c>
+      <c r="D518" t="s">
         <v>700</v>
-      </c>
-      <c r="D518" t="s">
-        <v>661</v>
       </c>
       <c r="E518" t="s">
         <v>15</v>
@@ -14907,10 +14907,10 @@
         <v>112</v>
       </c>
       <c r="C528" t="s">
+        <v>660</v>
+      </c>
+      <c r="D528" t="s">
         <v>712</v>
-      </c>
-      <c r="D528" t="s">
-        <v>661</v>
       </c>
       <c r="E528" t="s">
         <v>19</v>
@@ -14927,10 +14927,10 @@
         <v>112</v>
       </c>
       <c r="C529" t="s">
+        <v>660</v>
+      </c>
+      <c r="D529" t="s">
         <v>714</v>
-      </c>
-      <c r="D529" t="s">
-        <v>661</v>
       </c>
       <c r="E529" t="s">
         <v>13</v>
@@ -14947,10 +14947,10 @@
         <v>7</v>
       </c>
       <c r="C530" t="s">
+        <v>660</v>
+      </c>
+      <c r="D530" t="s">
         <v>716</v>
-      </c>
-      <c r="D530" t="s">
-        <v>661</v>
       </c>
       <c r="E530" t="s">
         <v>24</v>
@@ -14987,10 +14987,10 @@
         <v>7</v>
       </c>
       <c r="C532" t="s">
+        <v>719</v>
+      </c>
+      <c r="D532" t="s">
         <v>664</v>
-      </c>
-      <c r="D532" t="s">
-        <v>719</v>
       </c>
       <c r="E532" t="s">
         <v>720</v>
@@ -15007,10 +15007,10 @@
         <v>7</v>
       </c>
       <c r="C533" t="s">
+        <v>719</v>
+      </c>
+      <c r="D533" t="s">
         <v>664</v>
-      </c>
-      <c r="D533" t="s">
-        <v>719</v>
       </c>
       <c r="E533" t="s">
         <v>720</v>
@@ -15027,10 +15027,10 @@
         <v>7</v>
       </c>
       <c r="C534" t="s">
+        <v>719</v>
+      </c>
+      <c r="D534" t="s">
         <v>664</v>
-      </c>
-      <c r="D534" t="s">
-        <v>719</v>
       </c>
       <c r="E534" t="s">
         <v>720</v>
@@ -15047,10 +15047,10 @@
         <v>7</v>
       </c>
       <c r="C535" t="s">
+        <v>719</v>
+      </c>
+      <c r="D535" t="s">
         <v>664</v>
-      </c>
-      <c r="D535" t="s">
-        <v>719</v>
       </c>
       <c r="E535" t="s">
         <v>720</v>
@@ -15067,10 +15067,10 @@
         <v>7</v>
       </c>
       <c r="C536" t="s">
+        <v>719</v>
+      </c>
+      <c r="D536" t="s">
         <v>726</v>
-      </c>
-      <c r="D536" t="s">
-        <v>719</v>
       </c>
       <c r="E536" t="s">
         <v>15</v>
@@ -15087,10 +15087,10 @@
         <v>7</v>
       </c>
       <c r="C537" t="s">
+        <v>719</v>
+      </c>
+      <c r="D537" t="s">
         <v>664</v>
-      </c>
-      <c r="D537" t="s">
-        <v>719</v>
       </c>
       <c r="E537" t="s">
         <v>720</v>
@@ -15107,10 +15107,10 @@
         <v>7</v>
       </c>
       <c r="C538" t="s">
+        <v>719</v>
+      </c>
+      <c r="D538" t="s">
         <v>664</v>
-      </c>
-      <c r="D538" t="s">
-        <v>719</v>
       </c>
       <c r="E538" t="s">
         <v>720</v>
@@ -15127,10 +15127,10 @@
         <v>7</v>
       </c>
       <c r="C539" t="s">
+        <v>719</v>
+      </c>
+      <c r="D539" t="s">
         <v>664</v>
-      </c>
-      <c r="D539" t="s">
-        <v>719</v>
       </c>
       <c r="E539" t="s">
         <v>720</v>
@@ -15147,10 +15147,10 @@
         <v>7</v>
       </c>
       <c r="C540" t="s">
+        <v>719</v>
+      </c>
+      <c r="D540" t="s">
         <v>664</v>
-      </c>
-      <c r="D540" t="s">
-        <v>719</v>
       </c>
       <c r="E540" t="s">
         <v>720</v>
@@ -15167,10 +15167,10 @@
         <v>7</v>
       </c>
       <c r="C541" t="s">
+        <v>719</v>
+      </c>
+      <c r="D541" t="s">
         <v>664</v>
-      </c>
-      <c r="D541" t="s">
-        <v>719</v>
       </c>
       <c r="E541" t="s">
         <v>720</v>
@@ -15187,10 +15187,10 @@
         <v>7</v>
       </c>
       <c r="C542" t="s">
+        <v>719</v>
+      </c>
+      <c r="D542" t="s">
         <v>664</v>
-      </c>
-      <c r="D542" t="s">
-        <v>719</v>
       </c>
       <c r="E542" t="s">
         <v>720</v>
@@ -15207,10 +15207,10 @@
         <v>7</v>
       </c>
       <c r="C543" t="s">
+        <v>719</v>
+      </c>
+      <c r="D543" t="s">
         <v>735</v>
-      </c>
-      <c r="D543" t="s">
-        <v>719</v>
       </c>
       <c r="E543" t="s">
         <v>15</v>
@@ -15227,10 +15227,10 @@
         <v>7</v>
       </c>
       <c r="C544" t="s">
+        <v>719</v>
+      </c>
+      <c r="D544" t="s">
         <v>737</v>
-      </c>
-      <c r="D544" t="s">
-        <v>719</v>
       </c>
       <c r="E544" t="s">
         <v>15</v>
@@ -15247,10 +15247,10 @@
         <v>7</v>
       </c>
       <c r="C545" t="s">
+        <v>719</v>
+      </c>
+      <c r="D545" t="s">
         <v>664</v>
-      </c>
-      <c r="D545" t="s">
-        <v>719</v>
       </c>
       <c r="E545" t="s">
         <v>720</v>
@@ -15267,10 +15267,10 @@
         <v>7</v>
       </c>
       <c r="C546" t="s">
+        <v>719</v>
+      </c>
+      <c r="D546" t="s">
         <v>664</v>
-      </c>
-      <c r="D546" t="s">
-        <v>719</v>
       </c>
       <c r="E546" t="s">
         <v>720</v>
@@ -15287,10 +15287,10 @@
         <v>7</v>
       </c>
       <c r="C547" t="s">
+        <v>719</v>
+      </c>
+      <c r="D547" t="s">
         <v>664</v>
-      </c>
-      <c r="D547" t="s">
-        <v>719</v>
       </c>
       <c r="E547" t="s">
         <v>720</v>
@@ -15307,10 +15307,10 @@
         <v>7</v>
       </c>
       <c r="C548" t="s">
+        <v>719</v>
+      </c>
+      <c r="D548" t="s">
         <v>664</v>
-      </c>
-      <c r="D548" t="s">
-        <v>719</v>
       </c>
       <c r="E548" t="s">
         <v>720</v>
@@ -15327,10 +15327,10 @@
         <v>7</v>
       </c>
       <c r="C549" t="s">
+        <v>719</v>
+      </c>
+      <c r="D549" t="s">
         <v>664</v>
-      </c>
-      <c r="D549" t="s">
-        <v>719</v>
       </c>
       <c r="E549" t="s">
         <v>720</v>
@@ -15347,10 +15347,10 @@
         <v>7</v>
       </c>
       <c r="C550" t="s">
+        <v>719</v>
+      </c>
+      <c r="D550" t="s">
         <v>664</v>
-      </c>
-      <c r="D550" t="s">
-        <v>719</v>
       </c>
       <c r="E550" t="s">
         <v>720</v>
@@ -15367,10 +15367,10 @@
         <v>7</v>
       </c>
       <c r="C551" t="s">
+        <v>719</v>
+      </c>
+      <c r="D551" t="s">
         <v>664</v>
-      </c>
-      <c r="D551" t="s">
-        <v>719</v>
       </c>
       <c r="E551" t="s">
         <v>720</v>
@@ -15387,10 +15387,10 @@
         <v>7</v>
       </c>
       <c r="C552" t="s">
+        <v>719</v>
+      </c>
+      <c r="D552" t="s">
         <v>664</v>
-      </c>
-      <c r="D552" t="s">
-        <v>719</v>
       </c>
       <c r="E552" t="s">
         <v>13</v>
@@ -15407,10 +15407,10 @@
         <v>7</v>
       </c>
       <c r="C553" t="s">
+        <v>719</v>
+      </c>
+      <c r="D553" t="s">
         <v>664</v>
-      </c>
-      <c r="D553" t="s">
-        <v>719</v>
       </c>
       <c r="E553" t="s">
         <v>720</v>
@@ -15427,10 +15427,10 @@
         <v>7</v>
       </c>
       <c r="C554" t="s">
+        <v>719</v>
+      </c>
+      <c r="D554" t="s">
         <v>664</v>
-      </c>
-      <c r="D554" t="s">
-        <v>719</v>
       </c>
       <c r="E554" t="s">
         <v>15</v>
@@ -15467,10 +15467,10 @@
         <v>7</v>
       </c>
       <c r="C556" t="s">
+        <v>750</v>
+      </c>
+      <c r="D556" t="s">
         <v>754</v>
-      </c>
-      <c r="D556" t="s">
-        <v>751</v>
       </c>
       <c r="E556" t="s">
         <v>720</v>
@@ -15487,10 +15487,10 @@
         <v>7</v>
       </c>
       <c r="C557" t="s">
+        <v>750</v>
+      </c>
+      <c r="D557" t="s">
         <v>756</v>
-      </c>
-      <c r="D557" t="s">
-        <v>751</v>
       </c>
       <c r="E557" t="s">
         <v>720</v>
@@ -15647,10 +15647,10 @@
         <v>7</v>
       </c>
       <c r="C565" t="s">
+        <v>750</v>
+      </c>
+      <c r="D565" t="s">
         <v>766</v>
-      </c>
-      <c r="D565" t="s">
-        <v>751</v>
       </c>
       <c r="E565" t="s">
         <v>24</v>
@@ -15687,10 +15687,10 @@
         <v>7</v>
       </c>
       <c r="C567" t="s">
+        <v>750</v>
+      </c>
+      <c r="D567" t="s">
         <v>770</v>
-      </c>
-      <c r="D567" t="s">
-        <v>751</v>
       </c>
       <c r="E567" t="s">
         <v>720</v>
@@ -15707,10 +15707,10 @@
         <v>7</v>
       </c>
       <c r="C568" t="s">
+        <v>750</v>
+      </c>
+      <c r="D568" t="s">
         <v>770</v>
-      </c>
-      <c r="D568" t="s">
-        <v>751</v>
       </c>
       <c r="E568" t="s">
         <v>720</v>
@@ -15867,10 +15867,10 @@
         <v>7</v>
       </c>
       <c r="C576" t="s">
+        <v>750</v>
+      </c>
+      <c r="D576" t="s">
         <v>781</v>
-      </c>
-      <c r="D576" t="s">
-        <v>751</v>
       </c>
       <c r="E576" t="s">
         <v>720</v>
@@ -16047,10 +16047,10 @@
         <v>7</v>
       </c>
       <c r="C585" t="s">
+        <v>787</v>
+      </c>
+      <c r="D585" t="s">
         <v>795</v>
-      </c>
-      <c r="D585" t="s">
-        <v>788</v>
       </c>
       <c r="E585" t="s">
         <v>720</v>
@@ -16067,10 +16067,10 @@
         <v>7</v>
       </c>
       <c r="C586" t="s">
+        <v>787</v>
+      </c>
+      <c r="D586" t="s">
         <v>797</v>
-      </c>
-      <c r="D586" t="s">
-        <v>788</v>
       </c>
       <c r="E586" t="s">
         <v>24</v>
@@ -16087,10 +16087,10 @@
         <v>7</v>
       </c>
       <c r="C587" t="s">
+        <v>787</v>
+      </c>
+      <c r="D587" t="s">
         <v>800</v>
-      </c>
-      <c r="D587" t="s">
-        <v>788</v>
       </c>
       <c r="E587" t="s">
         <v>720</v>
@@ -16107,10 +16107,10 @@
         <v>7</v>
       </c>
       <c r="C588" t="s">
+        <v>787</v>
+      </c>
+      <c r="D588" t="s">
         <v>802</v>
-      </c>
-      <c r="D588" t="s">
-        <v>788</v>
       </c>
       <c r="E588" t="s">
         <v>15</v>
@@ -16147,10 +16147,10 @@
         <v>7</v>
       </c>
       <c r="C590" t="s">
+        <v>787</v>
+      </c>
+      <c r="D590" t="s">
         <v>805</v>
-      </c>
-      <c r="D590" t="s">
-        <v>788</v>
       </c>
       <c r="E590" t="s">
         <v>24</v>
@@ -16167,10 +16167,10 @@
         <v>7</v>
       </c>
       <c r="C591" t="s">
+        <v>787</v>
+      </c>
+      <c r="D591" t="s">
         <v>808</v>
-      </c>
-      <c r="D591" t="s">
-        <v>788</v>
       </c>
       <c r="E591" t="s">
         <v>24</v>
@@ -16207,10 +16207,10 @@
         <v>7</v>
       </c>
       <c r="C593" t="s">
+        <v>787</v>
+      </c>
+      <c r="D593" t="s">
         <v>812</v>
-      </c>
-      <c r="D593" t="s">
-        <v>788</v>
       </c>
       <c r="E593" t="s">
         <v>24</v>
@@ -16227,10 +16227,10 @@
         <v>7</v>
       </c>
       <c r="C594" t="s">
+        <v>787</v>
+      </c>
+      <c r="D594" t="s">
         <v>815</v>
-      </c>
-      <c r="D594" t="s">
-        <v>788</v>
       </c>
       <c r="E594" t="s">
         <v>13</v>
@@ -16247,10 +16247,10 @@
         <v>7</v>
       </c>
       <c r="C595" t="s">
+        <v>787</v>
+      </c>
+      <c r="D595" t="s">
         <v>817</v>
-      </c>
-      <c r="D595" t="s">
-        <v>788</v>
       </c>
       <c r="E595" t="s">
         <v>720</v>
@@ -16447,10 +16447,10 @@
         <v>7</v>
       </c>
       <c r="C605" t="s">
+        <v>828</v>
+      </c>
+      <c r="D605" t="s">
         <v>832</v>
-      </c>
-      <c r="D605" t="s">
-        <v>829</v>
       </c>
       <c r="E605" t="s">
         <v>15</v>
@@ -16527,10 +16527,10 @@
         <v>7</v>
       </c>
       <c r="C609" t="s">
+        <v>828</v>
+      </c>
+      <c r="D609" t="s">
         <v>838</v>
-      </c>
-      <c r="D609" t="s">
-        <v>829</v>
       </c>
       <c r="E609" t="s">
         <v>24</v>
@@ -16547,10 +16547,10 @@
         <v>7</v>
       </c>
       <c r="C610" t="s">
+        <v>828</v>
+      </c>
+      <c r="D610" t="s">
         <v>841</v>
-      </c>
-      <c r="D610" t="s">
-        <v>829</v>
       </c>
       <c r="E610" t="s">
         <v>24</v>
@@ -16567,10 +16567,10 @@
         <v>7</v>
       </c>
       <c r="C611" t="s">
+        <v>828</v>
+      </c>
+      <c r="D611" t="s">
         <v>844</v>
-      </c>
-      <c r="D611" t="s">
-        <v>829</v>
       </c>
       <c r="E611" t="s">
         <v>720</v>
@@ -16587,10 +16587,10 @@
         <v>7</v>
       </c>
       <c r="C612" t="s">
+        <v>828</v>
+      </c>
+      <c r="D612" t="s">
         <v>847</v>
-      </c>
-      <c r="D612" t="s">
-        <v>829</v>
       </c>
       <c r="E612" t="s">
         <v>24</v>
@@ -16667,10 +16667,10 @@
         <v>7</v>
       </c>
       <c r="C616" t="s">
+        <v>828</v>
+      </c>
+      <c r="D616" t="s">
         <v>852</v>
-      </c>
-      <c r="D616" t="s">
-        <v>829</v>
       </c>
       <c r="E616" t="s">
         <v>24</v>
@@ -16687,10 +16687,10 @@
         <v>7</v>
       </c>
       <c r="C617" t="s">
+        <v>828</v>
+      </c>
+      <c r="D617" t="s">
         <v>855</v>
-      </c>
-      <c r="D617" t="s">
-        <v>829</v>
       </c>
       <c r="E617" t="s">
         <v>720</v>
@@ -16727,10 +16727,10 @@
         <v>7</v>
       </c>
       <c r="C619" t="s">
+        <v>828</v>
+      </c>
+      <c r="D619" t="s">
         <v>832</v>
-      </c>
-      <c r="D619" t="s">
-        <v>829</v>
       </c>
       <c r="E619" t="s">
         <v>24</v>
@@ -16747,10 +16747,10 @@
         <v>7</v>
       </c>
       <c r="C620" t="s">
+        <v>828</v>
+      </c>
+      <c r="D620" t="s">
         <v>860</v>
-      </c>
-      <c r="D620" t="s">
-        <v>829</v>
       </c>
       <c r="E620" t="s">
         <v>720</v>
@@ -16767,10 +16767,10 @@
         <v>112</v>
       </c>
       <c r="C621" t="s">
+        <v>828</v>
+      </c>
+      <c r="D621" t="s">
         <v>860</v>
-      </c>
-      <c r="D621" t="s">
-        <v>829</v>
       </c>
       <c r="E621" t="s">
         <v>15</v>
@@ -16807,10 +16807,10 @@
         <v>7</v>
       </c>
       <c r="C623" t="s">
+        <v>828</v>
+      </c>
+      <c r="D623" t="s">
         <v>864</v>
-      </c>
-      <c r="D623" t="s">
-        <v>829</v>
       </c>
       <c r="E623" t="s">
         <v>720</v>
@@ -17047,10 +17047,10 @@
         <v>7</v>
       </c>
       <c r="C635" t="s">
+        <v>876</v>
+      </c>
+      <c r="D635" t="s">
         <v>880</v>
-      </c>
-      <c r="D635" t="s">
-        <v>877</v>
       </c>
       <c r="E635" t="s">
         <v>24</v>
@@ -17147,10 +17147,10 @@
         <v>7</v>
       </c>
       <c r="C640" t="s">
+        <v>876</v>
+      </c>
+      <c r="D640" t="s">
         <v>888</v>
-      </c>
-      <c r="D640" t="s">
-        <v>877</v>
       </c>
       <c r="E640" t="s">
         <v>24</v>
@@ -17227,10 +17227,10 @@
         <v>7</v>
       </c>
       <c r="C644" t="s">
+        <v>876</v>
+      </c>
+      <c r="D644" t="s">
         <v>888</v>
-      </c>
-      <c r="D644" t="s">
-        <v>877</v>
       </c>
       <c r="E644" t="s">
         <v>24</v>
@@ -17247,10 +17247,10 @@
         <v>7</v>
       </c>
       <c r="C645" t="s">
+        <v>876</v>
+      </c>
+      <c r="D645" t="s">
         <v>895</v>
-      </c>
-      <c r="D645" t="s">
-        <v>877</v>
       </c>
       <c r="E645" t="s">
         <v>24</v>
@@ -17267,10 +17267,10 @@
         <v>7</v>
       </c>
       <c r="C646" t="s">
+        <v>876</v>
+      </c>
+      <c r="D646" t="s">
         <v>898</v>
-      </c>
-      <c r="D646" t="s">
-        <v>877</v>
       </c>
       <c r="E646" t="s">
         <v>24</v>
@@ -17307,10 +17307,10 @@
         <v>7</v>
       </c>
       <c r="C648" t="s">
+        <v>876</v>
+      </c>
+      <c r="D648" t="s">
         <v>902</v>
-      </c>
-      <c r="D648" t="s">
-        <v>877</v>
       </c>
       <c r="E648" t="s">
         <v>720</v>
@@ -17327,10 +17327,10 @@
         <v>7</v>
       </c>
       <c r="C649" t="s">
+        <v>876</v>
+      </c>
+      <c r="D649" t="s">
         <v>904</v>
-      </c>
-      <c r="D649" t="s">
-        <v>877</v>
       </c>
       <c r="E649" t="s">
         <v>24</v>
@@ -17407,10 +17407,10 @@
         <v>7</v>
       </c>
       <c r="C653" t="s">
+        <v>876</v>
+      </c>
+      <c r="D653" t="s">
         <v>910</v>
-      </c>
-      <c r="D653" t="s">
-        <v>877</v>
       </c>
       <c r="E653" t="s">
         <v>15</v>
@@ -17427,10 +17427,10 @@
         <v>7</v>
       </c>
       <c r="C654" t="s">
+        <v>876</v>
+      </c>
+      <c r="D654" t="s">
         <v>913</v>
-      </c>
-      <c r="D654" t="s">
-        <v>877</v>
       </c>
       <c r="E654" t="s">
         <v>15</v>
@@ -17447,10 +17447,10 @@
         <v>7</v>
       </c>
       <c r="C655" t="s">
+        <v>876</v>
+      </c>
+      <c r="D655" t="s">
         <v>915</v>
-      </c>
-      <c r="D655" t="s">
-        <v>877</v>
       </c>
       <c r="E655" t="s">
         <v>15</v>
@@ -17527,10 +17527,10 @@
         <v>7</v>
       </c>
       <c r="C659" t="s">
+        <v>876</v>
+      </c>
+      <c r="D659" t="s">
         <v>920</v>
-      </c>
-      <c r="D659" t="s">
-        <v>877</v>
       </c>
       <c r="E659" t="s">
         <v>24</v>
@@ -17607,10 +17607,10 @@
         <v>7</v>
       </c>
       <c r="C663" t="s">
+        <v>924</v>
+      </c>
+      <c r="D663" t="s">
         <v>928</v>
-      </c>
-      <c r="D663" t="s">
-        <v>925</v>
       </c>
       <c r="E663" t="s">
         <v>15</v>
@@ -17647,10 +17647,10 @@
         <v>7</v>
       </c>
       <c r="C665" t="s">
+        <v>924</v>
+      </c>
+      <c r="D665" t="s">
         <v>933</v>
-      </c>
-      <c r="D665" t="s">
-        <v>925</v>
       </c>
       <c r="E665" t="s">
         <v>720</v>
@@ -17667,10 +17667,10 @@
         <v>7</v>
       </c>
       <c r="C666" t="s">
+        <v>924</v>
+      </c>
+      <c r="D666" t="s">
         <v>933</v>
-      </c>
-      <c r="D666" t="s">
-        <v>925</v>
       </c>
       <c r="E666" t="s">
         <v>720</v>
@@ -17687,10 +17687,10 @@
         <v>7</v>
       </c>
       <c r="C667" t="s">
+        <v>924</v>
+      </c>
+      <c r="D667" t="s">
         <v>915</v>
-      </c>
-      <c r="D667" t="s">
-        <v>925</v>
       </c>
       <c r="E667" t="s">
         <v>15</v>
@@ -17707,10 +17707,10 @@
         <v>7</v>
       </c>
       <c r="C668" t="s">
+        <v>924</v>
+      </c>
+      <c r="D668" t="s">
         <v>933</v>
-      </c>
-      <c r="D668" t="s">
-        <v>925</v>
       </c>
       <c r="E668" t="s">
         <v>720</v>
@@ -17727,10 +17727,10 @@
         <v>7</v>
       </c>
       <c r="C669" t="s">
+        <v>924</v>
+      </c>
+      <c r="D669" t="s">
         <v>933</v>
-      </c>
-      <c r="D669" t="s">
-        <v>925</v>
       </c>
       <c r="E669" t="s">
         <v>720</v>
@@ -17747,10 +17747,10 @@
         <v>7</v>
       </c>
       <c r="C670" t="s">
+        <v>924</v>
+      </c>
+      <c r="D670" t="s">
         <v>940</v>
-      </c>
-      <c r="D670" t="s">
-        <v>925</v>
       </c>
       <c r="E670" t="s">
         <v>15</v>
@@ -17767,10 +17767,10 @@
         <v>7</v>
       </c>
       <c r="C671" t="s">
+        <v>924</v>
+      </c>
+      <c r="D671" t="s">
         <v>943</v>
-      </c>
-      <c r="D671" t="s">
-        <v>925</v>
       </c>
       <c r="E671" t="s">
         <v>24</v>
@@ -17787,10 +17787,10 @@
         <v>7</v>
       </c>
       <c r="C672" t="s">
+        <v>924</v>
+      </c>
+      <c r="D672" t="s">
         <v>902</v>
-      </c>
-      <c r="D672" t="s">
-        <v>925</v>
       </c>
       <c r="E672" t="s">
         <v>24</v>
@@ -17807,10 +17807,10 @@
         <v>7</v>
       </c>
       <c r="C673" t="s">
+        <v>924</v>
+      </c>
+      <c r="D673" t="s">
         <v>948</v>
-      </c>
-      <c r="D673" t="s">
-        <v>925</v>
       </c>
       <c r="E673" t="s">
         <v>24</v>
@@ -17827,10 +17827,10 @@
         <v>7</v>
       </c>
       <c r="C674" t="s">
+        <v>924</v>
+      </c>
+      <c r="D674" t="s">
         <v>933</v>
-      </c>
-      <c r="D674" t="s">
-        <v>925</v>
       </c>
       <c r="E674" t="s">
         <v>720</v>
@@ -17847,10 +17847,10 @@
         <v>7</v>
       </c>
       <c r="C675" t="s">
+        <v>924</v>
+      </c>
+      <c r="D675" t="s">
         <v>933</v>
-      </c>
-      <c r="D675" t="s">
-        <v>925</v>
       </c>
       <c r="E675" t="s">
         <v>24</v>
@@ -17867,10 +17867,10 @@
         <v>7</v>
       </c>
       <c r="C676" t="s">
+        <v>924</v>
+      </c>
+      <c r="D676" t="s">
         <v>953</v>
-      </c>
-      <c r="D676" t="s">
-        <v>925</v>
       </c>
       <c r="E676" t="s">
         <v>24</v>
@@ -17887,10 +17887,10 @@
         <v>7</v>
       </c>
       <c r="C677" t="s">
+        <v>924</v>
+      </c>
+      <c r="D677" t="s">
         <v>915</v>
-      </c>
-      <c r="D677" t="s">
-        <v>925</v>
       </c>
       <c r="E677" t="s">
         <v>15</v>
@@ -17907,10 +17907,10 @@
         <v>7</v>
       </c>
       <c r="C678" t="s">
+        <v>924</v>
+      </c>
+      <c r="D678" t="s">
         <v>958</v>
-      </c>
-      <c r="D678" t="s">
-        <v>925</v>
       </c>
       <c r="E678" t="s">
         <v>15</v>
@@ -17927,10 +17927,10 @@
         <v>112</v>
       </c>
       <c r="C679" t="s">
+        <v>924</v>
+      </c>
+      <c r="D679" t="s">
         <v>958</v>
-      </c>
-      <c r="D679" t="s">
-        <v>925</v>
       </c>
       <c r="E679" t="s">
         <v>720</v>
@@ -17947,10 +17947,10 @@
         <v>7</v>
       </c>
       <c r="C680" t="s">
+        <v>924</v>
+      </c>
+      <c r="D680" t="s">
         <v>958</v>
-      </c>
-      <c r="D680" t="s">
-        <v>925</v>
       </c>
       <c r="E680" t="s">
         <v>24</v>
@@ -17967,10 +17967,10 @@
         <v>7</v>
       </c>
       <c r="C681" t="s">
+        <v>924</v>
+      </c>
+      <c r="D681" t="s">
         <v>962</v>
-      </c>
-      <c r="D681" t="s">
-        <v>925</v>
       </c>
       <c r="E681" t="s">
         <v>24</v>
@@ -17987,10 +17987,10 @@
         <v>7</v>
       </c>
       <c r="C682" t="s">
+        <v>924</v>
+      </c>
+      <c r="D682" t="s">
         <v>933</v>
-      </c>
-      <c r="D682" t="s">
-        <v>925</v>
       </c>
       <c r="E682" t="s">
         <v>15</v>
@@ -18007,10 +18007,10 @@
         <v>7</v>
       </c>
       <c r="C683" t="s">
+        <v>924</v>
+      </c>
+      <c r="D683" t="s">
         <v>915</v>
-      </c>
-      <c r="D683" t="s">
-        <v>925</v>
       </c>
       <c r="E683" t="s">
         <v>15</v>
@@ -18027,10 +18027,10 @@
         <v>7</v>
       </c>
       <c r="C684" t="s">
+        <v>924</v>
+      </c>
+      <c r="D684" t="s">
         <v>933</v>
-      </c>
-      <c r="D684" t="s">
-        <v>925</v>
       </c>
       <c r="E684" t="s">
         <v>720</v>
@@ -18067,10 +18067,10 @@
         <v>7</v>
       </c>
       <c r="C686" t="s">
+        <v>924</v>
+      </c>
+      <c r="D686" t="s">
         <v>933</v>
-      </c>
-      <c r="D686" t="s">
-        <v>925</v>
       </c>
       <c r="E686" t="s">
         <v>15</v>
@@ -18087,10 +18087,10 @@
         <v>7</v>
       </c>
       <c r="C687" t="s">
+        <v>924</v>
+      </c>
+      <c r="D687" t="s">
         <v>933</v>
-      </c>
-      <c r="D687" t="s">
-        <v>925</v>
       </c>
       <c r="E687" t="s">
         <v>720</v>
@@ -18107,10 +18107,10 @@
         <v>7</v>
       </c>
       <c r="C688" t="s">
+        <v>924</v>
+      </c>
+      <c r="D688" t="s">
         <v>915</v>
-      </c>
-      <c r="D688" t="s">
-        <v>925</v>
       </c>
       <c r="E688" t="s">
         <v>15</v>
@@ -18147,10 +18147,10 @@
         <v>7</v>
       </c>
       <c r="C690" t="s">
+        <v>924</v>
+      </c>
+      <c r="D690" t="s">
         <v>974</v>
-      </c>
-      <c r="D690" t="s">
-        <v>925</v>
       </c>
       <c r="E690" t="s">
         <v>15</v>
@@ -18167,10 +18167,10 @@
         <v>7</v>
       </c>
       <c r="C691" t="s">
+        <v>924</v>
+      </c>
+      <c r="D691" t="s">
         <v>933</v>
-      </c>
-      <c r="D691" t="s">
-        <v>925</v>
       </c>
       <c r="E691" t="s">
         <v>720</v>
@@ -18187,10 +18187,10 @@
         <v>7</v>
       </c>
       <c r="C692" t="s">
+        <v>924</v>
+      </c>
+      <c r="D692" t="s">
         <v>933</v>
-      </c>
-      <c r="D692" t="s">
-        <v>925</v>
       </c>
       <c r="E692" t="s">
         <v>13</v>
@@ -18207,10 +18207,10 @@
         <v>112</v>
       </c>
       <c r="C693" t="s">
+        <v>924</v>
+      </c>
+      <c r="D693" t="s">
         <v>933</v>
-      </c>
-      <c r="D693" t="s">
-        <v>925</v>
       </c>
       <c r="E693" t="s">
         <v>720</v>
@@ -18227,10 +18227,10 @@
         <v>7</v>
       </c>
       <c r="C694" t="s">
+        <v>924</v>
+      </c>
+      <c r="D694" t="s">
         <v>948</v>
-      </c>
-      <c r="D694" t="s">
-        <v>925</v>
       </c>
       <c r="E694" t="s">
         <v>24</v>
@@ -18247,10 +18247,10 @@
         <v>7</v>
       </c>
       <c r="C695" t="s">
+        <v>924</v>
+      </c>
+      <c r="D695" t="s">
         <v>933</v>
-      </c>
-      <c r="D695" t="s">
-        <v>925</v>
       </c>
       <c r="E695" t="s">
         <v>720</v>
@@ -18267,10 +18267,10 @@
         <v>7</v>
       </c>
       <c r="C696" t="s">
+        <v>924</v>
+      </c>
+      <c r="D696" t="s">
         <v>933</v>
-      </c>
-      <c r="D696" t="s">
-        <v>925</v>
       </c>
       <c r="E696" t="s">
         <v>720</v>
@@ -18307,10 +18307,10 @@
         <v>7</v>
       </c>
       <c r="C698" t="s">
+        <v>982</v>
+      </c>
+      <c r="D698" t="s">
         <v>986</v>
-      </c>
-      <c r="D698" t="s">
-        <v>983</v>
       </c>
       <c r="E698" t="s">
         <v>24</v>
@@ -18327,10 +18327,10 @@
         <v>7</v>
       </c>
       <c r="C699" t="s">
+        <v>982</v>
+      </c>
+      <c r="D699" t="s">
         <v>989</v>
-      </c>
-      <c r="D699" t="s">
-        <v>983</v>
       </c>
       <c r="E699" t="s">
         <v>720</v>
@@ -18347,10 +18347,10 @@
         <v>7</v>
       </c>
       <c r="C700" t="s">
+        <v>982</v>
+      </c>
+      <c r="D700" t="s">
         <v>989</v>
-      </c>
-      <c r="D700" t="s">
-        <v>983</v>
       </c>
       <c r="E700" t="s">
         <v>720</v>
@@ -18367,10 +18367,10 @@
         <v>7</v>
       </c>
       <c r="C701" t="s">
+        <v>982</v>
+      </c>
+      <c r="D701" t="s">
         <v>989</v>
-      </c>
-      <c r="D701" t="s">
-        <v>983</v>
       </c>
       <c r="E701" t="s">
         <v>720</v>
@@ -18387,10 +18387,10 @@
         <v>7</v>
       </c>
       <c r="C702" t="s">
+        <v>982</v>
+      </c>
+      <c r="D702" t="s">
         <v>989</v>
-      </c>
-      <c r="D702" t="s">
-        <v>983</v>
       </c>
       <c r="E702" t="s">
         <v>720</v>
@@ -18407,10 +18407,10 @@
         <v>7</v>
       </c>
       <c r="C703" t="s">
+        <v>982</v>
+      </c>
+      <c r="D703" t="s">
         <v>989</v>
-      </c>
-      <c r="D703" t="s">
-        <v>983</v>
       </c>
       <c r="E703" t="s">
         <v>720</v>
@@ -18427,10 +18427,10 @@
         <v>7</v>
       </c>
       <c r="C704" t="s">
+        <v>982</v>
+      </c>
+      <c r="D704" t="s">
         <v>986</v>
-      </c>
-      <c r="D704" t="s">
-        <v>983</v>
       </c>
       <c r="E704" t="s">
         <v>24</v>
@@ -18447,10 +18447,10 @@
         <v>7</v>
       </c>
       <c r="C705" t="s">
+        <v>982</v>
+      </c>
+      <c r="D705" t="s">
         <v>998</v>
-      </c>
-      <c r="D705" t="s">
-        <v>983</v>
       </c>
       <c r="E705" t="s">
         <v>24</v>
@@ -18467,10 +18467,10 @@
         <v>7</v>
       </c>
       <c r="C706" t="s">
+        <v>982</v>
+      </c>
+      <c r="D706" t="s">
         <v>989</v>
-      </c>
-      <c r="D706" t="s">
-        <v>983</v>
       </c>
       <c r="E706" t="s">
         <v>13</v>
@@ -18487,10 +18487,10 @@
         <v>7</v>
       </c>
       <c r="C707" t="s">
+        <v>982</v>
+      </c>
+      <c r="D707" t="s">
         <v>1002</v>
-      </c>
-      <c r="D707" t="s">
-        <v>983</v>
       </c>
       <c r="E707" t="s">
         <v>13</v>
@@ -18507,10 +18507,10 @@
         <v>7</v>
       </c>
       <c r="C708" t="s">
+        <v>982</v>
+      </c>
+      <c r="D708" t="s">
         <v>1004</v>
-      </c>
-      <c r="D708" t="s">
-        <v>983</v>
       </c>
       <c r="E708" t="s">
         <v>24</v>
@@ -18527,10 +18527,10 @@
         <v>7</v>
       </c>
       <c r="C709" t="s">
+        <v>982</v>
+      </c>
+      <c r="D709" t="s">
         <v>1007</v>
-      </c>
-      <c r="D709" t="s">
-        <v>983</v>
       </c>
       <c r="E709" t="s">
         <v>15</v>
@@ -18547,10 +18547,10 @@
         <v>7</v>
       </c>
       <c r="C710" t="s">
+        <v>982</v>
+      </c>
+      <c r="D710" t="s">
         <v>1010</v>
-      </c>
-      <c r="D710" t="s">
-        <v>983</v>
       </c>
       <c r="E710" t="s">
         <v>24</v>
@@ -18567,10 +18567,10 @@
         <v>7</v>
       </c>
       <c r="C711" t="s">
+        <v>982</v>
+      </c>
+      <c r="D711" t="s">
         <v>989</v>
-      </c>
-      <c r="D711" t="s">
-        <v>983</v>
       </c>
       <c r="E711" t="s">
         <v>720</v>
@@ -18587,10 +18587,10 @@
         <v>7</v>
       </c>
       <c r="C712" t="s">
+        <v>982</v>
+      </c>
+      <c r="D712" t="s">
         <v>1014</v>
-      </c>
-      <c r="D712" t="s">
-        <v>983</v>
       </c>
       <c r="E712" t="s">
         <v>24</v>
@@ -18607,10 +18607,10 @@
         <v>7</v>
       </c>
       <c r="C713" t="s">
+        <v>982</v>
+      </c>
+      <c r="D713" t="s">
         <v>1017</v>
-      </c>
-      <c r="D713" t="s">
-        <v>983</v>
       </c>
       <c r="E713" t="s">
         <v>24</v>
@@ -18627,10 +18627,10 @@
         <v>7</v>
       </c>
       <c r="C714" t="s">
+        <v>982</v>
+      </c>
+      <c r="D714" t="s">
         <v>989</v>
-      </c>
-      <c r="D714" t="s">
-        <v>983</v>
       </c>
       <c r="E714" t="s">
         <v>15</v>
@@ -18647,10 +18647,10 @@
         <v>7</v>
       </c>
       <c r="C715" t="s">
+        <v>982</v>
+      </c>
+      <c r="D715" t="s">
         <v>1021</v>
-      </c>
-      <c r="D715" t="s">
-        <v>983</v>
       </c>
       <c r="E715" t="s">
         <v>24</v>
@@ -18667,10 +18667,10 @@
         <v>7</v>
       </c>
       <c r="C716" t="s">
+        <v>982</v>
+      </c>
+      <c r="D716" t="s">
         <v>989</v>
-      </c>
-      <c r="D716" t="s">
-        <v>983</v>
       </c>
       <c r="E716" t="s">
         <v>15</v>
@@ -18687,10 +18687,10 @@
         <v>7</v>
       </c>
       <c r="C717" t="s">
+        <v>982</v>
+      </c>
+      <c r="D717" t="s">
         <v>1025</v>
-      </c>
-      <c r="D717" t="s">
-        <v>983</v>
       </c>
       <c r="E717" t="s">
         <v>24</v>
@@ -18707,10 +18707,10 @@
         <v>7</v>
       </c>
       <c r="C718" t="s">
+        <v>982</v>
+      </c>
+      <c r="D718" t="s">
         <v>1028</v>
-      </c>
-      <c r="D718" t="s">
-        <v>983</v>
       </c>
       <c r="E718" t="s">
         <v>24</v>
@@ -18727,10 +18727,10 @@
         <v>7</v>
       </c>
       <c r="C719" t="s">
+        <v>982</v>
+      </c>
+      <c r="D719" t="s">
         <v>989</v>
-      </c>
-      <c r="D719" t="s">
-        <v>983</v>
       </c>
       <c r="E719" t="s">
         <v>720</v>
@@ -18747,10 +18747,10 @@
         <v>7</v>
       </c>
       <c r="C720" t="s">
+        <v>982</v>
+      </c>
+      <c r="D720" t="s">
         <v>1031</v>
-      </c>
-      <c r="D720" t="s">
-        <v>983</v>
       </c>
       <c r="E720" t="s">
         <v>15</v>
@@ -18767,10 +18767,10 @@
         <v>7</v>
       </c>
       <c r="C721" t="s">
+        <v>982</v>
+      </c>
+      <c r="D721" t="s">
         <v>989</v>
-      </c>
-      <c r="D721" t="s">
-        <v>983</v>
       </c>
       <c r="E721" t="s">
         <v>720</v>
@@ -18787,10 +18787,10 @@
         <v>7</v>
       </c>
       <c r="C722" t="s">
+        <v>982</v>
+      </c>
+      <c r="D722" t="s">
         <v>989</v>
-      </c>
-      <c r="D722" t="s">
-        <v>983</v>
       </c>
       <c r="E722" t="s">
         <v>720</v>
@@ -18807,10 +18807,10 @@
         <v>112</v>
       </c>
       <c r="C723" t="s">
+        <v>982</v>
+      </c>
+      <c r="D723" t="s">
         <v>989</v>
-      </c>
-      <c r="D723" t="s">
-        <v>983</v>
       </c>
       <c r="E723" t="s">
         <v>15</v>
@@ -18827,10 +18827,10 @@
         <v>7</v>
       </c>
       <c r="C724" t="s">
+        <v>982</v>
+      </c>
+      <c r="D724" t="s">
         <v>1036</v>
-      </c>
-      <c r="D724" t="s">
-        <v>983</v>
       </c>
       <c r="E724" t="s">
         <v>24</v>
@@ -18847,10 +18847,10 @@
         <v>7</v>
       </c>
       <c r="C725" t="s">
+        <v>982</v>
+      </c>
+      <c r="D725" t="s">
         <v>989</v>
-      </c>
-      <c r="D725" t="s">
-        <v>983</v>
       </c>
       <c r="E725" t="s">
         <v>720</v>
@@ -18867,10 +18867,10 @@
         <v>7</v>
       </c>
       <c r="C726" t="s">
+        <v>982</v>
+      </c>
+      <c r="D726" t="s">
         <v>1039</v>
-      </c>
-      <c r="D726" t="s">
-        <v>983</v>
       </c>
       <c r="E726" t="s">
         <v>24</v>
@@ -18887,10 +18887,10 @@
         <v>7</v>
       </c>
       <c r="C727" t="s">
+        <v>982</v>
+      </c>
+      <c r="D727" t="s">
         <v>989</v>
-      </c>
-      <c r="D727" t="s">
-        <v>983</v>
       </c>
       <c r="E727" t="s">
         <v>720</v>
@@ -18907,10 +18907,10 @@
         <v>7</v>
       </c>
       <c r="C728" t="s">
+        <v>982</v>
+      </c>
+      <c r="D728" t="s">
         <v>989</v>
-      </c>
-      <c r="D728" t="s">
-        <v>983</v>
       </c>
       <c r="E728" t="s">
         <v>720</v>
@@ -18927,10 +18927,10 @@
         <v>7</v>
       </c>
       <c r="C729" t="s">
+        <v>982</v>
+      </c>
+      <c r="D729" t="s">
         <v>998</v>
-      </c>
-      <c r="D729" t="s">
-        <v>983</v>
       </c>
       <c r="E729" t="s">
         <v>24</v>
@@ -18947,10 +18947,10 @@
         <v>7</v>
       </c>
       <c r="C730" t="s">
+        <v>982</v>
+      </c>
+      <c r="D730" t="s">
         <v>989</v>
-      </c>
-      <c r="D730" t="s">
-        <v>983</v>
       </c>
       <c r="E730" t="s">
         <v>13</v>
@@ -18967,10 +18967,10 @@
         <v>112</v>
       </c>
       <c r="C731" t="s">
+        <v>982</v>
+      </c>
+      <c r="D731" t="s">
         <v>989</v>
-      </c>
-      <c r="D731" t="s">
-        <v>983</v>
       </c>
       <c r="E731" t="s">
         <v>720</v>
@@ -18987,10 +18987,10 @@
         <v>7</v>
       </c>
       <c r="C732" t="s">
+        <v>982</v>
+      </c>
+      <c r="D732" t="s">
         <v>1014</v>
-      </c>
-      <c r="D732" t="s">
-        <v>983</v>
       </c>
       <c r="E732" t="s">
         <v>24</v>
@@ -19007,10 +19007,10 @@
         <v>7</v>
       </c>
       <c r="C733" t="s">
+        <v>982</v>
+      </c>
+      <c r="D733" t="s">
         <v>989</v>
-      </c>
-      <c r="D733" t="s">
-        <v>983</v>
       </c>
       <c r="E733" t="s">
         <v>720</v>
@@ -19027,10 +19027,10 @@
         <v>7</v>
       </c>
       <c r="C734" t="s">
+        <v>982</v>
+      </c>
+      <c r="D734" t="s">
         <v>989</v>
-      </c>
-      <c r="D734" t="s">
-        <v>983</v>
       </c>
       <c r="E734" t="s">
         <v>720</v>
@@ -19067,10 +19067,10 @@
         <v>7</v>
       </c>
       <c r="C736" t="s">
+        <v>1050</v>
+      </c>
+      <c r="D736" t="s">
         <v>1054</v>
-      </c>
-      <c r="D736" t="s">
-        <v>1051</v>
       </c>
       <c r="E736" t="s">
         <v>720</v>
@@ -19087,10 +19087,10 @@
         <v>7</v>
       </c>
       <c r="C737" t="s">
+        <v>1050</v>
+      </c>
+      <c r="D737" t="s">
         <v>1054</v>
-      </c>
-      <c r="D737" t="s">
-        <v>1051</v>
       </c>
       <c r="E737" t="s">
         <v>720</v>
@@ -19107,10 +19107,10 @@
         <v>7</v>
       </c>
       <c r="C738" t="s">
+        <v>1050</v>
+      </c>
+      <c r="D738" t="s">
         <v>1054</v>
-      </c>
-      <c r="D738" t="s">
-        <v>1051</v>
       </c>
       <c r="E738" t="s">
         <v>720</v>
@@ -19127,10 +19127,10 @@
         <v>7</v>
       </c>
       <c r="C739" t="s">
+        <v>1050</v>
+      </c>
+      <c r="D739" t="s">
         <v>1054</v>
-      </c>
-      <c r="D739" t="s">
-        <v>1051</v>
       </c>
       <c r="E739" t="s">
         <v>720</v>
@@ -19147,10 +19147,10 @@
         <v>7</v>
       </c>
       <c r="C740" t="s">
+        <v>1050</v>
+      </c>
+      <c r="D740" t="s">
         <v>1054</v>
-      </c>
-      <c r="D740" t="s">
-        <v>1051</v>
       </c>
       <c r="E740" t="s">
         <v>720</v>
@@ -19167,10 +19167,10 @@
         <v>7</v>
       </c>
       <c r="C741" t="s">
+        <v>1050</v>
+      </c>
+      <c r="D741" t="s">
         <v>1054</v>
-      </c>
-      <c r="D741" t="s">
-        <v>1051</v>
       </c>
       <c r="E741" t="s">
         <v>15</v>
@@ -19187,10 +19187,10 @@
         <v>7</v>
       </c>
       <c r="C742" t="s">
+        <v>1050</v>
+      </c>
+      <c r="D742" t="s">
         <v>1061</v>
-      </c>
-      <c r="D742" t="s">
-        <v>1051</v>
       </c>
       <c r="E742" t="s">
         <v>15</v>
@@ -19207,10 +19207,10 @@
         <v>7</v>
       </c>
       <c r="C743" t="s">
+        <v>1050</v>
+      </c>
+      <c r="D743" t="s">
         <v>1064</v>
-      </c>
-      <c r="D743" t="s">
-        <v>1051</v>
       </c>
       <c r="E743" t="s">
         <v>15</v>
@@ -19227,10 +19227,10 @@
         <v>7</v>
       </c>
       <c r="C744" t="s">
+        <v>1050</v>
+      </c>
+      <c r="D744" t="s">
         <v>1054</v>
-      </c>
-      <c r="D744" t="s">
-        <v>1051</v>
       </c>
       <c r="E744" t="s">
         <v>720</v>
@@ -19247,10 +19247,10 @@
         <v>7</v>
       </c>
       <c r="C745" t="s">
+        <v>1050</v>
+      </c>
+      <c r="D745" t="s">
         <v>1054</v>
-      </c>
-      <c r="D745" t="s">
-        <v>1051</v>
       </c>
       <c r="E745" t="s">
         <v>720</v>
@@ -19267,10 +19267,10 @@
         <v>7</v>
       </c>
       <c r="C746" t="s">
+        <v>1050</v>
+      </c>
+      <c r="D746" t="s">
         <v>1069</v>
-      </c>
-      <c r="D746" t="s">
-        <v>1051</v>
       </c>
       <c r="E746" t="s">
         <v>24</v>
@@ -19287,10 +19287,10 @@
         <v>7</v>
       </c>
       <c r="C747" t="s">
+        <v>1050</v>
+      </c>
+      <c r="D747" t="s">
         <v>1054</v>
-      </c>
-      <c r="D747" t="s">
-        <v>1051</v>
       </c>
       <c r="E747" t="s">
         <v>13</v>
@@ -19307,10 +19307,10 @@
         <v>7</v>
       </c>
       <c r="C748" t="s">
+        <v>1050</v>
+      </c>
+      <c r="D748" t="s">
         <v>1069</v>
-      </c>
-      <c r="D748" t="s">
-        <v>1051</v>
       </c>
       <c r="E748" t="s">
         <v>24</v>
@@ -19327,10 +19327,10 @@
         <v>7</v>
       </c>
       <c r="C749" t="s">
+        <v>1050</v>
+      </c>
+      <c r="D749" t="s">
         <v>1074</v>
-      </c>
-      <c r="D749" t="s">
-        <v>1051</v>
       </c>
       <c r="E749" t="s">
         <v>24</v>
@@ -19347,10 +19347,10 @@
         <v>7</v>
       </c>
       <c r="C750" t="s">
+        <v>1050</v>
+      </c>
+      <c r="D750" t="s">
         <v>1077</v>
-      </c>
-      <c r="D750" t="s">
-        <v>1051</v>
       </c>
       <c r="E750" t="s">
         <v>24</v>
@@ -19367,10 +19367,10 @@
         <v>7</v>
       </c>
       <c r="C751" t="s">
+        <v>1050</v>
+      </c>
+      <c r="D751" t="s">
         <v>1079</v>
-      </c>
-      <c r="D751" t="s">
-        <v>1051</v>
       </c>
       <c r="E751" t="s">
         <v>24</v>
@@ -19387,10 +19387,10 @@
         <v>7</v>
       </c>
       <c r="C752" t="s">
+        <v>1050</v>
+      </c>
+      <c r="D752" t="s">
         <v>1054</v>
-      </c>
-      <c r="D752" t="s">
-        <v>1051</v>
       </c>
       <c r="E752" t="s">
         <v>720</v>
@@ -19407,10 +19407,10 @@
         <v>7</v>
       </c>
       <c r="C753" t="s">
+        <v>1050</v>
+      </c>
+      <c r="D753" t="s">
         <v>1083</v>
-      </c>
-      <c r="D753" t="s">
-        <v>1051</v>
       </c>
       <c r="E753" t="s">
         <v>720</v>
@@ -19427,10 +19427,10 @@
         <v>7</v>
       </c>
       <c r="C754" t="s">
+        <v>1050</v>
+      </c>
+      <c r="D754" t="s">
         <v>1054</v>
-      </c>
-      <c r="D754" t="s">
-        <v>1051</v>
       </c>
       <c r="E754" t="s">
         <v>15</v>
@@ -19447,10 +19447,10 @@
         <v>7</v>
       </c>
       <c r="C755" t="s">
+        <v>1050</v>
+      </c>
+      <c r="D755" t="s">
         <v>1086</v>
-      </c>
-      <c r="D755" t="s">
-        <v>1051</v>
       </c>
       <c r="E755" t="s">
         <v>15</v>
@@ -19467,10 +19467,10 @@
         <v>7</v>
       </c>
       <c r="C756" t="s">
+        <v>1050</v>
+      </c>
+      <c r="D756" t="s">
         <v>1054</v>
-      </c>
-      <c r="D756" t="s">
-        <v>1051</v>
       </c>
       <c r="E756" t="s">
         <v>720</v>
@@ -19487,10 +19487,10 @@
         <v>7</v>
       </c>
       <c r="C757" t="s">
+        <v>1050</v>
+      </c>
+      <c r="D757" t="s">
         <v>1054</v>
-      </c>
-      <c r="D757" t="s">
-        <v>1051</v>
       </c>
       <c r="E757" t="s">
         <v>720</v>
@@ -19507,10 +19507,10 @@
         <v>7</v>
       </c>
       <c r="C758" t="s">
+        <v>1050</v>
+      </c>
+      <c r="D758" t="s">
         <v>1090</v>
-      </c>
-      <c r="D758" t="s">
-        <v>1051</v>
       </c>
       <c r="E758" t="s">
         <v>24</v>
@@ -19527,10 +19527,10 @@
         <v>7</v>
       </c>
       <c r="C759" t="s">
+        <v>1050</v>
+      </c>
+      <c r="D759" t="s">
         <v>1093</v>
-      </c>
-      <c r="D759" t="s">
-        <v>1051</v>
       </c>
       <c r="E759" t="s">
         <v>15</v>
@@ -19547,10 +19547,10 @@
         <v>7</v>
       </c>
       <c r="C760" t="s">
+        <v>1050</v>
+      </c>
+      <c r="D760" t="s">
         <v>1054</v>
-      </c>
-      <c r="D760" t="s">
-        <v>1051</v>
       </c>
       <c r="E760" t="s">
         <v>720</v>
@@ -19587,10 +19587,10 @@
         <v>7</v>
       </c>
       <c r="C762" t="s">
+        <v>1050</v>
+      </c>
+      <c r="D762" t="s">
         <v>1097</v>
-      </c>
-      <c r="D762" t="s">
-        <v>1051</v>
       </c>
       <c r="E762" t="s">
         <v>24</v>
@@ -19607,10 +19607,10 @@
         <v>7</v>
       </c>
       <c r="C763" t="s">
+        <v>1050</v>
+      </c>
+      <c r="D763" t="s">
         <v>1054</v>
-      </c>
-      <c r="D763" t="s">
-        <v>1051</v>
       </c>
       <c r="E763" t="s">
         <v>720</v>
@@ -19627,10 +19627,10 @@
         <v>7</v>
       </c>
       <c r="C764" t="s">
+        <v>1050</v>
+      </c>
+      <c r="D764" t="s">
         <v>1054</v>
-      </c>
-      <c r="D764" t="s">
-        <v>1051</v>
       </c>
       <c r="E764" t="s">
         <v>13</v>
@@ -19647,10 +19647,10 @@
         <v>112</v>
       </c>
       <c r="C765" t="s">
+        <v>1050</v>
+      </c>
+      <c r="D765" t="s">
         <v>1054</v>
-      </c>
-      <c r="D765" t="s">
-        <v>1051</v>
       </c>
       <c r="E765" t="s">
         <v>720</v>
@@ -19667,10 +19667,10 @@
         <v>7</v>
       </c>
       <c r="C766" t="s">
+        <v>1050</v>
+      </c>
+      <c r="D766" t="s">
         <v>1054</v>
-      </c>
-      <c r="D766" t="s">
-        <v>1051</v>
       </c>
       <c r="E766" t="s">
         <v>720</v>
@@ -19687,10 +19687,10 @@
         <v>7</v>
       </c>
       <c r="C767" t="s">
+        <v>1050</v>
+      </c>
+      <c r="D767" t="s">
         <v>1054</v>
-      </c>
-      <c r="D767" t="s">
-        <v>1051</v>
       </c>
       <c r="E767" t="s">
         <v>720</v>
@@ -19727,10 +19727,10 @@
         <v>7</v>
       </c>
       <c r="C769" t="s">
+        <v>1104</v>
+      </c>
+      <c r="D769" t="s">
         <v>1108</v>
-      </c>
-      <c r="D769" t="s">
-        <v>1105</v>
       </c>
       <c r="E769" t="s">
         <v>24</v>
@@ -19747,10 +19747,10 @@
         <v>7</v>
       </c>
       <c r="C770" t="s">
+        <v>1104</v>
+      </c>
+      <c r="D770" t="s">
         <v>1111</v>
-      </c>
-      <c r="D770" t="s">
-        <v>1105</v>
       </c>
       <c r="E770" t="s">
         <v>720</v>
@@ -19767,10 +19767,10 @@
         <v>7</v>
       </c>
       <c r="C771" t="s">
+        <v>1104</v>
+      </c>
+      <c r="D771" t="s">
         <v>1111</v>
-      </c>
-      <c r="D771" t="s">
-        <v>1105</v>
       </c>
       <c r="E771" t="s">
         <v>720</v>
@@ -19787,10 +19787,10 @@
         <v>7</v>
       </c>
       <c r="C772" t="s">
+        <v>1104</v>
+      </c>
+      <c r="D772" t="s">
         <v>1111</v>
-      </c>
-      <c r="D772" t="s">
-        <v>1105</v>
       </c>
       <c r="E772" t="s">
         <v>720</v>
@@ -19807,10 +19807,10 @@
         <v>7</v>
       </c>
       <c r="C773" t="s">
+        <v>1104</v>
+      </c>
+      <c r="D773" t="s">
         <v>1111</v>
-      </c>
-      <c r="D773" t="s">
-        <v>1105</v>
       </c>
       <c r="E773" t="s">
         <v>720</v>
@@ -19827,10 +19827,10 @@
         <v>7</v>
       </c>
       <c r="C774" t="s">
+        <v>1104</v>
+      </c>
+      <c r="D774" t="s">
         <v>1111</v>
-      </c>
-      <c r="D774" t="s">
-        <v>1105</v>
       </c>
       <c r="E774" t="s">
         <v>720</v>
@@ -19847,10 +19847,10 @@
         <v>7</v>
       </c>
       <c r="C775" t="s">
+        <v>1104</v>
+      </c>
+      <c r="D775" t="s">
         <v>1111</v>
-      </c>
-      <c r="D775" t="s">
-        <v>1105</v>
       </c>
       <c r="E775" t="s">
         <v>720</v>
@@ -19887,10 +19887,10 @@
         <v>7</v>
       </c>
       <c r="C777" t="s">
+        <v>1104</v>
+      </c>
+      <c r="D777" t="s">
         <v>1083</v>
-      </c>
-      <c r="D777" t="s">
-        <v>1105</v>
       </c>
       <c r="E777" t="s">
         <v>15</v>
@@ -19907,10 +19907,10 @@
         <v>7</v>
       </c>
       <c r="C778" t="s">
+        <v>1104</v>
+      </c>
+      <c r="D778" t="s">
         <v>1111</v>
-      </c>
-      <c r="D778" t="s">
-        <v>1105</v>
       </c>
       <c r="E778" t="s">
         <v>720</v>
@@ -19927,10 +19927,10 @@
         <v>7</v>
       </c>
       <c r="C779" t="s">
+        <v>1104</v>
+      </c>
+      <c r="D779" t="s">
         <v>1111</v>
-      </c>
-      <c r="D779" t="s">
-        <v>1105</v>
       </c>
       <c r="E779" t="s">
         <v>13</v>
@@ -19947,10 +19947,10 @@
         <v>112</v>
       </c>
       <c r="C780" t="s">
+        <v>1104</v>
+      </c>
+      <c r="D780" t="s">
         <v>1111</v>
-      </c>
-      <c r="D780" t="s">
-        <v>1105</v>
       </c>
       <c r="E780" t="s">
         <v>720</v>
@@ -19967,10 +19967,10 @@
         <v>7</v>
       </c>
       <c r="C781" t="s">
+        <v>1104</v>
+      </c>
+      <c r="D781" t="s">
         <v>1083</v>
-      </c>
-      <c r="D781" t="s">
-        <v>1105</v>
       </c>
       <c r="E781" t="s">
         <v>24</v>
@@ -19987,10 +19987,10 @@
         <v>7</v>
       </c>
       <c r="C782" t="s">
+        <v>1104</v>
+      </c>
+      <c r="D782" t="s">
         <v>1111</v>
-      </c>
-      <c r="D782" t="s">
-        <v>1105</v>
       </c>
       <c r="E782" t="s">
         <v>720</v>
@@ -20007,10 +20007,10 @@
         <v>7</v>
       </c>
       <c r="C783" t="s">
+        <v>1104</v>
+      </c>
+      <c r="D783" t="s">
         <v>1127</v>
-      </c>
-      <c r="D783" t="s">
-        <v>1105</v>
       </c>
       <c r="E783" t="s">
         <v>24</v>
@@ -20027,10 +20027,10 @@
         <v>112</v>
       </c>
       <c r="C784" t="s">
+        <v>1104</v>
+      </c>
+      <c r="D784" t="s">
         <v>1111</v>
-      </c>
-      <c r="D784" t="s">
-        <v>1105</v>
       </c>
       <c r="E784" t="s">
         <v>24</v>
@@ -20047,10 +20047,10 @@
         <v>7</v>
       </c>
       <c r="C785" t="s">
+        <v>1104</v>
+      </c>
+      <c r="D785" t="s">
         <v>1131</v>
-      </c>
-      <c r="D785" t="s">
-        <v>1105</v>
       </c>
       <c r="E785" t="s">
         <v>24</v>
@@ -20067,10 +20067,10 @@
         <v>7</v>
       </c>
       <c r="C786" t="s">
+        <v>1104</v>
+      </c>
+      <c r="D786" t="s">
         <v>1133</v>
-      </c>
-      <c r="D786" t="s">
-        <v>1105</v>
       </c>
       <c r="E786" t="s">
         <v>24</v>
@@ -20087,10 +20087,10 @@
         <v>7</v>
       </c>
       <c r="C787" t="s">
+        <v>1104</v>
+      </c>
+      <c r="D787" t="s">
         <v>1111</v>
-      </c>
-      <c r="D787" t="s">
-        <v>1105</v>
       </c>
       <c r="E787" t="s">
         <v>720</v>
@@ -20107,10 +20107,10 @@
         <v>7</v>
       </c>
       <c r="C788" t="s">
+        <v>1104</v>
+      </c>
+      <c r="D788" t="s">
         <v>1111</v>
-      </c>
-      <c r="D788" t="s">
-        <v>1105</v>
       </c>
       <c r="E788" t="s">
         <v>720</v>
@@ -20127,10 +20127,10 @@
         <v>7</v>
       </c>
       <c r="C789" t="s">
+        <v>1104</v>
+      </c>
+      <c r="D789" t="s">
         <v>1138</v>
-      </c>
-      <c r="D789" t="s">
-        <v>1105</v>
       </c>
       <c r="E789" t="s">
         <v>13</v>
@@ -20147,10 +20147,10 @@
         <v>7</v>
       </c>
       <c r="C790" t="s">
+        <v>1104</v>
+      </c>
+      <c r="D790" t="s">
         <v>1111</v>
-      </c>
-      <c r="D790" t="s">
-        <v>1105</v>
       </c>
       <c r="E790" t="s">
         <v>15</v>
@@ -20167,10 +20167,10 @@
         <v>112</v>
       </c>
       <c r="C791" t="s">
+        <v>1104</v>
+      </c>
+      <c r="D791" t="s">
         <v>1142</v>
-      </c>
-      <c r="D791" t="s">
-        <v>1105</v>
       </c>
       <c r="E791" t="s">
         <v>24</v>
@@ -20187,10 +20187,10 @@
         <v>112</v>
       </c>
       <c r="C792" t="s">
+        <v>1104</v>
+      </c>
+      <c r="D792" t="s">
         <v>1111</v>
-      </c>
-      <c r="D792" t="s">
-        <v>1105</v>
       </c>
       <c r="E792" t="s">
         <v>720</v>
@@ -20207,10 +20207,10 @@
         <v>7</v>
       </c>
       <c r="C793" t="s">
+        <v>1104</v>
+      </c>
+      <c r="D793" t="s">
         <v>1111</v>
-      </c>
-      <c r="D793" t="s">
-        <v>1105</v>
       </c>
       <c r="E793" t="s">
         <v>720</v>
@@ -20227,10 +20227,10 @@
         <v>7</v>
       </c>
       <c r="C794" t="s">
+        <v>1104</v>
+      </c>
+      <c r="D794" t="s">
         <v>1111</v>
-      </c>
-      <c r="D794" t="s">
-        <v>1105</v>
       </c>
       <c r="E794" t="s">
         <v>13</v>
@@ -20247,10 +20247,10 @@
         <v>112</v>
       </c>
       <c r="C795" t="s">
+        <v>1104</v>
+      </c>
+      <c r="D795" t="s">
         <v>1138</v>
-      </c>
-      <c r="D795" t="s">
-        <v>1105</v>
       </c>
       <c r="E795" t="s">
         <v>24</v>
@@ -20267,10 +20267,10 @@
         <v>7</v>
       </c>
       <c r="C796" t="s">
+        <v>1104</v>
+      </c>
+      <c r="D796" t="s">
         <v>1111</v>
-      </c>
-      <c r="D796" t="s">
-        <v>1105</v>
       </c>
       <c r="E796" t="s">
         <v>720</v>
@@ -20307,10 +20307,10 @@
         <v>7</v>
       </c>
       <c r="C798" t="s">
+        <v>1150</v>
+      </c>
+      <c r="D798" t="s">
         <v>1154</v>
-      </c>
-      <c r="D798" t="s">
-        <v>1151</v>
       </c>
       <c r="E798" t="s">
         <v>720</v>
@@ -20327,10 +20327,10 @@
         <v>7</v>
       </c>
       <c r="C799" t="s">
+        <v>1150</v>
+      </c>
+      <c r="D799" t="s">
         <v>1156</v>
-      </c>
-      <c r="D799" t="s">
-        <v>1151</v>
       </c>
       <c r="E799" t="s">
         <v>24</v>
@@ -20347,10 +20347,10 @@
         <v>7</v>
       </c>
       <c r="C800" t="s">
+        <v>1150</v>
+      </c>
+      <c r="D800" t="s">
         <v>1159</v>
-      </c>
-      <c r="D800" t="s">
-        <v>1151</v>
       </c>
       <c r="E800" t="s">
         <v>24</v>
@@ -20367,10 +20367,10 @@
         <v>7</v>
       </c>
       <c r="C801" t="s">
+        <v>1150</v>
+      </c>
+      <c r="D801" t="s">
         <v>1154</v>
-      </c>
-      <c r="D801" t="s">
-        <v>1151</v>
       </c>
       <c r="E801" t="s">
         <v>720</v>
@@ -20387,10 +20387,10 @@
         <v>7</v>
       </c>
       <c r="C802" t="s">
+        <v>1150</v>
+      </c>
+      <c r="D802" t="s">
         <v>1154</v>
-      </c>
-      <c r="D802" t="s">
-        <v>1151</v>
       </c>
       <c r="E802" t="s">
         <v>720</v>
@@ -20407,10 +20407,10 @@
         <v>7</v>
       </c>
       <c r="C803" t="s">
+        <v>1150</v>
+      </c>
+      <c r="D803" t="s">
         <v>1164</v>
-      </c>
-      <c r="D803" t="s">
-        <v>1151</v>
       </c>
       <c r="E803" t="s">
         <v>720</v>
@@ -20427,10 +20427,10 @@
         <v>7</v>
       </c>
       <c r="C804" t="s">
+        <v>1150</v>
+      </c>
+      <c r="D804" t="s">
         <v>1154</v>
-      </c>
-      <c r="D804" t="s">
-        <v>1151</v>
       </c>
       <c r="E804" t="s">
         <v>720</v>
@@ -20447,10 +20447,10 @@
         <v>7</v>
       </c>
       <c r="C805" t="s">
+        <v>1150</v>
+      </c>
+      <c r="D805" t="s">
         <v>1154</v>
-      </c>
-      <c r="D805" t="s">
-        <v>1151</v>
       </c>
       <c r="E805" t="s">
         <v>13</v>
@@ -20467,10 +20467,10 @@
         <v>112</v>
       </c>
       <c r="C806" t="s">
+        <v>1150</v>
+      </c>
+      <c r="D806" t="s">
         <v>1154</v>
-      </c>
-      <c r="D806" t="s">
-        <v>1151</v>
       </c>
       <c r="E806" t="s">
         <v>720</v>
@@ -20487,10 +20487,10 @@
         <v>7</v>
       </c>
       <c r="C807" t="s">
+        <v>1150</v>
+      </c>
+      <c r="D807" t="s">
         <v>1154</v>
-      </c>
-      <c r="D807" t="s">
-        <v>1151</v>
       </c>
       <c r="E807" t="s">
         <v>720</v>
@@ -20507,10 +20507,10 @@
         <v>7</v>
       </c>
       <c r="C808" t="s">
+        <v>1150</v>
+      </c>
+      <c r="D808" t="s">
         <v>1154</v>
-      </c>
-      <c r="D808" t="s">
-        <v>1151</v>
       </c>
       <c r="E808" t="s">
         <v>720</v>
@@ -20527,10 +20527,10 @@
         <v>7</v>
       </c>
       <c r="C809" t="s">
+        <v>1150</v>
+      </c>
+      <c r="D809" t="s">
         <v>1154</v>
-      </c>
-      <c r="D809" t="s">
-        <v>1151</v>
       </c>
       <c r="E809" t="s">
         <v>720</v>
@@ -20547,10 +20547,10 @@
         <v>112</v>
       </c>
       <c r="C810" t="s">
+        <v>1150</v>
+      </c>
+      <c r="D810" t="s">
         <v>1154</v>
-      </c>
-      <c r="D810" t="s">
-        <v>1151</v>
       </c>
       <c r="E810" t="s">
         <v>720</v>
@@ -20587,10 +20587,10 @@
         <v>7</v>
       </c>
       <c r="C812" t="s">
+        <v>1150</v>
+      </c>
+      <c r="D812" t="s">
         <v>1154</v>
-      </c>
-      <c r="D812" t="s">
-        <v>1151</v>
       </c>
       <c r="E812" t="s">
         <v>720</v>
@@ -20607,10 +20607,10 @@
         <v>7</v>
       </c>
       <c r="C813" t="s">
+        <v>1150</v>
+      </c>
+      <c r="D813" t="s">
         <v>1164</v>
-      </c>
-      <c r="D813" t="s">
-        <v>1151</v>
       </c>
       <c r="E813" t="s">
         <v>24</v>
@@ -20627,10 +20627,10 @@
         <v>7</v>
       </c>
       <c r="C814" t="s">
+        <v>1150</v>
+      </c>
+      <c r="D814" t="s">
         <v>1178</v>
-      </c>
-      <c r="D814" t="s">
-        <v>1151</v>
       </c>
       <c r="E814" t="s">
         <v>24</v>
@@ -20647,10 +20647,10 @@
         <v>7</v>
       </c>
       <c r="C815" t="s">
+        <v>1150</v>
+      </c>
+      <c r="D815" t="s">
         <v>1154</v>
-      </c>
-      <c r="D815" t="s">
-        <v>1151</v>
       </c>
       <c r="E815" t="s">
         <v>720</v>
@@ -20667,10 +20667,10 @@
         <v>7</v>
       </c>
       <c r="C816" t="s">
+        <v>1150</v>
+      </c>
+      <c r="D816" t="s">
         <v>1154</v>
-      </c>
-      <c r="D816" t="s">
-        <v>1151</v>
       </c>
       <c r="E816" t="s">
         <v>24</v>
@@ -20687,10 +20687,10 @@
         <v>7</v>
       </c>
       <c r="C817" t="s">
+        <v>1150</v>
+      </c>
+      <c r="D817" t="s">
         <v>1183</v>
-      </c>
-      <c r="D817" t="s">
-        <v>1151</v>
       </c>
       <c r="E817" t="s">
         <v>24</v>
@@ -20707,10 +20707,10 @@
         <v>7</v>
       </c>
       <c r="C818" t="s">
+        <v>1150</v>
+      </c>
+      <c r="D818" t="s">
         <v>1154</v>
-      </c>
-      <c r="D818" t="s">
-        <v>1151</v>
       </c>
       <c r="E818" t="s">
         <v>720</v>
@@ -20727,10 +20727,10 @@
         <v>7</v>
       </c>
       <c r="C819" t="s">
+        <v>1150</v>
+      </c>
+      <c r="D819" t="s">
         <v>1186</v>
-      </c>
-      <c r="D819" t="s">
-        <v>1151</v>
       </c>
       <c r="E819" t="s">
         <v>24</v>
@@ -20747,10 +20747,10 @@
         <v>7</v>
       </c>
       <c r="C820" t="s">
+        <v>1150</v>
+      </c>
+      <c r="D820" t="s">
         <v>1189</v>
-      </c>
-      <c r="D820" t="s">
-        <v>1151</v>
       </c>
       <c r="E820" t="s">
         <v>24</v>
@@ -20767,10 +20767,10 @@
         <v>7</v>
       </c>
       <c r="C821" t="s">
+        <v>1150</v>
+      </c>
+      <c r="D821" t="s">
         <v>1154</v>
-      </c>
-      <c r="D821" t="s">
-        <v>1151</v>
       </c>
       <c r="E821" t="s">
         <v>720</v>
@@ -20787,10 +20787,10 @@
         <v>7</v>
       </c>
       <c r="C822" t="s">
+        <v>1150</v>
+      </c>
+      <c r="D822" t="s">
         <v>1154</v>
-      </c>
-      <c r="D822" t="s">
-        <v>1151</v>
       </c>
       <c r="E822" t="s">
         <v>720</v>
@@ -20807,10 +20807,10 @@
         <v>7</v>
       </c>
       <c r="C823" t="s">
+        <v>1150</v>
+      </c>
+      <c r="D823" t="s">
         <v>1154</v>
-      </c>
-      <c r="D823" t="s">
-        <v>1151</v>
       </c>
       <c r="E823" t="s">
         <v>720</v>
@@ -20827,10 +20827,10 @@
         <v>7</v>
       </c>
       <c r="C824" t="s">
+        <v>1150</v>
+      </c>
+      <c r="D824" t="s">
         <v>1154</v>
-      </c>
-      <c r="D824" t="s">
-        <v>1151</v>
       </c>
       <c r="E824" t="s">
         <v>720</v>
@@ -20847,10 +20847,10 @@
         <v>7</v>
       </c>
       <c r="C825" t="s">
+        <v>1150</v>
+      </c>
+      <c r="D825" t="s">
         <v>1154</v>
-      </c>
-      <c r="D825" t="s">
-        <v>1151</v>
       </c>
       <c r="E825" t="s">
         <v>720</v>
@@ -20867,10 +20867,10 @@
         <v>7</v>
       </c>
       <c r="C826" t="s">
+        <v>1150</v>
+      </c>
+      <c r="D826" t="s">
         <v>1154</v>
-      </c>
-      <c r="D826" t="s">
-        <v>1151</v>
       </c>
       <c r="E826" t="s">
         <v>720</v>
@@ -20887,10 +20887,10 @@
         <v>112</v>
       </c>
       <c r="C827" t="s">
+        <v>1150</v>
+      </c>
+      <c r="D827" t="s">
         <v>1154</v>
-      </c>
-      <c r="D827" t="s">
-        <v>1151</v>
       </c>
       <c r="E827" t="s">
         <v>720</v>
@@ -20907,10 +20907,10 @@
         <v>7</v>
       </c>
       <c r="C828" t="s">
+        <v>1150</v>
+      </c>
+      <c r="D828" t="s">
         <v>1154</v>
-      </c>
-      <c r="D828" t="s">
-        <v>1151</v>
       </c>
       <c r="E828" t="s">
         <v>720</v>
@@ -20927,10 +20927,10 @@
         <v>7</v>
       </c>
       <c r="C829" t="s">
+        <v>1150</v>
+      </c>
+      <c r="D829" t="s">
         <v>1154</v>
-      </c>
-      <c r="D829" t="s">
-        <v>1151</v>
       </c>
       <c r="E829" t="s">
         <v>720</v>
@@ -21007,10 +21007,10 @@
         <v>7</v>
       </c>
       <c r="C833" t="s">
+        <v>1201</v>
+      </c>
+      <c r="D833" t="s">
         <v>1208</v>
-      </c>
-      <c r="D833" t="s">
-        <v>1202</v>
       </c>
       <c r="E833" t="s">
         <v>24</v>
@@ -21067,10 +21067,10 @@
         <v>7</v>
       </c>
       <c r="C836" t="s">
+        <v>1201</v>
+      </c>
+      <c r="D836" t="s">
         <v>1208</v>
-      </c>
-      <c r="D836" t="s">
-        <v>1202</v>
       </c>
       <c r="E836" t="s">
         <v>13</v>
@@ -21087,10 +21087,10 @@
         <v>7</v>
       </c>
       <c r="C837" t="s">
+        <v>1201</v>
+      </c>
+      <c r="D837" t="s">
         <v>1214</v>
-      </c>
-      <c r="D837" t="s">
-        <v>1202</v>
       </c>
       <c r="E837" t="s">
         <v>13</v>
@@ -21107,10 +21107,10 @@
         <v>112</v>
       </c>
       <c r="C838" t="s">
+        <v>1201</v>
+      </c>
+      <c r="D838" t="s">
         <v>1208</v>
-      </c>
-      <c r="D838" t="s">
-        <v>1202</v>
       </c>
       <c r="E838" t="s">
         <v>720</v>
@@ -21127,10 +21127,10 @@
         <v>112</v>
       </c>
       <c r="C839" t="s">
+        <v>1201</v>
+      </c>
+      <c r="D839" t="s">
         <v>1214</v>
-      </c>
-      <c r="D839" t="s">
-        <v>1202</v>
       </c>
       <c r="E839" t="s">
         <v>24</v>
@@ -21267,10 +21267,10 @@
         <v>7</v>
       </c>
       <c r="C846" t="s">
+        <v>1201</v>
+      </c>
+      <c r="D846" t="s">
         <v>1225</v>
-      </c>
-      <c r="D846" t="s">
-        <v>1202</v>
       </c>
       <c r="E846" t="s">
         <v>15</v>
@@ -21287,10 +21287,10 @@
         <v>7</v>
       </c>
       <c r="C847" t="s">
+        <v>1201</v>
+      </c>
+      <c r="D847" t="s">
         <v>1228</v>
-      </c>
-      <c r="D847" t="s">
-        <v>1202</v>
       </c>
       <c r="E847" t="s">
         <v>1205</v>
@@ -21307,10 +21307,10 @@
         <v>7</v>
       </c>
       <c r="C848" t="s">
+        <v>1201</v>
+      </c>
+      <c r="D848" t="s">
         <v>1228</v>
-      </c>
-      <c r="D848" t="s">
-        <v>1202</v>
       </c>
       <c r="E848" t="s">
         <v>1205</v>
@@ -21327,10 +21327,10 @@
         <v>7</v>
       </c>
       <c r="C849" t="s">
+        <v>1201</v>
+      </c>
+      <c r="D849" t="s">
         <v>1228</v>
-      </c>
-      <c r="D849" t="s">
-        <v>1202</v>
       </c>
       <c r="E849" t="s">
         <v>1205</v>
@@ -21347,10 +21347,10 @@
         <v>7</v>
       </c>
       <c r="C850" t="s">
+        <v>1201</v>
+      </c>
+      <c r="D850" t="s">
         <v>1228</v>
-      </c>
-      <c r="D850" t="s">
-        <v>1202</v>
       </c>
       <c r="E850" t="s">
         <v>13</v>
@@ -21367,10 +21367,10 @@
         <v>112</v>
       </c>
       <c r="C851" t="s">
+        <v>1201</v>
+      </c>
+      <c r="D851" t="s">
         <v>1228</v>
-      </c>
-      <c r="D851" t="s">
-        <v>1202</v>
       </c>
       <c r="E851" t="s">
         <v>720</v>
@@ -21387,10 +21387,10 @@
         <v>7</v>
       </c>
       <c r="C852" t="s">
+        <v>1201</v>
+      </c>
+      <c r="D852" t="s">
         <v>1228</v>
-      </c>
-      <c r="D852" t="s">
-        <v>1202</v>
       </c>
       <c r="E852" t="s">
         <v>1205</v>
@@ -21407,10 +21407,10 @@
         <v>7</v>
       </c>
       <c r="C853" t="s">
+        <v>1201</v>
+      </c>
+      <c r="D853" t="s">
         <v>1228</v>
-      </c>
-      <c r="D853" t="s">
-        <v>1202</v>
       </c>
       <c r="E853" t="s">
         <v>1205</v>
@@ -21427,10 +21427,10 @@
         <v>7</v>
       </c>
       <c r="C854" t="s">
+        <v>1201</v>
+      </c>
+      <c r="D854" t="s">
         <v>1228</v>
-      </c>
-      <c r="D854" t="s">
-        <v>1202</v>
       </c>
       <c r="E854" t="s">
         <v>1205</v>
@@ -21467,10 +21467,10 @@
         <v>7</v>
       </c>
       <c r="C856" t="s">
+        <v>1201</v>
+      </c>
+      <c r="D856" t="s">
         <v>1208</v>
-      </c>
-      <c r="D856" t="s">
-        <v>1202</v>
       </c>
       <c r="E856" t="s">
         <v>24</v>
@@ -21487,10 +21487,10 @@
         <v>112</v>
       </c>
       <c r="C857" t="s">
+        <v>1201</v>
+      </c>
+      <c r="D857" t="s">
         <v>1208</v>
-      </c>
-      <c r="D857" t="s">
-        <v>1202</v>
       </c>
       <c r="E857" t="s">
         <v>1205</v>
@@ -21687,10 +21687,10 @@
         <v>7</v>
       </c>
       <c r="C867" t="s">
+        <v>1249</v>
+      </c>
+      <c r="D867" t="s">
         <v>1253</v>
-      </c>
-      <c r="D867" t="s">
-        <v>1250</v>
       </c>
       <c r="E867" t="s">
         <v>1205</v>
@@ -21707,10 +21707,10 @@
         <v>7</v>
       </c>
       <c r="C868" t="s">
+        <v>1249</v>
+      </c>
+      <c r="D868" t="s">
         <v>1253</v>
-      </c>
-      <c r="D868" t="s">
-        <v>1250</v>
       </c>
       <c r="E868" t="s">
         <v>1205</v>
@@ -21727,10 +21727,10 @@
         <v>7</v>
       </c>
       <c r="C869" t="s">
+        <v>1249</v>
+      </c>
+      <c r="D869" t="s">
         <v>1253</v>
-      </c>
-      <c r="D869" t="s">
-        <v>1250</v>
       </c>
       <c r="E869" t="s">
         <v>1205</v>
@@ -21747,10 +21747,10 @@
         <v>7</v>
       </c>
       <c r="C870" t="s">
+        <v>1249</v>
+      </c>
+      <c r="D870" t="s">
         <v>1253</v>
-      </c>
-      <c r="D870" t="s">
-        <v>1250</v>
       </c>
       <c r="E870" t="s">
         <v>1205</v>
@@ -21767,10 +21767,10 @@
         <v>7</v>
       </c>
       <c r="C871" t="s">
+        <v>1249</v>
+      </c>
+      <c r="D871" t="s">
         <v>1253</v>
-      </c>
-      <c r="D871" t="s">
-        <v>1250</v>
       </c>
       <c r="E871" t="s">
         <v>1205</v>
@@ -21787,10 +21787,10 @@
         <v>7</v>
       </c>
       <c r="C872" t="s">
+        <v>1249</v>
+      </c>
+      <c r="D872" t="s">
         <v>1253</v>
-      </c>
-      <c r="D872" t="s">
-        <v>1250</v>
       </c>
       <c r="E872" t="s">
         <v>13</v>
@@ -21807,10 +21807,10 @@
         <v>112</v>
       </c>
       <c r="C873" t="s">
+        <v>1249</v>
+      </c>
+      <c r="D873" t="s">
         <v>1253</v>
-      </c>
-      <c r="D873" t="s">
-        <v>1250</v>
       </c>
       <c r="E873" t="s">
         <v>720</v>
@@ -21827,10 +21827,10 @@
         <v>7</v>
       </c>
       <c r="C874" t="s">
+        <v>1249</v>
+      </c>
+      <c r="D874" t="s">
         <v>1253</v>
-      </c>
-      <c r="D874" t="s">
-        <v>1250</v>
       </c>
       <c r="E874" t="s">
         <v>1205</v>
@@ -21847,10 +21847,10 @@
         <v>7</v>
       </c>
       <c r="C875" t="s">
+        <v>1249</v>
+      </c>
+      <c r="D875" t="s">
         <v>1262</v>
-      </c>
-      <c r="D875" t="s">
-        <v>1250</v>
       </c>
       <c r="E875" t="s">
         <v>1205</v>
@@ -21867,10 +21867,10 @@
         <v>7</v>
       </c>
       <c r="C876" t="s">
+        <v>1249</v>
+      </c>
+      <c r="D876" t="s">
         <v>1262</v>
-      </c>
-      <c r="D876" t="s">
-        <v>1250</v>
       </c>
       <c r="E876" t="s">
         <v>1205</v>
@@ -21887,10 +21887,10 @@
         <v>7</v>
       </c>
       <c r="C877" t="s">
+        <v>1249</v>
+      </c>
+      <c r="D877" t="s">
         <v>1262</v>
-      </c>
-      <c r="D877" t="s">
-        <v>1250</v>
       </c>
       <c r="E877" t="s">
         <v>13</v>
@@ -21907,10 +21907,10 @@
         <v>112</v>
       </c>
       <c r="C878" t="s">
+        <v>1249</v>
+      </c>
+      <c r="D878" t="s">
         <v>1262</v>
-      </c>
-      <c r="D878" t="s">
-        <v>1250</v>
       </c>
       <c r="E878" t="s">
         <v>720</v>
@@ -21927,10 +21927,10 @@
         <v>7</v>
       </c>
       <c r="C879" t="s">
+        <v>1249</v>
+      </c>
+      <c r="D879" t="s">
         <v>1262</v>
-      </c>
-      <c r="D879" t="s">
-        <v>1250</v>
       </c>
       <c r="E879" t="s">
         <v>1205</v>
@@ -21947,10 +21947,10 @@
         <v>7</v>
       </c>
       <c r="C880" t="s">
+        <v>1249</v>
+      </c>
+      <c r="D880" t="s">
         <v>1262</v>
-      </c>
-      <c r="D880" t="s">
-        <v>1250</v>
       </c>
       <c r="E880" t="s">
         <v>1205</v>
@@ -21967,10 +21967,10 @@
         <v>7</v>
       </c>
       <c r="C881" t="s">
+        <v>1249</v>
+      </c>
+      <c r="D881" t="s">
         <v>1262</v>
-      </c>
-      <c r="D881" t="s">
-        <v>1250</v>
       </c>
       <c r="E881" t="s">
         <v>1205</v>
@@ -21987,10 +21987,10 @@
         <v>7</v>
       </c>
       <c r="C882" t="s">
+        <v>1249</v>
+      </c>
+      <c r="D882" t="s">
         <v>1253</v>
-      </c>
-      <c r="D882" t="s">
-        <v>1250</v>
       </c>
       <c r="E882" t="s">
         <v>1205</v>
@@ -22007,10 +22007,10 @@
         <v>7</v>
       </c>
       <c r="C883" t="s">
+        <v>1249</v>
+      </c>
+      <c r="D883" t="s">
         <v>1253</v>
-      </c>
-      <c r="D883" t="s">
-        <v>1250</v>
       </c>
       <c r="E883" t="s">
         <v>15</v>
@@ -22027,10 +22027,10 @@
         <v>7</v>
       </c>
       <c r="C884" t="s">
+        <v>1249</v>
+      </c>
+      <c r="D884" t="s">
         <v>1253</v>
-      </c>
-      <c r="D884" t="s">
-        <v>1250</v>
       </c>
       <c r="E884" t="s">
         <v>15</v>
@@ -22047,10 +22047,10 @@
         <v>7</v>
       </c>
       <c r="C885" t="s">
+        <v>1249</v>
+      </c>
+      <c r="D885" t="s">
         <v>1253</v>
-      </c>
-      <c r="D885" t="s">
-        <v>1250</v>
       </c>
       <c r="E885" t="s">
         <v>15</v>
@@ -22067,10 +22067,10 @@
         <v>7</v>
       </c>
       <c r="C886" t="s">
+        <v>1249</v>
+      </c>
+      <c r="D886" t="s">
         <v>1253</v>
-      </c>
-      <c r="D886" t="s">
-        <v>1250</v>
       </c>
       <c r="E886" t="s">
         <v>1205</v>
@@ -22087,10 +22087,10 @@
         <v>7</v>
       </c>
       <c r="C887" t="s">
+        <v>1249</v>
+      </c>
+      <c r="D887" t="s">
         <v>1253</v>
-      </c>
-      <c r="D887" t="s">
-        <v>1250</v>
       </c>
       <c r="E887" t="s">
         <v>1205</v>
@@ -22107,10 +22107,10 @@
         <v>7</v>
       </c>
       <c r="C888" t="s">
+        <v>1249</v>
+      </c>
+      <c r="D888" t="s">
         <v>1253</v>
-      </c>
-      <c r="D888" t="s">
-        <v>1250</v>
       </c>
       <c r="E888" t="s">
         <v>15</v>
@@ -22127,10 +22127,10 @@
         <v>7</v>
       </c>
       <c r="C889" t="s">
+        <v>1249</v>
+      </c>
+      <c r="D889" t="s">
         <v>1253</v>
-      </c>
-      <c r="D889" t="s">
-        <v>1250</v>
       </c>
       <c r="E889" t="s">
         <v>1205</v>
@@ -22147,10 +22147,10 @@
         <v>7</v>
       </c>
       <c r="C890" t="s">
+        <v>1249</v>
+      </c>
+      <c r="D890" t="s">
         <v>1253</v>
-      </c>
-      <c r="D890" t="s">
-        <v>1250</v>
       </c>
       <c r="E890" t="s">
         <v>1205</v>
@@ -22167,10 +22167,10 @@
         <v>112</v>
       </c>
       <c r="C891" t="s">
+        <v>1249</v>
+      </c>
+      <c r="D891" t="s">
         <v>1253</v>
-      </c>
-      <c r="D891" t="s">
-        <v>1250</v>
       </c>
       <c r="E891" t="s">
         <v>720</v>
@@ -22187,10 +22187,10 @@
         <v>7</v>
       </c>
       <c r="C892" t="s">
+        <v>1249</v>
+      </c>
+      <c r="D892" t="s">
         <v>1253</v>
-      </c>
-      <c r="D892" t="s">
-        <v>1250</v>
       </c>
       <c r="E892" t="s">
         <v>1205</v>
@@ -22207,10 +22207,10 @@
         <v>7</v>
       </c>
       <c r="C893" t="s">
+        <v>1249</v>
+      </c>
+      <c r="D893" t="s">
         <v>1253</v>
-      </c>
-      <c r="D893" t="s">
-        <v>1250</v>
       </c>
       <c r="E893" t="s">
         <v>1205</v>
@@ -22227,10 +22227,10 @@
         <v>7</v>
       </c>
       <c r="C894" t="s">
+        <v>1249</v>
+      </c>
+      <c r="D894" t="s">
         <v>1253</v>
-      </c>
-      <c r="D894" t="s">
-        <v>1250</v>
       </c>
       <c r="E894" t="s">
         <v>1205</v>
@@ -22247,10 +22247,10 @@
         <v>112</v>
       </c>
       <c r="C895" t="s">
+        <v>1249</v>
+      </c>
+      <c r="D895" t="s">
         <v>1253</v>
-      </c>
-      <c r="D895" t="s">
-        <v>1250</v>
       </c>
       <c r="E895" t="s">
         <v>720</v>
@@ -22847,10 +22847,10 @@
         <v>7</v>
       </c>
       <c r="C925" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D925" t="s">
         <v>1321</v>
-      </c>
-      <c r="D925" t="s">
-        <v>1314</v>
       </c>
       <c r="E925" t="s">
         <v>1205</v>
@@ -22867,10 +22867,10 @@
         <v>112</v>
       </c>
       <c r="C926" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D926" t="s">
         <v>1321</v>
-      </c>
-      <c r="D926" t="s">
-        <v>1314</v>
       </c>
       <c r="E926" t="s">
         <v>720</v>
@@ -23047,10 +23047,10 @@
         <v>7</v>
       </c>
       <c r="C935" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D935" t="s">
         <v>1332</v>
-      </c>
-      <c r="D935" t="s">
-        <v>1314</v>
       </c>
       <c r="E935" t="s">
         <v>1205</v>
@@ -23087,10 +23087,10 @@
         <v>7</v>
       </c>
       <c r="C937" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D937" t="s">
         <v>1335</v>
-      </c>
-      <c r="D937" t="s">
-        <v>1314</v>
       </c>
       <c r="E937" t="s">
         <v>1205</v>
@@ -23107,10 +23107,10 @@
         <v>7</v>
       </c>
       <c r="C938" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D938" t="s">
         <v>1332</v>
-      </c>
-      <c r="D938" t="s">
-        <v>1314</v>
       </c>
       <c r="E938" t="s">
         <v>1205</v>
